--- a/Financial Analysis/RHM.xlsx
+++ b/Financial Analysis/RHM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D91EC34-FB68-4886-9B65-327FF9DCC40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53DF77D-AF69-4553-80AE-F91A8C70426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="108">
   <si>
     <t>RHM</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>FCF</t>
+  </si>
+  <si>
+    <t>CapEx y/y</t>
   </si>
 </sst>
 </file>
@@ -408,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -430,6 +433,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,16 +460,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -475,8 +484,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12534900" y="0"/>
-          <a:ext cx="0" cy="11605260"/>
+          <a:off x="13754100" y="0"/>
+          <a:ext cx="0" cy="15834360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -873,21 +882,23 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.21875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E2" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="F2" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H2" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,75 +906,84 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>1417</v>
+        <v>1744.5</v>
+      </c>
+      <c r="E3" s="11">
+        <v>45906</v>
       </c>
       <c r="F3" s="11">
-        <v>45734</v>
+        <f ca="1">TODAY()</f>
+        <v>45906</v>
       </c>
       <c r="G3" s="11">
-        <f ca="1">TODAY()</f>
-        <v>45736</v>
-      </c>
-      <c r="H3" s="11">
-        <v>45455</v>
+        <v>45967</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>43.43</f>
-        <v>43.43</v>
+        <v>43.84</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>61540.31</v>
+        <v>76478.880000000005</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>1184+346</f>
-        <v>1530</v>
+        <f>1083+328</f>
+        <v>1411</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>552+1871</f>
-        <v>2423</v>
+        <f>193+1511</f>
+        <v>1704</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-893</v>
+        <v>-293</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>62433.31</v>
+        <v>76771.88</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1107,20 +1127,40 @@
       <c r="J3" s="3">
         <v>3521</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="K3" s="3">
+        <v>1230</v>
+      </c>
+      <c r="L3" s="3">
+        <f>1775-K3</f>
+        <v>545</v>
+      </c>
+      <c r="M3" s="3">
+        <v>592</v>
+      </c>
       <c r="N3" s="3">
         <v>3480</v>
       </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+      <c r="O3" s="3">
+        <v>620</v>
+      </c>
+      <c r="P3" s="3">
+        <f>1357-O3</f>
+        <v>737</v>
+      </c>
+      <c r="Q3" s="3">
+        <f>2119-P3-O3</f>
+        <v>762</v>
+      </c>
       <c r="R3" s="3">
-        <v>2508</v>
-      </c>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+        <f>2508-Q3-P3-O3</f>
+        <v>389</v>
+      </c>
+      <c r="S3" s="3">
+        <v>325</v>
+      </c>
+      <c r="T3" s="3">
+        <v>664</v>
+      </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
       <c r="Z3" s="3"/>
@@ -1160,20 +1200,40 @@
       <c r="J4" s="3">
         <v>350</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="K4" s="3">
+        <v>370</v>
+      </c>
+      <c r="L4" s="3">
+        <f>1163-K4</f>
+        <v>793</v>
+      </c>
+      <c r="M4" s="3">
+        <v>5877</v>
+      </c>
       <c r="N4" s="3">
         <v>7362</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
+        <f>7478-O4</f>
+        <v>7478</v>
+      </c>
+      <c r="Q4" s="3">
+        <f>10858-P4-O4</f>
+        <v>3380</v>
+      </c>
       <c r="R4" s="3">
-        <v>11518</v>
-      </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+        <f>11518-Q4-P4-O4</f>
+        <v>660</v>
+      </c>
+      <c r="S4" s="3">
+        <v>9348</v>
+      </c>
+      <c r="T4" s="3">
+        <v>433</v>
+      </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="Z4" s="3"/>
@@ -1213,20 +1273,40 @@
       <c r="J5" s="3">
         <v>0</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <f>-638-K5</f>
+        <v>-638</v>
+      </c>
+      <c r="M5" s="3">
+        <v>-1726</v>
+      </c>
       <c r="N5" s="3">
         <v>-2804</v>
       </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
+      <c r="O5" s="3">
+        <v>-444</v>
+      </c>
+      <c r="P5" s="3">
+        <f>-2369-O5</f>
+        <v>-1925</v>
+      </c>
+      <c r="Q5" s="3">
+        <f>-2824-P5-O5</f>
+        <v>-455</v>
+      </c>
       <c r="R5" s="3">
-        <v>-3738</v>
-      </c>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+        <f>-3738-Q5-P5-O5</f>
+        <v>-914</v>
+      </c>
+      <c r="S5" s="3">
+        <v>-1995</v>
+      </c>
+      <c r="T5" s="3">
+        <v>-256</v>
+      </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="Z5" s="3"/>
@@ -1266,20 +1346,39 @@
       <c r="J6" s="3">
         <v>5629</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="K6" s="3">
+        <v>1504</v>
+      </c>
+      <c r="L6" s="3">
+        <v>3392</v>
+      </c>
+      <c r="M6" s="3">
+        <v>2570</v>
+      </c>
       <c r="N6" s="3">
         <v>11843</v>
       </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="O6" s="3">
+        <v>3757</v>
+      </c>
+      <c r="P6" s="3">
+        <f>8910-O6</f>
+        <v>5153</v>
+      </c>
+      <c r="Q6" s="3">
+        <f>11275-P6-O6</f>
+        <v>2365</v>
+      </c>
       <c r="R6" s="3">
-        <v>16554</v>
-      </c>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+        <f>16554-Q6-P6-O6</f>
+        <v>5279</v>
+      </c>
+      <c r="S6" s="3">
+        <v>3361</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1798</v>
+      </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="Z6" s="3"/>
@@ -1317,25 +1416,49 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="3">
-        <f>SUM(J3:J6)</f>
+        <f t="shared" ref="J7:S7" si="0">SUM(J3:J6)</f>
         <v>9500</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
+      <c r="K7" s="3">
+        <f t="shared" si="0"/>
+        <v>3104</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" si="0"/>
+        <v>4092</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="0"/>
+        <v>7313</v>
+      </c>
       <c r="N7" s="3">
-        <f>SUM(N3:N6)</f>
+        <f t="shared" si="0"/>
         <v>19881</v>
       </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="O7" s="3">
+        <f t="shared" si="0"/>
+        <v>3933</v>
+      </c>
+      <c r="P7" s="3">
+        <f t="shared" si="0"/>
+        <v>11443</v>
+      </c>
+      <c r="Q7" s="3">
+        <f t="shared" si="0"/>
+        <v>6052</v>
+      </c>
       <c r="R7" s="3">
-        <f>SUM(R3:R6)</f>
-        <v>26842</v>
-      </c>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
+        <f t="shared" si="0"/>
+        <v>5414</v>
+      </c>
+      <c r="S7" s="3">
+        <f t="shared" si="0"/>
+        <v>11039</v>
+      </c>
+      <c r="T7" s="3">
+        <f t="shared" ref="T7" si="1">SUM(T3:T6)</f>
+        <v>2639</v>
+      </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="Z7" s="3"/>
@@ -1378,20 +1501,36 @@
       <c r="J8" s="3">
         <v>8056</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="K8" s="3">
+        <v>8741</v>
+      </c>
+      <c r="L8" s="3">
+        <v>8806</v>
+      </c>
+      <c r="M8" s="3">
+        <v>8875</v>
+      </c>
       <c r="N8" s="3">
         <v>8381</v>
       </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="O8" s="3">
+        <v>8461</v>
+      </c>
+      <c r="P8" s="3">
+        <v>7938</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>8060</v>
+      </c>
       <c r="R8" s="3">
         <v>7712</v>
       </c>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="S8" s="3">
+        <v>6994</v>
+      </c>
+      <c r="T8" s="3">
+        <v>7192</v>
+      </c>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="Z8" s="3"/>
@@ -1431,20 +1570,36 @@
       <c r="J9" s="3">
         <v>3427</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="K9" s="3">
+        <v>3750</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3255</v>
+      </c>
+      <c r="M9" s="3">
+        <v>8118</v>
+      </c>
       <c r="N9" s="3">
         <v>7931</v>
       </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="O9" s="3">
+        <v>7596</v>
+      </c>
+      <c r="P9" s="3">
+        <v>13041</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>15896</v>
+      </c>
       <c r="R9" s="3">
         <v>16533</v>
       </c>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="S9" s="3">
+        <v>22987</v>
+      </c>
+      <c r="T9" s="3">
+        <v>23707</v>
+      </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="Z9" s="3"/>
@@ -1484,20 +1639,36 @@
       <c r="J10" s="3">
         <v>15089</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
+      <c r="K10" s="3">
+        <v>15703</v>
+      </c>
+      <c r="L10" s="3">
+        <v>17989</v>
+      </c>
+      <c r="M10" s="3">
+        <v>19751</v>
+      </c>
       <c r="N10" s="3">
         <v>21977</v>
       </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="O10" s="3">
+        <v>24140</v>
+      </c>
+      <c r="P10" s="3">
+        <v>27661</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>27950</v>
+      </c>
       <c r="R10" s="3">
         <v>30728</v>
       </c>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
+      <c r="S10" s="3">
+        <v>32579</v>
+      </c>
+      <c r="T10" s="3">
+        <v>32266</v>
+      </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="Z10" s="3"/>
@@ -1523,73 +1694,86 @@
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
     </row>
-    <row r="11" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+    <row r="11" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14">
         <v>26572</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="14">
+        <f>SUM(K8:K10)</f>
         <v>28194</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="14">
+        <f>SUM(L8:L10)</f>
         <v>30050</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="14">
+        <f>SUM(M8:M10)</f>
         <v>36744</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="14">
         <v>38290</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="14">
+        <f t="shared" ref="O11:T11" si="2">SUM(O8:O10)</f>
         <v>40197</v>
       </c>
-      <c r="P11" s="9">
-        <v>48460</v>
-      </c>
-      <c r="Q11" s="9">
+      <c r="P11" s="14">
+        <f t="shared" si="2"/>
+        <v>48640</v>
+      </c>
+      <c r="Q11" s="14">
+        <f t="shared" si="2"/>
         <v>51906</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="14">
+        <f t="shared" si="2"/>
         <v>54973</v>
       </c>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3">
+      <c r="S11" s="14">
+        <f t="shared" si="2"/>
+        <v>62560</v>
+      </c>
+      <c r="T11" s="14">
+        <f t="shared" si="2"/>
+        <v>63165</v>
+      </c>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6">
         <f>SUM(AB8:AB10)</f>
         <v>26572</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC11" s="6">
         <f>SUM(AC8:AC10)</f>
         <v>38289</v>
       </c>
-      <c r="AD11" s="3">
+      <c r="AD11" s="6">
         <f>SUM(AD8:AD10)</f>
         <v>54973</v>
       </c>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="6"/>
+      <c r="AJ11" s="6"/>
+      <c r="AK11" s="6"/>
+      <c r="AL11" s="6"/>
+      <c r="AM11" s="6"/>
+      <c r="AN11" s="6"/>
+      <c r="AO11" s="6"/>
     </row>
     <row r="12" spans="2:41" x14ac:dyDescent="0.3">
       <c r="C12" s="4"/>
@@ -1679,19 +1863,17 @@
         <v>1241</v>
       </c>
       <c r="S13" s="9">
-        <f>O13*1.35</f>
-        <v>660.15000000000009</v>
+        <v>945</v>
       </c>
       <c r="T13" s="9">
-        <f>P13*1.5</f>
-        <v>1207.5</v>
+        <v>930</v>
       </c>
       <c r="U13" s="9">
-        <f>Q13*1.3</f>
-        <v>1604.2</v>
+        <f>Q13*1.2</f>
+        <v>1480.8</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" ref="V13" si="0">R13*1.35</f>
+        <f t="shared" ref="V13" si="3">R13*1.35</f>
         <v>1675.3500000000001</v>
       </c>
       <c r="Z13" s="3">
@@ -1711,47 +1893,47 @@
       </c>
       <c r="AE13" s="3">
         <f>SUM(S13:V13)</f>
-        <v>5147.2000000000007</v>
+        <v>5031.1500000000005</v>
       </c>
       <c r="AF13" s="3">
-        <f>AE13*1.15</f>
-        <v>5919.2800000000007</v>
+        <f>AE13*1.22</f>
+        <v>6138.0030000000006</v>
       </c>
       <c r="AG13" s="3">
         <f>AF13*1.08</f>
-        <v>6392.8224000000009</v>
+        <v>6629.0432400000009</v>
       </c>
       <c r="AH13" s="3">
         <f>AG13*1.05</f>
-        <v>6712.4635200000012</v>
+        <v>6960.4954020000014</v>
       </c>
       <c r="AI13" s="3">
         <f>AH13*1.03</f>
-        <v>6913.8374256000016</v>
+        <v>7169.3102640600018</v>
       </c>
       <c r="AJ13" s="3">
-        <f t="shared" ref="AJ13:AO13" si="1">AI13*1.02</f>
-        <v>7052.1141741120018</v>
+        <f t="shared" ref="AJ13:AO13" si="4">AI13*1.02</f>
+        <v>7312.6964693412019</v>
       </c>
       <c r="AK13" s="3">
-        <f t="shared" si="1"/>
-        <v>7193.1564575942421</v>
+        <f t="shared" si="4"/>
+        <v>7458.9503987280259</v>
       </c>
       <c r="AL13" s="3">
-        <f t="shared" si="1"/>
-        <v>7337.0195867461271</v>
+        <f t="shared" si="4"/>
+        <v>7608.1294067025865</v>
       </c>
       <c r="AM13" s="3">
-        <f t="shared" si="1"/>
-        <v>7483.75997848105</v>
+        <f t="shared" si="4"/>
+        <v>7760.291994836638</v>
       </c>
       <c r="AN13" s="3">
-        <f t="shared" si="1"/>
-        <v>7633.4351780506713</v>
+        <f t="shared" si="4"/>
+        <v>7915.4978347333708</v>
       </c>
       <c r="AO13" s="3">
-        <f t="shared" si="1"/>
-        <v>7786.1038816116852</v>
+        <f t="shared" si="4"/>
+        <v>8073.8077914280384</v>
       </c>
     </row>
     <row r="14" spans="2:41" x14ac:dyDescent="0.3">
@@ -1804,16 +1986,14 @@
         <v>1132</v>
       </c>
       <c r="S14" s="9">
-        <f>O14*1.6</f>
-        <v>513.6</v>
+        <v>530</v>
       </c>
       <c r="T14" s="9">
-        <f>P14*1.05</f>
-        <v>666.75</v>
+        <v>661</v>
       </c>
       <c r="U14" s="9">
-        <f>Q14*1.7</f>
-        <v>759.9</v>
+        <f>Q14*1.8</f>
+        <v>804.6</v>
       </c>
       <c r="V14" s="9">
         <f>R14*1.2</f>
@@ -1836,47 +2016,47 @@
       </c>
       <c r="AE14" s="3">
         <f>SUM(S14:V14)</f>
-        <v>3298.6499999999996</v>
+        <v>3354</v>
       </c>
       <c r="AF14" s="3">
         <f>AE14*1.2</f>
-        <v>3958.3799999999992</v>
+        <v>4024.7999999999997</v>
       </c>
       <c r="AG14" s="3">
         <f>AF14*1.1</f>
-        <v>4354.2179999999998</v>
+        <v>4427.28</v>
       </c>
       <c r="AH14" s="3">
         <f>AG14*1.05</f>
-        <v>4571.9288999999999</v>
+        <v>4648.6440000000002</v>
       </c>
       <c r="AI14" s="3">
         <f>AH14*1.03</f>
-        <v>4709.0867669999998</v>
+        <v>4788.1033200000002</v>
       </c>
       <c r="AJ14" s="3">
         <f>AI14*1.02</f>
-        <v>4803.2685023399999</v>
+        <v>4883.8653863999998</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" ref="AK14:AO14" si="2">AJ14*1.02</f>
-        <v>4899.3338723868001</v>
+        <f t="shared" ref="AK14:AO14" si="5">AJ14*1.02</f>
+        <v>4981.5426941280002</v>
       </c>
       <c r="AL14" s="3">
-        <f t="shared" si="2"/>
-        <v>4997.320549834536</v>
+        <f t="shared" si="5"/>
+        <v>5081.1735480105599</v>
       </c>
       <c r="AM14" s="3">
-        <f t="shared" si="2"/>
-        <v>5097.2669608312272</v>
+        <f t="shared" si="5"/>
+        <v>5182.7970189707712</v>
       </c>
       <c r="AN14" s="3">
-        <f t="shared" si="2"/>
-        <v>5199.2123000478514</v>
+        <f t="shared" si="5"/>
+        <v>5286.4529593501866</v>
       </c>
       <c r="AO14" s="3">
-        <f t="shared" si="2"/>
-        <v>5303.1965460488082</v>
+        <f t="shared" si="5"/>
+        <v>5392.1820185371907</v>
       </c>
     </row>
     <row r="15" spans="2:41" x14ac:dyDescent="0.3">
@@ -1929,20 +2109,18 @@
         <v>533</v>
       </c>
       <c r="S15" s="9">
-        <f>O15*1.35</f>
-        <v>306.45000000000005</v>
+        <v>335</v>
       </c>
       <c r="T15" s="9">
-        <f>P15*1.3</f>
-        <v>353.6</v>
+        <v>403</v>
       </c>
       <c r="U15" s="9">
-        <f>Q15*1.3</f>
-        <v>369.2</v>
+        <f>Q15*1.4</f>
+        <v>397.59999999999997</v>
       </c>
       <c r="V15" s="9">
-        <f>R15*1.2</f>
-        <v>639.6</v>
+        <f>R15*1.33</f>
+        <v>708.89</v>
       </c>
       <c r="Z15" s="3">
         <v>776</v>
@@ -1961,47 +2139,47 @@
       </c>
       <c r="AE15" s="3">
         <f>SUM(S15:V15)</f>
-        <v>1668.85</v>
+        <v>1844.4899999999998</v>
       </c>
       <c r="AF15" s="3">
-        <f>AE15*1.15</f>
-        <v>1919.1774999999998</v>
+        <f>AE15*1.22</f>
+        <v>2250.2777999999998</v>
       </c>
       <c r="AG15" s="3">
-        <f>AF15*1.08</f>
-        <v>2072.7116999999998</v>
+        <f>AF15*1.15</f>
+        <v>2587.8194699999995</v>
       </c>
       <c r="AH15" s="3">
-        <f>AG15*1.05</f>
-        <v>2176.3472849999998</v>
+        <f>AG15*1.08</f>
+        <v>2794.8450275999994</v>
       </c>
       <c r="AI15" s="3">
-        <f>AH15*1.04</f>
-        <v>2263.4011763999997</v>
+        <f>AH15*1.05</f>
+        <v>2934.5872789799996</v>
       </c>
       <c r="AJ15" s="3">
-        <f>AI15*1.03</f>
-        <v>2331.3032116919999</v>
+        <f>AI15*1.04</f>
+        <v>3051.9707701391999</v>
       </c>
       <c r="AK15" s="3">
-        <f t="shared" ref="AK15:AO15" si="3">AJ15*1.03</f>
-        <v>2401.2423080427598</v>
+        <f>AJ15*1.03</f>
+        <v>3143.5298932433761</v>
       </c>
       <c r="AL15" s="3">
-        <f t="shared" si="3"/>
-        <v>2473.2795772840427</v>
+        <f t="shared" ref="AL15:AO15" si="6">AK15*1.03</f>
+        <v>3237.8357900406777</v>
       </c>
       <c r="AM15" s="3">
-        <f t="shared" si="3"/>
-        <v>2547.477964602564</v>
+        <f t="shared" si="6"/>
+        <v>3334.970863741898</v>
       </c>
       <c r="AN15" s="3">
-        <f t="shared" si="3"/>
-        <v>2623.9023035406412</v>
+        <f t="shared" si="6"/>
+        <v>3435.0199896541549</v>
       </c>
       <c r="AO15" s="3">
-        <f t="shared" si="3"/>
-        <v>2702.6193726468605</v>
+        <f t="shared" si="6"/>
+        <v>3538.0705893437798</v>
       </c>
     </row>
     <row r="16" spans="2:41" x14ac:dyDescent="0.3">
@@ -2060,12 +2238,10 @@
         <v>495</v>
       </c>
       <c r="S16" s="9">
-        <f>O16*0.93</f>
-        <v>502.20000000000005</v>
+        <v>504</v>
       </c>
       <c r="T16" s="9">
-        <f>P16*0.93</f>
-        <v>477.09000000000003</v>
+        <v>480</v>
       </c>
       <c r="U16" s="9">
         <f>Q16*0.95</f>
@@ -2096,47 +2272,47 @@
       </c>
       <c r="AE16" s="3">
         <f>SUM(S16:V16)</f>
-        <v>1924.19</v>
+        <v>1928.8999999999999</v>
       </c>
       <c r="AF16" s="3">
-        <f t="shared" ref="AF16:AO16" si="4">AE16*1.01</f>
-        <v>1943.4319</v>
+        <f t="shared" ref="AF16:AO16" si="7">AE16*1.01</f>
+        <v>1948.1889999999999</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" si="4"/>
-        <v>1962.866219</v>
+        <f t="shared" si="7"/>
+        <v>1967.6708899999999</v>
       </c>
       <c r="AH16" s="3">
-        <f t="shared" si="4"/>
-        <v>1982.4948811900001</v>
+        <f t="shared" si="7"/>
+        <v>1987.3475988999999</v>
       </c>
       <c r="AI16" s="3">
-        <f t="shared" si="4"/>
-        <v>2002.3198300019001</v>
+        <f t="shared" si="7"/>
+        <v>2007.221074889</v>
       </c>
       <c r="AJ16" s="3">
-        <f t="shared" si="4"/>
-        <v>2022.343028301919</v>
+        <f t="shared" si="7"/>
+        <v>2027.29328563789</v>
       </c>
       <c r="AK16" s="3">
-        <f t="shared" si="4"/>
-        <v>2042.5664585849383</v>
+        <f t="shared" si="7"/>
+        <v>2047.5662184942689</v>
       </c>
       <c r="AL16" s="3">
-        <f t="shared" si="4"/>
-        <v>2062.9921231707876</v>
+        <f t="shared" si="7"/>
+        <v>2068.0418806792118</v>
       </c>
       <c r="AM16" s="3">
-        <f t="shared" si="4"/>
-        <v>2083.6220444024957</v>
+        <f t="shared" si="7"/>
+        <v>2088.722299486004</v>
       </c>
       <c r="AN16" s="3">
-        <f t="shared" si="4"/>
-        <v>2104.4582648465207</v>
+        <f t="shared" si="7"/>
+        <v>2109.6095224808641</v>
       </c>
       <c r="AO16" s="3">
-        <f t="shared" si="4"/>
-        <v>2125.5028474949859</v>
+        <f t="shared" si="7"/>
+        <v>2130.7056177056729</v>
       </c>
     </row>
     <row r="17" spans="2:41" x14ac:dyDescent="0.3">
@@ -2189,15 +2365,13 @@
         <v>80</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" ref="S17" si="5">O17*1.35</f>
-        <v>6.75</v>
+        <v>-9</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" ref="T17" si="6">P17*1.35</f>
-        <v>13.5</v>
+        <v>-43</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="7">Q17*1.35</f>
+        <f t="shared" ref="U17" si="8">Q17*1.35</f>
         <v>5.4</v>
       </c>
       <c r="V17" s="9">
@@ -2221,47 +2395,47 @@
       </c>
       <c r="AE17" s="3">
         <f>SUM(S17:V17)</f>
-        <v>145.65</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="AF17" s="3">
         <f>AE17*1.4</f>
-        <v>203.91</v>
+        <v>102.76</v>
       </c>
       <c r="AG17" s="3">
-        <f t="shared" ref="AG17" si="8">AF17*1.3</f>
-        <v>265.08300000000003</v>
+        <f t="shared" ref="AG17" si="9">AF17*1.3</f>
+        <v>133.58800000000002</v>
       </c>
       <c r="AH17" s="3">
         <f>AG17*1.2</f>
-        <v>318.09960000000001</v>
+        <v>160.30560000000003</v>
       </c>
       <c r="AI17" s="3">
         <f>AH17*1.1</f>
-        <v>349.90956000000006</v>
+        <v>176.33616000000004</v>
       </c>
       <c r="AJ17" s="3">
         <f>AI17*1.05</f>
-        <v>367.40503800000005</v>
+        <v>185.15296800000004</v>
       </c>
       <c r="AK17" s="3">
-        <f t="shared" ref="AK17:AO17" si="9">AJ17*1.05</f>
-        <v>385.77528990000008</v>
+        <f t="shared" ref="AK17:AO17" si="10">AJ17*1.05</f>
+        <v>194.41061640000007</v>
       </c>
       <c r="AL17" s="3">
-        <f t="shared" si="9"/>
-        <v>405.06405439500008</v>
+        <f t="shared" si="10"/>
+        <v>204.13114722000009</v>
       </c>
       <c r="AM17" s="3">
-        <f t="shared" si="9"/>
-        <v>425.31725711475013</v>
+        <f t="shared" si="10"/>
+        <v>214.33770458100011</v>
       </c>
       <c r="AN17" s="3">
-        <f t="shared" si="9"/>
-        <v>446.58311997048764</v>
+        <f t="shared" si="10"/>
+        <v>225.05458981005012</v>
       </c>
       <c r="AO17" s="3">
-        <f t="shared" si="9"/>
-        <v>468.91227596901206</v>
+        <f t="shared" si="10"/>
+        <v>236.30731930055262</v>
       </c>
     </row>
     <row r="18" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2317,87 +2491,87 @@
         <v>2453</v>
       </c>
       <c r="R18" s="6">
-        <f t="shared" ref="R18:V18" si="10">SUM(R13:R17)</f>
+        <f t="shared" ref="R18:V18" si="11">SUM(R13:R17)</f>
         <v>3481</v>
       </c>
       <c r="S18" s="6">
-        <f t="shared" si="10"/>
-        <v>1989.15</v>
+        <f t="shared" si="11"/>
+        <v>2305</v>
       </c>
       <c r="T18" s="6">
-        <f t="shared" si="10"/>
-        <v>2718.44</v>
+        <f t="shared" si="11"/>
+        <v>2431</v>
       </c>
       <c r="U18" s="6">
-        <f t="shared" si="10"/>
-        <v>3198.4999999999995</v>
+        <f t="shared" si="11"/>
+        <v>3148.2000000000003</v>
       </c>
       <c r="V18" s="6">
-        <f t="shared" si="10"/>
-        <v>4278.45</v>
+        <f t="shared" si="11"/>
+        <v>4347.74</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" ref="Z18:AE18" si="11">SUM(Z13:Z17)</f>
+        <f t="shared" ref="Z18:AE18" si="12">SUM(Z13:Z17)</f>
         <v>5405</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5659</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6410</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7175</v>
       </c>
       <c r="AD18" s="6">
         <v>9751</v>
       </c>
       <c r="AE18" s="6">
-        <f t="shared" si="11"/>
-        <v>12184.54</v>
+        <f t="shared" si="12"/>
+        <v>12231.94</v>
       </c>
       <c r="AF18" s="6">
-        <f t="shared" ref="AF18:AO18" si="12">SUM(AF13:AF17)</f>
-        <v>13944.179399999999</v>
+        <f t="shared" ref="AF18:AO18" si="13">SUM(AF13:AF17)</f>
+        <v>14464.0298</v>
       </c>
       <c r="AG18" s="6">
-        <f t="shared" si="12"/>
-        <v>15047.701319000002</v>
+        <f t="shared" si="13"/>
+        <v>15745.401599999999</v>
       </c>
       <c r="AH18" s="6">
-        <f t="shared" si="12"/>
-        <v>15761.334186189999</v>
+        <f t="shared" si="13"/>
+        <v>16551.637628500001</v>
       </c>
       <c r="AI18" s="6">
-        <f t="shared" si="12"/>
-        <v>16238.554759001901</v>
+        <f t="shared" si="13"/>
+        <v>17075.558097929003</v>
       </c>
       <c r="AJ18" s="6">
-        <f t="shared" si="12"/>
-        <v>16576.433954445922</v>
+        <f t="shared" si="13"/>
+        <v>17460.97887951829</v>
       </c>
       <c r="AK18" s="6">
-        <f t="shared" si="12"/>
-        <v>16922.074386508742</v>
+        <f t="shared" si="13"/>
+        <v>17825.999820993671</v>
       </c>
       <c r="AL18" s="6">
-        <f t="shared" si="12"/>
-        <v>17275.675891430496</v>
+        <f t="shared" si="13"/>
+        <v>18199.311772653036</v>
       </c>
       <c r="AM18" s="6">
-        <f t="shared" si="12"/>
-        <v>17637.444205432086</v>
+        <f t="shared" si="13"/>
+        <v>18581.119881616312</v>
       </c>
       <c r="AN18" s="6">
-        <f t="shared" si="12"/>
-        <v>18007.591166456172</v>
+        <f t="shared" si="13"/>
+        <v>18971.634896028627</v>
       </c>
       <c r="AO18" s="6">
-        <f t="shared" si="12"/>
-        <v>18386.334923771352</v>
+        <f t="shared" si="13"/>
+        <v>19371.073336315232</v>
       </c>
     </row>
     <row r="19" spans="2:41" x14ac:dyDescent="0.3">
@@ -2450,10 +2624,10 @@
         <v>136</v>
       </c>
       <c r="S19" s="3">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="T19" s="3">
-        <v>0</v>
+        <v>-353</v>
       </c>
       <c r="U19" s="3">
         <v>0</v>
@@ -2478,43 +2652,43 @@
       </c>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3">
-        <f t="shared" ref="AF19:AO19" si="13">AE19*0.97</f>
+        <f t="shared" ref="AF19:AO19" si="14">AE19*0.97</f>
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AH19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AI19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AK19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AL19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AM19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AN19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AO19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -2567,8 +2741,12 @@
         <f>AD20-Q20-P20-O20</f>
         <v>1563</v>
       </c>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
+      <c r="S20" s="3">
+        <v>1314</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1485</v>
+      </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="Z20" s="3">
@@ -2589,43 +2767,43 @@
       <c r="AE20" s="3"/>
       <c r="AF20" s="3">
         <f>AF18*0.5</f>
-        <v>6972.0896999999995</v>
+        <v>7232.0149000000001</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" ref="AG20:AO20" si="14">AG18*0.5</f>
-        <v>7523.8506595000008</v>
+        <f t="shared" ref="AG20:AO20" si="15">AG18*0.5</f>
+        <v>7872.7007999999996</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="14"/>
-        <v>7880.6670930949995</v>
+        <f t="shared" si="15"/>
+        <v>8275.8188142500003</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="14"/>
-        <v>8119.2773795009507</v>
+        <f t="shared" si="15"/>
+        <v>8537.7790489645013</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="14"/>
-        <v>8288.2169772229608</v>
+        <f t="shared" si="15"/>
+        <v>8730.4894397591452</v>
       </c>
       <c r="AK20" s="3">
-        <f t="shared" si="14"/>
-        <v>8461.0371932543712</v>
+        <f t="shared" si="15"/>
+        <v>8912.9999104968356</v>
       </c>
       <c r="AL20" s="3">
-        <f t="shared" si="14"/>
-        <v>8637.8379457152478</v>
+        <f t="shared" si="15"/>
+        <v>9099.6558863265182</v>
       </c>
       <c r="AM20" s="3">
-        <f t="shared" si="14"/>
-        <v>8818.7221027160431</v>
+        <f t="shared" si="15"/>
+        <v>9290.5599408081562</v>
       </c>
       <c r="AN20" s="3">
-        <f t="shared" si="14"/>
-        <v>9003.7955832280859</v>
+        <f t="shared" si="15"/>
+        <v>9485.8174480143134</v>
       </c>
       <c r="AO20" s="3">
-        <f t="shared" si="14"/>
-        <v>9193.1674618856759</v>
+        <f t="shared" si="15"/>
+        <v>9685.5366681576161</v>
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
@@ -2677,8 +2855,12 @@
         <f>AD21-Q21-P21-O21</f>
         <v>642</v>
       </c>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
+      <c r="S21" s="3">
+        <v>696</v>
+      </c>
+      <c r="T21" s="3">
+        <v>704</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="Z21" s="3">
@@ -2699,43 +2881,43 @@
       <c r="AE21" s="3"/>
       <c r="AF21" s="3">
         <f>AF18*0.25</f>
-        <v>3486.0448499999998</v>
+        <v>3616.0074500000001</v>
       </c>
       <c r="AG21" s="3">
-        <f t="shared" ref="AG21:AO21" si="15">AG18*0.25</f>
-        <v>3761.9253297500004</v>
+        <f t="shared" ref="AG21:AO21" si="16">AG18*0.25</f>
+        <v>3936.3503999999998</v>
       </c>
       <c r="AH21" s="3">
-        <f t="shared" si="15"/>
-        <v>3940.3335465474997</v>
+        <f t="shared" si="16"/>
+        <v>4137.9094071250001</v>
       </c>
       <c r="AI21" s="3">
-        <f t="shared" si="15"/>
-        <v>4059.6386897504754</v>
+        <f t="shared" si="16"/>
+        <v>4268.8895244822506</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" si="15"/>
-        <v>4144.1084886114804</v>
+        <f t="shared" si="16"/>
+        <v>4365.2447198795726</v>
       </c>
       <c r="AK21" s="3">
-        <f t="shared" si="15"/>
-        <v>4230.5185966271856</v>
+        <f t="shared" si="16"/>
+        <v>4456.4999552484178</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="15"/>
-        <v>4318.9189728576239</v>
+        <f t="shared" si="16"/>
+        <v>4549.8279431632591</v>
       </c>
       <c r="AM21" s="3">
-        <f t="shared" si="15"/>
-        <v>4409.3610513580215</v>
+        <f t="shared" si="16"/>
+        <v>4645.2799704040781</v>
       </c>
       <c r="AN21" s="3">
-        <f t="shared" si="15"/>
-        <v>4501.8977916140429</v>
+        <f t="shared" si="16"/>
+        <v>4742.9087240071567</v>
       </c>
       <c r="AO21" s="3">
-        <f t="shared" si="15"/>
-        <v>4596.583730942838</v>
+        <f t="shared" si="16"/>
+        <v>4842.768334078808</v>
       </c>
     </row>
     <row r="22" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2751,68 +2933,68 @@
         <v>1029</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" ref="G22:P22" si="16">SUM(G19:G21)</f>
+        <f t="shared" ref="G22:P22" si="17">SUM(G19:G21)</f>
         <v>999</v>
       </c>
       <c r="H22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1092</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1099</v>
       </c>
       <c r="J22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1676</v>
       </c>
       <c r="K22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1061</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1155</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1329</v>
       </c>
       <c r="N22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1741</v>
       </c>
       <c r="O22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1188</v>
       </c>
       <c r="P22" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1664</v>
       </c>
       <c r="Q22" s="6">
-        <f t="shared" ref="Q22:R22" si="17">SUM(Q19:Q21)</f>
+        <f t="shared" ref="Q22:R22" si="18">SUM(Q19:Q21)</f>
         <v>1872</v>
       </c>
       <c r="R22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2341</v>
       </c>
       <c r="S22" s="6">
-        <f>S18-S23</f>
-        <v>1491.8625000000002</v>
+        <f t="shared" ref="S22:T22" si="19">SUM(S19:S21)</f>
+        <v>1763</v>
       </c>
       <c r="T22" s="6">
-        <f t="shared" ref="T22:V22" si="18">T18-T23</f>
-        <v>2038.83</v>
+        <f t="shared" si="19"/>
+        <v>1836</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" si="18"/>
-        <v>2366.8899999999994</v>
+        <f t="shared" ref="U22:V22" si="20">U18-U23</f>
+        <v>2329.6680000000001</v>
       </c>
       <c r="V22" s="6">
-        <f t="shared" si="18"/>
-        <v>2823.777</v>
+        <f t="shared" si="20"/>
+        <v>2869.5083999999997</v>
       </c>
       <c r="Z22" s="6">
         <f>SUM(Z19:Z21)</f>
@@ -2836,47 +3018,47 @@
       </c>
       <c r="AE22" s="3">
         <f>SUM(S22:V22)</f>
-        <v>8721.3594999999987</v>
+        <v>8798.1764000000003</v>
       </c>
       <c r="AF22" s="6">
-        <f t="shared" ref="AF22:AO22" si="19">SUM(AF19:AF21)</f>
-        <v>10458.134549999999</v>
+        <f t="shared" ref="AF22:AO22" si="21">SUM(AF19:AF21)</f>
+        <v>10848.022349999999</v>
       </c>
       <c r="AG22" s="6">
-        <f t="shared" si="19"/>
-        <v>11285.775989250002</v>
+        <f t="shared" si="21"/>
+        <v>11809.0512</v>
       </c>
       <c r="AH22" s="6">
-        <f t="shared" si="19"/>
-        <v>11821.0006396425</v>
+        <f t="shared" si="21"/>
+        <v>12413.728221375</v>
       </c>
       <c r="AI22" s="6">
-        <f t="shared" si="19"/>
-        <v>12178.916069251427</v>
+        <f t="shared" si="21"/>
+        <v>12806.668573446752</v>
       </c>
       <c r="AJ22" s="6">
-        <f t="shared" si="19"/>
-        <v>12432.325465834441</v>
+        <f t="shared" si="21"/>
+        <v>13095.734159638718</v>
       </c>
       <c r="AK22" s="6">
-        <f t="shared" si="19"/>
-        <v>12691.555789881557</v>
+        <f t="shared" si="21"/>
+        <v>13369.499865745252</v>
       </c>
       <c r="AL22" s="6">
-        <f t="shared" si="19"/>
-        <v>12956.756918572872</v>
+        <f t="shared" si="21"/>
+        <v>13649.483829489778</v>
       </c>
       <c r="AM22" s="6">
-        <f t="shared" si="19"/>
-        <v>13228.083154074066</v>
+        <f t="shared" si="21"/>
+        <v>13935.839911212235</v>
       </c>
       <c r="AN22" s="6">
-        <f t="shared" si="19"/>
-        <v>13505.693374842129</v>
+        <f t="shared" si="21"/>
+        <v>14228.72617202147</v>
       </c>
       <c r="AO22" s="6">
-        <f t="shared" si="19"/>
-        <v>13789.751192828513</v>
+        <f t="shared" si="21"/>
+        <v>14528.305002236424</v>
       </c>
     </row>
     <row r="23" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2892,68 +3074,68 @@
         <v>287</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" ref="G23:P23" si="20">G18-G22</f>
+        <f t="shared" ref="G23:P23" si="22">G18-G22</f>
         <v>267</v>
       </c>
       <c r="H23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>316</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>316</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>645</v>
       </c>
       <c r="K23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>302</v>
       </c>
       <c r="L23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>342</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>429</v>
       </c>
       <c r="N23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>816</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>394</v>
       </c>
       <c r="P23" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>571</v>
       </c>
       <c r="Q23" s="6">
-        <f t="shared" ref="Q23:R23" si="21">Q18-Q22</f>
+        <f t="shared" ref="Q23:R23" si="23">Q18-Q22</f>
         <v>581</v>
       </c>
       <c r="R23" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1140</v>
       </c>
       <c r="S23" s="6">
-        <f>S18*0.25</f>
-        <v>497.28750000000002</v>
+        <f t="shared" ref="S23:T23" si="24">S18-S22</f>
+        <v>542</v>
       </c>
       <c r="T23" s="6">
-        <f>T18*0.25</f>
-        <v>679.61</v>
+        <f t="shared" si="24"/>
+        <v>595</v>
       </c>
       <c r="U23" s="6">
         <f>U18*0.26</f>
-        <v>831.6099999999999</v>
+        <v>818.53200000000015</v>
       </c>
       <c r="V23" s="6">
         <f>V18*0.34</f>
-        <v>1454.673</v>
+        <v>1478.2316000000001</v>
       </c>
       <c r="Z23" s="6">
         <f>Z18-Z22</f>
@@ -2976,48 +3158,48 @@
         <v>2686</v>
       </c>
       <c r="AE23" s="6">
-        <f t="shared" ref="AE23:AO23" si="22">AE18-AE22</f>
-        <v>3463.1805000000022</v>
+        <f t="shared" ref="AE23:AO23" si="25">AE18-AE22</f>
+        <v>3433.7636000000002</v>
       </c>
       <c r="AF23" s="6">
-        <f t="shared" si="22"/>
-        <v>3486.0448500000002</v>
+        <f t="shared" si="25"/>
+        <v>3616.007450000001</v>
       </c>
       <c r="AG23" s="6">
-        <f t="shared" si="22"/>
-        <v>3761.9253297499999</v>
+        <f t="shared" si="25"/>
+        <v>3936.3503999999994</v>
       </c>
       <c r="AH23" s="6">
-        <f t="shared" si="22"/>
-        <v>3940.3335465474993</v>
+        <f t="shared" si="25"/>
+        <v>4137.9094071250001</v>
       </c>
       <c r="AI23" s="6">
-        <f t="shared" si="22"/>
-        <v>4059.6386897504744</v>
+        <f t="shared" si="25"/>
+        <v>4268.8895244822506</v>
       </c>
       <c r="AJ23" s="6">
-        <f t="shared" si="22"/>
-        <v>4144.1084886114804</v>
+        <f t="shared" si="25"/>
+        <v>4365.2447198795726</v>
       </c>
       <c r="AK23" s="6">
-        <f t="shared" si="22"/>
-        <v>4230.5185966271856</v>
+        <f t="shared" si="25"/>
+        <v>4456.4999552484187</v>
       </c>
       <c r="AL23" s="6">
-        <f t="shared" si="22"/>
-        <v>4318.9189728576239</v>
+        <f t="shared" si="25"/>
+        <v>4549.8279431632582</v>
       </c>
       <c r="AM23" s="6">
-        <f t="shared" si="22"/>
-        <v>4409.3610513580206</v>
+        <f t="shared" si="25"/>
+        <v>4645.2799704040772</v>
       </c>
       <c r="AN23" s="6">
-        <f t="shared" si="22"/>
-        <v>4501.8977916140429</v>
+        <f t="shared" si="25"/>
+        <v>4742.9087240071567</v>
       </c>
       <c r="AO23" s="6">
-        <f t="shared" si="22"/>
-        <v>4596.5837309428389</v>
+        <f t="shared" si="25"/>
+        <v>4842.768334078808</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
@@ -3070,10 +3252,10 @@
         <v>126</v>
       </c>
       <c r="S24" s="3">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="T24" s="3">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="U24" s="3">
         <v>95</v>
@@ -3158,19 +3340,17 @@
         <v>-96</v>
       </c>
       <c r="S25" s="3">
-        <f>O25*1.3</f>
-        <v>-54.6</v>
+        <v>-36</v>
       </c>
       <c r="T25" s="3">
-        <f t="shared" ref="T25:V25" si="23">P25*1.3</f>
-        <v>-50.7</v>
+        <v>-51</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="U25:V25" si="26">Q25*1.3</f>
         <v>-66.3</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-124.80000000000001</v>
       </c>
       <c r="Z25" s="3">
@@ -3250,12 +3430,10 @@
         <v>368</v>
       </c>
       <c r="S26" s="3">
-        <f>O26*1.2</f>
-        <v>273.59999999999997</v>
+        <v>287</v>
       </c>
       <c r="T26" s="3">
-        <f t="shared" ref="T26" si="24">P26*1.2</f>
-        <v>332.4</v>
+        <v>287</v>
       </c>
       <c r="U26" s="3">
         <f>Q26*1.15</f>
@@ -3305,67 +3483,67 @@
         <v>182</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" ref="G27:P27" si="25">SUM(G24:G26)</f>
+        <f t="shared" ref="G27:P27" si="27">SUM(G24:G26)</f>
         <v>184</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>189</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>204</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>219</v>
       </c>
       <c r="K27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>213</v>
       </c>
       <c r="L27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>224</v>
       </c>
       <c r="M27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>257</v>
       </c>
       <c r="N27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>350</v>
       </c>
       <c r="O27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>277</v>
       </c>
       <c r="P27" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>329</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" ref="Q27:R27" si="26">SUM(Q24:Q26)</f>
+        <f t="shared" ref="Q27:R27" si="28">SUM(Q24:Q26)</f>
         <v>291</v>
       </c>
       <c r="R27" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>398</v>
       </c>
       <c r="S27" s="3">
-        <f t="shared" ref="S27:V27" si="27">SUM(S24:S26)</f>
-        <v>313.99999999999994</v>
+        <f t="shared" ref="S27:V27" si="29">SUM(S24:S26)</f>
+        <v>363</v>
       </c>
       <c r="T27" s="3">
-        <f t="shared" si="27"/>
-        <v>376.7</v>
+        <f t="shared" si="29"/>
+        <v>363</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>312.74999999999994</v>
       </c>
       <c r="V27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>410</v>
       </c>
       <c r="Z27" s="3">
@@ -3390,47 +3568,47 @@
       </c>
       <c r="AE27" s="3">
         <f>SUM(S27:V27)</f>
-        <v>1413.4499999999998</v>
+        <v>1448.75</v>
       </c>
       <c r="AF27" s="3">
-        <f>(AE27*1.05)-400</f>
-        <v>1084.1224999999999</v>
+        <f>(AE27*1.05)</f>
+        <v>1521.1875</v>
       </c>
       <c r="AG27" s="3">
         <f>AF27*1.04</f>
-        <v>1127.4874</v>
+        <v>1582.0350000000001</v>
       </c>
       <c r="AH27" s="3">
         <f>AG27*1.03</f>
-        <v>1161.3120220000001</v>
+        <v>1629.4960500000002</v>
       </c>
       <c r="AI27" s="3">
         <f>AH27*1.02</f>
-        <v>1184.5382624400002</v>
+        <v>1662.0859710000002</v>
       </c>
       <c r="AJ27" s="3">
-        <f t="shared" ref="AJ27:AO27" si="28">AI27*1.02</f>
-        <v>1208.2290276888002</v>
+        <f t="shared" ref="AJ27:AO27" si="30">AI27*1.02</f>
+        <v>1695.3276904200002</v>
       </c>
       <c r="AK27" s="3">
-        <f t="shared" si="28"/>
-        <v>1232.3936082425762</v>
+        <f t="shared" si="30"/>
+        <v>1729.2342442284003</v>
       </c>
       <c r="AL27" s="3">
-        <f t="shared" si="28"/>
-        <v>1257.0414804074278</v>
+        <f t="shared" si="30"/>
+        <v>1763.8189291129684</v>
       </c>
       <c r="AM27" s="3">
-        <f t="shared" si="28"/>
-        <v>1282.1823100155764</v>
+        <f t="shared" si="30"/>
+        <v>1799.0953076952278</v>
       </c>
       <c r="AN27" s="3">
-        <f t="shared" si="28"/>
-        <v>1307.825956215888</v>
+        <f t="shared" si="30"/>
+        <v>1835.0772138491325</v>
       </c>
       <c r="AO27" s="3">
-        <f t="shared" si="28"/>
-        <v>1333.9824753402058</v>
+        <f t="shared" si="30"/>
+        <v>1871.7787581261152</v>
       </c>
     </row>
     <row r="28" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3446,68 +3624,68 @@
         <v>105</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" ref="G28:P28" si="29">G23-G27</f>
+        <f t="shared" ref="G28:P28" si="31">G23-G27</f>
         <v>83</v>
       </c>
       <c r="H28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>127</v>
       </c>
       <c r="I28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>112</v>
       </c>
       <c r="J28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>426</v>
       </c>
       <c r="K28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>89</v>
       </c>
       <c r="L28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>118</v>
       </c>
       <c r="M28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>172</v>
       </c>
       <c r="N28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>466</v>
       </c>
       <c r="O28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>117</v>
       </c>
       <c r="P28" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>242</v>
       </c>
       <c r="Q28" s="6">
-        <f t="shared" ref="Q28:R28" si="30">Q23-Q27</f>
+        <f t="shared" ref="Q28:R28" si="32">Q23-Q27</f>
         <v>290</v>
       </c>
       <c r="R28" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>742</v>
       </c>
       <c r="S28" s="6">
-        <f t="shared" ref="S28:V28" si="31">S23-S27</f>
-        <v>183.28750000000008</v>
+        <f t="shared" ref="S28:V28" si="33">S23-S27</f>
+        <v>179</v>
       </c>
       <c r="T28" s="6">
-        <f t="shared" si="31"/>
-        <v>302.91000000000003</v>
+        <f t="shared" si="33"/>
+        <v>232</v>
       </c>
       <c r="U28" s="6">
-        <f t="shared" si="31"/>
-        <v>518.8599999999999</v>
+        <f t="shared" si="33"/>
+        <v>505.78200000000021</v>
       </c>
       <c r="V28" s="6">
-        <f t="shared" si="31"/>
-        <v>1044.673</v>
+        <f t="shared" si="33"/>
+        <v>1068.2316000000001</v>
       </c>
       <c r="Z28" s="6">
         <f>Z23-Z27</f>
@@ -3526,52 +3704,52 @@
         <v>845</v>
       </c>
       <c r="AD28" s="6">
-        <f t="shared" ref="AD28:AO28" si="32">AD23-AD27</f>
+        <f t="shared" ref="AD28:AO28" si="34">AD23-AD27</f>
         <v>1391</v>
       </c>
       <c r="AE28" s="6">
-        <f t="shared" si="32"/>
-        <v>2049.7305000000024</v>
+        <f t="shared" si="34"/>
+        <v>1985.0136000000002</v>
       </c>
       <c r="AF28" s="6">
-        <f t="shared" si="32"/>
-        <v>2401.9223500000003</v>
+        <f t="shared" si="34"/>
+        <v>2094.819950000001</v>
       </c>
       <c r="AG28" s="6">
-        <f t="shared" si="32"/>
-        <v>2634.43792975</v>
+        <f t="shared" si="34"/>
+        <v>2354.3153999999995</v>
       </c>
       <c r="AH28" s="6">
-        <f t="shared" si="32"/>
-        <v>2779.0215245474992</v>
+        <f t="shared" si="34"/>
+        <v>2508.4133571249999</v>
       </c>
       <c r="AI28" s="6">
-        <f t="shared" si="32"/>
-        <v>2875.1004273104745</v>
+        <f t="shared" si="34"/>
+        <v>2606.8035534822502</v>
       </c>
       <c r="AJ28" s="6">
-        <f t="shared" si="32"/>
-        <v>2935.8794609226802</v>
+        <f t="shared" si="34"/>
+        <v>2669.9170294595724</v>
       </c>
       <c r="AK28" s="6">
-        <f t="shared" si="32"/>
-        <v>2998.1249883846094</v>
+        <f t="shared" si="34"/>
+        <v>2727.2657110200184</v>
       </c>
       <c r="AL28" s="6">
-        <f t="shared" si="32"/>
-        <v>3061.8774924501959</v>
+        <f t="shared" si="34"/>
+        <v>2786.0090140502898</v>
       </c>
       <c r="AM28" s="6">
-        <f t="shared" si="32"/>
-        <v>3127.1787413424445</v>
+        <f t="shared" si="34"/>
+        <v>2846.1846627088494</v>
       </c>
       <c r="AN28" s="6">
-        <f t="shared" si="32"/>
-        <v>3194.0718353981547</v>
+        <f t="shared" si="34"/>
+        <v>2907.8315101580242</v>
       </c>
       <c r="AO28" s="6">
-        <f t="shared" si="32"/>
-        <v>3262.601255602633</v>
+        <f t="shared" si="34"/>
+        <v>2970.9895759526926</v>
       </c>
     </row>
     <row r="29" spans="2:41" x14ac:dyDescent="0.3">
@@ -3623,8 +3801,12 @@
         <f>AD29-Q29-P29-O29</f>
         <v>20</v>
       </c>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
+      <c r="S29" s="3">
+        <v>3</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="Z29" s="3">
@@ -3703,8 +3885,12 @@
         <f>AD30-Q30-P30-O30</f>
         <v>-9</v>
       </c>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
+      <c r="S30" s="3">
+        <v>3</v>
+      </c>
+      <c r="T30" s="3">
+        <v>-7</v>
+      </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="Z30" s="3">
@@ -3783,8 +3969,12 @@
         <f>AD31-Q31-P31-O31</f>
         <v>-5</v>
       </c>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
+      <c r="S31" s="3">
+        <v>-6</v>
+      </c>
+      <c r="T31" s="3">
+        <v>-4</v>
+      </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="Z31" s="3">
@@ -3863,8 +4053,12 @@
         <f>AD32-Q32-P32-O32</f>
         <v>49</v>
       </c>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
+      <c r="S32" s="3">
+        <v>33</v>
+      </c>
+      <c r="T32" s="3">
+        <v>20</v>
+      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="Z32" s="3">
@@ -3907,67 +4101,67 @@
         <v>2</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" ref="G33:P33" si="33">SUM(G29:G32)</f>
+        <f t="shared" ref="G33:P33" si="35">SUM(G29:G32)</f>
         <v>10</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>29</v>
       </c>
       <c r="I33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-11</v>
       </c>
       <c r="K33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>20</v>
       </c>
       <c r="L33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>14</v>
       </c>
       <c r="M33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>27</v>
       </c>
       <c r="N33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-30</v>
       </c>
       <c r="O33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>31</v>
       </c>
       <c r="P33" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>34</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" ref="Q33:R33" si="34">SUM(Q29:Q32)</f>
+        <f t="shared" ref="Q33:T33" si="36">SUM(Q29:Q32)</f>
         <v>43</v>
       </c>
       <c r="R33" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>55</v>
       </c>
       <c r="S33" s="3">
-        <f>O33*1.05</f>
-        <v>32.550000000000004</v>
+        <f t="shared" si="36"/>
+        <v>33</v>
       </c>
       <c r="T33" s="3">
-        <f t="shared" ref="T33:V33" si="35">P33*1.05</f>
-        <v>35.700000000000003</v>
+        <f t="shared" si="36"/>
+        <v>9</v>
       </c>
       <c r="U33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="U33:V33" si="37">Q33*1.05</f>
         <v>45.15</v>
       </c>
       <c r="V33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>57.75</v>
       </c>
       <c r="Z33" s="3">
@@ -3987,52 +4181,52 @@
         <v>31</v>
       </c>
       <c r="AD33" s="3">
-        <f t="shared" ref="AD33" si="36">SUM(AD29:AD32)</f>
+        <f t="shared" ref="AD33" si="38">SUM(AD29:AD32)</f>
         <v>163</v>
       </c>
       <c r="AE33" s="3">
         <f>SUM(S33:V33)</f>
-        <v>171.15</v>
+        <v>144.9</v>
       </c>
       <c r="AF33" s="3">
         <f>AE33*1.03</f>
-        <v>176.28450000000001</v>
+        <v>149.24700000000001</v>
       </c>
       <c r="AG33" s="3">
-        <f t="shared" ref="AG33:AO33" si="37">AF33*1.03</f>
-        <v>181.573035</v>
+        <f t="shared" ref="AG33:AO33" si="39">AF33*1.03</f>
+        <v>153.72441000000001</v>
       </c>
       <c r="AH33" s="3">
-        <f t="shared" si="37"/>
-        <v>187.02022605000002</v>
+        <f t="shared" si="39"/>
+        <v>158.33614230000001</v>
       </c>
       <c r="AI33" s="3">
-        <f t="shared" si="37"/>
-        <v>192.63083283150002</v>
+        <f t="shared" si="39"/>
+        <v>163.08622656900002</v>
       </c>
       <c r="AJ33" s="3">
-        <f t="shared" si="37"/>
-        <v>198.40975781644502</v>
+        <f t="shared" si="39"/>
+        <v>167.97881336607003</v>
       </c>
       <c r="AK33" s="3">
-        <f t="shared" si="37"/>
-        <v>204.36205055093839</v>
+        <f t="shared" si="39"/>
+        <v>173.01817776705212</v>
       </c>
       <c r="AL33" s="3">
-        <f t="shared" si="37"/>
-        <v>210.49291206746656</v>
+        <f t="shared" si="39"/>
+        <v>178.20872310006368</v>
       </c>
       <c r="AM33" s="3">
-        <f t="shared" si="37"/>
-        <v>216.80769942949055</v>
+        <f t="shared" si="39"/>
+        <v>183.55498479306559</v>
       </c>
       <c r="AN33" s="3">
-        <f t="shared" si="37"/>
-        <v>223.31193041237529</v>
+        <f t="shared" si="39"/>
+        <v>189.06163433685757</v>
       </c>
       <c r="AO33" s="3">
-        <f t="shared" si="37"/>
-        <v>230.01128832474654</v>
+        <f t="shared" si="39"/>
+        <v>194.7334833669633</v>
       </c>
     </row>
     <row r="34" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4048,68 +4242,68 @@
         <v>103</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" ref="G34:P34" si="38">G28-G33</f>
+        <f t="shared" ref="G34:P34" si="40">G28-G33</f>
         <v>73</v>
       </c>
       <c r="H34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>98</v>
       </c>
       <c r="I34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>111</v>
       </c>
       <c r="J34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>437</v>
       </c>
       <c r="K34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>69</v>
       </c>
       <c r="L34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>104</v>
       </c>
       <c r="M34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>145</v>
       </c>
       <c r="N34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>496</v>
       </c>
       <c r="O34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>86</v>
       </c>
       <c r="P34" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>208</v>
       </c>
       <c r="Q34" s="6">
-        <f t="shared" ref="Q34:V34" si="39">Q28-Q33</f>
+        <f t="shared" ref="Q34:V34" si="41">Q28-Q33</f>
         <v>247</v>
       </c>
       <c r="R34" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>687</v>
       </c>
       <c r="S34" s="6">
-        <f t="shared" si="39"/>
-        <v>150.73750000000007</v>
+        <f t="shared" si="41"/>
+        <v>146</v>
       </c>
       <c r="T34" s="6">
-        <f t="shared" si="39"/>
-        <v>267.21000000000004</v>
+        <f t="shared" si="41"/>
+        <v>223</v>
       </c>
       <c r="U34" s="6">
-        <f t="shared" si="39"/>
-        <v>473.70999999999992</v>
+        <f t="shared" si="41"/>
+        <v>460.63200000000023</v>
       </c>
       <c r="V34" s="6">
-        <f t="shared" si="39"/>
-        <v>986.923</v>
+        <f t="shared" si="41"/>
+        <v>1010.4816000000001</v>
       </c>
       <c r="Z34" s="6">
         <f>Z28-Z33</f>
@@ -4128,52 +4322,52 @@
         <v>814</v>
       </c>
       <c r="AD34" s="6">
-        <f t="shared" ref="AD34:AO34" si="40">AD28-AD33</f>
+        <f t="shared" ref="AD34:AO34" si="42">AD28-AD33</f>
         <v>1228</v>
       </c>
       <c r="AE34" s="6">
-        <f t="shared" si="40"/>
-        <v>1878.5805000000023</v>
+        <f t="shared" si="42"/>
+        <v>1840.1136000000001</v>
       </c>
       <c r="AF34" s="6">
-        <f t="shared" si="40"/>
-        <v>2225.6378500000001</v>
+        <f t="shared" si="42"/>
+        <v>1945.5729500000009</v>
       </c>
       <c r="AG34" s="6">
-        <f t="shared" si="40"/>
-        <v>2452.8648947500001</v>
+        <f t="shared" si="42"/>
+        <v>2200.5909899999997</v>
       </c>
       <c r="AH34" s="6">
-        <f t="shared" si="40"/>
-        <v>2592.0012984974992</v>
+        <f t="shared" si="42"/>
+        <v>2350.0772148249998</v>
       </c>
       <c r="AI34" s="6">
-        <f t="shared" si="40"/>
-        <v>2682.4695944789746</v>
+        <f t="shared" si="42"/>
+        <v>2443.71732691325</v>
       </c>
       <c r="AJ34" s="6">
-        <f t="shared" si="40"/>
-        <v>2737.4697031062351</v>
+        <f t="shared" si="42"/>
+        <v>2501.9382160935024</v>
       </c>
       <c r="AK34" s="6">
-        <f t="shared" si="40"/>
-        <v>2793.762937833671</v>
+        <f t="shared" si="42"/>
+        <v>2554.2475332529662</v>
       </c>
       <c r="AL34" s="6">
-        <f t="shared" si="40"/>
-        <v>2851.3845803827294</v>
+        <f t="shared" si="42"/>
+        <v>2607.8002909502261</v>
       </c>
       <c r="AM34" s="6">
-        <f t="shared" si="40"/>
-        <v>2910.3710419129538</v>
+        <f t="shared" si="42"/>
+        <v>2662.6296779157838</v>
       </c>
       <c r="AN34" s="6">
-        <f t="shared" si="40"/>
-        <v>2970.7599049857795</v>
+        <f t="shared" si="42"/>
+        <v>2718.7698758211668</v>
       </c>
       <c r="AO34" s="6">
-        <f t="shared" si="40"/>
-        <v>3032.5899672778864</v>
+        <f t="shared" si="42"/>
+        <v>2776.2560925857292</v>
       </c>
     </row>
     <row r="35" spans="2:152" x14ac:dyDescent="0.3">
@@ -4226,20 +4420,18 @@
         <v>172</v>
       </c>
       <c r="S35" s="3">
-        <f>S34*0.27</f>
-        <v>40.699125000000024</v>
+        <v>39</v>
       </c>
       <c r="T35" s="3">
-        <f t="shared" ref="T35:V35" si="41">T34*0.27</f>
-        <v>72.14670000000001</v>
+        <v>53</v>
       </c>
       <c r="U35" s="3">
-        <f t="shared" si="41"/>
-        <v>127.90169999999999</v>
+        <f t="shared" ref="U35:V35" si="43">U34*0.27</f>
+        <v>124.37064000000007</v>
       </c>
       <c r="V35" s="3">
-        <f t="shared" si="41"/>
-        <v>266.46921000000003</v>
+        <f t="shared" si="43"/>
+        <v>272.83003200000002</v>
       </c>
       <c r="Z35" s="3">
         <v>83</v>
@@ -4258,47 +4450,47 @@
       </c>
       <c r="AE35" s="3">
         <f>SUM(S35:V35)</f>
-        <v>507.21673500000009</v>
+        <v>489.20067200000005</v>
       </c>
       <c r="AF35" s="3">
         <f>AF34*0.25</f>
-        <v>556.40946250000002</v>
+        <v>486.39323750000023</v>
       </c>
       <c r="AG35" s="3">
-        <f t="shared" ref="AG35:AO35" si="42">AG34*0.25</f>
-        <v>613.21622368750002</v>
+        <f t="shared" ref="AG35:AO35" si="44">AG34*0.25</f>
+        <v>550.14774749999992</v>
       </c>
       <c r="AH35" s="3">
-        <f t="shared" si="42"/>
-        <v>648.0003246243748</v>
+        <f t="shared" si="44"/>
+        <v>587.51930370624996</v>
       </c>
       <c r="AI35" s="3">
-        <f t="shared" si="42"/>
-        <v>670.61739861974365</v>
+        <f t="shared" si="44"/>
+        <v>610.92933172831249</v>
       </c>
       <c r="AJ35" s="3">
-        <f t="shared" si="42"/>
-        <v>684.36742577655878</v>
+        <f t="shared" si="44"/>
+        <v>625.48455402337561</v>
       </c>
       <c r="AK35" s="3">
-        <f t="shared" si="42"/>
-        <v>698.44073445841775</v>
+        <f t="shared" si="44"/>
+        <v>638.56188331324154</v>
       </c>
       <c r="AL35" s="3">
-        <f t="shared" si="42"/>
-        <v>712.84614509568235</v>
+        <f t="shared" si="44"/>
+        <v>651.95007273755652</v>
       </c>
       <c r="AM35" s="3">
-        <f t="shared" si="42"/>
-        <v>727.59276047823846</v>
+        <f t="shared" si="44"/>
+        <v>665.65741947894594</v>
       </c>
       <c r="AN35" s="3">
-        <f t="shared" si="42"/>
-        <v>742.68997624644487</v>
+        <f t="shared" si="44"/>
+        <v>679.6924689552917</v>
       </c>
       <c r="AO35" s="3">
-        <f t="shared" si="42"/>
-        <v>758.14749181947161</v>
+        <f t="shared" si="44"/>
+        <v>694.06402314643231</v>
       </c>
     </row>
     <row r="36" spans="2:152" x14ac:dyDescent="0.3">
@@ -4361,20 +4553,18 @@
         <v>46</v>
       </c>
       <c r="S36" s="3">
-        <f>S34*0.1</f>
-        <v>15.073750000000008</v>
+        <v>24</v>
       </c>
       <c r="T36" s="3">
-        <f t="shared" ref="T36:V36" si="43">T34*0.1</f>
-        <v>26.721000000000004</v>
+        <v>27</v>
       </c>
       <c r="U36" s="3">
-        <f t="shared" si="43"/>
-        <v>47.370999999999995</v>
+        <f t="shared" ref="U36:V36" si="45">U34*0.1</f>
+        <v>46.063200000000023</v>
       </c>
       <c r="V36" s="3">
-        <f t="shared" si="43"/>
-        <v>98.692300000000003</v>
+        <f t="shared" si="45"/>
+        <v>101.04816000000001</v>
       </c>
       <c r="Z36" s="3">
         <f>283+27</f>
@@ -4398,47 +4588,47 @@
       </c>
       <c r="AE36" s="3">
         <f>SUM(S36:V36)</f>
-        <v>187.85804999999999</v>
+        <v>198.11136000000005</v>
       </c>
       <c r="AF36" s="3">
-        <f t="shared" ref="AF36:AO36" si="44">AF34*0.1</f>
-        <v>222.56378500000002</v>
+        <f t="shared" ref="AF36:AO36" si="46">AF34*0.1</f>
+        <v>194.5572950000001</v>
       </c>
       <c r="AG36" s="3">
-        <f t="shared" si="44"/>
-        <v>245.28648947500002</v>
+        <f t="shared" si="46"/>
+        <v>220.05909899999997</v>
       </c>
       <c r="AH36" s="3">
-        <f t="shared" si="44"/>
-        <v>259.20012984974994</v>
+        <f t="shared" si="46"/>
+        <v>235.00772148249999</v>
       </c>
       <c r="AI36" s="3">
-        <f t="shared" si="44"/>
-        <v>268.2469594478975</v>
+        <f t="shared" si="46"/>
+        <v>244.37173269132501</v>
       </c>
       <c r="AJ36" s="3">
-        <f t="shared" si="44"/>
-        <v>273.74697031062351</v>
+        <f t="shared" si="46"/>
+        <v>250.19382160935027</v>
       </c>
       <c r="AK36" s="3">
-        <f t="shared" si="44"/>
-        <v>279.37629378336709</v>
+        <f t="shared" si="46"/>
+        <v>255.42475332529662</v>
       </c>
       <c r="AL36" s="3">
-        <f t="shared" si="44"/>
-        <v>285.13845803827297</v>
+        <f t="shared" si="46"/>
+        <v>260.7800290950226</v>
       </c>
       <c r="AM36" s="3">
-        <f t="shared" si="44"/>
-        <v>291.03710419129538</v>
+        <f t="shared" si="46"/>
+        <v>266.26296779157838</v>
       </c>
       <c r="AN36" s="3">
-        <f t="shared" si="44"/>
-        <v>297.07599049857794</v>
+        <f t="shared" si="46"/>
+        <v>271.87698758211667</v>
       </c>
       <c r="AO36" s="3">
-        <f t="shared" si="44"/>
-        <v>303.25899672778866</v>
+        <f t="shared" si="46"/>
+        <v>277.62560925857292</v>
       </c>
     </row>
     <row r="37" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4454,68 +4644,68 @@
         <v>-37</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" ref="G37:P37" si="45">G34-G35-G36</f>
+        <f t="shared" ref="G37:P37" si="47">G34-G35-G36</f>
         <v>46</v>
       </c>
       <c r="H37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>57</v>
       </c>
       <c r="I37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>76</v>
       </c>
       <c r="J37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>297</v>
       </c>
       <c r="K37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>48</v>
       </c>
       <c r="L37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>57</v>
       </c>
       <c r="M37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>102</v>
       </c>
       <c r="N37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>327</v>
       </c>
       <c r="O37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>50</v>
       </c>
       <c r="P37" s="6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>63</v>
       </c>
       <c r="Q37" s="6">
-        <f t="shared" ref="Q37:R37" si="46">Q34-Q35-Q36</f>
+        <f t="shared" ref="Q37:R37" si="48">Q34-Q35-Q36</f>
         <v>135</v>
       </c>
       <c r="R37" s="6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>469</v>
       </c>
       <c r="S37" s="6">
-        <f t="shared" ref="S37:V37" si="47">S34-S35-S36</f>
-        <v>94.964625000000041</v>
+        <f t="shared" ref="S37:V37" si="49">S34-S35-S36</f>
+        <v>83</v>
       </c>
       <c r="T37" s="6">
-        <f t="shared" si="47"/>
-        <v>168.34230000000002</v>
+        <f t="shared" si="49"/>
+        <v>143</v>
       </c>
       <c r="U37" s="6">
-        <f t="shared" si="47"/>
-        <v>298.43729999999994</v>
+        <f t="shared" si="49"/>
+        <v>290.19816000000014</v>
       </c>
       <c r="V37" s="6">
-        <f t="shared" si="47"/>
-        <v>621.76148999999998</v>
+        <f t="shared" si="49"/>
+        <v>636.60340799999994</v>
       </c>
       <c r="Z37" s="6">
         <f>Z34-Z35-Z36</f>
@@ -4534,496 +4724,496 @@
         <v>534</v>
       </c>
       <c r="AD37" s="6">
-        <f t="shared" ref="AD37:AO37" si="48">AD34-AD35-AD36</f>
+        <f t="shared" ref="AD37:AO37" si="50">AD34-AD35-AD36</f>
         <v>717</v>
       </c>
       <c r="AE37" s="6">
-        <f t="shared" si="48"/>
-        <v>1183.5057150000023</v>
+        <f t="shared" si="50"/>
+        <v>1152.8015680000001</v>
       </c>
       <c r="AF37" s="6">
-        <f t="shared" si="48"/>
-        <v>1446.6646025</v>
+        <f t="shared" si="50"/>
+        <v>1264.6224175000007</v>
       </c>
       <c r="AG37" s="6">
-        <f t="shared" si="48"/>
-        <v>1594.3621815874999</v>
+        <f t="shared" si="50"/>
+        <v>1430.3841434999997</v>
       </c>
       <c r="AH37" s="6">
-        <f t="shared" si="48"/>
-        <v>1684.8008440233743</v>
+        <f t="shared" si="50"/>
+        <v>1527.5501896362498</v>
       </c>
       <c r="AI37" s="6">
-        <f t="shared" si="48"/>
-        <v>1743.6052364113334</v>
+        <f t="shared" si="50"/>
+        <v>1588.4162624936125</v>
       </c>
       <c r="AJ37" s="6">
-        <f t="shared" si="48"/>
-        <v>1779.3553070190528</v>
+        <f t="shared" si="50"/>
+        <v>1626.2598404607766</v>
       </c>
       <c r="AK37" s="6">
-        <f t="shared" si="48"/>
-        <v>1815.945909591886</v>
+        <f t="shared" si="50"/>
+        <v>1660.2608966144278</v>
       </c>
       <c r="AL37" s="6">
-        <f t="shared" si="48"/>
-        <v>1853.3999772487739</v>
+        <f t="shared" si="50"/>
+        <v>1695.0701891176468</v>
       </c>
       <c r="AM37" s="6">
-        <f t="shared" si="48"/>
-        <v>1891.7411772434202</v>
+        <f t="shared" si="50"/>
+        <v>1730.7092906452594</v>
       </c>
       <c r="AN37" s="6">
-        <f t="shared" si="48"/>
-        <v>1930.9939382407565</v>
+        <f t="shared" si="50"/>
+        <v>1767.2004192837585</v>
       </c>
       <c r="AO37" s="6">
-        <f t="shared" si="48"/>
-        <v>1971.1834787306261</v>
+        <f t="shared" si="50"/>
+        <v>1804.5664601807241</v>
       </c>
       <c r="AP37" s="1">
         <f>AO37*(1+$AS$45)</f>
-        <v>1951.4716439433198</v>
+        <v>1786.5207955789169</v>
       </c>
       <c r="AQ37" s="1">
-        <f t="shared" ref="AQ37:DB37" si="49">AP37*(1+$AS$45)</f>
-        <v>1931.9569275038866</v>
+        <f t="shared" ref="AQ37:DB37" si="51">AP37*(1+$AS$45)</f>
+        <v>1768.6555876231278</v>
       </c>
       <c r="AR37" s="1">
-        <f t="shared" si="49"/>
-        <v>1912.6373582288477</v>
+        <f t="shared" si="51"/>
+        <v>1750.9690317468965</v>
       </c>
       <c r="AS37" s="1">
-        <f t="shared" si="49"/>
-        <v>1893.5109846465591</v>
+        <f t="shared" si="51"/>
+        <v>1733.4593414294275</v>
       </c>
       <c r="AT37" s="1">
-        <f t="shared" si="49"/>
-        <v>1874.5758748000935</v>
+        <f t="shared" si="51"/>
+        <v>1716.1247480151333</v>
       </c>
       <c r="AU37" s="1">
-        <f t="shared" si="49"/>
-        <v>1855.8301160520925</v>
+        <f t="shared" si="51"/>
+        <v>1698.9635005349819</v>
       </c>
       <c r="AV37" s="1">
-        <f t="shared" si="49"/>
-        <v>1837.2718148915717</v>
+        <f t="shared" si="51"/>
+        <v>1681.9738655296321</v>
       </c>
       <c r="AW37" s="1">
-        <f t="shared" si="49"/>
-        <v>1818.899096742656</v>
+        <f t="shared" si="51"/>
+        <v>1665.1541268743358</v>
       </c>
       <c r="AX37" s="1">
-        <f t="shared" si="49"/>
-        <v>1800.7101057752293</v>
+        <f t="shared" si="51"/>
+        <v>1648.5025856055925</v>
       </c>
       <c r="AY37" s="1">
-        <f t="shared" si="49"/>
-        <v>1782.7030047174769</v>
+        <f t="shared" si="51"/>
+        <v>1632.0175597495365</v>
       </c>
       <c r="AZ37" s="1">
-        <f t="shared" si="49"/>
-        <v>1764.8759746703022</v>
+        <f t="shared" si="51"/>
+        <v>1615.6973841520412</v>
       </c>
       <c r="BA37" s="1">
-        <f t="shared" si="49"/>
-        <v>1747.2272149235991</v>
+        <f t="shared" si="51"/>
+        <v>1599.5404103105207</v>
       </c>
       <c r="BB37" s="1">
-        <f t="shared" si="49"/>
-        <v>1729.7549427743631</v>
+        <f t="shared" si="51"/>
+        <v>1583.5450062074153</v>
       </c>
       <c r="BC37" s="1">
-        <f t="shared" si="49"/>
-        <v>1712.4573933466195</v>
+        <f t="shared" si="51"/>
+        <v>1567.7095561453411</v>
       </c>
       <c r="BD37" s="1">
-        <f t="shared" si="49"/>
-        <v>1695.3328194131532</v>
+        <f t="shared" si="51"/>
+        <v>1552.0324605838878</v>
       </c>
       <c r="BE37" s="1">
-        <f t="shared" si="49"/>
-        <v>1678.3794912190217</v>
+        <f t="shared" si="51"/>
+        <v>1536.5121359780489</v>
       </c>
       <c r="BF37" s="1">
-        <f t="shared" si="49"/>
-        <v>1661.5956963068315</v>
+        <f t="shared" si="51"/>
+        <v>1521.1470146182685</v>
       </c>
       <c r="BG37" s="1">
-        <f t="shared" si="49"/>
-        <v>1644.9797393437632</v>
+        <f t="shared" si="51"/>
+        <v>1505.9355444720859</v>
       </c>
       <c r="BH37" s="1">
-        <f t="shared" si="49"/>
-        <v>1628.5299419503256</v>
+        <f t="shared" si="51"/>
+        <v>1490.8761890273649</v>
       </c>
       <c r="BI37" s="1">
-        <f t="shared" si="49"/>
-        <v>1612.2446425308224</v>
+        <f t="shared" si="51"/>
+        <v>1475.9674271370914</v>
       </c>
       <c r="BJ37" s="1">
-        <f t="shared" si="49"/>
-        <v>1596.1221961055141</v>
+        <f t="shared" si="51"/>
+        <v>1461.2077528657205</v>
       </c>
       <c r="BK37" s="1">
-        <f t="shared" si="49"/>
-        <v>1580.160974144459</v>
+        <f t="shared" si="51"/>
+        <v>1446.5956753370633</v>
       </c>
       <c r="BL37" s="1">
-        <f t="shared" si="49"/>
-        <v>1564.3593644030145</v>
+        <f t="shared" si="51"/>
+        <v>1432.1297185836927</v>
       </c>
       <c r="BM37" s="1">
-        <f t="shared" si="49"/>
-        <v>1548.7157707589843</v>
+        <f t="shared" si="51"/>
+        <v>1417.8084213978557</v>
       </c>
       <c r="BN37" s="1">
-        <f t="shared" si="49"/>
-        <v>1533.2286130513944</v>
+        <f t="shared" si="51"/>
+        <v>1403.6303371838771</v>
       </c>
       <c r="BO37" s="1">
-        <f t="shared" si="49"/>
-        <v>1517.8963269208805</v>
+        <f t="shared" si="51"/>
+        <v>1389.5940338120383</v>
       </c>
       <c r="BP37" s="1">
-        <f t="shared" si="49"/>
-        <v>1502.7173636516716</v>
+        <f t="shared" si="51"/>
+        <v>1375.6980934739179</v>
       </c>
       <c r="BQ37" s="1">
-        <f t="shared" si="49"/>
-        <v>1487.6901900151549</v>
+        <f t="shared" si="51"/>
+        <v>1361.9411125391787</v>
       </c>
       <c r="BR37" s="1">
-        <f t="shared" si="49"/>
-        <v>1472.8132881150034</v>
+        <f t="shared" si="51"/>
+        <v>1348.321701413787</v>
       </c>
       <c r="BS37" s="1">
-        <f t="shared" si="49"/>
-        <v>1458.0851552338534</v>
+        <f t="shared" si="51"/>
+        <v>1334.8384843996491</v>
       </c>
       <c r="BT37" s="1">
-        <f t="shared" si="49"/>
-        <v>1443.5043036815148</v>
+        <f t="shared" si="51"/>
+        <v>1321.4900995556527</v>
       </c>
       <c r="BU37" s="1">
-        <f t="shared" si="49"/>
-        <v>1429.0692606446996</v>
+        <f t="shared" si="51"/>
+        <v>1308.2751985600962</v>
       </c>
       <c r="BV37" s="1">
-        <f t="shared" si="49"/>
-        <v>1414.7785680382526</v>
+        <f t="shared" si="51"/>
+        <v>1295.1924465744953</v>
       </c>
       <c r="BW37" s="1">
-        <f t="shared" si="49"/>
-        <v>1400.63078235787</v>
+        <f t="shared" si="51"/>
+        <v>1282.2405221087504</v>
       </c>
       <c r="BX37" s="1">
-        <f t="shared" si="49"/>
-        <v>1386.6244745342913</v>
+        <f t="shared" si="51"/>
+        <v>1269.4181168876628</v>
       </c>
       <c r="BY37" s="1">
-        <f t="shared" si="49"/>
-        <v>1372.7582297889483</v>
+        <f t="shared" si="51"/>
+        <v>1256.7239357187862</v>
       </c>
       <c r="BZ37" s="1">
-        <f t="shared" si="49"/>
-        <v>1359.0306474910587</v>
+        <f t="shared" si="51"/>
+        <v>1244.1566963615983</v>
       </c>
       <c r="CA37" s="1">
-        <f t="shared" si="49"/>
-        <v>1345.4403410161481</v>
+        <f t="shared" si="51"/>
+        <v>1231.7151293979823</v>
       </c>
       <c r="CB37" s="1">
-        <f t="shared" si="49"/>
-        <v>1331.9859376059865</v>
+        <f t="shared" si="51"/>
+        <v>1219.3979781040025</v>
       </c>
       <c r="CC37" s="1">
-        <f t="shared" si="49"/>
-        <v>1318.6660782299266</v>
+        <f t="shared" si="51"/>
+        <v>1207.2039983229624</v>
       </c>
       <c r="CD37" s="1">
-        <f t="shared" si="49"/>
-        <v>1305.4794174476274</v>
+        <f t="shared" si="51"/>
+        <v>1195.1319583397328</v>
       </c>
       <c r="CE37" s="1">
-        <f t="shared" si="49"/>
-        <v>1292.4246232731512</v>
+        <f t="shared" si="51"/>
+        <v>1183.1806387563354</v>
       </c>
       <c r="CF37" s="1">
-        <f t="shared" si="49"/>
-        <v>1279.5003770404196</v>
+        <f t="shared" si="51"/>
+        <v>1171.348832368772</v>
       </c>
       <c r="CG37" s="1">
-        <f t="shared" si="49"/>
-        <v>1266.7053732700153</v>
+        <f t="shared" si="51"/>
+        <v>1159.6353440450844</v>
       </c>
       <c r="CH37" s="1">
-        <f t="shared" si="49"/>
-        <v>1254.0383195373151</v>
+        <f t="shared" si="51"/>
+        <v>1148.0389906046335</v>
       </c>
       <c r="CI37" s="1">
-        <f t="shared" si="49"/>
-        <v>1241.497936341942</v>
+        <f t="shared" si="51"/>
+        <v>1136.558600698587</v>
       </c>
       <c r="CJ37" s="1">
-        <f t="shared" si="49"/>
-        <v>1229.0829569785226</v>
+        <f t="shared" si="51"/>
+        <v>1125.1930146916011</v>
       </c>
       <c r="CK37" s="1">
-        <f t="shared" si="49"/>
-        <v>1216.7921274087373</v>
+        <f t="shared" si="51"/>
+        <v>1113.9410845446851</v>
       </c>
       <c r="CL37" s="1">
-        <f t="shared" si="49"/>
-        <v>1204.62420613465</v>
+        <f t="shared" si="51"/>
+        <v>1102.8016736992381</v>
       </c>
       <c r="CM37" s="1">
-        <f t="shared" si="49"/>
-        <v>1192.5779640733035</v>
+        <f t="shared" si="51"/>
+        <v>1091.7736569622457</v>
       </c>
       <c r="CN37" s="1">
-        <f t="shared" si="49"/>
-        <v>1180.6521844325705</v>
+        <f t="shared" si="51"/>
+        <v>1080.8559203926231</v>
       </c>
       <c r="CO37" s="1">
-        <f t="shared" si="49"/>
-        <v>1168.8456625882447</v>
+        <f t="shared" si="51"/>
+        <v>1070.0473611886969</v>
       </c>
       <c r="CP37" s="1">
-        <f t="shared" si="49"/>
-        <v>1157.1572059623622</v>
+        <f t="shared" si="51"/>
+        <v>1059.3468875768099</v>
       </c>
       <c r="CQ37" s="1">
-        <f t="shared" si="49"/>
-        <v>1145.5856339027387</v>
+        <f t="shared" si="51"/>
+        <v>1048.7534187010417</v>
       </c>
       <c r="CR37" s="1">
-        <f t="shared" si="49"/>
-        <v>1134.1297775637113</v>
+        <f t="shared" si="51"/>
+        <v>1038.2658845140313</v>
       </c>
       <c r="CS37" s="1">
-        <f t="shared" si="49"/>
-        <v>1122.7884797880743</v>
+        <f t="shared" si="51"/>
+        <v>1027.8832256688911</v>
       </c>
       <c r="CT37" s="1">
-        <f t="shared" si="49"/>
-        <v>1111.5605949901935</v>
+        <f t="shared" si="51"/>
+        <v>1017.6043934122022</v>
       </c>
       <c r="CU37" s="1">
-        <f t="shared" si="49"/>
-        <v>1100.4449890402916</v>
+        <f t="shared" si="51"/>
+        <v>1007.4283494780801</v>
       </c>
       <c r="CV37" s="1">
-        <f t="shared" si="49"/>
-        <v>1089.4405391498888</v>
+        <f t="shared" si="51"/>
+        <v>997.35406598329928</v>
       </c>
       <c r="CW37" s="1">
-        <f t="shared" si="49"/>
-        <v>1078.5461337583899</v>
+        <f t="shared" si="51"/>
+        <v>987.38052532346626</v>
       </c>
       <c r="CX37" s="1">
-        <f t="shared" si="49"/>
-        <v>1067.760672420806</v>
+        <f t="shared" si="51"/>
+        <v>977.50672007023161</v>
       </c>
       <c r="CY37" s="1">
-        <f t="shared" si="49"/>
-        <v>1057.0830656965979</v>
+        <f t="shared" si="51"/>
+        <v>967.73165286952928</v>
       </c>
       <c r="CZ37" s="1">
-        <f t="shared" si="49"/>
-        <v>1046.5122350396321</v>
+        <f t="shared" si="51"/>
+        <v>958.05433634083397</v>
       </c>
       <c r="DA37" s="1">
-        <f t="shared" si="49"/>
-        <v>1036.0471126892357</v>
+        <f t="shared" si="51"/>
+        <v>948.47379297742566</v>
       </c>
       <c r="DB37" s="1">
-        <f t="shared" si="49"/>
-        <v>1025.6866415623433</v>
+        <f t="shared" si="51"/>
+        <v>938.98905504765139</v>
       </c>
       <c r="DC37" s="1">
-        <f t="shared" ref="DC37:EV37" si="50">DB37*(1+$AS$45)</f>
-        <v>1015.4297751467199</v>
+        <f t="shared" ref="DC37:EV37" si="52">DB37*(1+$AS$45)</f>
+        <v>929.59916449717491</v>
       </c>
       <c r="DD37" s="1">
-        <f t="shared" si="50"/>
-        <v>1005.2754773952527</v>
+        <f t="shared" si="52"/>
+        <v>920.30317285220315</v>
       </c>
       <c r="DE37" s="1">
-        <f t="shared" si="50"/>
-        <v>995.22272262130014</v>
+        <f t="shared" si="52"/>
+        <v>911.10014112368106</v>
       </c>
       <c r="DF37" s="1">
-        <f t="shared" si="50"/>
-        <v>985.2704953950871</v>
+        <f t="shared" si="52"/>
+        <v>901.98913971244428</v>
       </c>
       <c r="DG37" s="1">
-        <f t="shared" si="50"/>
-        <v>975.41779044113616</v>
+        <f t="shared" si="52"/>
+        <v>892.96924831531987</v>
       </c>
       <c r="DH37" s="1">
-        <f t="shared" si="50"/>
-        <v>965.66361253672483</v>
+        <f t="shared" si="52"/>
+        <v>884.03955583216668</v>
       </c>
       <c r="DI37" s="1">
-        <f t="shared" si="50"/>
-        <v>956.00697641135753</v>
+        <f t="shared" si="52"/>
+        <v>875.199160273845</v>
       </c>
       <c r="DJ37" s="1">
-        <f t="shared" si="50"/>
-        <v>946.44690664724396</v>
+        <f t="shared" si="52"/>
+        <v>866.44716867110651</v>
       </c>
       <c r="DK37" s="1">
-        <f t="shared" si="50"/>
-        <v>936.98243758077149</v>
+        <f t="shared" si="52"/>
+        <v>857.78269698439544</v>
       </c>
       <c r="DL37" s="1">
-        <f t="shared" si="50"/>
-        <v>927.61261320496374</v>
+        <f t="shared" si="52"/>
+        <v>849.20487001455149</v>
       </c>
       <c r="DM37" s="1">
-        <f t="shared" si="50"/>
-        <v>918.33648707291411</v>
+        <f t="shared" si="52"/>
+        <v>840.71282131440591</v>
       </c>
       <c r="DN37" s="1">
-        <f t="shared" si="50"/>
-        <v>909.15312220218493</v>
+        <f t="shared" si="52"/>
+        <v>832.3056931012618</v>
       </c>
       <c r="DO37" s="1">
-        <f t="shared" si="50"/>
-        <v>900.06159098016303</v>
+        <f t="shared" si="52"/>
+        <v>823.98263617024918</v>
       </c>
       <c r="DP37" s="1">
-        <f t="shared" si="50"/>
-        <v>891.06097507036134</v>
+        <f t="shared" si="52"/>
+        <v>815.74280980854667</v>
       </c>
       <c r="DQ37" s="1">
-        <f t="shared" si="50"/>
-        <v>882.15036531965768</v>
+        <f t="shared" si="52"/>
+        <v>807.58538171046121</v>
       </c>
       <c r="DR37" s="1">
-        <f t="shared" si="50"/>
-        <v>873.32886166646108</v>
+        <f t="shared" si="52"/>
+        <v>799.50952789335656</v>
       </c>
       <c r="DS37" s="1">
-        <f t="shared" si="50"/>
-        <v>864.59557304979649</v>
+        <f t="shared" si="52"/>
+        <v>791.51443261442296</v>
       </c>
       <c r="DT37" s="1">
-        <f t="shared" si="50"/>
-        <v>855.94961731929857</v>
+        <f t="shared" si="52"/>
+        <v>783.59928828827867</v>
       </c>
       <c r="DU37" s="1">
-        <f t="shared" si="50"/>
-        <v>847.39012114610557</v>
+        <f t="shared" si="52"/>
+        <v>775.76329540539587</v>
       </c>
       <c r="DV37" s="1">
-        <f t="shared" si="50"/>
-        <v>838.91621993464446</v>
+        <f t="shared" si="52"/>
+        <v>768.00566245134189</v>
       </c>
       <c r="DW37" s="1">
-        <f t="shared" si="50"/>
-        <v>830.52705773529806</v>
+        <f t="shared" si="52"/>
+        <v>760.32560582682845</v>
       </c>
       <c r="DX37" s="1">
-        <f t="shared" si="50"/>
-        <v>822.22178715794507</v>
+        <f t="shared" si="52"/>
+        <v>752.72234976856021</v>
       </c>
       <c r="DY37" s="1">
-        <f t="shared" si="50"/>
-        <v>813.99956928636561</v>
+        <f t="shared" si="52"/>
+        <v>745.19512627087465</v>
       </c>
       <c r="DZ37" s="1">
-        <f t="shared" si="50"/>
-        <v>805.85957359350198</v>
+        <f t="shared" si="52"/>
+        <v>737.74317500816585</v>
       </c>
       <c r="EA37" s="1">
-        <f t="shared" si="50"/>
-        <v>797.80097785756698</v>
+        <f t="shared" si="52"/>
+        <v>730.36574325808419</v>
       </c>
       <c r="EB37" s="1">
-        <f t="shared" si="50"/>
-        <v>789.82296807899127</v>
+        <f t="shared" si="52"/>
+        <v>723.06208582550335</v>
       </c>
       <c r="EC37" s="1">
-        <f t="shared" si="50"/>
-        <v>781.92473839820138</v>
+        <f t="shared" si="52"/>
+        <v>715.83146496724828</v>
       </c>
       <c r="ED37" s="1">
-        <f t="shared" si="50"/>
-        <v>774.10549101421941</v>
+        <f t="shared" si="52"/>
+        <v>708.67315031757585</v>
       </c>
       <c r="EE37" s="1">
-        <f t="shared" si="50"/>
-        <v>766.36443610407719</v>
+        <f t="shared" si="52"/>
+        <v>701.58641881440008</v>
       </c>
       <c r="EF37" s="1">
-        <f t="shared" si="50"/>
-        <v>758.70079174303646</v>
+        <f t="shared" si="52"/>
+        <v>694.57055462625613</v>
       </c>
       <c r="EG37" s="1">
-        <f t="shared" si="50"/>
-        <v>751.11378382560611</v>
+        <f t="shared" si="52"/>
+        <v>687.62484907999351</v>
       </c>
       <c r="EH37" s="1">
-        <f t="shared" si="50"/>
-        <v>743.60264598735</v>
+        <f t="shared" si="52"/>
+        <v>680.74860058919353</v>
       </c>
       <c r="EI37" s="1">
-        <f t="shared" si="50"/>
-        <v>736.16661952747654</v>
+        <f t="shared" si="52"/>
+        <v>673.94111458330156</v>
       </c>
       <c r="EJ37" s="1">
-        <f t="shared" si="50"/>
-        <v>728.80495333220176</v>
+        <f t="shared" si="52"/>
+        <v>667.2017034374685</v>
       </c>
       <c r="EK37" s="1">
-        <f t="shared" si="50"/>
-        <v>721.51690379887975</v>
+        <f t="shared" si="52"/>
+        <v>660.52968640309382</v>
       </c>
       <c r="EL37" s="1">
-        <f t="shared" si="50"/>
-        <v>714.30173476089089</v>
+        <f t="shared" si="52"/>
+        <v>653.92438953906287</v>
       </c>
       <c r="EM37" s="1">
-        <f t="shared" si="50"/>
-        <v>707.15871741328203</v>
+        <f t="shared" si="52"/>
+        <v>647.38514564367222</v>
       </c>
       <c r="EN37" s="1">
-        <f t="shared" si="50"/>
-        <v>700.08713023914925</v>
+        <f t="shared" si="52"/>
+        <v>640.91129418723551</v>
       </c>
       <c r="EO37" s="1">
-        <f t="shared" si="50"/>
-        <v>693.08625893675776</v>
+        <f t="shared" si="52"/>
+        <v>634.5021812453632</v>
       </c>
       <c r="EP37" s="1">
-        <f t="shared" si="50"/>
-        <v>686.15539634739014</v>
+        <f t="shared" si="52"/>
+        <v>628.15715943290957</v>
       </c>
       <c r="EQ37" s="1">
-        <f t="shared" si="50"/>
-        <v>679.29384238391629</v>
+        <f t="shared" si="52"/>
+        <v>621.87558783858049</v>
       </c>
       <c r="ER37" s="1">
-        <f t="shared" si="50"/>
-        <v>672.50090396007715</v>
+        <f t="shared" si="52"/>
+        <v>615.65683196019472</v>
       </c>
       <c r="ES37" s="1">
-        <f t="shared" si="50"/>
-        <v>665.77589492047639</v>
+        <f t="shared" si="52"/>
+        <v>609.50026364059272</v>
       </c>
       <c r="ET37" s="1">
-        <f t="shared" si="50"/>
-        <v>659.11813597127161</v>
+        <f t="shared" si="52"/>
+        <v>603.40526100418674</v>
       </c>
       <c r="EU37" s="1">
-        <f t="shared" si="50"/>
-        <v>652.52695461155884</v>
+        <f t="shared" si="52"/>
+        <v>597.3712083941449</v>
       </c>
       <c r="EV37" s="1">
-        <f t="shared" si="50"/>
-        <v>646.00168506544321</v>
+        <f t="shared" si="52"/>
+        <v>591.39749631020345</v>
       </c>
     </row>
     <row r="38" spans="2:152" x14ac:dyDescent="0.3">
@@ -5073,16 +5263,16 @@
         <v>43.43</v>
       </c>
       <c r="S38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="T38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="U38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="V38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="Z38" s="3">
         <v>43.43</v>
@@ -5100,37 +5290,37 @@
         <v>43.43</v>
       </c>
       <c r="AE38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AF38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AG38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AH38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AI38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AJ38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AK38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AL38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AM38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AN38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
       <c r="AO38" s="3">
-        <v>43.43</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="39" spans="2:152" x14ac:dyDescent="0.3">
@@ -5146,68 +5336,68 @@
         <v>-0.85194565968224734</v>
       </c>
       <c r="G39" s="5">
-        <f t="shared" ref="G39:P39" si="51">G37/G38</f>
+        <f t="shared" ref="G39:P39" si="53">G37/G38</f>
         <v>1.0591756850103615</v>
       </c>
       <c r="H39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.3124568270780566</v>
       </c>
       <c r="I39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.7499424361040756</v>
       </c>
       <c r="J39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>6.8385908358277687</v>
       </c>
       <c r="K39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.1052268017499425</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.3124568270780566</v>
       </c>
       <c r="M39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>2.3486069537186278</v>
       </c>
       <c r="N39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>7.529357586921483</v>
       </c>
       <c r="O39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.1512779184895234</v>
       </c>
       <c r="P39" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1.4506101772967994</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" ref="Q39:R39" si="52">Q37/Q38</f>
+        <f t="shared" ref="Q39:R39" si="54">Q37/Q38</f>
         <v>3.1084503799217131</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>10.79898687543173</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" ref="S39:V39" si="53">S37/S38</f>
-        <v>2.186613516002764</v>
+        <f t="shared" ref="S39:V39" si="55">S37/S38</f>
+        <v>1.8932481751824817</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="53"/>
-        <v>3.8761754547547782</v>
+        <f t="shared" si="55"/>
+        <v>3.261861313868613</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="53"/>
-        <v>6.8716854708726673</v>
+        <f t="shared" si="55"/>
+        <v>6.6194835766423381</v>
       </c>
       <c r="V39" s="5">
-        <f t="shared" si="53"/>
-        <v>14.316405480082892</v>
+        <f t="shared" si="55"/>
+        <v>14.521063138686129</v>
       </c>
       <c r="Z39" s="5">
         <f>Z37/Z38</f>
@@ -5226,60 +5416,88 @@
         <v>12.295648169468111</v>
       </c>
       <c r="AD39" s="5">
-        <f t="shared" ref="AD39:AO39" si="54">AD37/AD38</f>
+        <f t="shared" ref="AD39:AO39" si="56">AD37/AD38</f>
         <v>16.509325351139765</v>
       </c>
       <c r="AE39" s="5">
-        <f t="shared" si="54"/>
-        <v>27.250879921713153</v>
+        <f t="shared" si="56"/>
+        <v>26.295656204379561</v>
       </c>
       <c r="AF39" s="5">
-        <f t="shared" si="54"/>
-        <v>33.310260246373474</v>
+        <f t="shared" si="56"/>
+        <v>28.846314267791985</v>
       </c>
       <c r="AG39" s="5">
-        <f t="shared" si="54"/>
-        <v>36.711079474729445</v>
+        <f t="shared" si="56"/>
+        <v>32.627375536040134</v>
       </c>
       <c r="AH39" s="5">
-        <f t="shared" si="54"/>
-        <v>38.793480175532451</v>
+        <f t="shared" si="56"/>
+        <v>34.843754325644383</v>
       </c>
       <c r="AI39" s="5">
-        <f t="shared" si="54"/>
-        <v>40.147484144861465</v>
+        <f t="shared" si="56"/>
+        <v>36.232122775857945</v>
       </c>
       <c r="AJ39" s="5">
-        <f t="shared" si="54"/>
-        <v>40.97064948236364</v>
+        <f t="shared" si="56"/>
+        <v>37.095343076203839</v>
       </c>
       <c r="AK39" s="5">
-        <f t="shared" si="54"/>
-        <v>41.813168537690217</v>
+        <f t="shared" si="56"/>
+        <v>37.870914612555374</v>
       </c>
       <c r="AL39" s="5">
-        <f t="shared" si="54"/>
-        <v>42.675569358709971</v>
+        <f t="shared" si="56"/>
+        <v>38.664922197026613</v>
       </c>
       <c r="AM39" s="5">
-        <f t="shared" si="54"/>
-        <v>43.558396897154509</v>
+        <f t="shared" si="56"/>
+        <v>39.477857907054272</v>
       </c>
       <c r="AN39" s="5">
-        <f t="shared" si="54"/>
-        <v>44.462213636674107</v>
+        <f t="shared" si="56"/>
+        <v>40.310228542056535</v>
       </c>
       <c r="AO39" s="5">
-        <f t="shared" si="54"/>
-        <v>45.387600247078659</v>
+        <f t="shared" si="56"/>
+        <v>41.16255611726104</v>
       </c>
     </row>
     <row r="41" spans="2:152" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>86</v>
       </c>
+      <c r="O41" s="8">
+        <f t="shared" ref="O41:Q41" si="57">O10/K10-1</f>
+        <v>0.5372858689422404</v>
+      </c>
+      <c r="P41" s="8">
+        <f t="shared" si="57"/>
+        <v>0.53766190449719264</v>
+      </c>
+      <c r="Q41" s="8">
+        <f t="shared" si="57"/>
+        <v>0.41511822186218428</v>
+      </c>
       <c r="R41" s="8">
         <f>R10/N10-1</f>
+        <v>0.39818901578923427</v>
+      </c>
+      <c r="S41" s="8">
+        <f>S10/O10-1</f>
+        <v>0.34958574979287493</v>
+      </c>
+      <c r="T41" s="8">
+        <f>T10/P10-1</f>
+        <v>0.16647988142149606</v>
+      </c>
+      <c r="AC41" s="8">
+        <f>AC10/AB10-1</f>
+        <v>0.45649148386241634</v>
+      </c>
+      <c r="AD41" s="8">
+        <f>AD10/AC10-1</f>
         <v>0.39818901578923427</v>
       </c>
     </row>
@@ -5290,16 +5508,16 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8">
-        <f t="shared" ref="N42:O42" si="55">N11/J11-1</f>
+        <f t="shared" ref="N42:O42" si="58">N11/J11-1</f>
         <v>0.44099051633298214</v>
       </c>
       <c r="O42" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>0.42572887848478391</v>
       </c>
       <c r="P42" s="8">
         <f>P11/L11-1</f>
-        <v>0.61264559068219637</v>
+        <v>0.61863560732113143</v>
       </c>
       <c r="Q42" s="8">
         <f>Q11/M11-1</f>
@@ -5308,6 +5526,22 @@
       <c r="R42" s="8">
         <f>R11/N11-1</f>
         <v>0.43570122747453643</v>
+      </c>
+      <c r="S42" s="8">
+        <f>S11/O11-1</f>
+        <v>0.55633504987934423</v>
+      </c>
+      <c r="T42" s="8">
+        <f>T11/P11-1</f>
+        <v>0.29862253289473695</v>
+      </c>
+      <c r="AC42" s="8">
+        <f>AC11/AB11-1</f>
+        <v>0.44095288273370459</v>
+      </c>
+      <c r="AD42" s="8">
+        <f>AD11/AC11-1</f>
+        <v>0.43573872391548485</v>
       </c>
     </row>
     <row r="43" spans="2:152" x14ac:dyDescent="0.3">
@@ -5324,121 +5558,121 @@
         <v>53</v>
       </c>
       <c r="G44" s="8">
-        <f t="shared" ref="G44:G49" si="56">G13/C13-1</f>
+        <f t="shared" ref="G44:G49" si="59">G13/C13-1</f>
         <v>-2.7093596059113323E-2</v>
       </c>
       <c r="H44" s="8">
-        <f t="shared" ref="H44:H49" si="57">H13/D13-1</f>
+        <f t="shared" ref="H44:H49" si="60">H13/D13-1</f>
         <v>-3.2537960954446832E-2</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8">
-        <f t="shared" ref="K44:K49" si="58">K13/G13-1</f>
+        <f t="shared" ref="K44:K49" si="61">K13/G13-1</f>
         <v>0.15696202531645564</v>
       </c>
       <c r="L44" s="8">
-        <f t="shared" ref="L44:L49" si="59">L13/H13-1</f>
+        <f t="shared" ref="L44:L49" si="62">L13/H13-1</f>
         <v>0.22197309417040367</v>
       </c>
       <c r="M44" s="8">
-        <f t="shared" ref="M44:M49" si="60">M13/I13-1</f>
+        <f t="shared" ref="M44:M49" si="63">M13/I13-1</f>
         <v>0.40128755364806867</v>
       </c>
       <c r="N44" s="8">
-        <f t="shared" ref="N44:N49" si="61">N13/J13-1</f>
+        <f t="shared" ref="N44:N49" si="64">N13/J13-1</f>
         <v>-2.3305084745762761E-2</v>
       </c>
       <c r="O44" s="8">
-        <f t="shared" ref="O44" si="62">O13/K13-1</f>
+        <f t="shared" ref="O44" si="65">O13/K13-1</f>
         <v>7.0021881838074451E-2</v>
       </c>
       <c r="P44" s="8">
-        <f t="shared" ref="P44:P45" si="63">P13/L13-1</f>
+        <f t="shared" ref="P44:P45" si="66">P13/L13-1</f>
         <v>0.47706422018348627</v>
       </c>
       <c r="Q44" s="8">
-        <f t="shared" ref="Q44:Q49" si="64">Q13/M13-1</f>
+        <f t="shared" ref="Q44:Q49" si="67">Q13/M13-1</f>
         <v>0.8897396630934149</v>
       </c>
       <c r="R44" s="8">
-        <f t="shared" ref="R44:R49" si="65">R13/N13-1</f>
+        <f t="shared" ref="R44:R49" si="68">R13/N13-1</f>
         <v>0.34598698481561829</v>
       </c>
       <c r="S44" s="8">
-        <f t="shared" ref="S44:S49" si="66">S13/O13-1</f>
+        <f t="shared" ref="S44:S49" si="69">S13/O13-1</f>
+        <v>0.93251533742331283</v>
+      </c>
+      <c r="T44" s="8">
+        <f t="shared" ref="T44:T49" si="70">T13/P13-1</f>
+        <v>0.15527950310559002</v>
+      </c>
+      <c r="U44" s="8">
+        <f t="shared" ref="U44:U49" si="71">U13/Q13-1</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="V44" s="8">
+        <f t="shared" ref="V44:V49" si="72">V13/R13-1</f>
         <v>0.35000000000000009</v>
       </c>
-      <c r="T44" s="8">
-        <f t="shared" ref="T44:T49" si="67">T13/P13-1</f>
-        <v>0.5</v>
-      </c>
-      <c r="U44" s="8">
-        <f t="shared" ref="U44:U49" si="68">U13/Q13-1</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="V44" s="8">
-        <f t="shared" ref="V44:V49" si="69">V13/R13-1</f>
-        <v>0.35000000000000009</v>
-      </c>
       <c r="AA44" s="8">
-        <f t="shared" ref="AA44:AO44" si="70">AA13/Z13-1</f>
+        <f t="shared" ref="AA44:AO44" si="73">AA13/Z13-1</f>
         <v>2.5711159737417999E-2</v>
       </c>
       <c r="AB44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>0.20053333333333323</v>
       </c>
       <c r="AC44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>0.14482452243447352</v>
       </c>
       <c r="AD44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>0.46255335661622032</v>
       </c>
       <c r="AE44" s="8">
-        <f t="shared" si="70"/>
-        <v>0.36566728575218921</v>
+        <f t="shared" si="73"/>
+        <v>0.33487662509949612</v>
       </c>
       <c r="AF44" s="8">
-        <f t="shared" si="70"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="73"/>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AG44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO44" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5447,121 +5681,121 @@
         <v>54</v>
       </c>
       <c r="G45" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>2.857142857142847E-2</v>
       </c>
       <c r="H45" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.11255411255411252</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-0.19444444444444442</v>
       </c>
       <c r="L45" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>-3.5019455252918275E-2</v>
       </c>
       <c r="M45" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.66228070175438591</v>
       </c>
       <c r="N45" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>0.55606407322654472</v>
       </c>
       <c r="O45" s="8">
-        <f t="shared" ref="O45" si="71">O14/K14-1</f>
+        <f t="shared" ref="O45" si="74">O14/K14-1</f>
         <v>0.84482758620689657</v>
       </c>
       <c r="P45" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>1.560483870967742</v>
       </c>
       <c r="Q45" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>0.17941952506596315</v>
       </c>
       <c r="R45" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>0.66470588235294126</v>
       </c>
       <c r="S45" s="8">
-        <f t="shared" si="66"/>
-        <v>0.60000000000000009</v>
+        <f t="shared" si="69"/>
+        <v>0.65109034267912769</v>
       </c>
       <c r="T45" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
+        <v>4.0944881889763751E-2</v>
+      </c>
+      <c r="U45" s="8">
+        <f t="shared" si="71"/>
+        <v>0.8</v>
+      </c>
+      <c r="V45" s="8">
+        <f t="shared" si="72"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AA45" s="8">
+        <f t="shared" ref="AA45" si="75">AA14/Z14-1</f>
+        <v>1.878354203935606E-2</v>
+      </c>
+      <c r="AB45" s="8">
+        <f t="shared" ref="AB45:AC45" si="76">AB14/AA14-1</f>
+        <v>-8.779631255487752E-4</v>
+      </c>
+      <c r="AC45" s="8">
+        <f t="shared" si="76"/>
+        <v>0.30140597539543057</v>
+      </c>
+      <c r="AD45" s="8">
+        <f t="shared" ref="AD45:AO45" si="77">AD14/AC14-1</f>
+        <v>0.71168129642133704</v>
+      </c>
+      <c r="AE45" s="8">
+        <f t="shared" si="77"/>
+        <v>0.32307692307692304</v>
+      </c>
+      <c r="AF45" s="8">
+        <f t="shared" si="77"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AG45" s="8">
+        <f t="shared" si="77"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AH45" s="8">
+        <f t="shared" si="77"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="U45" s="8">
-        <f t="shared" si="68"/>
-        <v>0.7</v>
-      </c>
-      <c r="V45" s="8">
-        <f t="shared" si="69"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AA45" s="8">
-        <f t="shared" ref="AA45" si="72">AA14/Z14-1</f>
-        <v>1.878354203935606E-2</v>
-      </c>
-      <c r="AB45" s="8">
-        <f t="shared" ref="AB45:AC45" si="73">AB14/AA14-1</f>
-        <v>-8.779631255487752E-4</v>
-      </c>
-      <c r="AC45" s="8">
-        <f t="shared" si="73"/>
-        <v>0.30140597539543057</v>
-      </c>
-      <c r="AD45" s="8">
-        <f t="shared" ref="AD45:AO45" si="74">AD14/AC14-1</f>
-        <v>0.71168129642133704</v>
-      </c>
-      <c r="AE45" s="8">
-        <f t="shared" si="74"/>
-        <v>0.30124260355029575</v>
-      </c>
-      <c r="AF45" s="8">
-        <f t="shared" si="74"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="AG45" s="8">
-        <f t="shared" si="74"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AH45" s="8">
-        <f t="shared" si="74"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
       <c r="AI45" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ45" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK45" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL45" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM45" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN45" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO45" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AR45" t="s">
@@ -5576,121 +5810,121 @@
         <v>55</v>
       </c>
       <c r="G46" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-6.3829787234042534E-2</v>
       </c>
       <c r="H46" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.17283950617283961</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.4015151515151516</v>
       </c>
       <c r="L46" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.11052631578947358</v>
       </c>
       <c r="M46" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>9.6774193548387011E-2</v>
       </c>
       <c r="N46" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>-3.4642032332563466E-2</v>
       </c>
       <c r="O46" s="8">
-        <f t="shared" ref="O46:P46" si="75">O15/K15-1</f>
+        <f t="shared" ref="O46:P46" si="78">O15/K15-1</f>
         <v>0.22702702702702693</v>
       </c>
       <c r="P46" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>0.2890995260663507</v>
       </c>
       <c r="Q46" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>0.39215686274509798</v>
       </c>
       <c r="R46" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>0.27511961722488043</v>
       </c>
       <c r="S46" s="8">
-        <f t="shared" si="66"/>
-        <v>0.35000000000000031</v>
+        <f t="shared" si="69"/>
+        <v>0.47577092511013208</v>
       </c>
       <c r="T46" s="8">
-        <f t="shared" si="67"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="70"/>
+        <v>0.48161764705882359</v>
       </c>
       <c r="U46" s="8">
-        <f t="shared" si="68"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="71"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="V46" s="8">
-        <f t="shared" si="69"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="72"/>
+        <v>0.33000000000000007</v>
       </c>
       <c r="AA46" s="8">
-        <f t="shared" ref="AA46:AC46" si="76">AA15/Z15-1</f>
+        <f t="shared" ref="AA46:AC46" si="79">AA15/Z15-1</f>
         <v>-3.9948453608247392E-2</v>
       </c>
       <c r="AB46" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>0.26308724832214758</v>
       </c>
       <c r="AC46" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>8.1827842720510136E-2</v>
       </c>
       <c r="AD46" s="8">
-        <f t="shared" ref="AD46:AO46" si="77">AD15/AC15-1</f>
+        <f t="shared" ref="AD46:AO46" si="80">AD15/AC15-1</f>
         <v>0.29273084479371314</v>
       </c>
       <c r="AE46" s="8">
-        <f t="shared" si="77"/>
-        <v>0.26812310030395126</v>
+        <f t="shared" si="80"/>
+        <v>0.40158814589665637</v>
       </c>
       <c r="AF46" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
+        <v>0.21999999999999997</v>
+      </c>
+      <c r="AG46" s="8">
+        <f t="shared" si="80"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AG46" s="8">
-        <f t="shared" si="77"/>
+      <c r="AH46" s="8">
+        <f t="shared" si="80"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AH46" s="8">
-        <f t="shared" si="77"/>
+      <c r="AI46" s="8">
+        <f t="shared" si="80"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AI46" s="8">
-        <f t="shared" si="77"/>
+      <c r="AJ46" s="8">
+        <f t="shared" si="80"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AJ46" s="8">
-        <f t="shared" si="77"/>
+      <c r="AK46" s="8">
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AK46" s="8">
-        <f t="shared" si="77"/>
+      <c r="AL46" s="8">
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AL46" s="8">
-        <f t="shared" si="77"/>
+      <c r="AM46" s="8">
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AM46" s="8">
-        <f t="shared" si="77"/>
+      <c r="AN46" s="8">
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN46" s="8">
-        <f t="shared" si="77"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="AO46" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR46" t="s">
@@ -5705,121 +5939,121 @@
         <v>56</v>
       </c>
       <c r="G47" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1.3752455795677854E-2</v>
       </c>
       <c r="H47" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>9.0128755364806912E-2</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>4.8449612403100861E-2</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>-4.7244094488189003E-2</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>-3.8022813688213253E-3</v>
       </c>
       <c r="N47" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>5.9760956175298752E-2</v>
       </c>
       <c r="O47" s="8">
-        <f t="shared" ref="O47:P47" si="78">O16/K16-1</f>
+        <f t="shared" ref="O47:P47" si="81">O16/K16-1</f>
         <v>-1.848428835489857E-3</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>5.9917355371900793E-2</v>
       </c>
       <c r="Q47" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>-7.6335877862595436E-2</v>
       </c>
       <c r="R47" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>-6.9548872180451138E-2</v>
       </c>
       <c r="S47" s="8">
-        <f t="shared" si="66"/>
-        <v>-6.9999999999999951E-2</v>
+        <f t="shared" si="69"/>
+        <v>-6.6666666666666652E-2</v>
       </c>
       <c r="T47" s="8">
-        <f t="shared" si="67"/>
-        <v>-6.9999999999999951E-2</v>
+        <f t="shared" si="70"/>
+        <v>-6.4327485380117011E-2</v>
       </c>
       <c r="U47" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>-5.0000000000000044E-2</v>
       </c>
       <c r="V47" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AA47" s="8">
-        <f t="shared" ref="AA47:AC47" si="79">AA16/Z16-1</f>
+        <f t="shared" ref="AA47:AC47" si="82">AA16/Z16-1</f>
         <v>0.1166666666666667</v>
       </c>
       <c r="AB47" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>9.3816631130063888E-2</v>
       </c>
       <c r="AC47" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>1.4132553606237774E-2</v>
       </c>
       <c r="AD47" s="8">
-        <f t="shared" ref="AD47:AO47" si="80">AD16/AC16-1</f>
+        <f t="shared" ref="AD47:AO47" si="83">AD16/AC16-1</f>
         <v>-2.3546371936568944E-2</v>
       </c>
       <c r="AE47" s="8">
-        <f t="shared" si="80"/>
-        <v>-5.3056102362204705E-2</v>
+        <f t="shared" si="83"/>
+        <v>-5.0738188976378051E-2</v>
       </c>
       <c r="AF47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO47" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR47" t="s">
@@ -5827,7 +6061,7 @@
       </c>
       <c r="AS47" s="3">
         <f>NPV(AS46,AE37:EV37)</f>
-        <v>24128.998815699284</v>
+        <v>22056.291446968597</v>
       </c>
     </row>
     <row r="48" spans="2:152" x14ac:dyDescent="0.3">
@@ -5835,121 +6069,121 @@
         <v>57</v>
       </c>
       <c r="G48" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>2.5</v>
       </c>
       <c r="H48" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>-2.75</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>0.28571428571428581</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>-1.2222222222222223</v>
       </c>
       <c r="N48" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="O48" s="8">
-        <f t="shared" ref="O48:P48" si="81">O17/K17-1</f>
+        <f t="shared" ref="O48:P48" si="84">O17/K17-1</f>
         <v>-0.16666666666666663</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="Q48" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>-3</v>
       </c>
       <c r="R48" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>15</v>
       </c>
       <c r="S48" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
+        <v>-2.8</v>
+      </c>
+      <c r="T48" s="8">
+        <f t="shared" si="70"/>
+        <v>-5.3</v>
+      </c>
+      <c r="U48" s="8">
+        <f t="shared" si="71"/>
         <v>0.35000000000000009</v>
       </c>
-      <c r="T48" s="8">
-        <f t="shared" si="67"/>
-        <v>0.35000000000000009</v>
-      </c>
-      <c r="U48" s="8">
-        <f t="shared" si="68"/>
-        <v>0.35000000000000009</v>
-      </c>
       <c r="V48" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>0.5</v>
       </c>
       <c r="AA48" s="8">
-        <f t="shared" ref="AA48:AC48" si="82">AA17/Z17-1</f>
+        <f t="shared" ref="AA48:AC48" si="85">AA17/Z17-1</f>
         <v>7</v>
       </c>
       <c r="AB48" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>0.16666666666666674</v>
       </c>
       <c r="AC48" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>-0.3571428571428571</v>
       </c>
       <c r="AD48" s="8">
-        <f t="shared" ref="AD48:AO48" si="83">AD17/AC17-1</f>
+        <f t="shared" ref="AD48:AO48" si="86">AD17/AC17-1</f>
         <v>4.5</v>
       </c>
       <c r="AE48" s="8">
-        <f t="shared" si="83"/>
-        <v>0.47121212121212119</v>
+        <f t="shared" si="86"/>
+        <v>-0.25858585858585847</v>
       </c>
       <c r="AF48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="AG48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AH48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AI48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO48" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AR48" t="s">
@@ -5957,7 +6191,7 @@
       </c>
       <c r="AS48" s="3">
         <f>Main!D8</f>
-        <v>-893</v>
+        <v>-293</v>
       </c>
     </row>
     <row r="49" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5965,29 +6199,29 @@
         <v>37</v>
       </c>
       <c r="G49" s="7">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>-1.577287066246047E-3</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>6.990881458966558E-2</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>7.6619273301737678E-2</v>
       </c>
       <c r="L49" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="62"/>
         <v>6.3210227272727293E-2</v>
       </c>
       <c r="M49" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0.24240282685512371</v>
       </c>
       <c r="N49" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>0.1016803102111159</v>
       </c>
       <c r="O49" s="7">
@@ -5999,28 +6233,28 @@
         <v>0.49298597194388782</v>
       </c>
       <c r="Q49" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>0.39533560864618877</v>
       </c>
       <c r="R49" s="7">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>0.36136096988658584</v>
       </c>
       <c r="S49" s="7">
-        <f t="shared" si="66"/>
-        <v>0.25736409608091027</v>
+        <f t="shared" si="69"/>
+        <v>0.45701643489254118</v>
       </c>
       <c r="T49" s="7">
-        <f t="shared" si="67"/>
-        <v>0.21630425055928404</v>
+        <f t="shared" si="70"/>
+        <v>8.7695749440715787E-2</v>
       </c>
       <c r="U49" s="7">
-        <f t="shared" si="68"/>
-        <v>0.3039135752140234</v>
+        <f t="shared" si="71"/>
+        <v>0.28340807174887894</v>
       </c>
       <c r="V49" s="7">
-        <f t="shared" si="69"/>
-        <v>0.22908646940534316</v>
+        <f t="shared" si="72"/>
+        <v>0.24899166906061465</v>
       </c>
       <c r="Z49" s="7"/>
       <c r="AA49" s="7">
@@ -6028,67 +6262,67 @@
         <v>4.6993524514338469E-2</v>
       </c>
       <c r="AB49" s="7">
-        <f t="shared" ref="AB49:AO49" si="84">AB18/AA18-1</f>
+        <f t="shared" ref="AB49:AO49" si="87">AB18/AA18-1</f>
         <v>0.1327089591800672</v>
       </c>
       <c r="AC49" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.11934477379095165</v>
       </c>
       <c r="AD49" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.35902439024390254</v>
       </c>
       <c r="AE49" s="7">
-        <f t="shared" si="84"/>
-        <v>0.24956824941031708</v>
+        <f t="shared" si="87"/>
+        <v>0.25442928930366127</v>
       </c>
       <c r="AF49" s="7">
-        <f t="shared" si="84"/>
-        <v>0.14441574322871431</v>
+        <f t="shared" si="87"/>
+        <v>0.18248044055153967</v>
       </c>
       <c r="AG49" s="7">
-        <f t="shared" si="84"/>
-        <v>7.9138534247487069E-2</v>
+        <f t="shared" si="87"/>
+        <v>8.8590235067131706E-2</v>
       </c>
       <c r="AH49" s="7">
-        <f t="shared" si="84"/>
-        <v>4.7424709732172055E-2</v>
+        <f t="shared" si="87"/>
+        <v>5.1204538885816664E-2</v>
       </c>
       <c r="AI49" s="7">
-        <f t="shared" si="84"/>
-        <v>3.0277929975626172E-2</v>
+        <f t="shared" si="87"/>
+        <v>3.1653693802894178E-2</v>
       </c>
       <c r="AJ49" s="7">
-        <f t="shared" si="84"/>
-        <v>2.0807220867775644E-2</v>
+        <f t="shared" si="87"/>
+        <v>2.2571489574682468E-2</v>
       </c>
       <c r="AK49" s="7">
-        <f t="shared" si="84"/>
-        <v>2.0851314161579149E-2</v>
+        <f t="shared" si="87"/>
+        <v>2.0904952923547215E-2</v>
       </c>
       <c r="AL49" s="7">
-        <f t="shared" si="84"/>
-        <v>2.0895872269871552E-2</v>
+        <f t="shared" si="87"/>
+        <v>2.0941992337490944E-2</v>
       </c>
       <c r="AM49" s="7">
-        <f t="shared" si="84"/>
-        <v>2.0940906525170666E-2</v>
+        <f t="shared" si="87"/>
+        <v>2.0979260849687487E-2</v>
       </c>
       <c r="AN49" s="7">
-        <f t="shared" si="84"/>
-        <v>2.0986428459407236E-2</v>
+        <f t="shared" si="87"/>
+        <v>2.1016764161705837E-2</v>
       </c>
       <c r="AO49" s="7">
-        <f t="shared" si="84"/>
-        <v>2.1032449804873954E-2</v>
+        <f t="shared" si="87"/>
+        <v>2.1054508084077606E-2</v>
       </c>
       <c r="AR49" t="s">
         <v>62</v>
       </c>
       <c r="AS49" s="3">
         <f>AS47+AS48</f>
-        <v>23235.998815699284</v>
+        <v>21763.291446968597</v>
       </c>
     </row>
     <row r="50" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6110,52 +6344,52 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8">
-        <f t="shared" ref="K50:R50" si="85">(K18+K19)/(G18+G19)-1</f>
+        <f t="shared" ref="K50:R50" si="88">(K18+K19)/(G18+G19)-1</f>
         <v>-8.2740213523131656E-2</v>
       </c>
       <c r="L50" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>-2.874432677760963E-2</v>
       </c>
       <c r="M50" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>0.24119028974158185</v>
       </c>
       <c r="N50" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>1.7758484609313285E-2</v>
       </c>
       <c r="O50" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>0.11542192046556732</v>
       </c>
       <c r="P50" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>0.7398753894080996</v>
       </c>
       <c r="Q50" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>0.62965299684542586</v>
       </c>
       <c r="R50" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>0.40248158200853035</v>
       </c>
       <c r="S50" s="8">
-        <f t="shared" ref="S50" si="86">(S18+S19)/(O18+O19)-1</f>
-        <v>0.72969565217391308</v>
+        <f t="shared" ref="S50" si="89">(S18+S19)/(O18+O19)-1</f>
+        <v>0.78956521739130436</v>
       </c>
       <c r="T50" s="8">
-        <f t="shared" ref="T50" si="87">(T18+T19)/(P18+P19)-1</f>
-        <v>0.2168487018800358</v>
+        <f t="shared" ref="T50" si="90">(T18+T19)/(P18+P19)-1</f>
+        <v>-6.9829901521933802E-2</v>
       </c>
       <c r="U50" s="8">
-        <f t="shared" ref="U50" si="88">(U18+U19)/(Q18+Q19)-1</f>
-        <v>0.23828881145954295</v>
+        <f t="shared" ref="U50" si="91">(U18+U19)/(Q18+Q19)-1</f>
+        <v>0.21881533101045303</v>
       </c>
       <c r="V50" s="8">
-        <f t="shared" ref="V50" si="89">(V18+V19)/(R18+R19)-1</f>
-        <v>0.18287254630909588</v>
+        <f t="shared" ref="V50" si="92">(V18+V19)/(R18+R19)-1</f>
+        <v>0.20202930605474134</v>
       </c>
       <c r="Z50" s="7"/>
       <c r="AA50" s="8">
@@ -6163,67 +6397,67 @@
         <v>5.3011590347710413E-2</v>
       </c>
       <c r="AB50" s="8">
-        <f t="shared" ref="AB50:AO50" si="90">(AB18+AB19)/(AA18+AA19)-1</f>
+        <f t="shared" ref="AB50:AO50" si="93">(AB18+AB19)/(AA18+AA19)-1</f>
         <v>0.12901479610249011</v>
       </c>
       <c r="AC50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>3.548026210644073E-2</v>
       </c>
       <c r="AD50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>0.47924062355301733</v>
       </c>
       <c r="AE50" s="8">
-        <f t="shared" si="90"/>
-        <v>0.27134181969949922</v>
+        <f t="shared" si="93"/>
+        <v>0.27628756260434062</v>
       </c>
       <c r="AF50" s="8">
-        <f t="shared" si="90"/>
-        <v>0.14441574322871431</v>
+        <f t="shared" si="93"/>
+        <v>0.18248044055153967</v>
       </c>
       <c r="AG50" s="8">
-        <f t="shared" si="90"/>
-        <v>7.9138534247487069E-2</v>
+        <f t="shared" si="93"/>
+        <v>8.8590235067131706E-2</v>
       </c>
       <c r="AH50" s="8">
-        <f t="shared" si="90"/>
-        <v>4.7424709732172055E-2</v>
+        <f t="shared" si="93"/>
+        <v>5.1204538885816664E-2</v>
       </c>
       <c r="AI50" s="8">
-        <f t="shared" si="90"/>
-        <v>3.0277929975626172E-2</v>
+        <f t="shared" si="93"/>
+        <v>3.1653693802894178E-2</v>
       </c>
       <c r="AJ50" s="8">
-        <f t="shared" si="90"/>
-        <v>2.0807220867775644E-2</v>
+        <f t="shared" si="93"/>
+        <v>2.2571489574682468E-2</v>
       </c>
       <c r="AK50" s="8">
-        <f t="shared" si="90"/>
-        <v>2.0851314161579149E-2</v>
+        <f t="shared" si="93"/>
+        <v>2.0904952923547215E-2</v>
       </c>
       <c r="AL50" s="8">
-        <f t="shared" si="90"/>
-        <v>2.0895872269871552E-2</v>
+        <f t="shared" si="93"/>
+        <v>2.0941992337490944E-2</v>
       </c>
       <c r="AM50" s="8">
-        <f t="shared" si="90"/>
-        <v>2.0940906525170666E-2</v>
+        <f t="shared" si="93"/>
+        <v>2.0979260849687487E-2</v>
       </c>
       <c r="AN50" s="8">
-        <f t="shared" si="90"/>
-        <v>2.0986428459407236E-2</v>
+        <f t="shared" si="93"/>
+        <v>2.1016764161705837E-2</v>
       </c>
       <c r="AO50" s="8">
-        <f t="shared" si="90"/>
-        <v>2.1032449804873954E-2</v>
+        <f t="shared" si="93"/>
+        <v>2.1054508084077606E-2</v>
       </c>
       <c r="AR50" t="s">
         <v>63</v>
       </c>
       <c r="AS50" s="2">
         <f>AS49/AO38</f>
-        <v>535.021847011266</v>
+        <v>496.42544358961209</v>
       </c>
     </row>
     <row r="51" spans="2:45" x14ac:dyDescent="0.3">
@@ -6241,67 +6475,67 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8">
-        <f t="shared" ref="G51:P51" si="91">G23/G18</f>
+        <f t="shared" ref="G51:P51" si="94">G23/G18</f>
         <v>0.2109004739336493</v>
       </c>
       <c r="H51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.22443181818181818</v>
       </c>
       <c r="I51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.22332155477031801</v>
       </c>
       <c r="J51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.27789745799224475</v>
       </c>
       <c r="K51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.22157006603081439</v>
       </c>
       <c r="L51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.22845691382765532</v>
       </c>
       <c r="M51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.24402730375426621</v>
       </c>
       <c r="N51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.31912397340633553</v>
       </c>
       <c r="O51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.24905183312262957</v>
       </c>
       <c r="P51" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>0.25548098434004474</v>
       </c>
       <c r="Q51" s="8">
-        <f t="shared" ref="Q51:R51" si="92">Q23/Q18</f>
+        <f t="shared" ref="Q51:R51" si="95">Q23/Q18</f>
         <v>0.23685283326538931</v>
       </c>
       <c r="R51" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>0.3274920999712726</v>
       </c>
       <c r="S51" s="8">
-        <f t="shared" ref="S51:V51" si="93">S23/S18</f>
-        <v>0.25</v>
+        <f t="shared" ref="S51:V51" si="96">S23/S18</f>
+        <v>0.23514099783080261</v>
       </c>
       <c r="T51" s="8">
-        <f t="shared" si="93"/>
-        <v>0.25</v>
+        <f t="shared" si="96"/>
+        <v>0.24475524475524477</v>
       </c>
       <c r="U51" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>0.26</v>
       </c>
       <c r="V51" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>0.34</v>
       </c>
       <c r="Z51" s="8">
@@ -6313,67 +6547,67 @@
         <v>0.24527301643399893</v>
       </c>
       <c r="AB51" s="8">
-        <f t="shared" ref="AB51:AO51" si="94">AB23/AB18</f>
+        <f t="shared" ref="AB51:AO51" si="97">AB23/AB18</f>
         <v>0.24087363494539782</v>
       </c>
       <c r="AC51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>0.26327526132404183</v>
       </c>
       <c r="AD51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>0.27545892728950877</v>
       </c>
       <c r="AE51" s="8">
-        <f t="shared" si="94"/>
-        <v>0.28422743082627672</v>
+        <f t="shared" si="97"/>
+        <v>0.28072109575423032</v>
       </c>
       <c r="AF51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="AG51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>0.24999999999999997</v>
       </c>
       <c r="AH51" s="8">
-        <f t="shared" si="94"/>
-        <v>0.24999999999999997</v>
+        <f t="shared" si="97"/>
+        <v>0.25</v>
       </c>
       <c r="AI51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
+        <v>0.25</v>
+      </c>
+      <c r="AJ51" s="8">
+        <f t="shared" si="97"/>
+        <v>0.25</v>
+      </c>
+      <c r="AK51" s="8">
+        <f t="shared" si="97"/>
+        <v>0.25000000000000006</v>
+      </c>
+      <c r="AL51" s="8">
+        <f t="shared" si="97"/>
         <v>0.24999999999999994</v>
       </c>
-      <c r="AJ51" s="8">
-        <f t="shared" si="94"/>
+      <c r="AM51" s="8">
+        <f t="shared" si="97"/>
+        <v>0.24999999999999994</v>
+      </c>
+      <c r="AN51" s="8">
+        <f t="shared" si="97"/>
         <v>0.25</v>
       </c>
-      <c r="AK51" s="8">
-        <f t="shared" si="94"/>
+      <c r="AO51" s="8">
+        <f t="shared" si="97"/>
         <v>0.25</v>
-      </c>
-      <c r="AL51" s="8">
-        <f t="shared" si="94"/>
-        <v>0.25</v>
-      </c>
-      <c r="AM51" s="8">
-        <f t="shared" si="94"/>
-        <v>0.24999999999999994</v>
-      </c>
-      <c r="AN51" s="8">
-        <f t="shared" si="94"/>
-        <v>0.25</v>
-      </c>
-      <c r="AO51" s="8">
-        <f t="shared" si="94"/>
-        <v>0.25000000000000006</v>
       </c>
       <c r="AR51" t="s">
         <v>64</v>
       </c>
       <c r="AS51" s="2">
         <f>Main!D3</f>
-        <v>1417</v>
+        <v>1744.5</v>
       </c>
     </row>
     <row r="52" spans="2:45" x14ac:dyDescent="0.3">
@@ -6391,131 +6625,131 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8">
-        <f t="shared" ref="G52:N52" si="95">G20/G18</f>
+        <f t="shared" ref="G52:N52" si="98">G20/G18</f>
         <v>0.54028436018957349</v>
       </c>
       <c r="H52" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0.50710227272727271</v>
       </c>
       <c r="I52" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0.56325088339222618</v>
       </c>
       <c r="J52" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0.42567858681602755</v>
       </c>
       <c r="K52" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0.65517241379310343</v>
       </c>
       <c r="L52" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0.57515030060120242</v>
       </c>
       <c r="M52" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0.57281001137656429</v>
       </c>
       <c r="N52" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>0.45913179507235041</v>
       </c>
       <c r="O52" s="8">
-        <f t="shared" ref="O52:P52" si="96">O20/O18</f>
+        <f t="shared" ref="O52:P52" si="99">O20/O18</f>
         <v>0.65676359039190901</v>
       </c>
       <c r="P52" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="99"/>
         <v>0.48635346756152126</v>
       </c>
       <c r="Q52" s="8">
-        <f t="shared" ref="Q52:R52" si="97">Q20/Q18</f>
+        <f t="shared" ref="Q52:R52" si="100">Q20/Q18</f>
         <v>0.47696697920913167</v>
       </c>
       <c r="R52" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="100"/>
         <v>0.44900890548692907</v>
       </c>
       <c r="S52" s="8">
-        <f t="shared" ref="S52:V52" si="98">S20/S18</f>
-        <v>0</v>
+        <f t="shared" ref="S52:V52" si="101">S20/S18</f>
+        <v>0.57006507592190891</v>
       </c>
       <c r="T52" s="8">
-        <f t="shared" si="98"/>
-        <v>0</v>
+        <f t="shared" si="101"/>
+        <v>0.61085972850678738</v>
       </c>
       <c r="U52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="V52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="Z52" s="8">
-        <f t="shared" ref="Z52:AO52" si="99">Z20/Z18</f>
+        <f t="shared" ref="Z52:AO52" si="102">Z20/Z18</f>
         <v>0.51655874190564288</v>
       </c>
       <c r="AA52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.48506803322141723</v>
       </c>
       <c r="AB52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.49656786271450859</v>
       </c>
       <c r="AC52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5484320557491289</v>
       </c>
       <c r="AD52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.49830786585991182</v>
       </c>
       <c r="AE52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="AF52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AG52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AH52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AI52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AJ52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AK52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AL52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AM52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AN52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AO52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="102"/>
         <v>0.5</v>
       </c>
       <c r="AR52" s="1" t="s">
@@ -6523,7 +6757,7 @@
       </c>
       <c r="AS52" s="7">
         <f>AS50/AS51-1</f>
-        <v>-0.62242636061307977</v>
+        <v>-0.71543396756112809</v>
       </c>
     </row>
     <row r="53" spans="2:45" x14ac:dyDescent="0.3">
@@ -6541,131 +6775,131 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8">
-        <f t="shared" ref="G53:N53" si="100">G21/G18</f>
+        <f t="shared" ref="G53:N53" si="103">G21/G18</f>
         <v>0.3609794628751975</v>
       </c>
       <c r="H53" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>0.32954545454545453</v>
       </c>
       <c r="I53" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>0.31095406360424027</v>
       </c>
       <c r="J53" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>0.20465316673847481</v>
       </c>
       <c r="K53" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>0.36683785766691124</v>
       </c>
       <c r="L53" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>0.33867735470941884</v>
       </c>
       <c r="M53" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>0.28156996587030719</v>
       </c>
       <c r="N53" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="103"/>
         <v>0.21314039890496675</v>
       </c>
       <c r="O53" s="8">
-        <f t="shared" ref="O53:P53" si="101">O21/O18</f>
+        <f t="shared" ref="O53:P53" si="104">O21/O18</f>
         <v>0.36725663716814161</v>
       </c>
       <c r="P53" s="8">
-        <f t="shared" si="101"/>
+        <f t="shared" si="104"/>
         <v>0.25861297539149886</v>
       </c>
       <c r="Q53" s="8">
-        <f t="shared" ref="Q53:R53" si="102">Q21/Q18</f>
+        <f t="shared" ref="Q53:R53" si="105">Q21/Q18</f>
         <v>0.23318385650224216</v>
       </c>
       <c r="R53" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="105"/>
         <v>0.18442976156276933</v>
       </c>
       <c r="S53" s="8">
-        <f t="shared" ref="S53:V53" si="103">S21/S18</f>
-        <v>0</v>
+        <f t="shared" ref="S53:V53" si="106">S21/S18</f>
+        <v>0.30195227765726679</v>
       </c>
       <c r="T53" s="8">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <f t="shared" si="106"/>
+        <v>0.2895927601809955</v>
       </c>
       <c r="U53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="V53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="Z53" s="8">
-        <f t="shared" ref="Z53:AO53" si="104">Z21/Z18</f>
+        <f t="shared" ref="Z53:AO53" si="107">Z21/Z18</f>
         <v>0.28436632747456059</v>
       </c>
       <c r="AA53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.29033398126877541</v>
       </c>
       <c r="AB53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.28642745709828393</v>
       </c>
       <c r="AC53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.28529616724738677</v>
       </c>
       <c r="AD53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.24335965541995694</v>
       </c>
       <c r="AE53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="AF53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AG53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AH53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AI53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AJ53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AK53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AL53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AM53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AN53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AO53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="107"/>
         <v>0.25</v>
       </c>
       <c r="AR53" t="s">
@@ -6684,128 +6918,128 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8">
-        <f t="shared" ref="G54:V54" si="105">G25/C25-1</f>
+        <f t="shared" ref="G54:V54" si="108">G25/C25-1</f>
         <v>0.38095238095238093</v>
       </c>
       <c r="H54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="I54" s="8" t="e">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J54" s="8" t="e">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.10344827586206895</v>
       </c>
       <c r="L54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>-0.4358974358974359</v>
       </c>
       <c r="M54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>-0.22641509433962259</v>
       </c>
       <c r="N54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>-0.42000000000000004</v>
       </c>
       <c r="O54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.3125</v>
       </c>
       <c r="P54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.77272727272727271</v>
       </c>
       <c r="Q54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.24390243902439024</v>
       </c>
       <c r="R54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.65517241379310343</v>
       </c>
       <c r="S54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="T54" s="8">
+        <f t="shared" si="108"/>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="U54" s="8">
+        <f t="shared" si="108"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="T54" s="8">
-        <f t="shared" si="105"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="U54" s="8">
-        <f t="shared" si="105"/>
-        <v>0.30000000000000004</v>
-      </c>
       <c r="V54" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="108"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8">
-        <f t="shared" ref="AA54:AO54" si="106">AA25/Z25-1</f>
+        <f t="shared" ref="AA54:AO54" si="109">AA25/Z25-1</f>
         <v>0.17543859649122817</v>
       </c>
       <c r="AB54" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>0.64925373134328357</v>
       </c>
       <c r="AC54" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>-0.30769230769230771</v>
       </c>
       <c r="AD54" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>0.49019607843137258</v>
       </c>
       <c r="AE54" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>-1</v>
       </c>
       <c r="AF54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO54" s="8" t="e">
-        <f t="shared" si="106"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AS54" s="4"/>
@@ -6829,51 +7063,51 @@
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8">
-        <f t="shared" ref="K55:P55" si="107">K26/G26-1</f>
+        <f t="shared" ref="K55:P55" si="110">K26/G26-1</f>
         <v>0.18954248366013071</v>
       </c>
       <c r="L55" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.10240963855421681</v>
       </c>
       <c r="M55" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.12886597938144329</v>
       </c>
       <c r="N55" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.19607843137254899</v>
       </c>
       <c r="O55" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.25274725274725274</v>
       </c>
       <c r="P55" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="110"/>
         <v>0.51366120218579225</v>
       </c>
       <c r="Q55" s="8">
-        <f t="shared" ref="Q55:R55" si="108">Q26/M26-1</f>
+        <f t="shared" ref="Q55:R55" si="111">Q26/M26-1</f>
         <v>0.12785388127853881</v>
       </c>
       <c r="R55" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="111"/>
         <v>0.20655737704918042</v>
       </c>
       <c r="S55" s="8">
-        <f t="shared" ref="S55" si="109">S26/O26-1</f>
-        <v>0.19999999999999996</v>
+        <f t="shared" ref="S55" si="112">S26/O26-1</f>
+        <v>0.25877192982456143</v>
       </c>
       <c r="T55" s="8">
-        <f t="shared" ref="T55" si="110">T26/P26-1</f>
-        <v>0.19999999999999996</v>
+        <f t="shared" ref="T55" si="113">T26/P26-1</f>
+        <v>3.6101083032491044E-2</v>
       </c>
       <c r="U55" s="8">
-        <f t="shared" ref="U55" si="111">U26/Q26-1</f>
+        <f t="shared" ref="U55" si="114">U26/Q26-1</f>
         <v>0.14999999999999991</v>
       </c>
       <c r="V55" s="8">
-        <f t="shared" ref="V55" si="112">V26/R26-1</f>
+        <f t="shared" ref="V55" si="115">V26/R26-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="Z55" s="8"/>
@@ -6882,59 +7116,59 @@
         <v>2.1806853582554409E-2</v>
       </c>
       <c r="AB55" s="8">
-        <f t="shared" ref="AB55:AO55" si="113">AB26/AA26-1</f>
+        <f t="shared" ref="AB55:AO55" si="116">AB26/AA26-1</f>
         <v>0.1707317073170731</v>
       </c>
       <c r="AC55" s="8">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>0.15755208333333326</v>
       </c>
       <c r="AD55" s="8">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>0.25984251968503935</v>
       </c>
       <c r="AE55" s="8">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>-1</v>
       </c>
       <c r="AF55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO55" s="8" t="e">
-        <f t="shared" si="113"/>
+        <f t="shared" si="116"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6953,68 +7187,68 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8">
-        <f t="shared" ref="G56:P56" si="114">G28/G18</f>
+        <f t="shared" ref="G56:P56" si="117">G28/G18</f>
         <v>6.5560821484992107E-2</v>
       </c>
       <c r="H56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>9.0198863636363633E-2</v>
       </c>
       <c r="I56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>7.9151943462897528E-2</v>
       </c>
       <c r="J56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>0.18354157690650583</v>
       </c>
       <c r="K56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>6.5297138664710194E-2</v>
       </c>
       <c r="L56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>7.8824315297261194E-2</v>
       </c>
       <c r="M56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>9.7838452787258251E-2</v>
       </c>
       <c r="N56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>0.18224481814626514</v>
       </c>
       <c r="O56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>7.3957016434892539E-2</v>
       </c>
       <c r="P56" s="8">
-        <f t="shared" si="114"/>
+        <f t="shared" si="117"/>
         <v>0.10827740492170022</v>
       </c>
       <c r="Q56" s="8">
-        <f t="shared" ref="Q56:R56" si="115">Q28/Q18</f>
+        <f t="shared" ref="Q56:R56" si="118">Q28/Q18</f>
         <v>0.11822258459029759</v>
       </c>
       <c r="R56" s="8">
-        <f t="shared" si="115"/>
+        <f t="shared" si="118"/>
         <v>0.21315713875323183</v>
       </c>
       <c r="S56" s="8">
-        <f t="shared" ref="S56:V56" si="116">S28/S18</f>
-        <v>9.2143629188346815E-2</v>
+        <f t="shared" ref="S56:V56" si="119">S28/S18</f>
+        <v>7.7657266811279824E-2</v>
       </c>
       <c r="T56" s="8">
-        <f t="shared" si="116"/>
-        <v>0.11142787775341741</v>
+        <f t="shared" si="119"/>
+        <v>9.5433977786918964E-2</v>
       </c>
       <c r="U56" s="8">
-        <f t="shared" si="116"/>
-        <v>0.16221979052680943</v>
+        <f t="shared" si="119"/>
+        <v>0.16065751858204694</v>
       </c>
       <c r="V56" s="8">
-        <f t="shared" si="116"/>
-        <v>0.24417090301394198</v>
+        <f t="shared" si="119"/>
+        <v>0.24569813282302994</v>
       </c>
       <c r="Z56" s="8">
         <f>Z28/Z18</f>
@@ -7025,60 +7259,60 @@
         <v>0.10867644460151971</v>
       </c>
       <c r="AB56" s="8">
-        <f t="shared" ref="AB56:AO56" si="117">AB28/AB18</f>
+        <f t="shared" ref="AB56:AO56" si="120">AB28/AB18</f>
         <v>0.11669266770670828</v>
       </c>
       <c r="AC56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="120"/>
         <v>0.11777003484320557</v>
       </c>
       <c r="AD56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="120"/>
         <v>0.14265203568864732</v>
       </c>
       <c r="AE56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.16822387221840154</v>
+        <f t="shared" si="120"/>
+        <v>0.16228117534912698</v>
       </c>
       <c r="AF56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17225268559008933</v>
+        <f t="shared" si="120"/>
+        <v>0.14482962071884012</v>
       </c>
       <c r="AG56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17507244953244938</v>
+        <f t="shared" si="120"/>
+        <v>0.14952399816845571</v>
       </c>
       <c r="AH56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17631892654001738</v>
+        <f t="shared" si="120"/>
+        <v>0.15155076575660423</v>
       </c>
       <c r="AI56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17705396015717792</v>
+        <f t="shared" si="120"/>
+        <v>0.15266286106328875</v>
       </c>
       <c r="AJ56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17711164349285485</v>
+        <f t="shared" si="120"/>
+        <v>0.15290763753178707</v>
       </c>
       <c r="AK56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17717242696763513</v>
+        <f t="shared" si="120"/>
+        <v>0.15299370236771342</v>
       </c>
       <c r="AL56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17723633574122696</v>
+        <f t="shared" si="120"/>
+        <v>0.15308320714834123</v>
       </c>
       <c r="AM56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.1773033952605966</v>
+        <f t="shared" si="120"/>
+        <v>0.15317616380726287</v>
       </c>
       <c r="AN56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17737363125768565</v>
+        <f t="shared" si="120"/>
+        <v>0.15327258436576421</v>
       </c>
       <c r="AO56" s="8">
-        <f t="shared" si="117"/>
-        <v>0.17744706974659077</v>
+        <f t="shared" si="120"/>
+        <v>0.15337248093439074</v>
       </c>
     </row>
     <row r="57" spans="2:45" x14ac:dyDescent="0.3">
@@ -7096,67 +7330,67 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8">
-        <f t="shared" ref="G57:P57" si="118">G35/G34</f>
+        <f t="shared" ref="G57:P57" si="121">G35/G34</f>
         <v>0.20547945205479451</v>
       </c>
       <c r="H57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.30612244897959184</v>
       </c>
       <c r="I57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.27027027027027029</v>
       </c>
       <c r="J57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.24713958810068651</v>
       </c>
       <c r="K57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.28985507246376813</v>
       </c>
       <c r="L57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.29807692307692307</v>
       </c>
       <c r="M57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.24827586206896551</v>
       </c>
       <c r="N57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.19758064516129031</v>
       </c>
       <c r="O57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.36046511627906974</v>
       </c>
       <c r="P57" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="121"/>
         <v>0.26923076923076922</v>
       </c>
       <c r="Q57" s="8">
-        <f t="shared" ref="Q57:R57" si="119">Q35/Q34</f>
+        <f t="shared" ref="Q57:R57" si="122">Q35/Q34</f>
         <v>0.29959514170040485</v>
       </c>
       <c r="R57" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="122"/>
         <v>0.25036390101892286</v>
       </c>
       <c r="S57" s="8">
-        <f t="shared" ref="S57:V57" si="120">S35/S34</f>
+        <f t="shared" ref="S57:V57" si="123">S35/S34</f>
+        <v>0.26712328767123289</v>
+      </c>
+      <c r="T57" s="8">
+        <f t="shared" si="123"/>
+        <v>0.23766816143497757</v>
+      </c>
+      <c r="U57" s="8">
+        <f t="shared" si="123"/>
         <v>0.27</v>
       </c>
-      <c r="T57" s="8">
-        <f t="shared" si="120"/>
-        <v>0.27</v>
-      </c>
-      <c r="U57" s="8">
-        <f t="shared" si="120"/>
-        <v>0.27</v>
-      </c>
       <c r="V57" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="123"/>
         <v>0.27</v>
       </c>
       <c r="Z57" s="8">
@@ -7168,59 +7402,59 @@
         <v>0.25773195876288657</v>
       </c>
       <c r="AB57" s="8">
-        <f t="shared" ref="AB57:AO57" si="121">AB35/AB34</f>
+        <f t="shared" ref="AB57:AO57" si="124">AB35/AB34</f>
         <v>0.25452016689847012</v>
       </c>
       <c r="AC57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.22727272727272727</v>
       </c>
       <c r="AD57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.27117263843648209</v>
       </c>
       <c r="AE57" s="8">
-        <f t="shared" si="121"/>
-        <v>0.26999999999999974</v>
+        <f t="shared" si="124"/>
+        <v>0.26585351686982805</v>
       </c>
       <c r="AF57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AG57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AH57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AI57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AJ57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AK57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AL57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AM57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AN57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AO57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
     </row>
@@ -7239,131 +7473,131 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8">
-        <f t="shared" ref="G58:N58" si="122">G36/G34</f>
+        <f t="shared" ref="G58:N58" si="125">G36/G34</f>
         <v>0.16438356164383561</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>0.11224489795918367</v>
       </c>
       <c r="I58" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>4.5045045045045043E-2</v>
       </c>
       <c r="J58" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>7.3226544622425629E-2</v>
       </c>
       <c r="K58" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>1.4492753623188406E-2</v>
       </c>
       <c r="L58" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>0.15384615384615385</v>
       </c>
       <c r="M58" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>4.8275862068965517E-2</v>
       </c>
       <c r="N58" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="125"/>
         <v>0.14314516129032259</v>
       </c>
       <c r="O58" s="8">
-        <f t="shared" ref="O58:P58" si="123">O36/O34</f>
+        <f t="shared" ref="O58:P58" si="126">O36/O34</f>
         <v>5.8139534883720929E-2</v>
       </c>
       <c r="P58" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="126"/>
         <v>0.42788461538461536</v>
       </c>
       <c r="Q58" s="8">
-        <f t="shared" ref="Q58:R58" si="124">Q36/Q34</f>
+        <f t="shared" ref="Q58:R58" si="127">Q36/Q34</f>
         <v>0.15384615384615385</v>
       </c>
       <c r="R58" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="127"/>
         <v>6.6957787481804948E-2</v>
       </c>
       <c r="S58" s="8">
-        <f t="shared" ref="S58:V58" si="125">S36/S34</f>
+        <f t="shared" ref="S58:V58" si="128">S36/S34</f>
+        <v>0.16438356164383561</v>
+      </c>
+      <c r="T58" s="8">
+        <f t="shared" si="128"/>
+        <v>0.1210762331838565</v>
+      </c>
+      <c r="U58" s="8">
+        <f t="shared" si="128"/>
         <v>0.1</v>
       </c>
-      <c r="T58" s="8">
-        <f t="shared" si="125"/>
+      <c r="V58" s="8">
+        <f t="shared" si="128"/>
         <v>0.1</v>
       </c>
-      <c r="U58" s="8">
-        <f t="shared" si="125"/>
+      <c r="Z58" s="8">
+        <f t="shared" ref="Z58:AO58" si="129">Z36/Z34</f>
+        <v>0.84699453551912574</v>
+      </c>
+      <c r="AA58" s="8">
+        <f t="shared" si="129"/>
+        <v>0.2422680412371134</v>
+      </c>
+      <c r="AB58" s="8">
+        <f t="shared" si="129"/>
+        <v>8.3449235048678724E-2</v>
+      </c>
+      <c r="AC58" s="8">
+        <f t="shared" si="129"/>
+        <v>0.1167076167076167</v>
+      </c>
+      <c r="AD58" s="8">
+        <f t="shared" si="129"/>
+        <v>0.14495114006514659</v>
+      </c>
+      <c r="AE58" s="8">
+        <f t="shared" si="129"/>
+        <v>0.10766257039782763</v>
+      </c>
+      <c r="AF58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="V58" s="8">
-        <f t="shared" si="125"/>
+      <c r="AG58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="Z58" s="8">
-        <f t="shared" ref="Z58:AO58" si="126">Z36/Z34</f>
-        <v>0.84699453551912574</v>
-      </c>
-      <c r="AA58" s="8">
-        <f t="shared" si="126"/>
-        <v>0.2422680412371134</v>
-      </c>
-      <c r="AB58" s="8">
-        <f t="shared" si="126"/>
-        <v>8.3449235048678724E-2</v>
-      </c>
-      <c r="AC58" s="8">
-        <f t="shared" si="126"/>
-        <v>0.1167076167076167</v>
-      </c>
-      <c r="AD58" s="8">
-        <f t="shared" si="126"/>
-        <v>0.14495114006514659</v>
-      </c>
-      <c r="AE58" s="8">
-        <f t="shared" si="126"/>
-        <v>9.9999999999999867E-2</v>
-      </c>
-      <c r="AF58" s="8">
-        <f t="shared" si="126"/>
+      <c r="AH58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AG58" s="8">
-        <f t="shared" si="126"/>
+      <c r="AI58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AH58" s="8">
-        <f t="shared" si="126"/>
+      <c r="AJ58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AI58" s="8">
-        <f t="shared" si="126"/>
-        <v>0.10000000000000002</v>
-      </c>
-      <c r="AJ58" s="8">
-        <f t="shared" si="126"/>
+      <c r="AK58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AK58" s="8">
-        <f t="shared" si="126"/>
+      <c r="AL58" s="8">
+        <f t="shared" si="129"/>
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="AL58" s="8">
-        <f t="shared" si="126"/>
+      <c r="AM58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AM58" s="8">
-        <f t="shared" si="126"/>
-        <v>0.1</v>
-      </c>
       <c r="AN58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="129"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AO58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
     </row>
@@ -7382,68 +7616,68 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8">
-        <f t="shared" ref="G59:P59" si="127">G37/G23</f>
+        <f t="shared" ref="G59:P59" si="130">G37/G23</f>
         <v>0.17228464419475656</v>
       </c>
       <c r="H59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.18037974683544303</v>
       </c>
       <c r="I59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.24050632911392406</v>
       </c>
       <c r="J59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.46046511627906977</v>
       </c>
       <c r="K59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.15894039735099338</v>
       </c>
       <c r="L59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.16666666666666666</v>
       </c>
       <c r="M59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.23776223776223776</v>
       </c>
       <c r="N59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.40073529411764708</v>
       </c>
       <c r="O59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.12690355329949238</v>
       </c>
       <c r="P59" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="130"/>
         <v>0.11033274956217162</v>
       </c>
       <c r="Q59" s="8">
-        <f t="shared" ref="Q59:R59" si="128">Q37/Q23</f>
+        <f t="shared" ref="Q59:R59" si="131">Q37/Q23</f>
         <v>0.23235800344234078</v>
       </c>
       <c r="R59" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="131"/>
         <v>0.41140350877192983</v>
       </c>
       <c r="S59" s="8">
-        <f t="shared" ref="S59:V59" si="129">S37/S23</f>
-        <v>0.19096523640751081</v>
+        <f t="shared" ref="S59:V59" si="132">S37/S23</f>
+        <v>0.15313653136531366</v>
       </c>
       <c r="T59" s="8">
-        <f t="shared" si="129"/>
-        <v>0.2477042715675167</v>
+        <f t="shared" si="132"/>
+        <v>0.24033613445378152</v>
       </c>
       <c r="U59" s="8">
-        <f t="shared" si="129"/>
-        <v>0.35886689674246336</v>
+        <f t="shared" si="132"/>
+        <v>0.35453489906320107</v>
       </c>
       <c r="V59" s="8">
-        <f t="shared" si="129"/>
-        <v>0.42742354467292648</v>
+        <f t="shared" si="132"/>
+        <v>0.43065200879212695</v>
       </c>
       <c r="Z59" s="8">
         <f>Z37/Z23</f>
@@ -7454,81 +7688,113 @@
         <v>0.20965417867435157</v>
       </c>
       <c r="AB59" s="8">
-        <f t="shared" ref="AB59:AO59" si="130">AB37/AB23</f>
+        <f t="shared" ref="AB59:AO59" si="133">AB37/AB23</f>
         <v>0.30829015544041449</v>
       </c>
       <c r="AC59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="133"/>
         <v>0.2826892535733192</v>
       </c>
       <c r="AD59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="133"/>
         <v>0.26693968726731199</v>
       </c>
       <c r="AE59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.34173954115299549</v>
+        <f t="shared" si="133"/>
+        <v>0.33572537375607336</v>
       </c>
       <c r="AF59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.414987375305857</v>
+        <f t="shared" si="133"/>
+        <v>0.34972893031511876</v>
       </c>
       <c r="AG59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42381547793598917</v>
+        <f t="shared" si="133"/>
+        <v>0.36337825603635282</v>
       </c>
       <c r="AH59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42757823014744234</v>
+        <f t="shared" si="133"/>
+        <v>0.36915989195074828</v>
       </c>
       <c r="AI59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42949763997803064</v>
+        <f t="shared" si="133"/>
+        <v>0.37209120858808414</v>
       </c>
       <c r="AJ59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42936986613862543</v>
+        <f t="shared" si="133"/>
+        <v>0.37254723270260126</v>
       </c>
       <c r="AK59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42924900768422652</v>
+        <f t="shared" si="133"/>
+        <v>0.37254816858219397</v>
       </c>
       <c r="AL59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42913515833395388</v>
+        <f t="shared" si="133"/>
+        <v>0.37255698683391375</v>
       </c>
       <c r="AM59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42902841368837119</v>
+        <f t="shared" si="133"/>
+        <v>0.37257373111457714</v>
       </c>
       <c r="AN59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42892887125019491</v>
+        <f t="shared" si="133"/>
+        <v>0.37259844583108448</v>
       </c>
       <c r="AO59" s="8">
-        <f t="shared" si="130"/>
-        <v>0.42883663044386711</v>
+        <f t="shared" si="133"/>
+        <v>0.37263117615639341</v>
       </c>
     </row>
     <row r="61" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>92</v>
       </c>
+      <c r="O61" s="3">
+        <f t="shared" ref="O61:V61" si="134">O37</f>
+        <v>50</v>
+      </c>
+      <c r="P61" s="3">
+        <f t="shared" si="134"/>
+        <v>63</v>
+      </c>
+      <c r="Q61" s="3">
+        <f t="shared" si="134"/>
+        <v>135</v>
+      </c>
+      <c r="R61" s="3">
+        <f t="shared" si="134"/>
+        <v>469</v>
+      </c>
+      <c r="S61" s="3">
+        <f t="shared" si="134"/>
+        <v>83</v>
+      </c>
+      <c r="T61" s="3">
+        <f t="shared" si="134"/>
+        <v>143</v>
+      </c>
+      <c r="U61" s="3">
+        <f t="shared" si="134"/>
+        <v>290.19816000000014</v>
+      </c>
+      <c r="V61" s="3">
+        <f t="shared" si="134"/>
+        <v>636.60340799999994</v>
+      </c>
       <c r="Y61" s="3"/>
       <c r="Z61" s="3">
-        <f t="shared" ref="Z61:AC61" si="131">Z37</f>
+        <f t="shared" ref="Z61:AC61" si="135">Z37</f>
         <v>-27</v>
       </c>
       <c r="AA61" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="135"/>
         <v>291</v>
       </c>
       <c r="AB61" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="135"/>
         <v>476</v>
       </c>
       <c r="AC61" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="135"/>
         <v>534</v>
       </c>
       <c r="AD61" s="3">
@@ -7536,54 +7802,84 @@
         <v>717</v>
       </c>
       <c r="AE61" s="3">
-        <f t="shared" ref="AE61:AO61" si="132">AE37</f>
-        <v>1183.5057150000023</v>
+        <f t="shared" ref="AE61:AO61" si="136">AE37</f>
+        <v>1152.8015680000001</v>
       </c>
       <c r="AF61" s="3">
-        <f t="shared" si="132"/>
-        <v>1446.6646025</v>
+        <f t="shared" si="136"/>
+        <v>1264.6224175000007</v>
       </c>
       <c r="AG61" s="3">
-        <f t="shared" si="132"/>
-        <v>1594.3621815874999</v>
+        <f t="shared" si="136"/>
+        <v>1430.3841434999997</v>
       </c>
       <c r="AH61" s="3">
-        <f t="shared" si="132"/>
-        <v>1684.8008440233743</v>
+        <f t="shared" si="136"/>
+        <v>1527.5501896362498</v>
       </c>
       <c r="AI61" s="3">
-        <f t="shared" si="132"/>
-        <v>1743.6052364113334</v>
+        <f t="shared" si="136"/>
+        <v>1588.4162624936125</v>
       </c>
       <c r="AJ61" s="3">
-        <f t="shared" si="132"/>
-        <v>1779.3553070190528</v>
+        <f t="shared" si="136"/>
+        <v>1626.2598404607766</v>
       </c>
       <c r="AK61" s="3">
-        <f t="shared" si="132"/>
-        <v>1815.945909591886</v>
+        <f t="shared" si="136"/>
+        <v>1660.2608966144278</v>
       </c>
       <c r="AL61" s="3">
-        <f t="shared" si="132"/>
-        <v>1853.3999772487739</v>
+        <f t="shared" si="136"/>
+        <v>1695.0701891176468</v>
       </c>
       <c r="AM61" s="3">
-        <f t="shared" si="132"/>
-        <v>1891.7411772434202</v>
+        <f t="shared" si="136"/>
+        <v>1730.7092906452594</v>
       </c>
       <c r="AN61" s="3">
-        <f t="shared" si="132"/>
-        <v>1930.9939382407565</v>
+        <f t="shared" si="136"/>
+        <v>1767.2004192837585</v>
       </c>
       <c r="AO61" s="3">
-        <f t="shared" si="132"/>
-        <v>1971.1834787306261</v>
+        <f t="shared" si="136"/>
+        <v>1804.5664601807241</v>
       </c>
     </row>
     <row r="62" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="O62" s="6">
+        <v>54</v>
+      </c>
+      <c r="P62" s="6">
+        <f>133-O62</f>
+        <v>79</v>
+      </c>
+      <c r="Q62" s="6">
+        <f>306-P62-O62</f>
+        <v>173</v>
+      </c>
+      <c r="R62" s="6">
+        <f>AD62-Q62-P62-O62</f>
+        <v>502</v>
+      </c>
+      <c r="S62" s="6">
+        <v>108</v>
+      </c>
+      <c r="T62" s="6">
+        <f>267-S62</f>
+        <v>159</v>
+      </c>
+      <c r="U62" s="6">
+        <f>U61</f>
+        <v>290.19816000000014</v>
+      </c>
+      <c r="V62" s="6">
+        <f>V61</f>
+        <v>636.60340799999994</v>
+      </c>
       <c r="Y62" s="1">
         <v>354</v>
       </c>
@@ -7603,54 +7899,84 @@
         <v>808</v>
       </c>
       <c r="AE62" s="6">
-        <f>AE61</f>
-        <v>1183.5057150000023</v>
+        <f>AE61*1.1</f>
+        <v>1268.0817248000003</v>
       </c>
       <c r="AF62" s="6">
-        <f t="shared" ref="AF62:AO62" si="133">AF61</f>
-        <v>1446.6646025</v>
+        <f t="shared" ref="AF62:AO62" si="137">AF61*1.1</f>
+        <v>1391.0846592500009</v>
       </c>
       <c r="AG62" s="6">
-        <f t="shared" si="133"/>
-        <v>1594.3621815874999</v>
+        <f t="shared" si="137"/>
+        <v>1573.4225578499997</v>
       </c>
       <c r="AH62" s="6">
-        <f t="shared" si="133"/>
-        <v>1684.8008440233743</v>
+        <f t="shared" si="137"/>
+        <v>1680.305208599875</v>
       </c>
       <c r="AI62" s="6">
-        <f t="shared" si="133"/>
-        <v>1743.6052364113334</v>
+        <f t="shared" si="137"/>
+        <v>1747.2578887429738</v>
       </c>
       <c r="AJ62" s="6">
-        <f t="shared" si="133"/>
-        <v>1779.3553070190528</v>
+        <f t="shared" si="137"/>
+        <v>1788.8858245068543</v>
       </c>
       <c r="AK62" s="6">
-        <f t="shared" si="133"/>
-        <v>1815.945909591886</v>
+        <f t="shared" si="137"/>
+        <v>1826.2869862758707</v>
       </c>
       <c r="AL62" s="6">
-        <f t="shared" si="133"/>
-        <v>1853.3999772487739</v>
+        <f t="shared" si="137"/>
+        <v>1864.5772080294116</v>
       </c>
       <c r="AM62" s="6">
-        <f t="shared" si="133"/>
-        <v>1891.7411772434202</v>
+        <f t="shared" si="137"/>
+        <v>1903.7802197097856</v>
       </c>
       <c r="AN62" s="6">
-        <f t="shared" si="133"/>
-        <v>1930.9939382407565</v>
+        <f t="shared" si="137"/>
+        <v>1943.9204612121346</v>
       </c>
       <c r="AO62" s="6">
-        <f t="shared" si="133"/>
-        <v>1971.1834787306261</v>
+        <f t="shared" si="137"/>
+        <v>1985.0231061987968</v>
       </c>
     </row>
     <row r="63" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>12</v>
       </c>
+      <c r="O63" s="3">
+        <v>91</v>
+      </c>
+      <c r="P63" s="3">
+        <f>181-O63</f>
+        <v>90</v>
+      </c>
+      <c r="Q63" s="3">
+        <f>277-P63-O63</f>
+        <v>96</v>
+      </c>
+      <c r="R63" s="3">
+        <f>AD63-Q63-P63-O63</f>
+        <v>126</v>
+      </c>
+      <c r="S63" s="3">
+        <v>112</v>
+      </c>
+      <c r="T63" s="3">
+        <f>239-S63</f>
+        <v>127</v>
+      </c>
+      <c r="U63">
+        <f>Q63*1.4</f>
+        <v>134.39999999999998</v>
+      </c>
+      <c r="V63">
+        <f>R63*1.4</f>
+        <v>176.39999999999998</v>
+      </c>
       <c r="Y63" s="3">
         <v>280</v>
       </c>
@@ -7670,54 +7996,59 @@
         <v>403</v>
       </c>
       <c r="AE63" s="3">
-        <f>AD63*1.2</f>
-        <v>483.59999999999997</v>
+        <f>SUM(S63:V63)</f>
+        <v>549.79999999999995</v>
       </c>
       <c r="AF63" s="3">
         <f>AE63*1.15</f>
-        <v>556.13999999999987</v>
+        <v>632.26999999999987</v>
       </c>
       <c r="AG63" s="3">
         <f>AF63*1.1</f>
-        <v>611.75399999999991</v>
+        <v>695.49699999999996</v>
       </c>
       <c r="AH63" s="3">
         <f>AG63*1.05</f>
-        <v>642.34169999999995</v>
+        <v>730.27184999999997</v>
       </c>
       <c r="AI63" s="3">
         <f>AH63*1.04</f>
-        <v>668.03536799999995</v>
+        <v>759.48272399999996</v>
       </c>
       <c r="AJ63" s="3">
         <f>AI63*1.03</f>
-        <v>688.07642903999999</v>
+        <v>782.26720571999999</v>
       </c>
       <c r="AK63" s="3">
         <f>AJ63*1.02</f>
-        <v>701.83795762080001</v>
+        <v>797.91254983440001</v>
       </c>
       <c r="AL63" s="3">
-        <f t="shared" ref="AL63:AO63" si="134">AK63*1.02</f>
-        <v>715.87471677321605</v>
+        <f t="shared" ref="AL63:AO63" si="138">AK63*1.02</f>
+        <v>813.87080083108799</v>
       </c>
       <c r="AM63" s="3">
-        <f t="shared" si="134"/>
-        <v>730.19221110868034</v>
+        <f t="shared" si="138"/>
+        <v>830.14821684770982</v>
       </c>
       <c r="AN63" s="3">
-        <f t="shared" si="134"/>
-        <v>744.79605533085396</v>
+        <f t="shared" si="138"/>
+        <v>846.75118118466401</v>
       </c>
       <c r="AO63" s="3">
-        <f t="shared" si="134"/>
-        <v>759.691976437471</v>
+        <f t="shared" si="138"/>
+        <v>863.68620480835727</v>
       </c>
     </row>
     <row r="64" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>94</v>
       </c>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
       <c r="AA64" s="3">
@@ -7733,6 +8064,7 @@
         <v>0</v>
       </c>
       <c r="AE64" s="3">
+        <f t="shared" ref="AE64:AE73" si="139">SUM(S64:V64)</f>
         <v>0</v>
       </c>
       <c r="AF64" s="3">
@@ -7770,6 +8102,36 @@
       <c r="B65" t="s">
         <v>95</v>
       </c>
+      <c r="O65" s="3">
+        <f>-3-6</f>
+        <v>-9</v>
+      </c>
+      <c r="P65" s="3">
+        <f>-7-O65</f>
+        <v>2</v>
+      </c>
+      <c r="Q65" s="3">
+        <f>-13-5-P65-O65</f>
+        <v>-11</v>
+      </c>
+      <c r="R65" s="3">
+        <f t="shared" ref="R65:R69" si="140">AD65-Q65-P65-O65</f>
+        <v>-6</v>
+      </c>
+      <c r="S65" s="3">
+        <f>-4-3</f>
+        <v>-7</v>
+      </c>
+      <c r="T65" s="3">
+        <f>14-S65</f>
+        <v>21</v>
+      </c>
+      <c r="U65">
+        <v>-10</v>
+      </c>
+      <c r="V65">
+        <v>-25</v>
+      </c>
       <c r="Y65" s="3">
         <f>-20-2</f>
         <v>-22</v>
@@ -7791,46 +8153,85 @@
         <v>-12</v>
       </c>
       <c r="AD65" s="3">
-        <v>-18</v>
+        <f>-18-6</f>
+        <v>-24</v>
       </c>
       <c r="AE65" s="3">
-        <v>-30</v>
+        <f t="shared" si="139"/>
+        <v>-21</v>
       </c>
       <c r="AF65" s="3">
-        <v>-30</v>
+        <f>AE65*1.1</f>
+        <v>-23.1</v>
       </c>
       <c r="AG65" s="3">
-        <v>-30</v>
+        <f t="shared" ref="AG65:AO65" si="141">AF65*1.1</f>
+        <v>-25.410000000000004</v>
       </c>
       <c r="AH65" s="3">
-        <v>-30</v>
+        <f t="shared" si="141"/>
+        <v>-27.951000000000008</v>
       </c>
       <c r="AI65" s="3">
-        <v>-30</v>
+        <f t="shared" si="141"/>
+        <v>-30.746100000000009</v>
       </c>
       <c r="AJ65" s="3">
-        <v>-30</v>
+        <f t="shared" si="141"/>
+        <v>-33.820710000000012</v>
       </c>
       <c r="AK65" s="3">
-        <v>-30</v>
+        <f t="shared" si="141"/>
+        <v>-37.202781000000016</v>
       </c>
       <c r="AL65" s="3">
-        <v>-30</v>
+        <f t="shared" si="141"/>
+        <v>-40.923059100000017</v>
       </c>
       <c r="AM65" s="3">
-        <v>-30</v>
+        <f t="shared" si="141"/>
+        <v>-45.015365010000025</v>
       </c>
       <c r="AN65" s="3">
-        <v>-30</v>
+        <f t="shared" si="141"/>
+        <v>-49.516901511000029</v>
       </c>
       <c r="AO65" s="3">
-        <v>-30</v>
+        <f t="shared" si="141"/>
+        <v>-54.468591662100039</v>
       </c>
     </row>
     <row r="66" spans="2:139" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>96</v>
       </c>
+      <c r="O66" s="3">
+        <v>1</v>
+      </c>
+      <c r="P66" s="3">
+        <f>69-O66</f>
+        <v>68</v>
+      </c>
+      <c r="Q66" s="3">
+        <f>66-P66-O66</f>
+        <v>-3</v>
+      </c>
+      <c r="R66" s="3">
+        <f t="shared" si="140"/>
+        <v>37</v>
+      </c>
+      <c r="S66" s="3">
+        <v>0</v>
+      </c>
+      <c r="T66" s="3">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66" s="3">
+        <v>0</v>
+      </c>
       <c r="Y66" s="3">
         <v>0</v>
       </c>
@@ -7847,46 +8248,75 @@
         <v>-48</v>
       </c>
       <c r="AD66" s="3">
-        <v>-6</v>
+        <v>103</v>
       </c>
       <c r="AE66" s="3">
-        <v>-6</v>
+        <f t="shared" si="139"/>
+        <v>0</v>
       </c>
       <c r="AF66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AG66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AH66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AI66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AK66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AL66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AM66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AN66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AO66" s="3">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="2:139" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>97</v>
       </c>
+      <c r="O67" s="3">
+        <v>93</v>
+      </c>
+      <c r="P67" s="3">
+        <f>16-O67</f>
+        <v>-77</v>
+      </c>
+      <c r="Q67" s="3">
+        <f>94-P67-O67</f>
+        <v>78</v>
+      </c>
+      <c r="R67" s="3">
+        <f t="shared" si="140"/>
+        <v>41</v>
+      </c>
+      <c r="S67" s="3">
+        <v>90</v>
+      </c>
+      <c r="T67" s="3">
+        <f>-15-S67</f>
+        <v>-105</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>110</v>
+      </c>
       <c r="Y67" s="3">
         <v>23</v>
       </c>
@@ -7903,10 +8333,11 @@
         <v>-59</v>
       </c>
       <c r="AD67" s="3">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="AE67" s="3">
-        <v>0</v>
+        <f t="shared" si="139"/>
+        <v>95</v>
       </c>
       <c r="AF67" s="3">
         <v>0</v>
@@ -7943,6 +8374,35 @@
       <c r="B68" t="s">
         <v>98</v>
       </c>
+      <c r="O68" s="3">
+        <v>-202</v>
+      </c>
+      <c r="P68" s="3">
+        <f>-74-O68</f>
+        <v>128</v>
+      </c>
+      <c r="Q68" s="3">
+        <f>-151-P68-O68</f>
+        <v>-77</v>
+      </c>
+      <c r="R68" s="3">
+        <f t="shared" si="140"/>
+        <v>558</v>
+      </c>
+      <c r="S68" s="3">
+        <v>122</v>
+      </c>
+      <c r="T68" s="3">
+        <f>-669-S68</f>
+        <v>-791</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <f>R68*1.5</f>
+        <v>837</v>
+      </c>
       <c r="Y68" s="3">
         <v>31</v>
       </c>
@@ -7959,10 +8419,11 @@
         <v>29</v>
       </c>
       <c r="AD68" s="3">
-        <v>135</v>
+        <v>407</v>
       </c>
       <c r="AE68" s="3">
-        <v>0</v>
+        <f t="shared" si="139"/>
+        <v>168</v>
       </c>
       <c r="AF68" s="3">
         <v>0</v>
@@ -7999,6 +8460,34 @@
       <c r="B69" t="s">
         <v>99</v>
       </c>
+      <c r="O69" s="3">
+        <v>-145</v>
+      </c>
+      <c r="P69" s="3">
+        <f>-159-O69</f>
+        <v>-14</v>
+      </c>
+      <c r="Q69" s="3">
+        <f>-174-P69-O69</f>
+        <v>-15</v>
+      </c>
+      <c r="R69" s="3">
+        <f t="shared" si="140"/>
+        <v>72</v>
+      </c>
+      <c r="S69" s="3">
+        <v>-5</v>
+      </c>
+      <c r="T69" s="3">
+        <f>-100-S69</f>
+        <v>-95</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
       <c r="Y69" s="3">
         <v>-68</v>
       </c>
@@ -8015,10 +8504,11 @@
         <v>-217</v>
       </c>
       <c r="AD69" s="3">
-        <v>407</v>
+        <v>-102</v>
       </c>
       <c r="AE69" s="3">
-        <v>0</v>
+        <f t="shared" si="139"/>
+        <v>-100</v>
       </c>
       <c r="AF69" s="3">
         <v>0</v>
@@ -8055,6 +8545,11 @@
       <c r="B70" t="s">
         <v>100</v>
       </c>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
       <c r="AA70" s="3"/>
@@ -8063,9 +8558,10 @@
         <v>39</v>
       </c>
       <c r="AD70" s="3">
-        <v>-102</v>
+        <v>0</v>
       </c>
       <c r="AE70" s="3">
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="AF70" s="3">
@@ -8103,6 +8599,34 @@
       <c r="B71" t="s">
         <v>101</v>
       </c>
+      <c r="O71" s="3">
+        <v>1</v>
+      </c>
+      <c r="P71" s="3">
+        <f>4-O71</f>
+        <v>3</v>
+      </c>
+      <c r="Q71" s="3">
+        <f>16-P71-O71</f>
+        <v>12</v>
+      </c>
+      <c r="R71" s="3">
+        <f t="shared" ref="R71:R73" si="142">AD71-Q71-P71-O71</f>
+        <v>-1</v>
+      </c>
+      <c r="S71" s="3">
+        <v>4</v>
+      </c>
+      <c r="T71" s="3">
+        <f>4-S71</f>
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
       <c r="Y71" s="3">
         <v>-37</v>
       </c>
@@ -8122,7 +8646,8 @@
         <v>15</v>
       </c>
       <c r="AE71" s="3">
-        <v>0</v>
+        <f t="shared" si="139"/>
+        <v>4</v>
       </c>
       <c r="AF71" s="3">
         <v>0</v>
@@ -8159,6 +8684,33 @@
       <c r="B72" t="s">
         <v>102</v>
       </c>
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3">
+        <f>9-P72-O72</f>
+        <v>9</v>
+      </c>
+      <c r="R72" s="3">
+        <f t="shared" si="142"/>
+        <v>7</v>
+      </c>
+      <c r="S72" s="3">
+        <v>6</v>
+      </c>
+      <c r="T72" s="3">
+        <f>8-S72</f>
+        <v>2</v>
+      </c>
+      <c r="U72">
+        <v>3</v>
+      </c>
+      <c r="V72">
+        <v>5</v>
+      </c>
       <c r="Y72" s="3">
         <v>17</v>
       </c>
@@ -8178,43 +8730,72 @@
         <v>16</v>
       </c>
       <c r="AE72" s="3">
+        <f t="shared" si="139"/>
         <v>16</v>
       </c>
       <c r="AF72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AH72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AK72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AM72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AN72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AO72" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="2:139" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>103</v>
       </c>
+      <c r="O73" s="3">
+        <v>11</v>
+      </c>
+      <c r="P73" s="3">
+        <f>29-O73</f>
+        <v>18</v>
+      </c>
+      <c r="Q73" s="3">
+        <f>67-P73-O73</f>
+        <v>38</v>
+      </c>
+      <c r="R73" s="3">
+        <f t="shared" si="142"/>
+        <v>-109</v>
+      </c>
+      <c r="S73" s="3">
+        <v>-10</v>
+      </c>
+      <c r="T73" s="3">
+        <f>-25-S73</f>
+        <v>-15</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
       <c r="Y73" s="3">
         <v>24</v>
       </c>
@@ -8234,7 +8815,8 @@
         <v>-42</v>
       </c>
       <c r="AE73" s="3">
-        <v>0</v>
+        <f t="shared" si="139"/>
+        <v>-25</v>
       </c>
       <c r="AF73" s="3">
         <v>0</v>
@@ -8271,79 +8853,141 @@
       <c r="B74" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="O74" s="6">
+        <f t="shared" ref="O74:P74" si="143">O62+SUM(O63:O73)</f>
+        <v>-105</v>
+      </c>
+      <c r="P74" s="6">
+        <f t="shared" si="143"/>
+        <v>297</v>
+      </c>
+      <c r="Q74" s="6">
+        <f t="shared" ref="Q74:R74" si="144">Q62+SUM(Q63:Q73)</f>
+        <v>300</v>
+      </c>
+      <c r="R74" s="6">
+        <f t="shared" si="144"/>
+        <v>1227</v>
+      </c>
+      <c r="S74" s="6">
+        <f t="shared" ref="S74:V74" si="145">S62+SUM(S63:S73)</f>
+        <v>420</v>
+      </c>
+      <c r="T74" s="6">
+        <f t="shared" si="145"/>
+        <v>-697</v>
+      </c>
+      <c r="U74" s="6">
+        <f>U62+SUM(U63:U73)</f>
+        <v>417.59816000000012</v>
+      </c>
+      <c r="V74" s="6">
+        <f>V62+SUM(V63:V73)</f>
+        <v>1740.003408</v>
+      </c>
       <c r="Y74" s="6">
-        <f t="shared" ref="Y74:AD74" si="135">Y62+SUM(Y63:Y73)</f>
+        <f t="shared" ref="Y74:AD74" si="146">Y62+SUM(Y63:Y73)</f>
         <v>602</v>
       </c>
       <c r="Z74" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="146"/>
         <v>453</v>
       </c>
       <c r="AA74" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="146"/>
         <v>690</v>
       </c>
       <c r="AB74" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="146"/>
         <v>174</v>
       </c>
       <c r="AC74" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="146"/>
         <v>742</v>
       </c>
       <c r="AD74" s="6">
-        <f t="shared" si="135"/>
+        <f t="shared" si="146"/>
         <v>1719</v>
       </c>
       <c r="AE74" s="6">
-        <f t="shared" ref="AE74:AO74" si="136">AE62+SUM(AE63:AE73)</f>
-        <v>1647.1057150000022</v>
+        <f t="shared" ref="AE74:AO74" si="147">AE62+SUM(AE63:AE73)</f>
+        <v>1954.8817248000003</v>
       </c>
       <c r="AF74" s="6">
-        <f t="shared" si="136"/>
-        <v>1982.8046024999999</v>
+        <f t="shared" si="147"/>
+        <v>2000.2546592500007</v>
       </c>
       <c r="AG74" s="6">
-        <f t="shared" si="136"/>
-        <v>2186.1161815874998</v>
+        <f t="shared" si="147"/>
+        <v>2243.5095578499995</v>
       </c>
       <c r="AH74" s="6">
-        <f t="shared" si="136"/>
-        <v>2307.1425440233743</v>
+        <f t="shared" si="147"/>
+        <v>2382.6260585998748</v>
       </c>
       <c r="AI74" s="6">
-        <f t="shared" si="136"/>
-        <v>2391.6406044113332</v>
+        <f t="shared" si="147"/>
+        <v>2475.9945127429737</v>
       </c>
       <c r="AJ74" s="6">
-        <f t="shared" si="136"/>
-        <v>2447.431736059053</v>
+        <f t="shared" si="147"/>
+        <v>2537.3323202268543</v>
       </c>
       <c r="AK74" s="6">
-        <f t="shared" si="136"/>
-        <v>2497.7838672126859</v>
+        <f t="shared" si="147"/>
+        <v>2586.9967551102709</v>
       </c>
       <c r="AL74" s="6">
-        <f t="shared" si="136"/>
-        <v>2549.2746940219899</v>
+        <f t="shared" si="147"/>
+        <v>2637.5249497604996</v>
       </c>
       <c r="AM74" s="6">
-        <f t="shared" si="136"/>
-        <v>2601.9333883521003</v>
+        <f t="shared" si="147"/>
+        <v>2688.9130715474953</v>
       </c>
       <c r="AN74" s="6">
-        <f t="shared" si="136"/>
-        <v>2655.7899935716105</v>
+        <f t="shared" si="147"/>
+        <v>2741.1547408857987</v>
       </c>
       <c r="AO74" s="6">
-        <f t="shared" si="136"/>
-        <v>2710.8754551680972</v>
+        <f t="shared" si="147"/>
+        <v>2794.240719345054</v>
       </c>
     </row>
     <row r="75" spans="2:139" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>105</v>
       </c>
+      <c r="O75" s="3">
+        <v>105</v>
+      </c>
+      <c r="P75" s="3">
+        <f>232-O75</f>
+        <v>127</v>
+      </c>
+      <c r="Q75" s="3">
+        <f>416-P75-O75</f>
+        <v>184</v>
+      </c>
+      <c r="R75" s="3">
+        <f>AD75-Q75-P75-O75</f>
+        <v>316</v>
+      </c>
+      <c r="S75" s="3">
+        <v>153</v>
+      </c>
+      <c r="T75" s="3">
+        <f>352-S75</f>
+        <v>199</v>
+      </c>
+      <c r="U75" s="3">
+        <f t="shared" ref="U75:V75" si="148">Q75*1.45</f>
+        <v>266.8</v>
+      </c>
+      <c r="V75" s="3">
+        <f t="shared" si="148"/>
+        <v>458.2</v>
+      </c>
       <c r="Y75" s="3">
         <v>288</v>
       </c>
@@ -8363,548 +9007,600 @@
         <v>732</v>
       </c>
       <c r="AE75" s="3">
-        <v>1000</v>
+        <f>SUM(S75:V75)</f>
+        <v>1077</v>
       </c>
       <c r="AF75" s="3">
-        <f>AE75*0.9</f>
-        <v>900</v>
+        <f>AE75*1.1</f>
+        <v>1184.7</v>
       </c>
       <c r="AG75" s="3">
-        <f t="shared" ref="AG75:AJ75" si="137">AF75*0.9</f>
-        <v>810</v>
+        <f t="shared" ref="AG75:AJ75" si="149">AF75*0.9</f>
+        <v>1066.23</v>
       </c>
       <c r="AH75" s="3">
-        <f t="shared" si="137"/>
-        <v>729</v>
+        <f t="shared" si="149"/>
+        <v>959.60700000000008</v>
       </c>
       <c r="AI75" s="3">
-        <f t="shared" si="137"/>
-        <v>656.1</v>
+        <f t="shared" si="149"/>
+        <v>863.64630000000011</v>
       </c>
       <c r="AJ75" s="3">
-        <f t="shared" si="137"/>
-        <v>590.49</v>
+        <f t="shared" si="149"/>
+        <v>777.28167000000008</v>
       </c>
       <c r="AK75" s="3">
         <f>AJ75*0.95</f>
-        <v>560.96550000000002</v>
+        <v>738.41758650000008</v>
       </c>
       <c r="AL75" s="3">
-        <f t="shared" ref="AL75:AO75" si="138">AK75*0.95</f>
-        <v>532.91722500000003</v>
+        <f t="shared" ref="AL75:AO75" si="150">AK75*0.95</f>
+        <v>701.4967071750001</v>
       </c>
       <c r="AM75" s="3">
-        <f t="shared" si="138"/>
-        <v>506.27136374999998</v>
+        <f t="shared" si="150"/>
+        <v>666.42187181625002</v>
       </c>
       <c r="AN75" s="3">
-        <f t="shared" si="138"/>
-        <v>480.95779556249994</v>
+        <f t="shared" si="150"/>
+        <v>633.10077822543747</v>
       </c>
       <c r="AO75" s="3">
-        <f t="shared" si="138"/>
-        <v>456.90990578437493</v>
+        <f t="shared" si="150"/>
+        <v>601.44573931416562</v>
       </c>
     </row>
     <row r="76" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="O76" s="6">
+        <f t="shared" ref="O76:P76" si="151">O74-O75</f>
+        <v>-210</v>
+      </c>
+      <c r="P76" s="6">
+        <f t="shared" si="151"/>
+        <v>170</v>
+      </c>
+      <c r="Q76" s="6">
+        <f t="shared" ref="Q76:R76" si="152">Q74-Q75</f>
+        <v>116</v>
+      </c>
+      <c r="R76" s="6">
+        <f t="shared" si="152"/>
+        <v>911</v>
+      </c>
+      <c r="S76" s="6">
+        <f t="shared" ref="S76:V76" si="153">S74-S75</f>
+        <v>267</v>
+      </c>
+      <c r="T76" s="6">
+        <f t="shared" si="153"/>
+        <v>-896</v>
+      </c>
+      <c r="U76" s="6">
+        <f t="shared" si="153"/>
+        <v>150.79816000000011</v>
+      </c>
+      <c r="V76" s="6">
+        <f t="shared" si="153"/>
+        <v>1281.803408</v>
+      </c>
       <c r="Y76" s="6">
-        <f t="shared" ref="Y76:AD76" si="139">Y74-Y75</f>
+        <f t="shared" ref="Y76:AD76" si="154">Y74-Y75</f>
         <v>314</v>
       </c>
       <c r="Z76" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="154"/>
         <v>216</v>
       </c>
       <c r="AA76" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="154"/>
         <v>419</v>
       </c>
       <c r="AB76" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="154"/>
         <v>-175</v>
       </c>
       <c r="AC76" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="154"/>
         <v>344</v>
       </c>
       <c r="AD76" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="154"/>
         <v>987</v>
       </c>
       <c r="AE76" s="6">
-        <f t="shared" ref="AE76:AO76" si="140">AE74-AE75</f>
-        <v>647.10571500000219</v>
+        <f t="shared" ref="AE76:AO76" si="155">AE74-AE75</f>
+        <v>877.88172480000026</v>
       </c>
       <c r="AF76" s="6">
-        <f t="shared" si="140"/>
-        <v>1082.8046024999999</v>
+        <f t="shared" si="155"/>
+        <v>815.55465925000067</v>
       </c>
       <c r="AG76" s="6">
-        <f t="shared" si="140"/>
-        <v>1376.1161815874998</v>
+        <f t="shared" si="155"/>
+        <v>1177.2795578499995</v>
       </c>
       <c r="AH76" s="6">
-        <f t="shared" si="140"/>
-        <v>1578.1425440233743</v>
+        <f t="shared" si="155"/>
+        <v>1423.0190585998748</v>
       </c>
       <c r="AI76" s="6">
-        <f t="shared" si="140"/>
-        <v>1735.5406044113333</v>
+        <f t="shared" si="155"/>
+        <v>1612.3482127429736</v>
       </c>
       <c r="AJ76" s="6">
-        <f t="shared" si="140"/>
-        <v>1856.941736059053</v>
+        <f t="shared" si="155"/>
+        <v>1760.0506502268543</v>
       </c>
       <c r="AK76" s="6">
-        <f t="shared" si="140"/>
-        <v>1936.8183672126859</v>
+        <f t="shared" si="155"/>
+        <v>1848.5791686102707</v>
       </c>
       <c r="AL76" s="6">
-        <f t="shared" si="140"/>
-        <v>2016.3574690219898</v>
+        <f t="shared" si="155"/>
+        <v>1936.0282425854994</v>
       </c>
       <c r="AM76" s="6">
-        <f t="shared" si="140"/>
-        <v>2095.6620246021002</v>
+        <f t="shared" si="155"/>
+        <v>2022.4911997312452</v>
       </c>
       <c r="AN76" s="6">
-        <f t="shared" si="140"/>
-        <v>2174.8321980091105</v>
+        <f t="shared" si="155"/>
+        <v>2108.0539626603613</v>
       </c>
       <c r="AO76" s="6">
-        <f t="shared" si="140"/>
-        <v>2253.9655493837222</v>
+        <f t="shared" si="155"/>
+        <v>2192.7949800308884</v>
       </c>
       <c r="AP76" s="1">
         <f>AO76*(1+AS45)</f>
-        <v>2231.4258938898852</v>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AQ76" s="1">
-        <f t="shared" ref="AQ76:DB76" si="141">AP76*(1+AT45)</f>
-        <v>2231.4258938898852</v>
+        <f t="shared" ref="AQ76:DB76" si="156">AP76*(1+AT45)</f>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AR76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AS76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AT76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AU76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AV76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AW76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AX76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AY76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="AZ76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BA76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BB76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BC76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BD76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BE76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BF76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BG76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BH76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BI76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BJ76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BK76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BL76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BM76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BN76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BO76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BP76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BQ76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BR76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BS76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BT76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BU76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BV76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BW76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BX76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BY76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="BZ76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CA76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CB76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CC76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CD76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CE76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CF76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CG76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CH76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CI76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CJ76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CK76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CL76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CM76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CN76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CO76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CP76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CQ76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CR76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CS76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CT76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CU76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CV76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CW76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CX76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CY76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="CZ76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DA76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DB76" s="1">
-        <f t="shared" si="141"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="156"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DC76" s="1">
-        <f t="shared" ref="DC76:EI76" si="142">DB76*(1+DF45)</f>
-        <v>2231.4258938898852</v>
+        <f t="shared" ref="DC76:EI76" si="157">DB76*(1+DF45)</f>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DD76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DE76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DF76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DG76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DH76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DI76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DJ76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DK76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DL76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DM76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DN76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DO76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DP76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DQ76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DR76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DS76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DT76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DU76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DV76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DW76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DX76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DY76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="DZ76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="EA76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="EB76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="EC76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="ED76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="EE76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="EF76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="EG76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="EH76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
       <c r="EI76" s="1">
-        <f t="shared" si="142"/>
-        <v>2231.4258938898852</v>
+        <f t="shared" si="157"/>
+        <v>2170.8670302305795</v>
       </c>
     </row>
     <row r="78" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>107</v>
+      </c>
+      <c r="S78" s="8">
+        <f>S75/O75-1</f>
+        <v>0.45714285714285707</v>
+      </c>
+      <c r="T78" s="8">
+        <f t="shared" ref="T78:V78" si="158">T75/P75-1</f>
+        <v>0.56692913385826782</v>
+      </c>
+      <c r="U78" s="8">
+        <f t="shared" si="158"/>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="V78" s="8">
+        <f t="shared" si="158"/>
+        <v>0.44999999999999996</v>
+      </c>
       <c r="AS78" s="3">
         <f>NPV(AS46,AE76:EI76)</f>
-        <v>27173.392518958393</v>
+        <v>26107.609767880786</v>
       </c>
     </row>
     <row r="79" spans="2:139" x14ac:dyDescent="0.3">
       <c r="AS79" s="3">
         <f>AS48</f>
-        <v>-893</v>
+        <v>-293</v>
       </c>
     </row>
     <row r="80" spans="2:139" x14ac:dyDescent="0.3">
       <c r="AS80" s="3">
         <f>AS78+AS79</f>
-        <v>26280.392518958393</v>
+        <v>25814.609767880786</v>
       </c>
     </row>
     <row r="81" spans="45:45" x14ac:dyDescent="0.3">
       <c r="AS81" s="12">
         <f>AS80/AO38</f>
-        <v>605.12071192628127</v>
+        <v>588.83690163961637</v>
       </c>
     </row>
     <row r="82" spans="45:45" x14ac:dyDescent="0.3">
       <c r="AS82" s="12">
         <f>Main!D3</f>
-        <v>1417</v>
+        <v>1744.5</v>
       </c>
     </row>
     <row r="83" spans="45:45" x14ac:dyDescent="0.3">
       <c r="AS83" s="7">
         <f>AS81/AS82-1</f>
-        <v>-0.57295644888759267</v>
+        <v>-0.66246093342527002</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RHM.xlsx
+++ b/Financial Analysis/RHM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53DF77D-AF69-4553-80AE-F91A8C70426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C026707B-15E6-4172-B8A3-B6085C43B931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45906</v>
+        <v>45930</v>
       </c>
       <c r="G3" s="11">
         <v>45967</v>
@@ -2878,7 +2878,6 @@
       <c r="AD21" s="3">
         <v>2373</v>
       </c>
-      <c r="AE21" s="3"/>
       <c r="AF21" s="3">
         <f>AF18*0.25</f>
         <v>3616.0074500000001</v>
@@ -5481,15 +5480,15 @@
         <v>0.41511822186218428</v>
       </c>
       <c r="R41" s="8">
-        <f>R10/N10-1</f>
+        <f t="shared" ref="R41:T42" si="58">R10/N10-1</f>
         <v>0.39818901578923427</v>
       </c>
       <c r="S41" s="8">
-        <f>S10/O10-1</f>
+        <f t="shared" si="58"/>
         <v>0.34958574979287493</v>
       </c>
       <c r="T41" s="8">
-        <f>T10/P10-1</f>
+        <f t="shared" si="58"/>
         <v>0.16647988142149606</v>
       </c>
       <c r="AC41" s="8">
@@ -5508,11 +5507,11 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8">
-        <f t="shared" ref="N42:O42" si="58">N11/J11-1</f>
+        <f t="shared" ref="N42:O42" si="59">N11/J11-1</f>
         <v>0.44099051633298214</v>
       </c>
       <c r="O42" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.42572887848478391</v>
       </c>
       <c r="P42" s="8">
@@ -5524,15 +5523,15 @@
         <v>0.41263879817112992</v>
       </c>
       <c r="R42" s="8">
-        <f>R11/N11-1</f>
+        <f t="shared" si="58"/>
         <v>0.43570122747453643</v>
       </c>
       <c r="S42" s="8">
-        <f>S11/O11-1</f>
+        <f t="shared" si="58"/>
         <v>0.55633504987934423</v>
       </c>
       <c r="T42" s="8">
-        <f>T11/P11-1</f>
+        <f t="shared" si="58"/>
         <v>0.29862253289473695</v>
       </c>
       <c r="AC42" s="8">
@@ -5558,121 +5557,121 @@
         <v>53</v>
       </c>
       <c r="G44" s="8">
-        <f t="shared" ref="G44:G49" si="59">G13/C13-1</f>
+        <f t="shared" ref="G44:G49" si="60">G13/C13-1</f>
         <v>-2.7093596059113323E-2</v>
       </c>
       <c r="H44" s="8">
-        <f t="shared" ref="H44:H49" si="60">H13/D13-1</f>
+        <f t="shared" ref="H44:H49" si="61">H13/D13-1</f>
         <v>-3.2537960954446832E-2</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8">
-        <f t="shared" ref="K44:K49" si="61">K13/G13-1</f>
+        <f t="shared" ref="K44:K49" si="62">K13/G13-1</f>
         <v>0.15696202531645564</v>
       </c>
       <c r="L44" s="8">
-        <f t="shared" ref="L44:L49" si="62">L13/H13-1</f>
+        <f t="shared" ref="L44:L49" si="63">L13/H13-1</f>
         <v>0.22197309417040367</v>
       </c>
       <c r="M44" s="8">
-        <f t="shared" ref="M44:M49" si="63">M13/I13-1</f>
+        <f t="shared" ref="M44:M49" si="64">M13/I13-1</f>
         <v>0.40128755364806867</v>
       </c>
       <c r="N44" s="8">
-        <f t="shared" ref="N44:N49" si="64">N13/J13-1</f>
+        <f t="shared" ref="N44:N49" si="65">N13/J13-1</f>
         <v>-2.3305084745762761E-2</v>
       </c>
       <c r="O44" s="8">
-        <f t="shared" ref="O44" si="65">O13/K13-1</f>
+        <f t="shared" ref="O44" si="66">O13/K13-1</f>
         <v>7.0021881838074451E-2</v>
       </c>
       <c r="P44" s="8">
-        <f t="shared" ref="P44:P45" si="66">P13/L13-1</f>
+        <f t="shared" ref="P44:P45" si="67">P13/L13-1</f>
         <v>0.47706422018348627</v>
       </c>
       <c r="Q44" s="8">
-        <f t="shared" ref="Q44:Q49" si="67">Q13/M13-1</f>
+        <f t="shared" ref="Q44:Q49" si="68">Q13/M13-1</f>
         <v>0.8897396630934149</v>
       </c>
       <c r="R44" s="8">
-        <f t="shared" ref="R44:R49" si="68">R13/N13-1</f>
+        <f t="shared" ref="R44:R49" si="69">R13/N13-1</f>
         <v>0.34598698481561829</v>
       </c>
       <c r="S44" s="8">
-        <f t="shared" ref="S44:S49" si="69">S13/O13-1</f>
+        <f t="shared" ref="S44:S49" si="70">S13/O13-1</f>
         <v>0.93251533742331283</v>
       </c>
       <c r="T44" s="8">
-        <f t="shared" ref="T44:T49" si="70">T13/P13-1</f>
+        <f t="shared" ref="T44:T49" si="71">T13/P13-1</f>
         <v>0.15527950310559002</v>
       </c>
       <c r="U44" s="8">
-        <f t="shared" ref="U44:U49" si="71">U13/Q13-1</f>
+        <f t="shared" ref="U44:U49" si="72">U13/Q13-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="V44" s="8">
-        <f t="shared" ref="V44:V49" si="72">V13/R13-1</f>
+        <f t="shared" ref="V44:V49" si="73">V13/R13-1</f>
         <v>0.35000000000000009</v>
       </c>
       <c r="AA44" s="8">
-        <f t="shared" ref="AA44:AO44" si="73">AA13/Z13-1</f>
+        <f t="shared" ref="AA44:AO44" si="74">AA13/Z13-1</f>
         <v>2.5711159737417999E-2</v>
       </c>
       <c r="AB44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.20053333333333323</v>
       </c>
       <c r="AC44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.14482452243447352</v>
       </c>
       <c r="AD44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.46255335661622032</v>
       </c>
       <c r="AE44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.33487662509949612</v>
       </c>
       <c r="AF44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AG44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO44" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5681,121 +5680,121 @@
         <v>54</v>
       </c>
       <c r="G45" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>2.857142857142847E-2</v>
       </c>
       <c r="H45" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.11255411255411252</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-0.19444444444444442</v>
       </c>
       <c r="L45" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-3.5019455252918275E-2</v>
       </c>
       <c r="M45" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.66228070175438591</v>
       </c>
       <c r="N45" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.55606407322654472</v>
       </c>
       <c r="O45" s="8">
-        <f t="shared" ref="O45" si="74">O14/K14-1</f>
+        <f t="shared" ref="O45" si="75">O14/K14-1</f>
         <v>0.84482758620689657</v>
       </c>
       <c r="P45" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>1.560483870967742</v>
       </c>
       <c r="Q45" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.17941952506596315</v>
       </c>
       <c r="R45" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.66470588235294126</v>
       </c>
       <c r="S45" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.65109034267912769</v>
       </c>
       <c r="T45" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>4.0944881889763751E-2</v>
       </c>
       <c r="U45" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.8</v>
       </c>
       <c r="V45" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA45" s="8">
-        <f t="shared" ref="AA45" si="75">AA14/Z14-1</f>
+        <f t="shared" ref="AA45" si="76">AA14/Z14-1</f>
         <v>1.878354203935606E-2</v>
       </c>
       <c r="AB45" s="8">
-        <f t="shared" ref="AB45:AC45" si="76">AB14/AA14-1</f>
+        <f t="shared" ref="AB45:AC45" si="77">AB14/AA14-1</f>
         <v>-8.779631255487752E-4</v>
       </c>
       <c r="AC45" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.30140597539543057</v>
       </c>
       <c r="AD45" s="8">
-        <f t="shared" ref="AD45:AO45" si="77">AD14/AC14-1</f>
+        <f t="shared" ref="AD45:AO45" si="78">AD14/AC14-1</f>
         <v>0.71168129642133704</v>
       </c>
       <c r="AE45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.32307692307692304</v>
       </c>
       <c r="AF45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AG45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AR45" t="s">
@@ -5810,121 +5809,121 @@
         <v>55</v>
       </c>
       <c r="G46" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-6.3829787234042534E-2</v>
       </c>
       <c r="H46" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.17283950617283961</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.4015151515151516</v>
       </c>
       <c r="L46" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.11052631578947358</v>
       </c>
       <c r="M46" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>9.6774193548387011E-2</v>
       </c>
       <c r="N46" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-3.4642032332563466E-2</v>
       </c>
       <c r="O46" s="8">
-        <f t="shared" ref="O46:P46" si="78">O15/K15-1</f>
+        <f t="shared" ref="O46:P46" si="79">O15/K15-1</f>
         <v>0.22702702702702693</v>
       </c>
       <c r="P46" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.2890995260663507</v>
       </c>
       <c r="Q46" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.39215686274509798</v>
       </c>
       <c r="R46" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.27511961722488043</v>
       </c>
       <c r="S46" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.47577092511013208</v>
       </c>
       <c r="T46" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.48161764705882359</v>
       </c>
       <c r="U46" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="V46" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.33000000000000007</v>
       </c>
       <c r="AA46" s="8">
-        <f t="shared" ref="AA46:AC46" si="79">AA15/Z15-1</f>
+        <f t="shared" ref="AA46:AC46" si="80">AA15/Z15-1</f>
         <v>-3.9948453608247392E-2</v>
       </c>
       <c r="AB46" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.26308724832214758</v>
       </c>
       <c r="AC46" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>8.1827842720510136E-2</v>
       </c>
       <c r="AD46" s="8">
-        <f t="shared" ref="AD46:AO46" si="80">AD15/AC15-1</f>
+        <f t="shared" ref="AD46:AO46" si="81">AD15/AC15-1</f>
         <v>0.29273084479371314</v>
       </c>
       <c r="AE46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.40158814589665637</v>
       </c>
       <c r="AF46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AG46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AH46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AI46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR46" t="s">
@@ -5939,121 +5938,121 @@
         <v>56</v>
       </c>
       <c r="G47" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.3752455795677854E-2</v>
       </c>
       <c r="H47" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>9.0128755364806912E-2</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>4.8449612403100861E-2</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-4.7244094488189003E-2</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-3.8022813688213253E-3</v>
       </c>
       <c r="N47" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>5.9760956175298752E-2</v>
       </c>
       <c r="O47" s="8">
-        <f t="shared" ref="O47:P47" si="81">O16/K16-1</f>
+        <f t="shared" ref="O47:P47" si="82">O16/K16-1</f>
         <v>-1.848428835489857E-3</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>5.9917355371900793E-2</v>
       </c>
       <c r="Q47" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>-7.6335877862595436E-2</v>
       </c>
       <c r="R47" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-6.9548872180451138E-2</v>
       </c>
       <c r="S47" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-6.6666666666666652E-2</v>
       </c>
       <c r="T47" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>-6.4327485380117011E-2</v>
       </c>
       <c r="U47" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-5.0000000000000044E-2</v>
       </c>
       <c r="V47" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AA47" s="8">
-        <f t="shared" ref="AA47:AC47" si="82">AA16/Z16-1</f>
+        <f t="shared" ref="AA47:AC47" si="83">AA16/Z16-1</f>
         <v>0.1166666666666667</v>
       </c>
       <c r="AB47" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>9.3816631130063888E-2</v>
       </c>
       <c r="AC47" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1.4132553606237774E-2</v>
       </c>
       <c r="AD47" s="8">
-        <f t="shared" ref="AD47:AO47" si="83">AD16/AC16-1</f>
+        <f t="shared" ref="AD47:AO47" si="84">AD16/AC16-1</f>
         <v>-2.3546371936568944E-2</v>
       </c>
       <c r="AE47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>-5.0738188976378051E-2</v>
       </c>
       <c r="AF47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR47" t="s">
@@ -6069,121 +6068,121 @@
         <v>57</v>
       </c>
       <c r="G48" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>2.5</v>
       </c>
       <c r="H48" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-2.75</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.28571428571428581</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-1.2222222222222223</v>
       </c>
       <c r="N48" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="O48" s="8">
-        <f t="shared" ref="O48:P48" si="84">O17/K17-1</f>
+        <f t="shared" ref="O48:P48" si="85">O17/K17-1</f>
         <v>-0.16666666666666663</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="Q48" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>-3</v>
       </c>
       <c r="R48" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>15</v>
       </c>
       <c r="S48" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-2.8</v>
       </c>
       <c r="T48" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>-5.3</v>
       </c>
       <c r="U48" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.35000000000000009</v>
       </c>
       <c r="V48" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.5</v>
       </c>
       <c r="AA48" s="8">
-        <f t="shared" ref="AA48:AC48" si="85">AA17/Z17-1</f>
+        <f t="shared" ref="AA48:AC48" si="86">AA17/Z17-1</f>
         <v>7</v>
       </c>
       <c r="AB48" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.16666666666666674</v>
       </c>
       <c r="AC48" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>-0.3571428571428571</v>
       </c>
       <c r="AD48" s="8">
-        <f t="shared" ref="AD48:AO48" si="86">AD17/AC17-1</f>
+        <f t="shared" ref="AD48:AO48" si="87">AD17/AC17-1</f>
         <v>4.5</v>
       </c>
       <c r="AE48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-0.25858585858585847</v>
       </c>
       <c r="AF48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="AG48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AH48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AI48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AR48" t="s">
@@ -6199,29 +6198,29 @@
         <v>37</v>
       </c>
       <c r="G49" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-1.577287066246047E-3</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>6.990881458966558E-2</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>7.6619273301737678E-2</v>
       </c>
       <c r="L49" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>6.3210227272727293E-2</v>
       </c>
       <c r="M49" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.24240282685512371</v>
       </c>
       <c r="N49" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.1016803102111159</v>
       </c>
       <c r="O49" s="7">
@@ -6233,27 +6232,27 @@
         <v>0.49298597194388782</v>
       </c>
       <c r="Q49" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0.39533560864618877</v>
       </c>
       <c r="R49" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.36136096988658584</v>
       </c>
       <c r="S49" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.45701643489254118</v>
       </c>
       <c r="T49" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8.7695749440715787E-2</v>
       </c>
       <c r="U49" s="7">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.28340807174887894</v>
       </c>
       <c r="V49" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.24899166906061465</v>
       </c>
       <c r="Z49" s="7"/>
@@ -6262,59 +6261,59 @@
         <v>4.6993524514338469E-2</v>
       </c>
       <c r="AB49" s="7">
-        <f t="shared" ref="AB49:AO49" si="87">AB18/AA18-1</f>
+        <f t="shared" ref="AB49:AO49" si="88">AB18/AA18-1</f>
         <v>0.1327089591800672</v>
       </c>
       <c r="AC49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.11934477379095165</v>
       </c>
       <c r="AD49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.35902439024390254</v>
       </c>
       <c r="AE49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.25442928930366127</v>
       </c>
       <c r="AF49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.18248044055153967</v>
       </c>
       <c r="AG49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>8.8590235067131706E-2</v>
       </c>
       <c r="AH49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>5.1204538885816664E-2</v>
       </c>
       <c r="AI49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>3.1653693802894178E-2</v>
       </c>
       <c r="AJ49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>2.2571489574682468E-2</v>
       </c>
       <c r="AK49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>2.0904952923547215E-2</v>
       </c>
       <c r="AL49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>2.0941992337490944E-2</v>
       </c>
       <c r="AM49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>2.0979260849687487E-2</v>
       </c>
       <c r="AN49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>2.1016764161705837E-2</v>
       </c>
       <c r="AO49" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>2.1054508084077606E-2</v>
       </c>
       <c r="AR49" t="s">
@@ -6344,51 +6343,51 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8">
-        <f t="shared" ref="K50:R50" si="88">(K18+K19)/(G18+G19)-1</f>
+        <f t="shared" ref="K50:R50" si="89">(K18+K19)/(G18+G19)-1</f>
         <v>-8.2740213523131656E-2</v>
       </c>
       <c r="L50" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>-2.874432677760963E-2</v>
       </c>
       <c r="M50" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.24119028974158185</v>
       </c>
       <c r="N50" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1.7758484609313285E-2</v>
       </c>
       <c r="O50" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.11542192046556732</v>
       </c>
       <c r="P50" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.7398753894080996</v>
       </c>
       <c r="Q50" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.62965299684542586</v>
       </c>
       <c r="R50" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.40248158200853035</v>
       </c>
       <c r="S50" s="8">
-        <f t="shared" ref="S50" si="89">(S18+S19)/(O18+O19)-1</f>
+        <f t="shared" ref="S50" si="90">(S18+S19)/(O18+O19)-1</f>
         <v>0.78956521739130436</v>
       </c>
       <c r="T50" s="8">
-        <f t="shared" ref="T50" si="90">(T18+T19)/(P18+P19)-1</f>
+        <f t="shared" ref="T50" si="91">(T18+T19)/(P18+P19)-1</f>
         <v>-6.9829901521933802E-2</v>
       </c>
       <c r="U50" s="8">
-        <f t="shared" ref="U50" si="91">(U18+U19)/(Q18+Q19)-1</f>
+        <f t="shared" ref="U50" si="92">(U18+U19)/(Q18+Q19)-1</f>
         <v>0.21881533101045303</v>
       </c>
       <c r="V50" s="8">
-        <f t="shared" ref="V50" si="92">(V18+V19)/(R18+R19)-1</f>
+        <f t="shared" ref="V50" si="93">(V18+V19)/(R18+R19)-1</f>
         <v>0.20202930605474134</v>
       </c>
       <c r="Z50" s="7"/>
@@ -6397,59 +6396,59 @@
         <v>5.3011590347710413E-2</v>
       </c>
       <c r="AB50" s="8">
-        <f t="shared" ref="AB50:AO50" si="93">(AB18+AB19)/(AA18+AA19)-1</f>
+        <f t="shared" ref="AB50:AO50" si="94">(AB18+AB19)/(AA18+AA19)-1</f>
         <v>0.12901479610249011</v>
       </c>
       <c r="AC50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>3.548026210644073E-2</v>
       </c>
       <c r="AD50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.47924062355301733</v>
       </c>
       <c r="AE50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.27628756260434062</v>
       </c>
       <c r="AF50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0.18248044055153967</v>
       </c>
       <c r="AG50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>8.8590235067131706E-2</v>
       </c>
       <c r="AH50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>5.1204538885816664E-2</v>
       </c>
       <c r="AI50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>3.1653693802894178E-2</v>
       </c>
       <c r="AJ50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.2571489574682468E-2</v>
       </c>
       <c r="AK50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.0904952923547215E-2</v>
       </c>
       <c r="AL50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.0941992337490944E-2</v>
       </c>
       <c r="AM50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.0979260849687487E-2</v>
       </c>
       <c r="AN50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.1016764161705837E-2</v>
       </c>
       <c r="AO50" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>2.1054508084077606E-2</v>
       </c>
       <c r="AR50" t="s">
@@ -6475,67 +6474,67 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8">
-        <f t="shared" ref="G51:P51" si="94">G23/G18</f>
+        <f t="shared" ref="G51:P51" si="95">G23/G18</f>
         <v>0.2109004739336493</v>
       </c>
       <c r="H51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.22443181818181818</v>
       </c>
       <c r="I51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.22332155477031801</v>
       </c>
       <c r="J51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.27789745799224475</v>
       </c>
       <c r="K51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.22157006603081439</v>
       </c>
       <c r="L51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.22845691382765532</v>
       </c>
       <c r="M51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.24402730375426621</v>
       </c>
       <c r="N51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.31912397340633553</v>
       </c>
       <c r="O51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.24905183312262957</v>
       </c>
       <c r="P51" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.25548098434004474</v>
       </c>
       <c r="Q51" s="8">
-        <f t="shared" ref="Q51:R51" si="95">Q23/Q18</f>
+        <f t="shared" ref="Q51:R51" si="96">Q23/Q18</f>
         <v>0.23685283326538931</v>
       </c>
       <c r="R51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.3274920999712726</v>
       </c>
       <c r="S51" s="8">
-        <f t="shared" ref="S51:V51" si="96">S23/S18</f>
+        <f t="shared" ref="S51:V51" si="97">S23/S18</f>
         <v>0.23514099783080261</v>
       </c>
       <c r="T51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.24475524475524477</v>
       </c>
       <c r="U51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.26</v>
       </c>
       <c r="V51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.34</v>
       </c>
       <c r="Z51" s="8">
@@ -6547,59 +6546,59 @@
         <v>0.24527301643399893</v>
       </c>
       <c r="AB51" s="8">
-        <f t="shared" ref="AB51:AO51" si="97">AB23/AB18</f>
+        <f t="shared" ref="AB51:AO51" si="98">AB23/AB18</f>
         <v>0.24087363494539782</v>
       </c>
       <c r="AC51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.26327526132404183</v>
       </c>
       <c r="AD51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.27545892728950877</v>
       </c>
       <c r="AE51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.28072109575423032</v>
       </c>
       <c r="AF51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="AG51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.24999999999999997</v>
       </c>
       <c r="AH51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.25</v>
       </c>
       <c r="AI51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.25</v>
       </c>
       <c r="AJ51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.25</v>
       </c>
       <c r="AK51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="AL51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.24999999999999994</v>
       </c>
       <c r="AM51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.24999999999999994</v>
       </c>
       <c r="AN51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.25</v>
       </c>
       <c r="AO51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.25</v>
       </c>
       <c r="AR51" t="s">
@@ -6625,131 +6624,128 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8">
-        <f t="shared" ref="G52:N52" si="98">G20/G18</f>
+        <f t="shared" ref="G52:N52" si="99">G20/G18</f>
         <v>0.54028436018957349</v>
       </c>
       <c r="H52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.50710227272727271</v>
       </c>
       <c r="I52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.56325088339222618</v>
       </c>
       <c r="J52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.42567858681602755</v>
       </c>
       <c r="K52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.65517241379310343</v>
       </c>
       <c r="L52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.57515030060120242</v>
       </c>
       <c r="M52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.57281001137656429</v>
       </c>
       <c r="N52" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.45913179507235041</v>
       </c>
       <c r="O52" s="8">
-        <f t="shared" ref="O52:P52" si="99">O20/O18</f>
+        <f t="shared" ref="O52:P52" si="100">O20/O18</f>
         <v>0.65676359039190901</v>
       </c>
       <c r="P52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.48635346756152126</v>
       </c>
       <c r="Q52" s="8">
-        <f t="shared" ref="Q52:R52" si="100">Q20/Q18</f>
+        <f t="shared" ref="Q52:R52" si="101">Q20/Q18</f>
         <v>0.47696697920913167</v>
       </c>
       <c r="R52" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.44900890548692907</v>
       </c>
       <c r="S52" s="8">
-        <f t="shared" ref="S52:V52" si="101">S20/S18</f>
+        <f t="shared" ref="S52:V52" si="102">S20/S18</f>
         <v>0.57006507592190891</v>
       </c>
       <c r="T52" s="8">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.61085972850678738</v>
       </c>
       <c r="U52" s="8">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="V52" s="8">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="Z52" s="8">
-        <f t="shared" ref="Z52:AO52" si="102">Z20/Z18</f>
+        <f t="shared" ref="Z52:AO52" si="103">Z20/Z18</f>
         <v>0.51655874190564288</v>
       </c>
       <c r="AA52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.48506803322141723</v>
       </c>
       <c r="AB52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.49656786271450859</v>
       </c>
       <c r="AC52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5484320557491289</v>
       </c>
       <c r="AD52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.49830786585991182</v>
       </c>
-      <c r="AE52" s="8">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
+      <c r="AE52" s="8"/>
       <c r="AF52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AG52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AH52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AI52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AJ52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AK52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AL52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AM52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AN52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AO52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.5</v>
       </c>
       <c r="AR52" s="1" t="s">
@@ -6775,131 +6771,128 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8">
-        <f t="shared" ref="G53:N53" si="103">G21/G18</f>
+        <f t="shared" ref="G53:N53" si="104">G21/G18</f>
         <v>0.3609794628751975</v>
       </c>
       <c r="H53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.32954545454545453</v>
       </c>
       <c r="I53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.31095406360424027</v>
       </c>
       <c r="J53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.20465316673847481</v>
       </c>
       <c r="K53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.36683785766691124</v>
       </c>
       <c r="L53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.33867735470941884</v>
       </c>
       <c r="M53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.28156996587030719</v>
       </c>
       <c r="N53" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.21314039890496675</v>
       </c>
       <c r="O53" s="8">
-        <f t="shared" ref="O53:P53" si="104">O21/O18</f>
+        <f t="shared" ref="O53:P53" si="105">O21/O18</f>
         <v>0.36725663716814161</v>
       </c>
       <c r="P53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.25861297539149886</v>
       </c>
       <c r="Q53" s="8">
-        <f t="shared" ref="Q53:R53" si="105">Q21/Q18</f>
+        <f t="shared" ref="Q53:R53" si="106">Q21/Q18</f>
         <v>0.23318385650224216</v>
       </c>
       <c r="R53" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.18442976156276933</v>
       </c>
       <c r="S53" s="8">
-        <f t="shared" ref="S53:V53" si="106">S21/S18</f>
+        <f t="shared" ref="S53:V53" si="107">S21/S18</f>
         <v>0.30195227765726679</v>
       </c>
       <c r="T53" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.2895927601809955</v>
       </c>
       <c r="U53" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="V53" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="Z53" s="8">
-        <f t="shared" ref="Z53:AO53" si="107">Z21/Z18</f>
+        <f t="shared" ref="Z53:AO53" si="108">Z21/Z18</f>
         <v>0.28436632747456059</v>
       </c>
       <c r="AA53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.29033398126877541</v>
       </c>
       <c r="AB53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.28642745709828393</v>
       </c>
       <c r="AC53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.28529616724738677</v>
       </c>
       <c r="AD53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.24335965541995694</v>
       </c>
-      <c r="AE53" s="8">
-        <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
+      <c r="AE53" s="8"/>
       <c r="AF53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AG53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AH53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AI53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AJ53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AK53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AL53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AM53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AN53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AO53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25</v>
       </c>
       <c r="AR53" t="s">
@@ -6918,128 +6911,128 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8">
-        <f t="shared" ref="G54:V54" si="108">G25/C25-1</f>
+        <f t="shared" ref="G54:V54" si="109">G25/C25-1</f>
         <v>0.38095238095238093</v>
       </c>
       <c r="H54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="I54" s="8" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J54" s="8" t="e">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.10344827586206895</v>
       </c>
       <c r="L54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>-0.4358974358974359</v>
       </c>
       <c r="M54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>-0.22641509433962259</v>
       </c>
       <c r="N54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>-0.42000000000000004</v>
       </c>
       <c r="O54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.3125</v>
       </c>
       <c r="P54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.77272727272727271</v>
       </c>
       <c r="Q54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.24390243902439024</v>
       </c>
       <c r="R54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.65517241379310343</v>
       </c>
       <c r="S54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="T54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.30769230769230771</v>
       </c>
       <c r="U54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="V54" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8">
-        <f t="shared" ref="AA54:AO54" si="109">AA25/Z25-1</f>
+        <f t="shared" ref="AA54:AO54" si="110">AA25/Z25-1</f>
         <v>0.17543859649122817</v>
       </c>
       <c r="AB54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.64925373134328357</v>
       </c>
       <c r="AC54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>-0.30769230769230771</v>
       </c>
       <c r="AD54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.49019607843137258</v>
       </c>
       <c r="AE54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>-1</v>
       </c>
       <c r="AF54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AS54" s="4"/>
@@ -7063,51 +7056,51 @@
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8">
-        <f t="shared" ref="K55:P55" si="110">K26/G26-1</f>
+        <f t="shared" ref="K55:P55" si="111">K26/G26-1</f>
         <v>0.18954248366013071</v>
       </c>
       <c r="L55" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.10240963855421681</v>
       </c>
       <c r="M55" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.12886597938144329</v>
       </c>
       <c r="N55" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.19607843137254899</v>
       </c>
       <c r="O55" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.25274725274725274</v>
       </c>
       <c r="P55" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.51366120218579225</v>
       </c>
       <c r="Q55" s="8">
-        <f t="shared" ref="Q55:R55" si="111">Q26/M26-1</f>
+        <f t="shared" ref="Q55:R55" si="112">Q26/M26-1</f>
         <v>0.12785388127853881</v>
       </c>
       <c r="R55" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.20655737704918042</v>
       </c>
       <c r="S55" s="8">
-        <f t="shared" ref="S55" si="112">S26/O26-1</f>
+        <f t="shared" ref="S55" si="113">S26/O26-1</f>
         <v>0.25877192982456143</v>
       </c>
       <c r="T55" s="8">
-        <f t="shared" ref="T55" si="113">T26/P26-1</f>
+        <f t="shared" ref="T55" si="114">T26/P26-1</f>
         <v>3.6101083032491044E-2</v>
       </c>
       <c r="U55" s="8">
-        <f t="shared" ref="U55" si="114">U26/Q26-1</f>
+        <f t="shared" ref="U55" si="115">U26/Q26-1</f>
         <v>0.14999999999999991</v>
       </c>
       <c r="V55" s="8">
-        <f t="shared" ref="V55" si="115">V26/R26-1</f>
+        <f t="shared" ref="V55" si="116">V26/R26-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="Z55" s="8"/>
@@ -7116,59 +7109,59 @@
         <v>2.1806853582554409E-2</v>
       </c>
       <c r="AB55" s="8">
-        <f t="shared" ref="AB55:AO55" si="116">AB26/AA26-1</f>
+        <f t="shared" ref="AB55:AO55" si="117">AB26/AA26-1</f>
         <v>0.1707317073170731</v>
       </c>
       <c r="AC55" s="8">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.15755208333333326</v>
       </c>
       <c r="AD55" s="8">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.25984251968503935</v>
       </c>
       <c r="AE55" s="8">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>-1</v>
       </c>
       <c r="AF55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO55" s="8" t="e">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -7187,67 +7180,67 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8">
-        <f t="shared" ref="G56:P56" si="117">G28/G18</f>
+        <f t="shared" ref="G56:P56" si="118">G28/G18</f>
         <v>6.5560821484992107E-2</v>
       </c>
       <c r="H56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>9.0198863636363633E-2</v>
       </c>
       <c r="I56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>7.9151943462897528E-2</v>
       </c>
       <c r="J56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.18354157690650583</v>
       </c>
       <c r="K56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>6.5297138664710194E-2</v>
       </c>
       <c r="L56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>7.8824315297261194E-2</v>
       </c>
       <c r="M56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>9.7838452787258251E-2</v>
       </c>
       <c r="N56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.18224481814626514</v>
       </c>
       <c r="O56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>7.3957016434892539E-2</v>
       </c>
       <c r="P56" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.10827740492170022</v>
       </c>
       <c r="Q56" s="8">
-        <f t="shared" ref="Q56:R56" si="118">Q28/Q18</f>
+        <f t="shared" ref="Q56:R56" si="119">Q28/Q18</f>
         <v>0.11822258459029759</v>
       </c>
       <c r="R56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.21315713875323183</v>
       </c>
       <c r="S56" s="8">
-        <f t="shared" ref="S56:V56" si="119">S28/S18</f>
+        <f t="shared" ref="S56:V56" si="120">S28/S18</f>
         <v>7.7657266811279824E-2</v>
       </c>
       <c r="T56" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>9.5433977786918964E-2</v>
       </c>
       <c r="U56" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.16065751858204694</v>
       </c>
       <c r="V56" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.24569813282302994</v>
       </c>
       <c r="Z56" s="8">
@@ -7259,59 +7252,59 @@
         <v>0.10867644460151971</v>
       </c>
       <c r="AB56" s="8">
-        <f t="shared" ref="AB56:AO56" si="120">AB28/AB18</f>
+        <f t="shared" ref="AB56:AO56" si="121">AB28/AB18</f>
         <v>0.11669266770670828</v>
       </c>
       <c r="AC56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.11777003484320557</v>
       </c>
       <c r="AD56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.14265203568864732</v>
       </c>
       <c r="AE56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.16228117534912698</v>
       </c>
       <c r="AF56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.14482962071884012</v>
       </c>
       <c r="AG56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.14952399816845571</v>
       </c>
       <c r="AH56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15155076575660423</v>
       </c>
       <c r="AI56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15266286106328875</v>
       </c>
       <c r="AJ56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15290763753178707</v>
       </c>
       <c r="AK56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15299370236771342</v>
       </c>
       <c r="AL56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15308320714834123</v>
       </c>
       <c r="AM56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15317616380726287</v>
       </c>
       <c r="AN56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15327258436576421</v>
       </c>
       <c r="AO56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.15337248093439074</v>
       </c>
     </row>
@@ -7330,67 +7323,67 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8">
-        <f t="shared" ref="G57:P57" si="121">G35/G34</f>
+        <f t="shared" ref="G57:P57" si="122">G35/G34</f>
         <v>0.20547945205479451</v>
       </c>
       <c r="H57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.30612244897959184</v>
       </c>
       <c r="I57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.27027027027027029</v>
       </c>
       <c r="J57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.24713958810068651</v>
       </c>
       <c r="K57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.28985507246376813</v>
       </c>
       <c r="L57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.29807692307692307</v>
       </c>
       <c r="M57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.24827586206896551</v>
       </c>
       <c r="N57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.19758064516129031</v>
       </c>
       <c r="O57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.36046511627906974</v>
       </c>
       <c r="P57" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.26923076923076922</v>
       </c>
       <c r="Q57" s="8">
-        <f t="shared" ref="Q57:R57" si="122">Q35/Q34</f>
+        <f t="shared" ref="Q57:R57" si="123">Q35/Q34</f>
         <v>0.29959514170040485</v>
       </c>
       <c r="R57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.25036390101892286</v>
       </c>
       <c r="S57" s="8">
-        <f t="shared" ref="S57:V57" si="123">S35/S34</f>
+        <f t="shared" ref="S57:V57" si="124">S35/S34</f>
         <v>0.26712328767123289</v>
       </c>
       <c r="T57" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.23766816143497757</v>
       </c>
       <c r="U57" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.27</v>
       </c>
       <c r="V57" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.27</v>
       </c>
       <c r="Z57" s="8">
@@ -7402,59 +7395,59 @@
         <v>0.25773195876288657</v>
       </c>
       <c r="AB57" s="8">
-        <f t="shared" ref="AB57:AO57" si="124">AB35/AB34</f>
+        <f t="shared" ref="AB57:AO57" si="125">AB35/AB34</f>
         <v>0.25452016689847012</v>
       </c>
       <c r="AC57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.22727272727272727</v>
       </c>
       <c r="AD57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.27117263843648209</v>
       </c>
       <c r="AE57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.26585351686982805</v>
       </c>
       <c r="AF57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AG57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AH57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AI57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AJ57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AK57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AL57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AM57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AN57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
       <c r="AO57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.25</v>
       </c>
     </row>
@@ -7473,131 +7466,131 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8">
-        <f t="shared" ref="G58:N58" si="125">G36/G34</f>
+        <f t="shared" ref="G58:N58" si="126">G36/G34</f>
         <v>0.16438356164383561</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.11224489795918367</v>
       </c>
       <c r="I58" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>4.5045045045045043E-2</v>
       </c>
       <c r="J58" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>7.3226544622425629E-2</v>
       </c>
       <c r="K58" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>1.4492753623188406E-2</v>
       </c>
       <c r="L58" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.15384615384615385</v>
       </c>
       <c r="M58" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>4.8275862068965517E-2</v>
       </c>
       <c r="N58" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.14314516129032259</v>
       </c>
       <c r="O58" s="8">
-        <f t="shared" ref="O58:P58" si="126">O36/O34</f>
+        <f t="shared" ref="O58:P58" si="127">O36/O34</f>
         <v>5.8139534883720929E-2</v>
       </c>
       <c r="P58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.42788461538461536</v>
       </c>
       <c r="Q58" s="8">
-        <f t="shared" ref="Q58:R58" si="127">Q36/Q34</f>
+        <f t="shared" ref="Q58:R58" si="128">Q36/Q34</f>
         <v>0.15384615384615385</v>
       </c>
       <c r="R58" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>6.6957787481804948E-2</v>
       </c>
       <c r="S58" s="8">
-        <f t="shared" ref="S58:V58" si="128">S36/S34</f>
+        <f t="shared" ref="S58:V58" si="129">S36/S34</f>
         <v>0.16438356164383561</v>
       </c>
       <c r="T58" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.1210762331838565</v>
       </c>
       <c r="U58" s="8">
-        <f t="shared" si="128"/>
-        <v>0.1</v>
-      </c>
-      <c r="V58" s="8">
-        <f t="shared" si="128"/>
-        <v>0.1</v>
-      </c>
-      <c r="Z58" s="8">
-        <f t="shared" ref="Z58:AO58" si="129">Z36/Z34</f>
-        <v>0.84699453551912574</v>
-      </c>
-      <c r="AA58" s="8">
-        <f t="shared" si="129"/>
-        <v>0.2422680412371134</v>
-      </c>
-      <c r="AB58" s="8">
-        <f t="shared" si="129"/>
-        <v>8.3449235048678724E-2</v>
-      </c>
-      <c r="AC58" s="8">
-        <f t="shared" si="129"/>
-        <v>0.1167076167076167</v>
-      </c>
-      <c r="AD58" s="8">
-        <f t="shared" si="129"/>
-        <v>0.14495114006514659</v>
-      </c>
-      <c r="AE58" s="8">
-        <f t="shared" si="129"/>
-        <v>0.10766257039782763</v>
-      </c>
-      <c r="AF58" s="8">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AG58" s="8">
+      <c r="V58" s="8">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
+      <c r="Z58" s="8">
+        <f t="shared" ref="Z58:AO58" si="130">Z36/Z34</f>
+        <v>0.84699453551912574</v>
+      </c>
+      <c r="AA58" s="8">
+        <f t="shared" si="130"/>
+        <v>0.2422680412371134</v>
+      </c>
+      <c r="AB58" s="8">
+        <f t="shared" si="130"/>
+        <v>8.3449235048678724E-2</v>
+      </c>
+      <c r="AC58" s="8">
+        <f t="shared" si="130"/>
+        <v>0.1167076167076167</v>
+      </c>
+      <c r="AD58" s="8">
+        <f t="shared" si="130"/>
+        <v>0.14495114006514659</v>
+      </c>
+      <c r="AE58" s="8">
+        <f t="shared" si="130"/>
+        <v>0.10766257039782763</v>
+      </c>
+      <c r="AF58" s="8">
+        <f t="shared" si="130"/>
+        <v>0.1</v>
+      </c>
+      <c r="AG58" s="8">
+        <f t="shared" si="130"/>
+        <v>0.1</v>
+      </c>
       <c r="AH58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.1</v>
       </c>
       <c r="AI58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.1</v>
       </c>
       <c r="AJ58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.1</v>
       </c>
       <c r="AK58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.1</v>
       </c>
       <c r="AL58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AM58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.1</v>
       </c>
       <c r="AN58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AO58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.1</v>
       </c>
     </row>
@@ -7616,132 +7609,132 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8">
-        <f t="shared" ref="G59:P59" si="130">G37/G23</f>
+        <f t="shared" ref="G59:P59" si="131">G37/G23</f>
         <v>0.17228464419475656</v>
       </c>
       <c r="H59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.18037974683544303</v>
       </c>
       <c r="I59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.24050632911392406</v>
       </c>
       <c r="J59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.46046511627906977</v>
       </c>
       <c r="K59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.15894039735099338</v>
       </c>
       <c r="L59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.16666666666666666</v>
       </c>
       <c r="M59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.23776223776223776</v>
       </c>
       <c r="N59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.40073529411764708</v>
       </c>
       <c r="O59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.12690355329949238</v>
       </c>
       <c r="P59" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.11033274956217162</v>
       </c>
       <c r="Q59" s="8">
-        <f t="shared" ref="Q59:R59" si="131">Q37/Q23</f>
+        <f t="shared" ref="Q59:R59" si="132">Q37/Q23</f>
         <v>0.23235800344234078</v>
       </c>
       <c r="R59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.41140350877192983</v>
       </c>
       <c r="S59" s="8">
-        <f t="shared" ref="S59:V59" si="132">S37/S23</f>
+        <f t="shared" ref="S59:V59" si="133">S37/S23</f>
         <v>0.15313653136531366</v>
       </c>
       <c r="T59" s="8">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.24033613445378152</v>
       </c>
       <c r="U59" s="8">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.35453489906320107</v>
       </c>
       <c r="V59" s="8">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.43065200879212695</v>
       </c>
       <c r="Z59" s="8">
-        <f>Z37/Z23</f>
-        <v>-2.2167487684729065E-2</v>
+        <f t="shared" ref="Z59:AD59" si="134">Z37/Z18</f>
+        <v>-4.9953746530989824E-3</v>
       </c>
       <c r="AA59" s="8">
-        <f>AA37/AA23</f>
-        <v>0.20965417867435157</v>
+        <f t="shared" si="134"/>
+        <v>5.1422512811450785E-2</v>
       </c>
       <c r="AB59" s="8">
-        <f t="shared" ref="AB59:AO59" si="133">AB37/AB23</f>
-        <v>0.30829015544041449</v>
+        <f t="shared" si="134"/>
+        <v>7.4258970358814347E-2</v>
       </c>
       <c r="AC59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.2826892535733192</v>
+        <f t="shared" si="134"/>
+        <v>7.4425087108013932E-2</v>
       </c>
       <c r="AD59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.26693968726731199</v>
+        <f t="shared" si="134"/>
+        <v>7.3530919905650707E-2</v>
       </c>
       <c r="AE59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.33572537375607336</v>
+        <f>AE37/AE18</f>
+        <v>9.4245194793303441E-2</v>
       </c>
       <c r="AF59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.34972893031511876</v>
+        <f t="shared" ref="AF59:AO59" si="135">AF37/AF18</f>
+        <v>8.7432232578779717E-2</v>
       </c>
       <c r="AG59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.36337825603635282</v>
+        <f t="shared" si="135"/>
+        <v>9.0844564009088205E-2</v>
       </c>
       <c r="AH59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.36915989195074828</v>
+        <f t="shared" si="135"/>
+        <v>9.2289972987687069E-2</v>
       </c>
       <c r="AI59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.37209120858808414</v>
+        <f t="shared" si="135"/>
+        <v>9.3022802147021036E-2</v>
       </c>
       <c r="AJ59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.37254723270260126</v>
+        <f t="shared" si="135"/>
+        <v>9.3136808175650315E-2</v>
       </c>
       <c r="AK59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.37254816858219397</v>
+        <f t="shared" si="135"/>
+        <v>9.3137042145548507E-2</v>
       </c>
       <c r="AL59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.37255698683391375</v>
+        <f t="shared" si="135"/>
+        <v>9.313924670847841E-2</v>
       </c>
       <c r="AM59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.37257373111457714</v>
+        <f t="shared" si="135"/>
+        <v>9.3143432778644258E-2</v>
       </c>
       <c r="AN59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.37259844583108448</v>
+        <f t="shared" si="135"/>
+        <v>9.314961145777112E-2</v>
       </c>
       <c r="AO59" s="8">
-        <f t="shared" si="133"/>
-        <v>0.37263117615639341</v>
+        <f t="shared" si="135"/>
+        <v>9.3157794039098352E-2</v>
       </c>
     </row>
     <row r="61" spans="2:45" x14ac:dyDescent="0.3">
@@ -7749,52 +7742,52 @@
         <v>92</v>
       </c>
       <c r="O61" s="3">
-        <f t="shared" ref="O61:V61" si="134">O37</f>
+        <f t="shared" ref="O61:V61" si="136">O37</f>
         <v>50</v>
       </c>
       <c r="P61" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>63</v>
       </c>
       <c r="Q61" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>135</v>
       </c>
       <c r="R61" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>469</v>
       </c>
       <c r="S61" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>83</v>
       </c>
       <c r="T61" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>143</v>
       </c>
       <c r="U61" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>290.19816000000014</v>
       </c>
       <c r="V61" s="3">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>636.60340799999994</v>
       </c>
       <c r="Y61" s="3"/>
       <c r="Z61" s="3">
-        <f t="shared" ref="Z61:AC61" si="135">Z37</f>
+        <f t="shared" ref="Z61:AC61" si="137">Z37</f>
         <v>-27</v>
       </c>
       <c r="AA61" s="3">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>291</v>
       </c>
       <c r="AB61" s="3">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>476</v>
       </c>
       <c r="AC61" s="3">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>534</v>
       </c>
       <c r="AD61" s="3">
@@ -7802,47 +7795,47 @@
         <v>717</v>
       </c>
       <c r="AE61" s="3">
-        <f t="shared" ref="AE61:AO61" si="136">AE37</f>
+        <f t="shared" ref="AE61:AO61" si="138">AE37</f>
         <v>1152.8015680000001</v>
       </c>
       <c r="AF61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1264.6224175000007</v>
       </c>
       <c r="AG61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1430.3841434999997</v>
       </c>
       <c r="AH61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1527.5501896362498</v>
       </c>
       <c r="AI61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1588.4162624936125</v>
       </c>
       <c r="AJ61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1626.2598404607766</v>
       </c>
       <c r="AK61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1660.2608966144278</v>
       </c>
       <c r="AL61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1695.0701891176468</v>
       </c>
       <c r="AM61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1730.7092906452594</v>
       </c>
       <c r="AN61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1767.2004192837585</v>
       </c>
       <c r="AO61" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="138"/>
         <v>1804.5664601807241</v>
       </c>
     </row>
@@ -7903,43 +7896,43 @@
         <v>1268.0817248000003</v>
       </c>
       <c r="AF62" s="6">
-        <f t="shared" ref="AF62:AO62" si="137">AF61*1.1</f>
+        <f t="shared" ref="AF62:AO62" si="139">AF61*1.1</f>
         <v>1391.0846592500009</v>
       </c>
       <c r="AG62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1573.4225578499997</v>
       </c>
       <c r="AH62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1680.305208599875</v>
       </c>
       <c r="AI62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1747.2578887429738</v>
       </c>
       <c r="AJ62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1788.8858245068543</v>
       </c>
       <c r="AK62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1826.2869862758707</v>
       </c>
       <c r="AL62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1864.5772080294116</v>
       </c>
       <c r="AM62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1903.7802197097856</v>
       </c>
       <c r="AN62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1943.9204612121346</v>
       </c>
       <c r="AO62" s="6">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>1985.0231061987968</v>
       </c>
     </row>
@@ -8024,19 +8017,19 @@
         <v>797.91254983440001</v>
       </c>
       <c r="AL63" s="3">
-        <f t="shared" ref="AL63:AO63" si="138">AK63*1.02</f>
+        <f t="shared" ref="AL63:AO63" si="140">AK63*1.02</f>
         <v>813.87080083108799</v>
       </c>
       <c r="AM63" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>830.14821684770982</v>
       </c>
       <c r="AN63" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>846.75118118466401</v>
       </c>
       <c r="AO63" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="140"/>
         <v>863.68620480835727</v>
       </c>
     </row>
@@ -8064,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="AE64" s="3">
-        <f t="shared" ref="AE64:AE73" si="139">SUM(S64:V64)</f>
+        <f t="shared" ref="AE64:AE73" si="141">SUM(S64:V64)</f>
         <v>0</v>
       </c>
       <c r="AF64" s="3">
@@ -8115,7 +8108,7 @@
         <v>-11</v>
       </c>
       <c r="R65" s="3">
-        <f t="shared" ref="R65:R69" si="140">AD65-Q65-P65-O65</f>
+        <f t="shared" ref="R65:R69" si="142">AD65-Q65-P65-O65</f>
         <v>-6</v>
       </c>
       <c r="S65" s="3">
@@ -8157,7 +8150,7 @@
         <v>-24</v>
       </c>
       <c r="AE65" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>-21</v>
       </c>
       <c r="AF65" s="3">
@@ -8165,39 +8158,39 @@
         <v>-23.1</v>
       </c>
       <c r="AG65" s="3">
-        <f t="shared" ref="AG65:AO65" si="141">AF65*1.1</f>
+        <f t="shared" ref="AG65:AO65" si="143">AF65*1.1</f>
         <v>-25.410000000000004</v>
       </c>
       <c r="AH65" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>-27.951000000000008</v>
       </c>
       <c r="AI65" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>-30.746100000000009</v>
       </c>
       <c r="AJ65" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>-33.820710000000012</v>
       </c>
       <c r="AK65" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>-37.202781000000016</v>
       </c>
       <c r="AL65" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>-40.923059100000017</v>
       </c>
       <c r="AM65" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>-45.015365010000025</v>
       </c>
       <c r="AN65" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>-49.516901511000029</v>
       </c>
       <c r="AO65" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="143"/>
         <v>-54.468591662100039</v>
       </c>
     </row>
@@ -8217,7 +8210,7 @@
         <v>-3</v>
       </c>
       <c r="R66" s="3">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>37</v>
       </c>
       <c r="S66" s="3">
@@ -8251,7 +8244,7 @@
         <v>103</v>
       </c>
       <c r="AE66" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="AF66" s="3">
@@ -8301,7 +8294,7 @@
         <v>78</v>
       </c>
       <c r="R67" s="3">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>41</v>
       </c>
       <c r="S67" s="3">
@@ -8336,7 +8329,7 @@
         <v>135</v>
       </c>
       <c r="AE67" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>95</v>
       </c>
       <c r="AF67" s="3">
@@ -8386,7 +8379,7 @@
         <v>-77</v>
       </c>
       <c r="R68" s="3">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>558</v>
       </c>
       <c r="S68" s="3">
@@ -8422,7 +8415,7 @@
         <v>407</v>
       </c>
       <c r="AE68" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>168</v>
       </c>
       <c r="AF68" s="3">
@@ -8472,7 +8465,7 @@
         <v>-15</v>
       </c>
       <c r="R69" s="3">
-        <f t="shared" si="140"/>
+        <f t="shared" si="142"/>
         <v>72</v>
       </c>
       <c r="S69" s="3">
@@ -8507,7 +8500,7 @@
         <v>-102</v>
       </c>
       <c r="AE69" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>-100</v>
       </c>
       <c r="AF69" s="3">
@@ -8561,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="AF70" s="3">
@@ -8611,7 +8604,7 @@
         <v>12</v>
       </c>
       <c r="R71" s="3">
-        <f t="shared" ref="R71:R73" si="142">AD71-Q71-P71-O71</f>
+        <f t="shared" ref="R71:R73" si="144">AD71-Q71-P71-O71</f>
         <v>-1</v>
       </c>
       <c r="S71" s="3">
@@ -8646,7 +8639,7 @@
         <v>15</v>
       </c>
       <c r="AE71" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>4</v>
       </c>
       <c r="AF71" s="3">
@@ -8695,7 +8688,7 @@
         <v>9</v>
       </c>
       <c r="R72" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>7</v>
       </c>
       <c r="S72" s="3">
@@ -8730,7 +8723,7 @@
         <v>16</v>
       </c>
       <c r="AE72" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>16</v>
       </c>
       <c r="AF72" s="3">
@@ -8780,7 +8773,7 @@
         <v>38</v>
       </c>
       <c r="R73" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="144"/>
         <v>-109</v>
       </c>
       <c r="S73" s="3">
@@ -8815,7 +8808,7 @@
         <v>-42</v>
       </c>
       <c r="AE73" s="3">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>-25</v>
       </c>
       <c r="AF73" s="3">
@@ -8854,27 +8847,27 @@
         <v>104</v>
       </c>
       <c r="O74" s="6">
-        <f t="shared" ref="O74:P74" si="143">O62+SUM(O63:O73)</f>
+        <f t="shared" ref="O74:P74" si="145">O62+SUM(O63:O73)</f>
         <v>-105</v>
       </c>
       <c r="P74" s="6">
-        <f t="shared" si="143"/>
+        <f t="shared" si="145"/>
         <v>297</v>
       </c>
       <c r="Q74" s="6">
-        <f t="shared" ref="Q74:R74" si="144">Q62+SUM(Q63:Q73)</f>
+        <f t="shared" ref="Q74:R74" si="146">Q62+SUM(Q63:Q73)</f>
         <v>300</v>
       </c>
       <c r="R74" s="6">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>1227</v>
       </c>
       <c r="S74" s="6">
-        <f t="shared" ref="S74:V74" si="145">S62+SUM(S63:S73)</f>
+        <f t="shared" ref="S74:T74" si="147">S62+SUM(S63:S73)</f>
         <v>420</v>
       </c>
       <c r="T74" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>-697</v>
       </c>
       <c r="U74" s="6">
@@ -8886,71 +8879,71 @@
         <v>1740.003408</v>
       </c>
       <c r="Y74" s="6">
-        <f t="shared" ref="Y74:AD74" si="146">Y62+SUM(Y63:Y73)</f>
+        <f t="shared" ref="Y74:AD74" si="148">Y62+SUM(Y63:Y73)</f>
         <v>602</v>
       </c>
       <c r="Z74" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>453</v>
       </c>
       <c r="AA74" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>690</v>
       </c>
       <c r="AB74" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>174</v>
       </c>
       <c r="AC74" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>742</v>
       </c>
       <c r="AD74" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="148"/>
         <v>1719</v>
       </c>
       <c r="AE74" s="6">
-        <f t="shared" ref="AE74:AO74" si="147">AE62+SUM(AE63:AE73)</f>
+        <f t="shared" ref="AE74:AO74" si="149">AE62+SUM(AE63:AE73)</f>
         <v>1954.8817248000003</v>
       </c>
       <c r="AF74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2000.2546592500007</v>
       </c>
       <c r="AG74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2243.5095578499995</v>
       </c>
       <c r="AH74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2382.6260585998748</v>
       </c>
       <c r="AI74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2475.9945127429737</v>
       </c>
       <c r="AJ74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2537.3323202268543</v>
       </c>
       <c r="AK74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2586.9967551102709</v>
       </c>
       <c r="AL74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2637.5249497604996</v>
       </c>
       <c r="AM74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2688.9130715474953</v>
       </c>
       <c r="AN74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2741.1547408857987</v>
       </c>
       <c r="AO74" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="149"/>
         <v>2794.240719345054</v>
       </c>
     </row>
@@ -8981,11 +8974,11 @@
         <v>199</v>
       </c>
       <c r="U75" s="3">
-        <f t="shared" ref="U75:V75" si="148">Q75*1.45</f>
+        <f t="shared" ref="U75:V75" si="150">Q75*1.45</f>
         <v>266.8</v>
       </c>
       <c r="V75" s="3">
-        <f t="shared" si="148"/>
+        <f t="shared" si="150"/>
         <v>458.2</v>
       </c>
       <c r="Y75" s="3">
@@ -9015,19 +9008,19 @@
         <v>1184.7</v>
       </c>
       <c r="AG75" s="3">
-        <f t="shared" ref="AG75:AJ75" si="149">AF75*0.9</f>
+        <f t="shared" ref="AG75:AJ75" si="151">AF75*0.9</f>
         <v>1066.23</v>
       </c>
       <c r="AH75" s="3">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>959.60700000000008</v>
       </c>
       <c r="AI75" s="3">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>863.64630000000011</v>
       </c>
       <c r="AJ75" s="3">
-        <f t="shared" si="149"/>
+        <f t="shared" si="151"/>
         <v>777.28167000000008</v>
       </c>
       <c r="AK75" s="3">
@@ -9035,19 +9028,19 @@
         <v>738.41758650000008</v>
       </c>
       <c r="AL75" s="3">
-        <f t="shared" ref="AL75:AO75" si="150">AK75*0.95</f>
+        <f t="shared" ref="AL75:AO75" si="152">AK75*0.95</f>
         <v>701.4967071750001</v>
       </c>
       <c r="AM75" s="3">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>666.42187181625002</v>
       </c>
       <c r="AN75" s="3">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>633.10077822543747</v>
       </c>
       <c r="AO75" s="3">
-        <f t="shared" si="150"/>
+        <f t="shared" si="152"/>
         <v>601.44573931416562</v>
       </c>
     </row>
@@ -9056,103 +9049,103 @@
         <v>106</v>
       </c>
       <c r="O76" s="6">
-        <f t="shared" ref="O76:P76" si="151">O74-O75</f>
+        <f t="shared" ref="O76:P76" si="153">O74-O75</f>
         <v>-210</v>
       </c>
       <c r="P76" s="6">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>170</v>
       </c>
       <c r="Q76" s="6">
-        <f t="shared" ref="Q76:R76" si="152">Q74-Q75</f>
+        <f t="shared" ref="Q76:R76" si="154">Q74-Q75</f>
         <v>116</v>
       </c>
       <c r="R76" s="6">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>911</v>
       </c>
       <c r="S76" s="6">
-        <f t="shared" ref="S76:V76" si="153">S74-S75</f>
+        <f t="shared" ref="S76:V76" si="155">S74-S75</f>
         <v>267</v>
       </c>
       <c r="T76" s="6">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>-896</v>
       </c>
       <c r="U76" s="6">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>150.79816000000011</v>
       </c>
       <c r="V76" s="6">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>1281.803408</v>
       </c>
       <c r="Y76" s="6">
-        <f t="shared" ref="Y76:AD76" si="154">Y74-Y75</f>
+        <f t="shared" ref="Y76:AD76" si="156">Y74-Y75</f>
         <v>314</v>
       </c>
       <c r="Z76" s="6">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>216</v>
       </c>
       <c r="AA76" s="6">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>419</v>
       </c>
       <c r="AB76" s="6">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>-175</v>
       </c>
       <c r="AC76" s="6">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>344</v>
       </c>
       <c r="AD76" s="6">
-        <f t="shared" si="154"/>
+        <f t="shared" si="156"/>
         <v>987</v>
       </c>
       <c r="AE76" s="6">
-        <f t="shared" ref="AE76:AO76" si="155">AE74-AE75</f>
+        <f t="shared" ref="AE76:AO76" si="157">AE74-AE75</f>
         <v>877.88172480000026</v>
       </c>
       <c r="AF76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>815.55465925000067</v>
       </c>
       <c r="AG76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1177.2795578499995</v>
       </c>
       <c r="AH76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1423.0190585998748</v>
       </c>
       <c r="AI76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1612.3482127429736</v>
       </c>
       <c r="AJ76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1760.0506502268543</v>
       </c>
       <c r="AK76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1848.5791686102707</v>
       </c>
       <c r="AL76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1936.0282425854994</v>
       </c>
       <c r="AM76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>2022.4911997312452</v>
       </c>
       <c r="AN76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>2108.0539626603613</v>
       </c>
       <c r="AO76" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>2192.7949800308884</v>
       </c>
       <c r="AP76" s="1">
@@ -9160,391 +9153,391 @@
         <v>2170.8670302305795</v>
       </c>
       <c r="AQ76" s="1">
-        <f t="shared" ref="AQ76:DB76" si="156">AP76*(1+AT45)</f>
+        <f t="shared" ref="AQ76:DB76" si="158">AP76*(1+AT45)</f>
         <v>2170.8670302305795</v>
       </c>
       <c r="AR76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AS76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AT76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AU76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AV76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AW76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AX76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AY76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AZ76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BA76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BB76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BC76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BD76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BE76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BF76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BG76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BH76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BI76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BJ76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BK76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BL76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BM76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BN76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BO76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BP76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BQ76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BR76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BS76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BT76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BU76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BV76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BW76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BX76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BY76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BZ76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CA76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CB76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CC76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CD76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CE76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CF76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CG76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CH76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CI76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CJ76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CK76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CL76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CM76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CN76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CO76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CP76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CQ76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CR76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CS76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CT76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CU76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CV76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CW76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CX76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CY76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CZ76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DA76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DB76" s="1">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DC76" s="1">
-        <f t="shared" ref="DC76:EI76" si="157">DB76*(1+DF45)</f>
+        <f t="shared" ref="DC76:EI76" si="159">DB76*(1+DF45)</f>
         <v>2170.8670302305795</v>
       </c>
       <c r="DD76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DE76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DF76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DG76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DH76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DI76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DJ76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DK76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DL76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DM76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DN76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DO76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DP76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DQ76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DR76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DS76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DT76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DU76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DV76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DW76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DX76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DY76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DZ76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EA76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EB76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EC76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="ED76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EE76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EF76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EG76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EH76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EI76" s="1">
-        <f t="shared" si="157"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
     </row>
@@ -9557,15 +9550,15 @@
         <v>0.45714285714285707</v>
       </c>
       <c r="T78" s="8">
-        <f t="shared" ref="T78:V78" si="158">T75/P75-1</f>
+        <f t="shared" ref="T78:V78" si="160">T75/P75-1</f>
         <v>0.56692913385826782</v>
       </c>
       <c r="U78" s="8">
-        <f t="shared" si="158"/>
+        <f t="shared" si="160"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="V78" s="8">
-        <f t="shared" si="158"/>
+        <f t="shared" si="160"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="AS78" s="3">

--- a/Financial Analysis/RHM.xlsx
+++ b/Financial Analysis/RHM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C026707B-15E6-4172-B8A3-B6085C43B931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803FFD32-5992-44B5-B86E-605A0C6700D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
   <si>
     <t>RHM</t>
   </si>
@@ -350,17 +350,27 @@
   </si>
   <si>
     <t>CapEx y/y</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-1]"/>
+    <numFmt numFmtId="166" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +400,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -411,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -439,6 +458,8 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,7 +489,7 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -518,7 +539,7 @@
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -913,7 +934,7 @@
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45930</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="11">
         <v>45967</v>
@@ -989,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501EC44B-4F3D-481F-98FD-E9305230A697}">
-  <dimension ref="B2:EV83"/>
+  <dimension ref="B2:EV89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
@@ -7737,806 +7758,331 @@
         <v>9.3157794039098352E-2</v>
       </c>
     </row>
-    <row r="61" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B61" t="s">
-        <v>92</v>
-      </c>
-      <c r="O61" s="3">
-        <f t="shared" ref="O61:V61" si="136">O37</f>
-        <v>50</v>
-      </c>
-      <c r="P61" s="3">
-        <f t="shared" si="136"/>
-        <v>63</v>
-      </c>
-      <c r="Q61" s="3">
-        <f t="shared" si="136"/>
-        <v>135</v>
-      </c>
-      <c r="R61" s="3">
-        <f t="shared" si="136"/>
-        <v>469</v>
-      </c>
-      <c r="S61" s="3">
-        <f t="shared" si="136"/>
-        <v>83</v>
-      </c>
-      <c r="T61" s="3">
-        <f t="shared" si="136"/>
-        <v>143</v>
-      </c>
-      <c r="U61" s="3">
-        <f t="shared" si="136"/>
-        <v>290.19816000000014</v>
-      </c>
-      <c r="V61" s="3">
-        <f t="shared" si="136"/>
-        <v>636.60340799999994</v>
-      </c>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3">
-        <f t="shared" ref="Z61:AC61" si="137">Z37</f>
-        <v>-27</v>
-      </c>
-      <c r="AA61" s="3">
-        <f t="shared" si="137"/>
-        <v>291</v>
-      </c>
-      <c r="AB61" s="3">
-        <f t="shared" si="137"/>
-        <v>476</v>
-      </c>
-      <c r="AC61" s="3">
-        <f t="shared" si="137"/>
-        <v>534</v>
-      </c>
-      <c r="AD61" s="3">
-        <f>AD37</f>
-        <v>717</v>
-      </c>
-      <c r="AE61" s="3">
-        <f t="shared" ref="AE61:AO61" si="138">AE37</f>
-        <v>1152.8015680000001</v>
-      </c>
-      <c r="AF61" s="3">
-        <f t="shared" si="138"/>
-        <v>1264.6224175000007</v>
-      </c>
-      <c r="AG61" s="3">
-        <f t="shared" si="138"/>
-        <v>1430.3841434999997</v>
-      </c>
-      <c r="AH61" s="3">
-        <f t="shared" si="138"/>
-        <v>1527.5501896362498</v>
-      </c>
-      <c r="AI61" s="3">
-        <f t="shared" si="138"/>
-        <v>1588.4162624936125</v>
-      </c>
-      <c r="AJ61" s="3">
-        <f t="shared" si="138"/>
-        <v>1626.2598404607766</v>
-      </c>
-      <c r="AK61" s="3">
-        <f t="shared" si="138"/>
-        <v>1660.2608966144278</v>
-      </c>
-      <c r="AL61" s="3">
-        <f t="shared" si="138"/>
-        <v>1695.0701891176468</v>
-      </c>
-      <c r="AM61" s="3">
-        <f t="shared" si="138"/>
-        <v>1730.7092906452594</v>
-      </c>
-      <c r="AN61" s="3">
-        <f t="shared" si="138"/>
-        <v>1767.2004192837585</v>
-      </c>
-      <c r="AO61" s="3">
-        <f t="shared" si="138"/>
-        <v>1804.5664601807241</v>
-      </c>
-    </row>
-    <row r="62" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="O62" s="6">
-        <v>54</v>
-      </c>
-      <c r="P62" s="6">
-        <f>133-O62</f>
-        <v>79</v>
-      </c>
-      <c r="Q62" s="6">
-        <f>306-P62-O62</f>
-        <v>173</v>
-      </c>
-      <c r="R62" s="6">
-        <f>AD62-Q62-P62-O62</f>
-        <v>502</v>
-      </c>
-      <c r="S62" s="6">
+    <row r="61" spans="2:45" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="T62" s="6">
-        <f>267-S62</f>
-        <v>159</v>
-      </c>
-      <c r="U62" s="6">
-        <f>U61</f>
-        <v>290.19816000000014</v>
-      </c>
-      <c r="V62" s="6">
-        <f>V61</f>
-        <v>636.60340799999994</v>
-      </c>
-      <c r="Y62" s="1">
-        <v>354</v>
-      </c>
-      <c r="Z62" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="1">
-        <v>332</v>
-      </c>
-      <c r="AB62" s="1">
-        <v>535</v>
-      </c>
-      <c r="AC62" s="1">
-        <v>586</v>
-      </c>
-      <c r="AD62" s="6">
-        <v>808</v>
-      </c>
-      <c r="AE62" s="6">
-        <f>AE61*1.1</f>
-        <v>1268.0817248000003</v>
-      </c>
-      <c r="AF62" s="6">
-        <f t="shared" ref="AF62:AO62" si="139">AF61*1.1</f>
-        <v>1391.0846592500009</v>
-      </c>
-      <c r="AG62" s="6">
-        <f t="shared" si="139"/>
-        <v>1573.4225578499997</v>
-      </c>
-      <c r="AH62" s="6">
-        <f t="shared" si="139"/>
-        <v>1680.305208599875</v>
-      </c>
-      <c r="AI62" s="6">
-        <f t="shared" si="139"/>
-        <v>1747.2578887429738</v>
-      </c>
-      <c r="AJ62" s="6">
-        <f t="shared" si="139"/>
-        <v>1788.8858245068543</v>
-      </c>
-      <c r="AK62" s="6">
-        <f t="shared" si="139"/>
-        <v>1826.2869862758707</v>
-      </c>
-      <c r="AL62" s="6">
-        <f t="shared" si="139"/>
-        <v>1864.5772080294116</v>
-      </c>
-      <c r="AM62" s="6">
-        <f t="shared" si="139"/>
-        <v>1903.7802197097856</v>
-      </c>
-      <c r="AN62" s="6">
-        <f t="shared" si="139"/>
-        <v>1943.9204612121346</v>
-      </c>
-      <c r="AO62" s="6">
-        <f t="shared" si="139"/>
-        <v>1985.0231061987968</v>
+      <c r="T61" s="15">
+        <v>14593</v>
       </c>
     </row>
     <row r="63" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>12</v>
-      </c>
-      <c r="O63" s="3">
-        <v>91</v>
-      </c>
-      <c r="P63" s="3">
-        <f>181-O63</f>
-        <v>90</v>
-      </c>
-      <c r="Q63" s="3">
-        <f>277-P63-O63</f>
-        <v>96</v>
-      </c>
-      <c r="R63" s="3">
-        <f>AD63-Q63-P63-O63</f>
-        <v>126</v>
-      </c>
-      <c r="S63" s="3">
-        <v>112</v>
-      </c>
-      <c r="T63" s="3">
-        <f>239-S63</f>
-        <v>127</v>
-      </c>
-      <c r="U63">
-        <f>Q63*1.4</f>
-        <v>134.39999999999998</v>
-      </c>
-      <c r="V63">
-        <f>R63*1.4</f>
-        <v>176.39999999999998</v>
-      </c>
-      <c r="Y63" s="3">
-        <v>280</v>
-      </c>
-      <c r="Z63" s="3">
-        <v>557</v>
-      </c>
-      <c r="AA63" s="3">
-        <v>254</v>
-      </c>
-      <c r="AB63" s="3">
-        <v>249</v>
-      </c>
-      <c r="AC63" s="3">
-        <v>308</v>
-      </c>
-      <c r="AD63" s="3">
-        <v>403</v>
-      </c>
-      <c r="AE63" s="3">
-        <f>SUM(S63:V63)</f>
-        <v>549.79999999999995</v>
-      </c>
-      <c r="AF63" s="3">
-        <f>AE63*1.15</f>
-        <v>632.26999999999987</v>
-      </c>
-      <c r="AG63" s="3">
-        <f>AF63*1.1</f>
-        <v>695.49699999999996</v>
-      </c>
-      <c r="AH63" s="3">
-        <f>AG63*1.05</f>
-        <v>730.27184999999997</v>
-      </c>
-      <c r="AI63" s="3">
-        <f>AH63*1.04</f>
-        <v>759.48272399999996</v>
-      </c>
-      <c r="AJ63" s="3">
-        <f>AI63*1.03</f>
-        <v>782.26720571999999</v>
-      </c>
-      <c r="AK63" s="3">
-        <f>AJ63*1.02</f>
-        <v>797.91254983440001</v>
-      </c>
-      <c r="AL63" s="3">
-        <f t="shared" ref="AL63:AO63" si="140">AK63*1.02</f>
-        <v>813.87080083108799</v>
-      </c>
-      <c r="AM63" s="3">
-        <f t="shared" si="140"/>
-        <v>830.14821684770982</v>
-      </c>
-      <c r="AN63" s="3">
-        <f t="shared" si="140"/>
-        <v>846.75118118466401</v>
-      </c>
-      <c r="AO63" s="3">
-        <f t="shared" si="140"/>
-        <v>863.68620480835727</v>
+        <v>109</v>
+      </c>
+      <c r="T63" s="16">
+        <f>Main!D9/Model!T61</f>
+        <v>5.2608702802713632</v>
       </c>
     </row>
     <row r="64" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
+        <v>110</v>
+      </c>
+      <c r="T64" s="8">
+        <f>T61/Main!D9-1</f>
+        <v>-0.80991738120780687</v>
+      </c>
+    </row>
+    <row r="67" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>92</v>
+      </c>
+      <c r="O67" s="3">
+        <f t="shared" ref="O67:V67" si="136">O37</f>
+        <v>50</v>
+      </c>
+      <c r="P67" s="3">
+        <f t="shared" si="136"/>
+        <v>63</v>
+      </c>
+      <c r="Q67" s="3">
+        <f t="shared" si="136"/>
+        <v>135</v>
+      </c>
+      <c r="R67" s="3">
+        <f t="shared" si="136"/>
+        <v>469</v>
+      </c>
+      <c r="S67" s="3">
+        <f t="shared" si="136"/>
+        <v>83</v>
+      </c>
+      <c r="T67" s="3">
+        <f t="shared" si="136"/>
+        <v>143</v>
+      </c>
+      <c r="U67" s="3">
+        <f t="shared" si="136"/>
+        <v>290.19816000000014</v>
+      </c>
+      <c r="V67" s="3">
+        <f t="shared" si="136"/>
+        <v>636.60340799999994</v>
+      </c>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3">
+        <f t="shared" ref="Z67:AC67" si="137">Z37</f>
+        <v>-27</v>
+      </c>
+      <c r="AA67" s="3">
+        <f t="shared" si="137"/>
+        <v>291</v>
+      </c>
+      <c r="AB67" s="3">
+        <f t="shared" si="137"/>
+        <v>476</v>
+      </c>
+      <c r="AC67" s="3">
+        <f t="shared" si="137"/>
+        <v>534</v>
+      </c>
+      <c r="AD67" s="3">
+        <f>AD37</f>
+        <v>717</v>
+      </c>
+      <c r="AE67" s="3">
+        <f t="shared" ref="AE67:AO67" si="138">AE37</f>
+        <v>1152.8015680000001</v>
+      </c>
+      <c r="AF67" s="3">
+        <f t="shared" si="138"/>
+        <v>1264.6224175000007</v>
+      </c>
+      <c r="AG67" s="3">
+        <f t="shared" si="138"/>
+        <v>1430.3841434999997</v>
+      </c>
+      <c r="AH67" s="3">
+        <f t="shared" si="138"/>
+        <v>1527.5501896362498</v>
+      </c>
+      <c r="AI67" s="3">
+        <f t="shared" si="138"/>
+        <v>1588.4162624936125</v>
+      </c>
+      <c r="AJ67" s="3">
+        <f t="shared" si="138"/>
+        <v>1626.2598404607766</v>
+      </c>
+      <c r="AK67" s="3">
+        <f t="shared" si="138"/>
+        <v>1660.2608966144278</v>
+      </c>
+      <c r="AL67" s="3">
+        <f t="shared" si="138"/>
+        <v>1695.0701891176468</v>
+      </c>
+      <c r="AM67" s="3">
+        <f t="shared" si="138"/>
+        <v>1730.7092906452594</v>
+      </c>
+      <c r="AN67" s="3">
+        <f t="shared" si="138"/>
+        <v>1767.2004192837585</v>
+      </c>
+      <c r="AO67" s="3">
+        <f t="shared" si="138"/>
+        <v>1804.5664601807241</v>
+      </c>
+    </row>
+    <row r="68" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O68" s="6">
+        <v>54</v>
+      </c>
+      <c r="P68" s="6">
+        <f>133-O68</f>
+        <v>79</v>
+      </c>
+      <c r="Q68" s="6">
+        <f>306-P68-O68</f>
+        <v>173</v>
+      </c>
+      <c r="R68" s="6">
+        <f>AD68-Q68-P68-O68</f>
+        <v>502</v>
+      </c>
+      <c r="S68" s="6">
+        <v>108</v>
+      </c>
+      <c r="T68" s="6">
+        <f>267-S68</f>
+        <v>159</v>
+      </c>
+      <c r="U68" s="6">
+        <f>U67</f>
+        <v>290.19816000000014</v>
+      </c>
+      <c r="V68" s="6">
+        <f>V67</f>
+        <v>636.60340799999994</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>354</v>
+      </c>
+      <c r="Z68" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA68" s="1">
+        <v>332</v>
+      </c>
+      <c r="AB68" s="1">
+        <v>535</v>
+      </c>
+      <c r="AC68" s="1">
+        <v>586</v>
+      </c>
+      <c r="AD68" s="6">
+        <v>808</v>
+      </c>
+      <c r="AE68" s="6">
+        <f>AE67*1.1</f>
+        <v>1268.0817248000003</v>
+      </c>
+      <c r="AF68" s="6">
+        <f t="shared" ref="AF68:AO68" si="139">AF67*1.1</f>
+        <v>1391.0846592500009</v>
+      </c>
+      <c r="AG68" s="6">
+        <f t="shared" si="139"/>
+        <v>1573.4225578499997</v>
+      </c>
+      <c r="AH68" s="6">
+        <f t="shared" si="139"/>
+        <v>1680.305208599875</v>
+      </c>
+      <c r="AI68" s="6">
+        <f t="shared" si="139"/>
+        <v>1747.2578887429738</v>
+      </c>
+      <c r="AJ68" s="6">
+        <f t="shared" si="139"/>
+        <v>1788.8858245068543</v>
+      </c>
+      <c r="AK68" s="6">
+        <f t="shared" si="139"/>
+        <v>1826.2869862758707</v>
+      </c>
+      <c r="AL68" s="6">
+        <f t="shared" si="139"/>
+        <v>1864.5772080294116</v>
+      </c>
+      <c r="AM68" s="6">
+        <f t="shared" si="139"/>
+        <v>1903.7802197097856</v>
+      </c>
+      <c r="AN68" s="6">
+        <f t="shared" si="139"/>
+        <v>1943.9204612121346</v>
+      </c>
+      <c r="AO68" s="6">
+        <f t="shared" si="139"/>
+        <v>1985.0231061987968</v>
+      </c>
+    </row>
+    <row r="69" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O69" s="3">
+        <v>91</v>
+      </c>
+      <c r="P69" s="3">
+        <f>181-O69</f>
+        <v>90</v>
+      </c>
+      <c r="Q69" s="3">
+        <f>277-P69-O69</f>
+        <v>96</v>
+      </c>
+      <c r="R69" s="3">
+        <f>AD69-Q69-P69-O69</f>
+        <v>126</v>
+      </c>
+      <c r="S69" s="3">
+        <v>112</v>
+      </c>
+      <c r="T69" s="3">
+        <f>239-S69</f>
+        <v>127</v>
+      </c>
+      <c r="U69">
+        <f>Q69*1.4</f>
+        <v>134.39999999999998</v>
+      </c>
+      <c r="V69">
+        <f>R69*1.4</f>
+        <v>176.39999999999998</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>280</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>557</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>254</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>249</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>308</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>403</v>
+      </c>
+      <c r="AE69" s="3">
+        <f>SUM(S69:V69)</f>
+        <v>549.79999999999995</v>
+      </c>
+      <c r="AF69" s="3">
+        <f>AE69*1.15</f>
+        <v>632.26999999999987</v>
+      </c>
+      <c r="AG69" s="3">
+        <f>AF69*1.1</f>
+        <v>695.49699999999996</v>
+      </c>
+      <c r="AH69" s="3">
+        <f>AG69*1.05</f>
+        <v>730.27184999999997</v>
+      </c>
+      <c r="AI69" s="3">
+        <f>AH69*1.04</f>
+        <v>759.48272399999996</v>
+      </c>
+      <c r="AJ69" s="3">
+        <f>AI69*1.03</f>
+        <v>782.26720571999999</v>
+      </c>
+      <c r="AK69" s="3">
+        <f>AJ69*1.02</f>
+        <v>797.91254983440001</v>
+      </c>
+      <c r="AL69" s="3">
+        <f t="shared" ref="AL69:AO69" si="140">AK69*1.02</f>
+        <v>813.87080083108799</v>
+      </c>
+      <c r="AM69" s="3">
+        <f t="shared" si="140"/>
+        <v>830.14821684770982</v>
+      </c>
+      <c r="AN69" s="3">
+        <f t="shared" si="140"/>
+        <v>846.75118118466401</v>
+      </c>
+      <c r="AO69" s="3">
+        <f t="shared" si="140"/>
+        <v>863.68620480835727</v>
+      </c>
+    </row>
+    <row r="70" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
         <v>94</v>
-      </c>
-      <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
-      <c r="R64" s="3"/>
-      <c r="S64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3">
-        <v>91</v>
-      </c>
-      <c r="AB64" s="3">
-        <v>12</v>
-      </c>
-      <c r="AC64" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE64" s="3">
-        <f t="shared" ref="AE64:AE73" si="141">SUM(S64:V64)</f>
-        <v>0</v>
-      </c>
-      <c r="AF64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B65" t="s">
-        <v>95</v>
-      </c>
-      <c r="O65" s="3">
-        <f>-3-6</f>
-        <v>-9</v>
-      </c>
-      <c r="P65" s="3">
-        <f>-7-O65</f>
-        <v>2</v>
-      </c>
-      <c r="Q65" s="3">
-        <f>-13-5-P65-O65</f>
-        <v>-11</v>
-      </c>
-      <c r="R65" s="3">
-        <f t="shared" ref="R65:R69" si="142">AD65-Q65-P65-O65</f>
-        <v>-6</v>
-      </c>
-      <c r="S65" s="3">
-        <f>-4-3</f>
-        <v>-7</v>
-      </c>
-      <c r="T65" s="3">
-        <f>14-S65</f>
-        <v>21</v>
-      </c>
-      <c r="U65">
-        <v>-10</v>
-      </c>
-      <c r="V65">
-        <v>-25</v>
-      </c>
-      <c r="Y65" s="3">
-        <f>-20-2</f>
-        <v>-22</v>
-      </c>
-      <c r="Z65" s="3">
-        <f>-42-4</f>
-        <v>-46</v>
-      </c>
-      <c r="AA65" s="3">
-        <f>-35-17</f>
-        <v>-52</v>
-      </c>
-      <c r="AB65" s="3">
-        <f>-62-18</f>
-        <v>-80</v>
-      </c>
-      <c r="AC65" s="3">
-        <f>-20+8</f>
-        <v>-12</v>
-      </c>
-      <c r="AD65" s="3">
-        <f>-18-6</f>
-        <v>-24</v>
-      </c>
-      <c r="AE65" s="3">
-        <f t="shared" si="141"/>
-        <v>-21</v>
-      </c>
-      <c r="AF65" s="3">
-        <f>AE65*1.1</f>
-        <v>-23.1</v>
-      </c>
-      <c r="AG65" s="3">
-        <f t="shared" ref="AG65:AO65" si="143">AF65*1.1</f>
-        <v>-25.410000000000004</v>
-      </c>
-      <c r="AH65" s="3">
-        <f t="shared" si="143"/>
-        <v>-27.951000000000008</v>
-      </c>
-      <c r="AI65" s="3">
-        <f t="shared" si="143"/>
-        <v>-30.746100000000009</v>
-      </c>
-      <c r="AJ65" s="3">
-        <f t="shared" si="143"/>
-        <v>-33.820710000000012</v>
-      </c>
-      <c r="AK65" s="3">
-        <f t="shared" si="143"/>
-        <v>-37.202781000000016</v>
-      </c>
-      <c r="AL65" s="3">
-        <f t="shared" si="143"/>
-        <v>-40.923059100000017</v>
-      </c>
-      <c r="AM65" s="3">
-        <f t="shared" si="143"/>
-        <v>-45.015365010000025</v>
-      </c>
-      <c r="AN65" s="3">
-        <f t="shared" si="143"/>
-        <v>-49.516901511000029</v>
-      </c>
-      <c r="AO65" s="3">
-        <f t="shared" si="143"/>
-        <v>-54.468591662100039</v>
-      </c>
-    </row>
-    <row r="66" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B66" t="s">
-        <v>96</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1</v>
-      </c>
-      <c r="P66" s="3">
-        <f>69-O66</f>
-        <v>68</v>
-      </c>
-      <c r="Q66" s="3">
-        <f>66-P66-O66</f>
-        <v>-3</v>
-      </c>
-      <c r="R66" s="3">
-        <f t="shared" si="142"/>
-        <v>37</v>
-      </c>
-      <c r="S66" s="3">
-        <v>0</v>
-      </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>-6</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>-5</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>-48</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>103</v>
-      </c>
-      <c r="AE66" s="3">
-        <f t="shared" si="141"/>
-        <v>0</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B67" t="s">
-        <v>97</v>
-      </c>
-      <c r="O67" s="3">
-        <v>93</v>
-      </c>
-      <c r="P67" s="3">
-        <f>16-O67</f>
-        <v>-77</v>
-      </c>
-      <c r="Q67" s="3">
-        <f>94-P67-O67</f>
-        <v>78</v>
-      </c>
-      <c r="R67" s="3">
-        <f t="shared" si="142"/>
-        <v>41</v>
-      </c>
-      <c r="S67" s="3">
-        <v>90</v>
-      </c>
-      <c r="T67" s="3">
-        <f>-15-S67</f>
-        <v>-105</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>110</v>
-      </c>
-      <c r="Y67" s="3">
-        <v>23</v>
-      </c>
-      <c r="Z67" s="3">
-        <v>88</v>
-      </c>
-      <c r="AA67" s="3">
-        <v>-51</v>
-      </c>
-      <c r="AB67" s="3">
-        <v>-9</v>
-      </c>
-      <c r="AC67" s="3">
-        <v>-59</v>
-      </c>
-      <c r="AD67" s="3">
-        <v>135</v>
-      </c>
-      <c r="AE67" s="3">
-        <f t="shared" si="141"/>
-        <v>95</v>
-      </c>
-      <c r="AF67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN67" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO67" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B68" t="s">
-        <v>98</v>
-      </c>
-      <c r="O68" s="3">
-        <v>-202</v>
-      </c>
-      <c r="P68" s="3">
-        <f>-74-O68</f>
-        <v>128</v>
-      </c>
-      <c r="Q68" s="3">
-        <f>-151-P68-O68</f>
-        <v>-77</v>
-      </c>
-      <c r="R68" s="3">
-        <f t="shared" si="142"/>
-        <v>558</v>
-      </c>
-      <c r="S68" s="3">
-        <v>122</v>
-      </c>
-      <c r="T68" s="3">
-        <f>-669-S68</f>
-        <v>-791</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <f>R68*1.5</f>
-        <v>837</v>
-      </c>
-      <c r="Y68" s="3">
-        <v>31</v>
-      </c>
-      <c r="Z68" s="3">
-        <v>-119</v>
-      </c>
-      <c r="AA68" s="3">
-        <v>22</v>
-      </c>
-      <c r="AB68" s="3">
-        <v>-507</v>
-      </c>
-      <c r="AC68" s="3">
-        <v>29</v>
-      </c>
-      <c r="AD68" s="3">
-        <v>407</v>
-      </c>
-      <c r="AE68" s="3">
-        <f t="shared" si="141"/>
-        <v>168</v>
-      </c>
-      <c r="AF68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B69" t="s">
-        <v>99</v>
-      </c>
-      <c r="O69" s="3">
-        <v>-145</v>
-      </c>
-      <c r="P69" s="3">
-        <f>-159-O69</f>
-        <v>-14</v>
-      </c>
-      <c r="Q69" s="3">
-        <f>-174-P69-O69</f>
-        <v>-15</v>
-      </c>
-      <c r="R69" s="3">
-        <f t="shared" si="142"/>
-        <v>72</v>
-      </c>
-      <c r="S69" s="3">
-        <v>-5</v>
-      </c>
-      <c r="T69" s="3">
-        <f>-100-S69</f>
-        <v>-95</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="3">
-        <v>-68</v>
-      </c>
-      <c r="Z69" s="3">
-        <v>-28</v>
-      </c>
-      <c r="AA69" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB69" s="3">
-        <v>-39</v>
-      </c>
-      <c r="AC69" s="3">
-        <v>-217</v>
-      </c>
-      <c r="AD69" s="3">
-        <v>-102</v>
-      </c>
-      <c r="AE69" s="3">
-        <f t="shared" si="141"/>
-        <v>-100</v>
-      </c>
-      <c r="AF69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B70" t="s">
-        <v>100</v>
       </c>
       <c r="O70" s="3"/>
       <c r="P70" s="3"/>
@@ -8545,16 +8091,20 @@
       <c r="S70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
-      <c r="AA70" s="3"/>
-      <c r="AB70" s="3"/>
+      <c r="AA70" s="3">
+        <v>91</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>12</v>
+      </c>
       <c r="AC70" s="3">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
       <c r="AE70" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" ref="AE70:AE79" si="141">SUM(S70:V70)</f>
         <v>0</v>
       </c>
       <c r="AF70" s="3">
@@ -8588,1011 +8138,1508 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:139" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O71" s="3">
-        <v>1</v>
+        <f>-3-6</f>
+        <v>-9</v>
       </c>
       <c r="P71" s="3">
-        <f>4-O71</f>
-        <v>3</v>
+        <f>-7-O71</f>
+        <v>2</v>
       </c>
       <c r="Q71" s="3">
-        <f>16-P71-O71</f>
-        <v>12</v>
+        <f>-13-5-P71-O71</f>
+        <v>-11</v>
       </c>
       <c r="R71" s="3">
-        <f t="shared" ref="R71:R73" si="144">AD71-Q71-P71-O71</f>
-        <v>-1</v>
+        <f t="shared" ref="R71:R75" si="142">AD71-Q71-P71-O71</f>
+        <v>-6</v>
       </c>
       <c r="S71" s="3">
-        <v>4</v>
+        <f>-4-3</f>
+        <v>-7</v>
       </c>
       <c r="T71" s="3">
-        <f>4-S71</f>
-        <v>0</v>
+        <f>14-S71</f>
+        <v>21</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="Y71" s="3">
-        <v>-37</v>
+        <f>-20-2</f>
+        <v>-22</v>
       </c>
       <c r="Z71" s="3">
-        <v>-10</v>
+        <f>-42-4</f>
+        <v>-46</v>
       </c>
       <c r="AA71" s="3">
-        <v>-15</v>
+        <f>-35-17</f>
+        <v>-52</v>
       </c>
       <c r="AB71" s="3">
-        <v>-32</v>
+        <f>-62-18</f>
+        <v>-80</v>
       </c>
       <c r="AC71" s="3">
-        <v>-4</v>
+        <f>-20+8</f>
+        <v>-12</v>
       </c>
       <c r="AD71" s="3">
-        <v>15</v>
+        <f>-18-6</f>
+        <v>-24</v>
       </c>
       <c r="AE71" s="3">
         <f t="shared" si="141"/>
+        <v>-21</v>
+      </c>
+      <c r="AF71" s="3">
+        <f>AE71*1.1</f>
+        <v>-23.1</v>
+      </c>
+      <c r="AG71" s="3">
+        <f t="shared" ref="AG71:AO71" si="143">AF71*1.1</f>
+        <v>-25.410000000000004</v>
+      </c>
+      <c r="AH71" s="3">
+        <f t="shared" si="143"/>
+        <v>-27.951000000000008</v>
+      </c>
+      <c r="AI71" s="3">
+        <f t="shared" si="143"/>
+        <v>-30.746100000000009</v>
+      </c>
+      <c r="AJ71" s="3">
+        <f t="shared" si="143"/>
+        <v>-33.820710000000012</v>
+      </c>
+      <c r="AK71" s="3">
+        <f t="shared" si="143"/>
+        <v>-37.202781000000016</v>
+      </c>
+      <c r="AL71" s="3">
+        <f t="shared" si="143"/>
+        <v>-40.923059100000017</v>
+      </c>
+      <c r="AM71" s="3">
+        <f t="shared" si="143"/>
+        <v>-45.015365010000025</v>
+      </c>
+      <c r="AN71" s="3">
+        <f t="shared" si="143"/>
+        <v>-49.516901511000029</v>
+      </c>
+      <c r="AO71" s="3">
+        <f t="shared" si="143"/>
+        <v>-54.468591662100039</v>
+      </c>
+    </row>
+    <row r="72" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>96</v>
+      </c>
+      <c r="O72" s="3">
+        <v>1</v>
+      </c>
+      <c r="P72" s="3">
+        <f>69-O72</f>
+        <v>68</v>
+      </c>
+      <c r="Q72" s="3">
+        <f>66-P72-O72</f>
+        <v>-3</v>
+      </c>
+      <c r="R72" s="3">
+        <f t="shared" si="142"/>
+        <v>37</v>
+      </c>
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="3">
+        <v>-6</v>
+      </c>
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="3">
+        <v>-5</v>
+      </c>
+      <c r="AC72" s="3">
+        <v>-48</v>
+      </c>
+      <c r="AD72" s="3">
+        <v>103</v>
+      </c>
+      <c r="AE72" s="3">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>97</v>
+      </c>
+      <c r="O73" s="3">
+        <v>93</v>
+      </c>
+      <c r="P73" s="3">
+        <f>16-O73</f>
+        <v>-77</v>
+      </c>
+      <c r="Q73" s="3">
+        <f>94-P73-O73</f>
+        <v>78</v>
+      </c>
+      <c r="R73" s="3">
+        <f t="shared" si="142"/>
+        <v>41</v>
+      </c>
+      <c r="S73" s="3">
+        <v>90</v>
+      </c>
+      <c r="T73" s="3">
+        <f>-15-S73</f>
+        <v>-105</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>110</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>23</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>88</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>-51</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>-9</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>-59</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>135</v>
+      </c>
+      <c r="AE73" s="3">
+        <f t="shared" si="141"/>
+        <v>95</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>98</v>
+      </c>
+      <c r="O74" s="3">
+        <v>-202</v>
+      </c>
+      <c r="P74" s="3">
+        <f>-74-O74</f>
+        <v>128</v>
+      </c>
+      <c r="Q74" s="3">
+        <f>-151-P74-O74</f>
+        <v>-77</v>
+      </c>
+      <c r="R74" s="3">
+        <f t="shared" si="142"/>
+        <v>558</v>
+      </c>
+      <c r="S74" s="3">
+        <v>122</v>
+      </c>
+      <c r="T74" s="3">
+        <f>-669-S74</f>
+        <v>-791</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <f>R74*1.5</f>
+        <v>837</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>31</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>-119</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>22</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>-507</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>29</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>407</v>
+      </c>
+      <c r="AE74" s="3">
+        <f t="shared" si="141"/>
+        <v>168</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>99</v>
+      </c>
+      <c r="O75" s="3">
+        <v>-145</v>
+      </c>
+      <c r="P75" s="3">
+        <f>-159-O75</f>
+        <v>-14</v>
+      </c>
+      <c r="Q75" s="3">
+        <f>-174-P75-O75</f>
+        <v>-15</v>
+      </c>
+      <c r="R75" s="3">
+        <f t="shared" si="142"/>
+        <v>72</v>
+      </c>
+      <c r="S75" s="3">
+        <v>-5</v>
+      </c>
+      <c r="T75" s="3">
+        <f>-100-S75</f>
+        <v>-95</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>-68</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>-28</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>-39</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>-217</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>-102</v>
+      </c>
+      <c r="AE75" s="3">
+        <f t="shared" si="141"/>
+        <v>-100</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>100</v>
+      </c>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="3"/>
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
+      <c r="AC76" s="3">
+        <v>39</v>
+      </c>
+      <c r="AD76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="3">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>101</v>
+      </c>
+      <c r="O77" s="3">
+        <v>1</v>
+      </c>
+      <c r="P77" s="3">
+        <f>4-O77</f>
+        <v>3</v>
+      </c>
+      <c r="Q77" s="3">
+        <f>16-P77-O77</f>
+        <v>12</v>
+      </c>
+      <c r="R77" s="3">
+        <f t="shared" ref="R77:R79" si="144">AD77-Q77-P77-O77</f>
+        <v>-1</v>
+      </c>
+      <c r="S77" s="3">
         <v>4</v>
       </c>
-      <c r="AF71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO71" s="3">
+      <c r="T77" s="3">
+        <f>4-S77</f>
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>-37</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>-10</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>-15</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>-32</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>-4</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>15</v>
+      </c>
+      <c r="AE77" s="3">
+        <f t="shared" si="141"/>
+        <v>4</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
+    <row r="78" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
         <v>102</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3">
-        <f>9-P72-O72</f>
+      <c r="O78" s="3">
+        <v>0</v>
+      </c>
+      <c r="P78" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="3">
+        <f>9-P78-O78</f>
         <v>9</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R78" s="3">
         <f t="shared" si="144"/>
         <v>7</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S78" s="3">
         <v>6</v>
       </c>
-      <c r="T72" s="3">
-        <f>8-S72</f>
+      <c r="T78" s="3">
+        <f>8-S78</f>
         <v>2</v>
       </c>
-      <c r="U72">
+      <c r="U78">
         <v>3</v>
       </c>
-      <c r="V72">
+      <c r="V78">
         <v>5</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y78" s="3">
         <v>17</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="Z78" s="3">
         <v>21</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA78" s="3">
         <v>30</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB78" s="3">
         <v>17</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC78" s="3">
         <v>29</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AD78" s="3">
         <v>16</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AE78" s="3">
         <f t="shared" si="141"/>
         <v>16</v>
       </c>
-      <c r="AF72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO72" s="3">
+      <c r="AF78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO78" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
         <v>103</v>
       </c>
-      <c r="O73" s="3">
+      <c r="O79" s="3">
         <v>11</v>
       </c>
-      <c r="P73" s="3">
-        <f>29-O73</f>
+      <c r="P79" s="3">
+        <f>29-O79</f>
         <v>18</v>
       </c>
-      <c r="Q73" s="3">
-        <f>67-P73-O73</f>
+      <c r="Q79" s="3">
+        <f>67-P79-O79</f>
         <v>38</v>
       </c>
-      <c r="R73" s="3">
+      <c r="R79" s="3">
         <f t="shared" si="144"/>
         <v>-109</v>
       </c>
-      <c r="S73" s="3">
+      <c r="S79" s="3">
         <v>-10</v>
       </c>
-      <c r="T73" s="3">
-        <f>-25-S73</f>
+      <c r="T79" s="3">
+        <f>-25-S79</f>
         <v>-15</v>
       </c>
-      <c r="U73">
-        <v>0</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="3">
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="3">
         <v>24</v>
       </c>
-      <c r="Z73" s="3">
+      <c r="Z79" s="3">
         <v>-5</v>
       </c>
-      <c r="AA73" s="3">
+      <c r="AA79" s="3">
         <v>16</v>
       </c>
-      <c r="AB73" s="3">
+      <c r="AB79" s="3">
         <v>33</v>
       </c>
-      <c r="AC73" s="3">
+      <c r="AC79" s="3">
         <v>28</v>
       </c>
-      <c r="AD73" s="3">
+      <c r="AD79" s="3">
         <v>-42</v>
       </c>
-      <c r="AE73" s="3">
+      <c r="AE79" s="3">
         <f t="shared" si="141"/>
         <v>-25</v>
       </c>
-      <c r="AF73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO73" s="3">
+      <c r="AF79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO79" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="1" t="s">
+    <row r="80" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O74" s="6">
-        <f t="shared" ref="O74:P74" si="145">O62+SUM(O63:O73)</f>
+      <c r="O80" s="6">
+        <f t="shared" ref="O80:P80" si="145">O68+SUM(O69:O79)</f>
         <v>-105</v>
       </c>
-      <c r="P74" s="6">
+      <c r="P80" s="6">
         <f t="shared" si="145"/>
         <v>297</v>
       </c>
-      <c r="Q74" s="6">
-        <f t="shared" ref="Q74:R74" si="146">Q62+SUM(Q63:Q73)</f>
+      <c r="Q80" s="6">
+        <f t="shared" ref="Q80:R80" si="146">Q68+SUM(Q69:Q79)</f>
         <v>300</v>
       </c>
-      <c r="R74" s="6">
+      <c r="R80" s="6">
         <f t="shared" si="146"/>
         <v>1227</v>
       </c>
-      <c r="S74" s="6">
-        <f t="shared" ref="S74:T74" si="147">S62+SUM(S63:S73)</f>
+      <c r="S80" s="6">
+        <f t="shared" ref="S80:T80" si="147">S68+SUM(S69:S79)</f>
         <v>420</v>
       </c>
-      <c r="T74" s="6">
+      <c r="T80" s="6">
         <f t="shared" si="147"/>
         <v>-697</v>
       </c>
-      <c r="U74" s="6">
-        <f>U62+SUM(U63:U73)</f>
+      <c r="U80" s="6">
+        <f>U68+SUM(U69:U79)</f>
         <v>417.59816000000012</v>
       </c>
-      <c r="V74" s="6">
-        <f>V62+SUM(V63:V73)</f>
+      <c r="V80" s="6">
+        <f>V68+SUM(V69:V79)</f>
         <v>1740.003408</v>
       </c>
-      <c r="Y74" s="6">
-        <f t="shared" ref="Y74:AD74" si="148">Y62+SUM(Y63:Y73)</f>
+      <c r="Y80" s="6">
+        <f t="shared" ref="Y80:AD80" si="148">Y68+SUM(Y69:Y79)</f>
         <v>602</v>
       </c>
-      <c r="Z74" s="6">
+      <c r="Z80" s="6">
         <f t="shared" si="148"/>
         <v>453</v>
       </c>
-      <c r="AA74" s="6">
+      <c r="AA80" s="6">
         <f t="shared" si="148"/>
         <v>690</v>
       </c>
-      <c r="AB74" s="6">
+      <c r="AB80" s="6">
         <f t="shared" si="148"/>
         <v>174</v>
       </c>
-      <c r="AC74" s="6">
+      <c r="AC80" s="6">
         <f t="shared" si="148"/>
         <v>742</v>
       </c>
-      <c r="AD74" s="6">
+      <c r="AD80" s="6">
         <f t="shared" si="148"/>
         <v>1719</v>
       </c>
-      <c r="AE74" s="6">
-        <f t="shared" ref="AE74:AO74" si="149">AE62+SUM(AE63:AE73)</f>
+      <c r="AE80" s="6">
+        <f t="shared" ref="AE80:AO80" si="149">AE68+SUM(AE69:AE79)</f>
         <v>1954.8817248000003</v>
       </c>
-      <c r="AF74" s="6">
+      <c r="AF80" s="6">
         <f t="shared" si="149"/>
         <v>2000.2546592500007</v>
       </c>
-      <c r="AG74" s="6">
+      <c r="AG80" s="6">
         <f t="shared" si="149"/>
         <v>2243.5095578499995</v>
       </c>
-      <c r="AH74" s="6">
+      <c r="AH80" s="6">
         <f t="shared" si="149"/>
         <v>2382.6260585998748</v>
       </c>
-      <c r="AI74" s="6">
+      <c r="AI80" s="6">
         <f t="shared" si="149"/>
         <v>2475.9945127429737</v>
       </c>
-      <c r="AJ74" s="6">
+      <c r="AJ80" s="6">
         <f t="shared" si="149"/>
         <v>2537.3323202268543</v>
       </c>
-      <c r="AK74" s="6">
+      <c r="AK80" s="6">
         <f t="shared" si="149"/>
         <v>2586.9967551102709</v>
       </c>
-      <c r="AL74" s="6">
+      <c r="AL80" s="6">
         <f t="shared" si="149"/>
         <v>2637.5249497604996</v>
       </c>
-      <c r="AM74" s="6">
+      <c r="AM80" s="6">
         <f t="shared" si="149"/>
         <v>2688.9130715474953</v>
       </c>
-      <c r="AN74" s="6">
+      <c r="AN80" s="6">
         <f t="shared" si="149"/>
         <v>2741.1547408857987</v>
       </c>
-      <c r="AO74" s="6">
+      <c r="AO80" s="6">
         <f t="shared" si="149"/>
         <v>2794.240719345054</v>
       </c>
     </row>
-    <row r="75" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B75" t="s">
+    <row r="81" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
         <v>105</v>
       </c>
-      <c r="O75" s="3">
+      <c r="O81" s="3">
         <v>105</v>
       </c>
-      <c r="P75" s="3">
-        <f>232-O75</f>
+      <c r="P81" s="3">
+        <f>232-O81</f>
         <v>127</v>
       </c>
-      <c r="Q75" s="3">
-        <f>416-P75-O75</f>
+      <c r="Q81" s="3">
+        <f>416-P81-O81</f>
         <v>184</v>
       </c>
-      <c r="R75" s="3">
-        <f>AD75-Q75-P75-O75</f>
+      <c r="R81" s="3">
+        <f>AD81-Q81-P81-O81</f>
         <v>316</v>
       </c>
-      <c r="S75" s="3">
+      <c r="S81" s="3">
         <v>153</v>
       </c>
-      <c r="T75" s="3">
-        <f>352-S75</f>
+      <c r="T81" s="3">
+        <f>352-S81</f>
         <v>199</v>
       </c>
-      <c r="U75" s="3">
-        <f t="shared" ref="U75:V75" si="150">Q75*1.45</f>
+      <c r="U81" s="3">
+        <f t="shared" ref="U81:V81" si="150">Q81*1.45</f>
         <v>266.8</v>
       </c>
-      <c r="V75" s="3">
+      <c r="V81" s="3">
         <f t="shared" si="150"/>
         <v>458.2</v>
       </c>
-      <c r="Y75" s="3">
+      <c r="Y81" s="3">
         <v>288</v>
       </c>
-      <c r="Z75" s="3">
+      <c r="Z81" s="3">
         <v>237</v>
       </c>
-      <c r="AA75" s="3">
+      <c r="AA81" s="3">
         <v>271</v>
       </c>
-      <c r="AB75" s="3">
+      <c r="AB81" s="3">
         <v>349</v>
       </c>
-      <c r="AC75" s="3">
+      <c r="AC81" s="3">
         <v>398</v>
       </c>
-      <c r="AD75" s="3">
+      <c r="AD81" s="3">
         <v>732</v>
       </c>
-      <c r="AE75" s="3">
-        <f>SUM(S75:V75)</f>
+      <c r="AE81" s="3">
+        <f>SUM(S81:V81)</f>
         <v>1077</v>
       </c>
-      <c r="AF75" s="3">
-        <f>AE75*1.1</f>
+      <c r="AF81" s="3">
+        <f>AE81*1.1</f>
         <v>1184.7</v>
       </c>
-      <c r="AG75" s="3">
-        <f t="shared" ref="AG75:AJ75" si="151">AF75*0.9</f>
+      <c r="AG81" s="3">
+        <f t="shared" ref="AG81:AJ81" si="151">AF81*0.9</f>
         <v>1066.23</v>
       </c>
-      <c r="AH75" s="3">
+      <c r="AH81" s="3">
         <f t="shared" si="151"/>
         <v>959.60700000000008</v>
       </c>
-      <c r="AI75" s="3">
+      <c r="AI81" s="3">
         <f t="shared" si="151"/>
         <v>863.64630000000011</v>
       </c>
-      <c r="AJ75" s="3">
+      <c r="AJ81" s="3">
         <f t="shared" si="151"/>
         <v>777.28167000000008</v>
       </c>
-      <c r="AK75" s="3">
-        <f>AJ75*0.95</f>
+      <c r="AK81" s="3">
+        <f>AJ81*0.95</f>
         <v>738.41758650000008</v>
       </c>
-      <c r="AL75" s="3">
-        <f t="shared" ref="AL75:AO75" si="152">AK75*0.95</f>
+      <c r="AL81" s="3">
+        <f t="shared" ref="AL81:AO81" si="152">AK81*0.95</f>
         <v>701.4967071750001</v>
       </c>
-      <c r="AM75" s="3">
+      <c r="AM81" s="3">
         <f t="shared" si="152"/>
         <v>666.42187181625002</v>
       </c>
-      <c r="AN75" s="3">
+      <c r="AN81" s="3">
         <f t="shared" si="152"/>
         <v>633.10077822543747</v>
       </c>
-      <c r="AO75" s="3">
+      <c r="AO81" s="3">
         <f t="shared" si="152"/>
         <v>601.44573931416562</v>
       </c>
     </row>
-    <row r="76" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="1" t="s">
+    <row r="82" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="O76" s="6">
-        <f t="shared" ref="O76:P76" si="153">O74-O75</f>
+      <c r="O82" s="6">
+        <f t="shared" ref="O82:P82" si="153">O80-O81</f>
         <v>-210</v>
       </c>
-      <c r="P76" s="6">
+      <c r="P82" s="6">
         <f t="shared" si="153"/>
         <v>170</v>
       </c>
-      <c r="Q76" s="6">
-        <f t="shared" ref="Q76:R76" si="154">Q74-Q75</f>
+      <c r="Q82" s="6">
+        <f t="shared" ref="Q82:R82" si="154">Q80-Q81</f>
         <v>116</v>
       </c>
-      <c r="R76" s="6">
+      <c r="R82" s="6">
         <f t="shared" si="154"/>
         <v>911</v>
       </c>
-      <c r="S76" s="6">
-        <f t="shared" ref="S76:V76" si="155">S74-S75</f>
+      <c r="S82" s="6">
+        <f t="shared" ref="S82:V82" si="155">S80-S81</f>
         <v>267</v>
       </c>
-      <c r="T76" s="6">
+      <c r="T82" s="6">
         <f t="shared" si="155"/>
         <v>-896</v>
       </c>
-      <c r="U76" s="6">
+      <c r="U82" s="6">
         <f t="shared" si="155"/>
         <v>150.79816000000011</v>
       </c>
-      <c r="V76" s="6">
+      <c r="V82" s="6">
         <f t="shared" si="155"/>
         <v>1281.803408</v>
       </c>
-      <c r="Y76" s="6">
-        <f t="shared" ref="Y76:AD76" si="156">Y74-Y75</f>
+      <c r="Y82" s="6">
+        <f t="shared" ref="Y82:AD82" si="156">Y80-Y81</f>
         <v>314</v>
       </c>
-      <c r="Z76" s="6">
+      <c r="Z82" s="6">
         <f t="shared" si="156"/>
         <v>216</v>
       </c>
-      <c r="AA76" s="6">
+      <c r="AA82" s="6">
         <f t="shared" si="156"/>
         <v>419</v>
       </c>
-      <c r="AB76" s="6">
+      <c r="AB82" s="6">
         <f t="shared" si="156"/>
         <v>-175</v>
       </c>
-      <c r="AC76" s="6">
+      <c r="AC82" s="6">
         <f t="shared" si="156"/>
         <v>344</v>
       </c>
-      <c r="AD76" s="6">
+      <c r="AD82" s="6">
         <f t="shared" si="156"/>
         <v>987</v>
       </c>
-      <c r="AE76" s="6">
-        <f t="shared" ref="AE76:AO76" si="157">AE74-AE75</f>
+      <c r="AE82" s="6">
+        <f t="shared" ref="AE82:AO82" si="157">AE80-AE81</f>
         <v>877.88172480000026</v>
       </c>
-      <c r="AF76" s="6">
+      <c r="AF82" s="6">
         <f t="shared" si="157"/>
         <v>815.55465925000067</v>
       </c>
-      <c r="AG76" s="6">
+      <c r="AG82" s="6">
         <f t="shared" si="157"/>
         <v>1177.2795578499995</v>
       </c>
-      <c r="AH76" s="6">
+      <c r="AH82" s="6">
         <f t="shared" si="157"/>
         <v>1423.0190585998748</v>
       </c>
-      <c r="AI76" s="6">
+      <c r="AI82" s="6">
         <f t="shared" si="157"/>
         <v>1612.3482127429736</v>
       </c>
-      <c r="AJ76" s="6">
+      <c r="AJ82" s="6">
         <f t="shared" si="157"/>
         <v>1760.0506502268543</v>
       </c>
-      <c r="AK76" s="6">
+      <c r="AK82" s="6">
         <f t="shared" si="157"/>
         <v>1848.5791686102707</v>
       </c>
-      <c r="AL76" s="6">
+      <c r="AL82" s="6">
         <f t="shared" si="157"/>
         <v>1936.0282425854994</v>
       </c>
-      <c r="AM76" s="6">
+      <c r="AM82" s="6">
         <f t="shared" si="157"/>
         <v>2022.4911997312452</v>
       </c>
-      <c r="AN76" s="6">
+      <c r="AN82" s="6">
         <f t="shared" si="157"/>
         <v>2108.0539626603613</v>
       </c>
-      <c r="AO76" s="6">
+      <c r="AO82" s="6">
         <f t="shared" si="157"/>
         <v>2192.7949800308884</v>
       </c>
-      <c r="AP76" s="1">
-        <f>AO76*(1+AS45)</f>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AQ76" s="1">
-        <f t="shared" ref="AQ76:DB76" si="158">AP76*(1+AT45)</f>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AR76" s="1">
+      <c r="AP82" s="1">
+        <f>AO82*(1+AS45)</f>
+        <v>2170.8670302305795</v>
+      </c>
+      <c r="AQ82" s="1">
+        <f t="shared" ref="AQ82:DB82" si="158">AP82*(1+AT45)</f>
+        <v>2170.8670302305795</v>
+      </c>
+      <c r="AR82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="AS76" s="1">
+      <c r="AS82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="AT76" s="1">
+      <c r="AT82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="AU76" s="1">
+      <c r="AU82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="AV76" s="1">
+      <c r="AV82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="AW76" s="1">
+      <c r="AW82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="AX76" s="1">
+      <c r="AX82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="AY76" s="1">
+      <c r="AY82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="AZ76" s="1">
+      <c r="AZ82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BA76" s="1">
+      <c r="BA82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BB76" s="1">
+      <c r="BB82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BC76" s="1">
+      <c r="BC82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BD76" s="1">
+      <c r="BD82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BE76" s="1">
+      <c r="BE82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BF76" s="1">
+      <c r="BF82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BG76" s="1">
+      <c r="BG82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BH76" s="1">
+      <c r="BH82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BI76" s="1">
+      <c r="BI82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BJ76" s="1">
+      <c r="BJ82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BK76" s="1">
+      <c r="BK82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BL76" s="1">
+      <c r="BL82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BM76" s="1">
+      <c r="BM82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BN76" s="1">
+      <c r="BN82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BO76" s="1">
+      <c r="BO82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BP76" s="1">
+      <c r="BP82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BQ76" s="1">
+      <c r="BQ82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BR76" s="1">
+      <c r="BR82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BS76" s="1">
+      <c r="BS82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BT76" s="1">
+      <c r="BT82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BU76" s="1">
+      <c r="BU82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BV76" s="1">
+      <c r="BV82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BW76" s="1">
+      <c r="BW82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BX76" s="1">
+      <c r="BX82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BY76" s="1">
+      <c r="BY82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="BZ76" s="1">
+      <c r="BZ82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CA76" s="1">
+      <c r="CA82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CB76" s="1">
+      <c r="CB82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CC76" s="1">
+      <c r="CC82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CD76" s="1">
+      <c r="CD82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CE76" s="1">
+      <c r="CE82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CF76" s="1">
+      <c r="CF82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CG76" s="1">
+      <c r="CG82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CH76" s="1">
+      <c r="CH82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CI76" s="1">
+      <c r="CI82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CJ76" s="1">
+      <c r="CJ82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CK76" s="1">
+      <c r="CK82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CL76" s="1">
+      <c r="CL82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CM76" s="1">
+      <c r="CM82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CN76" s="1">
+      <c r="CN82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CO76" s="1">
+      <c r="CO82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CP76" s="1">
+      <c r="CP82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CQ76" s="1">
+      <c r="CQ82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CR76" s="1">
+      <c r="CR82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CS76" s="1">
+      <c r="CS82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CT76" s="1">
+      <c r="CT82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CU76" s="1">
+      <c r="CU82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CV76" s="1">
+      <c r="CV82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CW76" s="1">
+      <c r="CW82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CX76" s="1">
+      <c r="CX82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CY76" s="1">
+      <c r="CY82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="CZ76" s="1">
+      <c r="CZ82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DA76" s="1">
+      <c r="DA82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DB76" s="1">
+      <c r="DB82" s="1">
         <f t="shared" si="158"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DC76" s="1">
-        <f t="shared" ref="DC76:EI76" si="159">DB76*(1+DF45)</f>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DD76" s="1">
+      <c r="DC82" s="1">
+        <f t="shared" ref="DC82:EI82" si="159">DB82*(1+DF45)</f>
+        <v>2170.8670302305795</v>
+      </c>
+      <c r="DD82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DE76" s="1">
+      <c r="DE82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DF76" s="1">
+      <c r="DF82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DG76" s="1">
+      <c r="DG82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DH76" s="1">
+      <c r="DH82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DI76" s="1">
+      <c r="DI82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DJ76" s="1">
+      <c r="DJ82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DK76" s="1">
+      <c r="DK82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DL76" s="1">
+      <c r="DL82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DM76" s="1">
+      <c r="DM82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DN76" s="1">
+      <c r="DN82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DO76" s="1">
+      <c r="DO82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DP76" s="1">
+      <c r="DP82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DQ76" s="1">
+      <c r="DQ82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DR76" s="1">
+      <c r="DR82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DS76" s="1">
+      <c r="DS82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DT76" s="1">
+      <c r="DT82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DU76" s="1">
+      <c r="DU82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DV76" s="1">
+      <c r="DV82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DW76" s="1">
+      <c r="DW82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DX76" s="1">
+      <c r="DX82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DY76" s="1">
+      <c r="DY82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="DZ76" s="1">
+      <c r="DZ82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="EA76" s="1">
+      <c r="EA82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="EB76" s="1">
+      <c r="EB82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="EC76" s="1">
+      <c r="EC82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="ED76" s="1">
+      <c r="ED82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="EE76" s="1">
+      <c r="EE82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="EF76" s="1">
+      <c r="EF82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="EG76" s="1">
+      <c r="EG82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="EH76" s="1">
+      <c r="EH82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
-      <c r="EI76" s="1">
+      <c r="EI82" s="1">
         <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
     </row>
-    <row r="78" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B78" t="s">
+    <row r="84" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
         <v>107</v>
       </c>
-      <c r="S78" s="8">
-        <f>S75/O75-1</f>
+      <c r="S84" s="8">
+        <f>S81/O81-1</f>
         <v>0.45714285714285707</v>
       </c>
-      <c r="T78" s="8">
-        <f t="shared" ref="T78:V78" si="160">T75/P75-1</f>
+      <c r="T84" s="8">
+        <f t="shared" ref="T84:V84" si="160">T81/P81-1</f>
         <v>0.56692913385826782</v>
       </c>
-      <c r="U78" s="8">
+      <c r="U84" s="8">
         <f t="shared" si="160"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="V78" s="8">
+      <c r="V84" s="8">
         <f t="shared" si="160"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="AS78" s="3">
-        <f>NPV(AS46,AE76:EI76)</f>
+      <c r="AS84" s="3">
+        <f>NPV(AS46,AE82:EI82)</f>
         <v>26107.609767880786</v>
       </c>
     </row>
-    <row r="79" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="AS79" s="3">
+    <row r="85" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="AS85" s="3">
         <f>AS48</f>
         <v>-293</v>
       </c>
     </row>
-    <row r="80" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="AS80" s="3">
-        <f>AS78+AS79</f>
+    <row r="86" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="AS86" s="3">
+        <f>AS84+AS85</f>
         <v>25814.609767880786</v>
       </c>
     </row>
-    <row r="81" spans="45:45" x14ac:dyDescent="0.3">
-      <c r="AS81" s="12">
-        <f>AS80/AO38</f>
+    <row r="87" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="AS87" s="12">
+        <f>AS86/AO38</f>
         <v>588.83690163961637</v>
       </c>
     </row>
-    <row r="82" spans="45:45" x14ac:dyDescent="0.3">
-      <c r="AS82" s="12">
+    <row r="88" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="AS88" s="12">
         <f>Main!D3</f>
         <v>1744.5</v>
       </c>
     </row>
-    <row r="83" spans="45:45" x14ac:dyDescent="0.3">
-      <c r="AS83" s="7">
-        <f>AS81/AS82-1</f>
+    <row r="89" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="AS89" s="7">
+        <f>AS87/AS88-1</f>
         <v>-0.66246093342527002</v>
       </c>
     </row>

--- a/Financial Analysis/RHM.xlsx
+++ b/Financial Analysis/RHM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803FFD32-5992-44B5-B86E-605A0C6700D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8073CBF-0EE6-4DD6-BB1F-B990CB029970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
   </bookViews>
@@ -927,14 +927,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>1744.5</v>
+        <v>1764</v>
       </c>
       <c r="E3" s="11">
-        <v>45906</v>
+        <v>45955</v>
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45934</v>
+        <v>45955</v>
       </c>
       <c r="G3" s="11">
         <v>45967</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>76478.880000000005</v>
+        <v>77333.760000000009</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -999,7 +999,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>76771.88</v>
+        <v>77626.760000000009</v>
       </c>
     </row>
   </sheetData>
@@ -1565,7 +1565,9 @@
       <c r="AD8" s="3">
         <v>7712</v>
       </c>
-      <c r="AE8" s="3"/>
+      <c r="AE8" s="3">
+        <v>7192</v>
+      </c>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
@@ -1634,7 +1636,9 @@
       <c r="AD9" s="3">
         <v>16533</v>
       </c>
-      <c r="AE9" s="3"/>
+      <c r="AE9" s="3">
+        <v>23707</v>
+      </c>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1703,7 +1707,9 @@
       <c r="AD10" s="3">
         <v>30728</v>
       </c>
-      <c r="AE10" s="3"/>
+      <c r="AE10" s="3">
+        <v>32266</v>
+      </c>
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
@@ -1784,7 +1790,10 @@
         <f>SUM(AD8:AD10)</f>
         <v>54973</v>
       </c>
-      <c r="AE11" s="6"/>
+      <c r="AE11" s="14">
+        <f t="shared" ref="AE11" si="3">SUM(AE8:AE10)</f>
+        <v>63165</v>
+      </c>
       <c r="AF11" s="6"/>
       <c r="AG11" s="6"/>
       <c r="AH11" s="6"/>
@@ -1894,7 +1903,7 @@
         <v>1480.8</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" ref="V13" si="3">R13*1.35</f>
+        <f t="shared" ref="V13" si="4">R13*1.35</f>
         <v>1675.3500000000001</v>
       </c>
       <c r="Z13" s="3">
@@ -1933,27 +1942,27 @@
         <v>7169.3102640600018</v>
       </c>
       <c r="AJ13" s="3">
-        <f t="shared" ref="AJ13:AO13" si="4">AI13*1.02</f>
+        <f t="shared" ref="AJ13:AO13" si="5">AI13*1.02</f>
         <v>7312.6964693412019</v>
       </c>
       <c r="AK13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7458.9503987280259</v>
       </c>
       <c r="AL13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7608.1294067025865</v>
       </c>
       <c r="AM13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7760.291994836638</v>
       </c>
       <c r="AN13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7915.4978347333708</v>
       </c>
       <c r="AO13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8073.8077914280384</v>
       </c>
     </row>
@@ -2060,23 +2069,23 @@
         <v>4883.8653863999998</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" ref="AK14:AO14" si="5">AJ14*1.02</f>
+        <f t="shared" ref="AK14:AO14" si="6">AJ14*1.02</f>
         <v>4981.5426941280002</v>
       </c>
       <c r="AL14" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5081.1735480105599</v>
       </c>
       <c r="AM14" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5182.7970189707712</v>
       </c>
       <c r="AN14" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5286.4529593501866</v>
       </c>
       <c r="AO14" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5392.1820185371907</v>
       </c>
     </row>
@@ -2187,19 +2196,19 @@
         <v>3143.5298932433761</v>
       </c>
       <c r="AL15" s="3">
-        <f t="shared" ref="AL15:AO15" si="6">AK15*1.03</f>
+        <f t="shared" ref="AL15:AO15" si="7">AK15*1.03</f>
         <v>3237.8357900406777</v>
       </c>
       <c r="AM15" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3334.970863741898</v>
       </c>
       <c r="AN15" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3435.0199896541549</v>
       </c>
       <c r="AO15" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3538.0705893437798</v>
       </c>
     </row>
@@ -2296,43 +2305,43 @@
         <v>1928.8999999999999</v>
       </c>
       <c r="AF16" s="3">
-        <f t="shared" ref="AF16:AO16" si="7">AE16*1.01</f>
+        <f t="shared" ref="AF16:AO16" si="8">AE16*1.01</f>
         <v>1948.1889999999999</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1967.6708899999999</v>
       </c>
       <c r="AH16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1987.3475988999999</v>
       </c>
       <c r="AI16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2007.221074889</v>
       </c>
       <c r="AJ16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2027.29328563789</v>
       </c>
       <c r="AK16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2047.5662184942689</v>
       </c>
       <c r="AL16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2068.0418806792118</v>
       </c>
       <c r="AM16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2088.722299486004</v>
       </c>
       <c r="AN16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2109.6095224808641</v>
       </c>
       <c r="AO16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2130.7056177056729</v>
       </c>
     </row>
@@ -2392,7 +2401,7 @@
         <v>-43</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="8">Q17*1.35</f>
+        <f t="shared" ref="U17" si="9">Q17*1.35</f>
         <v>5.4</v>
       </c>
       <c r="V17" s="9">
@@ -2423,7 +2432,7 @@
         <v>102.76</v>
       </c>
       <c r="AG17" s="3">
-        <f t="shared" ref="AG17" si="9">AF17*1.3</f>
+        <f t="shared" ref="AG17" si="10">AF17*1.3</f>
         <v>133.58800000000002</v>
       </c>
       <c r="AH17" s="3">
@@ -2439,23 +2448,23 @@
         <v>185.15296800000004</v>
       </c>
       <c r="AK17" s="3">
-        <f t="shared" ref="AK17:AO17" si="10">AJ17*1.05</f>
+        <f t="shared" ref="AK17:AO17" si="11">AJ17*1.05</f>
         <v>194.41061640000007</v>
       </c>
       <c r="AL17" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>204.13114722000009</v>
       </c>
       <c r="AM17" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>214.33770458100011</v>
       </c>
       <c r="AN17" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>225.05458981005012</v>
       </c>
       <c r="AO17" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>236.30731930055262</v>
       </c>
     </row>
@@ -2512,86 +2521,86 @@
         <v>2453</v>
       </c>
       <c r="R18" s="6">
-        <f t="shared" ref="R18:V18" si="11">SUM(R13:R17)</f>
+        <f t="shared" ref="R18:V18" si="12">SUM(R13:R17)</f>
         <v>3481</v>
       </c>
       <c r="S18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2305</v>
       </c>
       <c r="T18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2431</v>
       </c>
       <c r="U18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3148.2000000000003</v>
       </c>
       <c r="V18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4347.74</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" ref="Z18:AE18" si="12">SUM(Z13:Z17)</f>
+        <f t="shared" ref="Z18:AE18" si="13">SUM(Z13:Z17)</f>
         <v>5405</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5659</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6410</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7175</v>
       </c>
       <c r="AD18" s="6">
         <v>9751</v>
       </c>
       <c r="AE18" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12231.94</v>
       </c>
       <c r="AF18" s="6">
-        <f t="shared" ref="AF18:AO18" si="13">SUM(AF13:AF17)</f>
+        <f t="shared" ref="AF18:AO18" si="14">SUM(AF13:AF17)</f>
         <v>14464.0298</v>
       </c>
       <c r="AG18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15745.401599999999</v>
       </c>
       <c r="AH18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>16551.637628500001</v>
       </c>
       <c r="AI18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>17075.558097929003</v>
       </c>
       <c r="AJ18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>17460.97887951829</v>
       </c>
       <c r="AK18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>17825.999820993671</v>
       </c>
       <c r="AL18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>18199.311772653036</v>
       </c>
       <c r="AM18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>18581.119881616312</v>
       </c>
       <c r="AN18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>18971.634896028627</v>
       </c>
       <c r="AO18" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>19371.073336315232</v>
       </c>
     </row>
@@ -2673,43 +2682,43 @@
       </c>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3">
-        <f t="shared" ref="AF19:AO19" si="14">AE19*0.97</f>
+        <f t="shared" ref="AF19:AO19" si="15">AE19*0.97</f>
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AI19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AJ19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AK19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AL19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AM19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AN19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AO19" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -2791,39 +2800,39 @@
         <v>7232.0149000000001</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" ref="AG20:AO20" si="15">AG18*0.5</f>
+        <f t="shared" ref="AG20:AO20" si="16">AG18*0.5</f>
         <v>7872.7007999999996</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8275.8188142500003</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8537.7790489645013</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8730.4894397591452</v>
       </c>
       <c r="AK20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8912.9999104968356</v>
       </c>
       <c r="AL20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9099.6558863265182</v>
       </c>
       <c r="AM20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9290.5599408081562</v>
       </c>
       <c r="AN20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9485.8174480143134</v>
       </c>
       <c r="AO20" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9685.5366681576161</v>
       </c>
     </row>
@@ -2904,39 +2913,39 @@
         <v>3616.0074500000001</v>
       </c>
       <c r="AG21" s="3">
-        <f t="shared" ref="AG21:AO21" si="16">AG18*0.25</f>
+        <f t="shared" ref="AG21:AO21" si="17">AG18*0.25</f>
         <v>3936.3503999999998</v>
       </c>
       <c r="AH21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4137.9094071250001</v>
       </c>
       <c r="AI21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4268.8895244822506</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4365.2447198795726</v>
       </c>
       <c r="AK21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4456.4999552484178</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4549.8279431632591</v>
       </c>
       <c r="AM21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4645.2799704040781</v>
       </c>
       <c r="AN21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4742.9087240071567</v>
       </c>
       <c r="AO21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4842.768334078808</v>
       </c>
     </row>
@@ -2953,67 +2962,67 @@
         <v>1029</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" ref="G22:P22" si="17">SUM(G19:G21)</f>
+        <f t="shared" ref="G22:P22" si="18">SUM(G19:G21)</f>
         <v>999</v>
       </c>
       <c r="H22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1092</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1099</v>
       </c>
       <c r="J22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1676</v>
       </c>
       <c r="K22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1061</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1155</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1329</v>
       </c>
       <c r="N22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1741</v>
       </c>
       <c r="O22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1188</v>
       </c>
       <c r="P22" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1664</v>
       </c>
       <c r="Q22" s="6">
-        <f t="shared" ref="Q22:R22" si="18">SUM(Q19:Q21)</f>
+        <f t="shared" ref="Q22:R22" si="19">SUM(Q19:Q21)</f>
         <v>1872</v>
       </c>
       <c r="R22" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2341</v>
       </c>
       <c r="S22" s="6">
-        <f t="shared" ref="S22:T22" si="19">SUM(S19:S21)</f>
+        <f t="shared" ref="S22:T22" si="20">SUM(S19:S21)</f>
         <v>1763</v>
       </c>
       <c r="T22" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1836</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" ref="U22:V22" si="20">U18-U23</f>
+        <f t="shared" ref="U22:V22" si="21">U18-U23</f>
         <v>2329.6680000000001</v>
       </c>
       <c r="V22" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2869.5083999999997</v>
       </c>
       <c r="Z22" s="6">
@@ -3041,43 +3050,43 @@
         <v>8798.1764000000003</v>
       </c>
       <c r="AF22" s="6">
-        <f t="shared" ref="AF22:AO22" si="21">SUM(AF19:AF21)</f>
+        <f t="shared" ref="AF22:AO22" si="22">SUM(AF19:AF21)</f>
         <v>10848.022349999999</v>
       </c>
       <c r="AG22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>11809.0512</v>
       </c>
       <c r="AH22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12413.728221375</v>
       </c>
       <c r="AI22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12806.668573446752</v>
       </c>
       <c r="AJ22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13095.734159638718</v>
       </c>
       <c r="AK22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13369.499865745252</v>
       </c>
       <c r="AL22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13649.483829489778</v>
       </c>
       <c r="AM22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13935.839911212235</v>
       </c>
       <c r="AN22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14228.72617202147</v>
       </c>
       <c r="AO22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>14528.305002236424</v>
       </c>
     </row>
@@ -3094,59 +3103,59 @@
         <v>287</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" ref="G23:P23" si="22">G18-G22</f>
+        <f t="shared" ref="G23:P23" si="23">G18-G22</f>
         <v>267</v>
       </c>
       <c r="H23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>316</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>316</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>645</v>
       </c>
       <c r="K23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>302</v>
       </c>
       <c r="L23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>342</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>429</v>
       </c>
       <c r="N23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>816</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>394</v>
       </c>
       <c r="P23" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>571</v>
       </c>
       <c r="Q23" s="6">
-        <f t="shared" ref="Q23:R23" si="23">Q18-Q22</f>
+        <f t="shared" ref="Q23:R23" si="24">Q18-Q22</f>
         <v>581</v>
       </c>
       <c r="R23" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1140</v>
       </c>
       <c r="S23" s="6">
-        <f t="shared" ref="S23:T23" si="24">S18-S22</f>
+        <f t="shared" ref="S23:T23" si="25">S18-S22</f>
         <v>542</v>
       </c>
       <c r="T23" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>595</v>
       </c>
       <c r="U23" s="6">
@@ -3178,47 +3187,47 @@
         <v>2686</v>
       </c>
       <c r="AE23" s="6">
-        <f t="shared" ref="AE23:AO23" si="25">AE18-AE22</f>
+        <f t="shared" ref="AE23:AO23" si="26">AE18-AE22</f>
         <v>3433.7636000000002</v>
       </c>
       <c r="AF23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3616.007450000001</v>
       </c>
       <c r="AG23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3936.3503999999994</v>
       </c>
       <c r="AH23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4137.9094071250001</v>
       </c>
       <c r="AI23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4268.8895244822506</v>
       </c>
       <c r="AJ23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4365.2447198795726</v>
       </c>
       <c r="AK23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4456.4999552484187</v>
       </c>
       <c r="AL23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4549.8279431632582</v>
       </c>
       <c r="AM23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4645.2799704040772</v>
       </c>
       <c r="AN23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4742.9087240071567</v>
       </c>
       <c r="AO23" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4842.768334078808</v>
       </c>
     </row>
@@ -3366,11 +3375,11 @@
         <v>-51</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" ref="U25:V25" si="26">Q25*1.3</f>
+        <f t="shared" ref="U25:V25" si="27">Q25*1.3</f>
         <v>-66.3</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-124.80000000000001</v>
       </c>
       <c r="Z25" s="3">
@@ -3503,67 +3512,67 @@
         <v>182</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" ref="G27:P27" si="27">SUM(G24:G26)</f>
+        <f t="shared" ref="G27:P27" si="28">SUM(G24:G26)</f>
         <v>184</v>
       </c>
       <c r="H27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>189</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>204</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>219</v>
       </c>
       <c r="K27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>213</v>
       </c>
       <c r="L27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>224</v>
       </c>
       <c r="M27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>257</v>
       </c>
       <c r="N27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>350</v>
       </c>
       <c r="O27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>277</v>
       </c>
       <c r="P27" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>329</v>
       </c>
       <c r="Q27" s="3">
-        <f t="shared" ref="Q27:R27" si="28">SUM(Q24:Q26)</f>
+        <f t="shared" ref="Q27:R27" si="29">SUM(Q24:Q26)</f>
         <v>291</v>
       </c>
       <c r="R27" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>398</v>
       </c>
       <c r="S27" s="3">
-        <f t="shared" ref="S27:V27" si="29">SUM(S24:S26)</f>
+        <f t="shared" ref="S27:V27" si="30">SUM(S24:S26)</f>
         <v>363</v>
       </c>
       <c r="T27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>363</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>312.74999999999994</v>
       </c>
       <c r="V27" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>410</v>
       </c>
       <c r="Z27" s="3">
@@ -3607,27 +3616,27 @@
         <v>1662.0859710000002</v>
       </c>
       <c r="AJ27" s="3">
-        <f t="shared" ref="AJ27:AO27" si="30">AI27*1.02</f>
+        <f t="shared" ref="AJ27:AO27" si="31">AI27*1.02</f>
         <v>1695.3276904200002</v>
       </c>
       <c r="AK27" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1729.2342442284003</v>
       </c>
       <c r="AL27" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1763.8189291129684</v>
       </c>
       <c r="AM27" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1799.0953076952278</v>
       </c>
       <c r="AN27" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1835.0772138491325</v>
       </c>
       <c r="AO27" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1871.7787581261152</v>
       </c>
     </row>
@@ -3644,67 +3653,67 @@
         <v>105</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" ref="G28:P28" si="31">G23-G27</f>
+        <f t="shared" ref="G28:P28" si="32">G23-G27</f>
         <v>83</v>
       </c>
       <c r="H28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>127</v>
       </c>
       <c r="I28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>112</v>
       </c>
       <c r="J28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>426</v>
       </c>
       <c r="K28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>89</v>
       </c>
       <c r="L28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>118</v>
       </c>
       <c r="M28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>172</v>
       </c>
       <c r="N28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>466</v>
       </c>
       <c r="O28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>117</v>
       </c>
       <c r="P28" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>242</v>
       </c>
       <c r="Q28" s="6">
-        <f t="shared" ref="Q28:R28" si="32">Q23-Q27</f>
+        <f t="shared" ref="Q28:R28" si="33">Q23-Q27</f>
         <v>290</v>
       </c>
       <c r="R28" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>742</v>
       </c>
       <c r="S28" s="6">
-        <f t="shared" ref="S28:V28" si="33">S23-S27</f>
+        <f t="shared" ref="S28:V28" si="34">S23-S27</f>
         <v>179</v>
       </c>
       <c r="T28" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>232</v>
       </c>
       <c r="U28" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>505.78200000000021</v>
       </c>
       <c r="V28" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1068.2316000000001</v>
       </c>
       <c r="Z28" s="6">
@@ -3724,51 +3733,51 @@
         <v>845</v>
       </c>
       <c r="AD28" s="6">
-        <f t="shared" ref="AD28:AO28" si="34">AD23-AD27</f>
+        <f t="shared" ref="AD28:AO28" si="35">AD23-AD27</f>
         <v>1391</v>
       </c>
       <c r="AE28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1985.0136000000002</v>
       </c>
       <c r="AF28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2094.819950000001</v>
       </c>
       <c r="AG28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2354.3153999999995</v>
       </c>
       <c r="AH28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2508.4133571249999</v>
       </c>
       <c r="AI28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2606.8035534822502</v>
       </c>
       <c r="AJ28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2669.9170294595724</v>
       </c>
       <c r="AK28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2727.2657110200184</v>
       </c>
       <c r="AL28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2786.0090140502898</v>
       </c>
       <c r="AM28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2846.1846627088494</v>
       </c>
       <c r="AN28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2907.8315101580242</v>
       </c>
       <c r="AO28" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2970.9895759526926</v>
       </c>
     </row>
@@ -4121,67 +4130,67 @@
         <v>2</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" ref="G33:P33" si="35">SUM(G29:G32)</f>
+        <f t="shared" ref="G33:P33" si="36">SUM(G29:G32)</f>
         <v>10</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>29</v>
       </c>
       <c r="I33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-11</v>
       </c>
       <c r="K33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>20</v>
       </c>
       <c r="L33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="M33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>27</v>
       </c>
       <c r="N33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-30</v>
       </c>
       <c r="O33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>31</v>
       </c>
       <c r="P33" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>34</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" ref="Q33:T33" si="36">SUM(Q29:Q32)</f>
+        <f t="shared" ref="Q33:T33" si="37">SUM(Q29:Q32)</f>
         <v>43</v>
       </c>
       <c r="R33" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>55</v>
       </c>
       <c r="S33" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>33</v>
       </c>
       <c r="T33" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9</v>
       </c>
       <c r="U33" s="3">
-        <f t="shared" ref="U33:V33" si="37">Q33*1.05</f>
+        <f t="shared" ref="U33:V33" si="38">Q33*1.05</f>
         <v>45.15</v>
       </c>
       <c r="V33" s="3">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>57.75</v>
       </c>
       <c r="Z33" s="3">
@@ -4201,7 +4210,7 @@
         <v>31</v>
       </c>
       <c r="AD33" s="3">
-        <f t="shared" ref="AD33" si="38">SUM(AD29:AD32)</f>
+        <f t="shared" ref="AD33" si="39">SUM(AD29:AD32)</f>
         <v>163</v>
       </c>
       <c r="AE33" s="3">
@@ -4213,39 +4222,39 @@
         <v>149.24700000000001</v>
       </c>
       <c r="AG33" s="3">
-        <f t="shared" ref="AG33:AO33" si="39">AF33*1.03</f>
+        <f t="shared" ref="AG33:AO33" si="40">AF33*1.03</f>
         <v>153.72441000000001</v>
       </c>
       <c r="AH33" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>158.33614230000001</v>
       </c>
       <c r="AI33" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>163.08622656900002</v>
       </c>
       <c r="AJ33" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>167.97881336607003</v>
       </c>
       <c r="AK33" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>173.01817776705212</v>
       </c>
       <c r="AL33" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>178.20872310006368</v>
       </c>
       <c r="AM33" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>183.55498479306559</v>
       </c>
       <c r="AN33" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>189.06163433685757</v>
       </c>
       <c r="AO33" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>194.7334833669633</v>
       </c>
     </row>
@@ -4262,67 +4271,67 @@
         <v>103</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" ref="G34:P34" si="40">G28-G33</f>
+        <f t="shared" ref="G34:P34" si="41">G28-G33</f>
         <v>73</v>
       </c>
       <c r="H34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>98</v>
       </c>
       <c r="I34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>111</v>
       </c>
       <c r="J34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>437</v>
       </c>
       <c r="K34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>69</v>
       </c>
       <c r="L34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>104</v>
       </c>
       <c r="M34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>145</v>
       </c>
       <c r="N34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>496</v>
       </c>
       <c r="O34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>86</v>
       </c>
       <c r="P34" s="6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>208</v>
       </c>
       <c r="Q34" s="6">
-        <f t="shared" ref="Q34:V34" si="41">Q28-Q33</f>
+        <f t="shared" ref="Q34:V34" si="42">Q28-Q33</f>
         <v>247</v>
       </c>
       <c r="R34" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>687</v>
       </c>
       <c r="S34" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>146</v>
       </c>
       <c r="T34" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>223</v>
       </c>
       <c r="U34" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>460.63200000000023</v>
       </c>
       <c r="V34" s="6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1010.4816000000001</v>
       </c>
       <c r="Z34" s="6">
@@ -4342,51 +4351,51 @@
         <v>814</v>
       </c>
       <c r="AD34" s="6">
-        <f t="shared" ref="AD34:AO34" si="42">AD28-AD33</f>
+        <f t="shared" ref="AD34:AO34" si="43">AD28-AD33</f>
         <v>1228</v>
       </c>
       <c r="AE34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1840.1136000000001</v>
       </c>
       <c r="AF34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1945.5729500000009</v>
       </c>
       <c r="AG34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2200.5909899999997</v>
       </c>
       <c r="AH34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2350.0772148249998</v>
       </c>
       <c r="AI34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2443.71732691325</v>
       </c>
       <c r="AJ34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2501.9382160935024</v>
       </c>
       <c r="AK34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2554.2475332529662</v>
       </c>
       <c r="AL34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2607.8002909502261</v>
       </c>
       <c r="AM34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2662.6296779157838</v>
       </c>
       <c r="AN34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2718.7698758211668</v>
       </c>
       <c r="AO34" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2776.2560925857292</v>
       </c>
     </row>
@@ -4446,11 +4455,11 @@
         <v>53</v>
       </c>
       <c r="U35" s="3">
-        <f t="shared" ref="U35:V35" si="43">U34*0.27</f>
+        <f t="shared" ref="U35:V35" si="44">U34*0.27</f>
         <v>124.37064000000007</v>
       </c>
       <c r="V35" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>272.83003200000002</v>
       </c>
       <c r="Z35" s="3">
@@ -4477,39 +4486,39 @@
         <v>486.39323750000023</v>
       </c>
       <c r="AG35" s="3">
-        <f t="shared" ref="AG35:AO35" si="44">AG34*0.25</f>
+        <f t="shared" ref="AG35:AO35" si="45">AG34*0.25</f>
         <v>550.14774749999992</v>
       </c>
       <c r="AH35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>587.51930370624996</v>
       </c>
       <c r="AI35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>610.92933172831249</v>
       </c>
       <c r="AJ35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>625.48455402337561</v>
       </c>
       <c r="AK35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>638.56188331324154</v>
       </c>
       <c r="AL35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>651.95007273755652</v>
       </c>
       <c r="AM35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>665.65741947894594</v>
       </c>
       <c r="AN35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>679.6924689552917</v>
       </c>
       <c r="AO35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>694.06402314643231</v>
       </c>
     </row>
@@ -4579,11 +4588,11 @@
         <v>27</v>
       </c>
       <c r="U36" s="3">
-        <f t="shared" ref="U36:V36" si="45">U34*0.1</f>
+        <f t="shared" ref="U36:V36" si="46">U34*0.1</f>
         <v>46.063200000000023</v>
       </c>
       <c r="V36" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>101.04816000000001</v>
       </c>
       <c r="Z36" s="3">
@@ -4611,43 +4620,43 @@
         <v>198.11136000000005</v>
       </c>
       <c r="AF36" s="3">
-        <f t="shared" ref="AF36:AO36" si="46">AF34*0.1</f>
+        <f t="shared" ref="AF36:AO36" si="47">AF34*0.1</f>
         <v>194.5572950000001</v>
       </c>
       <c r="AG36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>220.05909899999997</v>
       </c>
       <c r="AH36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>235.00772148249999</v>
       </c>
       <c r="AI36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>244.37173269132501</v>
       </c>
       <c r="AJ36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>250.19382160935027</v>
       </c>
       <c r="AK36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>255.42475332529662</v>
       </c>
       <c r="AL36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>260.7800290950226</v>
       </c>
       <c r="AM36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>266.26296779157838</v>
       </c>
       <c r="AN36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>271.87698758211667</v>
       </c>
       <c r="AO36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>277.62560925857292</v>
       </c>
     </row>
@@ -4664,67 +4673,67 @@
         <v>-37</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" ref="G37:P37" si="47">G34-G35-G36</f>
+        <f t="shared" ref="G37:P37" si="48">G34-G35-G36</f>
         <v>46</v>
       </c>
       <c r="H37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>57</v>
       </c>
       <c r="I37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>76</v>
       </c>
       <c r="J37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>297</v>
       </c>
       <c r="K37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>48</v>
       </c>
       <c r="L37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>57</v>
       </c>
       <c r="M37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>102</v>
       </c>
       <c r="N37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>327</v>
       </c>
       <c r="O37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>50</v>
       </c>
       <c r="P37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>63</v>
       </c>
       <c r="Q37" s="6">
-        <f t="shared" ref="Q37:R37" si="48">Q34-Q35-Q36</f>
+        <f t="shared" ref="Q37:R37" si="49">Q34-Q35-Q36</f>
         <v>135</v>
       </c>
       <c r="R37" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>469</v>
       </c>
       <c r="S37" s="6">
-        <f t="shared" ref="S37:V37" si="49">S34-S35-S36</f>
+        <f t="shared" ref="S37:V37" si="50">S34-S35-S36</f>
         <v>83</v>
       </c>
       <c r="T37" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>143</v>
       </c>
       <c r="U37" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>290.19816000000014</v>
       </c>
       <c r="V37" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>636.60340799999994</v>
       </c>
       <c r="Z37" s="6">
@@ -4744,51 +4753,51 @@
         <v>534</v>
       </c>
       <c r="AD37" s="6">
-        <f t="shared" ref="AD37:AO37" si="50">AD34-AD35-AD36</f>
+        <f t="shared" ref="AD37:AO37" si="51">AD34-AD35-AD36</f>
         <v>717</v>
       </c>
       <c r="AE37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1152.8015680000001</v>
       </c>
       <c r="AF37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1264.6224175000007</v>
       </c>
       <c r="AG37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1430.3841434999997</v>
       </c>
       <c r="AH37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1527.5501896362498</v>
       </c>
       <c r="AI37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1588.4162624936125</v>
       </c>
       <c r="AJ37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1626.2598404607766</v>
       </c>
       <c r="AK37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1660.2608966144278</v>
       </c>
       <c r="AL37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1695.0701891176468</v>
       </c>
       <c r="AM37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1730.7092906452594</v>
       </c>
       <c r="AN37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1767.2004192837585</v>
       </c>
       <c r="AO37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1804.5664601807241</v>
       </c>
       <c r="AP37" s="1">
@@ -4796,443 +4805,443 @@
         <v>1786.5207955789169</v>
       </c>
       <c r="AQ37" s="1">
-        <f t="shared" ref="AQ37:DB37" si="51">AP37*(1+$AS$45)</f>
+        <f t="shared" ref="AQ37:DB37" si="52">AP37*(1+$AS$45)</f>
         <v>1768.6555876231278</v>
       </c>
       <c r="AR37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1750.9690317468965</v>
       </c>
       <c r="AS37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1733.4593414294275</v>
       </c>
       <c r="AT37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1716.1247480151333</v>
       </c>
       <c r="AU37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1698.9635005349819</v>
       </c>
       <c r="AV37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1681.9738655296321</v>
       </c>
       <c r="AW37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1665.1541268743358</v>
       </c>
       <c r="AX37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1648.5025856055925</v>
       </c>
       <c r="AY37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1632.0175597495365</v>
       </c>
       <c r="AZ37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1615.6973841520412</v>
       </c>
       <c r="BA37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1599.5404103105207</v>
       </c>
       <c r="BB37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1583.5450062074153</v>
       </c>
       <c r="BC37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1567.7095561453411</v>
       </c>
       <c r="BD37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1552.0324605838878</v>
       </c>
       <c r="BE37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1536.5121359780489</v>
       </c>
       <c r="BF37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1521.1470146182685</v>
       </c>
       <c r="BG37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1505.9355444720859</v>
       </c>
       <c r="BH37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1490.8761890273649</v>
       </c>
       <c r="BI37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1475.9674271370914</v>
       </c>
       <c r="BJ37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1461.2077528657205</v>
       </c>
       <c r="BK37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1446.5956753370633</v>
       </c>
       <c r="BL37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1432.1297185836927</v>
       </c>
       <c r="BM37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1417.8084213978557</v>
       </c>
       <c r="BN37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1403.6303371838771</v>
       </c>
       <c r="BO37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1389.5940338120383</v>
       </c>
       <c r="BP37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1375.6980934739179</v>
       </c>
       <c r="BQ37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1361.9411125391787</v>
       </c>
       <c r="BR37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1348.321701413787</v>
       </c>
       <c r="BS37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1334.8384843996491</v>
       </c>
       <c r="BT37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1321.4900995556527</v>
       </c>
       <c r="BU37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1308.2751985600962</v>
       </c>
       <c r="BV37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1295.1924465744953</v>
       </c>
       <c r="BW37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1282.2405221087504</v>
       </c>
       <c r="BX37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1269.4181168876628</v>
       </c>
       <c r="BY37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1256.7239357187862</v>
       </c>
       <c r="BZ37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1244.1566963615983</v>
       </c>
       <c r="CA37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1231.7151293979823</v>
       </c>
       <c r="CB37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1219.3979781040025</v>
       </c>
       <c r="CC37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1207.2039983229624</v>
       </c>
       <c r="CD37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1195.1319583397328</v>
       </c>
       <c r="CE37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1183.1806387563354</v>
       </c>
       <c r="CF37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1171.348832368772</v>
       </c>
       <c r="CG37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1159.6353440450844</v>
       </c>
       <c r="CH37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1148.0389906046335</v>
       </c>
       <c r="CI37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1136.558600698587</v>
       </c>
       <c r="CJ37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1125.1930146916011</v>
       </c>
       <c r="CK37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1113.9410845446851</v>
       </c>
       <c r="CL37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1102.8016736992381</v>
       </c>
       <c r="CM37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1091.7736569622457</v>
       </c>
       <c r="CN37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1080.8559203926231</v>
       </c>
       <c r="CO37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1070.0473611886969</v>
       </c>
       <c r="CP37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1059.3468875768099</v>
       </c>
       <c r="CQ37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1048.7534187010417</v>
       </c>
       <c r="CR37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1038.2658845140313</v>
       </c>
       <c r="CS37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1027.8832256688911</v>
       </c>
       <c r="CT37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1017.6043934122022</v>
       </c>
       <c r="CU37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1007.4283494780801</v>
       </c>
       <c r="CV37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>997.35406598329928</v>
       </c>
       <c r="CW37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>987.38052532346626</v>
       </c>
       <c r="CX37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>977.50672007023161</v>
       </c>
       <c r="CY37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>967.73165286952928</v>
       </c>
       <c r="CZ37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>958.05433634083397</v>
       </c>
       <c r="DA37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>948.47379297742566</v>
       </c>
       <c r="DB37" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>938.98905504765139</v>
       </c>
       <c r="DC37" s="1">
-        <f t="shared" ref="DC37:EV37" si="52">DB37*(1+$AS$45)</f>
+        <f t="shared" ref="DC37:EV37" si="53">DB37*(1+$AS$45)</f>
         <v>929.59916449717491</v>
       </c>
       <c r="DD37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>920.30317285220315</v>
       </c>
       <c r="DE37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>911.10014112368106</v>
       </c>
       <c r="DF37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>901.98913971244428</v>
       </c>
       <c r="DG37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>892.96924831531987</v>
       </c>
       <c r="DH37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>884.03955583216668</v>
       </c>
       <c r="DI37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>875.199160273845</v>
       </c>
       <c r="DJ37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>866.44716867110651</v>
       </c>
       <c r="DK37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>857.78269698439544</v>
       </c>
       <c r="DL37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>849.20487001455149</v>
       </c>
       <c r="DM37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>840.71282131440591</v>
       </c>
       <c r="DN37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>832.3056931012618</v>
       </c>
       <c r="DO37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>823.98263617024918</v>
       </c>
       <c r="DP37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>815.74280980854667</v>
       </c>
       <c r="DQ37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>807.58538171046121</v>
       </c>
       <c r="DR37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>799.50952789335656</v>
       </c>
       <c r="DS37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>791.51443261442296</v>
       </c>
       <c r="DT37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>783.59928828827867</v>
       </c>
       <c r="DU37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>775.76329540539587</v>
       </c>
       <c r="DV37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>768.00566245134189</v>
       </c>
       <c r="DW37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>760.32560582682845</v>
       </c>
       <c r="DX37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>752.72234976856021</v>
       </c>
       <c r="DY37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>745.19512627087465</v>
       </c>
       <c r="DZ37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>737.74317500816585</v>
       </c>
       <c r="EA37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>730.36574325808419</v>
       </c>
       <c r="EB37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>723.06208582550335</v>
       </c>
       <c r="EC37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>715.83146496724828</v>
       </c>
       <c r="ED37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>708.67315031757585</v>
       </c>
       <c r="EE37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>701.58641881440008</v>
       </c>
       <c r="EF37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>694.57055462625613</v>
       </c>
       <c r="EG37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>687.62484907999351</v>
       </c>
       <c r="EH37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>680.74860058919353</v>
       </c>
       <c r="EI37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>673.94111458330156</v>
       </c>
       <c r="EJ37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>667.2017034374685</v>
       </c>
       <c r="EK37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>660.52968640309382</v>
       </c>
       <c r="EL37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>653.92438953906287</v>
       </c>
       <c r="EM37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>647.38514564367222</v>
       </c>
       <c r="EN37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>640.91129418723551</v>
       </c>
       <c r="EO37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>634.5021812453632</v>
       </c>
       <c r="EP37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>628.15715943290957</v>
       </c>
       <c r="EQ37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>621.87558783858049</v>
       </c>
       <c r="ER37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>615.65683196019472</v>
       </c>
       <c r="ES37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>609.50026364059272</v>
       </c>
       <c r="ET37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>603.40526100418674</v>
       </c>
       <c r="EU37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>597.3712083941449</v>
       </c>
       <c r="EV37" s="1">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>591.39749631020345</v>
       </c>
     </row>
@@ -5356,67 +5365,67 @@
         <v>-0.85194565968224734</v>
       </c>
       <c r="G39" s="5">
-        <f t="shared" ref="G39:P39" si="53">G37/G38</f>
+        <f t="shared" ref="G39:P39" si="54">G37/G38</f>
         <v>1.0591756850103615</v>
       </c>
       <c r="H39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.3124568270780566</v>
       </c>
       <c r="I39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.7499424361040756</v>
       </c>
       <c r="J39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>6.8385908358277687</v>
       </c>
       <c r="K39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.1052268017499425</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.3124568270780566</v>
       </c>
       <c r="M39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>2.3486069537186278</v>
       </c>
       <c r="N39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>7.529357586921483</v>
       </c>
       <c r="O39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.1512779184895234</v>
       </c>
       <c r="P39" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.4506101772967994</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" ref="Q39:R39" si="54">Q37/Q38</f>
+        <f t="shared" ref="Q39:R39" si="55">Q37/Q38</f>
         <v>3.1084503799217131</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>10.79898687543173</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" ref="S39:V39" si="55">S37/S38</f>
+        <f t="shared" ref="S39:V39" si="56">S37/S38</f>
         <v>1.8932481751824817</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>3.261861313868613</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>6.6194835766423381</v>
       </c>
       <c r="V39" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>14.521063138686129</v>
       </c>
       <c r="Z39" s="5">
@@ -5436,51 +5445,51 @@
         <v>12.295648169468111</v>
       </c>
       <c r="AD39" s="5">
-        <f t="shared" ref="AD39:AO39" si="56">AD37/AD38</f>
+        <f t="shared" ref="AD39:AO39" si="57">AD37/AD38</f>
         <v>16.509325351139765</v>
       </c>
       <c r="AE39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>26.295656204379561</v>
       </c>
       <c r="AF39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>28.846314267791985</v>
       </c>
       <c r="AG39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>32.627375536040134</v>
       </c>
       <c r="AH39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>34.843754325644383</v>
       </c>
       <c r="AI39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>36.232122775857945</v>
       </c>
       <c r="AJ39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>37.095343076203839</v>
       </c>
       <c r="AK39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>37.870914612555374</v>
       </c>
       <c r="AL39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>38.664922197026613</v>
       </c>
       <c r="AM39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>39.477857907054272</v>
       </c>
       <c r="AN39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>40.310228542056535</v>
       </c>
       <c r="AO39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>41.16255611726104</v>
       </c>
     </row>
@@ -5489,27 +5498,27 @@
         <v>86</v>
       </c>
       <c r="O41" s="8">
-        <f t="shared" ref="O41:Q41" si="57">O10/K10-1</f>
+        <f t="shared" ref="O41:Q41" si="58">O10/K10-1</f>
         <v>0.5372858689422404</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.53766190449719264</v>
       </c>
       <c r="Q41" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.41511822186218428</v>
       </c>
       <c r="R41" s="8">
-        <f t="shared" ref="R41:T42" si="58">R10/N10-1</f>
+        <f t="shared" ref="R41:T42" si="59">R10/N10-1</f>
         <v>0.39818901578923427</v>
       </c>
       <c r="S41" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.34958574979287493</v>
       </c>
       <c r="T41" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.16647988142149606</v>
       </c>
       <c r="AC41" s="8">
@@ -5519,6 +5528,10 @@
       <c r="AD41" s="8">
         <f>AD10/AC10-1</f>
         <v>0.39818901578923427</v>
+      </c>
+      <c r="AE41" s="8">
+        <f>AE10/AD10-1</f>
+        <v>5.0052069773496521E-2</v>
       </c>
     </row>
     <row r="42" spans="2:152" x14ac:dyDescent="0.3">
@@ -5528,11 +5541,11 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8">
-        <f t="shared" ref="N42:O42" si="59">N11/J11-1</f>
+        <f t="shared" ref="N42:O42" si="60">N11/J11-1</f>
         <v>0.44099051633298214</v>
       </c>
       <c r="O42" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.42572887848478391</v>
       </c>
       <c r="P42" s="8">
@@ -5544,15 +5557,15 @@
         <v>0.41263879817112992</v>
       </c>
       <c r="R42" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.43570122747453643</v>
       </c>
       <c r="S42" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.55633504987934423</v>
       </c>
       <c r="T42" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.29862253289473695</v>
       </c>
       <c r="AC42" s="8">
@@ -5562,6 +5575,10 @@
       <c r="AD42" s="8">
         <f>AD11/AC11-1</f>
         <v>0.43573872391548485</v>
+      </c>
+      <c r="AE42" s="8">
+        <f>AE11/AD11-1</f>
+        <v>0.14901860913539378</v>
       </c>
     </row>
     <row r="43" spans="2:152" x14ac:dyDescent="0.3">
@@ -5578,121 +5595,121 @@
         <v>53</v>
       </c>
       <c r="G44" s="8">
-        <f t="shared" ref="G44:G49" si="60">G13/C13-1</f>
+        <f t="shared" ref="G44:G49" si="61">G13/C13-1</f>
         <v>-2.7093596059113323E-2</v>
       </c>
       <c r="H44" s="8">
-        <f t="shared" ref="H44:H49" si="61">H13/D13-1</f>
+        <f t="shared" ref="H44:H49" si="62">H13/D13-1</f>
         <v>-3.2537960954446832E-2</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8">
-        <f t="shared" ref="K44:K49" si="62">K13/G13-1</f>
+        <f t="shared" ref="K44:K49" si="63">K13/G13-1</f>
         <v>0.15696202531645564</v>
       </c>
       <c r="L44" s="8">
-        <f t="shared" ref="L44:L49" si="63">L13/H13-1</f>
+        <f t="shared" ref="L44:L49" si="64">L13/H13-1</f>
         <v>0.22197309417040367</v>
       </c>
       <c r="M44" s="8">
-        <f t="shared" ref="M44:M49" si="64">M13/I13-1</f>
+        <f t="shared" ref="M44:M49" si="65">M13/I13-1</f>
         <v>0.40128755364806867</v>
       </c>
       <c r="N44" s="8">
-        <f t="shared" ref="N44:N49" si="65">N13/J13-1</f>
+        <f t="shared" ref="N44:N49" si="66">N13/J13-1</f>
         <v>-2.3305084745762761E-2</v>
       </c>
       <c r="O44" s="8">
-        <f t="shared" ref="O44" si="66">O13/K13-1</f>
+        <f t="shared" ref="O44" si="67">O13/K13-1</f>
         <v>7.0021881838074451E-2</v>
       </c>
       <c r="P44" s="8">
-        <f t="shared" ref="P44:P45" si="67">P13/L13-1</f>
+        <f t="shared" ref="P44:P45" si="68">P13/L13-1</f>
         <v>0.47706422018348627</v>
       </c>
       <c r="Q44" s="8">
-        <f t="shared" ref="Q44:Q49" si="68">Q13/M13-1</f>
+        <f t="shared" ref="Q44:Q49" si="69">Q13/M13-1</f>
         <v>0.8897396630934149</v>
       </c>
       <c r="R44" s="8">
-        <f t="shared" ref="R44:R49" si="69">R13/N13-1</f>
+        <f t="shared" ref="R44:R49" si="70">R13/N13-1</f>
         <v>0.34598698481561829</v>
       </c>
       <c r="S44" s="8">
-        <f t="shared" ref="S44:S49" si="70">S13/O13-1</f>
+        <f t="shared" ref="S44:S49" si="71">S13/O13-1</f>
         <v>0.93251533742331283</v>
       </c>
       <c r="T44" s="8">
-        <f t="shared" ref="T44:T49" si="71">T13/P13-1</f>
+        <f t="shared" ref="T44:T49" si="72">T13/P13-1</f>
         <v>0.15527950310559002</v>
       </c>
       <c r="U44" s="8">
-        <f t="shared" ref="U44:U49" si="72">U13/Q13-1</f>
+        <f t="shared" ref="U44:U49" si="73">U13/Q13-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="V44" s="8">
-        <f t="shared" ref="V44:V49" si="73">V13/R13-1</f>
+        <f t="shared" ref="V44:V49" si="74">V13/R13-1</f>
         <v>0.35000000000000009</v>
       </c>
       <c r="AA44" s="8">
-        <f t="shared" ref="AA44:AO44" si="74">AA13/Z13-1</f>
+        <f t="shared" ref="AA44:AO44" si="75">AA13/Z13-1</f>
         <v>2.5711159737417999E-2</v>
       </c>
       <c r="AB44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.20053333333333323</v>
       </c>
       <c r="AC44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.14482452243447352</v>
       </c>
       <c r="AD44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.46255335661622032</v>
       </c>
       <c r="AE44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.33487662509949612</v>
       </c>
       <c r="AF44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AG44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO44" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5701,121 +5718,121 @@
         <v>54</v>
       </c>
       <c r="G45" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>2.857142857142847E-2</v>
       </c>
       <c r="H45" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.11255411255411252</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-0.19444444444444442</v>
       </c>
       <c r="L45" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-3.5019455252918275E-2</v>
       </c>
       <c r="M45" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.66228070175438591</v>
       </c>
       <c r="N45" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.55606407322654472</v>
       </c>
       <c r="O45" s="8">
-        <f t="shared" ref="O45" si="75">O14/K14-1</f>
+        <f t="shared" ref="O45" si="76">O14/K14-1</f>
         <v>0.84482758620689657</v>
       </c>
       <c r="P45" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>1.560483870967742</v>
       </c>
       <c r="Q45" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.17941952506596315</v>
       </c>
       <c r="R45" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.66470588235294126</v>
       </c>
       <c r="S45" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.65109034267912769</v>
       </c>
       <c r="T45" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>4.0944881889763751E-2</v>
       </c>
       <c r="U45" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.8</v>
       </c>
       <c r="V45" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA45" s="8">
-        <f t="shared" ref="AA45" si="76">AA14/Z14-1</f>
+        <f t="shared" ref="AA45" si="77">AA14/Z14-1</f>
         <v>1.878354203935606E-2</v>
       </c>
       <c r="AB45" s="8">
-        <f t="shared" ref="AB45:AC45" si="77">AB14/AA14-1</f>
+        <f t="shared" ref="AB45:AC45" si="78">AB14/AA14-1</f>
         <v>-8.779631255487752E-4</v>
       </c>
       <c r="AC45" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0.30140597539543057</v>
       </c>
       <c r="AD45" s="8">
-        <f t="shared" ref="AD45:AO45" si="78">AD14/AC14-1</f>
+        <f t="shared" ref="AD45:AO45" si="79">AD14/AC14-1</f>
         <v>0.71168129642133704</v>
       </c>
       <c r="AE45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.32307692307692304</v>
       </c>
       <c r="AF45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AG45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AR45" t="s">
@@ -5830,121 +5847,121 @@
         <v>55</v>
       </c>
       <c r="G46" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-6.3829787234042534E-2</v>
       </c>
       <c r="H46" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0.17283950617283961</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.4015151515151516</v>
       </c>
       <c r="L46" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.11052631578947358</v>
       </c>
       <c r="M46" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>9.6774193548387011E-2</v>
       </c>
       <c r="N46" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>-3.4642032332563466E-2</v>
       </c>
       <c r="O46" s="8">
-        <f t="shared" ref="O46:P46" si="79">O15/K15-1</f>
+        <f t="shared" ref="O46:P46" si="80">O15/K15-1</f>
         <v>0.22702702702702693</v>
       </c>
       <c r="P46" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.2890995260663507</v>
       </c>
       <c r="Q46" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.39215686274509798</v>
       </c>
       <c r="R46" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.27511961722488043</v>
       </c>
       <c r="S46" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.47577092511013208</v>
       </c>
       <c r="T46" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0.48161764705882359</v>
       </c>
       <c r="U46" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="V46" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.33000000000000007</v>
       </c>
       <c r="AA46" s="8">
-        <f t="shared" ref="AA46:AC46" si="80">AA15/Z15-1</f>
+        <f t="shared" ref="AA46:AC46" si="81">AA15/Z15-1</f>
         <v>-3.9948453608247392E-2</v>
       </c>
       <c r="AB46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.26308724832214758</v>
       </c>
       <c r="AC46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>8.1827842720510136E-2</v>
       </c>
       <c r="AD46" s="8">
-        <f t="shared" ref="AD46:AO46" si="81">AD15/AC15-1</f>
+        <f t="shared" ref="AD46:AO46" si="82">AD15/AC15-1</f>
         <v>0.29273084479371314</v>
       </c>
       <c r="AE46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.40158814589665637</v>
       </c>
       <c r="AF46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AG46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AH46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AI46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR46" t="s">
@@ -5959,121 +5976,121 @@
         <v>56</v>
       </c>
       <c r="G47" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1.3752455795677854E-2</v>
       </c>
       <c r="H47" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>9.0128755364806912E-2</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>4.8449612403100861E-2</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>-4.7244094488189003E-2</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-3.8022813688213253E-3</v>
       </c>
       <c r="N47" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>5.9760956175298752E-2</v>
       </c>
       <c r="O47" s="8">
-        <f t="shared" ref="O47:P47" si="82">O16/K16-1</f>
+        <f t="shared" ref="O47:P47" si="83">O16/K16-1</f>
         <v>-1.848428835489857E-3</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>5.9917355371900793E-2</v>
       </c>
       <c r="Q47" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-7.6335877862595436E-2</v>
       </c>
       <c r="R47" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-6.9548872180451138E-2</v>
       </c>
       <c r="S47" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>-6.6666666666666652E-2</v>
       </c>
       <c r="T47" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-6.4327485380117011E-2</v>
       </c>
       <c r="U47" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>-5.0000000000000044E-2</v>
       </c>
       <c r="V47" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AA47" s="8">
-        <f t="shared" ref="AA47:AC47" si="83">AA16/Z16-1</f>
+        <f t="shared" ref="AA47:AC47" si="84">AA16/Z16-1</f>
         <v>0.1166666666666667</v>
       </c>
       <c r="AB47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>9.3816631130063888E-2</v>
       </c>
       <c r="AC47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1.4132553606237774E-2</v>
       </c>
       <c r="AD47" s="8">
-        <f t="shared" ref="AD47:AO47" si="84">AD16/AC16-1</f>
+        <f t="shared" ref="AD47:AO47" si="85">AD16/AC16-1</f>
         <v>-2.3546371936568944E-2</v>
       </c>
       <c r="AE47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>-5.0738188976378051E-2</v>
       </c>
       <c r="AF47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR47" t="s">
@@ -6089,121 +6106,121 @@
         <v>57</v>
       </c>
       <c r="G48" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>2.5</v>
       </c>
       <c r="H48" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-2.75</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.28571428571428581</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>-1.2222222222222223</v>
       </c>
       <c r="N48" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="O48" s="8">
-        <f t="shared" ref="O48:P48" si="85">O17/K17-1</f>
+        <f t="shared" ref="O48:P48" si="86">O17/K17-1</f>
         <v>-0.16666666666666663</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="Q48" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>-3</v>
       </c>
       <c r="R48" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>15</v>
       </c>
       <c r="S48" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>-2.8</v>
       </c>
       <c r="T48" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>-5.3</v>
       </c>
       <c r="U48" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.35000000000000009</v>
       </c>
       <c r="V48" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.5</v>
       </c>
       <c r="AA48" s="8">
-        <f t="shared" ref="AA48:AC48" si="86">AA17/Z17-1</f>
+        <f t="shared" ref="AA48:AC48" si="87">AA17/Z17-1</f>
         <v>7</v>
       </c>
       <c r="AB48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0.16666666666666674</v>
       </c>
       <c r="AC48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-0.3571428571428571</v>
       </c>
       <c r="AD48" s="8">
-        <f t="shared" ref="AD48:AO48" si="87">AD17/AC17-1</f>
+        <f t="shared" ref="AD48:AO48" si="88">AD17/AC17-1</f>
         <v>4.5</v>
       </c>
       <c r="AE48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-0.25858585858585847</v>
       </c>
       <c r="AF48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="AG48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AH48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AI48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AR48" t="s">
@@ -6219,29 +6236,29 @@
         <v>37</v>
       </c>
       <c r="G49" s="7">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-1.577287066246047E-3</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>6.990881458966558E-2</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>7.6619273301737678E-2</v>
       </c>
       <c r="L49" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>6.3210227272727293E-2</v>
       </c>
       <c r="M49" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.24240282685512371</v>
       </c>
       <c r="N49" s="7">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.1016803102111159</v>
       </c>
       <c r="O49" s="7">
@@ -6253,27 +6270,27 @@
         <v>0.49298597194388782</v>
       </c>
       <c r="Q49" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.39533560864618877</v>
       </c>
       <c r="R49" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0.36136096988658584</v>
       </c>
       <c r="S49" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.45701643489254118</v>
       </c>
       <c r="T49" s="7">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>8.7695749440715787E-2</v>
       </c>
       <c r="U49" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.28340807174887894</v>
       </c>
       <c r="V49" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.24899166906061465</v>
       </c>
       <c r="Z49" s="7"/>
@@ -6282,59 +6299,59 @@
         <v>4.6993524514338469E-2</v>
       </c>
       <c r="AB49" s="7">
-        <f t="shared" ref="AB49:AO49" si="88">AB18/AA18-1</f>
+        <f t="shared" ref="AB49:AO49" si="89">AB18/AA18-1</f>
         <v>0.1327089591800672</v>
       </c>
       <c r="AC49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.11934477379095165</v>
       </c>
       <c r="AD49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.35902439024390254</v>
       </c>
       <c r="AE49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.25442928930366127</v>
       </c>
       <c r="AF49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.18248044055153967</v>
       </c>
       <c r="AG49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>8.8590235067131706E-2</v>
       </c>
       <c r="AH49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>5.1204538885816664E-2</v>
       </c>
       <c r="AI49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>3.1653693802894178E-2</v>
       </c>
       <c r="AJ49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2.2571489574682468E-2</v>
       </c>
       <c r="AK49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2.0904952923547215E-2</v>
       </c>
       <c r="AL49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2.0941992337490944E-2</v>
       </c>
       <c r="AM49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2.0979260849687487E-2</v>
       </c>
       <c r="AN49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2.1016764161705837E-2</v>
       </c>
       <c r="AO49" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2.1054508084077606E-2</v>
       </c>
       <c r="AR49" t="s">
@@ -6364,51 +6381,51 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8">
-        <f t="shared" ref="K50:R50" si="89">(K18+K19)/(G18+G19)-1</f>
+        <f t="shared" ref="K50:R50" si="90">(K18+K19)/(G18+G19)-1</f>
         <v>-8.2740213523131656E-2</v>
       </c>
       <c r="L50" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-2.874432677760963E-2</v>
       </c>
       <c r="M50" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.24119028974158185</v>
       </c>
       <c r="N50" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>1.7758484609313285E-2</v>
       </c>
       <c r="O50" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.11542192046556732</v>
       </c>
       <c r="P50" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.7398753894080996</v>
       </c>
       <c r="Q50" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.62965299684542586</v>
       </c>
       <c r="R50" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.40248158200853035</v>
       </c>
       <c r="S50" s="8">
-        <f t="shared" ref="S50" si="90">(S18+S19)/(O18+O19)-1</f>
+        <f t="shared" ref="S50" si="91">(S18+S19)/(O18+O19)-1</f>
         <v>0.78956521739130436</v>
       </c>
       <c r="T50" s="8">
-        <f t="shared" ref="T50" si="91">(T18+T19)/(P18+P19)-1</f>
+        <f t="shared" ref="T50" si="92">(T18+T19)/(P18+P19)-1</f>
         <v>-6.9829901521933802E-2</v>
       </c>
       <c r="U50" s="8">
-        <f t="shared" ref="U50" si="92">(U18+U19)/(Q18+Q19)-1</f>
+        <f t="shared" ref="U50" si="93">(U18+U19)/(Q18+Q19)-1</f>
         <v>0.21881533101045303</v>
       </c>
       <c r="V50" s="8">
-        <f t="shared" ref="V50" si="93">(V18+V19)/(R18+R19)-1</f>
+        <f t="shared" ref="V50" si="94">(V18+V19)/(R18+R19)-1</f>
         <v>0.20202930605474134</v>
       </c>
       <c r="Z50" s="7"/>
@@ -6417,59 +6434,59 @@
         <v>5.3011590347710413E-2</v>
       </c>
       <c r="AB50" s="8">
-        <f t="shared" ref="AB50:AO50" si="94">(AB18+AB19)/(AA18+AA19)-1</f>
+        <f t="shared" ref="AB50:AO50" si="95">(AB18+AB19)/(AA18+AA19)-1</f>
         <v>0.12901479610249011</v>
       </c>
       <c r="AC50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>3.548026210644073E-2</v>
       </c>
       <c r="AD50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.47924062355301733</v>
       </c>
       <c r="AE50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.27628756260434062</v>
       </c>
       <c r="AF50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0.18248044055153967</v>
       </c>
       <c r="AG50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>8.8590235067131706E-2</v>
       </c>
       <c r="AH50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>5.1204538885816664E-2</v>
       </c>
       <c r="AI50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>3.1653693802894178E-2</v>
       </c>
       <c r="AJ50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.2571489574682468E-2</v>
       </c>
       <c r="AK50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.0904952923547215E-2</v>
       </c>
       <c r="AL50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.0941992337490944E-2</v>
       </c>
       <c r="AM50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.0979260849687487E-2</v>
       </c>
       <c r="AN50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.1016764161705837E-2</v>
       </c>
       <c r="AO50" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>2.1054508084077606E-2</v>
       </c>
       <c r="AR50" t="s">
@@ -6495,67 +6512,67 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8">
-        <f t="shared" ref="G51:P51" si="95">G23/G18</f>
+        <f t="shared" ref="G51:P51" si="96">G23/G18</f>
         <v>0.2109004739336493</v>
       </c>
       <c r="H51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.22443181818181818</v>
       </c>
       <c r="I51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.22332155477031801</v>
       </c>
       <c r="J51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.27789745799224475</v>
       </c>
       <c r="K51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.22157006603081439</v>
       </c>
       <c r="L51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.22845691382765532</v>
       </c>
       <c r="M51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.24402730375426621</v>
       </c>
       <c r="N51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.31912397340633553</v>
       </c>
       <c r="O51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.24905183312262957</v>
       </c>
       <c r="P51" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0.25548098434004474</v>
       </c>
       <c r="Q51" s="8">
-        <f t="shared" ref="Q51:R51" si="96">Q23/Q18</f>
+        <f t="shared" ref="Q51:R51" si="97">Q23/Q18</f>
         <v>0.23685283326538931</v>
       </c>
       <c r="R51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0.3274920999712726</v>
       </c>
       <c r="S51" s="8">
-        <f t="shared" ref="S51:V51" si="97">S23/S18</f>
+        <f t="shared" ref="S51:V51" si="98">S23/S18</f>
         <v>0.23514099783080261</v>
       </c>
       <c r="T51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.24475524475524477</v>
       </c>
       <c r="U51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.26</v>
       </c>
       <c r="V51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.34</v>
       </c>
       <c r="Z51" s="8">
@@ -6567,59 +6584,59 @@
         <v>0.24527301643399893</v>
       </c>
       <c r="AB51" s="8">
-        <f t="shared" ref="AB51:AO51" si="98">AB23/AB18</f>
+        <f t="shared" ref="AB51:AO51" si="99">AB23/AB18</f>
         <v>0.24087363494539782</v>
       </c>
       <c r="AC51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.26327526132404183</v>
       </c>
       <c r="AD51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.27545892728950877</v>
       </c>
       <c r="AE51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.28072109575423032</v>
       </c>
       <c r="AF51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="AG51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.24999999999999997</v>
       </c>
       <c r="AH51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.25</v>
       </c>
       <c r="AI51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.25</v>
       </c>
       <c r="AJ51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.25</v>
       </c>
       <c r="AK51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="AL51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.24999999999999994</v>
       </c>
       <c r="AM51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.24999999999999994</v>
       </c>
       <c r="AN51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.25</v>
       </c>
       <c r="AO51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.25</v>
       </c>
       <c r="AR51" t="s">
@@ -6627,7 +6644,7 @@
       </c>
       <c r="AS51" s="2">
         <f>Main!D3</f>
-        <v>1744.5</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="52" spans="2:45" x14ac:dyDescent="0.3">
@@ -6645,128 +6662,128 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8">
-        <f t="shared" ref="G52:N52" si="99">G20/G18</f>
+        <f t="shared" ref="G52:N52" si="100">G20/G18</f>
         <v>0.54028436018957349</v>
       </c>
       <c r="H52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.50710227272727271</v>
       </c>
       <c r="I52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.56325088339222618</v>
       </c>
       <c r="J52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.42567858681602755</v>
       </c>
       <c r="K52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.65517241379310343</v>
       </c>
       <c r="L52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.57515030060120242</v>
       </c>
       <c r="M52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.57281001137656429</v>
       </c>
       <c r="N52" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.45913179507235041</v>
       </c>
       <c r="O52" s="8">
-        <f t="shared" ref="O52:P52" si="100">O20/O18</f>
+        <f t="shared" ref="O52:P52" si="101">O20/O18</f>
         <v>0.65676359039190901</v>
       </c>
       <c r="P52" s="8">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.48635346756152126</v>
       </c>
       <c r="Q52" s="8">
-        <f t="shared" ref="Q52:R52" si="101">Q20/Q18</f>
+        <f t="shared" ref="Q52:R52" si="102">Q20/Q18</f>
         <v>0.47696697920913167</v>
       </c>
       <c r="R52" s="8">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.44900890548692907</v>
       </c>
       <c r="S52" s="8">
-        <f t="shared" ref="S52:V52" si="102">S20/S18</f>
+        <f t="shared" ref="S52:V52" si="103">S20/S18</f>
         <v>0.57006507592190891</v>
       </c>
       <c r="T52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.61085972850678738</v>
       </c>
       <c r="U52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="V52" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="Z52" s="8">
-        <f t="shared" ref="Z52:AO52" si="103">Z20/Z18</f>
+        <f t="shared" ref="Z52:AO52" si="104">Z20/Z18</f>
         <v>0.51655874190564288</v>
       </c>
       <c r="AA52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.48506803322141723</v>
       </c>
       <c r="AB52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.49656786271450859</v>
       </c>
       <c r="AC52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5484320557491289</v>
       </c>
       <c r="AD52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.49830786585991182</v>
       </c>
       <c r="AE52" s="8"/>
       <c r="AF52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AG52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AH52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AI52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AJ52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AK52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AL52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AM52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AN52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AO52" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.5</v>
       </c>
       <c r="AR52" s="1" t="s">
@@ -6774,7 +6791,7 @@
       </c>
       <c r="AS52" s="7">
         <f>AS50/AS51-1</f>
-        <v>-0.71543396756112809</v>
+        <v>-0.71857968050475507</v>
       </c>
     </row>
     <row r="53" spans="2:45" x14ac:dyDescent="0.3">
@@ -6792,128 +6809,128 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8">
-        <f t="shared" ref="G53:N53" si="104">G21/G18</f>
+        <f t="shared" ref="G53:N53" si="105">G21/G18</f>
         <v>0.3609794628751975</v>
       </c>
       <c r="H53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.32954545454545453</v>
       </c>
       <c r="I53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.31095406360424027</v>
       </c>
       <c r="J53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.20465316673847481</v>
       </c>
       <c r="K53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.36683785766691124</v>
       </c>
       <c r="L53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.33867735470941884</v>
       </c>
       <c r="M53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.28156996587030719</v>
       </c>
       <c r="N53" s="8">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.21314039890496675</v>
       </c>
       <c r="O53" s="8">
-        <f t="shared" ref="O53:P53" si="105">O21/O18</f>
+        <f t="shared" ref="O53:P53" si="106">O21/O18</f>
         <v>0.36725663716814161</v>
       </c>
       <c r="P53" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.25861297539149886</v>
       </c>
       <c r="Q53" s="8">
-        <f t="shared" ref="Q53:R53" si="106">Q21/Q18</f>
+        <f t="shared" ref="Q53:R53" si="107">Q21/Q18</f>
         <v>0.23318385650224216</v>
       </c>
       <c r="R53" s="8">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18442976156276933</v>
       </c>
       <c r="S53" s="8">
-        <f t="shared" ref="S53:V53" si="107">S21/S18</f>
+        <f t="shared" ref="S53:V53" si="108">S21/S18</f>
         <v>0.30195227765726679</v>
       </c>
       <c r="T53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.2895927601809955</v>
       </c>
       <c r="U53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="V53" s="8">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="Z53" s="8">
-        <f t="shared" ref="Z53:AO53" si="108">Z21/Z18</f>
+        <f t="shared" ref="Z53:AO53" si="109">Z21/Z18</f>
         <v>0.28436632747456059</v>
       </c>
       <c r="AA53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.29033398126877541</v>
       </c>
       <c r="AB53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.28642745709828393</v>
       </c>
       <c r="AC53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.28529616724738677</v>
       </c>
       <c r="AD53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.24335965541995694</v>
       </c>
       <c r="AE53" s="8"/>
       <c r="AF53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AG53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AH53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AI53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AJ53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AK53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AL53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AM53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AN53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AO53" s="8">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.25</v>
       </c>
       <c r="AR53" t="s">
@@ -6932,128 +6949,128 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8">
-        <f t="shared" ref="G54:V54" si="109">G25/C25-1</f>
+        <f t="shared" ref="G54:V54" si="110">G25/C25-1</f>
         <v>0.38095238095238093</v>
       </c>
       <c r="H54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="I54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J54" s="8" t="e">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.10344827586206895</v>
       </c>
       <c r="L54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>-0.4358974358974359</v>
       </c>
       <c r="M54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>-0.22641509433962259</v>
       </c>
       <c r="N54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>-0.42000000000000004</v>
       </c>
       <c r="O54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.3125</v>
       </c>
       <c r="P54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.77272727272727271</v>
       </c>
       <c r="Q54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.24390243902439024</v>
       </c>
       <c r="R54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.65517241379310343</v>
       </c>
       <c r="S54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="T54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.30769230769230771</v>
       </c>
       <c r="U54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="V54" s="8">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8">
-        <f t="shared" ref="AA54:AO54" si="110">AA25/Z25-1</f>
+        <f t="shared" ref="AA54:AO54" si="111">AA25/Z25-1</f>
         <v>0.17543859649122817</v>
       </c>
       <c r="AB54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.64925373134328357</v>
       </c>
       <c r="AC54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-0.30769230769230771</v>
       </c>
       <c r="AD54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.49019607843137258</v>
       </c>
       <c r="AE54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>-1</v>
       </c>
       <c r="AF54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AS54" s="4"/>
@@ -7077,51 +7094,51 @@
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8">
-        <f t="shared" ref="K55:P55" si="111">K26/G26-1</f>
+        <f t="shared" ref="K55:P55" si="112">K26/G26-1</f>
         <v>0.18954248366013071</v>
       </c>
       <c r="L55" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.10240963855421681</v>
       </c>
       <c r="M55" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12886597938144329</v>
       </c>
       <c r="N55" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.19607843137254899</v>
       </c>
       <c r="O55" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.25274725274725274</v>
       </c>
       <c r="P55" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.51366120218579225</v>
       </c>
       <c r="Q55" s="8">
-        <f t="shared" ref="Q55:R55" si="112">Q26/M26-1</f>
+        <f t="shared" ref="Q55:R55" si="113">Q26/M26-1</f>
         <v>0.12785388127853881</v>
       </c>
       <c r="R55" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.20655737704918042</v>
       </c>
       <c r="S55" s="8">
-        <f t="shared" ref="S55" si="113">S26/O26-1</f>
+        <f t="shared" ref="S55" si="114">S26/O26-1</f>
         <v>0.25877192982456143</v>
       </c>
       <c r="T55" s="8">
-        <f t="shared" ref="T55" si="114">T26/P26-1</f>
+        <f t="shared" ref="T55" si="115">T26/P26-1</f>
         <v>3.6101083032491044E-2</v>
       </c>
       <c r="U55" s="8">
-        <f t="shared" ref="U55" si="115">U26/Q26-1</f>
+        <f t="shared" ref="U55" si="116">U26/Q26-1</f>
         <v>0.14999999999999991</v>
       </c>
       <c r="V55" s="8">
-        <f t="shared" ref="V55" si="116">V26/R26-1</f>
+        <f t="shared" ref="V55" si="117">V26/R26-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="Z55" s="8"/>
@@ -7130,59 +7147,59 @@
         <v>2.1806853582554409E-2</v>
       </c>
       <c r="AB55" s="8">
-        <f t="shared" ref="AB55:AO55" si="117">AB26/AA26-1</f>
+        <f t="shared" ref="AB55:AO55" si="118">AB26/AA26-1</f>
         <v>0.1707317073170731</v>
       </c>
       <c r="AC55" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.15755208333333326</v>
       </c>
       <c r="AD55" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.25984251968503935</v>
       </c>
       <c r="AE55" s="8">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>-1</v>
       </c>
       <c r="AF55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AO55" s="8" t="e">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -7201,67 +7218,67 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8">
-        <f t="shared" ref="G56:P56" si="118">G28/G18</f>
+        <f t="shared" ref="G56:P56" si="119">G28/G18</f>
         <v>6.5560821484992107E-2</v>
       </c>
       <c r="H56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>9.0198863636363633E-2</v>
       </c>
       <c r="I56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>7.9151943462897528E-2</v>
       </c>
       <c r="J56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.18354157690650583</v>
       </c>
       <c r="K56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>6.5297138664710194E-2</v>
       </c>
       <c r="L56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>7.8824315297261194E-2</v>
       </c>
       <c r="M56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>9.7838452787258251E-2</v>
       </c>
       <c r="N56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.18224481814626514</v>
       </c>
       <c r="O56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>7.3957016434892539E-2</v>
       </c>
       <c r="P56" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.10827740492170022</v>
       </c>
       <c r="Q56" s="8">
-        <f t="shared" ref="Q56:R56" si="119">Q28/Q18</f>
+        <f t="shared" ref="Q56:R56" si="120">Q28/Q18</f>
         <v>0.11822258459029759</v>
       </c>
       <c r="R56" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0.21315713875323183</v>
       </c>
       <c r="S56" s="8">
-        <f t="shared" ref="S56:V56" si="120">S28/S18</f>
+        <f t="shared" ref="S56:V56" si="121">S28/S18</f>
         <v>7.7657266811279824E-2</v>
       </c>
       <c r="T56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>9.5433977786918964E-2</v>
       </c>
       <c r="U56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.16065751858204694</v>
       </c>
       <c r="V56" s="8">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.24569813282302994</v>
       </c>
       <c r="Z56" s="8">
@@ -7273,59 +7290,59 @@
         <v>0.10867644460151971</v>
       </c>
       <c r="AB56" s="8">
-        <f t="shared" ref="AB56:AO56" si="121">AB28/AB18</f>
+        <f t="shared" ref="AB56:AO56" si="122">AB28/AB18</f>
         <v>0.11669266770670828</v>
       </c>
       <c r="AC56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.11777003484320557</v>
       </c>
       <c r="AD56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.14265203568864732</v>
       </c>
       <c r="AE56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.16228117534912698</v>
       </c>
       <c r="AF56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.14482962071884012</v>
       </c>
       <c r="AG56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.14952399816845571</v>
       </c>
       <c r="AH56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15155076575660423</v>
       </c>
       <c r="AI56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15266286106328875</v>
       </c>
       <c r="AJ56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15290763753178707</v>
       </c>
       <c r="AK56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15299370236771342</v>
       </c>
       <c r="AL56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15308320714834123</v>
       </c>
       <c r="AM56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15317616380726287</v>
       </c>
       <c r="AN56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15327258436576421</v>
       </c>
       <c r="AO56" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.15337248093439074</v>
       </c>
     </row>
@@ -7344,67 +7361,67 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8">
-        <f t="shared" ref="G57:P57" si="122">G35/G34</f>
+        <f t="shared" ref="G57:P57" si="123">G35/G34</f>
         <v>0.20547945205479451</v>
       </c>
       <c r="H57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.30612244897959184</v>
       </c>
       <c r="I57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.27027027027027029</v>
       </c>
       <c r="J57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.24713958810068651</v>
       </c>
       <c r="K57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.28985507246376813</v>
       </c>
       <c r="L57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.29807692307692307</v>
       </c>
       <c r="M57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.24827586206896551</v>
       </c>
       <c r="N57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.19758064516129031</v>
       </c>
       <c r="O57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.36046511627906974</v>
       </c>
       <c r="P57" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.26923076923076922</v>
       </c>
       <c r="Q57" s="8">
-        <f t="shared" ref="Q57:R57" si="123">Q35/Q34</f>
+        <f t="shared" ref="Q57:R57" si="124">Q35/Q34</f>
         <v>0.29959514170040485</v>
       </c>
       <c r="R57" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.25036390101892286</v>
       </c>
       <c r="S57" s="8">
-        <f t="shared" ref="S57:V57" si="124">S35/S34</f>
+        <f t="shared" ref="S57:V57" si="125">S35/S34</f>
         <v>0.26712328767123289</v>
       </c>
       <c r="T57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.23766816143497757</v>
       </c>
       <c r="U57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.27</v>
       </c>
       <c r="V57" s="8">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0.27</v>
       </c>
       <c r="Z57" s="8">
@@ -7416,59 +7433,59 @@
         <v>0.25773195876288657</v>
       </c>
       <c r="AB57" s="8">
-        <f t="shared" ref="AB57:AO57" si="125">AB35/AB34</f>
+        <f t="shared" ref="AB57:AO57" si="126">AB35/AB34</f>
         <v>0.25452016689847012</v>
       </c>
       <c r="AC57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.22727272727272727</v>
       </c>
       <c r="AD57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.27117263843648209</v>
       </c>
       <c r="AE57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.26585351686982805</v>
       </c>
       <c r="AF57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AG57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AH57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AI57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AJ57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AK57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AL57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AM57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AN57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
       <c r="AO57" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0.25</v>
       </c>
     </row>
@@ -7487,131 +7504,131 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8">
-        <f t="shared" ref="G58:N58" si="126">G36/G34</f>
+        <f t="shared" ref="G58:N58" si="127">G36/G34</f>
         <v>0.16438356164383561</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.11224489795918367</v>
       </c>
       <c r="I58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>4.5045045045045043E-2</v>
       </c>
       <c r="J58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>7.3226544622425629E-2</v>
       </c>
       <c r="K58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>1.4492753623188406E-2</v>
       </c>
       <c r="L58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.15384615384615385</v>
       </c>
       <c r="M58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>4.8275862068965517E-2</v>
       </c>
       <c r="N58" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.14314516129032259</v>
       </c>
       <c r="O58" s="8">
-        <f t="shared" ref="O58:P58" si="127">O36/O34</f>
+        <f t="shared" ref="O58:P58" si="128">O36/O34</f>
         <v>5.8139534883720929E-2</v>
       </c>
       <c r="P58" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.42788461538461536</v>
       </c>
       <c r="Q58" s="8">
-        <f t="shared" ref="Q58:R58" si="128">Q36/Q34</f>
+        <f t="shared" ref="Q58:R58" si="129">Q36/Q34</f>
         <v>0.15384615384615385</v>
       </c>
       <c r="R58" s="8">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>6.6957787481804948E-2</v>
       </c>
       <c r="S58" s="8">
-        <f t="shared" ref="S58:V58" si="129">S36/S34</f>
+        <f t="shared" ref="S58:V58" si="130">S36/S34</f>
         <v>0.16438356164383561</v>
       </c>
       <c r="T58" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.1210762331838565</v>
       </c>
       <c r="U58" s="8">
-        <f t="shared" si="129"/>
-        <v>0.1</v>
-      </c>
-      <c r="V58" s="8">
-        <f t="shared" si="129"/>
-        <v>0.1</v>
-      </c>
-      <c r="Z58" s="8">
-        <f t="shared" ref="Z58:AO58" si="130">Z36/Z34</f>
-        <v>0.84699453551912574</v>
-      </c>
-      <c r="AA58" s="8">
-        <f t="shared" si="130"/>
-        <v>0.2422680412371134</v>
-      </c>
-      <c r="AB58" s="8">
-        <f t="shared" si="130"/>
-        <v>8.3449235048678724E-2</v>
-      </c>
-      <c r="AC58" s="8">
-        <f t="shared" si="130"/>
-        <v>0.1167076167076167</v>
-      </c>
-      <c r="AD58" s="8">
-        <f t="shared" si="130"/>
-        <v>0.14495114006514659</v>
-      </c>
-      <c r="AE58" s="8">
-        <f t="shared" si="130"/>
-        <v>0.10766257039782763</v>
-      </c>
-      <c r="AF58" s="8">
         <f t="shared" si="130"/>
         <v>0.1</v>
       </c>
-      <c r="AG58" s="8">
+      <c r="V58" s="8">
         <f t="shared" si="130"/>
         <v>0.1</v>
       </c>
+      <c r="Z58" s="8">
+        <f t="shared" ref="Z58:AO58" si="131">Z36/Z34</f>
+        <v>0.84699453551912574</v>
+      </c>
+      <c r="AA58" s="8">
+        <f t="shared" si="131"/>
+        <v>0.2422680412371134</v>
+      </c>
+      <c r="AB58" s="8">
+        <f t="shared" si="131"/>
+        <v>8.3449235048678724E-2</v>
+      </c>
+      <c r="AC58" s="8">
+        <f t="shared" si="131"/>
+        <v>0.1167076167076167</v>
+      </c>
+      <c r="AD58" s="8">
+        <f t="shared" si="131"/>
+        <v>0.14495114006514659</v>
+      </c>
+      <c r="AE58" s="8">
+        <f t="shared" si="131"/>
+        <v>0.10766257039782763</v>
+      </c>
+      <c r="AF58" s="8">
+        <f t="shared" si="131"/>
+        <v>0.1</v>
+      </c>
+      <c r="AG58" s="8">
+        <f t="shared" si="131"/>
+        <v>0.1</v>
+      </c>
       <c r="AH58" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.1</v>
       </c>
       <c r="AI58" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.1</v>
       </c>
       <c r="AJ58" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.1</v>
       </c>
       <c r="AK58" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.1</v>
       </c>
       <c r="AL58" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AM58" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.1</v>
       </c>
       <c r="AN58" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AO58" s="8">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.1</v>
       </c>
     </row>
@@ -7630,87 +7647,87 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8">
-        <f t="shared" ref="G59:P59" si="131">G37/G23</f>
+        <f t="shared" ref="G59:P59" si="132">G37/G23</f>
         <v>0.17228464419475656</v>
       </c>
       <c r="H59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.18037974683544303</v>
       </c>
       <c r="I59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.24050632911392406</v>
       </c>
       <c r="J59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.46046511627906977</v>
       </c>
       <c r="K59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15894039735099338</v>
       </c>
       <c r="L59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.16666666666666666</v>
       </c>
       <c r="M59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.23776223776223776</v>
       </c>
       <c r="N59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.40073529411764708</v>
       </c>
       <c r="O59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.12690355329949238</v>
       </c>
       <c r="P59" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.11033274956217162</v>
       </c>
       <c r="Q59" s="8">
-        <f t="shared" ref="Q59:R59" si="132">Q37/Q23</f>
+        <f t="shared" ref="Q59:R59" si="133">Q37/Q23</f>
         <v>0.23235800344234078</v>
       </c>
       <c r="R59" s="8">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.41140350877192983</v>
       </c>
       <c r="S59" s="8">
-        <f t="shared" ref="S59:V59" si="133">S37/S23</f>
+        <f t="shared" ref="S59:V59" si="134">S37/S23</f>
         <v>0.15313653136531366</v>
       </c>
       <c r="T59" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.24033613445378152</v>
       </c>
       <c r="U59" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.35453489906320107</v>
       </c>
       <c r="V59" s="8">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.43065200879212695</v>
       </c>
       <c r="Z59" s="8">
-        <f t="shared" ref="Z59:AD59" si="134">Z37/Z18</f>
+        <f t="shared" ref="Z59:AD59" si="135">Z37/Z18</f>
         <v>-4.9953746530989824E-3</v>
       </c>
       <c r="AA59" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>5.1422512811450785E-2</v>
       </c>
       <c r="AB59" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>7.4258970358814347E-2</v>
       </c>
       <c r="AC59" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>7.4425087108013932E-2</v>
       </c>
       <c r="AD59" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>7.3530919905650707E-2</v>
       </c>
       <c r="AE59" s="8">
@@ -7718,43 +7735,43 @@
         <v>9.4245194793303441E-2</v>
       </c>
       <c r="AF59" s="8">
-        <f t="shared" ref="AF59:AO59" si="135">AF37/AF18</f>
+        <f t="shared" ref="AF59:AO59" si="136">AF37/AF18</f>
         <v>8.7432232578779717E-2</v>
       </c>
       <c r="AG59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.0844564009088205E-2</v>
       </c>
       <c r="AH59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.2289972987687069E-2</v>
       </c>
       <c r="AI59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.3022802147021036E-2</v>
       </c>
       <c r="AJ59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.3136808175650315E-2</v>
       </c>
       <c r="AK59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.3137042145548507E-2</v>
       </c>
       <c r="AL59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.313924670847841E-2</v>
       </c>
       <c r="AM59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.3143432778644258E-2</v>
       </c>
       <c r="AN59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.314961145777112E-2</v>
       </c>
       <c r="AO59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.3157794039098352E-2</v>
       </c>
     </row>
@@ -7772,7 +7789,7 @@
       </c>
       <c r="T63" s="16">
         <f>Main!D9/Model!T61</f>
-        <v>5.2608702802713632</v>
+        <v>5.3194517919550472</v>
       </c>
     </row>
     <row r="64" spans="2:45" x14ac:dyDescent="0.3">
@@ -7781,7 +7798,7 @@
       </c>
       <c r="T64" s="8">
         <f>T61/Main!D9-1</f>
-        <v>-0.80991738120780687</v>
+        <v>-0.81201070352543381</v>
       </c>
     </row>
     <row r="67" spans="2:41" x14ac:dyDescent="0.3">
@@ -7789,52 +7806,52 @@
         <v>92</v>
       </c>
       <c r="O67" s="3">
-        <f t="shared" ref="O67:V67" si="136">O37</f>
+        <f t="shared" ref="O67:V67" si="137">O37</f>
         <v>50</v>
       </c>
       <c r="P67" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>63</v>
       </c>
       <c r="Q67" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>135</v>
       </c>
       <c r="R67" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>469</v>
       </c>
       <c r="S67" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>83</v>
       </c>
       <c r="T67" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>143</v>
       </c>
       <c r="U67" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>290.19816000000014</v>
       </c>
       <c r="V67" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>636.60340799999994</v>
       </c>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3">
-        <f t="shared" ref="Z67:AC67" si="137">Z37</f>
+        <f t="shared" ref="Z67:AC67" si="138">Z37</f>
         <v>-27</v>
       </c>
       <c r="AA67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>291</v>
       </c>
       <c r="AB67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>476</v>
       </c>
       <c r="AC67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>534</v>
       </c>
       <c r="AD67" s="3">
@@ -7842,47 +7859,47 @@
         <v>717</v>
       </c>
       <c r="AE67" s="3">
-        <f t="shared" ref="AE67:AO67" si="138">AE37</f>
+        <f t="shared" ref="AE67:AO67" si="139">AE37</f>
         <v>1152.8015680000001</v>
       </c>
       <c r="AF67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1264.6224175000007</v>
       </c>
       <c r="AG67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1430.3841434999997</v>
       </c>
       <c r="AH67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1527.5501896362498</v>
       </c>
       <c r="AI67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1588.4162624936125</v>
       </c>
       <c r="AJ67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1626.2598404607766</v>
       </c>
       <c r="AK67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1660.2608966144278</v>
       </c>
       <c r="AL67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1695.0701891176468</v>
       </c>
       <c r="AM67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1730.7092906452594</v>
       </c>
       <c r="AN67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1767.2004192837585</v>
       </c>
       <c r="AO67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>1804.5664601807241</v>
       </c>
     </row>
@@ -7943,43 +7960,43 @@
         <v>1268.0817248000003</v>
       </c>
       <c r="AF68" s="6">
-        <f t="shared" ref="AF68:AO68" si="139">AF67*1.1</f>
+        <f t="shared" ref="AF68:AO68" si="140">AF67*1.1</f>
         <v>1391.0846592500009</v>
       </c>
       <c r="AG68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1573.4225578499997</v>
       </c>
       <c r="AH68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1680.305208599875</v>
       </c>
       <c r="AI68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1747.2578887429738</v>
       </c>
       <c r="AJ68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1788.8858245068543</v>
       </c>
       <c r="AK68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1826.2869862758707</v>
       </c>
       <c r="AL68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1864.5772080294116</v>
       </c>
       <c r="AM68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1903.7802197097856</v>
       </c>
       <c r="AN68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1943.9204612121346</v>
       </c>
       <c r="AO68" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>1985.0231061987968</v>
       </c>
     </row>
@@ -8064,19 +8081,19 @@
         <v>797.91254983440001</v>
       </c>
       <c r="AL69" s="3">
-        <f t="shared" ref="AL69:AO69" si="140">AK69*1.02</f>
+        <f t="shared" ref="AL69:AO69" si="141">AK69*1.02</f>
         <v>813.87080083108799</v>
       </c>
       <c r="AM69" s="3">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>830.14821684770982</v>
       </c>
       <c r="AN69" s="3">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>846.75118118466401</v>
       </c>
       <c r="AO69" s="3">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>863.68620480835727</v>
       </c>
     </row>
@@ -8104,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
-        <f t="shared" ref="AE70:AE79" si="141">SUM(S70:V70)</f>
+        <f t="shared" ref="AE70:AE79" si="142">SUM(S70:V70)</f>
         <v>0</v>
       </c>
       <c r="AF70" s="3">
@@ -8155,7 +8172,7 @@
         <v>-11</v>
       </c>
       <c r="R71" s="3">
-        <f t="shared" ref="R71:R75" si="142">AD71-Q71-P71-O71</f>
+        <f t="shared" ref="R71:R75" si="143">AD71-Q71-P71-O71</f>
         <v>-6</v>
       </c>
       <c r="S71" s="3">
@@ -8197,7 +8214,7 @@
         <v>-24</v>
       </c>
       <c r="AE71" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>-21</v>
       </c>
       <c r="AF71" s="3">
@@ -8205,39 +8222,39 @@
         <v>-23.1</v>
       </c>
       <c r="AG71" s="3">
-        <f t="shared" ref="AG71:AO71" si="143">AF71*1.1</f>
+        <f t="shared" ref="AG71:AO71" si="144">AF71*1.1</f>
         <v>-25.410000000000004</v>
       </c>
       <c r="AH71" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-27.951000000000008</v>
       </c>
       <c r="AI71" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-30.746100000000009</v>
       </c>
       <c r="AJ71" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-33.820710000000012</v>
       </c>
       <c r="AK71" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-37.202781000000016</v>
       </c>
       <c r="AL71" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-40.923059100000017</v>
       </c>
       <c r="AM71" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-45.015365010000025</v>
       </c>
       <c r="AN71" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-49.516901511000029</v>
       </c>
       <c r="AO71" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>-54.468591662100039</v>
       </c>
     </row>
@@ -8257,7 +8274,7 @@
         <v>-3</v>
       </c>
       <c r="R72" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>37</v>
       </c>
       <c r="S72" s="3">
@@ -8291,7 +8308,7 @@
         <v>103</v>
       </c>
       <c r="AE72" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>0</v>
       </c>
       <c r="AF72" s="3">
@@ -8341,7 +8358,7 @@
         <v>78</v>
       </c>
       <c r="R73" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>41</v>
       </c>
       <c r="S73" s="3">
@@ -8376,7 +8393,7 @@
         <v>135</v>
       </c>
       <c r="AE73" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>95</v>
       </c>
       <c r="AF73" s="3">
@@ -8426,7 +8443,7 @@
         <v>-77</v>
       </c>
       <c r="R74" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>558</v>
       </c>
       <c r="S74" s="3">
@@ -8462,7 +8479,7 @@
         <v>407</v>
       </c>
       <c r="AE74" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>168</v>
       </c>
       <c r="AF74" s="3">
@@ -8512,7 +8529,7 @@
         <v>-15</v>
       </c>
       <c r="R75" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>72</v>
       </c>
       <c r="S75" s="3">
@@ -8547,7 +8564,7 @@
         <v>-102</v>
       </c>
       <c r="AE75" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>-100</v>
       </c>
       <c r="AF75" s="3">
@@ -8601,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="AE76" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>0</v>
       </c>
       <c r="AF76" s="3">
@@ -8651,7 +8668,7 @@
         <v>12</v>
       </c>
       <c r="R77" s="3">
-        <f t="shared" ref="R77:R79" si="144">AD77-Q77-P77-O77</f>
+        <f t="shared" ref="R77:R79" si="145">AD77-Q77-P77-O77</f>
         <v>-1</v>
       </c>
       <c r="S77" s="3">
@@ -8686,7 +8703,7 @@
         <v>15</v>
       </c>
       <c r="AE77" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>4</v>
       </c>
       <c r="AF77" s="3">
@@ -8735,7 +8752,7 @@
         <v>9</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>7</v>
       </c>
       <c r="S78" s="3">
@@ -8770,7 +8787,7 @@
         <v>16</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>16</v>
       </c>
       <c r="AF78" s="3">
@@ -8820,7 +8837,7 @@
         <v>38</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>-109</v>
       </c>
       <c r="S79" s="3">
@@ -8855,7 +8872,7 @@
         <v>-42</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>-25</v>
       </c>
       <c r="AF79" s="3">
@@ -8894,27 +8911,27 @@
         <v>104</v>
       </c>
       <c r="O80" s="6">
-        <f t="shared" ref="O80:P80" si="145">O68+SUM(O69:O79)</f>
+        <f t="shared" ref="O80:P80" si="146">O68+SUM(O69:O79)</f>
         <v>-105</v>
       </c>
       <c r="P80" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>297</v>
       </c>
       <c r="Q80" s="6">
-        <f t="shared" ref="Q80:R80" si="146">Q68+SUM(Q69:Q79)</f>
+        <f t="shared" ref="Q80:R80" si="147">Q68+SUM(Q69:Q79)</f>
         <v>300</v>
       </c>
       <c r="R80" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>1227</v>
       </c>
       <c r="S80" s="6">
-        <f t="shared" ref="S80:T80" si="147">S68+SUM(S69:S79)</f>
+        <f t="shared" ref="S80:T80" si="148">S68+SUM(S69:S79)</f>
         <v>420</v>
       </c>
       <c r="T80" s="6">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>-697</v>
       </c>
       <c r="U80" s="6">
@@ -8926,71 +8943,71 @@
         <v>1740.003408</v>
       </c>
       <c r="Y80" s="6">
-        <f t="shared" ref="Y80:AD80" si="148">Y68+SUM(Y69:Y79)</f>
+        <f t="shared" ref="Y80:AD80" si="149">Y68+SUM(Y69:Y79)</f>
         <v>602</v>
       </c>
       <c r="Z80" s="6">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>453</v>
       </c>
       <c r="AA80" s="6">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>690</v>
       </c>
       <c r="AB80" s="6">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>174</v>
       </c>
       <c r="AC80" s="6">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>742</v>
       </c>
       <c r="AD80" s="6">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>1719</v>
       </c>
       <c r="AE80" s="6">
-        <f t="shared" ref="AE80:AO80" si="149">AE68+SUM(AE69:AE79)</f>
+        <f t="shared" ref="AE80:AO80" si="150">AE68+SUM(AE69:AE79)</f>
         <v>1954.8817248000003</v>
       </c>
       <c r="AF80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2000.2546592500007</v>
       </c>
       <c r="AG80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2243.5095578499995</v>
       </c>
       <c r="AH80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2382.6260585998748</v>
       </c>
       <c r="AI80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2475.9945127429737</v>
       </c>
       <c r="AJ80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2537.3323202268543</v>
       </c>
       <c r="AK80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2586.9967551102709</v>
       </c>
       <c r="AL80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2637.5249497604996</v>
       </c>
       <c r="AM80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2688.9130715474953</v>
       </c>
       <c r="AN80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2741.1547408857987</v>
       </c>
       <c r="AO80" s="6">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>2794.240719345054</v>
       </c>
     </row>
@@ -9021,11 +9038,11 @@
         <v>199</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" ref="U81:V81" si="150">Q81*1.45</f>
+        <f t="shared" ref="U81:V81" si="151">Q81*1.45</f>
         <v>266.8</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>458.2</v>
       </c>
       <c r="Y81" s="3">
@@ -9055,19 +9072,19 @@
         <v>1184.7</v>
       </c>
       <c r="AG81" s="3">
-        <f t="shared" ref="AG81:AJ81" si="151">AF81*0.9</f>
+        <f t="shared" ref="AG81:AJ81" si="152">AF81*0.9</f>
         <v>1066.23</v>
       </c>
       <c r="AH81" s="3">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>959.60700000000008</v>
       </c>
       <c r="AI81" s="3">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>863.64630000000011</v>
       </c>
       <c r="AJ81" s="3">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>777.28167000000008</v>
       </c>
       <c r="AK81" s="3">
@@ -9075,19 +9092,19 @@
         <v>738.41758650000008</v>
       </c>
       <c r="AL81" s="3">
-        <f t="shared" ref="AL81:AO81" si="152">AK81*0.95</f>
+        <f t="shared" ref="AL81:AO81" si="153">AK81*0.95</f>
         <v>701.4967071750001</v>
       </c>
       <c r="AM81" s="3">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>666.42187181625002</v>
       </c>
       <c r="AN81" s="3">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>633.10077822543747</v>
       </c>
       <c r="AO81" s="3">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>601.44573931416562</v>
       </c>
     </row>
@@ -9096,103 +9113,103 @@
         <v>106</v>
       </c>
       <c r="O82" s="6">
-        <f t="shared" ref="O82:P82" si="153">O80-O81</f>
+        <f t="shared" ref="O82:P82" si="154">O80-O81</f>
         <v>-210</v>
       </c>
       <c r="P82" s="6">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>170</v>
       </c>
       <c r="Q82" s="6">
-        <f t="shared" ref="Q82:R82" si="154">Q80-Q81</f>
+        <f t="shared" ref="Q82:R82" si="155">Q80-Q81</f>
         <v>116</v>
       </c>
       <c r="R82" s="6">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>911</v>
       </c>
       <c r="S82" s="6">
-        <f t="shared" ref="S82:V82" si="155">S80-S81</f>
+        <f t="shared" ref="S82:V82" si="156">S80-S81</f>
         <v>267</v>
       </c>
       <c r="T82" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>-896</v>
       </c>
       <c r="U82" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>150.79816000000011</v>
       </c>
       <c r="V82" s="6">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>1281.803408</v>
       </c>
       <c r="Y82" s="6">
-        <f t="shared" ref="Y82:AD82" si="156">Y80-Y81</f>
+        <f t="shared" ref="Y82:AD82" si="157">Y80-Y81</f>
         <v>314</v>
       </c>
       <c r="Z82" s="6">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>216</v>
       </c>
       <c r="AA82" s="6">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>419</v>
       </c>
       <c r="AB82" s="6">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>-175</v>
       </c>
       <c r="AC82" s="6">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>344</v>
       </c>
       <c r="AD82" s="6">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>987</v>
       </c>
       <c r="AE82" s="6">
-        <f t="shared" ref="AE82:AO82" si="157">AE80-AE81</f>
+        <f t="shared" ref="AE82:AO82" si="158">AE80-AE81</f>
         <v>877.88172480000026</v>
       </c>
       <c r="AF82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>815.55465925000067</v>
       </c>
       <c r="AG82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1177.2795578499995</v>
       </c>
       <c r="AH82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1423.0190585998748</v>
       </c>
       <c r="AI82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1612.3482127429736</v>
       </c>
       <c r="AJ82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1760.0506502268543</v>
       </c>
       <c r="AK82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1848.5791686102707</v>
       </c>
       <c r="AL82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>1936.0282425854994</v>
       </c>
       <c r="AM82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>2022.4911997312452</v>
       </c>
       <c r="AN82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>2108.0539626603613</v>
       </c>
       <c r="AO82" s="6">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>2192.7949800308884</v>
       </c>
       <c r="AP82" s="1">
@@ -9200,391 +9217,391 @@
         <v>2170.8670302305795</v>
       </c>
       <c r="AQ82" s="1">
-        <f t="shared" ref="AQ82:DB82" si="158">AP82*(1+AT45)</f>
+        <f t="shared" ref="AQ82:DB82" si="159">AP82*(1+AT45)</f>
         <v>2170.8670302305795</v>
       </c>
       <c r="AR82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AS82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AT82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AU82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AV82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AW82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AX82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AY82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="AZ82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BA82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BB82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BC82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BD82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BE82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BF82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BG82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BH82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BI82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BJ82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BK82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BL82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BM82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BN82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BO82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BP82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BQ82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BR82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BS82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BT82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BU82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BV82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BW82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BX82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BY82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="BZ82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CA82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CB82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CC82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CD82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CE82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CF82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CG82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CH82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CI82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CJ82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CK82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CL82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CM82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CN82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CO82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CP82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CQ82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CR82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CS82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CT82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CU82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CV82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CW82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CX82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CY82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="CZ82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DA82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DB82" s="1">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DC82" s="1">
-        <f t="shared" ref="DC82:EI82" si="159">DB82*(1+DF45)</f>
+        <f t="shared" ref="DC82:EI82" si="160">DB82*(1+DF45)</f>
         <v>2170.8670302305795</v>
       </c>
       <c r="DD82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DE82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DF82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DG82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DH82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DI82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DJ82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DK82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DL82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DM82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DN82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DO82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DP82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DQ82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DR82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DS82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DT82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DU82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DV82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DW82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DX82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DY82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="DZ82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EA82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EB82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EC82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="ED82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EE82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EF82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EG82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EH82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
       <c r="EI82" s="1">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>2170.8670302305795</v>
       </c>
     </row>
@@ -9597,15 +9614,15 @@
         <v>0.45714285714285707</v>
       </c>
       <c r="T84" s="8">
-        <f t="shared" ref="T84:V84" si="160">T81/P81-1</f>
+        <f t="shared" ref="T84:V84" si="161">T81/P81-1</f>
         <v>0.56692913385826782</v>
       </c>
       <c r="U84" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="V84" s="8">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="AS84" s="3">
@@ -9634,13 +9651,13 @@
     <row r="88" spans="2:139" x14ac:dyDescent="0.3">
       <c r="AS88" s="12">
         <f>Main!D3</f>
-        <v>1744.5</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="89" spans="2:139" x14ac:dyDescent="0.3">
       <c r="AS89" s="7">
         <f>AS87/AS88-1</f>
-        <v>-0.66246093342527002</v>
+        <v>-0.6661922326306029</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RHM.xlsx
+++ b/Financial Analysis/RHM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8073CBF-0EE6-4DD6-BB1F-B990CB029970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5623DB-4FD6-42C2-8964-E0E696DB246E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="112">
   <si>
     <t>RHM</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>B/EV</t>
+  </si>
+  <si>
+    <t>Disposals</t>
   </si>
 </sst>
 </file>
@@ -430,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -460,6 +463,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,15 +485,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -505,8 +509,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13754100" y="0"/>
-          <a:ext cx="0" cy="15834360"/>
+          <a:off x="14363700" y="0"/>
+          <a:ext cx="0" cy="16931640"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -539,7 +543,7 @@
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -927,17 +931,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>1764</v>
+        <v>1523.5</v>
       </c>
       <c r="E3" s="11">
-        <v>45955</v>
+        <v>45988</v>
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45955</v>
+        <v>46066</v>
       </c>
       <c r="G3" s="11">
-        <v>45967</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -945,10 +949,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <v>43.84</v>
+        <f>45.03</f>
+        <v>45.03</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -957,7 +962,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>77333.760000000009</v>
+        <v>68603.205000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -965,11 +970,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>1083+328</f>
-        <v>1411</v>
+        <f>557+320</f>
+        <v>877</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -977,11 +982,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>193+1511</f>
-        <v>1704</v>
+        <f>1232+1198</f>
+        <v>2430</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -990,7 +995,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-293</v>
+        <v>-1553</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -999,7 +1004,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>77626.760000000009</v>
+        <v>70156.205000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501EC44B-4F3D-481F-98FD-E9305230A697}">
-  <dimension ref="B2:EV89"/>
+  <dimension ref="B2:EV101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
@@ -1182,7 +1187,9 @@
       <c r="T3" s="3">
         <v>664</v>
       </c>
-      <c r="U3" s="4"/>
+      <c r="U3" s="3">
+        <v>555</v>
+      </c>
       <c r="V3" s="4"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
@@ -1255,7 +1262,9 @@
       <c r="T4" s="3">
         <v>433</v>
       </c>
-      <c r="U4" s="4"/>
+      <c r="U4" s="3">
+        <v>1500</v>
+      </c>
       <c r="V4" s="4"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
@@ -1328,7 +1337,9 @@
       <c r="T5" s="3">
         <v>-256</v>
       </c>
-      <c r="U5" s="4"/>
+      <c r="U5" s="3">
+        <v>-895</v>
+      </c>
       <c r="V5" s="4"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
@@ -1400,7 +1411,9 @@
       <c r="T6" s="3">
         <v>1798</v>
       </c>
-      <c r="U6" s="4"/>
+      <c r="U6" s="3">
+        <v>2721</v>
+      </c>
       <c r="V6" s="4"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
@@ -1477,10 +1490,13 @@
         <v>11039</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" ref="T7" si="1">SUM(T3:T6)</f>
+        <f t="shared" ref="T7:U7" si="1">SUM(T3:T6)</f>
         <v>2639</v>
       </c>
-      <c r="U7" s="4"/>
+      <c r="U7" s="3">
+        <f t="shared" si="1"/>
+        <v>3881</v>
+      </c>
       <c r="V7" s="4"/>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
@@ -1552,7 +1568,9 @@
       <c r="T8" s="3">
         <v>7192</v>
       </c>
-      <c r="U8" s="4"/>
+      <c r="U8" s="3">
+        <v>7143</v>
+      </c>
       <c r="V8" s="4"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
@@ -1566,7 +1584,7 @@
         <v>7712</v>
       </c>
       <c r="AE8" s="3">
-        <v>7192</v>
+        <v>7143</v>
       </c>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
@@ -1623,7 +1641,9 @@
       <c r="T9" s="3">
         <v>23707</v>
       </c>
-      <c r="U9" s="4"/>
+      <c r="U9" s="3">
+        <v>23985</v>
+      </c>
       <c r="V9" s="4"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
@@ -1637,7 +1657,7 @@
         <v>16533</v>
       </c>
       <c r="AE9" s="3">
-        <v>23707</v>
+        <v>23985</v>
       </c>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
@@ -1694,7 +1714,9 @@
       <c r="T10" s="3">
         <v>32266</v>
       </c>
-      <c r="U10" s="4"/>
+      <c r="U10" s="3">
+        <v>32675</v>
+      </c>
       <c r="V10" s="4"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
@@ -1708,7 +1730,7 @@
         <v>30728</v>
       </c>
       <c r="AE10" s="3">
-        <v>32266</v>
+        <v>32675</v>
       </c>
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
@@ -1774,7 +1796,10 @@
         <f t="shared" si="2"/>
         <v>63165</v>
       </c>
-      <c r="U11" s="13"/>
+      <c r="U11" s="14">
+        <f t="shared" ref="U11" si="3">SUM(U8:U10)</f>
+        <v>63803</v>
+      </c>
       <c r="V11" s="13"/>
       <c r="Z11" s="6"/>
       <c r="AA11" s="6"/>
@@ -1791,8 +1816,8 @@
         <v>54973</v>
       </c>
       <c r="AE11" s="14">
-        <f t="shared" ref="AE11" si="3">SUM(AE8:AE10)</f>
-        <v>63165</v>
+        <f t="shared" ref="AE11" si="4">SUM(AE8:AE10)</f>
+        <v>63803</v>
       </c>
       <c r="AF11" s="6"/>
       <c r="AG11" s="6"/>
@@ -1899,11 +1924,10 @@
         <v>930</v>
       </c>
       <c r="U13" s="9">
-        <f>Q13*1.2</f>
-        <v>1480.8</v>
+        <v>1309</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" ref="V13" si="4">R13*1.35</f>
+        <f t="shared" ref="V13" si="5">R13*1.35</f>
         <v>1675.3500000000001</v>
       </c>
       <c r="Z13" s="3">
@@ -1923,47 +1947,47 @@
       </c>
       <c r="AE13" s="3">
         <f>SUM(S13:V13)</f>
-        <v>5031.1500000000005</v>
+        <v>4859.3500000000004</v>
       </c>
       <c r="AF13" s="3">
         <f>AE13*1.22</f>
-        <v>6138.0030000000006</v>
+        <v>5928.4070000000002</v>
       </c>
       <c r="AG13" s="3">
         <f>AF13*1.08</f>
-        <v>6629.0432400000009</v>
+        <v>6402.6795600000005</v>
       </c>
       <c r="AH13" s="3">
         <f>AG13*1.05</f>
-        <v>6960.4954020000014</v>
+        <v>6722.8135380000012</v>
       </c>
       <c r="AI13" s="3">
         <f>AH13*1.03</f>
-        <v>7169.3102640600018</v>
+        <v>6924.4979441400019</v>
       </c>
       <c r="AJ13" s="3">
-        <f t="shared" ref="AJ13:AO13" si="5">AI13*1.02</f>
-        <v>7312.6964693412019</v>
+        <f t="shared" ref="AJ13:AO13" si="6">AI13*1.02</f>
+        <v>7062.9879030228021</v>
       </c>
       <c r="AK13" s="3">
-        <f t="shared" si="5"/>
-        <v>7458.9503987280259</v>
+        <f t="shared" si="6"/>
+        <v>7204.2476610832582</v>
       </c>
       <c r="AL13" s="3">
-        <f t="shared" si="5"/>
-        <v>7608.1294067025865</v>
+        <f t="shared" si="6"/>
+        <v>7348.3326143049235</v>
       </c>
       <c r="AM13" s="3">
-        <f t="shared" si="5"/>
-        <v>7760.291994836638</v>
+        <f t="shared" si="6"/>
+        <v>7495.2992665910224</v>
       </c>
       <c r="AN13" s="3">
-        <f t="shared" si="5"/>
-        <v>7915.4978347333708</v>
+        <f t="shared" si="6"/>
+        <v>7645.2052519228428</v>
       </c>
       <c r="AO13" s="3">
-        <f t="shared" si="5"/>
-        <v>8073.8077914280384</v>
+        <f t="shared" si="6"/>
+        <v>7798.1093569612995</v>
       </c>
     </row>
     <row r="14" spans="2:41" x14ac:dyDescent="0.3">
@@ -2022,8 +2046,7 @@
         <v>661</v>
       </c>
       <c r="U14" s="9">
-        <f>Q14*1.8</f>
-        <v>804.6</v>
+        <v>608</v>
       </c>
       <c r="V14" s="9">
         <f>R14*1.2</f>
@@ -2046,47 +2069,47 @@
       </c>
       <c r="AE14" s="3">
         <f>SUM(S14:V14)</f>
-        <v>3354</v>
+        <v>3157.3999999999996</v>
       </c>
       <c r="AF14" s="3">
         <f>AE14*1.2</f>
-        <v>4024.7999999999997</v>
+        <v>3788.8799999999992</v>
       </c>
       <c r="AG14" s="3">
         <f>AF14*1.1</f>
-        <v>4427.28</v>
+        <v>4167.7679999999991</v>
       </c>
       <c r="AH14" s="3">
         <f>AG14*1.05</f>
-        <v>4648.6440000000002</v>
+        <v>4376.1563999999989</v>
       </c>
       <c r="AI14" s="3">
         <f>AH14*1.03</f>
-        <v>4788.1033200000002</v>
+        <v>4507.4410919999991</v>
       </c>
       <c r="AJ14" s="3">
         <f>AI14*1.02</f>
-        <v>4883.8653863999998</v>
+        <v>4597.5899138399991</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" ref="AK14:AO14" si="6">AJ14*1.02</f>
-        <v>4981.5426941280002</v>
+        <f t="shared" ref="AK14:AO14" si="7">AJ14*1.02</f>
+        <v>4689.5417121167993</v>
       </c>
       <c r="AL14" s="3">
-        <f t="shared" si="6"/>
-        <v>5081.1735480105599</v>
+        <f t="shared" si="7"/>
+        <v>4783.3325463591354</v>
       </c>
       <c r="AM14" s="3">
-        <f t="shared" si="6"/>
-        <v>5182.7970189707712</v>
+        <f t="shared" si="7"/>
+        <v>4878.9991972863181</v>
       </c>
       <c r="AN14" s="3">
-        <f t="shared" si="6"/>
-        <v>5286.4529593501866</v>
+        <f t="shared" si="7"/>
+        <v>4976.5791812320449</v>
       </c>
       <c r="AO14" s="3">
-        <f t="shared" si="6"/>
-        <v>5392.1820185371907</v>
+        <f t="shared" si="7"/>
+        <v>5076.1107648566858</v>
       </c>
     </row>
     <row r="15" spans="2:41" x14ac:dyDescent="0.3">
@@ -2145,8 +2168,7 @@
         <v>403</v>
       </c>
       <c r="U15" s="9">
-        <f>Q15*1.4</f>
-        <v>397.59999999999997</v>
+        <v>404</v>
       </c>
       <c r="V15" s="9">
         <f>R15*1.33</f>
@@ -2169,47 +2191,47 @@
       </c>
       <c r="AE15" s="3">
         <f>SUM(S15:V15)</f>
-        <v>1844.4899999999998</v>
+        <v>1850.8899999999999</v>
       </c>
       <c r="AF15" s="3">
         <f>AE15*1.22</f>
-        <v>2250.2777999999998</v>
+        <v>2258.0857999999998</v>
       </c>
       <c r="AG15" s="3">
         <f>AF15*1.15</f>
-        <v>2587.8194699999995</v>
+        <v>2596.7986699999997</v>
       </c>
       <c r="AH15" s="3">
         <f>AG15*1.08</f>
-        <v>2794.8450275999994</v>
+        <v>2804.5425636</v>
       </c>
       <c r="AI15" s="3">
         <f>AH15*1.05</f>
-        <v>2934.5872789799996</v>
+        <v>2944.7696917799999</v>
       </c>
       <c r="AJ15" s="3">
         <f>AI15*1.04</f>
-        <v>3051.9707701391999</v>
+        <v>3062.5604794512001</v>
       </c>
       <c r="AK15" s="3">
         <f>AJ15*1.03</f>
-        <v>3143.5298932433761</v>
+        <v>3154.437293834736</v>
       </c>
       <c r="AL15" s="3">
-        <f t="shared" ref="AL15:AO15" si="7">AK15*1.03</f>
-        <v>3237.8357900406777</v>
+        <f t="shared" ref="AL15:AO15" si="8">AK15*1.03</f>
+        <v>3249.0704126497781</v>
       </c>
       <c r="AM15" s="3">
-        <f t="shared" si="7"/>
-        <v>3334.970863741898</v>
+        <f t="shared" si="8"/>
+        <v>3346.5425250292715</v>
       </c>
       <c r="AN15" s="3">
-        <f t="shared" si="7"/>
-        <v>3435.0199896541549</v>
+        <f t="shared" si="8"/>
+        <v>3446.9388007801499</v>
       </c>
       <c r="AO15" s="3">
-        <f t="shared" si="7"/>
-        <v>3538.0705893437798</v>
+        <f t="shared" si="8"/>
+        <v>3550.3469648035543</v>
       </c>
     </row>
     <row r="16" spans="2:41" x14ac:dyDescent="0.3">
@@ -2274,8 +2296,7 @@
         <v>480</v>
       </c>
       <c r="U16" s="9">
-        <f>Q16*0.95</f>
-        <v>459.79999999999995</v>
+        <v>471</v>
       </c>
       <c r="V16" s="9">
         <f>R16*0.98</f>
@@ -2302,47 +2323,47 @@
       </c>
       <c r="AE16" s="3">
         <f>SUM(S16:V16)</f>
-        <v>1928.8999999999999</v>
+        <v>1940.1</v>
       </c>
       <c r="AF16" s="3">
-        <f t="shared" ref="AF16:AO16" si="8">AE16*1.01</f>
-        <v>1948.1889999999999</v>
+        <f t="shared" ref="AF16:AO16" si="9">AE16*1.01</f>
+        <v>1959.501</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" si="8"/>
-        <v>1967.6708899999999</v>
+        <f t="shared" si="9"/>
+        <v>1979.09601</v>
       </c>
       <c r="AH16" s="3">
-        <f t="shared" si="8"/>
-        <v>1987.3475988999999</v>
+        <f t="shared" si="9"/>
+        <v>1998.8869701000001</v>
       </c>
       <c r="AI16" s="3">
-        <f t="shared" si="8"/>
-        <v>2007.221074889</v>
+        <f t="shared" si="9"/>
+        <v>2018.8758398010002</v>
       </c>
       <c r="AJ16" s="3">
-        <f t="shared" si="8"/>
-        <v>2027.29328563789</v>
+        <f t="shared" si="9"/>
+        <v>2039.0645981990103</v>
       </c>
       <c r="AK16" s="3">
-        <f t="shared" si="8"/>
-        <v>2047.5662184942689</v>
+        <f t="shared" si="9"/>
+        <v>2059.4552441810006</v>
       </c>
       <c r="AL16" s="3">
-        <f t="shared" si="8"/>
-        <v>2068.0418806792118</v>
+        <f t="shared" si="9"/>
+        <v>2080.0497966228104</v>
       </c>
       <c r="AM16" s="3">
-        <f t="shared" si="8"/>
-        <v>2088.722299486004</v>
+        <f t="shared" si="9"/>
+        <v>2100.8502945890386</v>
       </c>
       <c r="AN16" s="3">
-        <f t="shared" si="8"/>
-        <v>2109.6095224808641</v>
+        <f t="shared" si="9"/>
+        <v>2121.8587975349292</v>
       </c>
       <c r="AO16" s="3">
-        <f t="shared" si="8"/>
-        <v>2130.7056177056729</v>
+        <f t="shared" si="9"/>
+        <v>2143.0773855102784</v>
       </c>
     </row>
     <row r="17" spans="2:41" x14ac:dyDescent="0.3">
@@ -2401,8 +2422,7 @@
         <v>-43</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="9">Q17*1.35</f>
-        <v>5.4</v>
+        <v>-13</v>
       </c>
       <c r="V17" s="9">
         <f>R17*1.5</f>
@@ -2425,47 +2445,47 @@
       </c>
       <c r="AE17" s="3">
         <f>SUM(S17:V17)</f>
-        <v>73.400000000000006</v>
+        <v>55</v>
       </c>
       <c r="AF17" s="3">
         <f>AE17*1.4</f>
-        <v>102.76</v>
+        <v>77</v>
       </c>
       <c r="AG17" s="3">
         <f t="shared" ref="AG17" si="10">AF17*1.3</f>
-        <v>133.58800000000002</v>
+        <v>100.10000000000001</v>
       </c>
       <c r="AH17" s="3">
         <f>AG17*1.2</f>
-        <v>160.30560000000003</v>
+        <v>120.12</v>
       </c>
       <c r="AI17" s="3">
         <f>AH17*1.1</f>
-        <v>176.33616000000004</v>
+        <v>132.13200000000001</v>
       </c>
       <c r="AJ17" s="3">
         <f>AI17*1.05</f>
-        <v>185.15296800000004</v>
+        <v>138.73860000000002</v>
       </c>
       <c r="AK17" s="3">
         <f t="shared" ref="AK17:AO17" si="11">AJ17*1.05</f>
-        <v>194.41061640000007</v>
+        <v>145.67553000000004</v>
       </c>
       <c r="AL17" s="3">
         <f t="shared" si="11"/>
-        <v>204.13114722000009</v>
+        <v>152.95930650000005</v>
       </c>
       <c r="AM17" s="3">
         <f t="shared" si="11"/>
-        <v>214.33770458100011</v>
+        <v>160.60727182500005</v>
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="11"/>
-        <v>225.05458981005012</v>
+        <v>168.63763541625008</v>
       </c>
       <c r="AO17" s="3">
         <f t="shared" si="11"/>
-        <v>236.30731930055262</v>
+        <v>177.06951718706259</v>
       </c>
     </row>
     <row r="18" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2533,8 +2553,8 @@
         <v>2431</v>
       </c>
       <c r="U18" s="6">
-        <f t="shared" si="12"/>
-        <v>3148.2000000000003</v>
+        <f>SUM(U13:U17)</f>
+        <v>2779</v>
       </c>
       <c r="V18" s="6">
         <f t="shared" si="12"/>
@@ -2561,47 +2581,47 @@
       </c>
       <c r="AE18" s="6">
         <f t="shared" si="13"/>
-        <v>12231.94</v>
+        <v>11862.74</v>
       </c>
       <c r="AF18" s="6">
         <f t="shared" ref="AF18:AO18" si="14">SUM(AF13:AF17)</f>
-        <v>14464.0298</v>
+        <v>14011.873800000001</v>
       </c>
       <c r="AG18" s="6">
         <f t="shared" si="14"/>
-        <v>15745.401599999999</v>
+        <v>15246.44224</v>
       </c>
       <c r="AH18" s="6">
         <f t="shared" si="14"/>
-        <v>16551.637628500001</v>
+        <v>16022.519471700001</v>
       </c>
       <c r="AI18" s="6">
         <f t="shared" si="14"/>
-        <v>17075.558097929003</v>
+        <v>16527.716567721003</v>
       </c>
       <c r="AJ18" s="6">
         <f t="shared" si="14"/>
-        <v>17460.97887951829</v>
+        <v>16900.941494513012</v>
       </c>
       <c r="AK18" s="6">
         <f t="shared" si="14"/>
-        <v>17825.999820993671</v>
+        <v>17253.357441215794</v>
       </c>
       <c r="AL18" s="6">
         <f t="shared" si="14"/>
-        <v>18199.311772653036</v>
+        <v>17613.744676436647</v>
       </c>
       <c r="AM18" s="6">
         <f t="shared" si="14"/>
-        <v>18581.119881616312</v>
+        <v>17982.298555320653</v>
       </c>
       <c r="AN18" s="6">
         <f t="shared" si="14"/>
-        <v>18971.634896028627</v>
+        <v>18359.219666886216</v>
       </c>
       <c r="AO18" s="6">
         <f t="shared" si="14"/>
-        <v>19371.073336315232</v>
+        <v>18744.71398931888</v>
       </c>
     </row>
     <row r="19" spans="2:41" x14ac:dyDescent="0.3">
@@ -2660,7 +2680,7 @@
         <v>-353</v>
       </c>
       <c r="U19" s="3">
-        <v>0</v>
+        <v>-170</v>
       </c>
       <c r="V19" s="3">
         <v>0</v>
@@ -2777,7 +2797,9 @@
       <c r="T20" s="3">
         <v>1485</v>
       </c>
-      <c r="U20" s="3"/>
+      <c r="U20" s="3">
+        <v>1539</v>
+      </c>
       <c r="V20" s="3"/>
       <c r="Z20" s="3">
         <v>2792</v>
@@ -2796,44 +2818,44 @@
       </c>
       <c r="AE20" s="3"/>
       <c r="AF20" s="3">
-        <f>AF18*0.5</f>
-        <v>7232.0149000000001</v>
+        <f>AF18*0.45</f>
+        <v>6305.3432100000009</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" ref="AG20:AO20" si="16">AG18*0.5</f>
-        <v>7872.7007999999996</v>
+        <f t="shared" ref="AG20:AO20" si="16">AG18*0.45</f>
+        <v>6860.8990080000003</v>
       </c>
       <c r="AH20" s="3">
         <f t="shared" si="16"/>
-        <v>8275.8188142500003</v>
+        <v>7210.1337622650008</v>
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="16"/>
-        <v>8537.7790489645013</v>
+        <v>7437.4724554744516</v>
       </c>
       <c r="AJ20" s="3">
         <f t="shared" si="16"/>
-        <v>8730.4894397591452</v>
+        <v>7605.4236725308556</v>
       </c>
       <c r="AK20" s="3">
         <f t="shared" si="16"/>
-        <v>8912.9999104968356</v>
+        <v>7764.0108485471073</v>
       </c>
       <c r="AL20" s="3">
         <f t="shared" si="16"/>
-        <v>9099.6558863265182</v>
+        <v>7926.1851043964916</v>
       </c>
       <c r="AM20" s="3">
         <f t="shared" si="16"/>
-        <v>9290.5599408081562</v>
+        <v>8092.0343498942939</v>
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="16"/>
-        <v>9485.8174480143134</v>
+        <v>8261.648850098798</v>
       </c>
       <c r="AO20" s="3">
         <f t="shared" si="16"/>
-        <v>9685.5366681576161</v>
+        <v>8435.1212951934958</v>
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
@@ -2891,7 +2913,9 @@
       <c r="T21" s="3">
         <v>704</v>
       </c>
-      <c r="U21" s="3"/>
+      <c r="U21" s="3">
+        <v>692</v>
+      </c>
       <c r="V21" s="3"/>
       <c r="Z21" s="3">
         <v>1537</v>
@@ -2909,44 +2933,44 @@
         <v>2373</v>
       </c>
       <c r="AF21" s="3">
-        <f>AF18*0.25</f>
-        <v>3616.0074500000001</v>
+        <f>AF18*0.28</f>
+        <v>3923.3246640000007</v>
       </c>
       <c r="AG21" s="3">
-        <f t="shared" ref="AG21:AO21" si="17">AG18*0.25</f>
-        <v>3936.3503999999998</v>
+        <f t="shared" ref="AG21:AO21" si="17">AG18*0.28</f>
+        <v>4269.0038272000002</v>
       </c>
       <c r="AH21" s="3">
         <f t="shared" si="17"/>
-        <v>4137.9094071250001</v>
+        <v>4486.3054520760006</v>
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="17"/>
-        <v>4268.8895244822506</v>
+        <v>4627.7606389618813</v>
       </c>
       <c r="AJ21" s="3">
         <f t="shared" si="17"/>
-        <v>4365.2447198795726</v>
+        <v>4732.263618463644</v>
       </c>
       <c r="AK21" s="3">
         <f t="shared" si="17"/>
-        <v>4456.4999552484178</v>
+        <v>4830.9400835404231</v>
       </c>
       <c r="AL21" s="3">
         <f t="shared" si="17"/>
-        <v>4549.8279431632591</v>
+        <v>4931.8485094022617</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" si="17"/>
-        <v>4645.2799704040781</v>
+        <v>5035.043595489783</v>
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="17"/>
-        <v>4742.9087240071567</v>
+        <v>5140.581506728141</v>
       </c>
       <c r="AO21" s="3">
         <f t="shared" si="17"/>
-        <v>4842.768334078808</v>
+        <v>5248.5199170092865</v>
       </c>
     </row>
     <row r="22" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3010,7 +3034,7 @@
         <v>2341</v>
       </c>
       <c r="S22" s="6">
-        <f t="shared" ref="S22:T22" si="20">SUM(S19:S21)</f>
+        <f t="shared" ref="S22:U22" si="20">SUM(S19:S21)</f>
         <v>1763</v>
       </c>
       <c r="T22" s="6">
@@ -3018,11 +3042,11 @@
         <v>1836</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" ref="U22:V22" si="21">U18-U23</f>
-        <v>2329.6680000000001</v>
+        <f t="shared" si="20"/>
+        <v>2061</v>
       </c>
       <c r="V22" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="V22" si="21">V18-V23</f>
         <v>2869.5083999999997</v>
       </c>
       <c r="Z22" s="6">
@@ -3045,49 +3069,49 @@
         <f>SUM(AD19:AD21)</f>
         <v>7065</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="6">
         <f>SUM(S22:V22)</f>
-        <v>8798.1764000000003</v>
+        <v>8529.5083999999988</v>
       </c>
       <c r="AF22" s="6">
         <f t="shared" ref="AF22:AO22" si="22">SUM(AF19:AF21)</f>
-        <v>10848.022349999999</v>
+        <v>10228.667874000002</v>
       </c>
       <c r="AG22" s="6">
         <f t="shared" si="22"/>
-        <v>11809.0512</v>
+        <v>11129.9028352</v>
       </c>
       <c r="AH22" s="6">
         <f t="shared" si="22"/>
-        <v>12413.728221375</v>
+        <v>11696.439214341</v>
       </c>
       <c r="AI22" s="6">
         <f t="shared" si="22"/>
-        <v>12806.668573446752</v>
+        <v>12065.233094436333</v>
       </c>
       <c r="AJ22" s="6">
         <f t="shared" si="22"/>
-        <v>13095.734159638718</v>
+        <v>12337.6872909945</v>
       </c>
       <c r="AK22" s="6">
         <f t="shared" si="22"/>
-        <v>13369.499865745252</v>
+        <v>12594.95093208753</v>
       </c>
       <c r="AL22" s="6">
         <f t="shared" si="22"/>
-        <v>13649.483829489778</v>
+        <v>12858.033613798754</v>
       </c>
       <c r="AM22" s="6">
         <f t="shared" si="22"/>
-        <v>13935.839911212235</v>
+        <v>13127.077945384077</v>
       </c>
       <c r="AN22" s="6">
         <f t="shared" si="22"/>
-        <v>14228.72617202147</v>
+        <v>13402.230356826938</v>
       </c>
       <c r="AO22" s="6">
         <f t="shared" si="22"/>
-        <v>14528.305002236424</v>
+        <v>13683.641212202783</v>
       </c>
     </row>
     <row r="23" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3151,7 +3175,7 @@
         <v>1140</v>
       </c>
       <c r="S23" s="6">
-        <f t="shared" ref="S23:T23" si="25">S18-S22</f>
+        <f t="shared" ref="S23:U23" si="25">S18-S22</f>
         <v>542</v>
       </c>
       <c r="T23" s="6">
@@ -3159,8 +3183,8 @@
         <v>595</v>
       </c>
       <c r="U23" s="6">
-        <f>U18*0.26</f>
-        <v>818.53200000000015</v>
+        <f t="shared" si="25"/>
+        <v>718</v>
       </c>
       <c r="V23" s="6">
         <f>V18*0.34</f>
@@ -3188,47 +3212,47 @@
       </c>
       <c r="AE23" s="6">
         <f t="shared" ref="AE23:AO23" si="26">AE18-AE22</f>
-        <v>3433.7636000000002</v>
+        <v>3333.231600000001</v>
       </c>
       <c r="AF23" s="6">
         <f t="shared" si="26"/>
-        <v>3616.007450000001</v>
+        <v>3783.2059259999987</v>
       </c>
       <c r="AG23" s="6">
         <f t="shared" si="26"/>
-        <v>3936.3503999999994</v>
+        <v>4116.5394047999998</v>
       </c>
       <c r="AH23" s="6">
         <f t="shared" si="26"/>
-        <v>4137.9094071250001</v>
+        <v>4326.0802573590008</v>
       </c>
       <c r="AI23" s="6">
         <f t="shared" si="26"/>
-        <v>4268.8895244822506</v>
+        <v>4462.4834732846703</v>
       </c>
       <c r="AJ23" s="6">
         <f t="shared" si="26"/>
-        <v>4365.2447198795726</v>
+        <v>4563.2542035185124</v>
       </c>
       <c r="AK23" s="6">
         <f t="shared" si="26"/>
-        <v>4456.4999552484187</v>
+        <v>4658.4065091282646</v>
       </c>
       <c r="AL23" s="6">
         <f t="shared" si="26"/>
-        <v>4549.8279431632582</v>
+        <v>4755.7110626378926</v>
       </c>
       <c r="AM23" s="6">
         <f t="shared" si="26"/>
-        <v>4645.2799704040772</v>
+        <v>4855.2206099365758</v>
       </c>
       <c r="AN23" s="6">
         <f t="shared" si="26"/>
-        <v>4742.9087240071567</v>
+        <v>4956.9893100592781</v>
       </c>
       <c r="AO23" s="6">
         <f t="shared" si="26"/>
-        <v>4842.768334078808</v>
+        <v>5061.0727771160964</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
@@ -3287,7 +3311,7 @@
         <v>127</v>
       </c>
       <c r="U24" s="3">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="V24" s="3">
         <v>130</v>
@@ -3375,11 +3399,10 @@
         <v>-51</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" ref="U25:V25" si="27">Q25*1.3</f>
-        <v>-66.3</v>
+        <v>-43</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="V25" si="27">R25*1.3</f>
         <v>-124.80000000000001</v>
       </c>
       <c r="Z25" s="3">
@@ -3465,8 +3488,7 @@
         <v>287</v>
       </c>
       <c r="U26" s="3">
-        <f>Q26*1.15</f>
-        <v>284.04999999999995</v>
+        <v>321</v>
       </c>
       <c r="V26" s="3">
         <f>R26*1.1</f>
@@ -3569,7 +3591,7 @@
       </c>
       <c r="U27" s="3">
         <f t="shared" si="30"/>
-        <v>312.74999999999994</v>
+        <v>395</v>
       </c>
       <c r="V27" s="3">
         <f t="shared" si="30"/>
@@ -3597,47 +3619,47 @@
       </c>
       <c r="AE27" s="3">
         <f>SUM(S27:V27)</f>
-        <v>1448.75</v>
+        <v>1531</v>
       </c>
       <c r="AF27" s="3">
         <f>(AE27*1.05)</f>
-        <v>1521.1875</v>
+        <v>1607.55</v>
       </c>
       <c r="AG27" s="3">
         <f>AF27*1.04</f>
-        <v>1582.0350000000001</v>
+        <v>1671.8520000000001</v>
       </c>
       <c r="AH27" s="3">
         <f>AG27*1.03</f>
-        <v>1629.4960500000002</v>
+        <v>1722.0075600000002</v>
       </c>
       <c r="AI27" s="3">
         <f>AH27*1.02</f>
-        <v>1662.0859710000002</v>
+        <v>1756.4477112000002</v>
       </c>
       <c r="AJ27" s="3">
         <f t="shared" ref="AJ27:AO27" si="31">AI27*1.02</f>
-        <v>1695.3276904200002</v>
+        <v>1791.5766654240001</v>
       </c>
       <c r="AK27" s="3">
         <f t="shared" si="31"/>
-        <v>1729.2342442284003</v>
+        <v>1827.4081987324801</v>
       </c>
       <c r="AL27" s="3">
         <f t="shared" si="31"/>
-        <v>1763.8189291129684</v>
+        <v>1863.9563627071298</v>
       </c>
       <c r="AM27" s="3">
         <f t="shared" si="31"/>
-        <v>1799.0953076952278</v>
+        <v>1901.2354899612724</v>
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="31"/>
-        <v>1835.0772138491325</v>
+        <v>1939.2601997604979</v>
       </c>
       <c r="AO27" s="3">
         <f t="shared" si="31"/>
-        <v>1871.7787581261152</v>
+        <v>1978.0454037557079</v>
       </c>
     </row>
     <row r="28" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3710,7 +3732,7 @@
       </c>
       <c r="U28" s="6">
         <f t="shared" si="34"/>
-        <v>505.78200000000021</v>
+        <v>323</v>
       </c>
       <c r="V28" s="6">
         <f t="shared" si="34"/>
@@ -3738,47 +3760,47 @@
       </c>
       <c r="AE28" s="6">
         <f t="shared" si="35"/>
-        <v>1985.0136000000002</v>
+        <v>1802.231600000001</v>
       </c>
       <c r="AF28" s="6">
         <f t="shared" si="35"/>
-        <v>2094.819950000001</v>
+        <v>2175.6559259999985</v>
       </c>
       <c r="AG28" s="6">
         <f t="shared" si="35"/>
-        <v>2354.3153999999995</v>
+        <v>2444.6874048</v>
       </c>
       <c r="AH28" s="6">
         <f t="shared" si="35"/>
-        <v>2508.4133571249999</v>
+        <v>2604.0726973590008</v>
       </c>
       <c r="AI28" s="6">
         <f t="shared" si="35"/>
-        <v>2606.8035534822502</v>
+        <v>2706.0357620846698</v>
       </c>
       <c r="AJ28" s="6">
         <f t="shared" si="35"/>
-        <v>2669.9170294595724</v>
+        <v>2771.6775380945123</v>
       </c>
       <c r="AK28" s="6">
         <f t="shared" si="35"/>
-        <v>2727.2657110200184</v>
+        <v>2830.9983103957848</v>
       </c>
       <c r="AL28" s="6">
         <f t="shared" si="35"/>
-        <v>2786.0090140502898</v>
+        <v>2891.7546999307629</v>
       </c>
       <c r="AM28" s="6">
         <f t="shared" si="35"/>
-        <v>2846.1846627088494</v>
+        <v>2953.9851199753034</v>
       </c>
       <c r="AN28" s="6">
         <f t="shared" si="35"/>
-        <v>2907.8315101580242</v>
+        <v>3017.7291102987801</v>
       </c>
       <c r="AO28" s="6">
         <f t="shared" si="35"/>
-        <v>2970.9895759526926</v>
+        <v>3083.0273733603885</v>
       </c>
     </row>
     <row r="29" spans="2:41" x14ac:dyDescent="0.3">
@@ -3836,7 +3858,9 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3"/>
+      <c r="U29" s="3">
+        <v>4</v>
+      </c>
       <c r="V29" s="3"/>
       <c r="Z29" s="3">
         <v>-13</v>
@@ -3920,7 +3944,9 @@
       <c r="T30" s="3">
         <v>-7</v>
       </c>
-      <c r="U30" s="3"/>
+      <c r="U30" s="3">
+        <v>4</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="Z30" s="3">
         <v>24</v>
@@ -4004,7 +4030,9 @@
       <c r="T31" s="3">
         <v>-4</v>
       </c>
-      <c r="U31" s="3"/>
+      <c r="U31" s="3">
+        <v>-2</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="Z31" s="3">
         <v>-9</v>
@@ -4088,7 +4116,9 @@
       <c r="T32" s="3">
         <v>20</v>
       </c>
-      <c r="U32" s="3"/>
+      <c r="U32" s="3">
+        <v>27</v>
+      </c>
       <c r="V32" s="3"/>
       <c r="Z32" s="3">
         <v>40</v>
@@ -4170,7 +4200,7 @@
         <v>34</v>
       </c>
       <c r="Q33" s="3">
-        <f t="shared" ref="Q33:T33" si="37">SUM(Q29:Q32)</f>
+        <f t="shared" ref="Q33:U33" si="37">SUM(Q29:Q32)</f>
         <v>43</v>
       </c>
       <c r="R33" s="3">
@@ -4186,11 +4216,11 @@
         <v>9</v>
       </c>
       <c r="U33" s="3">
-        <f t="shared" ref="U33:V33" si="38">Q33*1.05</f>
-        <v>45.15</v>
+        <f t="shared" si="37"/>
+        <v>33</v>
       </c>
       <c r="V33" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="V33" si="38">R33*1.05</f>
         <v>57.75</v>
       </c>
       <c r="Z33" s="3">
@@ -4215,47 +4245,47 @@
       </c>
       <c r="AE33" s="3">
         <f>SUM(S33:V33)</f>
-        <v>144.9</v>
+        <v>132.75</v>
       </c>
       <c r="AF33" s="3">
         <f>AE33*1.03</f>
-        <v>149.24700000000001</v>
+        <v>136.73250000000002</v>
       </c>
       <c r="AG33" s="3">
         <f t="shared" ref="AG33:AO33" si="40">AF33*1.03</f>
-        <v>153.72441000000001</v>
+        <v>140.83447500000003</v>
       </c>
       <c r="AH33" s="3">
         <f t="shared" si="40"/>
-        <v>158.33614230000001</v>
+        <v>145.05950925000002</v>
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="40"/>
-        <v>163.08622656900002</v>
+        <v>149.41129452750002</v>
       </c>
       <c r="AJ33" s="3">
         <f t="shared" si="40"/>
-        <v>167.97881336607003</v>
+        <v>153.89363336332502</v>
       </c>
       <c r="AK33" s="3">
         <f t="shared" si="40"/>
-        <v>173.01817776705212</v>
+        <v>158.51044236422479</v>
       </c>
       <c r="AL33" s="3">
         <f t="shared" si="40"/>
-        <v>178.20872310006368</v>
+        <v>163.26575563515152</v>
       </c>
       <c r="AM33" s="3">
         <f t="shared" si="40"/>
-        <v>183.55498479306559</v>
+        <v>168.16372830420607</v>
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="40"/>
-        <v>189.06163433685757</v>
+        <v>173.20864015333225</v>
       </c>
       <c r="AO33" s="3">
         <f t="shared" si="40"/>
-        <v>194.7334833669633</v>
+        <v>178.40489935793224</v>
       </c>
     </row>
     <row r="34" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4328,7 +4358,7 @@
       </c>
       <c r="U34" s="6">
         <f t="shared" si="42"/>
-        <v>460.63200000000023</v>
+        <v>290</v>
       </c>
       <c r="V34" s="6">
         <f t="shared" si="42"/>
@@ -4356,47 +4386,47 @@
       </c>
       <c r="AE34" s="6">
         <f t="shared" si="43"/>
-        <v>1840.1136000000001</v>
+        <v>1669.481600000001</v>
       </c>
       <c r="AF34" s="6">
         <f t="shared" si="43"/>
-        <v>1945.5729500000009</v>
+        <v>2038.9234259999985</v>
       </c>
       <c r="AG34" s="6">
         <f t="shared" si="43"/>
-        <v>2200.5909899999997</v>
+        <v>2303.8529297999999</v>
       </c>
       <c r="AH34" s="6">
         <f t="shared" si="43"/>
-        <v>2350.0772148249998</v>
+        <v>2459.013188109001</v>
       </c>
       <c r="AI34" s="6">
         <f t="shared" si="43"/>
-        <v>2443.71732691325</v>
+        <v>2556.6244675571697</v>
       </c>
       <c r="AJ34" s="6">
         <f t="shared" si="43"/>
-        <v>2501.9382160935024</v>
+        <v>2617.7839047311872</v>
       </c>
       <c r="AK34" s="6">
         <f t="shared" si="43"/>
-        <v>2554.2475332529662</v>
+        <v>2672.4878680315601</v>
       </c>
       <c r="AL34" s="6">
         <f t="shared" si="43"/>
-        <v>2607.8002909502261</v>
+        <v>2728.4889442956114</v>
       </c>
       <c r="AM34" s="6">
         <f t="shared" si="43"/>
-        <v>2662.6296779157838</v>
+        <v>2785.8213916710974</v>
       </c>
       <c r="AN34" s="6">
         <f t="shared" si="43"/>
-        <v>2718.7698758211668</v>
+        <v>2844.5204701454477</v>
       </c>
       <c r="AO34" s="6">
         <f t="shared" si="43"/>
-        <v>2776.2560925857292</v>
+        <v>2904.6224740024563</v>
       </c>
     </row>
     <row r="35" spans="2:152" x14ac:dyDescent="0.3">
@@ -4455,11 +4485,10 @@
         <v>53</v>
       </c>
       <c r="U35" s="3">
-        <f t="shared" ref="U35:V35" si="44">U34*0.27</f>
-        <v>124.37064000000007</v>
+        <v>86</v>
       </c>
       <c r="V35" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="V35" si="44">V34*0.27</f>
         <v>272.83003200000002</v>
       </c>
       <c r="Z35" s="3">
@@ -4479,47 +4508,47 @@
       </c>
       <c r="AE35" s="3">
         <f>SUM(S35:V35)</f>
-        <v>489.20067200000005</v>
+        <v>450.83003200000002</v>
       </c>
       <c r="AF35" s="3">
         <f>AF34*0.25</f>
-        <v>486.39323750000023</v>
+        <v>509.73085649999962</v>
       </c>
       <c r="AG35" s="3">
         <f t="shared" ref="AG35:AO35" si="45">AG34*0.25</f>
-        <v>550.14774749999992</v>
+        <v>575.96323244999996</v>
       </c>
       <c r="AH35" s="3">
         <f t="shared" si="45"/>
-        <v>587.51930370624996</v>
+        <v>614.75329702725026</v>
       </c>
       <c r="AI35" s="3">
         <f t="shared" si="45"/>
-        <v>610.92933172831249</v>
+        <v>639.15611688929243</v>
       </c>
       <c r="AJ35" s="3">
         <f t="shared" si="45"/>
-        <v>625.48455402337561</v>
+        <v>654.44597618279681</v>
       </c>
       <c r="AK35" s="3">
         <f t="shared" si="45"/>
-        <v>638.56188331324154</v>
+        <v>668.12196700789002</v>
       </c>
       <c r="AL35" s="3">
         <f t="shared" si="45"/>
-        <v>651.95007273755652</v>
+        <v>682.12223607390285</v>
       </c>
       <c r="AM35" s="3">
         <f t="shared" si="45"/>
-        <v>665.65741947894594</v>
+        <v>696.45534791777436</v>
       </c>
       <c r="AN35" s="3">
         <f t="shared" si="45"/>
-        <v>679.6924689552917</v>
+        <v>711.13011753636192</v>
       </c>
       <c r="AO35" s="3">
         <f t="shared" si="45"/>
-        <v>694.06402314643231</v>
+        <v>726.15561850061408</v>
       </c>
     </row>
     <row r="36" spans="2:152" x14ac:dyDescent="0.3">
@@ -4588,11 +4617,11 @@
         <v>27</v>
       </c>
       <c r="U36" s="3">
-        <f t="shared" ref="U36:V36" si="46">U34*0.1</f>
-        <v>46.063200000000023</v>
+        <f>-1+51</f>
+        <v>50</v>
       </c>
       <c r="V36" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="V36" si="46">V34*0.1</f>
         <v>101.04816000000001</v>
       </c>
       <c r="Z36" s="3">
@@ -4617,47 +4646,47 @@
       </c>
       <c r="AE36" s="3">
         <f>SUM(S36:V36)</f>
-        <v>198.11136000000005</v>
+        <v>202.04816</v>
       </c>
       <c r="AF36" s="3">
         <f t="shared" ref="AF36:AO36" si="47">AF34*0.1</f>
-        <v>194.5572950000001</v>
+        <v>203.89234259999986</v>
       </c>
       <c r="AG36" s="3">
         <f t="shared" si="47"/>
-        <v>220.05909899999997</v>
+        <v>230.38529298</v>
       </c>
       <c r="AH36" s="3">
         <f t="shared" si="47"/>
-        <v>235.00772148249999</v>
+        <v>245.90131881090011</v>
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="47"/>
-        <v>244.37173269132501</v>
+        <v>255.66244675571699</v>
       </c>
       <c r="AJ36" s="3">
         <f t="shared" si="47"/>
-        <v>250.19382160935027</v>
+        <v>261.77839047311875</v>
       </c>
       <c r="AK36" s="3">
         <f t="shared" si="47"/>
-        <v>255.42475332529662</v>
+        <v>267.24878680315601</v>
       </c>
       <c r="AL36" s="3">
         <f t="shared" si="47"/>
-        <v>260.7800290950226</v>
+        <v>272.84889442956114</v>
       </c>
       <c r="AM36" s="3">
         <f t="shared" si="47"/>
-        <v>266.26296779157838</v>
+        <v>278.58213916710974</v>
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="47"/>
-        <v>271.87698758211667</v>
+        <v>284.4520470145448</v>
       </c>
       <c r="AO36" s="3">
         <f t="shared" si="47"/>
-        <v>277.62560925857292</v>
+        <v>290.46224740024564</v>
       </c>
     </row>
     <row r="37" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4730,7 +4759,7 @@
       </c>
       <c r="U37" s="6">
         <f t="shared" si="50"/>
-        <v>290.19816000000014</v>
+        <v>154</v>
       </c>
       <c r="V37" s="6">
         <f t="shared" si="50"/>
@@ -4758,491 +4787,491 @@
       </c>
       <c r="AE37" s="6">
         <f t="shared" si="51"/>
-        <v>1152.8015680000001</v>
+        <v>1016.6034080000009</v>
       </c>
       <c r="AF37" s="6">
         <f t="shared" si="51"/>
-        <v>1264.6224175000007</v>
+        <v>1325.300226899999</v>
       </c>
       <c r="AG37" s="6">
         <f t="shared" si="51"/>
-        <v>1430.3841434999997</v>
+        <v>1497.50440437</v>
       </c>
       <c r="AH37" s="6">
         <f t="shared" si="51"/>
-        <v>1527.5501896362498</v>
+        <v>1598.3585722708506</v>
       </c>
       <c r="AI37" s="6">
         <f t="shared" si="51"/>
-        <v>1588.4162624936125</v>
+        <v>1661.8059039121604</v>
       </c>
       <c r="AJ37" s="6">
         <f t="shared" si="51"/>
-        <v>1626.2598404607766</v>
+        <v>1701.5595380752716</v>
       </c>
       <c r="AK37" s="6">
         <f t="shared" si="51"/>
-        <v>1660.2608966144278</v>
+        <v>1737.1171142205142</v>
       </c>
       <c r="AL37" s="6">
         <f t="shared" si="51"/>
-        <v>1695.0701891176468</v>
+        <v>1773.5178137921473</v>
       </c>
       <c r="AM37" s="6">
         <f t="shared" si="51"/>
-        <v>1730.7092906452594</v>
+        <v>1810.7839045862133</v>
       </c>
       <c r="AN37" s="6">
         <f t="shared" si="51"/>
-        <v>1767.2004192837585</v>
+        <v>1848.9383055945409</v>
       </c>
       <c r="AO37" s="6">
         <f t="shared" si="51"/>
-        <v>1804.5664601807241</v>
+        <v>1888.0046081015969</v>
       </c>
       <c r="AP37" s="1">
         <f>AO37*(1+$AS$45)</f>
-        <v>1786.5207955789169</v>
+        <v>1869.1245620205809</v>
       </c>
       <c r="AQ37" s="1">
         <f t="shared" ref="AQ37:DB37" si="52">AP37*(1+$AS$45)</f>
-        <v>1768.6555876231278</v>
+        <v>1850.4333164003751</v>
       </c>
       <c r="AR37" s="1">
         <f t="shared" si="52"/>
-        <v>1750.9690317468965</v>
+        <v>1831.9289832363713</v>
       </c>
       <c r="AS37" s="1">
         <f t="shared" si="52"/>
-        <v>1733.4593414294275</v>
+        <v>1813.6096934040077</v>
       </c>
       <c r="AT37" s="1">
         <f t="shared" si="52"/>
-        <v>1716.1247480151333</v>
+        <v>1795.4735964699676</v>
       </c>
       <c r="AU37" s="1">
         <f t="shared" si="52"/>
-        <v>1698.9635005349819</v>
+        <v>1777.5188605052679</v>
       </c>
       <c r="AV37" s="1">
         <f t="shared" si="52"/>
-        <v>1681.9738655296321</v>
+        <v>1759.7436719002151</v>
       </c>
       <c r="AW37" s="1">
         <f t="shared" si="52"/>
-        <v>1665.1541268743358</v>
+        <v>1742.1462351812129</v>
       </c>
       <c r="AX37" s="1">
         <f t="shared" si="52"/>
-        <v>1648.5025856055925</v>
+        <v>1724.7247728294008</v>
       </c>
       <c r="AY37" s="1">
         <f t="shared" si="52"/>
-        <v>1632.0175597495365</v>
+        <v>1707.4775251011067</v>
       </c>
       <c r="AZ37" s="1">
         <f t="shared" si="52"/>
-        <v>1615.6973841520412</v>
+        <v>1690.4027498500957</v>
       </c>
       <c r="BA37" s="1">
         <f t="shared" si="52"/>
-        <v>1599.5404103105207</v>
+        <v>1673.4987223515948</v>
       </c>
       <c r="BB37" s="1">
         <f t="shared" si="52"/>
-        <v>1583.5450062074153</v>
+        <v>1656.7637351280789</v>
       </c>
       <c r="BC37" s="1">
         <f t="shared" si="52"/>
-        <v>1567.7095561453411</v>
+        <v>1640.1960977767981</v>
       </c>
       <c r="BD37" s="1">
         <f t="shared" si="52"/>
-        <v>1552.0324605838878</v>
+        <v>1623.7941367990302</v>
       </c>
       <c r="BE37" s="1">
         <f t="shared" si="52"/>
-        <v>1536.5121359780489</v>
+        <v>1607.5561954310399</v>
       </c>
       <c r="BF37" s="1">
         <f t="shared" si="52"/>
-        <v>1521.1470146182685</v>
+        <v>1591.4806334767295</v>
       </c>
       <c r="BG37" s="1">
         <f t="shared" si="52"/>
-        <v>1505.9355444720859</v>
+        <v>1575.5658271419622</v>
       </c>
       <c r="BH37" s="1">
         <f t="shared" si="52"/>
-        <v>1490.8761890273649</v>
+        <v>1559.8101688705426</v>
       </c>
       <c r="BI37" s="1">
         <f t="shared" si="52"/>
-        <v>1475.9674271370914</v>
+        <v>1544.2120671818373</v>
       </c>
       <c r="BJ37" s="1">
         <f t="shared" si="52"/>
-        <v>1461.2077528657205</v>
+        <v>1528.7699465100188</v>
       </c>
       <c r="BK37" s="1">
         <f t="shared" si="52"/>
-        <v>1446.5956753370633</v>
+        <v>1513.4822470449187</v>
       </c>
       <c r="BL37" s="1">
         <f t="shared" si="52"/>
-        <v>1432.1297185836927</v>
+        <v>1498.3474245744694</v>
       </c>
       <c r="BM37" s="1">
         <f t="shared" si="52"/>
-        <v>1417.8084213978557</v>
+        <v>1483.3639503287247</v>
       </c>
       <c r="BN37" s="1">
         <f t="shared" si="52"/>
-        <v>1403.6303371838771</v>
+        <v>1468.5303108254375</v>
       </c>
       <c r="BO37" s="1">
         <f t="shared" si="52"/>
-        <v>1389.5940338120383</v>
+        <v>1453.8450077171831</v>
       </c>
       <c r="BP37" s="1">
         <f t="shared" si="52"/>
-        <v>1375.6980934739179</v>
+        <v>1439.3065576400113</v>
       </c>
       <c r="BQ37" s="1">
         <f t="shared" si="52"/>
-        <v>1361.9411125391787</v>
+        <v>1424.9134920636111</v>
       </c>
       <c r="BR37" s="1">
         <f t="shared" si="52"/>
-        <v>1348.321701413787</v>
+        <v>1410.6643571429749</v>
       </c>
       <c r="BS37" s="1">
         <f t="shared" si="52"/>
-        <v>1334.8384843996491</v>
+        <v>1396.5577135715453</v>
       </c>
       <c r="BT37" s="1">
         <f t="shared" si="52"/>
-        <v>1321.4900995556527</v>
+        <v>1382.5921364358298</v>
       </c>
       <c r="BU37" s="1">
         <f t="shared" si="52"/>
-        <v>1308.2751985600962</v>
+        <v>1368.7662150714716</v>
       </c>
       <c r="BV37" s="1">
         <f t="shared" si="52"/>
-        <v>1295.1924465744953</v>
+        <v>1355.0785529207569</v>
       </c>
       <c r="BW37" s="1">
         <f t="shared" si="52"/>
-        <v>1282.2405221087504</v>
+        <v>1341.5277673915493</v>
       </c>
       <c r="BX37" s="1">
         <f t="shared" si="52"/>
-        <v>1269.4181168876628</v>
+        <v>1328.1124897176339</v>
       </c>
       <c r="BY37" s="1">
         <f t="shared" si="52"/>
-        <v>1256.7239357187862</v>
+        <v>1314.8313648204576</v>
       </c>
       <c r="BZ37" s="1">
         <f t="shared" si="52"/>
-        <v>1244.1566963615983</v>
+        <v>1301.683051172253</v>
       </c>
       <c r="CA37" s="1">
         <f t="shared" si="52"/>
-        <v>1231.7151293979823</v>
+        <v>1288.6662206605306</v>
       </c>
       <c r="CB37" s="1">
         <f t="shared" si="52"/>
-        <v>1219.3979781040025</v>
+        <v>1275.7795584539253</v>
       </c>
       <c r="CC37" s="1">
         <f t="shared" si="52"/>
-        <v>1207.2039983229624</v>
+        <v>1263.0217628693861</v>
       </c>
       <c r="CD37" s="1">
         <f t="shared" si="52"/>
-        <v>1195.1319583397328</v>
+        <v>1250.3915452406923</v>
       </c>
       <c r="CE37" s="1">
         <f t="shared" si="52"/>
-        <v>1183.1806387563354</v>
+        <v>1237.8876297882853</v>
       </c>
       <c r="CF37" s="1">
         <f t="shared" si="52"/>
-        <v>1171.348832368772</v>
+        <v>1225.5087534904023</v>
       </c>
       <c r="CG37" s="1">
         <f t="shared" si="52"/>
-        <v>1159.6353440450844</v>
+        <v>1213.2536659554983</v>
       </c>
       <c r="CH37" s="1">
         <f t="shared" si="52"/>
-        <v>1148.0389906046335</v>
+        <v>1201.1211292959433</v>
       </c>
       <c r="CI37" s="1">
         <f t="shared" si="52"/>
-        <v>1136.558600698587</v>
+        <v>1189.1099180029839</v>
       </c>
       <c r="CJ37" s="1">
         <f t="shared" si="52"/>
-        <v>1125.1930146916011</v>
+        <v>1177.2188188229541</v>
       </c>
       <c r="CK37" s="1">
         <f t="shared" si="52"/>
-        <v>1113.9410845446851</v>
+        <v>1165.4466306347244</v>
       </c>
       <c r="CL37" s="1">
         <f t="shared" si="52"/>
-        <v>1102.8016736992381</v>
+        <v>1153.7921643283771</v>
       </c>
       <c r="CM37" s="1">
         <f t="shared" si="52"/>
-        <v>1091.7736569622457</v>
+        <v>1142.2542426850932</v>
       </c>
       <c r="CN37" s="1">
         <f t="shared" si="52"/>
-        <v>1080.8559203926231</v>
+        <v>1130.8317002582423</v>
       </c>
       <c r="CO37" s="1">
         <f t="shared" si="52"/>
-        <v>1070.0473611886969</v>
+        <v>1119.5233832556598</v>
       </c>
       <c r="CP37" s="1">
         <f t="shared" si="52"/>
-        <v>1059.3468875768099</v>
+        <v>1108.3281494231032</v>
       </c>
       <c r="CQ37" s="1">
         <f t="shared" si="52"/>
-        <v>1048.7534187010417</v>
+        <v>1097.2448679288723</v>
       </c>
       <c r="CR37" s="1">
         <f t="shared" si="52"/>
-        <v>1038.2658845140313</v>
+        <v>1086.2724192495834</v>
       </c>
       <c r="CS37" s="1">
         <f t="shared" si="52"/>
-        <v>1027.8832256688911</v>
+        <v>1075.4096950570877</v>
       </c>
       <c r="CT37" s="1">
         <f t="shared" si="52"/>
-        <v>1017.6043934122022</v>
+        <v>1064.6555981065169</v>
       </c>
       <c r="CU37" s="1">
         <f t="shared" si="52"/>
-        <v>1007.4283494780801</v>
+        <v>1054.0090421254517</v>
       </c>
       <c r="CV37" s="1">
         <f t="shared" si="52"/>
-        <v>997.35406598329928</v>
+        <v>1043.4689517041973</v>
       </c>
       <c r="CW37" s="1">
         <f t="shared" si="52"/>
-        <v>987.38052532346626</v>
+        <v>1033.0342621871553</v>
       </c>
       <c r="CX37" s="1">
         <f t="shared" si="52"/>
-        <v>977.50672007023161</v>
+        <v>1022.7039195652837</v>
       </c>
       <c r="CY37" s="1">
         <f t="shared" si="52"/>
-        <v>967.73165286952928</v>
+        <v>1012.4768803696309</v>
       </c>
       <c r="CZ37" s="1">
         <f t="shared" si="52"/>
-        <v>958.05433634083397</v>
+        <v>1002.3521115659346</v>
       </c>
       <c r="DA37" s="1">
         <f t="shared" si="52"/>
-        <v>948.47379297742566</v>
+        <v>992.32859045027521</v>
       </c>
       <c r="DB37" s="1">
         <f t="shared" si="52"/>
-        <v>938.98905504765139</v>
+        <v>982.40530454577242</v>
       </c>
       <c r="DC37" s="1">
         <f t="shared" ref="DC37:EV37" si="53">DB37*(1+$AS$45)</f>
-        <v>929.59916449717491</v>
+        <v>972.58125150031469</v>
       </c>
       <c r="DD37" s="1">
         <f t="shared" si="53"/>
-        <v>920.30317285220315</v>
+        <v>962.85543898531159</v>
       </c>
       <c r="DE37" s="1">
         <f t="shared" si="53"/>
-        <v>911.10014112368106</v>
+        <v>953.2268845954585</v>
       </c>
       <c r="DF37" s="1">
         <f t="shared" si="53"/>
-        <v>901.98913971244428</v>
+        <v>943.6946157495039</v>
       </c>
       <c r="DG37" s="1">
         <f t="shared" si="53"/>
-        <v>892.96924831531987</v>
+        <v>934.25766959200882</v>
       </c>
       <c r="DH37" s="1">
         <f t="shared" si="53"/>
-        <v>884.03955583216668</v>
+        <v>924.91509289608871</v>
       </c>
       <c r="DI37" s="1">
         <f t="shared" si="53"/>
-        <v>875.199160273845</v>
+        <v>915.66594196712776</v>
       </c>
       <c r="DJ37" s="1">
         <f t="shared" si="53"/>
-        <v>866.44716867110651</v>
+        <v>906.50928254745645</v>
       </c>
       <c r="DK37" s="1">
         <f t="shared" si="53"/>
-        <v>857.78269698439544</v>
+        <v>897.44418972198184</v>
       </c>
       <c r="DL37" s="1">
         <f t="shared" si="53"/>
-        <v>849.20487001455149</v>
+        <v>888.46974782476207</v>
       </c>
       <c r="DM37" s="1">
         <f t="shared" si="53"/>
-        <v>840.71282131440591</v>
+        <v>879.58505034651444</v>
       </c>
       <c r="DN37" s="1">
         <f t="shared" si="53"/>
-        <v>832.3056931012618</v>
+        <v>870.78919984304923</v>
       </c>
       <c r="DO37" s="1">
         <f t="shared" si="53"/>
-        <v>823.98263617024918</v>
+        <v>862.08130784461878</v>
       </c>
       <c r="DP37" s="1">
         <f t="shared" si="53"/>
-        <v>815.74280980854667</v>
+        <v>853.46049476617259</v>
       </c>
       <c r="DQ37" s="1">
         <f t="shared" si="53"/>
-        <v>807.58538171046121</v>
+        <v>844.92588981851088</v>
       </c>
       <c r="DR37" s="1">
         <f t="shared" si="53"/>
-        <v>799.50952789335656</v>
+        <v>836.47663092032576</v>
       </c>
       <c r="DS37" s="1">
         <f t="shared" si="53"/>
-        <v>791.51443261442296</v>
+        <v>828.11186461112254</v>
       </c>
       <c r="DT37" s="1">
         <f t="shared" si="53"/>
-        <v>783.59928828827867</v>
+        <v>819.83074596501126</v>
       </c>
       <c r="DU37" s="1">
         <f t="shared" si="53"/>
-        <v>775.76329540539587</v>
+        <v>811.63243850536116</v>
       </c>
       <c r="DV37" s="1">
         <f t="shared" si="53"/>
-        <v>768.00566245134189</v>
+        <v>803.51611412030752</v>
       </c>
       <c r="DW37" s="1">
         <f t="shared" si="53"/>
-        <v>760.32560582682845</v>
+        <v>795.48095297910447</v>
       </c>
       <c r="DX37" s="1">
         <f t="shared" si="53"/>
-        <v>752.72234976856021</v>
+        <v>787.52614344931339</v>
       </c>
       <c r="DY37" s="1">
         <f t="shared" si="53"/>
-        <v>745.19512627087465</v>
+        <v>779.65088201482024</v>
       </c>
       <c r="DZ37" s="1">
         <f t="shared" si="53"/>
-        <v>737.74317500816585</v>
+        <v>771.85437319467201</v>
       </c>
       <c r="EA37" s="1">
         <f t="shared" si="53"/>
-        <v>730.36574325808419</v>
+        <v>764.13582946272527</v>
       </c>
       <c r="EB37" s="1">
         <f t="shared" si="53"/>
-        <v>723.06208582550335</v>
+        <v>756.49447116809802</v>
       </c>
       <c r="EC37" s="1">
         <f t="shared" si="53"/>
-        <v>715.83146496724828</v>
+        <v>748.92952645641708</v>
       </c>
       <c r="ED37" s="1">
         <f t="shared" si="53"/>
-        <v>708.67315031757585</v>
+        <v>741.44023119185294</v>
       </c>
       <c r="EE37" s="1">
         <f t="shared" si="53"/>
-        <v>701.58641881440008</v>
+        <v>734.02582887993447</v>
       </c>
       <c r="EF37" s="1">
         <f t="shared" si="53"/>
-        <v>694.57055462625613</v>
+        <v>726.68557059113516</v>
       </c>
       <c r="EG37" s="1">
         <f t="shared" si="53"/>
-        <v>687.62484907999351</v>
+        <v>719.41871488522384</v>
       </c>
       <c r="EH37" s="1">
         <f t="shared" si="53"/>
-        <v>680.74860058919353</v>
+        <v>712.22452773637156</v>
       </c>
       <c r="EI37" s="1">
         <f t="shared" si="53"/>
-        <v>673.94111458330156</v>
+        <v>705.10228245900782</v>
       </c>
       <c r="EJ37" s="1">
         <f t="shared" si="53"/>
-        <v>667.2017034374685</v>
+        <v>698.05125963441776</v>
       </c>
       <c r="EK37" s="1">
         <f t="shared" si="53"/>
-        <v>660.52968640309382</v>
+        <v>691.07074703807359</v>
       </c>
       <c r="EL37" s="1">
         <f t="shared" si="53"/>
-        <v>653.92438953906287</v>
+        <v>684.16003956769282</v>
       </c>
       <c r="EM37" s="1">
         <f t="shared" si="53"/>
-        <v>647.38514564367222</v>
+        <v>677.31843917201593</v>
       </c>
       <c r="EN37" s="1">
         <f t="shared" si="53"/>
-        <v>640.91129418723551</v>
+        <v>670.54525478029575</v>
       </c>
       <c r="EO37" s="1">
         <f t="shared" si="53"/>
-        <v>634.5021812453632</v>
+        <v>663.83980223249273</v>
       </c>
       <c r="EP37" s="1">
         <f t="shared" si="53"/>
-        <v>628.15715943290957</v>
+        <v>657.20140421016777</v>
       </c>
       <c r="EQ37" s="1">
         <f t="shared" si="53"/>
-        <v>621.87558783858049</v>
+        <v>650.62939016806604</v>
       </c>
       <c r="ER37" s="1">
         <f t="shared" si="53"/>
-        <v>615.65683196019472</v>
+        <v>644.12309626638535</v>
       </c>
       <c r="ES37" s="1">
         <f t="shared" si="53"/>
-        <v>609.50026364059272</v>
+        <v>637.68186530372145</v>
       </c>
       <c r="ET37" s="1">
         <f t="shared" si="53"/>
-        <v>603.40526100418674</v>
+        <v>631.30504665068418</v>
       </c>
       <c r="EU37" s="1">
         <f t="shared" si="53"/>
-        <v>597.3712083941449</v>
+        <v>624.99199618417731</v>
       </c>
       <c r="EV37" s="1">
         <f t="shared" si="53"/>
-        <v>591.39749631020345</v>
+        <v>618.74207622233553</v>
       </c>
     </row>
     <row r="38" spans="2:152" x14ac:dyDescent="0.3">
@@ -5298,10 +5327,12 @@
         <v>43.84</v>
       </c>
       <c r="U38" s="3">
-        <v>43.84</v>
+        <f>45.03</f>
+        <v>45.03</v>
       </c>
       <c r="V38" s="3">
-        <v>43.84</v>
+        <f>45.03</f>
+        <v>45.03</v>
       </c>
       <c r="Z38" s="3">
         <v>43.43</v>
@@ -5319,37 +5350,48 @@
         <v>43.43</v>
       </c>
       <c r="AE38" s="3">
-        <v>43.84</v>
+        <f t="shared" ref="AE38:AO38" si="54">45.03</f>
+        <v>45.03</v>
       </c>
       <c r="AF38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AG38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AH38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AI38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AJ38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AK38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AL38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AM38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AN38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
       <c r="AO38" s="3">
-        <v>43.84</v>
+        <f t="shared" si="54"/>
+        <v>45.03</v>
       </c>
     </row>
     <row r="39" spans="2:152" x14ac:dyDescent="0.3">
@@ -5365,68 +5407,68 @@
         <v>-0.85194565968224734</v>
       </c>
       <c r="G39" s="5">
-        <f t="shared" ref="G39:P39" si="54">G37/G38</f>
+        <f t="shared" ref="G39:P39" si="55">G37/G38</f>
         <v>1.0591756850103615</v>
       </c>
       <c r="H39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.3124568270780566</v>
       </c>
       <c r="I39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.7499424361040756</v>
       </c>
       <c r="J39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>6.8385908358277687</v>
       </c>
       <c r="K39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.1052268017499425</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.3124568270780566</v>
       </c>
       <c r="M39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.3486069537186278</v>
       </c>
       <c r="N39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>7.529357586921483</v>
       </c>
       <c r="O39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.1512779184895234</v>
       </c>
       <c r="P39" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1.4506101772967994</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" ref="Q39:R39" si="55">Q37/Q38</f>
+        <f t="shared" ref="Q39:R39" si="56">Q37/Q38</f>
         <v>3.1084503799217131</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>10.79898687543173</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" ref="S39:V39" si="56">S37/S38</f>
+        <f t="shared" ref="S39:V39" si="57">S37/S38</f>
         <v>1.8932481751824817</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>3.261861313868613</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="56"/>
-        <v>6.6194835766423381</v>
+        <f t="shared" si="57"/>
+        <v>3.4199422607150787</v>
       </c>
       <c r="V39" s="5">
-        <f t="shared" si="56"/>
-        <v>14.521063138686129</v>
+        <f t="shared" si="57"/>
+        <v>14.13731752165223</v>
       </c>
       <c r="Z39" s="5">
         <f>Z37/Z38</f>
@@ -5445,52 +5487,52 @@
         <v>12.295648169468111</v>
       </c>
       <c r="AD39" s="5">
-        <f t="shared" ref="AD39:AO39" si="57">AD37/AD38</f>
+        <f t="shared" ref="AD39:AO39" si="58">AD37/AD38</f>
         <v>16.509325351139765</v>
       </c>
       <c r="AE39" s="5">
-        <f t="shared" si="57"/>
-        <v>26.295656204379561</v>
+        <f t="shared" si="58"/>
+        <v>22.576136087053094</v>
       </c>
       <c r="AF39" s="5">
-        <f t="shared" si="57"/>
-        <v>28.846314267791985</v>
+        <f t="shared" si="58"/>
+        <v>29.431495156562267</v>
       </c>
       <c r="AG39" s="5">
-        <f t="shared" si="57"/>
-        <v>32.627375536040134</v>
+        <f t="shared" si="58"/>
+        <v>33.255705182544972</v>
       </c>
       <c r="AH39" s="5">
-        <f t="shared" si="57"/>
-        <v>34.843754325644383</v>
+        <f t="shared" si="58"/>
+        <v>35.495415773281159</v>
       </c>
       <c r="AI39" s="5">
-        <f t="shared" si="57"/>
-        <v>36.232122775857945</v>
+        <f t="shared" si="58"/>
+        <v>36.904417142175447</v>
       </c>
       <c r="AJ39" s="5">
-        <f t="shared" si="57"/>
-        <v>37.095343076203839</v>
+        <f t="shared" si="58"/>
+        <v>37.787242684327595</v>
       </c>
       <c r="AK39" s="5">
-        <f t="shared" si="57"/>
-        <v>37.870914612555374</v>
+        <f t="shared" si="58"/>
+        <v>38.576884615156878</v>
       </c>
       <c r="AL39" s="5">
-        <f t="shared" si="57"/>
-        <v>38.664922197026613</v>
+        <f t="shared" si="58"/>
+        <v>39.385250139732342</v>
       </c>
       <c r="AM39" s="5">
-        <f t="shared" si="57"/>
-        <v>39.477857907054272</v>
+        <f t="shared" si="58"/>
+        <v>40.212833768292548</v>
       </c>
       <c r="AN39" s="5">
-        <f t="shared" si="57"/>
-        <v>40.310228542056535</v>
+        <f t="shared" si="58"/>
+        <v>41.060144472452606</v>
       </c>
       <c r="AO39" s="5">
-        <f t="shared" si="57"/>
-        <v>41.16255611726104</v>
+        <f t="shared" si="58"/>
+        <v>41.927706153710787</v>
       </c>
     </row>
     <row r="41" spans="2:152" x14ac:dyDescent="0.3">
@@ -5498,40 +5540,44 @@
         <v>86</v>
       </c>
       <c r="O41" s="8">
-        <f t="shared" ref="O41:Q41" si="58">O10/K10-1</f>
+        <f t="shared" ref="O41:Q41" si="59">O10/K10-1</f>
         <v>0.5372858689422404</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.53766190449719264</v>
       </c>
       <c r="Q41" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.41511822186218428</v>
       </c>
       <c r="R41" s="8">
-        <f t="shared" ref="R41:T42" si="59">R10/N10-1</f>
+        <f t="shared" ref="R41:U42" si="60">R10/N10-1</f>
         <v>0.39818901578923427</v>
       </c>
       <c r="S41" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.34958574979287493</v>
       </c>
       <c r="T41" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.16647988142149606</v>
       </c>
+      <c r="U41" s="8">
+        <f t="shared" si="60"/>
+        <v>0.16905187835420388</v>
+      </c>
       <c r="AC41" s="8">
-        <f>AC10/AB10-1</f>
+        <f t="shared" ref="AC41:AE42" si="61">AC10/AB10-1</f>
         <v>0.45649148386241634</v>
       </c>
       <c r="AD41" s="8">
-        <f>AD10/AC10-1</f>
+        <f t="shared" si="61"/>
         <v>0.39818901578923427</v>
       </c>
       <c r="AE41" s="8">
-        <f>AE10/AD10-1</f>
-        <v>5.0052069773496521E-2</v>
+        <f t="shared" si="61"/>
+        <v>6.3362405623535567E-2</v>
       </c>
     </row>
     <row r="42" spans="2:152" x14ac:dyDescent="0.3">
@@ -5541,11 +5587,11 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8">
-        <f t="shared" ref="N42:O42" si="60">N11/J11-1</f>
+        <f t="shared" ref="N42:O42" si="62">N11/J11-1</f>
         <v>0.44099051633298214</v>
       </c>
       <c r="O42" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.42572887848478391</v>
       </c>
       <c r="P42" s="8">
@@ -5557,28 +5603,32 @@
         <v>0.41263879817112992</v>
       </c>
       <c r="R42" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.43570122747453643</v>
       </c>
       <c r="S42" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.55633504987934423</v>
       </c>
       <c r="T42" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.29862253289473695</v>
       </c>
+      <c r="U42" s="8">
+        <f t="shared" si="60"/>
+        <v>0.22920278965822827</v>
+      </c>
       <c r="AC42" s="8">
-        <f>AC11/AB11-1</f>
+        <f t="shared" si="61"/>
         <v>0.44095288273370459</v>
       </c>
       <c r="AD42" s="8">
-        <f>AD11/AC11-1</f>
+        <f t="shared" si="61"/>
         <v>0.43573872391548485</v>
       </c>
       <c r="AE42" s="8">
-        <f>AE11/AD11-1</f>
-        <v>0.14901860913539378</v>
+        <f t="shared" si="61"/>
+        <v>0.16062430647772552</v>
       </c>
     </row>
     <row r="43" spans="2:152" x14ac:dyDescent="0.3">
@@ -5595,121 +5645,121 @@
         <v>53</v>
       </c>
       <c r="G44" s="8">
-        <f t="shared" ref="G44:G49" si="61">G13/C13-1</f>
+        <f t="shared" ref="G44:G49" si="63">G13/C13-1</f>
         <v>-2.7093596059113323E-2</v>
       </c>
       <c r="H44" s="8">
-        <f t="shared" ref="H44:H49" si="62">H13/D13-1</f>
+        <f t="shared" ref="H44:H49" si="64">H13/D13-1</f>
         <v>-3.2537960954446832E-2</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8">
-        <f t="shared" ref="K44:K49" si="63">K13/G13-1</f>
+        <f t="shared" ref="K44:K49" si="65">K13/G13-1</f>
         <v>0.15696202531645564</v>
       </c>
       <c r="L44" s="8">
-        <f t="shared" ref="L44:L49" si="64">L13/H13-1</f>
+        <f t="shared" ref="L44:L49" si="66">L13/H13-1</f>
         <v>0.22197309417040367</v>
       </c>
       <c r="M44" s="8">
-        <f t="shared" ref="M44:M49" si="65">M13/I13-1</f>
+        <f t="shared" ref="M44:M49" si="67">M13/I13-1</f>
         <v>0.40128755364806867</v>
       </c>
       <c r="N44" s="8">
-        <f t="shared" ref="N44:N49" si="66">N13/J13-1</f>
+        <f t="shared" ref="N44:N49" si="68">N13/J13-1</f>
         <v>-2.3305084745762761E-2</v>
       </c>
       <c r="O44" s="8">
-        <f t="shared" ref="O44" si="67">O13/K13-1</f>
+        <f t="shared" ref="O44" si="69">O13/K13-1</f>
         <v>7.0021881838074451E-2</v>
       </c>
       <c r="P44" s="8">
-        <f t="shared" ref="P44:P45" si="68">P13/L13-1</f>
+        <f t="shared" ref="P44:P45" si="70">P13/L13-1</f>
         <v>0.47706422018348627</v>
       </c>
       <c r="Q44" s="8">
-        <f t="shared" ref="Q44:Q49" si="69">Q13/M13-1</f>
+        <f t="shared" ref="Q44:Q49" si="71">Q13/M13-1</f>
         <v>0.8897396630934149</v>
       </c>
       <c r="R44" s="8">
-        <f t="shared" ref="R44:R49" si="70">R13/N13-1</f>
+        <f t="shared" ref="R44:R49" si="72">R13/N13-1</f>
         <v>0.34598698481561829</v>
       </c>
       <c r="S44" s="8">
-        <f t="shared" ref="S44:S49" si="71">S13/O13-1</f>
+        <f t="shared" ref="S44:S49" si="73">S13/O13-1</f>
         <v>0.93251533742331283</v>
       </c>
       <c r="T44" s="8">
-        <f t="shared" ref="T44:T49" si="72">T13/P13-1</f>
+        <f t="shared" ref="T44:T49" si="74">T13/P13-1</f>
         <v>0.15527950310559002</v>
       </c>
       <c r="U44" s="8">
-        <f t="shared" ref="U44:U49" si="73">U13/Q13-1</f>
-        <v>0.19999999999999996</v>
+        <f t="shared" ref="U44:U49" si="75">U13/Q13-1</f>
+        <v>6.0777957860615794E-2</v>
       </c>
       <c r="V44" s="8">
-        <f t="shared" ref="V44:V49" si="74">V13/R13-1</f>
+        <f t="shared" ref="V44:V49" si="76">V13/R13-1</f>
         <v>0.35000000000000009</v>
       </c>
       <c r="AA44" s="8">
-        <f t="shared" ref="AA44:AO44" si="75">AA13/Z13-1</f>
+        <f t="shared" ref="AA44:AO44" si="77">AA13/Z13-1</f>
         <v>2.5711159737417999E-2</v>
       </c>
       <c r="AB44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.20053333333333323</v>
       </c>
       <c r="AC44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.14482452243447352</v>
       </c>
       <c r="AD44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.46255335661622032</v>
       </c>
       <c r="AE44" s="8">
-        <f t="shared" si="75"/>
-        <v>0.33487662509949612</v>
+        <f t="shared" si="77"/>
+        <v>0.2892942425046432</v>
       </c>
       <c r="AF44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AG44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO44" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5718,121 +5768,121 @@
         <v>54</v>
       </c>
       <c r="G45" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>2.857142857142847E-2</v>
       </c>
       <c r="H45" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.11255411255411252</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-0.19444444444444442</v>
       </c>
       <c r="L45" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-3.5019455252918275E-2</v>
       </c>
       <c r="M45" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.66228070175438591</v>
       </c>
       <c r="N45" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0.55606407322654472</v>
       </c>
       <c r="O45" s="8">
-        <f t="shared" ref="O45" si="76">O14/K14-1</f>
+        <f t="shared" ref="O45" si="78">O14/K14-1</f>
         <v>0.84482758620689657</v>
       </c>
       <c r="P45" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1.560483870967742</v>
       </c>
       <c r="Q45" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0.17941952506596315</v>
       </c>
       <c r="R45" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.66470588235294126</v>
       </c>
       <c r="S45" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.65109034267912769</v>
       </c>
       <c r="T45" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>4.0944881889763751E-2</v>
       </c>
       <c r="U45" s="8">
-        <f t="shared" si="73"/>
-        <v>0.8</v>
+        <f t="shared" si="75"/>
+        <v>0.36017897091722606</v>
       </c>
       <c r="V45" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AA45" s="8">
-        <f t="shared" ref="AA45" si="77">AA14/Z14-1</f>
+        <f t="shared" ref="AA45" si="79">AA14/Z14-1</f>
         <v>1.878354203935606E-2</v>
       </c>
       <c r="AB45" s="8">
-        <f t="shared" ref="AB45:AC45" si="78">AB14/AA14-1</f>
+        <f t="shared" ref="AB45:AC45" si="80">AB14/AA14-1</f>
         <v>-8.779631255487752E-4</v>
       </c>
       <c r="AC45" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0.30140597539543057</v>
       </c>
       <c r="AD45" s="8">
-        <f t="shared" ref="AD45:AO45" si="79">AD14/AC14-1</f>
+        <f t="shared" ref="AD45:AO45" si="81">AD14/AC14-1</f>
         <v>0.71168129642133704</v>
       </c>
       <c r="AE45" s="8">
-        <f t="shared" si="79"/>
-        <v>0.32307692307692304</v>
+        <f t="shared" si="81"/>
+        <v>0.24552268244575925</v>
       </c>
       <c r="AF45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AG45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AH45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO45" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AR45" t="s">
@@ -5847,121 +5897,121 @@
         <v>55</v>
       </c>
       <c r="G46" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-6.3829787234042534E-2</v>
       </c>
       <c r="H46" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>0.17283950617283961</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.4015151515151516</v>
       </c>
       <c r="L46" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.11052631578947358</v>
       </c>
       <c r="M46" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>9.6774193548387011E-2</v>
       </c>
       <c r="N46" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>-3.4642032332563466E-2</v>
       </c>
       <c r="O46" s="8">
-        <f t="shared" ref="O46:P46" si="80">O15/K15-1</f>
+        <f t="shared" ref="O46:P46" si="82">O15/K15-1</f>
         <v>0.22702702702702693</v>
       </c>
       <c r="P46" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>0.2890995260663507</v>
       </c>
       <c r="Q46" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0.39215686274509798</v>
       </c>
       <c r="R46" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.27511961722488043</v>
       </c>
       <c r="S46" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.47577092511013208</v>
       </c>
       <c r="T46" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>0.48161764705882359</v>
       </c>
       <c r="U46" s="8">
-        <f t="shared" si="73"/>
-        <v>0.39999999999999991</v>
+        <f t="shared" si="75"/>
+        <v>0.42253521126760574</v>
       </c>
       <c r="V46" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>0.33000000000000007</v>
       </c>
       <c r="AA46" s="8">
-        <f t="shared" ref="AA46:AC46" si="81">AA15/Z15-1</f>
+        <f t="shared" ref="AA46:AC46" si="83">AA15/Z15-1</f>
         <v>-3.9948453608247392E-2</v>
       </c>
       <c r="AB46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>0.26308724832214758</v>
       </c>
       <c r="AC46" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>8.1827842720510136E-2</v>
       </c>
       <c r="AD46" s="8">
-        <f t="shared" ref="AD46:AO46" si="82">AD15/AC15-1</f>
+        <f t="shared" ref="AD46:AO46" si="84">AD15/AC15-1</f>
         <v>0.29273084479371314</v>
       </c>
       <c r="AE46" s="8">
-        <f t="shared" si="82"/>
-        <v>0.40158814589665637</v>
+        <f t="shared" si="84"/>
+        <v>0.40645136778115498</v>
       </c>
       <c r="AF46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="AG46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AH46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AI46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO46" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR46" t="s">
@@ -5976,121 +6026,121 @@
         <v>56</v>
       </c>
       <c r="G47" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>1.3752455795677854E-2</v>
       </c>
       <c r="H47" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>9.0128755364806912E-2</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>4.8449612403100861E-2</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>-4.7244094488189003E-2</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>-3.8022813688213253E-3</v>
       </c>
       <c r="N47" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>5.9760956175298752E-2</v>
       </c>
       <c r="O47" s="8">
-        <f t="shared" ref="O47:P47" si="83">O16/K16-1</f>
+        <f t="shared" ref="O47:P47" si="85">O16/K16-1</f>
         <v>-1.848428835489857E-3</v>
       </c>
       <c r="P47" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>5.9917355371900793E-2</v>
       </c>
       <c r="Q47" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-7.6335877862595436E-2</v>
       </c>
       <c r="R47" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-6.9548872180451138E-2</v>
       </c>
       <c r="S47" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>-6.6666666666666652E-2</v>
       </c>
       <c r="T47" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>-6.4327485380117011E-2</v>
       </c>
       <c r="U47" s="8">
-        <f t="shared" si="73"/>
-        <v>-5.0000000000000044E-2</v>
+        <f t="shared" si="75"/>
+        <v>-2.6859504132231371E-2</v>
       </c>
       <c r="V47" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AA47" s="8">
-        <f t="shared" ref="AA47:AC47" si="84">AA16/Z16-1</f>
+        <f t="shared" ref="AA47:AC47" si="86">AA16/Z16-1</f>
         <v>0.1166666666666667</v>
       </c>
       <c r="AB47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>9.3816631130063888E-2</v>
       </c>
       <c r="AC47" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>1.4132553606237774E-2</v>
       </c>
       <c r="AD47" s="8">
-        <f t="shared" ref="AD47:AO47" si="85">AD16/AC16-1</f>
+        <f t="shared" ref="AD47:AO47" si="87">AD16/AC16-1</f>
         <v>-2.3546371936568944E-2</v>
       </c>
       <c r="AE47" s="8">
-        <f t="shared" si="85"/>
-        <v>-5.0738188976378051E-2</v>
+        <f t="shared" si="87"/>
+        <v>-4.522637795275597E-2</v>
       </c>
       <c r="AF47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO47" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR47" t="s">
@@ -6098,7 +6148,7 @@
       </c>
       <c r="AS47" s="3">
         <f>NPV(AS46,AE37:EV37)</f>
-        <v>22056.291446968597</v>
+        <v>22902.047088771727</v>
       </c>
     </row>
     <row r="48" spans="2:152" x14ac:dyDescent="0.3">
@@ -6106,121 +6156,121 @@
         <v>57</v>
       </c>
       <c r="G48" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>2.5</v>
       </c>
       <c r="H48" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>-2.75</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0.28571428571428581</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>-1.2222222222222223</v>
       </c>
       <c r="N48" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="O48" s="8">
-        <f t="shared" ref="O48:P48" si="86">O17/K17-1</f>
+        <f t="shared" ref="O48:P48" si="88">O17/K17-1</f>
         <v>-0.16666666666666663</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="Q48" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>-3</v>
       </c>
       <c r="R48" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>15</v>
       </c>
       <c r="S48" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>-2.8</v>
       </c>
       <c r="T48" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>-5.3</v>
       </c>
       <c r="U48" s="8">
-        <f t="shared" si="73"/>
-        <v>0.35000000000000009</v>
+        <f t="shared" si="75"/>
+        <v>-4.25</v>
       </c>
       <c r="V48" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>0.5</v>
       </c>
       <c r="AA48" s="8">
-        <f t="shared" ref="AA48:AC48" si="87">AA17/Z17-1</f>
+        <f t="shared" ref="AA48:AC48" si="89">AA17/Z17-1</f>
         <v>7</v>
       </c>
       <c r="AB48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0.16666666666666674</v>
       </c>
       <c r="AC48" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>-0.3571428571428571</v>
       </c>
       <c r="AD48" s="8">
-        <f t="shared" ref="AD48:AO48" si="88">AD17/AC17-1</f>
+        <f t="shared" ref="AD48:AO48" si="90">AD17/AC17-1</f>
         <v>4.5</v>
       </c>
       <c r="AE48" s="8">
-        <f t="shared" si="88"/>
-        <v>-0.25858585858585847</v>
+        <f t="shared" si="90"/>
+        <v>-0.44444444444444442</v>
       </c>
       <c r="AF48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="AG48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AH48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AI48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AJ48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO48" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AR48" t="s">
@@ -6228,7 +6278,7 @@
       </c>
       <c r="AS48" s="3">
         <f>Main!D8</f>
-        <v>-293</v>
+        <v>-1553</v>
       </c>
     </row>
     <row r="49" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6236,29 +6286,29 @@
         <v>37</v>
       </c>
       <c r="G49" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-1.577287066246047E-3</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>6.990881458966558E-2</v>
       </c>
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>7.6619273301737678E-2</v>
       </c>
       <c r="L49" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>6.3210227272727293E-2</v>
       </c>
       <c r="M49" s="7">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>0.24240282685512371</v>
       </c>
       <c r="N49" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0.1016803102111159</v>
       </c>
       <c r="O49" s="7">
@@ -6270,27 +6320,27 @@
         <v>0.49298597194388782</v>
       </c>
       <c r="Q49" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>0.39533560864618877</v>
       </c>
       <c r="R49" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>0.36136096988658584</v>
       </c>
       <c r="S49" s="7">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0.45701643489254118</v>
       </c>
       <c r="T49" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>8.7695749440715787E-2</v>
       </c>
       <c r="U49" s="7">
-        <f t="shared" si="73"/>
-        <v>0.28340807174887894</v>
+        <f t="shared" si="75"/>
+        <v>0.13289849164288636</v>
       </c>
       <c r="V49" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>0.24899166906061465</v>
       </c>
       <c r="Z49" s="7"/>
@@ -6299,67 +6349,67 @@
         <v>4.6993524514338469E-2</v>
       </c>
       <c r="AB49" s="7">
-        <f t="shared" ref="AB49:AO49" si="89">AB18/AA18-1</f>
+        <f t="shared" ref="AB49:AO49" si="91">AB18/AA18-1</f>
         <v>0.1327089591800672</v>
       </c>
       <c r="AC49" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>0.11934477379095165</v>
       </c>
       <c r="AD49" s="7">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>0.35902439024390254</v>
       </c>
       <c r="AE49" s="7">
-        <f t="shared" si="89"/>
-        <v>0.25442928930366127</v>
+        <f t="shared" si="91"/>
+        <v>0.21656650599938465</v>
       </c>
       <c r="AF49" s="7">
-        <f t="shared" si="89"/>
-        <v>0.18248044055153967</v>
+        <f t="shared" si="91"/>
+        <v>0.18116672876586692</v>
       </c>
       <c r="AG49" s="7">
-        <f t="shared" si="89"/>
-        <v>8.8590235067131706E-2</v>
+        <f t="shared" si="91"/>
+        <v>8.8108732466602557E-2</v>
       </c>
       <c r="AH49" s="7">
-        <f t="shared" si="89"/>
-        <v>5.1204538885816664E-2</v>
+        <f t="shared" si="91"/>
+        <v>5.0902185538335809E-2</v>
       </c>
       <c r="AI49" s="7">
-        <f t="shared" si="89"/>
-        <v>3.1653693802894178E-2</v>
+        <f t="shared" si="91"/>
+        <v>3.1530440447478547E-2</v>
       </c>
       <c r="AJ49" s="7">
-        <f t="shared" si="89"/>
-        <v>2.2571489574682468E-2</v>
+        <f t="shared" si="91"/>
+        <v>2.2581759873649077E-2</v>
       </c>
       <c r="AK49" s="7">
-        <f t="shared" si="89"/>
-        <v>2.0904952923547215E-2</v>
+        <f t="shared" si="91"/>
+        <v>2.0851852946606408E-2</v>
       </c>
       <c r="AL49" s="7">
-        <f t="shared" si="89"/>
-        <v>2.0941992337490944E-2</v>
+        <f t="shared" si="91"/>
+        <v>2.0887948125385636E-2</v>
       </c>
       <c r="AM49" s="7">
-        <f t="shared" si="89"/>
-        <v>2.0979260849687487E-2</v>
+        <f t="shared" si="91"/>
+        <v>2.0924220581955533E-2</v>
       </c>
       <c r="AN49" s="7">
-        <f t="shared" si="89"/>
-        <v>2.1016764161705837E-2</v>
+        <f t="shared" si="91"/>
+        <v>2.096067476613217E-2</v>
       </c>
       <c r="AO49" s="7">
-        <f t="shared" si="89"/>
-        <v>2.1054508084077606E-2</v>
+        <f t="shared" si="91"/>
+        <v>2.0997315214217105E-2</v>
       </c>
       <c r="AR49" t="s">
         <v>62</v>
       </c>
       <c r="AS49" s="3">
         <f>AS47+AS48</f>
-        <v>21763.291446968597</v>
+        <v>21349.047088771727</v>
       </c>
     </row>
     <row r="50" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6381,51 +6431,51 @@
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8">
-        <f t="shared" ref="K50:R50" si="90">(K18+K19)/(G18+G19)-1</f>
+        <f t="shared" ref="K50:R50" si="92">(K18+K19)/(G18+G19)-1</f>
         <v>-8.2740213523131656E-2</v>
       </c>
       <c r="L50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>-2.874432677760963E-2</v>
       </c>
       <c r="M50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.24119028974158185</v>
       </c>
       <c r="N50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>1.7758484609313285E-2</v>
       </c>
       <c r="O50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.11542192046556732</v>
       </c>
       <c r="P50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.7398753894080996</v>
       </c>
       <c r="Q50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.62965299684542586</v>
       </c>
       <c r="R50" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>0.40248158200853035</v>
       </c>
       <c r="S50" s="8">
-        <f t="shared" ref="S50" si="91">(S18+S19)/(O18+O19)-1</f>
+        <f t="shared" ref="S50" si="93">(S18+S19)/(O18+O19)-1</f>
         <v>0.78956521739130436</v>
       </c>
       <c r="T50" s="8">
-        <f t="shared" ref="T50" si="92">(T18+T19)/(P18+P19)-1</f>
+        <f t="shared" ref="T50" si="94">(T18+T19)/(P18+P19)-1</f>
         <v>-6.9829901521933802E-2</v>
       </c>
       <c r="U50" s="8">
-        <f t="shared" ref="U50" si="93">(U18+U19)/(Q18+Q19)-1</f>
-        <v>0.21881533101045303</v>
+        <f t="shared" ref="U50" si="95">(U18+U19)/(Q18+Q19)-1</f>
+        <v>1.0065814943863716E-2</v>
       </c>
       <c r="V50" s="8">
-        <f t="shared" ref="V50" si="94">(V18+V19)/(R18+R19)-1</f>
+        <f t="shared" ref="V50" si="96">(V18+V19)/(R18+R19)-1</f>
         <v>0.20202930605474134</v>
       </c>
       <c r="Z50" s="7"/>
@@ -6434,67 +6484,67 @@
         <v>5.3011590347710413E-2</v>
       </c>
       <c r="AB50" s="8">
-        <f t="shared" ref="AB50:AO50" si="95">(AB18+AB19)/(AA18+AA19)-1</f>
+        <f t="shared" ref="AB50:AO50" si="97">(AB18+AB19)/(AA18+AA19)-1</f>
         <v>0.12901479610249011</v>
       </c>
       <c r="AC50" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3.548026210644073E-2</v>
       </c>
       <c r="AD50" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>0.47924062355301733</v>
       </c>
       <c r="AE50" s="8">
-        <f t="shared" si="95"/>
-        <v>0.27628756260434062</v>
+        <f t="shared" si="97"/>
+        <v>0.23776502504173624</v>
       </c>
       <c r="AF50" s="8">
-        <f t="shared" si="95"/>
-        <v>0.18248044055153967</v>
+        <f t="shared" si="97"/>
+        <v>0.18116672876586692</v>
       </c>
       <c r="AG50" s="8">
-        <f t="shared" si="95"/>
-        <v>8.8590235067131706E-2</v>
+        <f t="shared" si="97"/>
+        <v>8.8108732466602557E-2</v>
       </c>
       <c r="AH50" s="8">
-        <f t="shared" si="95"/>
-        <v>5.1204538885816664E-2</v>
+        <f t="shared" si="97"/>
+        <v>5.0902185538335809E-2</v>
       </c>
       <c r="AI50" s="8">
-        <f t="shared" si="95"/>
-        <v>3.1653693802894178E-2</v>
+        <f t="shared" si="97"/>
+        <v>3.1530440447478547E-2</v>
       </c>
       <c r="AJ50" s="8">
-        <f t="shared" si="95"/>
-        <v>2.2571489574682468E-2</v>
+        <f t="shared" si="97"/>
+        <v>2.2581759873649077E-2</v>
       </c>
       <c r="AK50" s="8">
-        <f t="shared" si="95"/>
-        <v>2.0904952923547215E-2</v>
+        <f t="shared" si="97"/>
+        <v>2.0851852946606408E-2</v>
       </c>
       <c r="AL50" s="8">
-        <f t="shared" si="95"/>
-        <v>2.0941992337490944E-2</v>
+        <f t="shared" si="97"/>
+        <v>2.0887948125385636E-2</v>
       </c>
       <c r="AM50" s="8">
-        <f t="shared" si="95"/>
-        <v>2.0979260849687487E-2</v>
+        <f t="shared" si="97"/>
+        <v>2.0924220581955533E-2</v>
       </c>
       <c r="AN50" s="8">
-        <f t="shared" si="95"/>
-        <v>2.1016764161705837E-2</v>
+        <f t="shared" si="97"/>
+        <v>2.096067476613217E-2</v>
       </c>
       <c r="AO50" s="8">
-        <f t="shared" si="95"/>
-        <v>2.1054508084077606E-2</v>
+        <f t="shared" si="97"/>
+        <v>2.0997315214217105E-2</v>
       </c>
       <c r="AR50" t="s">
         <v>63</v>
       </c>
       <c r="AS50" s="2">
         <f>AS49/AO38</f>
-        <v>496.42544358961209</v>
+        <v>474.10719717458863</v>
       </c>
     </row>
     <row r="51" spans="2:45" x14ac:dyDescent="0.3">
@@ -6512,67 +6562,67 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8">
-        <f t="shared" ref="G51:P51" si="96">G23/G18</f>
+        <f t="shared" ref="G51:P51" si="98">G23/G18</f>
         <v>0.2109004739336493</v>
       </c>
       <c r="H51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.22443181818181818</v>
       </c>
       <c r="I51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.22332155477031801</v>
       </c>
       <c r="J51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.27789745799224475</v>
       </c>
       <c r="K51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.22157006603081439</v>
       </c>
       <c r="L51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.22845691382765532</v>
       </c>
       <c r="M51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.24402730375426621</v>
       </c>
       <c r="N51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.31912397340633553</v>
       </c>
       <c r="O51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.24905183312262957</v>
       </c>
       <c r="P51" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>0.25548098434004474</v>
       </c>
       <c r="Q51" s="8">
-        <f t="shared" ref="Q51:R51" si="97">Q23/Q18</f>
+        <f t="shared" ref="Q51:R51" si="99">Q23/Q18</f>
         <v>0.23685283326538931</v>
       </c>
       <c r="R51" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0.3274920999712726</v>
       </c>
       <c r="S51" s="8">
-        <f t="shared" ref="S51:V51" si="98">S23/S18</f>
+        <f t="shared" ref="S51:V51" si="100">S23/S18</f>
         <v>0.23514099783080261</v>
       </c>
       <c r="T51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.24475524475524477</v>
       </c>
       <c r="U51" s="8">
-        <f t="shared" si="98"/>
-        <v>0.26</v>
+        <f t="shared" si="100"/>
+        <v>0.25836631881971933</v>
       </c>
       <c r="V51" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>0.34</v>
       </c>
       <c r="Z51" s="8">
@@ -6584,67 +6634,67 @@
         <v>0.24527301643399893</v>
       </c>
       <c r="AB51" s="8">
-        <f t="shared" ref="AB51:AO51" si="99">AB23/AB18</f>
+        <f t="shared" ref="AB51:AO51" si="101">AB23/AB18</f>
         <v>0.24087363494539782</v>
       </c>
       <c r="AC51" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.26327526132404183</v>
       </c>
       <c r="AD51" s="8">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0.27545892728950877</v>
       </c>
       <c r="AE51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.28072109575423032</v>
+        <f t="shared" si="101"/>
+        <v>0.28098328042256687</v>
       </c>
       <c r="AF51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.25000000000000006</v>
+        <f t="shared" si="101"/>
+        <v>0.26999999999999991</v>
       </c>
       <c r="AG51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.24999999999999997</v>
+        <f t="shared" si="101"/>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AH51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.25</v>
+        <f t="shared" si="101"/>
+        <v>0.27</v>
       </c>
       <c r="AI51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.25</v>
+        <f t="shared" si="101"/>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AJ51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.25</v>
+        <f t="shared" si="101"/>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AK51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.25000000000000006</v>
+        <f t="shared" si="101"/>
+        <v>0.27</v>
       </c>
       <c r="AL51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.24999999999999994</v>
+        <f t="shared" si="101"/>
+        <v>0.26999999999999991</v>
       </c>
       <c r="AM51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.24999999999999994</v>
+        <f t="shared" si="101"/>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AN51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.25</v>
+        <f t="shared" si="101"/>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AO51" s="8">
-        <f t="shared" si="99"/>
-        <v>0.25</v>
+        <f t="shared" si="101"/>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AR51" t="s">
         <v>64</v>
       </c>
       <c r="AS51" s="2">
         <f>Main!D3</f>
-        <v>1764</v>
+        <v>1523.5</v>
       </c>
     </row>
     <row r="52" spans="2:45" x14ac:dyDescent="0.3">
@@ -6656,142 +6706,139 @@
         <v>0.52444794952681384</v>
       </c>
       <c r="D52" s="8">
-        <f>D20/D18</f>
-        <v>0.48252279635258361</v>
+        <f>(D18-D20)/D18</f>
+        <v>0.51747720364741645</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8">
-        <f t="shared" ref="G52:N52" si="100">G20/G18</f>
-        <v>0.54028436018957349</v>
+        <f>(G18-G20)/G18</f>
+        <v>0.45971563981042651</v>
       </c>
       <c r="H52" s="8">
-        <f t="shared" si="100"/>
-        <v>0.50710227272727271</v>
+        <f t="shared" ref="H52:U52" si="102">(H18-H20)/H18</f>
+        <v>0.49289772727272729</v>
       </c>
       <c r="I52" s="8">
-        <f t="shared" si="100"/>
-        <v>0.56325088339222618</v>
+        <f t="shared" si="102"/>
+        <v>0.43674911660777382</v>
       </c>
       <c r="J52" s="8">
-        <f t="shared" si="100"/>
-        <v>0.42567858681602755</v>
+        <f t="shared" si="102"/>
+        <v>0.57432141318397245</v>
       </c>
       <c r="K52" s="8">
-        <f t="shared" si="100"/>
-        <v>0.65517241379310343</v>
+        <f t="shared" si="102"/>
+        <v>0.34482758620689657</v>
       </c>
       <c r="L52" s="8">
-        <f t="shared" si="100"/>
-        <v>0.57515030060120242</v>
+        <f t="shared" si="102"/>
+        <v>0.42484969939879758</v>
       </c>
       <c r="M52" s="8">
-        <f t="shared" si="100"/>
-        <v>0.57281001137656429</v>
+        <f t="shared" si="102"/>
+        <v>0.42718998862343571</v>
       </c>
       <c r="N52" s="8">
-        <f t="shared" si="100"/>
-        <v>0.45913179507235041</v>
+        <f t="shared" si="102"/>
+        <v>0.54086820492764964</v>
       </c>
       <c r="O52" s="8">
-        <f t="shared" ref="O52:P52" si="101">O20/O18</f>
-        <v>0.65676359039190901</v>
+        <f t="shared" si="102"/>
+        <v>0.34323640960809104</v>
       </c>
       <c r="P52" s="8">
-        <f t="shared" si="101"/>
-        <v>0.48635346756152126</v>
+        <f t="shared" si="102"/>
+        <v>0.5136465324384788</v>
       </c>
       <c r="Q52" s="8">
-        <f t="shared" ref="Q52:R52" si="102">Q20/Q18</f>
-        <v>0.47696697920913167</v>
+        <f t="shared" si="102"/>
+        <v>0.52303302079086833</v>
       </c>
       <c r="R52" s="8">
         <f t="shared" si="102"/>
-        <v>0.44900890548692907</v>
+        <v>0.55099109451307093</v>
       </c>
       <c r="S52" s="8">
-        <f t="shared" ref="S52:V52" si="103">S20/S18</f>
-        <v>0.57006507592190891</v>
+        <f t="shared" si="102"/>
+        <v>0.42993492407809109</v>
       </c>
       <c r="T52" s="8">
+        <f t="shared" si="102"/>
+        <v>0.38914027149321267</v>
+      </c>
+      <c r="U52" s="8">
+        <f t="shared" si="102"/>
+        <v>0.44620367038503056</v>
+      </c>
+      <c r="V52" s="8"/>
+      <c r="Z52" s="8">
+        <f t="shared" ref="Z52:AD52" si="103">(Z18-Z20)/Z18</f>
+        <v>0.48344125809435706</v>
+      </c>
+      <c r="AA52" s="8">
         <f t="shared" si="103"/>
-        <v>0.61085972850678738</v>
-      </c>
-      <c r="U52" s="8">
+        <v>0.51493196677858277</v>
+      </c>
+      <c r="AB52" s="8">
         <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="V52" s="8">
+        <v>0.50343213728549141</v>
+      </c>
+      <c r="AC52" s="8">
         <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="Z52" s="8">
-        <f t="shared" ref="Z52:AO52" si="104">Z20/Z18</f>
-        <v>0.51655874190564288</v>
-      </c>
-      <c r="AA52" s="8">
-        <f t="shared" si="104"/>
-        <v>0.48506803322141723</v>
-      </c>
-      <c r="AB52" s="8">
-        <f t="shared" si="104"/>
-        <v>0.49656786271450859</v>
-      </c>
-      <c r="AC52" s="8">
-        <f t="shared" si="104"/>
-        <v>0.5484320557491289</v>
+        <v>0.4515679442508711</v>
       </c>
       <c r="AD52" s="8">
-        <f t="shared" si="104"/>
-        <v>0.49830786585991182</v>
+        <f t="shared" si="103"/>
+        <v>0.50169213414008818</v>
       </c>
       <c r="AE52" s="8"/>
       <c r="AF52" s="8">
-        <f t="shared" si="104"/>
-        <v>0.5</v>
+        <f t="shared" ref="AF52:AO52" si="104">(AF18-AF20)/AF18</f>
+        <v>0.54999999999999993</v>
       </c>
       <c r="AG52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="AH52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="AI52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AJ52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AK52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AL52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="AM52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AN52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="AO52" s="8">
         <f t="shared" si="104"/>
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AR52" s="1" t="s">
         <v>65</v>
       </c>
       <c r="AS52" s="7">
         <f>AS50/AS51-1</f>
-        <v>-0.71857968050475507</v>
+        <v>-0.68880394015452007</v>
       </c>
     </row>
     <row r="53" spans="2:45" x14ac:dyDescent="0.3">
@@ -6803,135 +6850,132 @@
         <v>0.32649842271293378</v>
       </c>
       <c r="D53" s="8">
-        <f>D21/D18</f>
-        <v>0.32142857142857145</v>
+        <f>(D18-D21)/D18</f>
+        <v>0.6785714285714286</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8">
-        <f t="shared" ref="G53:N53" si="105">G21/G18</f>
-        <v>0.3609794628751975</v>
+        <f t="shared" ref="G53:U53" si="105">(G18-G21)/G18</f>
+        <v>0.63902053712480256</v>
       </c>
       <c r="H53" s="8">
         <f t="shared" si="105"/>
-        <v>0.32954545454545453</v>
+        <v>0.67045454545454541</v>
       </c>
       <c r="I53" s="8">
         <f t="shared" si="105"/>
-        <v>0.31095406360424027</v>
+        <v>0.68904593639575973</v>
       </c>
       <c r="J53" s="8">
         <f t="shared" si="105"/>
-        <v>0.20465316673847481</v>
+        <v>0.79534683326152522</v>
       </c>
       <c r="K53" s="8">
         <f t="shared" si="105"/>
-        <v>0.36683785766691124</v>
+        <v>0.63316214233308876</v>
       </c>
       <c r="L53" s="8">
         <f t="shared" si="105"/>
-        <v>0.33867735470941884</v>
+        <v>0.66132264529058116</v>
       </c>
       <c r="M53" s="8">
         <f t="shared" si="105"/>
-        <v>0.28156996587030719</v>
+        <v>0.71843003412969286</v>
       </c>
       <c r="N53" s="8">
         <f t="shared" si="105"/>
-        <v>0.21314039890496675</v>
+        <v>0.78685960109503328</v>
       </c>
       <c r="O53" s="8">
-        <f t="shared" ref="O53:P53" si="106">O21/O18</f>
-        <v>0.36725663716814161</v>
+        <f t="shared" si="105"/>
+        <v>0.63274336283185839</v>
       </c>
       <c r="P53" s="8">
+        <f t="shared" si="105"/>
+        <v>0.74138702460850114</v>
+      </c>
+      <c r="Q53" s="8">
+        <f t="shared" si="105"/>
+        <v>0.76681614349775784</v>
+      </c>
+      <c r="R53" s="8">
+        <f t="shared" si="105"/>
+        <v>0.81557023843723064</v>
+      </c>
+      <c r="S53" s="8">
+        <f t="shared" si="105"/>
+        <v>0.69804772234273316</v>
+      </c>
+      <c r="T53" s="8">
+        <f t="shared" si="105"/>
+        <v>0.71040723981900455</v>
+      </c>
+      <c r="U53" s="8">
+        <f t="shared" si="105"/>
+        <v>0.75098956459157973</v>
+      </c>
+      <c r="V53" s="8"/>
+      <c r="Z53" s="8">
+        <f t="shared" ref="Z53:AD53" si="106">(Z18-Z21)/Z18</f>
+        <v>0.71563367252543941</v>
+      </c>
+      <c r="AA53" s="8">
         <f t="shared" si="106"/>
-        <v>0.25861297539149886</v>
-      </c>
-      <c r="Q53" s="8">
-        <f t="shared" ref="Q53:R53" si="107">Q21/Q18</f>
-        <v>0.23318385650224216</v>
-      </c>
-      <c r="R53" s="8">
-        <f t="shared" si="107"/>
-        <v>0.18442976156276933</v>
-      </c>
-      <c r="S53" s="8">
-        <f t="shared" ref="S53:V53" si="108">S21/S18</f>
-        <v>0.30195227765726679</v>
-      </c>
-      <c r="T53" s="8">
-        <f t="shared" si="108"/>
-        <v>0.2895927601809955</v>
-      </c>
-      <c r="U53" s="8">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="V53" s="8">
-        <f t="shared" si="108"/>
-        <v>0</v>
-      </c>
-      <c r="Z53" s="8">
-        <f t="shared" ref="Z53:AO53" si="109">Z21/Z18</f>
-        <v>0.28436632747456059</v>
-      </c>
-      <c r="AA53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.29033398126877541</v>
+        <v>0.70966601873122459</v>
       </c>
       <c r="AB53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.28642745709828393</v>
+        <f t="shared" si="106"/>
+        <v>0.71357254290171612</v>
       </c>
       <c r="AC53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.28529616724738677</v>
+        <f t="shared" si="106"/>
+        <v>0.71470383275261329</v>
       </c>
       <c r="AD53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.24335965541995694</v>
+        <f t="shared" si="106"/>
+        <v>0.75664034458004303</v>
       </c>
       <c r="AE53" s="8"/>
       <c r="AF53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" ref="AF53:AO53" si="107">(AF18-AF21)/AF18</f>
+        <v>0.72000000000000008</v>
       </c>
       <c r="AG53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72</v>
       </c>
       <c r="AH53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72</v>
       </c>
       <c r="AI53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72</v>
       </c>
       <c r="AJ53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72</v>
       </c>
       <c r="AK53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72</v>
       </c>
       <c r="AL53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72</v>
       </c>
       <c r="AM53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72</v>
       </c>
       <c r="AN53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72</v>
       </c>
       <c r="AO53" s="8">
-        <f t="shared" si="109"/>
-        <v>0.25</v>
+        <f t="shared" si="107"/>
+        <v>0.72000000000000008</v>
       </c>
       <c r="AR53" t="s">
         <v>66</v>
@@ -6949,130 +6993,97 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8">
-        <f t="shared" ref="G54:V54" si="110">G25/C25-1</f>
+        <f t="shared" ref="G54:V54" si="108">G25/C25-1</f>
         <v>0.38095238095238093</v>
       </c>
       <c r="H54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="I54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J54" s="8" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>0.10344827586206895</v>
       </c>
       <c r="L54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>-0.4358974358974359</v>
       </c>
       <c r="M54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>-0.22641509433962259</v>
       </c>
       <c r="N54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>-0.42000000000000004</v>
       </c>
       <c r="O54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>0.3125</v>
       </c>
       <c r="P54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>0.77272727272727271</v>
       </c>
       <c r="Q54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>0.24390243902439024</v>
       </c>
       <c r="R54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>0.65517241379310343</v>
       </c>
       <c r="S54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="T54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>0.30769230769230771</v>
       </c>
       <c r="U54" s="8">
-        <f t="shared" si="110"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="108"/>
+        <v>-0.15686274509803921</v>
       </c>
       <c r="V54" s="8">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8">
-        <f t="shared" ref="AA54:AO54" si="111">AA25/Z25-1</f>
+        <f t="shared" ref="AA54:AD54" si="109">AA25/Z25-1</f>
         <v>0.17543859649122817</v>
       </c>
       <c r="AB54" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.64925373134328357</v>
       </c>
       <c r="AC54" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>-0.30769230769230771</v>
       </c>
       <c r="AD54" s="8">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.49019607843137258</v>
       </c>
-      <c r="AE54" s="8">
-        <f t="shared" si="111"/>
-        <v>-1</v>
-      </c>
-      <c r="AF54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO54" s="8" t="e">
-        <f t="shared" si="111"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AE54" s="8"/>
+      <c r="AF54" s="8"/>
+      <c r="AG54" s="8"/>
+      <c r="AH54" s="8"/>
+      <c r="AI54" s="8"/>
+      <c r="AJ54" s="8"/>
+      <c r="AK54" s="8"/>
+      <c r="AL54" s="8"/>
+      <c r="AM54" s="8"/>
+      <c r="AN54" s="8"/>
+      <c r="AO54" s="8"/>
       <c r="AS54" s="4"/>
     </row>
     <row r="55" spans="2:45" x14ac:dyDescent="0.3">
@@ -7094,51 +7105,51 @@
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8">
-        <f t="shared" ref="K55:P55" si="112">K26/G26-1</f>
+        <f t="shared" ref="K55:P55" si="110">K26/G26-1</f>
         <v>0.18954248366013071</v>
       </c>
       <c r="L55" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>0.10240963855421681</v>
       </c>
       <c r="M55" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>0.12886597938144329</v>
       </c>
       <c r="N55" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>0.19607843137254899</v>
       </c>
       <c r="O55" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>0.25274725274725274</v>
       </c>
       <c r="P55" s="8">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>0.51366120218579225</v>
       </c>
       <c r="Q55" s="8">
-        <f t="shared" ref="Q55:R55" si="113">Q26/M26-1</f>
+        <f t="shared" ref="Q55:R55" si="111">Q26/M26-1</f>
         <v>0.12785388127853881</v>
       </c>
       <c r="R55" s="8">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.20655737704918042</v>
       </c>
       <c r="S55" s="8">
-        <f t="shared" ref="S55" si="114">S26/O26-1</f>
+        <f t="shared" ref="S55" si="112">S26/O26-1</f>
         <v>0.25877192982456143</v>
       </c>
       <c r="T55" s="8">
-        <f t="shared" ref="T55" si="115">T26/P26-1</f>
+        <f t="shared" ref="T55" si="113">T26/P26-1</f>
         <v>3.6101083032491044E-2</v>
       </c>
       <c r="U55" s="8">
-        <f t="shared" ref="U55" si="116">U26/Q26-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="U55" si="114">U26/Q26-1</f>
+        <v>0.2995951417004048</v>
       </c>
       <c r="V55" s="8">
-        <f t="shared" ref="V55" si="117">V26/R26-1</f>
+        <f t="shared" ref="V55" si="115">V26/R26-1</f>
         <v>0.10000000000000009</v>
       </c>
       <c r="Z55" s="8"/>
@@ -7147,61 +7158,28 @@
         <v>2.1806853582554409E-2</v>
       </c>
       <c r="AB55" s="8">
-        <f t="shared" ref="AB55:AO55" si="118">AB26/AA26-1</f>
+        <f t="shared" ref="AB55:AD55" si="116">AB26/AA26-1</f>
         <v>0.1707317073170731</v>
       </c>
       <c r="AC55" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.15755208333333326</v>
       </c>
       <c r="AD55" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.25984251968503935</v>
       </c>
-      <c r="AE55" s="8">
-        <f t="shared" si="118"/>
-        <v>-1</v>
-      </c>
-      <c r="AF55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO55" s="8" t="e">
-        <f t="shared" si="118"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="AE55" s="8"/>
+      <c r="AF55" s="8"/>
+      <c r="AG55" s="8"/>
+      <c r="AH55" s="8"/>
+      <c r="AI55" s="8"/>
+      <c r="AJ55" s="8"/>
+      <c r="AK55" s="8"/>
+      <c r="AL55" s="8"/>
+      <c r="AM55" s="8"/>
+      <c r="AN55" s="8"/>
+      <c r="AO55" s="8"/>
     </row>
     <row r="56" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
@@ -7218,67 +7196,67 @@
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8">
-        <f t="shared" ref="G56:P56" si="119">G28/G18</f>
+        <f t="shared" ref="G56:P56" si="117">G28/G18</f>
         <v>6.5560821484992107E-2</v>
       </c>
       <c r="H56" s="8">
+        <f t="shared" si="117"/>
+        <v>9.0198863636363633E-2</v>
+      </c>
+      <c r="I56" s="8">
+        <f t="shared" si="117"/>
+        <v>7.9151943462897528E-2</v>
+      </c>
+      <c r="J56" s="8">
+        <f t="shared" si="117"/>
+        <v>0.18354157690650583</v>
+      </c>
+      <c r="K56" s="8">
+        <f t="shared" si="117"/>
+        <v>6.5297138664710194E-2</v>
+      </c>
+      <c r="L56" s="8">
+        <f t="shared" si="117"/>
+        <v>7.8824315297261194E-2</v>
+      </c>
+      <c r="M56" s="8">
+        <f t="shared" si="117"/>
+        <v>9.7838452787258251E-2</v>
+      </c>
+      <c r="N56" s="8">
+        <f t="shared" si="117"/>
+        <v>0.18224481814626514</v>
+      </c>
+      <c r="O56" s="8">
+        <f t="shared" si="117"/>
+        <v>7.3957016434892539E-2</v>
+      </c>
+      <c r="P56" s="8">
+        <f t="shared" si="117"/>
+        <v>0.10827740492170022</v>
+      </c>
+      <c r="Q56" s="8">
+        <f t="shared" ref="Q56:R56" si="118">Q28/Q18</f>
+        <v>0.11822258459029759</v>
+      </c>
+      <c r="R56" s="8">
+        <f t="shared" si="118"/>
+        <v>0.21315713875323183</v>
+      </c>
+      <c r="S56" s="8">
+        <f t="shared" ref="S56:V56" si="119">S28/S18</f>
+        <v>7.7657266811279824E-2</v>
+      </c>
+      <c r="T56" s="8">
         <f t="shared" si="119"/>
-        <v>9.0198863636363633E-2</v>
-      </c>
-      <c r="I56" s="8">
+        <v>9.5433977786918964E-2</v>
+      </c>
+      <c r="U56" s="8">
         <f t="shared" si="119"/>
-        <v>7.9151943462897528E-2</v>
-      </c>
-      <c r="J56" s="8">
+        <v>0.11622885930190716</v>
+      </c>
+      <c r="V56" s="8">
         <f t="shared" si="119"/>
-        <v>0.18354157690650583</v>
-      </c>
-      <c r="K56" s="8">
-        <f t="shared" si="119"/>
-        <v>6.5297138664710194E-2</v>
-      </c>
-      <c r="L56" s="8">
-        <f t="shared" si="119"/>
-        <v>7.8824315297261194E-2</v>
-      </c>
-      <c r="M56" s="8">
-        <f t="shared" si="119"/>
-        <v>9.7838452787258251E-2</v>
-      </c>
-      <c r="N56" s="8">
-        <f t="shared" si="119"/>
-        <v>0.18224481814626514</v>
-      </c>
-      <c r="O56" s="8">
-        <f t="shared" si="119"/>
-        <v>7.3957016434892539E-2</v>
-      </c>
-      <c r="P56" s="8">
-        <f t="shared" si="119"/>
-        <v>0.10827740492170022</v>
-      </c>
-      <c r="Q56" s="8">
-        <f t="shared" ref="Q56:R56" si="120">Q28/Q18</f>
-        <v>0.11822258459029759</v>
-      </c>
-      <c r="R56" s="8">
-        <f t="shared" si="120"/>
-        <v>0.21315713875323183</v>
-      </c>
-      <c r="S56" s="8">
-        <f t="shared" ref="S56:V56" si="121">S28/S18</f>
-        <v>7.7657266811279824E-2</v>
-      </c>
-      <c r="T56" s="8">
-        <f t="shared" si="121"/>
-        <v>9.5433977786918964E-2</v>
-      </c>
-      <c r="U56" s="8">
-        <f t="shared" si="121"/>
-        <v>0.16065751858204694</v>
-      </c>
-      <c r="V56" s="8">
-        <f t="shared" si="121"/>
         <v>0.24569813282302994</v>
       </c>
       <c r="Z56" s="8">
@@ -7290,60 +7268,60 @@
         <v>0.10867644460151971</v>
       </c>
       <c r="AB56" s="8">
-        <f t="shared" ref="AB56:AO56" si="122">AB28/AB18</f>
+        <f t="shared" ref="AB56:AO56" si="120">AB28/AB18</f>
         <v>0.11669266770670828</v>
       </c>
       <c r="AC56" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>0.11777003484320557</v>
       </c>
       <c r="AD56" s="8">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>0.14265203568864732</v>
       </c>
       <c r="AE56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.16228117534912698</v>
+        <f t="shared" si="120"/>
+        <v>0.15192372082672309</v>
       </c>
       <c r="AF56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.14482962071884012</v>
+        <f t="shared" si="120"/>
+        <v>0.15527230383704985</v>
       </c>
       <c r="AG56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.14952399816845571</v>
+        <f t="shared" si="120"/>
+        <v>0.16034477855995866</v>
       </c>
       <c r="AH56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.15155076575660423</v>
+        <f t="shared" si="120"/>
+        <v>0.16252579389642688</v>
       </c>
       <c r="AI56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.15266286106328875</v>
+        <f t="shared" si="120"/>
+        <v>0.16372713986211609</v>
       </c>
       <c r="AJ56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.15290763753178707</v>
+        <f t="shared" si="120"/>
+        <v>0.16399545190984499</v>
       </c>
       <c r="AK56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.15299370236771342</v>
+        <f t="shared" si="120"/>
+        <v>0.16408390772876102</v>
       </c>
       <c r="AL56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.15308320714834123</v>
+        <f t="shared" si="120"/>
+        <v>0.16417603144885487</v>
       </c>
       <c r="AM56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.15317616380726287</v>
+        <f t="shared" si="120"/>
+        <v>0.16427183159525899</v>
       </c>
       <c r="AN56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.15327258436576421</v>
+        <f t="shared" si="120"/>
+        <v>0.16437131670371244</v>
       </c>
       <c r="AO56" s="8">
-        <f t="shared" si="122"/>
-        <v>0.15337248093439074</v>
+        <f t="shared" si="120"/>
+        <v>0.16447449532263658</v>
       </c>
     </row>
     <row r="57" spans="2:45" x14ac:dyDescent="0.3">
@@ -7361,67 +7339,67 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8">
-        <f t="shared" ref="G57:P57" si="123">G35/G34</f>
+        <f t="shared" ref="G57:P57" si="121">G35/G34</f>
         <v>0.20547945205479451</v>
       </c>
       <c r="H57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="I57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.27027027027027029</v>
+      </c>
+      <c r="J57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.24713958810068651</v>
+      </c>
+      <c r="K57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.28985507246376813</v>
+      </c>
+      <c r="L57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.29807692307692307</v>
+      </c>
+      <c r="M57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.24827586206896551</v>
+      </c>
+      <c r="N57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.19758064516129031</v>
+      </c>
+      <c r="O57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.36046511627906974</v>
+      </c>
+      <c r="P57" s="8">
+        <f t="shared" si="121"/>
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="Q57" s="8">
+        <f t="shared" ref="Q57:R57" si="122">Q35/Q34</f>
+        <v>0.29959514170040485</v>
+      </c>
+      <c r="R57" s="8">
+        <f t="shared" si="122"/>
+        <v>0.25036390101892286</v>
+      </c>
+      <c r="S57" s="8">
+        <f t="shared" ref="S57:V57" si="123">S35/S34</f>
+        <v>0.26712328767123289</v>
+      </c>
+      <c r="T57" s="8">
         <f t="shared" si="123"/>
-        <v>0.30612244897959184</v>
-      </c>
-      <c r="I57" s="8">
+        <v>0.23766816143497757</v>
+      </c>
+      <c r="U57" s="8">
         <f t="shared" si="123"/>
-        <v>0.27027027027027029</v>
-      </c>
-      <c r="J57" s="8">
+        <v>0.29655172413793102</v>
+      </c>
+      <c r="V57" s="8">
         <f t="shared" si="123"/>
-        <v>0.24713958810068651</v>
-      </c>
-      <c r="K57" s="8">
-        <f t="shared" si="123"/>
-        <v>0.28985507246376813</v>
-      </c>
-      <c r="L57" s="8">
-        <f t="shared" si="123"/>
-        <v>0.29807692307692307</v>
-      </c>
-      <c r="M57" s="8">
-        <f t="shared" si="123"/>
-        <v>0.24827586206896551</v>
-      </c>
-      <c r="N57" s="8">
-        <f t="shared" si="123"/>
-        <v>0.19758064516129031</v>
-      </c>
-      <c r="O57" s="8">
-        <f t="shared" si="123"/>
-        <v>0.36046511627906974</v>
-      </c>
-      <c r="P57" s="8">
-        <f t="shared" si="123"/>
-        <v>0.26923076923076922</v>
-      </c>
-      <c r="Q57" s="8">
-        <f t="shared" ref="Q57:R57" si="124">Q35/Q34</f>
-        <v>0.29959514170040485</v>
-      </c>
-      <c r="R57" s="8">
-        <f t="shared" si="124"/>
-        <v>0.25036390101892286</v>
-      </c>
-      <c r="S57" s="8">
-        <f t="shared" ref="S57:V57" si="125">S35/S34</f>
-        <v>0.26712328767123289</v>
-      </c>
-      <c r="T57" s="8">
-        <f t="shared" si="125"/>
-        <v>0.23766816143497757</v>
-      </c>
-      <c r="U57" s="8">
-        <f t="shared" si="125"/>
-        <v>0.27</v>
-      </c>
-      <c r="V57" s="8">
-        <f t="shared" si="125"/>
         <v>0.27</v>
       </c>
       <c r="Z57" s="8">
@@ -7433,59 +7411,59 @@
         <v>0.25773195876288657</v>
       </c>
       <c r="AB57" s="8">
-        <f t="shared" ref="AB57:AO57" si="126">AB35/AB34</f>
+        <f t="shared" ref="AB57:AO57" si="124">AB35/AB34</f>
         <v>0.25452016689847012</v>
       </c>
       <c r="AC57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.22727272727272727</v>
       </c>
       <c r="AD57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.27117263843648209</v>
       </c>
       <c r="AE57" s="8">
-        <f t="shared" si="126"/>
-        <v>0.26585351686982805</v>
+        <f t="shared" si="124"/>
+        <v>0.27004192918328646</v>
       </c>
       <c r="AF57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AG57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AH57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AI57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AJ57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AK57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AL57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AM57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AN57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
       <c r="AO57" s="8">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
     </row>
@@ -7504,131 +7482,131 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8">
-        <f t="shared" ref="G58:N58" si="127">G36/G34</f>
+        <f t="shared" ref="G58:N58" si="125">G36/G34</f>
         <v>0.16438356164383561</v>
       </c>
       <c r="H58" s="8">
+        <f t="shared" si="125"/>
+        <v>0.11224489795918367</v>
+      </c>
+      <c r="I58" s="8">
+        <f t="shared" si="125"/>
+        <v>4.5045045045045043E-2</v>
+      </c>
+      <c r="J58" s="8">
+        <f t="shared" si="125"/>
+        <v>7.3226544622425629E-2</v>
+      </c>
+      <c r="K58" s="8">
+        <f t="shared" si="125"/>
+        <v>1.4492753623188406E-2</v>
+      </c>
+      <c r="L58" s="8">
+        <f t="shared" si="125"/>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="M58" s="8">
+        <f t="shared" si="125"/>
+        <v>4.8275862068965517E-2</v>
+      </c>
+      <c r="N58" s="8">
+        <f t="shared" si="125"/>
+        <v>0.14314516129032259</v>
+      </c>
+      <c r="O58" s="8">
+        <f t="shared" ref="O58:P58" si="126">O36/O34</f>
+        <v>5.8139534883720929E-2</v>
+      </c>
+      <c r="P58" s="8">
+        <f t="shared" si="126"/>
+        <v>0.42788461538461536</v>
+      </c>
+      <c r="Q58" s="8">
+        <f t="shared" ref="Q58:R58" si="127">Q36/Q34</f>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="R58" s="8">
         <f t="shared" si="127"/>
-        <v>0.11224489795918367</v>
-      </c>
-      <c r="I58" s="8">
-        <f t="shared" si="127"/>
-        <v>4.5045045045045043E-2</v>
-      </c>
-      <c r="J58" s="8">
-        <f t="shared" si="127"/>
-        <v>7.3226544622425629E-2</v>
-      </c>
-      <c r="K58" s="8">
-        <f t="shared" si="127"/>
-        <v>1.4492753623188406E-2</v>
-      </c>
-      <c r="L58" s="8">
-        <f t="shared" si="127"/>
-        <v>0.15384615384615385</v>
-      </c>
-      <c r="M58" s="8">
-        <f t="shared" si="127"/>
-        <v>4.8275862068965517E-2</v>
-      </c>
-      <c r="N58" s="8">
-        <f t="shared" si="127"/>
-        <v>0.14314516129032259</v>
-      </c>
-      <c r="O58" s="8">
-        <f t="shared" ref="O58:P58" si="128">O36/O34</f>
-        <v>5.8139534883720929E-2</v>
-      </c>
-      <c r="P58" s="8">
+        <v>6.6957787481804948E-2</v>
+      </c>
+      <c r="S58" s="8">
+        <f t="shared" ref="S58:V58" si="128">S36/S34</f>
+        <v>0.16438356164383561</v>
+      </c>
+      <c r="T58" s="8">
         <f t="shared" si="128"/>
-        <v>0.42788461538461536</v>
-      </c>
-      <c r="Q58" s="8">
-        <f t="shared" ref="Q58:R58" si="129">Q36/Q34</f>
-        <v>0.15384615384615385</v>
-      </c>
-      <c r="R58" s="8">
+        <v>0.1210762331838565</v>
+      </c>
+      <c r="U58" s="8">
+        <f t="shared" si="128"/>
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="V58" s="8">
+        <f t="shared" si="128"/>
+        <v>0.1</v>
+      </c>
+      <c r="Z58" s="8">
+        <f t="shared" ref="Z58:AO58" si="129">Z36/Z34</f>
+        <v>0.84699453551912574</v>
+      </c>
+      <c r="AA58" s="8">
         <f t="shared" si="129"/>
-        <v>6.6957787481804948E-2</v>
-      </c>
-      <c r="S58" s="8">
-        <f t="shared" ref="S58:V58" si="130">S36/S34</f>
-        <v>0.16438356164383561</v>
-      </c>
-      <c r="T58" s="8">
-        <f t="shared" si="130"/>
-        <v>0.1210762331838565</v>
-      </c>
-      <c r="U58" s="8">
-        <f t="shared" si="130"/>
+        <v>0.2422680412371134</v>
+      </c>
+      <c r="AB58" s="8">
+        <f t="shared" si="129"/>
+        <v>8.3449235048678724E-2</v>
+      </c>
+      <c r="AC58" s="8">
+        <f t="shared" si="129"/>
+        <v>0.1167076167076167</v>
+      </c>
+      <c r="AD58" s="8">
+        <f t="shared" si="129"/>
+        <v>0.14495114006514659</v>
+      </c>
+      <c r="AE58" s="8">
+        <f t="shared" si="129"/>
+        <v>0.12102449047656463</v>
+      </c>
+      <c r="AF58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="V58" s="8">
-        <f t="shared" si="130"/>
+      <c r="AG58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="Z58" s="8">
-        <f t="shared" ref="Z58:AO58" si="131">Z36/Z34</f>
-        <v>0.84699453551912574</v>
-      </c>
-      <c r="AA58" s="8">
-        <f t="shared" si="131"/>
-        <v>0.2422680412371134</v>
-      </c>
-      <c r="AB58" s="8">
-        <f t="shared" si="131"/>
-        <v>8.3449235048678724E-2</v>
-      </c>
-      <c r="AC58" s="8">
-        <f t="shared" si="131"/>
-        <v>0.1167076167076167</v>
-      </c>
-      <c r="AD58" s="8">
-        <f t="shared" si="131"/>
-        <v>0.14495114006514659</v>
-      </c>
-      <c r="AE58" s="8">
-        <f t="shared" si="131"/>
-        <v>0.10766257039782763</v>
-      </c>
-      <c r="AF58" s="8">
-        <f t="shared" si="131"/>
+      <c r="AH58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AG58" s="8">
-        <f t="shared" si="131"/>
+      <c r="AI58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AH58" s="8">
-        <f t="shared" si="131"/>
+      <c r="AJ58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AI58" s="8">
-        <f t="shared" si="131"/>
+      <c r="AK58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AJ58" s="8">
-        <f t="shared" si="131"/>
+      <c r="AL58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AK58" s="8">
-        <f t="shared" si="131"/>
+      <c r="AM58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AL58" s="8">
-        <f t="shared" si="131"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
-      <c r="AM58" s="8">
-        <f t="shared" si="131"/>
+      <c r="AN58" s="8">
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AN58" s="8">
-        <f t="shared" si="131"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
       <c r="AO58" s="8">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
     </row>
@@ -7647,158 +7625,166 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8">
-        <f t="shared" ref="G59:P59" si="132">G37/G23</f>
+        <f t="shared" ref="G59:P59" si="130">G37/G23</f>
         <v>0.17228464419475656</v>
       </c>
       <c r="H59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.18037974683544303</v>
+      </c>
+      <c r="I59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.24050632911392406</v>
+      </c>
+      <c r="J59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.46046511627906977</v>
+      </c>
+      <c r="K59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.15894039735099338</v>
+      </c>
+      <c r="L59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.23776223776223776</v>
+      </c>
+      <c r="N59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.40073529411764708</v>
+      </c>
+      <c r="O59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.12690355329949238</v>
+      </c>
+      <c r="P59" s="8">
+        <f t="shared" si="130"/>
+        <v>0.11033274956217162</v>
+      </c>
+      <c r="Q59" s="8">
+        <f t="shared" ref="Q59:R59" si="131">Q37/Q23</f>
+        <v>0.23235800344234078</v>
+      </c>
+      <c r="R59" s="8">
+        <f t="shared" si="131"/>
+        <v>0.41140350877192983</v>
+      </c>
+      <c r="S59" s="8">
+        <f t="shared" ref="S59:V59" si="132">S37/S23</f>
+        <v>0.15313653136531366</v>
+      </c>
+      <c r="T59" s="8">
         <f t="shared" si="132"/>
-        <v>0.18037974683544303</v>
-      </c>
-      <c r="I59" s="8">
+        <v>0.24033613445378152</v>
+      </c>
+      <c r="U59" s="8">
         <f t="shared" si="132"/>
-        <v>0.24050632911392406</v>
-      </c>
-      <c r="J59" s="8">
+        <v>0.21448467966573817</v>
+      </c>
+      <c r="V59" s="8">
         <f t="shared" si="132"/>
-        <v>0.46046511627906977</v>
-      </c>
-      <c r="K59" s="8">
-        <f t="shared" si="132"/>
-        <v>0.15894039735099338</v>
-      </c>
-      <c r="L59" s="8">
-        <f t="shared" si="132"/>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="M59" s="8">
-        <f t="shared" si="132"/>
-        <v>0.23776223776223776</v>
-      </c>
-      <c r="N59" s="8">
-        <f t="shared" si="132"/>
-        <v>0.40073529411764708</v>
-      </c>
-      <c r="O59" s="8">
-        <f t="shared" si="132"/>
-        <v>0.12690355329949238</v>
-      </c>
-      <c r="P59" s="8">
-        <f t="shared" si="132"/>
-        <v>0.11033274956217162</v>
-      </c>
-      <c r="Q59" s="8">
-        <f t="shared" ref="Q59:R59" si="133">Q37/Q23</f>
-        <v>0.23235800344234078</v>
-      </c>
-      <c r="R59" s="8">
+        <v>0.43065200879212695</v>
+      </c>
+      <c r="Z59" s="8">
+        <f t="shared" ref="Z59:AD59" si="133">Z37/Z18</f>
+        <v>-4.9953746530989824E-3</v>
+      </c>
+      <c r="AA59" s="8">
         <f t="shared" si="133"/>
-        <v>0.41140350877192983</v>
-      </c>
-      <c r="S59" s="8">
-        <f t="shared" ref="S59:V59" si="134">S37/S23</f>
-        <v>0.15313653136531366</v>
-      </c>
-      <c r="T59" s="8">
-        <f t="shared" si="134"/>
-        <v>0.24033613445378152</v>
-      </c>
-      <c r="U59" s="8">
-        <f t="shared" si="134"/>
-        <v>0.35453489906320107</v>
-      </c>
-      <c r="V59" s="8">
-        <f t="shared" si="134"/>
-        <v>0.43065200879212695</v>
-      </c>
-      <c r="Z59" s="8">
-        <f t="shared" ref="Z59:AD59" si="135">Z37/Z18</f>
-        <v>-4.9953746530989824E-3</v>
-      </c>
-      <c r="AA59" s="8">
-        <f t="shared" si="135"/>
         <v>5.1422512811450785E-2</v>
       </c>
       <c r="AB59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="133"/>
         <v>7.4258970358814347E-2</v>
       </c>
       <c r="AC59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="133"/>
         <v>7.4425087108013932E-2</v>
       </c>
       <c r="AD59" s="8">
-        <f t="shared" si="135"/>
+        <f t="shared" si="133"/>
         <v>7.3530919905650707E-2</v>
       </c>
       <c r="AE59" s="8">
         <f>AE37/AE18</f>
-        <v>9.4245194793303441E-2</v>
+        <v>8.569718361862444E-2</v>
       </c>
       <c r="AF59" s="8">
-        <f t="shared" ref="AF59:AO59" si="136">AF37/AF18</f>
-        <v>8.7432232578779717E-2</v>
+        <f t="shared" ref="AF59:AO59" si="134">AF37/AF18</f>
+        <v>9.4584082458692917E-2</v>
       </c>
       <c r="AG59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.0844564009088205E-2</v>
+        <f t="shared" si="134"/>
+        <v>9.8219924412346046E-2</v>
       </c>
       <c r="AH59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.2289972987687069E-2</v>
+        <f t="shared" si="134"/>
+        <v>9.9757006074729621E-2</v>
       </c>
       <c r="AI59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.3022802147021036E-2</v>
+        <f t="shared" si="134"/>
+        <v>0.10054661193535375</v>
       </c>
       <c r="AJ59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.3136808175650315E-2</v>
+        <f t="shared" si="134"/>
+        <v>0.10067838756957373</v>
       </c>
       <c r="AK59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.3137042145548507E-2</v>
+        <f t="shared" si="134"/>
+        <v>0.10068284507169548</v>
       </c>
       <c r="AL59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.313924670847841E-2</v>
+        <f t="shared" si="134"/>
+        <v>0.10068942444503172</v>
       </c>
       <c r="AM59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.3143432778644258E-2</v>
+        <f t="shared" si="134"/>
+        <v>0.10069813372386889</v>
       </c>
       <c r="AN59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.314961145777112E-2</v>
+        <f t="shared" si="134"/>
+        <v>0.1007089810537752</v>
       </c>
       <c r="AO59" s="8">
-        <f t="shared" si="136"/>
-        <v>9.3157794039098352E-2</v>
+        <f t="shared" si="134"/>
+        <v>0.10072197469523517</v>
       </c>
     </row>
     <row r="61" spans="2:45" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B61" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="T61" s="15">
+      <c r="T61" s="17">
         <v>14593</v>
+      </c>
+      <c r="U61" s="17">
+        <v>15658</v>
+      </c>
+      <c r="AE61" s="17">
+        <v>15658</v>
       </c>
     </row>
     <row r="63" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>109</v>
       </c>
-      <c r="T63" s="16">
-        <f>Main!D9/Model!T61</f>
-        <v>5.3194517919550472</v>
+      <c r="T63" s="16"/>
+      <c r="AE63" s="16">
+        <f>Main!$D$9/Model!AE61</f>
+        <v>4.4805342317026442</v>
       </c>
     </row>
     <row r="64" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>110</v>
       </c>
-      <c r="T64" s="8">
-        <f>T61/Main!D9-1</f>
-        <v>-0.81201070352543381</v>
+      <c r="T64" s="8"/>
+      <c r="AE64" s="8">
+        <f>AE61/Main!$D$9-1</f>
+        <v>-0.7768123290021175</v>
       </c>
     </row>
     <row r="67" spans="2:41" x14ac:dyDescent="0.3">
@@ -7806,52 +7792,52 @@
         <v>92</v>
       </c>
       <c r="O67" s="3">
-        <f t="shared" ref="O67:V67" si="137">O37</f>
+        <f t="shared" ref="O67:V67" si="135">O37</f>
         <v>50</v>
       </c>
       <c r="P67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>63</v>
       </c>
       <c r="Q67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>135</v>
       </c>
       <c r="R67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>469</v>
       </c>
       <c r="S67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>83</v>
       </c>
       <c r="T67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>143</v>
       </c>
       <c r="U67" s="3">
-        <f t="shared" si="137"/>
-        <v>290.19816000000014</v>
+        <f t="shared" si="135"/>
+        <v>154</v>
       </c>
       <c r="V67" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>636.60340799999994</v>
       </c>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3">
-        <f t="shared" ref="Z67:AC67" si="138">Z37</f>
+        <f t="shared" ref="Z67:AC67" si="136">Z37</f>
         <v>-27</v>
       </c>
       <c r="AA67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>291</v>
       </c>
       <c r="AB67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>476</v>
       </c>
       <c r="AC67" s="3">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>534</v>
       </c>
       <c r="AD67" s="3">
@@ -7859,48 +7845,48 @@
         <v>717</v>
       </c>
       <c r="AE67" s="3">
-        <f t="shared" ref="AE67:AO67" si="139">AE37</f>
-        <v>1152.8015680000001</v>
+        <f t="shared" ref="AE67:AO67" si="137">AE37</f>
+        <v>1016.6034080000009</v>
       </c>
       <c r="AF67" s="3">
-        <f t="shared" si="139"/>
-        <v>1264.6224175000007</v>
+        <f t="shared" si="137"/>
+        <v>1325.300226899999</v>
       </c>
       <c r="AG67" s="3">
-        <f t="shared" si="139"/>
-        <v>1430.3841434999997</v>
+        <f t="shared" si="137"/>
+        <v>1497.50440437</v>
       </c>
       <c r="AH67" s="3">
-        <f t="shared" si="139"/>
-        <v>1527.5501896362498</v>
+        <f t="shared" si="137"/>
+        <v>1598.3585722708506</v>
       </c>
       <c r="AI67" s="3">
-        <f t="shared" si="139"/>
-        <v>1588.4162624936125</v>
+        <f t="shared" si="137"/>
+        <v>1661.8059039121604</v>
       </c>
       <c r="AJ67" s="3">
-        <f t="shared" si="139"/>
-        <v>1626.2598404607766</v>
+        <f t="shared" si="137"/>
+        <v>1701.5595380752716</v>
       </c>
       <c r="AK67" s="3">
-        <f t="shared" si="139"/>
-        <v>1660.2608966144278</v>
+        <f t="shared" si="137"/>
+        <v>1737.1171142205142</v>
       </c>
       <c r="AL67" s="3">
-        <f t="shared" si="139"/>
-        <v>1695.0701891176468</v>
+        <f t="shared" si="137"/>
+        <v>1773.5178137921473</v>
       </c>
       <c r="AM67" s="3">
-        <f t="shared" si="139"/>
-        <v>1730.7092906452594</v>
+        <f t="shared" si="137"/>
+        <v>1810.7839045862133</v>
       </c>
       <c r="AN67" s="3">
-        <f t="shared" si="139"/>
-        <v>1767.2004192837585</v>
+        <f t="shared" si="137"/>
+        <v>1848.9383055945409</v>
       </c>
       <c r="AO67" s="3">
-        <f t="shared" si="139"/>
-        <v>1804.5664601807241</v>
+        <f t="shared" si="137"/>
+        <v>1888.0046081015969</v>
       </c>
     </row>
     <row r="68" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7930,8 +7916,8 @@
         <v>159</v>
       </c>
       <c r="U68" s="6">
-        <f>U67</f>
-        <v>290.19816000000014</v>
+        <f>U86-T68-S68</f>
+        <v>203</v>
       </c>
       <c r="V68" s="6">
         <f>V67</f>
@@ -7957,47 +7943,47 @@
       </c>
       <c r="AE68" s="6">
         <f>AE67*1.1</f>
-        <v>1268.0817248000003</v>
+        <v>1118.2637488000009</v>
       </c>
       <c r="AF68" s="6">
-        <f t="shared" ref="AF68:AO68" si="140">AF67*1.1</f>
-        <v>1391.0846592500009</v>
+        <f t="shared" ref="AF68:AO68" si="138">AF67*1.1</f>
+        <v>1457.8302495899991</v>
       </c>
       <c r="AG68" s="6">
-        <f t="shared" si="140"/>
-        <v>1573.4225578499997</v>
+        <f t="shared" si="138"/>
+        <v>1647.2548448070002</v>
       </c>
       <c r="AH68" s="6">
-        <f t="shared" si="140"/>
-        <v>1680.305208599875</v>
+        <f t="shared" si="138"/>
+        <v>1758.1944294979357</v>
       </c>
       <c r="AI68" s="6">
-        <f t="shared" si="140"/>
-        <v>1747.2578887429738</v>
+        <f t="shared" si="138"/>
+        <v>1827.9864943033765</v>
       </c>
       <c r="AJ68" s="6">
-        <f t="shared" si="140"/>
-        <v>1788.8858245068543</v>
+        <f t="shared" si="138"/>
+        <v>1871.7154918827989</v>
       </c>
       <c r="AK68" s="6">
-        <f t="shared" si="140"/>
-        <v>1826.2869862758707</v>
+        <f t="shared" si="138"/>
+        <v>1910.8288256425658</v>
       </c>
       <c r="AL68" s="6">
-        <f t="shared" si="140"/>
-        <v>1864.5772080294116</v>
+        <f t="shared" si="138"/>
+        <v>1950.8695951713621</v>
       </c>
       <c r="AM68" s="6">
-        <f t="shared" si="140"/>
-        <v>1903.7802197097856</v>
+        <f t="shared" si="138"/>
+        <v>1991.8622950448348</v>
       </c>
       <c r="AN68" s="6">
-        <f t="shared" si="140"/>
-        <v>1943.9204612121346</v>
+        <f t="shared" si="138"/>
+        <v>2033.8321361539952</v>
       </c>
       <c r="AO68" s="6">
-        <f t="shared" si="140"/>
-        <v>1985.0231061987968</v>
+        <f t="shared" si="138"/>
+        <v>2076.8050689117567</v>
       </c>
     </row>
     <row r="69" spans="2:41" x14ac:dyDescent="0.3">
@@ -8026,11 +8012,11 @@
         <f>239-S69</f>
         <v>127</v>
       </c>
-      <c r="U69">
-        <f>Q69*1.4</f>
-        <v>134.39999999999998</v>
-      </c>
-      <c r="V69">
+      <c r="U69" s="3">
+        <f>U88-T69-S69</f>
+        <v>116</v>
+      </c>
+      <c r="V69" s="3">
         <f>R69*1.4</f>
         <v>176.39999999999998</v>
       </c>
@@ -8054,47 +8040,47 @@
       </c>
       <c r="AE69" s="3">
         <f>SUM(S69:V69)</f>
-        <v>549.79999999999995</v>
+        <v>531.4</v>
       </c>
       <c r="AF69" s="3">
         <f>AE69*1.15</f>
-        <v>632.26999999999987</v>
+        <v>611.1099999999999</v>
       </c>
       <c r="AG69" s="3">
         <f>AF69*1.1</f>
-        <v>695.49699999999996</v>
+        <v>672.22099999999989</v>
       </c>
       <c r="AH69" s="3">
         <f>AG69*1.05</f>
-        <v>730.27184999999997</v>
+        <v>705.83204999999987</v>
       </c>
       <c r="AI69" s="3">
         <f>AH69*1.04</f>
-        <v>759.48272399999996</v>
+        <v>734.0653319999999</v>
       </c>
       <c r="AJ69" s="3">
         <f>AI69*1.03</f>
-        <v>782.26720571999999</v>
+        <v>756.0872919599999</v>
       </c>
       <c r="AK69" s="3">
         <f>AJ69*1.02</f>
-        <v>797.91254983440001</v>
+        <v>771.2090377991999</v>
       </c>
       <c r="AL69" s="3">
-        <f t="shared" ref="AL69:AO69" si="141">AK69*1.02</f>
-        <v>813.87080083108799</v>
+        <f t="shared" ref="AL69:AO69" si="139">AK69*1.02</f>
+        <v>786.63321855518393</v>
       </c>
       <c r="AM69" s="3">
-        <f t="shared" si="141"/>
-        <v>830.14821684770982</v>
+        <f t="shared" si="139"/>
+        <v>802.36588292628767</v>
       </c>
       <c r="AN69" s="3">
-        <f t="shared" si="141"/>
-        <v>846.75118118466401</v>
+        <f t="shared" si="139"/>
+        <v>818.41320058481347</v>
       </c>
       <c r="AO69" s="3">
-        <f t="shared" si="141"/>
-        <v>863.68620480835727</v>
+        <f t="shared" si="139"/>
+        <v>834.78146459650975</v>
       </c>
     </row>
     <row r="70" spans="2:41" x14ac:dyDescent="0.3">
@@ -8121,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
-        <f t="shared" ref="AE70:AE79" si="142">SUM(S70:V70)</f>
+        <f t="shared" ref="AE70:AE79" si="140">SUM(S70:V70)</f>
         <v>0</v>
       </c>
       <c r="AF70" s="3">
@@ -8172,7 +8158,7 @@
         <v>-11</v>
       </c>
       <c r="R71" s="3">
-        <f t="shared" ref="R71:R75" si="143">AD71-Q71-P71-O71</f>
+        <f t="shared" ref="R71:R75" si="141">AD71-Q71-P71-O71</f>
         <v>-6</v>
       </c>
       <c r="S71" s="3">
@@ -8183,8 +8169,9 @@
         <f>14-S71</f>
         <v>21</v>
       </c>
-      <c r="U71">
-        <v>-10</v>
+      <c r="U71" s="3">
+        <f t="shared" ref="U71:U75" si="142">U90-T71-S71</f>
+        <v>-34</v>
       </c>
       <c r="V71">
         <v>-25</v>
@@ -8214,48 +8201,48 @@
         <v>-24</v>
       </c>
       <c r="AE71" s="3">
-        <f t="shared" si="142"/>
-        <v>-21</v>
+        <f t="shared" si="140"/>
+        <v>-45</v>
       </c>
       <c r="AF71" s="3">
         <f>AE71*1.1</f>
-        <v>-23.1</v>
+        <v>-49.500000000000007</v>
       </c>
       <c r="AG71" s="3">
-        <f t="shared" ref="AG71:AO71" si="144">AF71*1.1</f>
-        <v>-25.410000000000004</v>
+        <f t="shared" ref="AG71:AO71" si="143">AF71*1.1</f>
+        <v>-54.45000000000001</v>
       </c>
       <c r="AH71" s="3">
-        <f t="shared" si="144"/>
-        <v>-27.951000000000008</v>
+        <f t="shared" si="143"/>
+        <v>-59.895000000000017</v>
       </c>
       <c r="AI71" s="3">
-        <f t="shared" si="144"/>
-        <v>-30.746100000000009</v>
+        <f t="shared" si="143"/>
+        <v>-65.884500000000031</v>
       </c>
       <c r="AJ71" s="3">
-        <f t="shared" si="144"/>
-        <v>-33.820710000000012</v>
+        <f t="shared" si="143"/>
+        <v>-72.47295000000004</v>
       </c>
       <c r="AK71" s="3">
-        <f t="shared" si="144"/>
-        <v>-37.202781000000016</v>
+        <f t="shared" si="143"/>
+        <v>-79.720245000000048</v>
       </c>
       <c r="AL71" s="3">
-        <f t="shared" si="144"/>
-        <v>-40.923059100000017</v>
+        <f t="shared" si="143"/>
+        <v>-87.692269500000066</v>
       </c>
       <c r="AM71" s="3">
-        <f t="shared" si="144"/>
-        <v>-45.015365010000025</v>
+        <f t="shared" si="143"/>
+        <v>-96.461496450000084</v>
       </c>
       <c r="AN71" s="3">
-        <f t="shared" si="144"/>
-        <v>-49.516901511000029</v>
+        <f t="shared" si="143"/>
+        <v>-106.10764609500011</v>
       </c>
       <c r="AO71" s="3">
-        <f t="shared" si="144"/>
-        <v>-54.468591662100039</v>
+        <f t="shared" si="143"/>
+        <v>-116.71841070450013</v>
       </c>
     </row>
     <row r="72" spans="2:41" x14ac:dyDescent="0.3">
@@ -8274,7 +8261,7 @@
         <v>-3</v>
       </c>
       <c r="R72" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>37</v>
       </c>
       <c r="S72" s="3">
@@ -8283,8 +8270,9 @@
       <c r="T72" s="3">
         <v>0</v>
       </c>
-      <c r="U72">
-        <v>0</v>
+      <c r="U72" s="3">
+        <f t="shared" si="142"/>
+        <v>14</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -8308,8 +8296,8 @@
         <v>103</v>
       </c>
       <c r="AE72" s="3">
-        <f t="shared" si="142"/>
-        <v>0</v>
+        <f t="shared" si="140"/>
+        <v>14</v>
       </c>
       <c r="AF72" s="3">
         <v>0</v>
@@ -8358,7 +8346,7 @@
         <v>78</v>
       </c>
       <c r="R73" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>41</v>
       </c>
       <c r="S73" s="3">
@@ -8368,8 +8356,9 @@
         <f>-15-S73</f>
         <v>-105</v>
       </c>
-      <c r="U73">
-        <v>0</v>
+      <c r="U73" s="3">
+        <f t="shared" si="142"/>
+        <v>19</v>
       </c>
       <c r="V73">
         <v>110</v>
@@ -8393,8 +8382,8 @@
         <v>135</v>
       </c>
       <c r="AE73" s="3">
-        <f t="shared" si="142"/>
-        <v>95</v>
+        <f t="shared" si="140"/>
+        <v>114</v>
       </c>
       <c r="AF73" s="3">
         <v>0</v>
@@ -8443,7 +8432,7 @@
         <v>-77</v>
       </c>
       <c r="R74" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>558</v>
       </c>
       <c r="S74" s="3">
@@ -8453,8 +8442,9 @@
         <f>-669-S74</f>
         <v>-791</v>
       </c>
-      <c r="U74">
-        <v>0</v>
+      <c r="U74" s="3">
+        <f t="shared" si="142"/>
+        <v>-298</v>
       </c>
       <c r="V74">
         <f>R74*1.5</f>
@@ -8479,8 +8469,8 @@
         <v>407</v>
       </c>
       <c r="AE74" s="3">
-        <f t="shared" si="142"/>
-        <v>168</v>
+        <f t="shared" si="140"/>
+        <v>-130</v>
       </c>
       <c r="AF74" s="3">
         <v>0</v>
@@ -8529,7 +8519,7 @@
         <v>-15</v>
       </c>
       <c r="R75" s="3">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>72</v>
       </c>
       <c r="S75" s="3">
@@ -8539,8 +8529,9 @@
         <f>-100-S75</f>
         <v>-95</v>
       </c>
-      <c r="U75">
-        <v>0</v>
+      <c r="U75" s="3">
+        <f t="shared" si="142"/>
+        <v>46</v>
       </c>
       <c r="V75">
         <v>0</v>
@@ -8564,8 +8555,8 @@
         <v>-102</v>
       </c>
       <c r="AE75" s="3">
-        <f t="shared" si="142"/>
-        <v>-100</v>
+        <f t="shared" si="140"/>
+        <v>-54</v>
       </c>
       <c r="AF75" s="3">
         <v>0</v>
@@ -8618,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="AE76" s="3">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="AF76" s="3">
@@ -8668,7 +8659,7 @@
         <v>12</v>
       </c>
       <c r="R77" s="3">
-        <f t="shared" ref="R77:R79" si="145">AD77-Q77-P77-O77</f>
+        <f t="shared" ref="R77:R79" si="144">AD77-Q77-P77-O77</f>
         <v>-1</v>
       </c>
       <c r="S77" s="3">
@@ -8678,8 +8669,9 @@
         <f>4-S77</f>
         <v>0</v>
       </c>
-      <c r="U77">
-        <v>0</v>
+      <c r="U77" s="3">
+        <f t="shared" ref="U77:U79" si="145">U96-T77-S77</f>
+        <v>4</v>
       </c>
       <c r="V77">
         <v>0</v>
@@ -8703,8 +8695,8 @@
         <v>15</v>
       </c>
       <c r="AE77" s="3">
-        <f t="shared" si="142"/>
-        <v>4</v>
+        <f t="shared" si="140"/>
+        <v>8</v>
       </c>
       <c r="AF77" s="3">
         <v>0</v>
@@ -8752,7 +8744,7 @@
         <v>9</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="145"/>
+        <f t="shared" si="144"/>
         <v>7</v>
       </c>
       <c r="S78" s="3">
@@ -8762,8 +8754,9 @@
         <f>8-S78</f>
         <v>2</v>
       </c>
-      <c r="U78">
-        <v>3</v>
+      <c r="U78" s="3">
+        <f t="shared" si="145"/>
+        <v>2</v>
       </c>
       <c r="V78">
         <v>5</v>
@@ -8787,8 +8780,8 @@
         <v>16</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="142"/>
-        <v>16</v>
+        <f t="shared" si="140"/>
+        <v>15</v>
       </c>
       <c r="AF78" s="3">
         <v>0</v>
@@ -8837,7 +8830,7 @@
         <v>38</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="145"/>
+        <f t="shared" si="144"/>
         <v>-109</v>
       </c>
       <c r="S79" s="3">
@@ -8847,8 +8840,9 @@
         <f>-25-S79</f>
         <v>-15</v>
       </c>
-      <c r="U79">
-        <v>0</v>
+      <c r="U79" s="3">
+        <f t="shared" si="145"/>
+        <v>-10</v>
       </c>
       <c r="V79">
         <v>0</v>
@@ -8872,8 +8866,8 @@
         <v>-42</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="142"/>
-        <v>-25</v>
+        <f t="shared" si="140"/>
+        <v>-35</v>
       </c>
       <c r="AF79" s="3">
         <v>0</v>
@@ -8936,7 +8930,7 @@
       </c>
       <c r="U80" s="6">
         <f>U68+SUM(U69:U79)</f>
-        <v>417.59816000000012</v>
+        <v>62</v>
       </c>
       <c r="V80" s="6">
         <f>V68+SUM(V69:V79)</f>
@@ -8968,47 +8962,47 @@
       </c>
       <c r="AE80" s="6">
         <f t="shared" ref="AE80:AO80" si="150">AE68+SUM(AE69:AE79)</f>
-        <v>1954.8817248000003</v>
+        <v>1536.663748800001</v>
       </c>
       <c r="AF80" s="6">
         <f t="shared" si="150"/>
-        <v>2000.2546592500007</v>
+        <v>2019.440249589999</v>
       </c>
       <c r="AG80" s="6">
         <f t="shared" si="150"/>
-        <v>2243.5095578499995</v>
+        <v>2265.0258448069999</v>
       </c>
       <c r="AH80" s="6">
         <f t="shared" si="150"/>
-        <v>2382.6260585998748</v>
+        <v>2404.1314794979357</v>
       </c>
       <c r="AI80" s="6">
         <f t="shared" si="150"/>
-        <v>2475.9945127429737</v>
+        <v>2496.1673263033763</v>
       </c>
       <c r="AJ80" s="6">
         <f t="shared" si="150"/>
-        <v>2537.3323202268543</v>
+        <v>2555.3298338427985</v>
       </c>
       <c r="AK80" s="6">
         <f t="shared" si="150"/>
-        <v>2586.9967551102709</v>
+        <v>2602.3176184417657</v>
       </c>
       <c r="AL80" s="6">
         <f t="shared" si="150"/>
-        <v>2637.5249497604996</v>
+        <v>2649.810544226546</v>
       </c>
       <c r="AM80" s="6">
         <f t="shared" si="150"/>
-        <v>2688.9130715474953</v>
+        <v>2697.7666815211223</v>
       </c>
       <c r="AN80" s="6">
         <f t="shared" si="150"/>
-        <v>2741.1547408857987</v>
+        <v>2746.1376906438086</v>
       </c>
       <c r="AO80" s="6">
         <f t="shared" si="150"/>
-        <v>2794.240719345054</v>
+        <v>2794.8681228037663</v>
       </c>
     </row>
     <row r="81" spans="2:139" x14ac:dyDescent="0.3">
@@ -9038,12 +9032,12 @@
         <v>199</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" ref="U81:V81" si="151">Q81*1.45</f>
-        <v>266.8</v>
+        <f>U100-T81-S81</f>
+        <v>246</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="151"/>
-        <v>458.2</v>
+        <f>R81*1.4</f>
+        <v>442.4</v>
       </c>
       <c r="Y81" s="3">
         <v>288</v>
@@ -9065,47 +9059,47 @@
       </c>
       <c r="AE81" s="3">
         <f>SUM(S81:V81)</f>
-        <v>1077</v>
+        <v>1040.4000000000001</v>
       </c>
       <c r="AF81" s="3">
         <f>AE81*1.1</f>
-        <v>1184.7</v>
+        <v>1144.4400000000003</v>
       </c>
       <c r="AG81" s="3">
-        <f t="shared" ref="AG81:AJ81" si="152">AF81*0.9</f>
-        <v>1066.23</v>
+        <f>AF81*1.02</f>
+        <v>1167.3288000000002</v>
       </c>
       <c r="AH81" s="3">
+        <f t="shared" ref="AH81" si="151">AG81*1.02</f>
+        <v>1190.6753760000001</v>
+      </c>
+      <c r="AI81" s="3">
+        <f>AH81*0.97</f>
+        <v>1154.9551147200002</v>
+      </c>
+      <c r="AJ81" s="3">
+        <f t="shared" ref="AJ81:AO81" si="152">AI81*0.97</f>
+        <v>1120.3064612784001</v>
+      </c>
+      <c r="AK81" s="3">
         <f t="shared" si="152"/>
-        <v>959.60700000000008</v>
-      </c>
-      <c r="AI81" s="3">
+        <v>1086.6972674400481</v>
+      </c>
+      <c r="AL81" s="3">
         <f t="shared" si="152"/>
-        <v>863.64630000000011</v>
-      </c>
-      <c r="AJ81" s="3">
+        <v>1054.0963494168466</v>
+      </c>
+      <c r="AM81" s="3">
         <f t="shared" si="152"/>
-        <v>777.28167000000008</v>
-      </c>
-      <c r="AK81" s="3">
-        <f>AJ81*0.95</f>
-        <v>738.41758650000008</v>
-      </c>
-      <c r="AL81" s="3">
-        <f t="shared" ref="AL81:AO81" si="153">AK81*0.95</f>
-        <v>701.4967071750001</v>
-      </c>
-      <c r="AM81" s="3">
-        <f t="shared" si="153"/>
-        <v>666.42187181625002</v>
+        <v>1022.4734589343411</v>
       </c>
       <c r="AN81" s="3">
-        <f t="shared" si="153"/>
-        <v>633.10077822543747</v>
+        <f t="shared" si="152"/>
+        <v>991.7992551663109</v>
       </c>
       <c r="AO81" s="3">
-        <f t="shared" si="153"/>
-        <v>601.44573931416562</v>
+        <f t="shared" si="152"/>
+        <v>962.0452775113215</v>
       </c>
     </row>
     <row r="82" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -9113,496 +9107,496 @@
         <v>106</v>
       </c>
       <c r="O82" s="6">
-        <f t="shared" ref="O82:P82" si="154">O80-O81</f>
+        <f t="shared" ref="O82:P82" si="153">O80-O81</f>
         <v>-210</v>
       </c>
       <c r="P82" s="6">
+        <f t="shared" si="153"/>
+        <v>170</v>
+      </c>
+      <c r="Q82" s="6">
+        <f t="shared" ref="Q82:R82" si="154">Q80-Q81</f>
+        <v>116</v>
+      </c>
+      <c r="R82" s="6">
         <f t="shared" si="154"/>
-        <v>170</v>
-      </c>
-      <c r="Q82" s="6">
-        <f t="shared" ref="Q82:R82" si="155">Q80-Q81</f>
-        <v>116</v>
-      </c>
-      <c r="R82" s="6">
+        <v>911</v>
+      </c>
+      <c r="S82" s="6">
+        <f t="shared" ref="S82:V82" si="155">S80-S81</f>
+        <v>267</v>
+      </c>
+      <c r="T82" s="6">
         <f t="shared" si="155"/>
-        <v>911</v>
-      </c>
-      <c r="S82" s="6">
-        <f t="shared" ref="S82:V82" si="156">S80-S81</f>
-        <v>267</v>
-      </c>
-      <c r="T82" s="6">
+        <v>-896</v>
+      </c>
+      <c r="U82" s="6">
+        <f t="shared" si="155"/>
+        <v>-184</v>
+      </c>
+      <c r="V82" s="6">
+        <f t="shared" si="155"/>
+        <v>1297.6034079999999</v>
+      </c>
+      <c r="Y82" s="6">
+        <f t="shared" ref="Y82:AD82" si="156">Y80-Y81</f>
+        <v>314</v>
+      </c>
+      <c r="Z82" s="6">
         <f t="shared" si="156"/>
-        <v>-896</v>
-      </c>
-      <c r="U82" s="6">
+        <v>216</v>
+      </c>
+      <c r="AA82" s="6">
         <f t="shared" si="156"/>
-        <v>150.79816000000011</v>
-      </c>
-      <c r="V82" s="6">
+        <v>419</v>
+      </c>
+      <c r="AB82" s="6">
         <f t="shared" si="156"/>
-        <v>1281.803408</v>
-      </c>
-      <c r="Y82" s="6">
-        <f t="shared" ref="Y82:AD82" si="157">Y80-Y81</f>
-        <v>314</v>
-      </c>
-      <c r="Z82" s="6">
+        <v>-175</v>
+      </c>
+      <c r="AC82" s="6">
+        <f t="shared" si="156"/>
+        <v>344</v>
+      </c>
+      <c r="AD82" s="6">
+        <f t="shared" si="156"/>
+        <v>987</v>
+      </c>
+      <c r="AE82" s="6">
+        <f t="shared" ref="AE82:AO82" si="157">AE80-AE81</f>
+        <v>496.26374880000094</v>
+      </c>
+      <c r="AF82" s="6">
         <f t="shared" si="157"/>
-        <v>216</v>
-      </c>
-      <c r="AA82" s="6">
+        <v>875.0002495899987</v>
+      </c>
+      <c r="AG82" s="6">
         <f t="shared" si="157"/>
-        <v>419</v>
-      </c>
-      <c r="AB82" s="6">
+        <v>1097.6970448069997</v>
+      </c>
+      <c r="AH82" s="6">
         <f t="shared" si="157"/>
-        <v>-175</v>
-      </c>
-      <c r="AC82" s="6">
+        <v>1213.4561034979356</v>
+      </c>
+      <c r="AI82" s="6">
         <f t="shared" si="157"/>
-        <v>344</v>
-      </c>
-      <c r="AD82" s="6">
+        <v>1341.2122115833761</v>
+      </c>
+      <c r="AJ82" s="6">
         <f t="shared" si="157"/>
-        <v>987</v>
-      </c>
-      <c r="AE82" s="6">
-        <f t="shared" ref="AE82:AO82" si="158">AE80-AE81</f>
-        <v>877.88172480000026</v>
-      </c>
-      <c r="AF82" s="6">
-        <f t="shared" si="158"/>
-        <v>815.55465925000067</v>
-      </c>
-      <c r="AG82" s="6">
-        <f t="shared" si="158"/>
-        <v>1177.2795578499995</v>
-      </c>
-      <c r="AH82" s="6">
-        <f t="shared" si="158"/>
-        <v>1423.0190585998748</v>
-      </c>
-      <c r="AI82" s="6">
-        <f t="shared" si="158"/>
-        <v>1612.3482127429736</v>
-      </c>
-      <c r="AJ82" s="6">
-        <f t="shared" si="158"/>
-        <v>1760.0506502268543</v>
+        <v>1435.0233725643984</v>
       </c>
       <c r="AK82" s="6">
-        <f t="shared" si="158"/>
-        <v>1848.5791686102707</v>
+        <f t="shared" si="157"/>
+        <v>1515.6203510017176</v>
       </c>
       <c r="AL82" s="6">
-        <f t="shared" si="158"/>
-        <v>1936.0282425854994</v>
+        <f t="shared" si="157"/>
+        <v>1595.7141948096994</v>
       </c>
       <c r="AM82" s="6">
-        <f t="shared" si="158"/>
-        <v>2022.4911997312452</v>
+        <f t="shared" si="157"/>
+        <v>1675.2932225867812</v>
       </c>
       <c r="AN82" s="6">
-        <f t="shared" si="158"/>
-        <v>2108.0539626603613</v>
+        <f t="shared" si="157"/>
+        <v>1754.3384354774976</v>
       </c>
       <c r="AO82" s="6">
-        <f t="shared" si="158"/>
-        <v>2192.7949800308884</v>
+        <f t="shared" si="157"/>
+        <v>1832.8228452924448</v>
       </c>
       <c r="AP82" s="1">
         <f>AO82*(1+AS45)</f>
-        <v>2170.8670302305795</v>
+        <v>1814.4946168395202</v>
       </c>
       <c r="AQ82" s="1">
-        <f t="shared" ref="AQ82:DB82" si="159">AP82*(1+AT45)</f>
-        <v>2170.8670302305795</v>
+        <f t="shared" ref="AQ82:DB82" si="158">AP82*(1+AT45)</f>
+        <v>1814.4946168395202</v>
       </c>
       <c r="AR82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="AS82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="AT82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="AU82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="AV82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="AW82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="AX82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="AY82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="AZ82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BA82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BB82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BC82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BD82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BE82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BF82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BG82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BH82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BI82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BJ82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BK82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BL82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BM82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BN82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BO82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BP82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BQ82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BR82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BS82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BT82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BU82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BV82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BW82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BX82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BY82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="BZ82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CA82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CB82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CC82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CD82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CE82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CF82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CG82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CH82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CI82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CJ82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CK82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CL82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CM82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CN82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CO82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CP82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CQ82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CR82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CS82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CT82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CU82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CV82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CW82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CX82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CY82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="CZ82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DA82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DB82" s="1">
+        <f t="shared" si="158"/>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DC82" s="1">
+        <f t="shared" ref="DC82:EI82" si="159">DB82*(1+DF45)</f>
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DD82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AS82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DE82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AT82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DF82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AU82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DG82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AV82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DH82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AW82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DI82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AX82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DJ82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AY82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DK82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="AZ82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DL82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BA82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DM82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BB82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DN82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BC82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DO82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BD82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DP82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BE82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DQ82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BF82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DR82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BG82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DS82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BH82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DT82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BI82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DU82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BJ82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DV82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BK82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DW82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BL82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DX82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BM82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DY82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BN82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="DZ82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BO82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="EA82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BP82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="EB82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BQ82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="EC82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BR82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="ED82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BS82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="EE82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BT82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="EF82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BU82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="EG82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BV82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="EH82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BW82" s="1">
+        <v>1814.4946168395202</v>
+      </c>
+      <c r="EI82" s="1">
         <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BX82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BY82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="BZ82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CA82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CB82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CC82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CD82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CE82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CF82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CG82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CH82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CI82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CJ82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CK82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CL82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CM82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CN82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CO82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CP82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CQ82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CR82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CS82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CT82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CU82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CV82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CW82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CX82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CY82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="CZ82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DA82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DB82" s="1">
-        <f t="shared" si="159"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DC82" s="1">
-        <f t="shared" ref="DC82:EI82" si="160">DB82*(1+DF45)</f>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DD82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DE82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DF82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DG82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DH82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DI82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DJ82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DK82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DL82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DM82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DN82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DO82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DP82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DQ82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DR82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DS82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DT82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DU82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DV82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DW82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DX82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DY82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="DZ82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="EA82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="EB82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="EC82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="ED82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="EE82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="EF82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="EG82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="EH82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
-      </c>
-      <c r="EI82" s="1">
-        <f t="shared" si="160"/>
-        <v>2170.8670302305795</v>
+        <v>1814.4946168395202</v>
       </c>
     </row>
     <row r="84" spans="2:139" x14ac:dyDescent="0.3">
@@ -9614,50 +9608,152 @@
         <v>0.45714285714285707</v>
       </c>
       <c r="T84" s="8">
-        <f t="shared" ref="T84:V84" si="161">T81/P81-1</f>
+        <f t="shared" ref="T84:V84" si="160">T81/P81-1</f>
         <v>0.56692913385826782</v>
       </c>
       <c r="U84" s="8">
-        <f t="shared" si="161"/>
-        <v>0.44999999999999996</v>
+        <f t="shared" si="160"/>
+        <v>0.33695652173913038</v>
       </c>
       <c r="V84" s="8">
-        <f t="shared" si="161"/>
-        <v>0.44999999999999996</v>
+        <f t="shared" si="160"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="AS84" s="3">
         <f>NPV(AS46,AE82:EI82)</f>
-        <v>26107.609767880786</v>
+        <v>21807.524052147131</v>
       </c>
     </row>
     <row r="85" spans="2:139" x14ac:dyDescent="0.3">
       <c r="AS85" s="3">
         <f>AS48</f>
-        <v>-293</v>
+        <v>-1553</v>
       </c>
     </row>
     <row r="86" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="AS86" s="3">
+      <c r="U86">
+        <v>470</v>
+      </c>
+      <c r="AS86" s="3"/>
+    </row>
+    <row r="87" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="AS87" s="3"/>
+    </row>
+    <row r="88" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="U88">
+        <v>355</v>
+      </c>
+      <c r="AS88" s="3">
         <f>AS84+AS85</f>
-        <v>25814.609767880786</v>
-      </c>
-    </row>
-    <row r="87" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="AS87" s="12">
-        <f>AS86/AO38</f>
-        <v>588.83690163961637</v>
-      </c>
-    </row>
-    <row r="88" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="AS88" s="12">
+        <v>20254.524052147131</v>
+      </c>
+    </row>
+    <row r="89" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS89" s="12">
+        <f>AS88/AO38</f>
+        <v>449.80066738057144</v>
+      </c>
+    </row>
+    <row r="90" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>95</v>
+      </c>
+      <c r="U90">
+        <f>-21+1</f>
+        <v>-20</v>
+      </c>
+      <c r="AS90" s="12">
         <f>Main!D3</f>
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="89" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="AS89" s="7">
-        <f>AS87/AS88-1</f>
-        <v>-0.6661922326306029</v>
+        <v>1523.5</v>
+      </c>
+    </row>
+    <row r="91" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>111</v>
+      </c>
+      <c r="U91">
+        <v>14</v>
+      </c>
+      <c r="AS91" s="7">
+        <f>AS89/AS90-1</f>
+        <v>-0.70475834106952973</v>
+      </c>
+    </row>
+    <row r="92" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>97</v>
+      </c>
+      <c r="U92">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
+        <v>98</v>
+      </c>
+      <c r="U93">
+        <v>-967</v>
+      </c>
+    </row>
+    <row r="94" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>99</v>
+      </c>
+      <c r="U94">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="95" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>101</v>
+      </c>
+      <c r="U96">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B97" t="s">
+        <v>102</v>
+      </c>
+      <c r="U97">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>103</v>
+      </c>
+      <c r="U98">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="99" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B99" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="100" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
+        <v>105</v>
+      </c>
+      <c r="U100">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="101" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B101" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RHM.xlsx
+++ b/Financial Analysis/RHM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5623DB-4FD6-42C2-8964-E0E696DB246E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6E8BCD-FFC9-4392-9CB4-68AC31142174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
   </bookViews>
@@ -373,16 +373,8 @@
     <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-1]"/>
     <numFmt numFmtId="166" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -396,9 +388,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -407,21 +406,35 @@
       <b/>
       <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -429,41 +442,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -906,91 +935,93 @@
   <dimension ref="B2:H9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="10" customWidth="1"/>
+    <col min="1" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="17" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2">
-        <v>1523.5</v>
-      </c>
-      <c r="E3" s="11">
-        <v>45988</v>
-      </c>
-      <c r="F3" s="11">
+      <c r="D3" s="12">
+        <v>1580.5</v>
+      </c>
+      <c r="E3" s="18">
+        <v>46070</v>
+      </c>
+      <c r="F3" s="18">
         <f ca="1">TODAY()</f>
-        <v>46066</v>
-      </c>
-      <c r="G3" s="11">
+        <v>46080</v>
+      </c>
+      <c r="G3" s="18">
         <v>46092</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3">
         <f>45.03</f>
         <v>45.03</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>68603.205000000002</v>
+        <v>71169.915000000008</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="3">
         <f>557+320</f>
         <v>877</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="3">
         <f>1232+1198</f>
         <v>2430</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="3">
@@ -999,12 +1030,12 @@
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>70156.205000000002</v>
+        <v>72722.915000000008</v>
       </c>
     </row>
   </sheetData>
@@ -1018,138 +1049,143 @@
   <dimension ref="B2:EV101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="8.88671875" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="30.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="8.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="1"/>
+    <col min="13" max="13" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="8.88671875" style="1"/>
+    <col min="17" max="17" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="43" width="8.88671875" style="1"/>
+    <col min="44" max="44" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.44140625" style="1" customWidth="1"/>
+    <col min="46" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="T2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="1">
         <v>2019</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="1">
         <v>2020</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="1">
         <v>2021</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="1">
         <v>2022</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="1">
         <v>2023</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="1">
         <v>2024</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="1">
         <v>2025</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="1">
         <v>2026</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="1">
         <v>2027</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="1">
         <v>2028</v>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="1">
         <v>2029</v>
       </c>
-      <c r="AJ2">
+      <c r="AJ2" s="1">
         <v>2030</v>
       </c>
-      <c r="AK2">
+      <c r="AK2" s="1">
         <v>2031</v>
       </c>
-      <c r="AL2">
+      <c r="AL2" s="1">
         <v>2032</v>
       </c>
-      <c r="AM2">
+      <c r="AM2" s="1">
         <v>2033</v>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="1">
         <v>2034</v>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="1">
         <v>2035</v>
       </c>
     </row>
     <row r="3" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
       <c r="J3" s="3">
         <v>3521</v>
       </c>
@@ -1190,7 +1226,7 @@
       <c r="U3" s="3">
         <v>555</v>
       </c>
-      <c r="V3" s="4"/>
+      <c r="V3" s="2"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3">
@@ -1215,16 +1251,16 @@
       <c r="AO3" s="3"/>
     </row>
     <row r="4" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
       <c r="J4" s="3">
         <v>350</v>
       </c>
@@ -1265,7 +1301,7 @@
       <c r="U4" s="3">
         <v>1500</v>
       </c>
-      <c r="V4" s="4"/>
+      <c r="V4" s="2"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3">
@@ -1290,16 +1326,16 @@
       <c r="AO4" s="3"/>
     </row>
     <row r="5" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
       <c r="J5" s="3">
         <v>0</v>
       </c>
@@ -1340,7 +1376,7 @@
       <c r="U5" s="3">
         <v>-895</v>
       </c>
-      <c r="V5" s="4"/>
+      <c r="V5" s="2"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3">
@@ -1365,16 +1401,16 @@
       <c r="AO5" s="3"/>
     </row>
     <row r="6" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
       <c r="J6" s="3">
         <v>5629</v>
       </c>
@@ -1414,7 +1450,7 @@
       <c r="U6" s="3">
         <v>2721</v>
       </c>
-      <c r="V6" s="4"/>
+      <c r="V6" s="2"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3">
@@ -1439,16 +1475,16 @@
       <c r="AO6" s="3"/>
     </row>
     <row r="7" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
       <c r="J7" s="3">
         <f t="shared" ref="J7:S7" si="0">SUM(J3:J6)</f>
         <v>9500</v>
@@ -1497,7 +1533,7 @@
         <f t="shared" si="1"/>
         <v>3881</v>
       </c>
-      <c r="V7" s="4"/>
+      <c r="V7" s="2"/>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3">
@@ -1525,16 +1561,16 @@
       <c r="AO7" s="3"/>
     </row>
     <row r="8" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
       <c r="J8" s="3">
         <v>8056</v>
       </c>
@@ -1571,7 +1607,7 @@
       <c r="U8" s="3">
         <v>7143</v>
       </c>
-      <c r="V8" s="4"/>
+      <c r="V8" s="2"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3">
@@ -1598,16 +1634,16 @@
       <c r="AO8" s="3"/>
     </row>
     <row r="9" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="3">
         <v>3427</v>
       </c>
@@ -1644,7 +1680,7 @@
       <c r="U9" s="3">
         <v>23985</v>
       </c>
-      <c r="V9" s="4"/>
+      <c r="V9" s="2"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3">
@@ -1671,16 +1707,16 @@
       <c r="AO9" s="3"/>
     </row>
     <row r="10" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="3">
         <v>15089</v>
       </c>
@@ -1717,7 +1753,7 @@
       <c r="U10" s="3">
         <v>32675</v>
       </c>
-      <c r="V10" s="4"/>
+      <c r="V10" s="2"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3">
@@ -1743,114 +1779,114 @@
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
     </row>
-    <row r="11" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6">
         <v>26572</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="6">
         <f>SUM(K8:K10)</f>
         <v>28194</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="6">
         <f>SUM(L8:L10)</f>
         <v>30050</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="6">
         <f>SUM(M8:M10)</f>
         <v>36744</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="6">
         <v>38290</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="6">
         <f t="shared" ref="O11:T11" si="2">SUM(O8:O10)</f>
         <v>40197</v>
       </c>
-      <c r="P11" s="14">
+      <c r="P11" s="6">
         <f t="shared" si="2"/>
         <v>48640</v>
       </c>
-      <c r="Q11" s="14">
+      <c r="Q11" s="6">
         <f t="shared" si="2"/>
         <v>51906</v>
       </c>
-      <c r="R11" s="14">
+      <c r="R11" s="6">
         <f t="shared" si="2"/>
         <v>54973</v>
       </c>
-      <c r="S11" s="14">
+      <c r="S11" s="6">
         <f t="shared" si="2"/>
         <v>62560</v>
       </c>
-      <c r="T11" s="14">
+      <c r="T11" s="6">
         <f t="shared" si="2"/>
         <v>63165</v>
       </c>
-      <c r="U11" s="14">
+      <c r="U11" s="6">
         <f t="shared" ref="U11" si="3">SUM(U8:U10)</f>
         <v>63803</v>
       </c>
-      <c r="V11" s="13"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6">
+      <c r="V11" s="5"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7">
         <f>SUM(AB8:AB10)</f>
         <v>26572</v>
       </c>
-      <c r="AC11" s="6">
+      <c r="AC11" s="7">
         <f>SUM(AC8:AC10)</f>
         <v>38289</v>
       </c>
-      <c r="AD11" s="6">
+      <c r="AD11" s="7">
         <f>SUM(AD8:AD10)</f>
         <v>54973</v>
       </c>
-      <c r="AE11" s="14">
+      <c r="AE11" s="6">
         <f t="shared" ref="AE11" si="4">SUM(AE8:AE10)</f>
         <v>63803</v>
       </c>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="6"/>
-      <c r="AM11" s="6"/>
-      <c r="AN11" s="6"/>
-      <c r="AO11" s="6"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="7"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7"/>
+      <c r="AL11" s="7"/>
+      <c r="AM11" s="7"/>
+      <c r="AN11" s="7"/>
+      <c r="AO11" s="7"/>
     </row>
     <row r="12" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
@@ -1869,13 +1905,13 @@
       <c r="AO12" s="3"/>
     </row>
     <row r="13" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>406</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>461</v>
       </c>
       <c r="G13" s="3">
@@ -1887,46 +1923,46 @@
       <c r="I13" s="3">
         <v>466</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <f>AB13-I13-H13-G13</f>
         <v>944</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="8">
         <v>457</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="8">
         <v>545</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="8">
         <v>653</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="8">
         <f>AC13-M13-L13-K13</f>
         <v>922</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <v>489</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="8">
         <v>805</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="Q13" s="8">
         <v>1234</v>
       </c>
       <c r="R13" s="3">
         <f>AD13-Q13-P13-O13</f>
         <v>1241</v>
       </c>
-      <c r="S13" s="9">
+      <c r="S13" s="8">
         <v>945</v>
       </c>
-      <c r="T13" s="9">
+      <c r="T13" s="8">
         <v>930</v>
       </c>
-      <c r="U13" s="9">
+      <c r="U13" s="8">
         <v>1309</v>
       </c>
-      <c r="V13" s="9">
+      <c r="V13" s="8">
         <f t="shared" ref="V13" si="5">R13*1.35</f>
         <v>1675.3500000000001</v>
       </c>
@@ -1991,13 +2027,13 @@
       </c>
     </row>
     <row r="14" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>210</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>231</v>
       </c>
       <c r="G14" s="3">
@@ -2009,46 +2045,46 @@
       <c r="I14" s="3">
         <v>228</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <f>AB14-I14-H14-G14</f>
         <v>437</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="8">
         <v>174</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="8">
         <v>248</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="8">
         <v>379</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="8">
         <f>AC14-M14-L14-K14</f>
         <v>680</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="8">
         <v>321</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="8">
         <v>635</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="Q14" s="8">
         <v>447</v>
       </c>
       <c r="R14" s="3">
         <f>AD14-Q14-P14-O14</f>
         <v>1132</v>
       </c>
-      <c r="S14" s="9">
+      <c r="S14" s="8">
         <v>530</v>
       </c>
-      <c r="T14" s="9">
+      <c r="T14" s="8">
         <v>661</v>
       </c>
-      <c r="U14" s="9">
+      <c r="U14" s="8">
         <v>608</v>
       </c>
-      <c r="V14" s="9">
+      <c r="V14" s="8">
         <f>R14*1.2</f>
         <v>1358.3999999999999</v>
       </c>
@@ -2113,13 +2149,13 @@
       </c>
     </row>
     <row r="15" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>141</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>162</v>
       </c>
       <c r="G15" s="3">
@@ -2131,46 +2167,46 @@
       <c r="I15" s="3">
         <v>186</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <f>AB15-I15-H15-G15</f>
         <v>433</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="8">
         <v>185</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="8">
         <v>211</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="8">
         <v>204</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="8">
         <f>AC15-M15-L15-K15</f>
         <v>418</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="8">
         <v>227</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="8">
         <v>272</v>
       </c>
-      <c r="Q15" s="9">
+      <c r="Q15" s="8">
         <v>284</v>
       </c>
       <c r="R15" s="3">
         <f>AD15-Q15-P15-O15</f>
         <v>533</v>
       </c>
-      <c r="S15" s="9">
+      <c r="S15" s="8">
         <v>335</v>
       </c>
-      <c r="T15" s="9">
+      <c r="T15" s="8">
         <v>403</v>
       </c>
-      <c r="U15" s="9">
+      <c r="U15" s="8">
         <v>404</v>
       </c>
-      <c r="V15" s="9">
+      <c r="V15" s="8">
         <f>R15*1.33</f>
         <v>708.89</v>
       </c>
@@ -2235,14 +2271,14 @@
       </c>
     </row>
     <row r="16" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <f>351+158</f>
         <v>509</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <f>307+159</f>
         <v>466</v>
       </c>
@@ -2258,47 +2294,47 @@
         <f>339+187</f>
         <v>526</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <f>AB16-I16-H16-G16</f>
         <v>502</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="8">
         <v>541</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="8">
         <v>484</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="8">
         <f>327+197</f>
         <v>524</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="8">
         <f>AC16-M16-L16-K16</f>
         <v>532</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="8">
         <v>540</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="8">
         <v>513</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="Q16" s="8">
         <v>484</v>
       </c>
       <c r="R16" s="3">
         <f>AD16-Q16-P16-O16</f>
         <v>495</v>
       </c>
-      <c r="S16" s="9">
+      <c r="S16" s="8">
         <v>504</v>
       </c>
-      <c r="T16" s="9">
+      <c r="T16" s="8">
         <v>480</v>
       </c>
-      <c r="U16" s="9">
+      <c r="U16" s="8">
         <v>471</v>
       </c>
-      <c r="V16" s="9">
+      <c r="V16" s="8">
         <f>R16*0.98</f>
         <v>485.09999999999997</v>
       </c>
@@ -2367,13 +2403,13 @@
       </c>
     </row>
     <row r="17" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>2</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>-4</v>
       </c>
       <c r="G17" s="3">
@@ -2385,46 +2421,46 @@
       <c r="I17" s="3">
         <v>9</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <f>AB17-I17-H17-G17</f>
         <v>5</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="8">
         <v>6</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="8">
         <v>9</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="8">
         <v>-2</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="8">
         <f>AC17-M17-L17-K17</f>
         <v>5</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="8">
         <v>5</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="8">
         <v>10</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="Q17" s="8">
         <v>4</v>
       </c>
       <c r="R17" s="3">
         <f>AD17-Q17-P17-O17</f>
         <v>80</v>
       </c>
-      <c r="S17" s="9">
+      <c r="S17" s="8">
         <v>-9</v>
       </c>
-      <c r="T17" s="9">
+      <c r="T17" s="8">
         <v>-43</v>
       </c>
-      <c r="U17" s="9">
+      <c r="U17" s="8">
         <v>-13</v>
       </c>
-      <c r="V17" s="9">
+      <c r="V17" s="8">
         <f>R17*1.5</f>
         <v>120</v>
       </c>
@@ -2488,144 +2524,144 @@
         <v>177.06951718706259</v>
       </c>
     </row>
-    <row r="18" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
+    <row r="18" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <v>1268</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="7">
         <f>SUM(D13:D17)</f>
         <v>1316</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="7">
         <v>1266</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="7">
         <f>SUM(H13:H17)</f>
         <v>1408</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="7">
         <v>1415</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="7">
         <f>SUM(J13:J17)</f>
         <v>2321</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="7">
         <f>SUM(K13:K17)</f>
         <v>1363</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="7">
         <f>SUM(L13:L17)</f>
         <v>1497</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="7">
         <v>1758</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="7">
         <f>SUM(N13:N17)</f>
         <v>2557</v>
       </c>
-      <c r="O18" s="6">
+      <c r="O18" s="7">
         <f>SUM(O13:O17)</f>
         <v>1582</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="7">
         <f>SUM(P13:P17)</f>
         <v>2235</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q18" s="7">
         <f>SUM(Q13:Q17)</f>
         <v>2453</v>
       </c>
-      <c r="R18" s="6">
+      <c r="R18" s="7">
         <f t="shared" ref="R18:V18" si="12">SUM(R13:R17)</f>
         <v>3481</v>
       </c>
-      <c r="S18" s="6">
+      <c r="S18" s="7">
         <f t="shared" si="12"/>
         <v>2305</v>
       </c>
-      <c r="T18" s="6">
+      <c r="T18" s="7">
         <f t="shared" si="12"/>
         <v>2431</v>
       </c>
-      <c r="U18" s="6">
+      <c r="U18" s="7">
         <f>SUM(U13:U17)</f>
         <v>2779</v>
       </c>
-      <c r="V18" s="6">
+      <c r="V18" s="7">
         <f t="shared" si="12"/>
         <v>4347.74</v>
       </c>
-      <c r="Z18" s="6">
+      <c r="Z18" s="7">
         <f t="shared" ref="Z18:AE18" si="13">SUM(Z13:Z17)</f>
         <v>5405</v>
       </c>
-      <c r="AA18" s="6">
+      <c r="AA18" s="7">
         <f t="shared" si="13"/>
         <v>5659</v>
       </c>
-      <c r="AB18" s="6">
+      <c r="AB18" s="7">
         <f t="shared" si="13"/>
         <v>6410</v>
       </c>
-      <c r="AC18" s="6">
+      <c r="AC18" s="7">
         <f t="shared" si="13"/>
         <v>7175</v>
       </c>
-      <c r="AD18" s="6">
+      <c r="AD18" s="7">
         <v>9751</v>
       </c>
-      <c r="AE18" s="6">
+      <c r="AE18" s="7">
         <f t="shared" si="13"/>
         <v>11862.74</v>
       </c>
-      <c r="AF18" s="6">
+      <c r="AF18" s="7">
         <f t="shared" ref="AF18:AO18" si="14">SUM(AF13:AF17)</f>
         <v>14011.873800000001</v>
       </c>
-      <c r="AG18" s="6">
+      <c r="AG18" s="7">
         <f t="shared" si="14"/>
         <v>15246.44224</v>
       </c>
-      <c r="AH18" s="6">
+      <c r="AH18" s="7">
         <f t="shared" si="14"/>
         <v>16022.519471700001</v>
       </c>
-      <c r="AI18" s="6">
+      <c r="AI18" s="7">
         <f t="shared" si="14"/>
         <v>16527.716567721003</v>
       </c>
-      <c r="AJ18" s="6">
+      <c r="AJ18" s="7">
         <f t="shared" si="14"/>
         <v>16900.941494513012</v>
       </c>
-      <c r="AK18" s="6">
+      <c r="AK18" s="7">
         <f t="shared" si="14"/>
         <v>17253.357441215794</v>
       </c>
-      <c r="AL18" s="6">
+      <c r="AL18" s="7">
         <f t="shared" si="14"/>
         <v>17613.744676436647</v>
       </c>
-      <c r="AM18" s="6">
+      <c r="AM18" s="7">
         <f t="shared" si="14"/>
         <v>17982.298555320653</v>
       </c>
-      <c r="AN18" s="6">
+      <c r="AN18" s="7">
         <f t="shared" si="14"/>
         <v>18359.219666886216</v>
       </c>
-      <c r="AO18" s="6">
+      <c r="AO18" s="7">
         <f t="shared" si="14"/>
         <v>18744.71398931888</v>
       </c>
     </row>
     <row r="19" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="3">
@@ -2643,7 +2679,7 @@
       <c r="I19" s="3">
         <v>-138</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="8">
         <f>AB19-I19-H19-G19</f>
         <v>213</v>
       </c>
@@ -2656,7 +2692,7 @@
       <c r="M19" s="3">
         <v>-173</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="8">
         <f>AC19-M19-L19-K19</f>
         <v>22</v>
       </c>
@@ -2743,7 +2779,7 @@
       </c>
     </row>
     <row r="20" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="3">
@@ -2761,7 +2797,7 @@
       <c r="I20" s="3">
         <v>797</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="8">
         <f>AB20-I20-H20-G20</f>
         <v>988</v>
       </c>
@@ -2774,7 +2810,7 @@
       <c r="M20" s="3">
         <v>1007</v>
       </c>
-      <c r="N20" s="9">
+      <c r="N20" s="8">
         <f>AC20-M20-L20-K20</f>
         <v>1174</v>
       </c>
@@ -2859,7 +2895,7 @@
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="3">
@@ -2877,7 +2913,7 @@
       <c r="I21" s="3">
         <v>440</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="8">
         <f>AB21-I21-H21-G21</f>
         <v>475</v>
       </c>
@@ -2890,7 +2926,7 @@
       <c r="M21" s="3">
         <v>495</v>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="8">
         <f>AC21-M21-L21-K21</f>
         <v>545</v>
       </c>
@@ -2973,290 +3009,290 @@
         <v>5248.5199170092865</v>
       </c>
     </row>
-    <row r="22" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
+    <row r="22" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="7">
         <f>SUM(C19:C21)</f>
         <v>994</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="7">
         <f>SUM(D19:D21)</f>
         <v>1029</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="7">
         <f t="shared" ref="G22:P22" si="18">SUM(G19:G21)</f>
         <v>999</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="7">
         <f t="shared" si="18"/>
         <v>1092</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="7">
         <f t="shared" si="18"/>
         <v>1099</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="7">
         <f t="shared" si="18"/>
         <v>1676</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="7">
         <f t="shared" si="18"/>
         <v>1061</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="7">
         <f t="shared" si="18"/>
         <v>1155</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="7">
         <f t="shared" si="18"/>
         <v>1329</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="7">
         <f t="shared" si="18"/>
         <v>1741</v>
       </c>
-      <c r="O22" s="6">
+      <c r="O22" s="7">
         <f t="shared" si="18"/>
         <v>1188</v>
       </c>
-      <c r="P22" s="6">
+      <c r="P22" s="7">
         <f t="shared" si="18"/>
         <v>1664</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="Q22" s="7">
         <f t="shared" ref="Q22:R22" si="19">SUM(Q19:Q21)</f>
         <v>1872</v>
       </c>
-      <c r="R22" s="6">
+      <c r="R22" s="7">
         <f t="shared" si="19"/>
         <v>2341</v>
       </c>
-      <c r="S22" s="6">
+      <c r="S22" s="7">
         <f t="shared" ref="S22:U22" si="20">SUM(S19:S21)</f>
         <v>1763</v>
       </c>
-      <c r="T22" s="6">
+      <c r="T22" s="7">
         <f t="shared" si="20"/>
         <v>1836</v>
       </c>
-      <c r="U22" s="6">
+      <c r="U22" s="7">
         <f t="shared" si="20"/>
         <v>2061</v>
       </c>
-      <c r="V22" s="6">
+      <c r="V22" s="7">
         <f t="shared" ref="V22" si="21">V18-V23</f>
         <v>2869.5083999999997</v>
       </c>
-      <c r="Z22" s="6">
+      <c r="Z22" s="7">
         <f>SUM(Z19:Z21)</f>
         <v>4187</v>
       </c>
-      <c r="AA22" s="6">
+      <c r="AA22" s="7">
         <f>SUM(AA19:AA21)</f>
         <v>4271</v>
       </c>
-      <c r="AB22" s="6">
+      <c r="AB22" s="7">
         <f>SUM(AB19:AB21)</f>
         <v>4866</v>
       </c>
-      <c r="AC22" s="6">
+      <c r="AC22" s="7">
         <f>SUM(AC19:AC21)</f>
         <v>5286</v>
       </c>
-      <c r="AD22" s="6">
+      <c r="AD22" s="7">
         <f>SUM(AD19:AD21)</f>
         <v>7065</v>
       </c>
-      <c r="AE22" s="6">
+      <c r="AE22" s="7">
         <f>SUM(S22:V22)</f>
         <v>8529.5083999999988</v>
       </c>
-      <c r="AF22" s="6">
+      <c r="AF22" s="7">
         <f t="shared" ref="AF22:AO22" si="22">SUM(AF19:AF21)</f>
         <v>10228.667874000002</v>
       </c>
-      <c r="AG22" s="6">
+      <c r="AG22" s="7">
         <f t="shared" si="22"/>
         <v>11129.9028352</v>
       </c>
-      <c r="AH22" s="6">
+      <c r="AH22" s="7">
         <f t="shared" si="22"/>
         <v>11696.439214341</v>
       </c>
-      <c r="AI22" s="6">
+      <c r="AI22" s="7">
         <f t="shared" si="22"/>
         <v>12065.233094436333</v>
       </c>
-      <c r="AJ22" s="6">
+      <c r="AJ22" s="7">
         <f t="shared" si="22"/>
         <v>12337.6872909945</v>
       </c>
-      <c r="AK22" s="6">
+      <c r="AK22" s="7">
         <f t="shared" si="22"/>
         <v>12594.95093208753</v>
       </c>
-      <c r="AL22" s="6">
+      <c r="AL22" s="7">
         <f t="shared" si="22"/>
         <v>12858.033613798754</v>
       </c>
-      <c r="AM22" s="6">
+      <c r="AM22" s="7">
         <f t="shared" si="22"/>
         <v>13127.077945384077</v>
       </c>
-      <c r="AN22" s="6">
+      <c r="AN22" s="7">
         <f t="shared" si="22"/>
         <v>13402.230356826938</v>
       </c>
-      <c r="AO22" s="6">
+      <c r="AO22" s="7">
         <f t="shared" si="22"/>
         <v>13683.641212202783</v>
       </c>
     </row>
-    <row r="23" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
+    <row r="23" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
         <f>C18-C22</f>
         <v>274</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="7">
         <f>D18-D22</f>
         <v>287</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="7">
         <f t="shared" ref="G23:P23" si="23">G18-G22</f>
         <v>267</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="7">
         <f t="shared" si="23"/>
         <v>316</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="7">
         <f t="shared" si="23"/>
         <v>316</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="7">
         <f t="shared" si="23"/>
         <v>645</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="7">
         <f t="shared" si="23"/>
         <v>302</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="7">
         <f t="shared" si="23"/>
         <v>342</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="7">
         <f t="shared" si="23"/>
         <v>429</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="7">
         <f t="shared" si="23"/>
         <v>816</v>
       </c>
-      <c r="O23" s="6">
+      <c r="O23" s="7">
         <f t="shared" si="23"/>
         <v>394</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P23" s="7">
         <f t="shared" si="23"/>
         <v>571</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="Q23" s="7">
         <f t="shared" ref="Q23:R23" si="24">Q18-Q22</f>
         <v>581</v>
       </c>
-      <c r="R23" s="6">
+      <c r="R23" s="7">
         <f t="shared" si="24"/>
         <v>1140</v>
       </c>
-      <c r="S23" s="6">
+      <c r="S23" s="7">
         <f t="shared" ref="S23:U23" si="25">S18-S22</f>
         <v>542</v>
       </c>
-      <c r="T23" s="6">
+      <c r="T23" s="7">
         <f t="shared" si="25"/>
         <v>595</v>
       </c>
-      <c r="U23" s="6">
+      <c r="U23" s="7">
         <f t="shared" si="25"/>
         <v>718</v>
       </c>
-      <c r="V23" s="6">
+      <c r="V23" s="7">
         <f>V18*0.34</f>
         <v>1478.2316000000001</v>
       </c>
-      <c r="Z23" s="6">
+      <c r="Z23" s="7">
         <f>Z18-Z22</f>
         <v>1218</v>
       </c>
-      <c r="AA23" s="6">
+      <c r="AA23" s="7">
         <f>AA18-AA22</f>
         <v>1388</v>
       </c>
-      <c r="AB23" s="6">
+      <c r="AB23" s="7">
         <f>AB18-AB22</f>
         <v>1544</v>
       </c>
-      <c r="AC23" s="6">
+      <c r="AC23" s="7">
         <f>AC18-AC22</f>
         <v>1889</v>
       </c>
-      <c r="AD23" s="6">
+      <c r="AD23" s="7">
         <f>AD18-AD22</f>
         <v>2686</v>
       </c>
-      <c r="AE23" s="6">
+      <c r="AE23" s="7">
         <f t="shared" ref="AE23:AO23" si="26">AE18-AE22</f>
         <v>3333.231600000001</v>
       </c>
-      <c r="AF23" s="6">
+      <c r="AF23" s="7">
         <f t="shared" si="26"/>
         <v>3783.2059259999987</v>
       </c>
-      <c r="AG23" s="6">
+      <c r="AG23" s="7">
         <f t="shared" si="26"/>
         <v>4116.5394047999998</v>
       </c>
-      <c r="AH23" s="6">
+      <c r="AH23" s="7">
         <f t="shared" si="26"/>
         <v>4326.0802573590008</v>
       </c>
-      <c r="AI23" s="6">
+      <c r="AI23" s="7">
         <f t="shared" si="26"/>
         <v>4462.4834732846703</v>
       </c>
-      <c r="AJ23" s="6">
+      <c r="AJ23" s="7">
         <f t="shared" si="26"/>
         <v>4563.2542035185124</v>
       </c>
-      <c r="AK23" s="6">
+      <c r="AK23" s="7">
         <f t="shared" si="26"/>
         <v>4658.4065091282646</v>
       </c>
-      <c r="AL23" s="6">
+      <c r="AL23" s="7">
         <f t="shared" si="26"/>
         <v>4755.7110626378926</v>
       </c>
-      <c r="AM23" s="6">
+      <c r="AM23" s="7">
         <f t="shared" si="26"/>
         <v>4855.2206099365758</v>
       </c>
-      <c r="AN23" s="6">
+      <c r="AN23" s="7">
         <f t="shared" si="26"/>
         <v>4956.9893100592781</v>
       </c>
-      <c r="AO23" s="6">
+      <c r="AO23" s="7">
         <f t="shared" si="26"/>
         <v>5061.0727771160964</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="3">
@@ -3274,7 +3310,7 @@
       <c r="I24" s="3">
         <v>63</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="8">
         <f>AB24-I24-H24-G24</f>
         <v>64</v>
       </c>
@@ -3287,7 +3323,7 @@
       <c r="M24" s="3">
         <v>79</v>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="8">
         <f>AC24-M24-L24-K24</f>
         <v>103</v>
       </c>
@@ -3344,7 +3380,7 @@
       <c r="AO24" s="3"/>
     </row>
     <row r="25" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="3">
@@ -3362,7 +3398,7 @@
       <c r="I25" s="3">
         <v>-53</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="8">
         <f>AB25-I25-H25-G25</f>
         <v>-100</v>
       </c>
@@ -3375,7 +3411,7 @@
       <c r="M25" s="3">
         <v>-41</v>
       </c>
-      <c r="N25" s="9">
+      <c r="N25" s="8">
         <f>AC25-M25-L25-K25</f>
         <v>-58</v>
       </c>
@@ -3433,7 +3469,7 @@
       <c r="AO25" s="3"/>
     </row>
     <row r="26" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="3">
@@ -3451,7 +3487,7 @@
       <c r="I26" s="3">
         <v>194</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="8">
         <f>AB26-I26-H26-G26</f>
         <v>255</v>
       </c>
@@ -3464,7 +3500,7 @@
       <c r="M26" s="3">
         <v>219</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N26" s="8">
         <f>AC26-M26-L26-K26</f>
         <v>305</v>
       </c>
@@ -3522,7 +3558,7 @@
       <c r="AO26" s="3"/>
     </row>
     <row r="27" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="3">
@@ -3662,149 +3698,149 @@
         <v>1978.0454037557079</v>
       </c>
     </row>
-    <row r="28" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="s">
+    <row r="28" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="7">
         <f>C23-C27</f>
         <v>88</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="7">
         <f>D23-D27</f>
         <v>105</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="7">
         <f t="shared" ref="G28:P28" si="32">G23-G27</f>
         <v>83</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="7">
         <f t="shared" si="32"/>
         <v>127</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="7">
         <f t="shared" si="32"/>
         <v>112</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="7">
         <f t="shared" si="32"/>
         <v>426</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="7">
         <f t="shared" si="32"/>
         <v>89</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="7">
         <f t="shared" si="32"/>
         <v>118</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="7">
         <f t="shared" si="32"/>
         <v>172</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28" s="7">
         <f t="shared" si="32"/>
         <v>466</v>
       </c>
-      <c r="O28" s="6">
+      <c r="O28" s="7">
         <f t="shared" si="32"/>
         <v>117</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="7">
         <f t="shared" si="32"/>
         <v>242</v>
       </c>
-      <c r="Q28" s="6">
+      <c r="Q28" s="7">
         <f t="shared" ref="Q28:R28" si="33">Q23-Q27</f>
         <v>290</v>
       </c>
-      <c r="R28" s="6">
+      <c r="R28" s="7">
         <f t="shared" si="33"/>
         <v>742</v>
       </c>
-      <c r="S28" s="6">
+      <c r="S28" s="7">
         <f t="shared" ref="S28:V28" si="34">S23-S27</f>
         <v>179</v>
       </c>
-      <c r="T28" s="6">
+      <c r="T28" s="7">
         <f t="shared" si="34"/>
         <v>232</v>
       </c>
-      <c r="U28" s="6">
+      <c r="U28" s="7">
         <f t="shared" si="34"/>
         <v>323</v>
       </c>
-      <c r="V28" s="6">
+      <c r="V28" s="7">
         <f t="shared" si="34"/>
         <v>1068.2316000000001</v>
       </c>
-      <c r="Z28" s="6">
+      <c r="Z28" s="7">
         <f>Z23-Z27</f>
         <v>408</v>
       </c>
-      <c r="AA28" s="6">
+      <c r="AA28" s="7">
         <f>AA23-AA27</f>
         <v>615</v>
       </c>
-      <c r="AB28" s="6">
+      <c r="AB28" s="7">
         <f>AB23-AB27</f>
         <v>748</v>
       </c>
-      <c r="AC28" s="6">
+      <c r="AC28" s="7">
         <f>AC23-AC27</f>
         <v>845</v>
       </c>
-      <c r="AD28" s="6">
+      <c r="AD28" s="7">
         <f t="shared" ref="AD28:AO28" si="35">AD23-AD27</f>
         <v>1391</v>
       </c>
-      <c r="AE28" s="6">
+      <c r="AE28" s="7">
         <f t="shared" si="35"/>
         <v>1802.231600000001</v>
       </c>
-      <c r="AF28" s="6">
+      <c r="AF28" s="7">
         <f t="shared" si="35"/>
         <v>2175.6559259999985</v>
       </c>
-      <c r="AG28" s="6">
+      <c r="AG28" s="7">
         <f t="shared" si="35"/>
         <v>2444.6874048</v>
       </c>
-      <c r="AH28" s="6">
+      <c r="AH28" s="7">
         <f t="shared" si="35"/>
         <v>2604.0726973590008</v>
       </c>
-      <c r="AI28" s="6">
+      <c r="AI28" s="7">
         <f t="shared" si="35"/>
         <v>2706.0357620846698</v>
       </c>
-      <c r="AJ28" s="6">
+      <c r="AJ28" s="7">
         <f t="shared" si="35"/>
         <v>2771.6775380945123</v>
       </c>
-      <c r="AK28" s="6">
+      <c r="AK28" s="7">
         <f t="shared" si="35"/>
         <v>2830.9983103957848</v>
       </c>
-      <c r="AL28" s="6">
+      <c r="AL28" s="7">
         <f t="shared" si="35"/>
         <v>2891.7546999307629</v>
       </c>
-      <c r="AM28" s="6">
+      <c r="AM28" s="7">
         <f t="shared" si="35"/>
         <v>2953.9851199753034</v>
       </c>
-      <c r="AN28" s="6">
+      <c r="AN28" s="7">
         <f t="shared" si="35"/>
         <v>3017.7291102987801</v>
       </c>
-      <c r="AO28" s="6">
+      <c r="AO28" s="7">
         <f t="shared" si="35"/>
         <v>3083.0273733603885</v>
       </c>
     </row>
     <row r="29" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="3">
@@ -3822,7 +3858,7 @@
       <c r="I29" s="3">
         <v>-8</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="8">
         <f>AB29-I29-H29-G29</f>
         <v>-16</v>
       </c>
@@ -3835,7 +3871,7 @@
       <c r="M29" s="3">
         <v>-6</v>
       </c>
-      <c r="N29" s="9">
+      <c r="N29" s="8">
         <f>AC29-M29-L29-K29</f>
         <v>-63</v>
       </c>
@@ -3890,7 +3926,7 @@
       <c r="AO29" s="3"/>
     </row>
     <row r="30" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="3">
@@ -3908,7 +3944,7 @@
       <c r="I30" s="3">
         <v>3</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="8">
         <f>AB30-I30-H30-G30</f>
         <v>4</v>
       </c>
@@ -3921,7 +3957,7 @@
       <c r="M30" s="3">
         <v>8</v>
       </c>
-      <c r="N30" s="9">
+      <c r="N30" s="8">
         <f>AC30-M30-L30-K30</f>
         <v>-1</v>
       </c>
@@ -3976,7 +4012,7 @@
       <c r="AO30" s="3"/>
     </row>
     <row r="31" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="3">
@@ -3994,7 +4030,7 @@
       <c r="I31" s="3">
         <v>-1</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="8">
         <f>AB31-I31-H31-G31</f>
         <v>-9</v>
       </c>
@@ -4007,7 +4043,7 @@
       <c r="M31" s="3">
         <v>-5</v>
       </c>
-      <c r="N31" s="9">
+      <c r="N31" s="8">
         <f>AC31-M31-L31-K31</f>
         <v>-5</v>
       </c>
@@ -4062,7 +4098,7 @@
       <c r="AO31" s="3"/>
     </row>
     <row r="32" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C32" s="3">
@@ -4080,7 +4116,7 @@
       <c r="I32" s="3">
         <v>7</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="8">
         <f>AB32-I32-H32-G32</f>
         <v>10</v>
       </c>
@@ -4093,7 +4129,7 @@
       <c r="M32" s="3">
         <v>30</v>
       </c>
-      <c r="N32" s="9">
+      <c r="N32" s="8">
         <f>AC32-M32-L32-K32</f>
         <v>39</v>
       </c>
@@ -4148,7 +4184,7 @@
       <c r="AO32" s="3"/>
     </row>
     <row r="33" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="3">
@@ -4288,149 +4324,149 @@
         <v>178.40489935793224</v>
       </c>
     </row>
-    <row r="34" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
+    <row r="34" spans="2:152" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="7">
         <f>C28-C33</f>
         <v>76</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="7">
         <f>D28-D33</f>
         <v>103</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="7">
         <f t="shared" ref="G34:P34" si="41">G28-G33</f>
         <v>73</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="7">
         <f t="shared" si="41"/>
         <v>98</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="7">
         <f t="shared" si="41"/>
         <v>111</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="7">
         <f t="shared" si="41"/>
         <v>437</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="7">
         <f t="shared" si="41"/>
         <v>69</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="7">
         <f t="shared" si="41"/>
         <v>104</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="7">
         <f t="shared" si="41"/>
         <v>145</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="7">
         <f t="shared" si="41"/>
         <v>496</v>
       </c>
-      <c r="O34" s="6">
+      <c r="O34" s="7">
         <f t="shared" si="41"/>
         <v>86</v>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="7">
         <f t="shared" si="41"/>
         <v>208</v>
       </c>
-      <c r="Q34" s="6">
+      <c r="Q34" s="7">
         <f t="shared" ref="Q34:V34" si="42">Q28-Q33</f>
         <v>247</v>
       </c>
-      <c r="R34" s="6">
+      <c r="R34" s="7">
         <f t="shared" si="42"/>
         <v>687</v>
       </c>
-      <c r="S34" s="6">
+      <c r="S34" s="7">
         <f t="shared" si="42"/>
         <v>146</v>
       </c>
-      <c r="T34" s="6">
+      <c r="T34" s="7">
         <f t="shared" si="42"/>
         <v>223</v>
       </c>
-      <c r="U34" s="6">
+      <c r="U34" s="7">
         <f t="shared" si="42"/>
         <v>290</v>
       </c>
-      <c r="V34" s="6">
+      <c r="V34" s="7">
         <f t="shared" si="42"/>
         <v>1010.4816000000001</v>
       </c>
-      <c r="Z34" s="6">
+      <c r="Z34" s="7">
         <f>Z28-Z33</f>
         <v>366</v>
       </c>
-      <c r="AA34" s="6">
+      <c r="AA34" s="7">
         <f>AA28-AA33</f>
         <v>582</v>
       </c>
-      <c r="AB34" s="6">
+      <c r="AB34" s="7">
         <f>AB28-AB33</f>
         <v>719</v>
       </c>
-      <c r="AC34" s="6">
+      <c r="AC34" s="7">
         <f>AC28-AC33</f>
         <v>814</v>
       </c>
-      <c r="AD34" s="6">
+      <c r="AD34" s="7">
         <f t="shared" ref="AD34:AO34" si="43">AD28-AD33</f>
         <v>1228</v>
       </c>
-      <c r="AE34" s="6">
+      <c r="AE34" s="7">
         <f t="shared" si="43"/>
         <v>1669.481600000001</v>
       </c>
-      <c r="AF34" s="6">
+      <c r="AF34" s="7">
         <f t="shared" si="43"/>
         <v>2038.9234259999985</v>
       </c>
-      <c r="AG34" s="6">
+      <c r="AG34" s="7">
         <f t="shared" si="43"/>
         <v>2303.8529297999999</v>
       </c>
-      <c r="AH34" s="6">
+      <c r="AH34" s="7">
         <f t="shared" si="43"/>
         <v>2459.013188109001</v>
       </c>
-      <c r="AI34" s="6">
+      <c r="AI34" s="7">
         <f t="shared" si="43"/>
         <v>2556.6244675571697</v>
       </c>
-      <c r="AJ34" s="6">
+      <c r="AJ34" s="7">
         <f t="shared" si="43"/>
         <v>2617.7839047311872</v>
       </c>
-      <c r="AK34" s="6">
+      <c r="AK34" s="7">
         <f t="shared" si="43"/>
         <v>2672.4878680315601</v>
       </c>
-      <c r="AL34" s="6">
+      <c r="AL34" s="7">
         <f t="shared" si="43"/>
         <v>2728.4889442956114</v>
       </c>
-      <c r="AM34" s="6">
+      <c r="AM34" s="7">
         <f t="shared" si="43"/>
         <v>2785.8213916710974</v>
       </c>
-      <c r="AN34" s="6">
+      <c r="AN34" s="7">
         <f t="shared" si="43"/>
         <v>2844.5204701454477</v>
       </c>
-      <c r="AO34" s="6">
+      <c r="AO34" s="7">
         <f t="shared" si="43"/>
         <v>2904.6224740024563</v>
       </c>
     </row>
     <row r="35" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="3">
@@ -4448,7 +4484,7 @@
       <c r="I35" s="3">
         <v>30</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="8">
         <f>AB35-I35-H35-G35</f>
         <v>108</v>
       </c>
@@ -4461,7 +4497,7 @@
       <c r="M35" s="3">
         <v>36</v>
       </c>
-      <c r="N35" s="9">
+      <c r="N35" s="8">
         <f>AC35-M35-L35-K35</f>
         <v>98</v>
       </c>
@@ -4552,7 +4588,7 @@
       </c>
     </row>
     <row r="36" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C36" s="3">
@@ -4575,7 +4611,7 @@
         <f>-5+10</f>
         <v>5</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="8">
         <f>AB36-I36-H36-G36</f>
         <v>32</v>
       </c>
@@ -4591,7 +4627,7 @@
         <f>-2+9</f>
         <v>7</v>
       </c>
-      <c r="N36" s="9">
+      <c r="N36" s="8">
         <f>AC36-M36-L36-K36</f>
         <v>71</v>
       </c>
@@ -4689,593 +4725,593 @@
         <v>290.46224740024564</v>
       </c>
     </row>
-    <row r="37" spans="2:152" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="2:152" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="7">
         <f>C34-C35-C36</f>
         <v>50</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="7">
         <f>D34-D35-D36</f>
         <v>-37</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="7">
         <f t="shared" ref="G37:P37" si="48">G34-G35-G36</f>
         <v>46</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37" s="7">
         <f t="shared" si="48"/>
         <v>57</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="7">
         <f t="shared" si="48"/>
         <v>76</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="7">
         <f t="shared" si="48"/>
         <v>297</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="7">
         <f t="shared" si="48"/>
         <v>48</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="7">
         <f t="shared" si="48"/>
         <v>57</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="7">
         <f t="shared" si="48"/>
         <v>102</v>
       </c>
-      <c r="N37" s="6">
+      <c r="N37" s="7">
         <f t="shared" si="48"/>
         <v>327</v>
       </c>
-      <c r="O37" s="6">
+      <c r="O37" s="7">
         <f t="shared" si="48"/>
         <v>50</v>
       </c>
-      <c r="P37" s="6">
+      <c r="P37" s="7">
         <f t="shared" si="48"/>
         <v>63</v>
       </c>
-      <c r="Q37" s="6">
+      <c r="Q37" s="7">
         <f t="shared" ref="Q37:R37" si="49">Q34-Q35-Q36</f>
         <v>135</v>
       </c>
-      <c r="R37" s="6">
+      <c r="R37" s="7">
         <f t="shared" si="49"/>
         <v>469</v>
       </c>
-      <c r="S37" s="6">
+      <c r="S37" s="7">
         <f t="shared" ref="S37:V37" si="50">S34-S35-S36</f>
         <v>83</v>
       </c>
-      <c r="T37" s="6">
+      <c r="T37" s="7">
         <f t="shared" si="50"/>
         <v>143</v>
       </c>
-      <c r="U37" s="6">
+      <c r="U37" s="7">
         <f t="shared" si="50"/>
         <v>154</v>
       </c>
-      <c r="V37" s="6">
+      <c r="V37" s="7">
         <f t="shared" si="50"/>
         <v>636.60340799999994</v>
       </c>
-      <c r="Z37" s="6">
+      <c r="Z37" s="7">
         <f>Z34-Z35-Z36</f>
         <v>-27</v>
       </c>
-      <c r="AA37" s="6">
+      <c r="AA37" s="7">
         <f>AA34-AA35-AA36</f>
         <v>291</v>
       </c>
-      <c r="AB37" s="6">
+      <c r="AB37" s="7">
         <f>AB34-AB35-AB36</f>
         <v>476</v>
       </c>
-      <c r="AC37" s="6">
+      <c r="AC37" s="7">
         <f>AC34-AC35-AC36</f>
         <v>534</v>
       </c>
-      <c r="AD37" s="6">
+      <c r="AD37" s="7">
         <f t="shared" ref="AD37:AO37" si="51">AD34-AD35-AD36</f>
         <v>717</v>
       </c>
-      <c r="AE37" s="6">
+      <c r="AE37" s="7">
         <f t="shared" si="51"/>
         <v>1016.6034080000009</v>
       </c>
-      <c r="AF37" s="6">
+      <c r="AF37" s="7">
         <f t="shared" si="51"/>
         <v>1325.300226899999</v>
       </c>
-      <c r="AG37" s="6">
+      <c r="AG37" s="7">
         <f t="shared" si="51"/>
         <v>1497.50440437</v>
       </c>
-      <c r="AH37" s="6">
+      <c r="AH37" s="7">
         <f t="shared" si="51"/>
         <v>1598.3585722708506</v>
       </c>
-      <c r="AI37" s="6">
+      <c r="AI37" s="7">
         <f t="shared" si="51"/>
         <v>1661.8059039121604</v>
       </c>
-      <c r="AJ37" s="6">
+      <c r="AJ37" s="7">
         <f t="shared" si="51"/>
         <v>1701.5595380752716</v>
       </c>
-      <c r="AK37" s="6">
+      <c r="AK37" s="7">
         <f t="shared" si="51"/>
         <v>1737.1171142205142</v>
       </c>
-      <c r="AL37" s="6">
+      <c r="AL37" s="7">
         <f t="shared" si="51"/>
         <v>1773.5178137921473</v>
       </c>
-      <c r="AM37" s="6">
+      <c r="AM37" s="7">
         <f t="shared" si="51"/>
         <v>1810.7839045862133</v>
       </c>
-      <c r="AN37" s="6">
+      <c r="AN37" s="7">
         <f t="shared" si="51"/>
         <v>1848.9383055945409</v>
       </c>
-      <c r="AO37" s="6">
+      <c r="AO37" s="7">
         <f t="shared" si="51"/>
         <v>1888.0046081015969</v>
       </c>
-      <c r="AP37" s="1">
+      <c r="AP37" s="4">
         <f>AO37*(1+$AS$45)</f>
         <v>1869.1245620205809</v>
       </c>
-      <c r="AQ37" s="1">
+      <c r="AQ37" s="4">
         <f t="shared" ref="AQ37:DB37" si="52">AP37*(1+$AS$45)</f>
         <v>1850.4333164003751</v>
       </c>
-      <c r="AR37" s="1">
+      <c r="AR37" s="4">
         <f t="shared" si="52"/>
         <v>1831.9289832363713</v>
       </c>
-      <c r="AS37" s="1">
+      <c r="AS37" s="4">
         <f t="shared" si="52"/>
         <v>1813.6096934040077</v>
       </c>
-      <c r="AT37" s="1">
+      <c r="AT37" s="4">
         <f t="shared" si="52"/>
         <v>1795.4735964699676</v>
       </c>
-      <c r="AU37" s="1">
+      <c r="AU37" s="4">
         <f t="shared" si="52"/>
         <v>1777.5188605052679</v>
       </c>
-      <c r="AV37" s="1">
+      <c r="AV37" s="4">
         <f t="shared" si="52"/>
         <v>1759.7436719002151</v>
       </c>
-      <c r="AW37" s="1">
+      <c r="AW37" s="4">
         <f t="shared" si="52"/>
         <v>1742.1462351812129</v>
       </c>
-      <c r="AX37" s="1">
+      <c r="AX37" s="4">
         <f t="shared" si="52"/>
         <v>1724.7247728294008</v>
       </c>
-      <c r="AY37" s="1">
+      <c r="AY37" s="4">
         <f t="shared" si="52"/>
         <v>1707.4775251011067</v>
       </c>
-      <c r="AZ37" s="1">
+      <c r="AZ37" s="4">
         <f t="shared" si="52"/>
         <v>1690.4027498500957</v>
       </c>
-      <c r="BA37" s="1">
+      <c r="BA37" s="4">
         <f t="shared" si="52"/>
         <v>1673.4987223515948</v>
       </c>
-      <c r="BB37" s="1">
+      <c r="BB37" s="4">
         <f t="shared" si="52"/>
         <v>1656.7637351280789</v>
       </c>
-      <c r="BC37" s="1">
+      <c r="BC37" s="4">
         <f t="shared" si="52"/>
         <v>1640.1960977767981</v>
       </c>
-      <c r="BD37" s="1">
+      <c r="BD37" s="4">
         <f t="shared" si="52"/>
         <v>1623.7941367990302</v>
       </c>
-      <c r="BE37" s="1">
+      <c r="BE37" s="4">
         <f t="shared" si="52"/>
         <v>1607.5561954310399</v>
       </c>
-      <c r="BF37" s="1">
+      <c r="BF37" s="4">
         <f t="shared" si="52"/>
         <v>1591.4806334767295</v>
       </c>
-      <c r="BG37" s="1">
+      <c r="BG37" s="4">
         <f t="shared" si="52"/>
         <v>1575.5658271419622</v>
       </c>
-      <c r="BH37" s="1">
+      <c r="BH37" s="4">
         <f t="shared" si="52"/>
         <v>1559.8101688705426</v>
       </c>
-      <c r="BI37" s="1">
+      <c r="BI37" s="4">
         <f t="shared" si="52"/>
         <v>1544.2120671818373</v>
       </c>
-      <c r="BJ37" s="1">
+      <c r="BJ37" s="4">
         <f t="shared" si="52"/>
         <v>1528.7699465100188</v>
       </c>
-      <c r="BK37" s="1">
+      <c r="BK37" s="4">
         <f t="shared" si="52"/>
         <v>1513.4822470449187</v>
       </c>
-      <c r="BL37" s="1">
+      <c r="BL37" s="4">
         <f t="shared" si="52"/>
         <v>1498.3474245744694</v>
       </c>
-      <c r="BM37" s="1">
+      <c r="BM37" s="4">
         <f t="shared" si="52"/>
         <v>1483.3639503287247</v>
       </c>
-      <c r="BN37" s="1">
+      <c r="BN37" s="4">
         <f t="shared" si="52"/>
         <v>1468.5303108254375</v>
       </c>
-      <c r="BO37" s="1">
+      <c r="BO37" s="4">
         <f t="shared" si="52"/>
         <v>1453.8450077171831</v>
       </c>
-      <c r="BP37" s="1">
+      <c r="BP37" s="4">
         <f t="shared" si="52"/>
         <v>1439.3065576400113</v>
       </c>
-      <c r="BQ37" s="1">
+      <c r="BQ37" s="4">
         <f t="shared" si="52"/>
         <v>1424.9134920636111</v>
       </c>
-      <c r="BR37" s="1">
+      <c r="BR37" s="4">
         <f t="shared" si="52"/>
         <v>1410.6643571429749</v>
       </c>
-      <c r="BS37" s="1">
+      <c r="BS37" s="4">
         <f t="shared" si="52"/>
         <v>1396.5577135715453</v>
       </c>
-      <c r="BT37" s="1">
+      <c r="BT37" s="4">
         <f t="shared" si="52"/>
         <v>1382.5921364358298</v>
       </c>
-      <c r="BU37" s="1">
+      <c r="BU37" s="4">
         <f t="shared" si="52"/>
         <v>1368.7662150714716</v>
       </c>
-      <c r="BV37" s="1">
+      <c r="BV37" s="4">
         <f t="shared" si="52"/>
         <v>1355.0785529207569</v>
       </c>
-      <c r="BW37" s="1">
+      <c r="BW37" s="4">
         <f t="shared" si="52"/>
         <v>1341.5277673915493</v>
       </c>
-      <c r="BX37" s="1">
+      <c r="BX37" s="4">
         <f t="shared" si="52"/>
         <v>1328.1124897176339</v>
       </c>
-      <c r="BY37" s="1">
+      <c r="BY37" s="4">
         <f t="shared" si="52"/>
         <v>1314.8313648204576</v>
       </c>
-      <c r="BZ37" s="1">
+      <c r="BZ37" s="4">
         <f t="shared" si="52"/>
         <v>1301.683051172253</v>
       </c>
-      <c r="CA37" s="1">
+      <c r="CA37" s="4">
         <f t="shared" si="52"/>
         <v>1288.6662206605306</v>
       </c>
-      <c r="CB37" s="1">
+      <c r="CB37" s="4">
         <f t="shared" si="52"/>
         <v>1275.7795584539253</v>
       </c>
-      <c r="CC37" s="1">
+      <c r="CC37" s="4">
         <f t="shared" si="52"/>
         <v>1263.0217628693861</v>
       </c>
-      <c r="CD37" s="1">
+      <c r="CD37" s="4">
         <f t="shared" si="52"/>
         <v>1250.3915452406923</v>
       </c>
-      <c r="CE37" s="1">
+      <c r="CE37" s="4">
         <f t="shared" si="52"/>
         <v>1237.8876297882853</v>
       </c>
-      <c r="CF37" s="1">
+      <c r="CF37" s="4">
         <f t="shared" si="52"/>
         <v>1225.5087534904023</v>
       </c>
-      <c r="CG37" s="1">
+      <c r="CG37" s="4">
         <f t="shared" si="52"/>
         <v>1213.2536659554983</v>
       </c>
-      <c r="CH37" s="1">
+      <c r="CH37" s="4">
         <f t="shared" si="52"/>
         <v>1201.1211292959433</v>
       </c>
-      <c r="CI37" s="1">
+      <c r="CI37" s="4">
         <f t="shared" si="52"/>
         <v>1189.1099180029839</v>
       </c>
-      <c r="CJ37" s="1">
+      <c r="CJ37" s="4">
         <f t="shared" si="52"/>
         <v>1177.2188188229541</v>
       </c>
-      <c r="CK37" s="1">
+      <c r="CK37" s="4">
         <f t="shared" si="52"/>
         <v>1165.4466306347244</v>
       </c>
-      <c r="CL37" s="1">
+      <c r="CL37" s="4">
         <f t="shared" si="52"/>
         <v>1153.7921643283771</v>
       </c>
-      <c r="CM37" s="1">
+      <c r="CM37" s="4">
         <f t="shared" si="52"/>
         <v>1142.2542426850932</v>
       </c>
-      <c r="CN37" s="1">
+      <c r="CN37" s="4">
         <f t="shared" si="52"/>
         <v>1130.8317002582423</v>
       </c>
-      <c r="CO37" s="1">
+      <c r="CO37" s="4">
         <f t="shared" si="52"/>
         <v>1119.5233832556598</v>
       </c>
-      <c r="CP37" s="1">
+      <c r="CP37" s="4">
         <f t="shared" si="52"/>
         <v>1108.3281494231032</v>
       </c>
-      <c r="CQ37" s="1">
+      <c r="CQ37" s="4">
         <f t="shared" si="52"/>
         <v>1097.2448679288723</v>
       </c>
-      <c r="CR37" s="1">
+      <c r="CR37" s="4">
         <f t="shared" si="52"/>
         <v>1086.2724192495834</v>
       </c>
-      <c r="CS37" s="1">
+      <c r="CS37" s="4">
         <f t="shared" si="52"/>
         <v>1075.4096950570877</v>
       </c>
-      <c r="CT37" s="1">
+      <c r="CT37" s="4">
         <f t="shared" si="52"/>
         <v>1064.6555981065169</v>
       </c>
-      <c r="CU37" s="1">
+      <c r="CU37" s="4">
         <f t="shared" si="52"/>
         <v>1054.0090421254517</v>
       </c>
-      <c r="CV37" s="1">
+      <c r="CV37" s="4">
         <f t="shared" si="52"/>
         <v>1043.4689517041973</v>
       </c>
-      <c r="CW37" s="1">
+      <c r="CW37" s="4">
         <f t="shared" si="52"/>
         <v>1033.0342621871553</v>
       </c>
-      <c r="CX37" s="1">
+      <c r="CX37" s="4">
         <f t="shared" si="52"/>
         <v>1022.7039195652837</v>
       </c>
-      <c r="CY37" s="1">
+      <c r="CY37" s="4">
         <f t="shared" si="52"/>
         <v>1012.4768803696309</v>
       </c>
-      <c r="CZ37" s="1">
+      <c r="CZ37" s="4">
         <f t="shared" si="52"/>
         <v>1002.3521115659346</v>
       </c>
-      <c r="DA37" s="1">
+      <c r="DA37" s="4">
         <f t="shared" si="52"/>
         <v>992.32859045027521</v>
       </c>
-      <c r="DB37" s="1">
+      <c r="DB37" s="4">
         <f t="shared" si="52"/>
         <v>982.40530454577242</v>
       </c>
-      <c r="DC37" s="1">
+      <c r="DC37" s="4">
         <f t="shared" ref="DC37:EV37" si="53">DB37*(1+$AS$45)</f>
         <v>972.58125150031469</v>
       </c>
-      <c r="DD37" s="1">
+      <c r="DD37" s="4">
         <f t="shared" si="53"/>
         <v>962.85543898531159</v>
       </c>
-      <c r="DE37" s="1">
+      <c r="DE37" s="4">
         <f t="shared" si="53"/>
         <v>953.2268845954585</v>
       </c>
-      <c r="DF37" s="1">
+      <c r="DF37" s="4">
         <f t="shared" si="53"/>
         <v>943.6946157495039</v>
       </c>
-      <c r="DG37" s="1">
+      <c r="DG37" s="4">
         <f t="shared" si="53"/>
         <v>934.25766959200882</v>
       </c>
-      <c r="DH37" s="1">
+      <c r="DH37" s="4">
         <f t="shared" si="53"/>
         <v>924.91509289608871</v>
       </c>
-      <c r="DI37" s="1">
+      <c r="DI37" s="4">
         <f t="shared" si="53"/>
         <v>915.66594196712776</v>
       </c>
-      <c r="DJ37" s="1">
+      <c r="DJ37" s="4">
         <f t="shared" si="53"/>
         <v>906.50928254745645</v>
       </c>
-      <c r="DK37" s="1">
+      <c r="DK37" s="4">
         <f t="shared" si="53"/>
         <v>897.44418972198184</v>
       </c>
-      <c r="DL37" s="1">
+      <c r="DL37" s="4">
         <f t="shared" si="53"/>
         <v>888.46974782476207</v>
       </c>
-      <c r="DM37" s="1">
+      <c r="DM37" s="4">
         <f t="shared" si="53"/>
         <v>879.58505034651444</v>
       </c>
-      <c r="DN37" s="1">
+      <c r="DN37" s="4">
         <f t="shared" si="53"/>
         <v>870.78919984304923</v>
       </c>
-      <c r="DO37" s="1">
+      <c r="DO37" s="4">
         <f t="shared" si="53"/>
         <v>862.08130784461878</v>
       </c>
-      <c r="DP37" s="1">
+      <c r="DP37" s="4">
         <f t="shared" si="53"/>
         <v>853.46049476617259</v>
       </c>
-      <c r="DQ37" s="1">
+      <c r="DQ37" s="4">
         <f t="shared" si="53"/>
         <v>844.92588981851088</v>
       </c>
-      <c r="DR37" s="1">
+      <c r="DR37" s="4">
         <f t="shared" si="53"/>
         <v>836.47663092032576</v>
       </c>
-      <c r="DS37" s="1">
+      <c r="DS37" s="4">
         <f t="shared" si="53"/>
         <v>828.11186461112254</v>
       </c>
-      <c r="DT37" s="1">
+      <c r="DT37" s="4">
         <f t="shared" si="53"/>
         <v>819.83074596501126</v>
       </c>
-      <c r="DU37" s="1">
+      <c r="DU37" s="4">
         <f t="shared" si="53"/>
         <v>811.63243850536116</v>
       </c>
-      <c r="DV37" s="1">
+      <c r="DV37" s="4">
         <f t="shared" si="53"/>
         <v>803.51611412030752</v>
       </c>
-      <c r="DW37" s="1">
+      <c r="DW37" s="4">
         <f t="shared" si="53"/>
         <v>795.48095297910447</v>
       </c>
-      <c r="DX37" s="1">
+      <c r="DX37" s="4">
         <f t="shared" si="53"/>
         <v>787.52614344931339</v>
       </c>
-      <c r="DY37" s="1">
+      <c r="DY37" s="4">
         <f t="shared" si="53"/>
         <v>779.65088201482024</v>
       </c>
-      <c r="DZ37" s="1">
+      <c r="DZ37" s="4">
         <f t="shared" si="53"/>
         <v>771.85437319467201</v>
       </c>
-      <c r="EA37" s="1">
+      <c r="EA37" s="4">
         <f t="shared" si="53"/>
         <v>764.13582946272527</v>
       </c>
-      <c r="EB37" s="1">
+      <c r="EB37" s="4">
         <f t="shared" si="53"/>
         <v>756.49447116809802</v>
       </c>
-      <c r="EC37" s="1">
+      <c r="EC37" s="4">
         <f t="shared" si="53"/>
         <v>748.92952645641708</v>
       </c>
-      <c r="ED37" s="1">
+      <c r="ED37" s="4">
         <f t="shared" si="53"/>
         <v>741.44023119185294</v>
       </c>
-      <c r="EE37" s="1">
+      <c r="EE37" s="4">
         <f t="shared" si="53"/>
         <v>734.02582887993447</v>
       </c>
-      <c r="EF37" s="1">
+      <c r="EF37" s="4">
         <f t="shared" si="53"/>
         <v>726.68557059113516</v>
       </c>
-      <c r="EG37" s="1">
+      <c r="EG37" s="4">
         <f t="shared" si="53"/>
         <v>719.41871488522384</v>
       </c>
-      <c r="EH37" s="1">
+      <c r="EH37" s="4">
         <f t="shared" si="53"/>
         <v>712.22452773637156</v>
       </c>
-      <c r="EI37" s="1">
+      <c r="EI37" s="4">
         <f t="shared" si="53"/>
         <v>705.10228245900782</v>
       </c>
-      <c r="EJ37" s="1">
+      <c r="EJ37" s="4">
         <f t="shared" si="53"/>
         <v>698.05125963441776</v>
       </c>
-      <c r="EK37" s="1">
+      <c r="EK37" s="4">
         <f t="shared" si="53"/>
         <v>691.07074703807359</v>
       </c>
-      <c r="EL37" s="1">
+      <c r="EL37" s="4">
         <f t="shared" si="53"/>
         <v>684.16003956769282</v>
       </c>
-      <c r="EM37" s="1">
+      <c r="EM37" s="4">
         <f t="shared" si="53"/>
         <v>677.31843917201593</v>
       </c>
-      <c r="EN37" s="1">
+      <c r="EN37" s="4">
         <f t="shared" si="53"/>
         <v>670.54525478029575</v>
       </c>
-      <c r="EO37" s="1">
+      <c r="EO37" s="4">
         <f t="shared" si="53"/>
         <v>663.83980223249273</v>
       </c>
-      <c r="EP37" s="1">
+      <c r="EP37" s="4">
         <f t="shared" si="53"/>
         <v>657.20140421016777</v>
       </c>
-      <c r="EQ37" s="1">
+      <c r="EQ37" s="4">
         <f t="shared" si="53"/>
         <v>650.62939016806604</v>
       </c>
-      <c r="ER37" s="1">
+      <c r="ER37" s="4">
         <f t="shared" si="53"/>
         <v>644.12309626638535</v>
       </c>
-      <c r="ES37" s="1">
+      <c r="ES37" s="4">
         <f t="shared" si="53"/>
         <v>637.68186530372145</v>
       </c>
-      <c r="ET37" s="1">
+      <c r="ET37" s="4">
         <f t="shared" si="53"/>
         <v>631.30504665068418</v>
       </c>
-      <c r="EU37" s="1">
+      <c r="EU37" s="4">
         <f t="shared" si="53"/>
         <v>624.99199618417731</v>
       </c>
-      <c r="EV37" s="1">
+      <c r="EV37" s="4">
         <f t="shared" si="53"/>
         <v>618.74207622233553</v>
       </c>
     </row>
     <row r="38" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="3">
@@ -5395,755 +5431,755 @@
       </c>
     </row>
     <row r="39" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="9">
         <f>C37/C38</f>
         <v>1.1512779184895234</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="9">
         <f>D37/D38</f>
         <v>-0.85194565968224734</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="9">
         <f t="shared" ref="G39:P39" si="55">G37/G38</f>
         <v>1.0591756850103615</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="9">
         <f t="shared" si="55"/>
         <v>1.3124568270780566</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="9">
         <f t="shared" si="55"/>
         <v>1.7499424361040756</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J39" s="9">
         <f t="shared" si="55"/>
         <v>6.8385908358277687</v>
       </c>
-      <c r="K39" s="5">
+      <c r="K39" s="9">
         <f t="shared" si="55"/>
         <v>1.1052268017499425</v>
       </c>
-      <c r="L39" s="5">
+      <c r="L39" s="9">
         <f t="shared" si="55"/>
         <v>1.3124568270780566</v>
       </c>
-      <c r="M39" s="5">
+      <c r="M39" s="9">
         <f t="shared" si="55"/>
         <v>2.3486069537186278</v>
       </c>
-      <c r="N39" s="5">
+      <c r="N39" s="9">
         <f t="shared" si="55"/>
         <v>7.529357586921483</v>
       </c>
-      <c r="O39" s="5">
+      <c r="O39" s="9">
         <f t="shared" si="55"/>
         <v>1.1512779184895234</v>
       </c>
-      <c r="P39" s="5">
+      <c r="P39" s="9">
         <f t="shared" si="55"/>
         <v>1.4506101772967994</v>
       </c>
-      <c r="Q39" s="5">
+      <c r="Q39" s="9">
         <f t="shared" ref="Q39:R39" si="56">Q37/Q38</f>
         <v>3.1084503799217131</v>
       </c>
-      <c r="R39" s="5">
+      <c r="R39" s="9">
         <f t="shared" si="56"/>
         <v>10.79898687543173</v>
       </c>
-      <c r="S39" s="5">
+      <c r="S39" s="9">
         <f t="shared" ref="S39:V39" si="57">S37/S38</f>
         <v>1.8932481751824817</v>
       </c>
-      <c r="T39" s="5">
+      <c r="T39" s="9">
         <f t="shared" si="57"/>
         <v>3.261861313868613</v>
       </c>
-      <c r="U39" s="5">
+      <c r="U39" s="9">
         <f t="shared" si="57"/>
         <v>3.4199422607150787</v>
       </c>
-      <c r="V39" s="5">
+      <c r="V39" s="9">
         <f t="shared" si="57"/>
         <v>14.13731752165223</v>
       </c>
-      <c r="Z39" s="5">
+      <c r="Z39" s="9">
         <f>Z37/Z38</f>
         <v>-0.62169007598434267</v>
       </c>
-      <c r="AA39" s="5">
+      <c r="AA39" s="9">
         <f>AA37/AA38</f>
         <v>6.7004374856090259</v>
       </c>
-      <c r="AB39" s="5">
+      <c r="AB39" s="9">
         <f>AB37/AB38</f>
         <v>10.960165784020262</v>
       </c>
-      <c r="AC39" s="5">
+      <c r="AC39" s="9">
         <f>AC37/AC38</f>
         <v>12.295648169468111</v>
       </c>
-      <c r="AD39" s="5">
+      <c r="AD39" s="9">
         <f t="shared" ref="AD39:AO39" si="58">AD37/AD38</f>
         <v>16.509325351139765</v>
       </c>
-      <c r="AE39" s="5">
+      <c r="AE39" s="9">
         <f t="shared" si="58"/>
         <v>22.576136087053094</v>
       </c>
-      <c r="AF39" s="5">
+      <c r="AF39" s="9">
         <f t="shared" si="58"/>
         <v>29.431495156562267</v>
       </c>
-      <c r="AG39" s="5">
+      <c r="AG39" s="9">
         <f t="shared" si="58"/>
         <v>33.255705182544972</v>
       </c>
-      <c r="AH39" s="5">
+      <c r="AH39" s="9">
         <f t="shared" si="58"/>
         <v>35.495415773281159</v>
       </c>
-      <c r="AI39" s="5">
+      <c r="AI39" s="9">
         <f t="shared" si="58"/>
         <v>36.904417142175447</v>
       </c>
-      <c r="AJ39" s="5">
+      <c r="AJ39" s="9">
         <f t="shared" si="58"/>
         <v>37.787242684327595</v>
       </c>
-      <c r="AK39" s="5">
+      <c r="AK39" s="9">
         <f t="shared" si="58"/>
         <v>38.576884615156878</v>
       </c>
-      <c r="AL39" s="5">
+      <c r="AL39" s="9">
         <f t="shared" si="58"/>
         <v>39.385250139732342</v>
       </c>
-      <c r="AM39" s="5">
+      <c r="AM39" s="9">
         <f t="shared" si="58"/>
         <v>40.212833768292548</v>
       </c>
-      <c r="AN39" s="5">
+      <c r="AN39" s="9">
         <f t="shared" si="58"/>
         <v>41.060144472452606</v>
       </c>
-      <c r="AO39" s="5">
+      <c r="AO39" s="9">
         <f t="shared" si="58"/>
         <v>41.927706153710787</v>
       </c>
     </row>
     <row r="41" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="O41" s="8">
+      <c r="O41" s="10">
         <f t="shared" ref="O41:Q41" si="59">O10/K10-1</f>
         <v>0.5372858689422404</v>
       </c>
-      <c r="P41" s="8">
+      <c r="P41" s="10">
         <f t="shared" si="59"/>
         <v>0.53766190449719264</v>
       </c>
-      <c r="Q41" s="8">
+      <c r="Q41" s="10">
         <f t="shared" si="59"/>
         <v>0.41511822186218428</v>
       </c>
-      <c r="R41" s="8">
+      <c r="R41" s="10">
         <f t="shared" ref="R41:U42" si="60">R10/N10-1</f>
         <v>0.39818901578923427</v>
       </c>
-      <c r="S41" s="8">
+      <c r="S41" s="10">
         <f t="shared" si="60"/>
         <v>0.34958574979287493</v>
       </c>
-      <c r="T41" s="8">
+      <c r="T41" s="10">
         <f t="shared" si="60"/>
         <v>0.16647988142149606</v>
       </c>
-      <c r="U41" s="8">
+      <c r="U41" s="10">
         <f t="shared" si="60"/>
         <v>0.16905187835420388</v>
       </c>
-      <c r="AC41" s="8">
+      <c r="AC41" s="10">
         <f t="shared" ref="AC41:AE42" si="61">AC10/AB10-1</f>
         <v>0.45649148386241634</v>
       </c>
-      <c r="AD41" s="8">
+      <c r="AD41" s="10">
         <f t="shared" si="61"/>
         <v>0.39818901578923427</v>
       </c>
-      <c r="AE41" s="8">
+      <c r="AE41" s="10">
         <f t="shared" si="61"/>
         <v>6.3362405623535567E-2</v>
       </c>
     </row>
     <row r="42" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8">
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10">
         <f t="shared" ref="N42:O42" si="62">N11/J11-1</f>
         <v>0.44099051633298214</v>
       </c>
-      <c r="O42" s="8">
+      <c r="O42" s="10">
         <f t="shared" si="62"/>
         <v>0.42572887848478391</v>
       </c>
-      <c r="P42" s="8">
+      <c r="P42" s="10">
         <f>P11/L11-1</f>
         <v>0.61863560732113143</v>
       </c>
-      <c r="Q42" s="8">
+      <c r="Q42" s="10">
         <f>Q11/M11-1</f>
         <v>0.41263879817112992</v>
       </c>
-      <c r="R42" s="8">
+      <c r="R42" s="10">
         <f t="shared" si="60"/>
         <v>0.43570122747453643</v>
       </c>
-      <c r="S42" s="8">
+      <c r="S42" s="10">
         <f t="shared" si="60"/>
         <v>0.55633504987934423</v>
       </c>
-      <c r="T42" s="8">
+      <c r="T42" s="10">
         <f t="shared" si="60"/>
         <v>0.29862253289473695</v>
       </c>
-      <c r="U42" s="8">
+      <c r="U42" s="10">
         <f t="shared" si="60"/>
         <v>0.22920278965822827</v>
       </c>
-      <c r="AC42" s="8">
+      <c r="AC42" s="10">
         <f t="shared" si="61"/>
         <v>0.44095288273370459</v>
       </c>
-      <c r="AD42" s="8">
+      <c r="AD42" s="10">
         <f t="shared" si="61"/>
         <v>0.43573872391548485</v>
       </c>
-      <c r="AE42" s="8">
+      <c r="AE42" s="10">
         <f t="shared" si="61"/>
         <v>0.16062430647772552</v>
       </c>
     </row>
     <row r="43" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
     </row>
     <row r="44" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="10">
         <f t="shared" ref="G44:G49" si="63">G13/C13-1</f>
         <v>-2.7093596059113323E-2</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="10">
         <f t="shared" ref="H44:H49" si="64">H13/D13-1</f>
         <v>-3.2537960954446832E-2</v>
       </c>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8">
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10">
         <f t="shared" ref="K44:K49" si="65">K13/G13-1</f>
         <v>0.15696202531645564</v>
       </c>
-      <c r="L44" s="8">
+      <c r="L44" s="10">
         <f t="shared" ref="L44:L49" si="66">L13/H13-1</f>
         <v>0.22197309417040367</v>
       </c>
-      <c r="M44" s="8">
+      <c r="M44" s="10">
         <f t="shared" ref="M44:M49" si="67">M13/I13-1</f>
         <v>0.40128755364806867</v>
       </c>
-      <c r="N44" s="8">
+      <c r="N44" s="10">
         <f t="shared" ref="N44:N49" si="68">N13/J13-1</f>
         <v>-2.3305084745762761E-2</v>
       </c>
-      <c r="O44" s="8">
+      <c r="O44" s="10">
         <f t="shared" ref="O44" si="69">O13/K13-1</f>
         <v>7.0021881838074451E-2</v>
       </c>
-      <c r="P44" s="8">
+      <c r="P44" s="10">
         <f t="shared" ref="P44:P45" si="70">P13/L13-1</f>
         <v>0.47706422018348627</v>
       </c>
-      <c r="Q44" s="8">
+      <c r="Q44" s="10">
         <f t="shared" ref="Q44:Q49" si="71">Q13/M13-1</f>
         <v>0.8897396630934149</v>
       </c>
-      <c r="R44" s="8">
+      <c r="R44" s="10">
         <f t="shared" ref="R44:R49" si="72">R13/N13-1</f>
         <v>0.34598698481561829</v>
       </c>
-      <c r="S44" s="8">
+      <c r="S44" s="10">
         <f t="shared" ref="S44:S49" si="73">S13/O13-1</f>
         <v>0.93251533742331283</v>
       </c>
-      <c r="T44" s="8">
+      <c r="T44" s="10">
         <f t="shared" ref="T44:T49" si="74">T13/P13-1</f>
         <v>0.15527950310559002</v>
       </c>
-      <c r="U44" s="8">
+      <c r="U44" s="10">
         <f t="shared" ref="U44:U49" si="75">U13/Q13-1</f>
         <v>6.0777957860615794E-2</v>
       </c>
-      <c r="V44" s="8">
+      <c r="V44" s="10">
         <f t="shared" ref="V44:V49" si="76">V13/R13-1</f>
         <v>0.35000000000000009</v>
       </c>
-      <c r="AA44" s="8">
+      <c r="AA44" s="10">
         <f t="shared" ref="AA44:AO44" si="77">AA13/Z13-1</f>
         <v>2.5711159737417999E-2</v>
       </c>
-      <c r="AB44" s="8">
+      <c r="AB44" s="10">
         <f t="shared" si="77"/>
         <v>0.20053333333333323</v>
       </c>
-      <c r="AC44" s="8">
+      <c r="AC44" s="10">
         <f t="shared" si="77"/>
         <v>0.14482452243447352</v>
       </c>
-      <c r="AD44" s="8">
+      <c r="AD44" s="10">
         <f t="shared" si="77"/>
         <v>0.46255335661622032</v>
       </c>
-      <c r="AE44" s="8">
+      <c r="AE44" s="10">
         <f t="shared" si="77"/>
         <v>0.2892942425046432</v>
       </c>
-      <c r="AF44" s="8">
+      <c r="AF44" s="10">
         <f t="shared" si="77"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="AG44" s="8">
+      <c r="AG44" s="10">
         <f t="shared" si="77"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AH44" s="8">
+      <c r="AH44" s="10">
         <f t="shared" si="77"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AI44" s="8">
+      <c r="AI44" s="10">
         <f t="shared" si="77"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AJ44" s="8">
+      <c r="AJ44" s="10">
         <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK44" s="8">
+      <c r="AK44" s="10">
         <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL44" s="8">
+      <c r="AL44" s="10">
         <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AM44" s="8">
+      <c r="AM44" s="10">
         <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AN44" s="8">
+      <c r="AN44" s="10">
         <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AO44" s="8">
+      <c r="AO44" s="10">
         <f t="shared" si="77"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="45" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="10">
         <f t="shared" si="63"/>
         <v>2.857142857142847E-2</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="10">
         <f t="shared" si="64"/>
         <v>0.11255411255411252</v>
       </c>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8">
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10">
         <f t="shared" si="65"/>
         <v>-0.19444444444444442</v>
       </c>
-      <c r="L45" s="8">
+      <c r="L45" s="10">
         <f t="shared" si="66"/>
         <v>-3.5019455252918275E-2</v>
       </c>
-      <c r="M45" s="8">
+      <c r="M45" s="10">
         <f t="shared" si="67"/>
         <v>0.66228070175438591</v>
       </c>
-      <c r="N45" s="8">
+      <c r="N45" s="10">
         <f t="shared" si="68"/>
         <v>0.55606407322654472</v>
       </c>
-      <c r="O45" s="8">
+      <c r="O45" s="10">
         <f t="shared" ref="O45" si="78">O14/K14-1</f>
         <v>0.84482758620689657</v>
       </c>
-      <c r="P45" s="8">
+      <c r="P45" s="10">
         <f t="shared" si="70"/>
         <v>1.560483870967742</v>
       </c>
-      <c r="Q45" s="8">
+      <c r="Q45" s="10">
         <f t="shared" si="71"/>
         <v>0.17941952506596315</v>
       </c>
-      <c r="R45" s="8">
+      <c r="R45" s="10">
         <f t="shared" si="72"/>
         <v>0.66470588235294126</v>
       </c>
-      <c r="S45" s="8">
+      <c r="S45" s="10">
         <f t="shared" si="73"/>
         <v>0.65109034267912769</v>
       </c>
-      <c r="T45" s="8">
+      <c r="T45" s="10">
         <f t="shared" si="74"/>
         <v>4.0944881889763751E-2</v>
       </c>
-      <c r="U45" s="8">
+      <c r="U45" s="10">
         <f t="shared" si="75"/>
         <v>0.36017897091722606</v>
       </c>
-      <c r="V45" s="8">
+      <c r="V45" s="10">
         <f t="shared" si="76"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AA45" s="8">
+      <c r="AA45" s="10">
         <f t="shared" ref="AA45" si="79">AA14/Z14-1</f>
         <v>1.878354203935606E-2</v>
       </c>
-      <c r="AB45" s="8">
+      <c r="AB45" s="10">
         <f t="shared" ref="AB45:AC45" si="80">AB14/AA14-1</f>
         <v>-8.779631255487752E-4</v>
       </c>
-      <c r="AC45" s="8">
+      <c r="AC45" s="10">
         <f t="shared" si="80"/>
         <v>0.30140597539543057</v>
       </c>
-      <c r="AD45" s="8">
+      <c r="AD45" s="10">
         <f t="shared" ref="AD45:AO45" si="81">AD14/AC14-1</f>
         <v>0.71168129642133704</v>
       </c>
-      <c r="AE45" s="8">
+      <c r="AE45" s="10">
         <f t="shared" si="81"/>
         <v>0.24552268244575925</v>
       </c>
-      <c r="AF45" s="8">
+      <c r="AF45" s="10">
         <f t="shared" si="81"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AG45" s="8">
+      <c r="AG45" s="10">
         <f t="shared" si="81"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AH45" s="8">
+      <c r="AH45" s="10">
         <f t="shared" si="81"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AI45" s="8">
+      <c r="AI45" s="10">
         <f t="shared" si="81"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AJ45" s="8">
+      <c r="AJ45" s="10">
         <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK45" s="8">
+      <c r="AK45" s="10">
         <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL45" s="8">
+      <c r="AL45" s="10">
         <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AM45" s="8">
+      <c r="AM45" s="10">
         <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AN45" s="8">
+      <c r="AN45" s="10">
         <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AO45" s="8">
+      <c r="AO45" s="10">
         <f t="shared" si="81"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AR45" t="s">
+      <c r="AR45" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AS45" s="8">
+      <c r="AS45" s="10">
         <v>-0.01</v>
       </c>
     </row>
     <row r="46" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="10">
         <f t="shared" si="63"/>
         <v>-6.3829787234042534E-2</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="10">
         <f t="shared" si="64"/>
         <v>0.17283950617283961</v>
       </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8">
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10">
         <f t="shared" si="65"/>
         <v>0.4015151515151516</v>
       </c>
-      <c r="L46" s="8">
+      <c r="L46" s="10">
         <f t="shared" si="66"/>
         <v>0.11052631578947358</v>
       </c>
-      <c r="M46" s="8">
+      <c r="M46" s="10">
         <f t="shared" si="67"/>
         <v>9.6774193548387011E-2</v>
       </c>
-      <c r="N46" s="8">
+      <c r="N46" s="10">
         <f t="shared" si="68"/>
         <v>-3.4642032332563466E-2</v>
       </c>
-      <c r="O46" s="8">
+      <c r="O46" s="10">
         <f t="shared" ref="O46:P46" si="82">O15/K15-1</f>
         <v>0.22702702702702693</v>
       </c>
-      <c r="P46" s="8">
+      <c r="P46" s="10">
         <f t="shared" si="82"/>
         <v>0.2890995260663507</v>
       </c>
-      <c r="Q46" s="8">
+      <c r="Q46" s="10">
         <f t="shared" si="71"/>
         <v>0.39215686274509798</v>
       </c>
-      <c r="R46" s="8">
+      <c r="R46" s="10">
         <f t="shared" si="72"/>
         <v>0.27511961722488043</v>
       </c>
-      <c r="S46" s="8">
+      <c r="S46" s="10">
         <f t="shared" si="73"/>
         <v>0.47577092511013208</v>
       </c>
-      <c r="T46" s="8">
+      <c r="T46" s="10">
         <f t="shared" si="74"/>
         <v>0.48161764705882359</v>
       </c>
-      <c r="U46" s="8">
+      <c r="U46" s="10">
         <f t="shared" si="75"/>
         <v>0.42253521126760574</v>
       </c>
-      <c r="V46" s="8">
+      <c r="V46" s="10">
         <f t="shared" si="76"/>
         <v>0.33000000000000007</v>
       </c>
-      <c r="AA46" s="8">
+      <c r="AA46" s="10">
         <f t="shared" ref="AA46:AC46" si="83">AA15/Z15-1</f>
         <v>-3.9948453608247392E-2</v>
       </c>
-      <c r="AB46" s="8">
+      <c r="AB46" s="10">
         <f t="shared" si="83"/>
         <v>0.26308724832214758</v>
       </c>
-      <c r="AC46" s="8">
+      <c r="AC46" s="10">
         <f t="shared" si="83"/>
         <v>8.1827842720510136E-2</v>
       </c>
-      <c r="AD46" s="8">
+      <c r="AD46" s="10">
         <f t="shared" ref="AD46:AO46" si="84">AD15/AC15-1</f>
         <v>0.29273084479371314</v>
       </c>
-      <c r="AE46" s="8">
+      <c r="AE46" s="10">
         <f t="shared" si="84"/>
         <v>0.40645136778115498</v>
       </c>
-      <c r="AF46" s="8">
+      <c r="AF46" s="10">
         <f t="shared" si="84"/>
         <v>0.21999999999999997</v>
       </c>
-      <c r="AG46" s="8">
+      <c r="AG46" s="10">
         <f t="shared" si="84"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AH46" s="8">
+      <c r="AH46" s="10">
         <f t="shared" si="84"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="AI46" s="8">
+      <c r="AI46" s="10">
         <f t="shared" si="84"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AJ46" s="8">
+      <c r="AJ46" s="10">
         <f t="shared" si="84"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AK46" s="8">
+      <c r="AK46" s="10">
         <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AL46" s="8">
+      <c r="AL46" s="10">
         <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AM46" s="8">
+      <c r="AM46" s="10">
         <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN46" s="8">
+      <c r="AN46" s="10">
         <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AO46" s="8">
+      <c r="AO46" s="10">
         <f t="shared" si="84"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AR46" t="s">
+      <c r="AR46" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AS46" s="8">
+      <c r="AS46" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="47" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="10">
         <f t="shared" si="63"/>
         <v>1.3752455795677854E-2</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="10">
         <f t="shared" si="64"/>
         <v>9.0128755364806912E-2</v>
       </c>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8">
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10">
         <f t="shared" si="65"/>
         <v>4.8449612403100861E-2</v>
       </c>
-      <c r="L47" s="8">
+      <c r="L47" s="10">
         <f t="shared" si="66"/>
         <v>-4.7244094488189003E-2</v>
       </c>
-      <c r="M47" s="8">
+      <c r="M47" s="10">
         <f t="shared" si="67"/>
         <v>-3.8022813688213253E-3</v>
       </c>
-      <c r="N47" s="8">
+      <c r="N47" s="10">
         <f t="shared" si="68"/>
         <v>5.9760956175298752E-2</v>
       </c>
-      <c r="O47" s="8">
+      <c r="O47" s="10">
         <f t="shared" ref="O47:P47" si="85">O16/K16-1</f>
         <v>-1.848428835489857E-3</v>
       </c>
-      <c r="P47" s="8">
+      <c r="P47" s="10">
         <f t="shared" si="85"/>
         <v>5.9917355371900793E-2</v>
       </c>
-      <c r="Q47" s="8">
+      <c r="Q47" s="10">
         <f t="shared" si="71"/>
         <v>-7.6335877862595436E-2</v>
       </c>
-      <c r="R47" s="8">
+      <c r="R47" s="10">
         <f t="shared" si="72"/>
         <v>-6.9548872180451138E-2</v>
       </c>
-      <c r="S47" s="8">
+      <c r="S47" s="10">
         <f t="shared" si="73"/>
         <v>-6.6666666666666652E-2</v>
       </c>
-      <c r="T47" s="8">
+      <c r="T47" s="10">
         <f t="shared" si="74"/>
         <v>-6.4327485380117011E-2</v>
       </c>
-      <c r="U47" s="8">
+      <c r="U47" s="10">
         <f t="shared" si="75"/>
         <v>-2.6859504132231371E-2</v>
       </c>
-      <c r="V47" s="8">
+      <c r="V47" s="10">
         <f t="shared" si="76"/>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="AA47" s="8">
+      <c r="AA47" s="10">
         <f t="shared" ref="AA47:AC47" si="86">AA16/Z16-1</f>
         <v>0.1166666666666667</v>
       </c>
-      <c r="AB47" s="8">
+      <c r="AB47" s="10">
         <f t="shared" si="86"/>
         <v>9.3816631130063888E-2</v>
       </c>
-      <c r="AC47" s="8">
+      <c r="AC47" s="10">
         <f t="shared" si="86"/>
         <v>1.4132553606237774E-2</v>
       </c>
-      <c r="AD47" s="8">
+      <c r="AD47" s="10">
         <f t="shared" ref="AD47:AO47" si="87">AD16/AC16-1</f>
         <v>-2.3546371936568944E-2</v>
       </c>
-      <c r="AE47" s="8">
+      <c r="AE47" s="10">
         <f t="shared" si="87"/>
         <v>-4.522637795275597E-2</v>
       </c>
-      <c r="AF47" s="8">
+      <c r="AF47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG47" s="8">
+      <c r="AG47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH47" s="8">
+      <c r="AH47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI47" s="8">
+      <c r="AI47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ47" s="8">
+      <c r="AJ47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK47" s="8">
+      <c r="AK47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AL47" s="8">
+      <c r="AL47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM47" s="8">
+      <c r="AM47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN47" s="8">
+      <c r="AN47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AO47" s="8">
+      <c r="AO47" s="10">
         <f t="shared" si="87"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR47" t="s">
+      <c r="AR47" s="1" t="s">
         <v>60</v>
       </c>
       <c r="AS47" s="3">
@@ -6152,128 +6188,128 @@
       </c>
     </row>
     <row r="48" spans="2:152" x14ac:dyDescent="0.3">
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="10">
         <f t="shared" si="63"/>
         <v>2.5</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="10">
         <f t="shared" si="64"/>
         <v>-2.75</v>
       </c>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8">
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10">
         <f t="shared" si="65"/>
         <v>-0.1428571428571429</v>
       </c>
-      <c r="L48" s="8">
+      <c r="L48" s="10">
         <f t="shared" si="66"/>
         <v>0.28571428571428581</v>
       </c>
-      <c r="M48" s="8">
+      <c r="M48" s="10">
         <f t="shared" si="67"/>
         <v>-1.2222222222222223</v>
       </c>
-      <c r="N48" s="8">
+      <c r="N48" s="10">
         <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="O48" s="8">
+      <c r="O48" s="10">
         <f t="shared" ref="O48:P48" si="88">O17/K17-1</f>
         <v>-0.16666666666666663</v>
       </c>
-      <c r="P48" s="8">
+      <c r="P48" s="10">
         <f t="shared" si="88"/>
         <v>0.11111111111111116</v>
       </c>
-      <c r="Q48" s="8">
+      <c r="Q48" s="10">
         <f t="shared" si="71"/>
         <v>-3</v>
       </c>
-      <c r="R48" s="8">
+      <c r="R48" s="10">
         <f t="shared" si="72"/>
         <v>15</v>
       </c>
-      <c r="S48" s="8">
+      <c r="S48" s="10">
         <f t="shared" si="73"/>
         <v>-2.8</v>
       </c>
-      <c r="T48" s="8">
+      <c r="T48" s="10">
         <f t="shared" si="74"/>
         <v>-5.3</v>
       </c>
-      <c r="U48" s="8">
+      <c r="U48" s="10">
         <f t="shared" si="75"/>
         <v>-4.25</v>
       </c>
-      <c r="V48" s="8">
+      <c r="V48" s="10">
         <f t="shared" si="76"/>
         <v>0.5</v>
       </c>
-      <c r="AA48" s="8">
+      <c r="AA48" s="10">
         <f t="shared" ref="AA48:AC48" si="89">AA17/Z17-1</f>
         <v>7</v>
       </c>
-      <c r="AB48" s="8">
+      <c r="AB48" s="10">
         <f t="shared" si="89"/>
         <v>0.16666666666666674</v>
       </c>
-      <c r="AC48" s="8">
+      <c r="AC48" s="10">
         <f t="shared" si="89"/>
         <v>-0.3571428571428571</v>
       </c>
-      <c r="AD48" s="8">
+      <c r="AD48" s="10">
         <f t="shared" ref="AD48:AO48" si="90">AD17/AC17-1</f>
         <v>4.5</v>
       </c>
-      <c r="AE48" s="8">
+      <c r="AE48" s="10">
         <f t="shared" si="90"/>
         <v>-0.44444444444444442</v>
       </c>
-      <c r="AF48" s="8">
+      <c r="AF48" s="10">
         <f t="shared" si="90"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="AG48" s="8">
+      <c r="AG48" s="10">
         <f t="shared" si="90"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AH48" s="8">
+      <c r="AH48" s="10">
         <f t="shared" si="90"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AI48" s="8">
+      <c r="AI48" s="10">
         <f t="shared" si="90"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AJ48" s="8">
+      <c r="AJ48" s="10">
         <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AK48" s="8">
+      <c r="AK48" s="10">
         <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AL48" s="8">
+      <c r="AL48" s="10">
         <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AM48" s="8">
+      <c r="AM48" s="10">
         <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AN48" s="8">
+      <c r="AN48" s="10">
         <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AO48" s="8">
+      <c r="AO48" s="10">
         <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AR48" t="s">
+      <c r="AR48" s="1" t="s">
         <v>61</v>
       </c>
       <c r="AS48" s="3">
@@ -6281,130 +6317,130 @@
         <v>-1553</v>
       </c>
     </row>
-    <row r="49" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="2:45" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="11">
         <f t="shared" si="63"/>
         <v>-1.577287066246047E-3</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="11">
         <f t="shared" si="64"/>
         <v>6.990881458966558E-2</v>
       </c>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7">
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11">
         <f t="shared" si="65"/>
         <v>7.6619273301737678E-2</v>
       </c>
-      <c r="L49" s="7">
+      <c r="L49" s="11">
         <f t="shared" si="66"/>
         <v>6.3210227272727293E-2</v>
       </c>
-      <c r="M49" s="7">
+      <c r="M49" s="11">
         <f t="shared" si="67"/>
         <v>0.24240282685512371</v>
       </c>
-      <c r="N49" s="7">
+      <c r="N49" s="11">
         <f t="shared" si="68"/>
         <v>0.1016803102111159</v>
       </c>
-      <c r="O49" s="7">
+      <c r="O49" s="11">
         <f>O18/K18-1</f>
         <v>0.16067498165810701</v>
       </c>
-      <c r="P49" s="7">
+      <c r="P49" s="11">
         <f>P18/L18-1</f>
         <v>0.49298597194388782</v>
       </c>
-      <c r="Q49" s="7">
+      <c r="Q49" s="11">
         <f t="shared" si="71"/>
         <v>0.39533560864618877</v>
       </c>
-      <c r="R49" s="7">
+      <c r="R49" s="11">
         <f t="shared" si="72"/>
         <v>0.36136096988658584</v>
       </c>
-      <c r="S49" s="7">
+      <c r="S49" s="11">
         <f t="shared" si="73"/>
         <v>0.45701643489254118</v>
       </c>
-      <c r="T49" s="7">
+      <c r="T49" s="11">
         <f t="shared" si="74"/>
         <v>8.7695749440715787E-2</v>
       </c>
-      <c r="U49" s="7">
+      <c r="U49" s="11">
         <f t="shared" si="75"/>
         <v>0.13289849164288636</v>
       </c>
-      <c r="V49" s="7">
+      <c r="V49" s="11">
         <f t="shared" si="76"/>
         <v>0.24899166906061465</v>
       </c>
-      <c r="Z49" s="7"/>
-      <c r="AA49" s="7">
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="11">
         <f>AA18/Z18-1</f>
         <v>4.6993524514338469E-2</v>
       </c>
-      <c r="AB49" s="7">
+      <c r="AB49" s="11">
         <f t="shared" ref="AB49:AO49" si="91">AB18/AA18-1</f>
         <v>0.1327089591800672</v>
       </c>
-      <c r="AC49" s="7">
+      <c r="AC49" s="11">
         <f t="shared" si="91"/>
         <v>0.11934477379095165</v>
       </c>
-      <c r="AD49" s="7">
+      <c r="AD49" s="11">
         <f t="shared" si="91"/>
         <v>0.35902439024390254</v>
       </c>
-      <c r="AE49" s="7">
+      <c r="AE49" s="11">
         <f t="shared" si="91"/>
         <v>0.21656650599938465</v>
       </c>
-      <c r="AF49" s="7">
+      <c r="AF49" s="11">
         <f t="shared" si="91"/>
         <v>0.18116672876586692</v>
       </c>
-      <c r="AG49" s="7">
+      <c r="AG49" s="11">
         <f t="shared" si="91"/>
         <v>8.8108732466602557E-2</v>
       </c>
-      <c r="AH49" s="7">
+      <c r="AH49" s="11">
         <f t="shared" si="91"/>
         <v>5.0902185538335809E-2</v>
       </c>
-      <c r="AI49" s="7">
+      <c r="AI49" s="11">
         <f t="shared" si="91"/>
         <v>3.1530440447478547E-2</v>
       </c>
-      <c r="AJ49" s="7">
+      <c r="AJ49" s="11">
         <f t="shared" si="91"/>
         <v>2.2581759873649077E-2</v>
       </c>
-      <c r="AK49" s="7">
+      <c r="AK49" s="11">
         <f t="shared" si="91"/>
         <v>2.0851852946606408E-2</v>
       </c>
-      <c r="AL49" s="7">
+      <c r="AL49" s="11">
         <f t="shared" si="91"/>
         <v>2.0887948125385636E-2</v>
       </c>
-      <c r="AM49" s="7">
+      <c r="AM49" s="11">
         <f t="shared" si="91"/>
         <v>2.0924220581955533E-2</v>
       </c>
-      <c r="AN49" s="7">
+      <c r="AN49" s="11">
         <f t="shared" si="91"/>
         <v>2.096067476613217E-2</v>
       </c>
-      <c r="AO49" s="7">
+      <c r="AO49" s="11">
         <f t="shared" si="91"/>
         <v>2.0997315214217105E-2</v>
       </c>
-      <c r="AR49" t="s">
+      <c r="AR49" s="1" t="s">
         <v>62</v>
       </c>
       <c r="AS49" s="3">
@@ -6412,1383 +6448,1383 @@
         <v>21349.047088771727</v>
       </c>
     </row>
-    <row r="50" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B50" t="s">
+    <row r="50" spans="2:45" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50" s="8">
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="10">
         <f>(G18+G19)/(C18+C19)-1</f>
         <v>-4.9873203719357551E-2</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="10">
         <f>(H18+H19)/(D18+D19)-1</f>
         <v>2.7195027195027199E-2</v>
       </c>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8">
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10">
         <f t="shared" ref="K50:R50" si="92">(K18+K19)/(G18+G19)-1</f>
         <v>-8.2740213523131656E-2</v>
       </c>
-      <c r="L50" s="8">
+      <c r="L50" s="10">
         <f t="shared" si="92"/>
         <v>-2.874432677760963E-2</v>
       </c>
-      <c r="M50" s="8">
+      <c r="M50" s="10">
         <f t="shared" si="92"/>
         <v>0.24119028974158185</v>
       </c>
-      <c r="N50" s="8">
+      <c r="N50" s="10">
         <f t="shared" si="92"/>
         <v>1.7758484609313285E-2</v>
       </c>
-      <c r="O50" s="8">
+      <c r="O50" s="10">
         <f t="shared" si="92"/>
         <v>0.11542192046556732</v>
       </c>
-      <c r="P50" s="8">
+      <c r="P50" s="10">
         <f t="shared" si="92"/>
         <v>0.7398753894080996</v>
       </c>
-      <c r="Q50" s="8">
+      <c r="Q50" s="10">
         <f t="shared" si="92"/>
         <v>0.62965299684542586</v>
       </c>
-      <c r="R50" s="8">
+      <c r="R50" s="10">
         <f t="shared" si="92"/>
         <v>0.40248158200853035</v>
       </c>
-      <c r="S50" s="8">
+      <c r="S50" s="10">
         <f t="shared" ref="S50" si="93">(S18+S19)/(O18+O19)-1</f>
         <v>0.78956521739130436</v>
       </c>
-      <c r="T50" s="8">
+      <c r="T50" s="10">
         <f t="shared" ref="T50" si="94">(T18+T19)/(P18+P19)-1</f>
         <v>-6.9829901521933802E-2</v>
       </c>
-      <c r="U50" s="8">
+      <c r="U50" s="10">
         <f t="shared" ref="U50" si="95">(U18+U19)/(Q18+Q19)-1</f>
         <v>1.0065814943863716E-2</v>
       </c>
-      <c r="V50" s="8">
+      <c r="V50" s="10">
         <f t="shared" ref="V50" si="96">(V18+V19)/(R18+R19)-1</f>
         <v>0.20202930605474134</v>
       </c>
-      <c r="Z50" s="7"/>
-      <c r="AA50" s="8">
+      <c r="Z50" s="11"/>
+      <c r="AA50" s="10">
         <f>(AA18+AA19)/(Z18+Z19)-1</f>
         <v>5.3011590347710413E-2</v>
       </c>
-      <c r="AB50" s="8">
+      <c r="AB50" s="10">
         <f t="shared" ref="AB50:AO50" si="97">(AB18+AB19)/(AA18+AA19)-1</f>
         <v>0.12901479610249011</v>
       </c>
-      <c r="AC50" s="8">
+      <c r="AC50" s="10">
         <f t="shared" si="97"/>
         <v>3.548026210644073E-2</v>
       </c>
-      <c r="AD50" s="8">
+      <c r="AD50" s="10">
         <f t="shared" si="97"/>
         <v>0.47924062355301733</v>
       </c>
-      <c r="AE50" s="8">
+      <c r="AE50" s="10">
         <f t="shared" si="97"/>
         <v>0.23776502504173624</v>
       </c>
-      <c r="AF50" s="8">
+      <c r="AF50" s="10">
         <f t="shared" si="97"/>
         <v>0.18116672876586692</v>
       </c>
-      <c r="AG50" s="8">
+      <c r="AG50" s="10">
         <f t="shared" si="97"/>
         <v>8.8108732466602557E-2</v>
       </c>
-      <c r="AH50" s="8">
+      <c r="AH50" s="10">
         <f t="shared" si="97"/>
         <v>5.0902185538335809E-2</v>
       </c>
-      <c r="AI50" s="8">
+      <c r="AI50" s="10">
         <f t="shared" si="97"/>
         <v>3.1530440447478547E-2</v>
       </c>
-      <c r="AJ50" s="8">
+      <c r="AJ50" s="10">
         <f t="shared" si="97"/>
         <v>2.2581759873649077E-2</v>
       </c>
-      <c r="AK50" s="8">
+      <c r="AK50" s="10">
         <f t="shared" si="97"/>
         <v>2.0851852946606408E-2</v>
       </c>
-      <c r="AL50" s="8">
+      <c r="AL50" s="10">
         <f t="shared" si="97"/>
         <v>2.0887948125385636E-2</v>
       </c>
-      <c r="AM50" s="8">
+      <c r="AM50" s="10">
         <f t="shared" si="97"/>
         <v>2.0924220581955533E-2</v>
       </c>
-      <c r="AN50" s="8">
+      <c r="AN50" s="10">
         <f t="shared" si="97"/>
         <v>2.096067476613217E-2</v>
       </c>
-      <c r="AO50" s="8">
+      <c r="AO50" s="10">
         <f t="shared" si="97"/>
         <v>2.0997315214217105E-2</v>
       </c>
-      <c r="AR50" t="s">
+      <c r="AR50" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AS50" s="2">
+      <c r="AS50" s="12">
         <f>AS49/AO38</f>
         <v>474.10719717458863</v>
       </c>
     </row>
     <row r="51" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="10">
         <f>C23/C18</f>
         <v>0.21608832807570977</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="10">
         <f>D23/D18</f>
         <v>0.21808510638297873</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8">
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10">
         <f t="shared" ref="G51:P51" si="98">G23/G18</f>
         <v>0.2109004739336493</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="10">
         <f t="shared" si="98"/>
         <v>0.22443181818181818</v>
       </c>
-      <c r="I51" s="8">
+      <c r="I51" s="10">
         <f t="shared" si="98"/>
         <v>0.22332155477031801</v>
       </c>
-      <c r="J51" s="8">
+      <c r="J51" s="10">
         <f t="shared" si="98"/>
         <v>0.27789745799224475</v>
       </c>
-      <c r="K51" s="8">
+      <c r="K51" s="10">
         <f t="shared" si="98"/>
         <v>0.22157006603081439</v>
       </c>
-      <c r="L51" s="8">
+      <c r="L51" s="10">
         <f t="shared" si="98"/>
         <v>0.22845691382765532</v>
       </c>
-      <c r="M51" s="8">
+      <c r="M51" s="10">
         <f t="shared" si="98"/>
         <v>0.24402730375426621</v>
       </c>
-      <c r="N51" s="8">
+      <c r="N51" s="10">
         <f t="shared" si="98"/>
         <v>0.31912397340633553</v>
       </c>
-      <c r="O51" s="8">
+      <c r="O51" s="10">
         <f t="shared" si="98"/>
         <v>0.24905183312262957</v>
       </c>
-      <c r="P51" s="8">
+      <c r="P51" s="10">
         <f t="shared" si="98"/>
         <v>0.25548098434004474</v>
       </c>
-      <c r="Q51" s="8">
+      <c r="Q51" s="10">
         <f t="shared" ref="Q51:R51" si="99">Q23/Q18</f>
         <v>0.23685283326538931</v>
       </c>
-      <c r="R51" s="8">
+      <c r="R51" s="10">
         <f t="shared" si="99"/>
         <v>0.3274920999712726</v>
       </c>
-      <c r="S51" s="8">
+      <c r="S51" s="10">
         <f t="shared" ref="S51:V51" si="100">S23/S18</f>
         <v>0.23514099783080261</v>
       </c>
-      <c r="T51" s="8">
+      <c r="T51" s="10">
         <f t="shared" si="100"/>
         <v>0.24475524475524477</v>
       </c>
-      <c r="U51" s="8">
+      <c r="U51" s="10">
         <f t="shared" si="100"/>
         <v>0.25836631881971933</v>
       </c>
-      <c r="V51" s="8">
+      <c r="V51" s="10">
         <f t="shared" si="100"/>
         <v>0.34</v>
       </c>
-      <c r="Z51" s="8">
+      <c r="Z51" s="10">
         <f>Z23/Z18</f>
         <v>0.22534690101757632</v>
       </c>
-      <c r="AA51" s="8">
+      <c r="AA51" s="10">
         <f>AA23/AA18</f>
         <v>0.24527301643399893</v>
       </c>
-      <c r="AB51" s="8">
+      <c r="AB51" s="10">
         <f t="shared" ref="AB51:AO51" si="101">AB23/AB18</f>
         <v>0.24087363494539782</v>
       </c>
-      <c r="AC51" s="8">
+      <c r="AC51" s="10">
         <f t="shared" si="101"/>
         <v>0.26327526132404183</v>
       </c>
-      <c r="AD51" s="8">
+      <c r="AD51" s="10">
         <f t="shared" si="101"/>
         <v>0.27545892728950877</v>
       </c>
-      <c r="AE51" s="8">
+      <c r="AE51" s="10">
         <f t="shared" si="101"/>
         <v>0.28098328042256687</v>
       </c>
-      <c r="AF51" s="8">
+      <c r="AF51" s="10">
         <f t="shared" si="101"/>
         <v>0.26999999999999991</v>
       </c>
-      <c r="AG51" s="8">
+      <c r="AG51" s="10">
         <f t="shared" si="101"/>
         <v>0.26999999999999996</v>
       </c>
-      <c r="AH51" s="8">
+      <c r="AH51" s="10">
         <f t="shared" si="101"/>
         <v>0.27</v>
       </c>
-      <c r="AI51" s="8">
+      <c r="AI51" s="10">
         <f t="shared" si="101"/>
         <v>0.26999999999999996</v>
       </c>
-      <c r="AJ51" s="8">
+      <c r="AJ51" s="10">
         <f t="shared" si="101"/>
         <v>0.26999999999999996</v>
       </c>
-      <c r="AK51" s="8">
+      <c r="AK51" s="10">
         <f t="shared" si="101"/>
         <v>0.27</v>
       </c>
-      <c r="AL51" s="8">
+      <c r="AL51" s="10">
         <f t="shared" si="101"/>
         <v>0.26999999999999991</v>
       </c>
-      <c r="AM51" s="8">
+      <c r="AM51" s="10">
         <f t="shared" si="101"/>
         <v>0.26999999999999996</v>
       </c>
-      <c r="AN51" s="8">
+      <c r="AN51" s="10">
         <f t="shared" si="101"/>
         <v>0.26999999999999996</v>
       </c>
-      <c r="AO51" s="8">
+      <c r="AO51" s="10">
         <f t="shared" si="101"/>
         <v>0.26999999999999996</v>
       </c>
-      <c r="AR51" t="s">
+      <c r="AR51" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AS51" s="2">
+      <c r="AS51" s="12">
         <f>Main!D3</f>
-        <v>1523.5</v>
+        <v>1580.5</v>
       </c>
     </row>
     <row r="52" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="10">
         <f>C20/C18</f>
         <v>0.52444794952681384</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="10">
         <f>(D18-D20)/D18</f>
         <v>0.51747720364741645</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8">
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10">
         <f>(G18-G20)/G18</f>
         <v>0.45971563981042651</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="10">
         <f t="shared" ref="H52:U52" si="102">(H18-H20)/H18</f>
         <v>0.49289772727272729</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="10">
         <f t="shared" si="102"/>
         <v>0.43674911660777382</v>
       </c>
-      <c r="J52" s="8">
+      <c r="J52" s="10">
         <f t="shared" si="102"/>
         <v>0.57432141318397245</v>
       </c>
-      <c r="K52" s="8">
+      <c r="K52" s="10">
         <f t="shared" si="102"/>
         <v>0.34482758620689657</v>
       </c>
-      <c r="L52" s="8">
+      <c r="L52" s="10">
         <f t="shared" si="102"/>
         <v>0.42484969939879758</v>
       </c>
-      <c r="M52" s="8">
+      <c r="M52" s="10">
         <f t="shared" si="102"/>
         <v>0.42718998862343571</v>
       </c>
-      <c r="N52" s="8">
+      <c r="N52" s="10">
         <f t="shared" si="102"/>
         <v>0.54086820492764964</v>
       </c>
-      <c r="O52" s="8">
+      <c r="O52" s="10">
         <f t="shared" si="102"/>
         <v>0.34323640960809104</v>
       </c>
-      <c r="P52" s="8">
+      <c r="P52" s="10">
         <f t="shared" si="102"/>
         <v>0.5136465324384788</v>
       </c>
-      <c r="Q52" s="8">
+      <c r="Q52" s="10">
         <f t="shared" si="102"/>
         <v>0.52303302079086833</v>
       </c>
-      <c r="R52" s="8">
+      <c r="R52" s="10">
         <f t="shared" si="102"/>
         <v>0.55099109451307093</v>
       </c>
-      <c r="S52" s="8">
+      <c r="S52" s="10">
         <f t="shared" si="102"/>
         <v>0.42993492407809109</v>
       </c>
-      <c r="T52" s="8">
+      <c r="T52" s="10">
         <f t="shared" si="102"/>
         <v>0.38914027149321267</v>
       </c>
-      <c r="U52" s="8">
+      <c r="U52" s="10">
         <f t="shared" si="102"/>
         <v>0.44620367038503056</v>
       </c>
-      <c r="V52" s="8"/>
-      <c r="Z52" s="8">
+      <c r="V52" s="10"/>
+      <c r="Z52" s="10">
         <f t="shared" ref="Z52:AD52" si="103">(Z18-Z20)/Z18</f>
         <v>0.48344125809435706</v>
       </c>
-      <c r="AA52" s="8">
+      <c r="AA52" s="10">
         <f t="shared" si="103"/>
         <v>0.51493196677858277</v>
       </c>
-      <c r="AB52" s="8">
+      <c r="AB52" s="10">
         <f t="shared" si="103"/>
         <v>0.50343213728549141</v>
       </c>
-      <c r="AC52" s="8">
+      <c r="AC52" s="10">
         <f t="shared" si="103"/>
         <v>0.4515679442508711</v>
       </c>
-      <c r="AD52" s="8">
+      <c r="AD52" s="10">
         <f t="shared" si="103"/>
         <v>0.50169213414008818</v>
       </c>
-      <c r="AE52" s="8"/>
-      <c r="AF52" s="8">
+      <c r="AE52" s="10"/>
+      <c r="AF52" s="10">
         <f t="shared" ref="AF52:AO52" si="104">(AF18-AF20)/AF18</f>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AG52" s="8">
+      <c r="AG52" s="10">
         <f t="shared" si="104"/>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AH52" s="8">
+      <c r="AH52" s="10">
         <f t="shared" si="104"/>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AI52" s="8">
+      <c r="AI52" s="10">
         <f t="shared" si="104"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AJ52" s="8">
+      <c r="AJ52" s="10">
         <f t="shared" si="104"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AK52" s="8">
+      <c r="AK52" s="10">
         <f t="shared" si="104"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AL52" s="8">
+      <c r="AL52" s="10">
         <f t="shared" si="104"/>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AM52" s="8">
+      <c r="AM52" s="10">
         <f t="shared" si="104"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AN52" s="8">
+      <c r="AN52" s="10">
         <f t="shared" si="104"/>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AO52" s="8">
+      <c r="AO52" s="10">
         <f t="shared" si="104"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AR52" s="1" t="s">
+      <c r="AR52" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AS52" s="7">
+      <c r="AS52" s="11">
         <f>AS50/AS51-1</f>
-        <v>-0.68880394015452007</v>
+        <v>-0.700027081825632</v>
       </c>
     </row>
     <row r="53" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="10">
         <f>C21/C18</f>
         <v>0.32649842271293378</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="10">
         <f>(D18-D21)/D18</f>
         <v>0.6785714285714286</v>
       </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8">
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10">
         <f t="shared" ref="G53:U53" si="105">(G18-G21)/G18</f>
         <v>0.63902053712480256</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="10">
         <f t="shared" si="105"/>
         <v>0.67045454545454541</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="10">
         <f t="shared" si="105"/>
         <v>0.68904593639575973</v>
       </c>
-      <c r="J53" s="8">
+      <c r="J53" s="10">
         <f t="shared" si="105"/>
         <v>0.79534683326152522</v>
       </c>
-      <c r="K53" s="8">
+      <c r="K53" s="10">
         <f t="shared" si="105"/>
         <v>0.63316214233308876</v>
       </c>
-      <c r="L53" s="8">
+      <c r="L53" s="10">
         <f t="shared" si="105"/>
         <v>0.66132264529058116</v>
       </c>
-      <c r="M53" s="8">
+      <c r="M53" s="10">
         <f t="shared" si="105"/>
         <v>0.71843003412969286</v>
       </c>
-      <c r="N53" s="8">
+      <c r="N53" s="10">
         <f t="shared" si="105"/>
         <v>0.78685960109503328</v>
       </c>
-      <c r="O53" s="8">
+      <c r="O53" s="10">
         <f t="shared" si="105"/>
         <v>0.63274336283185839</v>
       </c>
-      <c r="P53" s="8">
+      <c r="P53" s="10">
         <f t="shared" si="105"/>
         <v>0.74138702460850114</v>
       </c>
-      <c r="Q53" s="8">
+      <c r="Q53" s="10">
         <f t="shared" si="105"/>
         <v>0.76681614349775784</v>
       </c>
-      <c r="R53" s="8">
+      <c r="R53" s="10">
         <f t="shared" si="105"/>
         <v>0.81557023843723064</v>
       </c>
-      <c r="S53" s="8">
+      <c r="S53" s="10">
         <f t="shared" si="105"/>
         <v>0.69804772234273316</v>
       </c>
-      <c r="T53" s="8">
+      <c r="T53" s="10">
         <f t="shared" si="105"/>
         <v>0.71040723981900455</v>
       </c>
-      <c r="U53" s="8">
+      <c r="U53" s="10">
         <f t="shared" si="105"/>
         <v>0.75098956459157973</v>
       </c>
-      <c r="V53" s="8"/>
-      <c r="Z53" s="8">
+      <c r="V53" s="10"/>
+      <c r="Z53" s="10">
         <f t="shared" ref="Z53:AD53" si="106">(Z18-Z21)/Z18</f>
         <v>0.71563367252543941</v>
       </c>
-      <c r="AA53" s="8">
+      <c r="AA53" s="10">
         <f t="shared" si="106"/>
         <v>0.70966601873122459</v>
       </c>
-      <c r="AB53" s="8">
+      <c r="AB53" s="10">
         <f t="shared" si="106"/>
         <v>0.71357254290171612</v>
       </c>
-      <c r="AC53" s="8">
+      <c r="AC53" s="10">
         <f t="shared" si="106"/>
         <v>0.71470383275261329</v>
       </c>
-      <c r="AD53" s="8">
+      <c r="AD53" s="10">
         <f t="shared" si="106"/>
         <v>0.75664034458004303</v>
       </c>
-      <c r="AE53" s="8"/>
-      <c r="AF53" s="8">
+      <c r="AE53" s="10"/>
+      <c r="AF53" s="10">
         <f t="shared" ref="AF53:AO53" si="107">(AF18-AF21)/AF18</f>
         <v>0.72000000000000008</v>
       </c>
-      <c r="AG53" s="8">
+      <c r="AG53" s="10">
         <f t="shared" si="107"/>
         <v>0.72</v>
       </c>
-      <c r="AH53" s="8">
+      <c r="AH53" s="10">
         <f t="shared" si="107"/>
         <v>0.72</v>
       </c>
-      <c r="AI53" s="8">
+      <c r="AI53" s="10">
         <f t="shared" si="107"/>
         <v>0.72</v>
       </c>
-      <c r="AJ53" s="8">
+      <c r="AJ53" s="10">
         <f t="shared" si="107"/>
         <v>0.72</v>
       </c>
-      <c r="AK53" s="8">
+      <c r="AK53" s="10">
         <f t="shared" si="107"/>
         <v>0.72</v>
       </c>
-      <c r="AL53" s="8">
+      <c r="AL53" s="10">
         <f t="shared" si="107"/>
         <v>0.72</v>
       </c>
-      <c r="AM53" s="8">
+      <c r="AM53" s="10">
         <f t="shared" si="107"/>
         <v>0.72</v>
       </c>
-      <c r="AN53" s="8">
+      <c r="AN53" s="10">
         <f t="shared" si="107"/>
         <v>0.72</v>
       </c>
-      <c r="AO53" s="8">
+      <c r="AO53" s="10">
         <f t="shared" si="107"/>
         <v>0.72000000000000008</v>
       </c>
-      <c r="AR53" t="s">
+      <c r="AR53" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AS53" s="4" t="s">
+      <c r="AS53" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="54" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8">
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10">
         <f t="shared" ref="G54:V54" si="108">G25/C25-1</f>
         <v>0.38095238095238093</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="10">
         <f t="shared" si="108"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="I54" s="8" t="e">
+      <c r="I54" s="10" t="e">
         <f t="shared" si="108"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J54" s="8" t="e">
+      <c r="J54" s="10" t="e">
         <f t="shared" si="108"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K54" s="8">
+      <c r="K54" s="10">
         <f t="shared" si="108"/>
         <v>0.10344827586206895</v>
       </c>
-      <c r="L54" s="8">
+      <c r="L54" s="10">
         <f t="shared" si="108"/>
         <v>-0.4358974358974359</v>
       </c>
-      <c r="M54" s="8">
+      <c r="M54" s="10">
         <f t="shared" si="108"/>
         <v>-0.22641509433962259</v>
       </c>
-      <c r="N54" s="8">
+      <c r="N54" s="10">
         <f t="shared" si="108"/>
         <v>-0.42000000000000004</v>
       </c>
-      <c r="O54" s="8">
+      <c r="O54" s="10">
         <f t="shared" si="108"/>
         <v>0.3125</v>
       </c>
-      <c r="P54" s="8">
+      <c r="P54" s="10">
         <f t="shared" si="108"/>
         <v>0.77272727272727271</v>
       </c>
-      <c r="Q54" s="8">
+      <c r="Q54" s="10">
         <f t="shared" si="108"/>
         <v>0.24390243902439024</v>
       </c>
-      <c r="R54" s="8">
+      <c r="R54" s="10">
         <f t="shared" si="108"/>
         <v>0.65517241379310343</v>
       </c>
-      <c r="S54" s="8">
+      <c r="S54" s="10">
         <f t="shared" si="108"/>
         <v>-0.1428571428571429</v>
       </c>
-      <c r="T54" s="8">
+      <c r="T54" s="10">
         <f t="shared" si="108"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="U54" s="8">
+      <c r="U54" s="10">
         <f t="shared" si="108"/>
         <v>-0.15686274509803921</v>
       </c>
-      <c r="V54" s="8">
+      <c r="V54" s="10">
         <f t="shared" si="108"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="Z54" s="8"/>
-      <c r="AA54" s="8">
+      <c r="Z54" s="10"/>
+      <c r="AA54" s="10">
         <f t="shared" ref="AA54:AD54" si="109">AA25/Z25-1</f>
         <v>0.17543859649122817</v>
       </c>
-      <c r="AB54" s="8">
+      <c r="AB54" s="10">
         <f t="shared" si="109"/>
         <v>0.64925373134328357</v>
       </c>
-      <c r="AC54" s="8">
+      <c r="AC54" s="10">
         <f t="shared" si="109"/>
         <v>-0.30769230769230771</v>
       </c>
-      <c r="AD54" s="8">
+      <c r="AD54" s="10">
         <f t="shared" si="109"/>
         <v>0.49019607843137258</v>
       </c>
-      <c r="AE54" s="8"/>
-      <c r="AF54" s="8"/>
-      <c r="AG54" s="8"/>
-      <c r="AH54" s="8"/>
-      <c r="AI54" s="8"/>
-      <c r="AJ54" s="8"/>
-      <c r="AK54" s="8"/>
-      <c r="AL54" s="8"/>
-      <c r="AM54" s="8"/>
-      <c r="AN54" s="8"/>
-      <c r="AO54" s="8"/>
-      <c r="AS54" s="4"/>
+      <c r="AE54" s="10"/>
+      <c r="AF54" s="10"/>
+      <c r="AG54" s="10"/>
+      <c r="AH54" s="10"/>
+      <c r="AI54" s="10"/>
+      <c r="AJ54" s="10"/>
+      <c r="AK54" s="10"/>
+      <c r="AL54" s="10"/>
+      <c r="AM54" s="10"/>
+      <c r="AN54" s="10"/>
+      <c r="AO54" s="10"/>
+      <c r="AS54" s="2"/>
     </row>
     <row r="55" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8">
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10">
         <f>G26/C26-1</f>
         <v>2.6845637583892579E-2</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="10">
         <f>H26/D26-1</f>
         <v>7.7922077922077948E-2</v>
       </c>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8">
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10">
         <f t="shared" ref="K55:P55" si="110">K26/G26-1</f>
         <v>0.18954248366013071</v>
       </c>
-      <c r="L55" s="8">
+      <c r="L55" s="10">
         <f t="shared" si="110"/>
         <v>0.10240963855421681</v>
       </c>
-      <c r="M55" s="8">
+      <c r="M55" s="10">
         <f t="shared" si="110"/>
         <v>0.12886597938144329</v>
       </c>
-      <c r="N55" s="8">
+      <c r="N55" s="10">
         <f t="shared" si="110"/>
         <v>0.19607843137254899</v>
       </c>
-      <c r="O55" s="8">
+      <c r="O55" s="10">
         <f t="shared" si="110"/>
         <v>0.25274725274725274</v>
       </c>
-      <c r="P55" s="8">
+      <c r="P55" s="10">
         <f t="shared" si="110"/>
         <v>0.51366120218579225</v>
       </c>
-      <c r="Q55" s="8">
+      <c r="Q55" s="10">
         <f t="shared" ref="Q55:R55" si="111">Q26/M26-1</f>
         <v>0.12785388127853881</v>
       </c>
-      <c r="R55" s="8">
+      <c r="R55" s="10">
         <f t="shared" si="111"/>
         <v>0.20655737704918042</v>
       </c>
-      <c r="S55" s="8">
+      <c r="S55" s="10">
         <f t="shared" ref="S55" si="112">S26/O26-1</f>
         <v>0.25877192982456143</v>
       </c>
-      <c r="T55" s="8">
+      <c r="T55" s="10">
         <f t="shared" ref="T55" si="113">T26/P26-1</f>
         <v>3.6101083032491044E-2</v>
       </c>
-      <c r="U55" s="8">
+      <c r="U55" s="10">
         <f t="shared" ref="U55" si="114">U26/Q26-1</f>
         <v>0.2995951417004048</v>
       </c>
-      <c r="V55" s="8">
+      <c r="V55" s="10">
         <f t="shared" ref="V55" si="115">V26/R26-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="Z55" s="8"/>
-      <c r="AA55" s="8">
+      <c r="Z55" s="10"/>
+      <c r="AA55" s="10">
         <f>AA26/Z26-1</f>
         <v>2.1806853582554409E-2</v>
       </c>
-      <c r="AB55" s="8">
+      <c r="AB55" s="10">
         <f t="shared" ref="AB55:AD55" si="116">AB26/AA26-1</f>
         <v>0.1707317073170731</v>
       </c>
-      <c r="AC55" s="8">
+      <c r="AC55" s="10">
         <f t="shared" si="116"/>
         <v>0.15755208333333326</v>
       </c>
-      <c r="AD55" s="8">
+      <c r="AD55" s="10">
         <f t="shared" si="116"/>
         <v>0.25984251968503935</v>
       </c>
-      <c r="AE55" s="8"/>
-      <c r="AF55" s="8"/>
-      <c r="AG55" s="8"/>
-      <c r="AH55" s="8"/>
-      <c r="AI55" s="8"/>
-      <c r="AJ55" s="8"/>
-      <c r="AK55" s="8"/>
-      <c r="AL55" s="8"/>
-      <c r="AM55" s="8"/>
-      <c r="AN55" s="8"/>
-      <c r="AO55" s="8"/>
+      <c r="AE55" s="10"/>
+      <c r="AF55" s="10"/>
+      <c r="AG55" s="10"/>
+      <c r="AH55" s="10"/>
+      <c r="AI55" s="10"/>
+      <c r="AJ55" s="10"/>
+      <c r="AK55" s="10"/>
+      <c r="AL55" s="10"/>
+      <c r="AM55" s="10"/>
+      <c r="AN55" s="10"/>
+      <c r="AO55" s="10"/>
     </row>
     <row r="56" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="10">
         <f>C28/C18</f>
         <v>6.9400630914826497E-2</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="10">
         <f>D28/D18</f>
         <v>7.9787234042553196E-2</v>
       </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8">
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10">
         <f t="shared" ref="G56:P56" si="117">G28/G18</f>
         <v>6.5560821484992107E-2</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="10">
         <f t="shared" si="117"/>
         <v>9.0198863636363633E-2</v>
       </c>
-      <c r="I56" s="8">
+      <c r="I56" s="10">
         <f t="shared" si="117"/>
         <v>7.9151943462897528E-2</v>
       </c>
-      <c r="J56" s="8">
+      <c r="J56" s="10">
         <f t="shared" si="117"/>
         <v>0.18354157690650583</v>
       </c>
-      <c r="K56" s="8">
+      <c r="K56" s="10">
         <f t="shared" si="117"/>
         <v>6.5297138664710194E-2</v>
       </c>
-      <c r="L56" s="8">
+      <c r="L56" s="10">
         <f t="shared" si="117"/>
         <v>7.8824315297261194E-2</v>
       </c>
-      <c r="M56" s="8">
+      <c r="M56" s="10">
         <f t="shared" si="117"/>
         <v>9.7838452787258251E-2</v>
       </c>
-      <c r="N56" s="8">
+      <c r="N56" s="10">
         <f t="shared" si="117"/>
         <v>0.18224481814626514</v>
       </c>
-      <c r="O56" s="8">
+      <c r="O56" s="10">
         <f t="shared" si="117"/>
         <v>7.3957016434892539E-2</v>
       </c>
-      <c r="P56" s="8">
+      <c r="P56" s="10">
         <f t="shared" si="117"/>
         <v>0.10827740492170022</v>
       </c>
-      <c r="Q56" s="8">
+      <c r="Q56" s="10">
         <f t="shared" ref="Q56:R56" si="118">Q28/Q18</f>
         <v>0.11822258459029759</v>
       </c>
-      <c r="R56" s="8">
+      <c r="R56" s="10">
         <f t="shared" si="118"/>
         <v>0.21315713875323183</v>
       </c>
-      <c r="S56" s="8">
+      <c r="S56" s="10">
         <f t="shared" ref="S56:V56" si="119">S28/S18</f>
         <v>7.7657266811279824E-2</v>
       </c>
-      <c r="T56" s="8">
+      <c r="T56" s="10">
         <f t="shared" si="119"/>
         <v>9.5433977786918964E-2</v>
       </c>
-      <c r="U56" s="8">
+      <c r="U56" s="10">
         <f t="shared" si="119"/>
         <v>0.11622885930190716</v>
       </c>
-      <c r="V56" s="8">
+      <c r="V56" s="10">
         <f t="shared" si="119"/>
         <v>0.24569813282302994</v>
       </c>
-      <c r="Z56" s="8">
+      <c r="Z56" s="10">
         <f>Z28/Z18</f>
         <v>7.5485661424606845E-2</v>
       </c>
-      <c r="AA56" s="8">
+      <c r="AA56" s="10">
         <f>AA28/AA18</f>
         <v>0.10867644460151971</v>
       </c>
-      <c r="AB56" s="8">
+      <c r="AB56" s="10">
         <f t="shared" ref="AB56:AO56" si="120">AB28/AB18</f>
         <v>0.11669266770670828</v>
       </c>
-      <c r="AC56" s="8">
+      <c r="AC56" s="10">
         <f t="shared" si="120"/>
         <v>0.11777003484320557</v>
       </c>
-      <c r="AD56" s="8">
+      <c r="AD56" s="10">
         <f t="shared" si="120"/>
         <v>0.14265203568864732</v>
       </c>
-      <c r="AE56" s="8">
+      <c r="AE56" s="10">
         <f t="shared" si="120"/>
         <v>0.15192372082672309</v>
       </c>
-      <c r="AF56" s="8">
+      <c r="AF56" s="10">
         <f t="shared" si="120"/>
         <v>0.15527230383704985</v>
       </c>
-      <c r="AG56" s="8">
+      <c r="AG56" s="10">
         <f t="shared" si="120"/>
         <v>0.16034477855995866</v>
       </c>
-      <c r="AH56" s="8">
+      <c r="AH56" s="10">
         <f t="shared" si="120"/>
         <v>0.16252579389642688</v>
       </c>
-      <c r="AI56" s="8">
+      <c r="AI56" s="10">
         <f t="shared" si="120"/>
         <v>0.16372713986211609</v>
       </c>
-      <c r="AJ56" s="8">
+      <c r="AJ56" s="10">
         <f t="shared" si="120"/>
         <v>0.16399545190984499</v>
       </c>
-      <c r="AK56" s="8">
+      <c r="AK56" s="10">
         <f t="shared" si="120"/>
         <v>0.16408390772876102</v>
       </c>
-      <c r="AL56" s="8">
+      <c r="AL56" s="10">
         <f t="shared" si="120"/>
         <v>0.16417603144885487</v>
       </c>
-      <c r="AM56" s="8">
+      <c r="AM56" s="10">
         <f t="shared" si="120"/>
         <v>0.16427183159525899</v>
       </c>
-      <c r="AN56" s="8">
+      <c r="AN56" s="10">
         <f t="shared" si="120"/>
         <v>0.16437131670371244</v>
       </c>
-      <c r="AO56" s="8">
+      <c r="AO56" s="10">
         <f t="shared" si="120"/>
         <v>0.16447449532263658</v>
       </c>
     </row>
     <row r="57" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="10">
         <f>C35/C34</f>
         <v>0.27631578947368424</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="10">
         <f>D35/D34</f>
         <v>0.23300970873786409</v>
       </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8">
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10">
         <f t="shared" ref="G57:P57" si="121">G35/G34</f>
         <v>0.20547945205479451</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="10">
         <f t="shared" si="121"/>
         <v>0.30612244897959184</v>
       </c>
-      <c r="I57" s="8">
+      <c r="I57" s="10">
         <f t="shared" si="121"/>
         <v>0.27027027027027029</v>
       </c>
-      <c r="J57" s="8">
+      <c r="J57" s="10">
         <f t="shared" si="121"/>
         <v>0.24713958810068651</v>
       </c>
-      <c r="K57" s="8">
+      <c r="K57" s="10">
         <f t="shared" si="121"/>
         <v>0.28985507246376813</v>
       </c>
-      <c r="L57" s="8">
+      <c r="L57" s="10">
         <f t="shared" si="121"/>
         <v>0.29807692307692307</v>
       </c>
-      <c r="M57" s="8">
+      <c r="M57" s="10">
         <f t="shared" si="121"/>
         <v>0.24827586206896551</v>
       </c>
-      <c r="N57" s="8">
+      <c r="N57" s="10">
         <f t="shared" si="121"/>
         <v>0.19758064516129031</v>
       </c>
-      <c r="O57" s="8">
+      <c r="O57" s="10">
         <f t="shared" si="121"/>
         <v>0.36046511627906974</v>
       </c>
-      <c r="P57" s="8">
+      <c r="P57" s="10">
         <f t="shared" si="121"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="Q57" s="8">
+      <c r="Q57" s="10">
         <f t="shared" ref="Q57:R57" si="122">Q35/Q34</f>
         <v>0.29959514170040485</v>
       </c>
-      <c r="R57" s="8">
+      <c r="R57" s="10">
         <f t="shared" si="122"/>
         <v>0.25036390101892286</v>
       </c>
-      <c r="S57" s="8">
+      <c r="S57" s="10">
         <f t="shared" ref="S57:V57" si="123">S35/S34</f>
         <v>0.26712328767123289</v>
       </c>
-      <c r="T57" s="8">
+      <c r="T57" s="10">
         <f t="shared" si="123"/>
         <v>0.23766816143497757</v>
       </c>
-      <c r="U57" s="8">
+      <c r="U57" s="10">
         <f t="shared" si="123"/>
         <v>0.29655172413793102</v>
       </c>
-      <c r="V57" s="8">
+      <c r="V57" s="10">
         <f t="shared" si="123"/>
         <v>0.27</v>
       </c>
-      <c r="Z57" s="8">
+      <c r="Z57" s="10">
         <f>Z35/Z34</f>
         <v>0.22677595628415301</v>
       </c>
-      <c r="AA57" s="8">
+      <c r="AA57" s="10">
         <f>AA35/AA34</f>
         <v>0.25773195876288657</v>
       </c>
-      <c r="AB57" s="8">
+      <c r="AB57" s="10">
         <f t="shared" ref="AB57:AO57" si="124">AB35/AB34</f>
         <v>0.25452016689847012</v>
       </c>
-      <c r="AC57" s="8">
+      <c r="AC57" s="10">
         <f t="shared" si="124"/>
         <v>0.22727272727272727</v>
       </c>
-      <c r="AD57" s="8">
+      <c r="AD57" s="10">
         <f t="shared" si="124"/>
         <v>0.27117263843648209</v>
       </c>
-      <c r="AE57" s="8">
+      <c r="AE57" s="10">
         <f t="shared" si="124"/>
         <v>0.27004192918328646</v>
       </c>
-      <c r="AF57" s="8">
+      <c r="AF57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AG57" s="8">
+      <c r="AG57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AH57" s="8">
+      <c r="AH57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AI57" s="8">
+      <c r="AI57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AJ57" s="8">
+      <c r="AJ57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AK57" s="8">
+      <c r="AK57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AL57" s="8">
+      <c r="AL57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AM57" s="8">
+      <c r="AM57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AN57" s="8">
+      <c r="AN57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
-      <c r="AO57" s="8">
+      <c r="AO57" s="10">
         <f t="shared" si="124"/>
         <v>0.25</v>
       </c>
     </row>
     <row r="58" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="10">
         <f>C36/C34</f>
         <v>6.5789473684210523E-2</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="10">
         <f>D36/D34</f>
         <v>1.1262135922330097</v>
       </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8">
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10">
         <f t="shared" ref="G58:N58" si="125">G36/G34</f>
         <v>0.16438356164383561</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="10">
         <f t="shared" si="125"/>
         <v>0.11224489795918367</v>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="10">
         <f t="shared" si="125"/>
         <v>4.5045045045045043E-2</v>
       </c>
-      <c r="J58" s="8">
+      <c r="J58" s="10">
         <f t="shared" si="125"/>
         <v>7.3226544622425629E-2</v>
       </c>
-      <c r="K58" s="8">
+      <c r="K58" s="10">
         <f t="shared" si="125"/>
         <v>1.4492753623188406E-2</v>
       </c>
-      <c r="L58" s="8">
+      <c r="L58" s="10">
         <f t="shared" si="125"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="M58" s="8">
+      <c r="M58" s="10">
         <f t="shared" si="125"/>
         <v>4.8275862068965517E-2</v>
       </c>
-      <c r="N58" s="8">
+      <c r="N58" s="10">
         <f t="shared" si="125"/>
         <v>0.14314516129032259</v>
       </c>
-      <c r="O58" s="8">
+      <c r="O58" s="10">
         <f t="shared" ref="O58:P58" si="126">O36/O34</f>
         <v>5.8139534883720929E-2</v>
       </c>
-      <c r="P58" s="8">
+      <c r="P58" s="10">
         <f t="shared" si="126"/>
         <v>0.42788461538461536</v>
       </c>
-      <c r="Q58" s="8">
+      <c r="Q58" s="10">
         <f t="shared" ref="Q58:R58" si="127">Q36/Q34</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="R58" s="8">
+      <c r="R58" s="10">
         <f t="shared" si="127"/>
         <v>6.6957787481804948E-2</v>
       </c>
-      <c r="S58" s="8">
+      <c r="S58" s="10">
         <f t="shared" ref="S58:V58" si="128">S36/S34</f>
         <v>0.16438356164383561</v>
       </c>
-      <c r="T58" s="8">
+      <c r="T58" s="10">
         <f t="shared" si="128"/>
         <v>0.1210762331838565</v>
       </c>
-      <c r="U58" s="8">
+      <c r="U58" s="10">
         <f t="shared" si="128"/>
         <v>0.17241379310344829</v>
       </c>
-      <c r="V58" s="8">
+      <c r="V58" s="10">
         <f t="shared" si="128"/>
         <v>0.1</v>
       </c>
-      <c r="Z58" s="8">
+      <c r="Z58" s="10">
         <f t="shared" ref="Z58:AO58" si="129">Z36/Z34</f>
         <v>0.84699453551912574</v>
       </c>
-      <c r="AA58" s="8">
+      <c r="AA58" s="10">
         <f t="shared" si="129"/>
         <v>0.2422680412371134</v>
       </c>
-      <c r="AB58" s="8">
+      <c r="AB58" s="10">
         <f t="shared" si="129"/>
         <v>8.3449235048678724E-2</v>
       </c>
-      <c r="AC58" s="8">
+      <c r="AC58" s="10">
         <f t="shared" si="129"/>
         <v>0.1167076167076167</v>
       </c>
-      <c r="AD58" s="8">
+      <c r="AD58" s="10">
         <f t="shared" si="129"/>
         <v>0.14495114006514659</v>
       </c>
-      <c r="AE58" s="8">
+      <c r="AE58" s="10">
         <f t="shared" si="129"/>
         <v>0.12102449047656463</v>
       </c>
-      <c r="AF58" s="8">
+      <c r="AF58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AG58" s="8">
+      <c r="AG58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AH58" s="8">
+      <c r="AH58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AI58" s="8">
+      <c r="AI58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AJ58" s="8">
+      <c r="AJ58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AK58" s="8">
+      <c r="AK58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AL58" s="8">
+      <c r="AL58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AM58" s="8">
+      <c r="AM58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AN58" s="8">
+      <c r="AN58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
-      <c r="AO58" s="8">
+      <c r="AO58" s="10">
         <f t="shared" si="129"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="59" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="10">
         <f>C37/C23</f>
         <v>0.18248175182481752</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="10">
         <f>D37/D23</f>
         <v>-0.1289198606271777</v>
       </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8">
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10">
         <f t="shared" ref="G59:P59" si="130">G37/G23</f>
         <v>0.17228464419475656</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="10">
         <f t="shared" si="130"/>
         <v>0.18037974683544303</v>
       </c>
-      <c r="I59" s="8">
+      <c r="I59" s="10">
         <f t="shared" si="130"/>
         <v>0.24050632911392406</v>
       </c>
-      <c r="J59" s="8">
+      <c r="J59" s="10">
         <f t="shared" si="130"/>
         <v>0.46046511627906977</v>
       </c>
-      <c r="K59" s="8">
+      <c r="K59" s="10">
         <f t="shared" si="130"/>
         <v>0.15894039735099338</v>
       </c>
-      <c r="L59" s="8">
+      <c r="L59" s="10">
         <f t="shared" si="130"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="M59" s="8">
+      <c r="M59" s="10">
         <f t="shared" si="130"/>
         <v>0.23776223776223776</v>
       </c>
-      <c r="N59" s="8">
+      <c r="N59" s="10">
         <f t="shared" si="130"/>
         <v>0.40073529411764708</v>
       </c>
-      <c r="O59" s="8">
+      <c r="O59" s="10">
         <f t="shared" si="130"/>
         <v>0.12690355329949238</v>
       </c>
-      <c r="P59" s="8">
+      <c r="P59" s="10">
         <f t="shared" si="130"/>
         <v>0.11033274956217162</v>
       </c>
-      <c r="Q59" s="8">
+      <c r="Q59" s="10">
         <f t="shared" ref="Q59:R59" si="131">Q37/Q23</f>
         <v>0.23235800344234078</v>
       </c>
-      <c r="R59" s="8">
+      <c r="R59" s="10">
         <f t="shared" si="131"/>
         <v>0.41140350877192983</v>
       </c>
-      <c r="S59" s="8">
+      <c r="S59" s="10">
         <f t="shared" ref="S59:V59" si="132">S37/S23</f>
         <v>0.15313653136531366</v>
       </c>
-      <c r="T59" s="8">
+      <c r="T59" s="10">
         <f t="shared" si="132"/>
         <v>0.24033613445378152</v>
       </c>
-      <c r="U59" s="8">
+      <c r="U59" s="10">
         <f t="shared" si="132"/>
         <v>0.21448467966573817</v>
       </c>
-      <c r="V59" s="8">
+      <c r="V59" s="10">
         <f t="shared" si="132"/>
         <v>0.43065200879212695</v>
       </c>
-      <c r="Z59" s="8">
+      <c r="Z59" s="10">
         <f t="shared" ref="Z59:AD59" si="133">Z37/Z18</f>
         <v>-4.9953746530989824E-3</v>
       </c>
-      <c r="AA59" s="8">
+      <c r="AA59" s="10">
         <f t="shared" si="133"/>
         <v>5.1422512811450785E-2</v>
       </c>
-      <c r="AB59" s="8">
+      <c r="AB59" s="10">
         <f t="shared" si="133"/>
         <v>7.4258970358814347E-2</v>
       </c>
-      <c r="AC59" s="8">
+      <c r="AC59" s="10">
         <f t="shared" si="133"/>
         <v>7.4425087108013932E-2</v>
       </c>
-      <c r="AD59" s="8">
+      <c r="AD59" s="10">
         <f t="shared" si="133"/>
         <v>7.3530919905650707E-2</v>
       </c>
-      <c r="AE59" s="8">
+      <c r="AE59" s="10">
         <f>AE37/AE18</f>
         <v>8.569718361862444E-2</v>
       </c>
-      <c r="AF59" s="8">
+      <c r="AF59" s="10">
         <f t="shared" ref="AF59:AO59" si="134">AF37/AF18</f>
         <v>9.4584082458692917E-2</v>
       </c>
-      <c r="AG59" s="8">
+      <c r="AG59" s="10">
         <f t="shared" si="134"/>
         <v>9.8219924412346046E-2</v>
       </c>
-      <c r="AH59" s="8">
+      <c r="AH59" s="10">
         <f t="shared" si="134"/>
         <v>9.9757006074729621E-2</v>
       </c>
-      <c r="AI59" s="8">
+      <c r="AI59" s="10">
         <f t="shared" si="134"/>
         <v>0.10054661193535375</v>
       </c>
-      <c r="AJ59" s="8">
+      <c r="AJ59" s="10">
         <f t="shared" si="134"/>
         <v>0.10067838756957373</v>
       </c>
-      <c r="AK59" s="8">
+      <c r="AK59" s="10">
         <f t="shared" si="134"/>
         <v>0.10068284507169548</v>
       </c>
-      <c r="AL59" s="8">
+      <c r="AL59" s="10">
         <f t="shared" si="134"/>
         <v>0.10068942444503172</v>
       </c>
-      <c r="AM59" s="8">
+      <c r="AM59" s="10">
         <f t="shared" si="134"/>
         <v>0.10069813372386889</v>
       </c>
-      <c r="AN59" s="8">
+      <c r="AN59" s="10">
         <f t="shared" si="134"/>
         <v>0.1007089810537752</v>
       </c>
-      <c r="AO59" s="8">
+      <c r="AO59" s="10">
         <f t="shared" si="134"/>
         <v>0.10072197469523517</v>
       </c>
     </row>
-    <row r="61" spans="2:45" s="15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="15" t="s">
+    <row r="61" spans="2:45" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="T61" s="17">
+      <c r="T61" s="14">
         <v>14593</v>
       </c>
-      <c r="U61" s="17">
+      <c r="U61" s="14">
         <v>15658</v>
       </c>
-      <c r="AE61" s="17">
+      <c r="AE61" s="14">
         <v>15658</v>
       </c>
     </row>
     <row r="63" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="T63" s="16"/>
-      <c r="AE63" s="16">
+      <c r="T63" s="15"/>
+      <c r="AE63" s="15">
         <f>Main!$D$9/Model!AE61</f>
-        <v>4.4805342317026442</v>
+        <v>4.6444574658321631</v>
       </c>
     </row>
     <row r="64" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="T64" s="8"/>
-      <c r="AE64" s="8">
+      <c r="T64" s="10"/>
+      <c r="AE64" s="10">
         <f>AE61/Main!$D$9-1</f>
-        <v>-0.7768123290021175</v>
+        <v>-0.78468959886990231</v>
       </c>
     </row>
     <row r="67" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>92</v>
       </c>
       <c r="O67" s="3">
@@ -7889,105 +7925,105 @@
         <v>1888.0046081015969</v>
       </c>
     </row>
-    <row r="68" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="1" t="s">
+    <row r="68" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="O68" s="6">
+      <c r="O68" s="7">
         <v>54</v>
       </c>
-      <c r="P68" s="6">
+      <c r="P68" s="7">
         <f>133-O68</f>
         <v>79</v>
       </c>
-      <c r="Q68" s="6">
+      <c r="Q68" s="7">
         <f>306-P68-O68</f>
         <v>173</v>
       </c>
-      <c r="R68" s="6">
+      <c r="R68" s="7">
         <f>AD68-Q68-P68-O68</f>
         <v>502</v>
       </c>
-      <c r="S68" s="6">
+      <c r="S68" s="7">
         <v>108</v>
       </c>
-      <c r="T68" s="6">
+      <c r="T68" s="7">
         <f>267-S68</f>
         <v>159</v>
       </c>
-      <c r="U68" s="6">
+      <c r="U68" s="7">
         <f>U86-T68-S68</f>
         <v>203</v>
       </c>
-      <c r="V68" s="6">
+      <c r="V68" s="7">
         <f>V67</f>
         <v>636.60340799999994</v>
       </c>
-      <c r="Y68" s="1">
+      <c r="Y68" s="4">
         <v>354</v>
       </c>
-      <c r="Z68" s="1">
+      <c r="Z68" s="4">
         <v>1</v>
       </c>
-      <c r="AA68" s="1">
+      <c r="AA68" s="4">
         <v>332</v>
       </c>
-      <c r="AB68" s="1">
+      <c r="AB68" s="4">
         <v>535</v>
       </c>
-      <c r="AC68" s="1">
+      <c r="AC68" s="4">
         <v>586</v>
       </c>
-      <c r="AD68" s="6">
+      <c r="AD68" s="7">
         <v>808</v>
       </c>
-      <c r="AE68" s="6">
+      <c r="AE68" s="7">
         <f>AE67*1.1</f>
         <v>1118.2637488000009</v>
       </c>
-      <c r="AF68" s="6">
+      <c r="AF68" s="7">
         <f t="shared" ref="AF68:AO68" si="138">AF67*1.1</f>
         <v>1457.8302495899991</v>
       </c>
-      <c r="AG68" s="6">
+      <c r="AG68" s="7">
         <f t="shared" si="138"/>
         <v>1647.2548448070002</v>
       </c>
-      <c r="AH68" s="6">
+      <c r="AH68" s="7">
         <f t="shared" si="138"/>
         <v>1758.1944294979357</v>
       </c>
-      <c r="AI68" s="6">
+      <c r="AI68" s="7">
         <f t="shared" si="138"/>
         <v>1827.9864943033765</v>
       </c>
-      <c r="AJ68" s="6">
+      <c r="AJ68" s="7">
         <f t="shared" si="138"/>
         <v>1871.7154918827989</v>
       </c>
-      <c r="AK68" s="6">
+      <c r="AK68" s="7">
         <f t="shared" si="138"/>
         <v>1910.8288256425658</v>
       </c>
-      <c r="AL68" s="6">
+      <c r="AL68" s="7">
         <f t="shared" si="138"/>
         <v>1950.8695951713621</v>
       </c>
-      <c r="AM68" s="6">
+      <c r="AM68" s="7">
         <f t="shared" si="138"/>
         <v>1991.8622950448348</v>
       </c>
-      <c r="AN68" s="6">
+      <c r="AN68" s="7">
         <f t="shared" si="138"/>
         <v>2033.8321361539952</v>
       </c>
-      <c r="AO68" s="6">
+      <c r="AO68" s="7">
         <f t="shared" si="138"/>
         <v>2076.8050689117567</v>
       </c>
     </row>
     <row r="69" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>12</v>
       </c>
       <c r="O69" s="3">
@@ -8084,7 +8120,7 @@
       </c>
     </row>
     <row r="70" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>94</v>
       </c>
       <c r="O70" s="3"/>
@@ -8142,7 +8178,7 @@
       </c>
     </row>
     <row r="71" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>95</v>
       </c>
       <c r="O71" s="3">
@@ -8173,7 +8209,7 @@
         <f t="shared" ref="U71:U75" si="142">U90-T71-S71</f>
         <v>-34</v>
       </c>
-      <c r="V71">
+      <c r="V71" s="1">
         <v>-25</v>
       </c>
       <c r="Y71" s="3">
@@ -8246,7 +8282,7 @@
       </c>
     </row>
     <row r="72" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>96</v>
       </c>
       <c r="O72" s="3">
@@ -8331,7 +8367,7 @@
       </c>
     </row>
     <row r="73" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>97</v>
       </c>
       <c r="O73" s="3">
@@ -8360,7 +8396,7 @@
         <f t="shared" si="142"/>
         <v>19</v>
       </c>
-      <c r="V73">
+      <c r="V73" s="1">
         <v>110</v>
       </c>
       <c r="Y73" s="3">
@@ -8417,7 +8453,7 @@
       </c>
     </row>
     <row r="74" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>98</v>
       </c>
       <c r="O74" s="3">
@@ -8446,7 +8482,7 @@
         <f t="shared" si="142"/>
         <v>-298</v>
       </c>
-      <c r="V74">
+      <c r="V74" s="1">
         <f>R74*1.5</f>
         <v>837</v>
       </c>
@@ -8504,7 +8540,7 @@
       </c>
     </row>
     <row r="75" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>99</v>
       </c>
       <c r="O75" s="3">
@@ -8533,7 +8569,7 @@
         <f t="shared" si="142"/>
         <v>46</v>
       </c>
-      <c r="V75">
+      <c r="V75" s="1">
         <v>0</v>
       </c>
       <c r="Y75" s="3">
@@ -8590,7 +8626,7 @@
       </c>
     </row>
     <row r="76" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>100</v>
       </c>
       <c r="O76" s="3"/>
@@ -8644,7 +8680,7 @@
       </c>
     </row>
     <row r="77" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>101</v>
       </c>
       <c r="O77" s="3">
@@ -8673,7 +8709,7 @@
         <f t="shared" ref="U77:U79" si="145">U96-T77-S77</f>
         <v>4</v>
       </c>
-      <c r="V77">
+      <c r="V77" s="1">
         <v>0</v>
       </c>
       <c r="Y77" s="3">
@@ -8730,7 +8766,7 @@
       </c>
     </row>
     <row r="78" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>102</v>
       </c>
       <c r="O78" s="3">
@@ -8758,7 +8794,7 @@
         <f t="shared" si="145"/>
         <v>2</v>
       </c>
-      <c r="V78">
+      <c r="V78" s="1">
         <v>5</v>
       </c>
       <c r="Y78" s="3">
@@ -8815,7 +8851,7 @@
       </c>
     </row>
     <row r="79" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>103</v>
       </c>
       <c r="O79" s="3">
@@ -8844,7 +8880,7 @@
         <f t="shared" si="145"/>
         <v>-10</v>
       </c>
-      <c r="V79">
+      <c r="V79" s="1">
         <v>0</v>
       </c>
       <c r="Y79" s="3">
@@ -8900,113 +8936,113 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="1" t="s">
+    <row r="80" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="O80" s="6">
+      <c r="O80" s="7">
         <f t="shared" ref="O80:P80" si="146">O68+SUM(O69:O79)</f>
         <v>-105</v>
       </c>
-      <c r="P80" s="6">
+      <c r="P80" s="7">
         <f t="shared" si="146"/>
         <v>297</v>
       </c>
-      <c r="Q80" s="6">
+      <c r="Q80" s="7">
         <f t="shared" ref="Q80:R80" si="147">Q68+SUM(Q69:Q79)</f>
         <v>300</v>
       </c>
-      <c r="R80" s="6">
+      <c r="R80" s="7">
         <f t="shared" si="147"/>
         <v>1227</v>
       </c>
-      <c r="S80" s="6">
+      <c r="S80" s="7">
         <f t="shared" ref="S80:T80" si="148">S68+SUM(S69:S79)</f>
         <v>420</v>
       </c>
-      <c r="T80" s="6">
+      <c r="T80" s="7">
         <f t="shared" si="148"/>
         <v>-697</v>
       </c>
-      <c r="U80" s="6">
+      <c r="U80" s="7">
         <f>U68+SUM(U69:U79)</f>
         <v>62</v>
       </c>
-      <c r="V80" s="6">
+      <c r="V80" s="7">
         <f>V68+SUM(V69:V79)</f>
         <v>1740.003408</v>
       </c>
-      <c r="Y80" s="6">
+      <c r="Y80" s="7">
         <f t="shared" ref="Y80:AD80" si="149">Y68+SUM(Y69:Y79)</f>
         <v>602</v>
       </c>
-      <c r="Z80" s="6">
+      <c r="Z80" s="7">
         <f t="shared" si="149"/>
         <v>453</v>
       </c>
-      <c r="AA80" s="6">
+      <c r="AA80" s="7">
         <f t="shared" si="149"/>
         <v>690</v>
       </c>
-      <c r="AB80" s="6">
+      <c r="AB80" s="7">
         <f t="shared" si="149"/>
         <v>174</v>
       </c>
-      <c r="AC80" s="6">
+      <c r="AC80" s="7">
         <f t="shared" si="149"/>
         <v>742</v>
       </c>
-      <c r="AD80" s="6">
+      <c r="AD80" s="7">
         <f t="shared" si="149"/>
         <v>1719</v>
       </c>
-      <c r="AE80" s="6">
+      <c r="AE80" s="7">
         <f t="shared" ref="AE80:AO80" si="150">AE68+SUM(AE69:AE79)</f>
         <v>1536.663748800001</v>
       </c>
-      <c r="AF80" s="6">
+      <c r="AF80" s="7">
         <f t="shared" si="150"/>
         <v>2019.440249589999</v>
       </c>
-      <c r="AG80" s="6">
+      <c r="AG80" s="7">
         <f t="shared" si="150"/>
         <v>2265.0258448069999</v>
       </c>
-      <c r="AH80" s="6">
+      <c r="AH80" s="7">
         <f t="shared" si="150"/>
         <v>2404.1314794979357</v>
       </c>
-      <c r="AI80" s="6">
+      <c r="AI80" s="7">
         <f t="shared" si="150"/>
         <v>2496.1673263033763</v>
       </c>
-      <c r="AJ80" s="6">
+      <c r="AJ80" s="7">
         <f t="shared" si="150"/>
         <v>2555.3298338427985</v>
       </c>
-      <c r="AK80" s="6">
+      <c r="AK80" s="7">
         <f t="shared" si="150"/>
         <v>2602.3176184417657</v>
       </c>
-      <c r="AL80" s="6">
+      <c r="AL80" s="7">
         <f t="shared" si="150"/>
         <v>2649.810544226546</v>
       </c>
-      <c r="AM80" s="6">
+      <c r="AM80" s="7">
         <f t="shared" si="150"/>
         <v>2697.7666815211223</v>
       </c>
-      <c r="AN80" s="6">
+      <c r="AN80" s="7">
         <f t="shared" si="150"/>
         <v>2746.1376906438086</v>
       </c>
-      <c r="AO80" s="6">
+      <c r="AO80" s="7">
         <f t="shared" si="150"/>
         <v>2794.8681228037663</v>
       </c>
     </row>
     <row r="81" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>105</v>
       </c>
       <c r="O81" s="3">
@@ -9102,520 +9138,520 @@
         <v>962.0452775113215</v>
       </c>
     </row>
-    <row r="82" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="1" t="s">
+    <row r="82" spans="2:139" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="O82" s="6">
+      <c r="O82" s="7">
         <f t="shared" ref="O82:P82" si="153">O80-O81</f>
         <v>-210</v>
       </c>
-      <c r="P82" s="6">
+      <c r="P82" s="7">
         <f t="shared" si="153"/>
         <v>170</v>
       </c>
-      <c r="Q82" s="6">
+      <c r="Q82" s="7">
         <f t="shared" ref="Q82:R82" si="154">Q80-Q81</f>
         <v>116</v>
       </c>
-      <c r="R82" s="6">
+      <c r="R82" s="7">
         <f t="shared" si="154"/>
         <v>911</v>
       </c>
-      <c r="S82" s="6">
+      <c r="S82" s="7">
         <f t="shared" ref="S82:V82" si="155">S80-S81</f>
         <v>267</v>
       </c>
-      <c r="T82" s="6">
+      <c r="T82" s="7">
         <f t="shared" si="155"/>
         <v>-896</v>
       </c>
-      <c r="U82" s="6">
+      <c r="U82" s="7">
         <f t="shared" si="155"/>
         <v>-184</v>
       </c>
-      <c r="V82" s="6">
+      <c r="V82" s="7">
         <f t="shared" si="155"/>
         <v>1297.6034079999999</v>
       </c>
-      <c r="Y82" s="6">
+      <c r="Y82" s="7">
         <f t="shared" ref="Y82:AD82" si="156">Y80-Y81</f>
         <v>314</v>
       </c>
-      <c r="Z82" s="6">
+      <c r="Z82" s="7">
         <f t="shared" si="156"/>
         <v>216</v>
       </c>
-      <c r="AA82" s="6">
+      <c r="AA82" s="7">
         <f t="shared" si="156"/>
         <v>419</v>
       </c>
-      <c r="AB82" s="6">
+      <c r="AB82" s="7">
         <f t="shared" si="156"/>
         <v>-175</v>
       </c>
-      <c r="AC82" s="6">
+      <c r="AC82" s="7">
         <f t="shared" si="156"/>
         <v>344</v>
       </c>
-      <c r="AD82" s="6">
+      <c r="AD82" s="7">
         <f t="shared" si="156"/>
         <v>987</v>
       </c>
-      <c r="AE82" s="6">
+      <c r="AE82" s="7">
         <f t="shared" ref="AE82:AO82" si="157">AE80-AE81</f>
         <v>496.26374880000094</v>
       </c>
-      <c r="AF82" s="6">
+      <c r="AF82" s="7">
         <f t="shared" si="157"/>
         <v>875.0002495899987</v>
       </c>
-      <c r="AG82" s="6">
+      <c r="AG82" s="7">
         <f t="shared" si="157"/>
         <v>1097.6970448069997</v>
       </c>
-      <c r="AH82" s="6">
+      <c r="AH82" s="7">
         <f t="shared" si="157"/>
         <v>1213.4561034979356</v>
       </c>
-      <c r="AI82" s="6">
+      <c r="AI82" s="7">
         <f t="shared" si="157"/>
         <v>1341.2122115833761</v>
       </c>
-      <c r="AJ82" s="6">
+      <c r="AJ82" s="7">
         <f t="shared" si="157"/>
         <v>1435.0233725643984</v>
       </c>
-      <c r="AK82" s="6">
+      <c r="AK82" s="7">
         <f t="shared" si="157"/>
         <v>1515.6203510017176</v>
       </c>
-      <c r="AL82" s="6">
+      <c r="AL82" s="7">
         <f t="shared" si="157"/>
         <v>1595.7141948096994</v>
       </c>
-      <c r="AM82" s="6">
+      <c r="AM82" s="7">
         <f t="shared" si="157"/>
         <v>1675.2932225867812</v>
       </c>
-      <c r="AN82" s="6">
+      <c r="AN82" s="7">
         <f t="shared" si="157"/>
         <v>1754.3384354774976</v>
       </c>
-      <c r="AO82" s="6">
+      <c r="AO82" s="7">
         <f t="shared" si="157"/>
         <v>1832.8228452924448</v>
       </c>
-      <c r="AP82" s="1">
+      <c r="AP82" s="4">
         <f>AO82*(1+AS45)</f>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AQ82" s="1">
+      <c r="AQ82" s="4">
         <f t="shared" ref="AQ82:DB82" si="158">AP82*(1+AT45)</f>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AR82" s="1">
+      <c r="AR82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AS82" s="1">
+      <c r="AS82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AT82" s="1">
+      <c r="AT82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AU82" s="1">
+      <c r="AU82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AV82" s="1">
+      <c r="AV82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AW82" s="1">
+      <c r="AW82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AX82" s="1">
+      <c r="AX82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AY82" s="1">
+      <c r="AY82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="AZ82" s="1">
+      <c r="AZ82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BA82" s="1">
+      <c r="BA82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BB82" s="1">
+      <c r="BB82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BC82" s="1">
+      <c r="BC82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BD82" s="1">
+      <c r="BD82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BE82" s="1">
+      <c r="BE82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BF82" s="1">
+      <c r="BF82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BG82" s="1">
+      <c r="BG82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BH82" s="1">
+      <c r="BH82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BI82" s="1">
+      <c r="BI82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BJ82" s="1">
+      <c r="BJ82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BK82" s="1">
+      <c r="BK82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BL82" s="1">
+      <c r="BL82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BM82" s="1">
+      <c r="BM82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BN82" s="1">
+      <c r="BN82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BO82" s="1">
+      <c r="BO82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BP82" s="1">
+      <c r="BP82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BQ82" s="1">
+      <c r="BQ82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BR82" s="1">
+      <c r="BR82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BS82" s="1">
+      <c r="BS82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BT82" s="1">
+      <c r="BT82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BU82" s="1">
+      <c r="BU82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BV82" s="1">
+      <c r="BV82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BW82" s="1">
+      <c r="BW82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BX82" s="1">
+      <c r="BX82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BY82" s="1">
+      <c r="BY82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="BZ82" s="1">
+      <c r="BZ82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CA82" s="1">
+      <c r="CA82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CB82" s="1">
+      <c r="CB82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CC82" s="1">
+      <c r="CC82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CD82" s="1">
+      <c r="CD82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CE82" s="1">
+      <c r="CE82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CF82" s="1">
+      <c r="CF82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CG82" s="1">
+      <c r="CG82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CH82" s="1">
+      <c r="CH82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CI82" s="1">
+      <c r="CI82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CJ82" s="1">
+      <c r="CJ82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CK82" s="1">
+      <c r="CK82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CL82" s="1">
+      <c r="CL82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CM82" s="1">
+      <c r="CM82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CN82" s="1">
+      <c r="CN82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CO82" s="1">
+      <c r="CO82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CP82" s="1">
+      <c r="CP82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CQ82" s="1">
+      <c r="CQ82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CR82" s="1">
+      <c r="CR82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CS82" s="1">
+      <c r="CS82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CT82" s="1">
+      <c r="CT82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CU82" s="1">
+      <c r="CU82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CV82" s="1">
+      <c r="CV82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CW82" s="1">
+      <c r="CW82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CX82" s="1">
+      <c r="CX82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CY82" s="1">
+      <c r="CY82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="CZ82" s="1">
+      <c r="CZ82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DA82" s="1">
+      <c r="DA82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DB82" s="1">
+      <c r="DB82" s="4">
         <f t="shared" si="158"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DC82" s="1">
+      <c r="DC82" s="4">
         <f t="shared" ref="DC82:EI82" si="159">DB82*(1+DF45)</f>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DD82" s="1">
+      <c r="DD82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DE82" s="1">
+      <c r="DE82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DF82" s="1">
+      <c r="DF82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DG82" s="1">
+      <c r="DG82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DH82" s="1">
+      <c r="DH82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DI82" s="1">
+      <c r="DI82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DJ82" s="1">
+      <c r="DJ82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DK82" s="1">
+      <c r="DK82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DL82" s="1">
+      <c r="DL82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DM82" s="1">
+      <c r="DM82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DN82" s="1">
+      <c r="DN82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DO82" s="1">
+      <c r="DO82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DP82" s="1">
+      <c r="DP82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DQ82" s="1">
+      <c r="DQ82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DR82" s="1">
+      <c r="DR82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DS82" s="1">
+      <c r="DS82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DT82" s="1">
+      <c r="DT82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DU82" s="1">
+      <c r="DU82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DV82" s="1">
+      <c r="DV82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DW82" s="1">
+      <c r="DW82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DX82" s="1">
+      <c r="DX82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DY82" s="1">
+      <c r="DY82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="DZ82" s="1">
+      <c r="DZ82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="EA82" s="1">
+      <c r="EA82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="EB82" s="1">
+      <c r="EB82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="EC82" s="1">
+      <c r="EC82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="ED82" s="1">
+      <c r="ED82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="EE82" s="1">
+      <c r="EE82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="EF82" s="1">
+      <c r="EF82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="EG82" s="1">
+      <c r="EG82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="EH82" s="1">
+      <c r="EH82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
-      <c r="EI82" s="1">
+      <c r="EI82" s="4">
         <f t="shared" si="159"/>
         <v>1814.4946168395202</v>
       </c>
     </row>
     <row r="84" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="S84" s="8">
+      <c r="S84" s="10">
         <f>S81/O81-1</f>
         <v>0.45714285714285707</v>
       </c>
-      <c r="T84" s="8">
+      <c r="T84" s="10">
         <f t="shared" ref="T84:V84" si="160">T81/P81-1</f>
         <v>0.56692913385826782</v>
       </c>
-      <c r="U84" s="8">
+      <c r="U84" s="10">
         <f t="shared" si="160"/>
         <v>0.33695652173913038</v>
       </c>
-      <c r="V84" s="8">
+      <c r="V84" s="10">
         <f t="shared" si="160"/>
         <v>0.39999999999999991</v>
       </c>
@@ -9631,7 +9667,7 @@
       </c>
     </row>
     <row r="86" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="U86">
+      <c r="U86" s="1">
         <v>470</v>
       </c>
       <c r="AS86" s="3"/>
@@ -9640,10 +9676,10 @@
       <c r="AS87" s="3"/>
     </row>
     <row r="88" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="U88">
+      <c r="U88" s="1">
         <v>355</v>
       </c>
       <c r="AS88" s="3">
@@ -9652,112 +9688,112 @@
       </c>
     </row>
     <row r="89" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AS89" s="12">
+      <c r="AS89" s="16">
         <f>AS88/AO38</f>
         <v>449.80066738057144</v>
       </c>
     </row>
     <row r="90" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="U90">
+      <c r="U90" s="1">
         <f>-21+1</f>
         <v>-20</v>
       </c>
-      <c r="AS90" s="12">
+      <c r="AS90" s="16">
         <f>Main!D3</f>
-        <v>1523.5</v>
+        <v>1580.5</v>
       </c>
     </row>
     <row r="91" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="U91">
+      <c r="U91" s="1">
         <v>14</v>
       </c>
-      <c r="AS91" s="7">
+      <c r="AS91" s="11">
         <f>AS89/AS90-1</f>
-        <v>-0.70475834106952973</v>
+        <v>-0.71540609466588334</v>
       </c>
     </row>
     <row r="92" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="U92">
+      <c r="U92" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="93" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="U93">
+      <c r="U93" s="1">
         <v>-967</v>
       </c>
     </row>
     <row r="94" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="U94">
+      <c r="U94" s="1">
         <v>-54</v>
       </c>
     </row>
     <row r="95" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="96" spans="2:139" x14ac:dyDescent="0.3">
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="U96">
+      <c r="U96" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="97" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B97" t="s">
+      <c r="B97" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="U97">
+      <c r="U97" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="98" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="U98">
+      <c r="U98" s="1">
         <v>-35</v>
       </c>
     </row>
     <row r="99" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="4" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="100" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B100" t="s">
+      <c r="B100" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="U100">
+      <c r="U100" s="1">
         <v>598</v>
       </c>
     </row>
     <row r="101" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="4" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Financial Analysis/RHM.xlsx
+++ b/Financial Analysis/RHM.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6E8BCD-FFC9-4392-9CB4-68AC31142174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D830C778-63B9-4984-B553-8C3858235086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{43F12638-722A-4181-A3AA-4360C00656D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
+    <sheet name="Segment Backlog" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="126">
   <si>
     <t>RHM</t>
   </si>
@@ -362,6 +363,92 @@
   </si>
   <si>
     <t>Disposals</t>
+  </si>
+  <si>
+    <t>Weapon &amp; Ammunition</t>
+  </si>
+  <si>
+    <t>Total Nomination</t>
+  </si>
+  <si>
+    <t>Vehicle Systems</t>
+  </si>
+  <si>
+    <t>Electronic Solutions</t>
+  </si>
+  <si>
+    <t>Power Systems</t>
+  </si>
+  <si>
+    <t>Rheinmetall Backlog</t>
+  </si>
+  <si>
+    <t>Total Segment Backlog</t>
+  </si>
+  <si>
+    <t>Eliminations</t>
+  </si>
+  <si>
+    <t>frame backlog tracks as external, so there are no intercompany eliminations</t>
+  </si>
+  <si>
+    <t>whereas segmented order backlog includes inter-segment/internal orders</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">“Segment-level order backlog is shown </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>before consolidation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, so the sum of segments is higher than the Group figure due to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intra-group eliminations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; frame backlog is externally driven and therefore aligns at Group level.”</t>
+    </r>
+  </si>
+  <si>
+    <t>Implied backlog burn</t>
+  </si>
+  <si>
+    <t>Old backlog + intake</t>
+  </si>
+  <si>
+    <t>Backlog burn change y/y</t>
   </si>
 </sst>
 </file>
@@ -373,7 +460,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-1]"/>
     <numFmt numFmtId="166" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,6 +500,14 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
@@ -461,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -493,6 +588,9 @@
     <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -610,6 +708,72 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88EC4D4D-146A-7E40-AC37-66E224A5C787}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7376160" y="678180"/>
+          <a:ext cx="5737860" cy="4107180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -969,7 +1133,7 @@
       </c>
       <c r="F3" s="18">
         <f ca="1">TODAY()</f>
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="G3" s="18">
         <v>46092</v>
@@ -2362,44 +2526,44 @@
         <v>1940.1</v>
       </c>
       <c r="AF16" s="3">
-        <f t="shared" ref="AF16:AO16" si="9">AE16*1.01</f>
-        <v>1959.501</v>
+        <f>AE16*0.97</f>
+        <v>1881.8969999999999</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" si="9"/>
-        <v>1979.09601</v>
+        <f t="shared" ref="AG16:AO16" si="9">AF16*0.97</f>
+        <v>1825.4400899999998</v>
       </c>
       <c r="AH16" s="3">
         <f t="shared" si="9"/>
-        <v>1998.8869701000001</v>
+        <v>1770.6768872999999</v>
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="9"/>
-        <v>2018.8758398010002</v>
+        <v>1717.5565806809998</v>
       </c>
       <c r="AJ16" s="3">
         <f t="shared" si="9"/>
-        <v>2039.0645981990103</v>
+        <v>1666.0298832605697</v>
       </c>
       <c r="AK16" s="3">
         <f t="shared" si="9"/>
-        <v>2059.4552441810006</v>
+        <v>1616.0489867627525</v>
       </c>
       <c r="AL16" s="3">
         <f t="shared" si="9"/>
-        <v>2080.0497966228104</v>
+        <v>1567.5675171598698</v>
       </c>
       <c r="AM16" s="3">
         <f t="shared" si="9"/>
-        <v>2100.8502945890386</v>
+        <v>1520.5404916450736</v>
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="9"/>
-        <v>2121.8587975349292</v>
+        <v>1474.9242768957215</v>
       </c>
       <c r="AO16" s="3">
         <f t="shared" si="9"/>
-        <v>2143.0773855102784</v>
+        <v>1430.6765485888498</v>
       </c>
     </row>
     <row r="17" spans="2:41" x14ac:dyDescent="0.3">
@@ -2621,43 +2785,43 @@
       </c>
       <c r="AF18" s="7">
         <f t="shared" ref="AF18:AO18" si="14">SUM(AF13:AF17)</f>
-        <v>14011.873800000001</v>
+        <v>13934.269800000002</v>
       </c>
       <c r="AG18" s="7">
         <f t="shared" si="14"/>
-        <v>15246.44224</v>
+        <v>15092.786320000001</v>
       </c>
       <c r="AH18" s="7">
         <f t="shared" si="14"/>
-        <v>16022.519471700001</v>
+        <v>15794.309388900001</v>
       </c>
       <c r="AI18" s="7">
         <f t="shared" si="14"/>
-        <v>16527.716567721003</v>
+        <v>16226.397308600999</v>
       </c>
       <c r="AJ18" s="7">
         <f t="shared" si="14"/>
-        <v>16900.941494513012</v>
+        <v>16527.906779574572</v>
       </c>
       <c r="AK18" s="7">
         <f t="shared" si="14"/>
-        <v>17253.357441215794</v>
+        <v>16809.951183797544</v>
       </c>
       <c r="AL18" s="7">
         <f t="shared" si="14"/>
-        <v>17613.744676436647</v>
+        <v>17101.262396973707</v>
       </c>
       <c r="AM18" s="7">
         <f t="shared" si="14"/>
-        <v>17982.298555320653</v>
+        <v>17401.988752376688</v>
       </c>
       <c r="AN18" s="7">
         <f t="shared" si="14"/>
-        <v>18359.219666886216</v>
+        <v>17712.28514624701</v>
       </c>
       <c r="AO18" s="7">
         <f t="shared" si="14"/>
-        <v>18744.71398931888</v>
+        <v>18032.313152397452</v>
       </c>
     </row>
     <row r="19" spans="2:41" x14ac:dyDescent="0.3">
@@ -2855,43 +3019,43 @@
       <c r="AE20" s="3"/>
       <c r="AF20" s="3">
         <f>AF18*0.45</f>
-        <v>6305.3432100000009</v>
+        <v>6270.4214100000008</v>
       </c>
       <c r="AG20" s="3">
         <f t="shared" ref="AG20:AO20" si="16">AG18*0.45</f>
-        <v>6860.8990080000003</v>
+        <v>6791.7538440000008</v>
       </c>
       <c r="AH20" s="3">
         <f t="shared" si="16"/>
-        <v>7210.1337622650008</v>
+        <v>7107.4392250050005</v>
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="16"/>
-        <v>7437.4724554744516</v>
+        <v>7301.8787888704501</v>
       </c>
       <c r="AJ20" s="3">
         <f t="shared" si="16"/>
-        <v>7605.4236725308556</v>
+        <v>7437.5580508085577</v>
       </c>
       <c r="AK20" s="3">
         <f t="shared" si="16"/>
-        <v>7764.0108485471073</v>
+        <v>7564.4780327088947</v>
       </c>
       <c r="AL20" s="3">
         <f t="shared" si="16"/>
-        <v>7926.1851043964916</v>
+        <v>7695.5680786381681</v>
       </c>
       <c r="AM20" s="3">
         <f t="shared" si="16"/>
-        <v>8092.0343498942939</v>
+        <v>7830.8949385695096</v>
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="16"/>
-        <v>8261.648850098798</v>
+        <v>7970.5283158111542</v>
       </c>
       <c r="AO20" s="3">
         <f t="shared" si="16"/>
-        <v>8435.1212951934958</v>
+        <v>8114.5409185788531</v>
       </c>
     </row>
     <row r="21" spans="2:41" x14ac:dyDescent="0.3">
@@ -2970,43 +3134,43 @@
       </c>
       <c r="AF21" s="3">
         <f>AF18*0.28</f>
-        <v>3923.3246640000007</v>
+        <v>3901.5955440000007</v>
       </c>
       <c r="AG21" s="3">
         <f t="shared" ref="AG21:AO21" si="17">AG18*0.28</f>
-        <v>4269.0038272000002</v>
+        <v>4225.9801696000004</v>
       </c>
       <c r="AH21" s="3">
         <f t="shared" si="17"/>
-        <v>4486.3054520760006</v>
+        <v>4422.4066288920003</v>
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="17"/>
-        <v>4627.7606389618813</v>
+        <v>4543.3912464082805</v>
       </c>
       <c r="AJ21" s="3">
         <f t="shared" si="17"/>
-        <v>4732.263618463644</v>
+        <v>4627.8138982808805</v>
       </c>
       <c r="AK21" s="3">
         <f t="shared" si="17"/>
-        <v>4830.9400835404231</v>
+        <v>4706.7863314633132</v>
       </c>
       <c r="AL21" s="3">
         <f t="shared" si="17"/>
-        <v>4931.8485094022617</v>
+        <v>4788.3534711526381</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" si="17"/>
-        <v>5035.043595489783</v>
+        <v>4872.5568506654736</v>
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="17"/>
-        <v>5140.581506728141</v>
+        <v>4959.4398409491632</v>
       </c>
       <c r="AO21" s="3">
         <f t="shared" si="17"/>
-        <v>5248.5199170092865</v>
+        <v>5049.0476826712866</v>
       </c>
     </row>
     <row r="22" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3111,43 +3275,43 @@
       </c>
       <c r="AF22" s="7">
         <f t="shared" ref="AF22:AO22" si="22">SUM(AF19:AF21)</f>
-        <v>10228.667874000002</v>
+        <v>10172.016954000002</v>
       </c>
       <c r="AG22" s="7">
         <f t="shared" si="22"/>
-        <v>11129.9028352</v>
+        <v>11017.734013600002</v>
       </c>
       <c r="AH22" s="7">
         <f t="shared" si="22"/>
-        <v>11696.439214341</v>
+        <v>11529.845853897001</v>
       </c>
       <c r="AI22" s="7">
         <f t="shared" si="22"/>
-        <v>12065.233094436333</v>
+        <v>11845.270035278731</v>
       </c>
       <c r="AJ22" s="7">
         <f t="shared" si="22"/>
-        <v>12337.6872909945</v>
+        <v>12065.371949089438</v>
       </c>
       <c r="AK22" s="7">
         <f t="shared" si="22"/>
-        <v>12594.95093208753</v>
+        <v>12271.264364172208</v>
       </c>
       <c r="AL22" s="7">
         <f t="shared" si="22"/>
-        <v>12858.033613798754</v>
+        <v>12483.921549790806</v>
       </c>
       <c r="AM22" s="7">
         <f t="shared" si="22"/>
-        <v>13127.077945384077</v>
+        <v>12703.451789234983</v>
       </c>
       <c r="AN22" s="7">
         <f t="shared" si="22"/>
-        <v>13402.230356826938</v>
+        <v>12929.968156760318</v>
       </c>
       <c r="AO22" s="7">
         <f t="shared" si="22"/>
-        <v>13683.641212202783</v>
+        <v>13163.58860125014</v>
       </c>
     </row>
     <row r="23" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3252,43 +3416,43 @@
       </c>
       <c r="AF23" s="7">
         <f t="shared" si="26"/>
-        <v>3783.2059259999987</v>
+        <v>3762.2528459999994</v>
       </c>
       <c r="AG23" s="7">
         <f t="shared" si="26"/>
-        <v>4116.5394047999998</v>
+        <v>4075.052306399999</v>
       </c>
       <c r="AH23" s="7">
         <f t="shared" si="26"/>
-        <v>4326.0802573590008</v>
+        <v>4264.4635350030003</v>
       </c>
       <c r="AI23" s="7">
         <f t="shared" si="26"/>
-        <v>4462.4834732846703</v>
+        <v>4381.1272733222686</v>
       </c>
       <c r="AJ23" s="7">
         <f t="shared" si="26"/>
-        <v>4563.2542035185124</v>
+        <v>4462.5348304851341</v>
       </c>
       <c r="AK23" s="7">
         <f t="shared" si="26"/>
-        <v>4658.4065091282646</v>
+        <v>4538.6868196253363</v>
       </c>
       <c r="AL23" s="7">
         <f t="shared" si="26"/>
-        <v>4755.7110626378926</v>
+        <v>4617.3408471829007</v>
       </c>
       <c r="AM23" s="7">
         <f t="shared" si="26"/>
-        <v>4855.2206099365758</v>
+        <v>4698.5369631417052</v>
       </c>
       <c r="AN23" s="7">
         <f t="shared" si="26"/>
-        <v>4956.9893100592781</v>
+        <v>4782.3169894866915</v>
       </c>
       <c r="AO23" s="7">
         <f t="shared" si="26"/>
-        <v>5061.0727771160964</v>
+        <v>4868.724551147312</v>
       </c>
     </row>
     <row r="24" spans="2:41" x14ac:dyDescent="0.3">
@@ -3800,43 +3964,43 @@
       </c>
       <c r="AF28" s="7">
         <f t="shared" si="35"/>
-        <v>2175.6559259999985</v>
+        <v>2154.7028459999992</v>
       </c>
       <c r="AG28" s="7">
         <f t="shared" si="35"/>
-        <v>2444.6874048</v>
+        <v>2403.2003063999991</v>
       </c>
       <c r="AH28" s="7">
         <f t="shared" si="35"/>
-        <v>2604.0726973590008</v>
+        <v>2542.4559750030003</v>
       </c>
       <c r="AI28" s="7">
         <f t="shared" si="35"/>
-        <v>2706.0357620846698</v>
+        <v>2624.6795621222682</v>
       </c>
       <c r="AJ28" s="7">
         <f t="shared" si="35"/>
-        <v>2771.6775380945123</v>
+        <v>2670.958165061134</v>
       </c>
       <c r="AK28" s="7">
         <f t="shared" si="35"/>
-        <v>2830.9983103957848</v>
+        <v>2711.2786208928565</v>
       </c>
       <c r="AL28" s="7">
         <f t="shared" si="35"/>
-        <v>2891.7546999307629</v>
+        <v>2753.3844844757709</v>
       </c>
       <c r="AM28" s="7">
         <f t="shared" si="35"/>
-        <v>2953.9851199753034</v>
+        <v>2797.3014731804328</v>
       </c>
       <c r="AN28" s="7">
         <f t="shared" si="35"/>
-        <v>3017.7291102987801</v>
+        <v>2843.0567897261935</v>
       </c>
       <c r="AO28" s="7">
         <f t="shared" si="35"/>
-        <v>3083.0273733603885</v>
+        <v>2890.6791473916041</v>
       </c>
     </row>
     <row r="29" spans="2:41" x14ac:dyDescent="0.3">
@@ -4426,43 +4590,43 @@
       </c>
       <c r="AF34" s="7">
         <f t="shared" si="43"/>
-        <v>2038.9234259999985</v>
+        <v>2017.9703459999992</v>
       </c>
       <c r="AG34" s="7">
         <f t="shared" si="43"/>
-        <v>2303.8529297999999</v>
+        <v>2262.365831399999</v>
       </c>
       <c r="AH34" s="7">
         <f t="shared" si="43"/>
-        <v>2459.013188109001</v>
+        <v>2397.3964657530005</v>
       </c>
       <c r="AI34" s="7">
         <f t="shared" si="43"/>
-        <v>2556.6244675571697</v>
+        <v>2475.2682675947681</v>
       </c>
       <c r="AJ34" s="7">
         <f t="shared" si="43"/>
-        <v>2617.7839047311872</v>
+        <v>2517.0645316978089</v>
       </c>
       <c r="AK34" s="7">
         <f t="shared" si="43"/>
-        <v>2672.4878680315601</v>
+        <v>2552.7681785286318</v>
       </c>
       <c r="AL34" s="7">
         <f t="shared" si="43"/>
-        <v>2728.4889442956114</v>
+        <v>2590.1187288406195</v>
       </c>
       <c r="AM34" s="7">
         <f t="shared" si="43"/>
-        <v>2785.8213916710974</v>
+        <v>2629.1377448762269</v>
       </c>
       <c r="AN34" s="7">
         <f t="shared" si="43"/>
-        <v>2844.5204701454477</v>
+        <v>2669.8481495728611</v>
       </c>
       <c r="AO34" s="7">
         <f t="shared" si="43"/>
-        <v>2904.6224740024563</v>
+        <v>2712.2742480336719</v>
       </c>
     </row>
     <row r="35" spans="2:152" x14ac:dyDescent="0.3">
@@ -4548,43 +4712,43 @@
       </c>
       <c r="AF35" s="3">
         <f>AF34*0.25</f>
-        <v>509.73085649999962</v>
+        <v>504.49258649999979</v>
       </c>
       <c r="AG35" s="3">
         <f t="shared" ref="AG35:AO35" si="45">AG34*0.25</f>
-        <v>575.96323244999996</v>
+        <v>565.59145784999976</v>
       </c>
       <c r="AH35" s="3">
         <f t="shared" si="45"/>
-        <v>614.75329702725026</v>
+        <v>599.34911643825012</v>
       </c>
       <c r="AI35" s="3">
         <f t="shared" si="45"/>
-        <v>639.15611688929243</v>
+        <v>618.81706689869202</v>
       </c>
       <c r="AJ35" s="3">
         <f t="shared" si="45"/>
-        <v>654.44597618279681</v>
+        <v>629.26613292445222</v>
       </c>
       <c r="AK35" s="3">
         <f t="shared" si="45"/>
-        <v>668.12196700789002</v>
+        <v>638.19204463215794</v>
       </c>
       <c r="AL35" s="3">
         <f t="shared" si="45"/>
-        <v>682.12223607390285</v>
+        <v>647.52968221015487</v>
       </c>
       <c r="AM35" s="3">
         <f t="shared" si="45"/>
-        <v>696.45534791777436</v>
+        <v>657.28443621905672</v>
       </c>
       <c r="AN35" s="3">
         <f t="shared" si="45"/>
-        <v>711.13011753636192</v>
+        <v>667.46203739321527</v>
       </c>
       <c r="AO35" s="3">
         <f t="shared" si="45"/>
-        <v>726.15561850061408</v>
+        <v>678.06856200841798</v>
       </c>
     </row>
     <row r="36" spans="2:152" x14ac:dyDescent="0.3">
@@ -4686,43 +4850,43 @@
       </c>
       <c r="AF36" s="3">
         <f t="shared" ref="AF36:AO36" si="47">AF34*0.1</f>
-        <v>203.89234259999986</v>
+        <v>201.79703459999993</v>
       </c>
       <c r="AG36" s="3">
         <f t="shared" si="47"/>
-        <v>230.38529298</v>
+        <v>226.23658313999991</v>
       </c>
       <c r="AH36" s="3">
         <f t="shared" si="47"/>
-        <v>245.90131881090011</v>
+        <v>239.73964657530007</v>
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="47"/>
-        <v>255.66244675571699</v>
+        <v>247.52682675947682</v>
       </c>
       <c r="AJ36" s="3">
         <f t="shared" si="47"/>
-        <v>261.77839047311875</v>
+        <v>251.7064531697809</v>
       </c>
       <c r="AK36" s="3">
         <f t="shared" si="47"/>
-        <v>267.24878680315601</v>
+        <v>255.27681785286319</v>
       </c>
       <c r="AL36" s="3">
         <f t="shared" si="47"/>
-        <v>272.84889442956114</v>
+        <v>259.01187288406197</v>
       </c>
       <c r="AM36" s="3">
         <f t="shared" si="47"/>
-        <v>278.58213916710974</v>
+        <v>262.91377448762267</v>
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="47"/>
-        <v>284.4520470145448</v>
+        <v>266.98481495728612</v>
       </c>
       <c r="AO36" s="3">
         <f t="shared" si="47"/>
-        <v>290.46224740024564</v>
+        <v>271.22742480336723</v>
       </c>
     </row>
     <row r="37" spans="2:152" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -4827,487 +4991,487 @@
       </c>
       <c r="AF37" s="7">
         <f t="shared" si="51"/>
-        <v>1325.300226899999</v>
+        <v>1311.6807248999994</v>
       </c>
       <c r="AG37" s="7">
         <f t="shared" si="51"/>
-        <v>1497.50440437</v>
+        <v>1470.5377904099994</v>
       </c>
       <c r="AH37" s="7">
         <f t="shared" si="51"/>
-        <v>1598.3585722708506</v>
+        <v>1558.3077027394502</v>
       </c>
       <c r="AI37" s="7">
         <f t="shared" si="51"/>
-        <v>1661.8059039121604</v>
+        <v>1608.9243739365993</v>
       </c>
       <c r="AJ37" s="7">
         <f t="shared" si="51"/>
-        <v>1701.5595380752716</v>
+        <v>1636.0919456035758</v>
       </c>
       <c r="AK37" s="7">
         <f t="shared" si="51"/>
-        <v>1737.1171142205142</v>
+        <v>1659.2993160436108</v>
       </c>
       <c r="AL37" s="7">
         <f t="shared" si="51"/>
-        <v>1773.5178137921473</v>
+        <v>1683.5771737464024</v>
       </c>
       <c r="AM37" s="7">
         <f t="shared" si="51"/>
-        <v>1810.7839045862133</v>
+        <v>1708.9395341695474</v>
       </c>
       <c r="AN37" s="7">
         <f t="shared" si="51"/>
-        <v>1848.9383055945409</v>
+        <v>1735.4012972223597</v>
       </c>
       <c r="AO37" s="7">
         <f t="shared" si="51"/>
-        <v>1888.0046081015969</v>
+        <v>1762.9782612218867</v>
       </c>
       <c r="AP37" s="4">
         <f>AO37*(1+$AS$45)</f>
-        <v>1869.1245620205809</v>
+        <v>1745.3484786096678</v>
       </c>
       <c r="AQ37" s="4">
         <f t="shared" ref="AQ37:DB37" si="52">AP37*(1+$AS$45)</f>
-        <v>1850.4333164003751</v>
+        <v>1727.8949938235712</v>
       </c>
       <c r="AR37" s="4">
         <f t="shared" si="52"/>
-        <v>1831.9289832363713</v>
+        <v>1710.6160438853356</v>
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="52"/>
-        <v>1813.6096934040077</v>
+        <v>1693.5098834464823</v>
       </c>
       <c r="AT37" s="4">
         <f t="shared" si="52"/>
-        <v>1795.4735964699676</v>
+        <v>1676.5747846120175</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="52"/>
-        <v>1777.5188605052679</v>
+        <v>1659.8090367658974</v>
       </c>
       <c r="AV37" s="4">
         <f t="shared" si="52"/>
-        <v>1759.7436719002151</v>
+        <v>1643.2109463982383</v>
       </c>
       <c r="AW37" s="4">
         <f t="shared" si="52"/>
-        <v>1742.1462351812129</v>
+        <v>1626.7788369342559</v>
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="52"/>
-        <v>1724.7247728294008</v>
+        <v>1610.5110485649134</v>
       </c>
       <c r="AY37" s="4">
         <f t="shared" si="52"/>
-        <v>1707.4775251011067</v>
+        <v>1594.4059380792642</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="52"/>
-        <v>1690.4027498500957</v>
+        <v>1578.4618786984715</v>
       </c>
       <c r="BA37" s="4">
         <f t="shared" si="52"/>
-        <v>1673.4987223515948</v>
+        <v>1562.6772599114868</v>
       </c>
       <c r="BB37" s="4">
         <f t="shared" si="52"/>
-        <v>1656.7637351280789</v>
+        <v>1547.0504873123718</v>
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="52"/>
-        <v>1640.1960977767981</v>
+        <v>1531.5799824392482</v>
       </c>
       <c r="BD37" s="4">
         <f t="shared" si="52"/>
-        <v>1623.7941367990302</v>
+        <v>1516.2641826148556</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="52"/>
-        <v>1607.5561954310399</v>
+        <v>1501.1015407887071</v>
       </c>
       <c r="BF37" s="4">
         <f t="shared" si="52"/>
-        <v>1591.4806334767295</v>
+        <v>1486.0905253808201</v>
       </c>
       <c r="BG37" s="4">
         <f t="shared" si="52"/>
-        <v>1575.5658271419622</v>
+        <v>1471.2296201270119</v>
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="52"/>
-        <v>1559.8101688705426</v>
+        <v>1456.5173239257417</v>
       </c>
       <c r="BI37" s="4">
         <f t="shared" si="52"/>
-        <v>1544.2120671818373</v>
+        <v>1441.9521506864844</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="52"/>
-        <v>1528.7699465100188</v>
+        <v>1427.5326291796196</v>
       </c>
       <c r="BK37" s="4">
         <f t="shared" si="52"/>
-        <v>1513.4822470449187</v>
+        <v>1413.2573028878232</v>
       </c>
       <c r="BL37" s="4">
         <f t="shared" si="52"/>
-        <v>1498.3474245744694</v>
+        <v>1399.1247298589451</v>
       </c>
       <c r="BM37" s="4">
         <f t="shared" si="52"/>
-        <v>1483.3639503287247</v>
+        <v>1385.1334825603556</v>
       </c>
       <c r="BN37" s="4">
         <f t="shared" si="52"/>
-        <v>1468.5303108254375</v>
+        <v>1371.282147734752</v>
       </c>
       <c r="BO37" s="4">
         <f t="shared" si="52"/>
-        <v>1453.8450077171831</v>
+        <v>1357.5693262574046</v>
       </c>
       <c r="BP37" s="4">
         <f t="shared" si="52"/>
-        <v>1439.3065576400113</v>
+        <v>1343.9936329948305</v>
       </c>
       <c r="BQ37" s="4">
         <f t="shared" si="52"/>
-        <v>1424.9134920636111</v>
+        <v>1330.5536966648822</v>
       </c>
       <c r="BR37" s="4">
         <f t="shared" si="52"/>
-        <v>1410.6643571429749</v>
+        <v>1317.2481596982334</v>
       </c>
       <c r="BS37" s="4">
         <f t="shared" si="52"/>
-        <v>1396.5577135715453</v>
+        <v>1304.075678101251</v>
       </c>
       <c r="BT37" s="4">
         <f t="shared" si="52"/>
-        <v>1382.5921364358298</v>
+        <v>1291.0349213202385</v>
       </c>
       <c r="BU37" s="4">
         <f t="shared" si="52"/>
-        <v>1368.7662150714716</v>
+        <v>1278.1245721070361</v>
       </c>
       <c r="BV37" s="4">
         <f t="shared" si="52"/>
-        <v>1355.0785529207569</v>
+        <v>1265.3433263859658</v>
       </c>
       <c r="BW37" s="4">
         <f t="shared" si="52"/>
-        <v>1341.5277673915493</v>
+        <v>1252.6898931221062</v>
       </c>
       <c r="BX37" s="4">
         <f t="shared" si="52"/>
-        <v>1328.1124897176339</v>
+        <v>1240.1629941908852</v>
       </c>
       <c r="BY37" s="4">
         <f t="shared" si="52"/>
-        <v>1314.8313648204576</v>
+        <v>1227.7613642489764</v>
       </c>
       <c r="BZ37" s="4">
         <f t="shared" si="52"/>
-        <v>1301.683051172253</v>
+        <v>1215.4837506064866</v>
       </c>
       <c r="CA37" s="4">
         <f t="shared" si="52"/>
-        <v>1288.6662206605306</v>
+        <v>1203.3289131004217</v>
       </c>
       <c r="CB37" s="4">
         <f t="shared" si="52"/>
-        <v>1275.7795584539253</v>
+        <v>1191.2956239694174</v>
       </c>
       <c r="CC37" s="4">
         <f t="shared" si="52"/>
-        <v>1263.0217628693861</v>
+        <v>1179.3826677297232</v>
       </c>
       <c r="CD37" s="4">
         <f t="shared" si="52"/>
-        <v>1250.3915452406923</v>
+        <v>1167.588841052426</v>
       </c>
       <c r="CE37" s="4">
         <f t="shared" si="52"/>
-        <v>1237.8876297882853</v>
+        <v>1155.9129526419017</v>
       </c>
       <c r="CF37" s="4">
         <f t="shared" si="52"/>
-        <v>1225.5087534904023</v>
+        <v>1144.3538231154828</v>
       </c>
       <c r="CG37" s="4">
         <f t="shared" si="52"/>
-        <v>1213.2536659554983</v>
+        <v>1132.9102848843279</v>
       </c>
       <c r="CH37" s="4">
         <f t="shared" si="52"/>
-        <v>1201.1211292959433</v>
+        <v>1121.5811820354845</v>
       </c>
       <c r="CI37" s="4">
         <f t="shared" si="52"/>
-        <v>1189.1099180029839</v>
+        <v>1110.3653702151296</v>
       </c>
       <c r="CJ37" s="4">
         <f t="shared" si="52"/>
-        <v>1177.2188188229541</v>
+        <v>1099.2617165129782</v>
       </c>
       <c r="CK37" s="4">
         <f t="shared" si="52"/>
-        <v>1165.4466306347244</v>
+        <v>1088.2690993478484</v>
       </c>
       <c r="CL37" s="4">
         <f t="shared" si="52"/>
-        <v>1153.7921643283771</v>
+        <v>1077.3864083543699</v>
       </c>
       <c r="CM37" s="4">
         <f t="shared" si="52"/>
-        <v>1142.2542426850932</v>
+        <v>1066.6125442708262</v>
       </c>
       <c r="CN37" s="4">
         <f t="shared" si="52"/>
-        <v>1130.8317002582423</v>
+        <v>1055.9464188281179</v>
       </c>
       <c r="CO37" s="4">
         <f t="shared" si="52"/>
-        <v>1119.5233832556598</v>
+        <v>1045.3869546398366</v>
       </c>
       <c r="CP37" s="4">
         <f t="shared" si="52"/>
-        <v>1108.3281494231032</v>
+        <v>1034.9330850934382</v>
       </c>
       <c r="CQ37" s="4">
         <f t="shared" si="52"/>
-        <v>1097.2448679288723</v>
+        <v>1024.5837542425038</v>
       </c>
       <c r="CR37" s="4">
         <f t="shared" si="52"/>
-        <v>1086.2724192495834</v>
+        <v>1014.3379167000787</v>
       </c>
       <c r="CS37" s="4">
         <f t="shared" si="52"/>
-        <v>1075.4096950570877</v>
+        <v>1004.1945375330779</v>
       </c>
       <c r="CT37" s="4">
         <f t="shared" si="52"/>
-        <v>1064.6555981065169</v>
+        <v>994.15259215774711</v>
       </c>
       <c r="CU37" s="4">
         <f t="shared" si="52"/>
-        <v>1054.0090421254517</v>
+        <v>984.21106623616959</v>
       </c>
       <c r="CV37" s="4">
         <f t="shared" si="52"/>
-        <v>1043.4689517041973</v>
+        <v>974.36895557380785</v>
       </c>
       <c r="CW37" s="4">
         <f t="shared" si="52"/>
-        <v>1033.0342621871553</v>
+        <v>964.62526601806974</v>
       </c>
       <c r="CX37" s="4">
         <f t="shared" si="52"/>
-        <v>1022.7039195652837</v>
+        <v>954.97901335788902</v>
       </c>
       <c r="CY37" s="4">
         <f t="shared" si="52"/>
-        <v>1012.4768803696309</v>
+        <v>945.42922322431014</v>
       </c>
       <c r="CZ37" s="4">
         <f t="shared" si="52"/>
-        <v>1002.3521115659346</v>
+        <v>935.97493099206702</v>
       </c>
       <c r="DA37" s="4">
         <f t="shared" si="52"/>
-        <v>992.32859045027521</v>
+        <v>926.61518168214639</v>
       </c>
       <c r="DB37" s="4">
         <f t="shared" si="52"/>
-        <v>982.40530454577242</v>
+        <v>917.34902986532495</v>
       </c>
       <c r="DC37" s="4">
         <f t="shared" ref="DC37:EV37" si="53">DB37*(1+$AS$45)</f>
-        <v>972.58125150031469</v>
+        <v>908.17553956667166</v>
       </c>
       <c r="DD37" s="4">
         <f t="shared" si="53"/>
-        <v>962.85543898531159</v>
+        <v>899.09378417100493</v>
       </c>
       <c r="DE37" s="4">
         <f t="shared" si="53"/>
-        <v>953.2268845954585</v>
+        <v>890.10284632929483</v>
       </c>
       <c r="DF37" s="4">
         <f t="shared" si="53"/>
-        <v>943.6946157495039</v>
+        <v>881.20181786600187</v>
       </c>
       <c r="DG37" s="4">
         <f t="shared" si="53"/>
-        <v>934.25766959200882</v>
+        <v>872.38979968734179</v>
       </c>
       <c r="DH37" s="4">
         <f t="shared" si="53"/>
-        <v>924.91509289608871</v>
+        <v>863.66590169046833</v>
       </c>
       <c r="DI37" s="4">
         <f t="shared" si="53"/>
-        <v>915.66594196712776</v>
+        <v>855.02924267356366</v>
       </c>
       <c r="DJ37" s="4">
         <f t="shared" si="53"/>
-        <v>906.50928254745645</v>
+        <v>846.47895024682805</v>
       </c>
       <c r="DK37" s="4">
         <f t="shared" si="53"/>
-        <v>897.44418972198184</v>
+        <v>838.01416074435974</v>
       </c>
       <c r="DL37" s="4">
         <f t="shared" si="53"/>
-        <v>888.46974782476207</v>
+        <v>829.63401913691609</v>
       </c>
       <c r="DM37" s="4">
         <f t="shared" si="53"/>
-        <v>879.58505034651444</v>
+        <v>821.33767894554694</v>
       </c>
       <c r="DN37" s="4">
         <f t="shared" si="53"/>
-        <v>870.78919984304923</v>
+        <v>813.12430215609152</v>
       </c>
       <c r="DO37" s="4">
         <f t="shared" si="53"/>
-        <v>862.08130784461878</v>
+        <v>804.99305913453054</v>
       </c>
       <c r="DP37" s="4">
         <f t="shared" si="53"/>
-        <v>853.46049476617259</v>
+        <v>796.94312854318525</v>
       </c>
       <c r="DQ37" s="4">
         <f t="shared" si="53"/>
-        <v>844.92588981851088</v>
+        <v>788.97369725775343</v>
       </c>
       <c r="DR37" s="4">
         <f t="shared" si="53"/>
-        <v>836.47663092032576</v>
+        <v>781.08396028517586</v>
       </c>
       <c r="DS37" s="4">
         <f t="shared" si="53"/>
-        <v>828.11186461112254</v>
+        <v>773.27312068232413</v>
       </c>
       <c r="DT37" s="4">
         <f t="shared" si="53"/>
-        <v>819.83074596501126</v>
+        <v>765.54038947550089</v>
       </c>
       <c r="DU37" s="4">
         <f t="shared" si="53"/>
-        <v>811.63243850536116</v>
+        <v>757.88498558074582</v>
       </c>
       <c r="DV37" s="4">
         <f t="shared" si="53"/>
-        <v>803.51611412030752</v>
+        <v>750.30613572493837</v>
       </c>
       <c r="DW37" s="4">
         <f t="shared" si="53"/>
-        <v>795.48095297910447</v>
+        <v>742.80307436768896</v>
       </c>
       <c r="DX37" s="4">
         <f t="shared" si="53"/>
-        <v>787.52614344931339</v>
+        <v>735.37504362401205</v>
       </c>
       <c r="DY37" s="4">
         <f t="shared" si="53"/>
-        <v>779.65088201482024</v>
+        <v>728.0212931877719</v>
       </c>
       <c r="DZ37" s="4">
         <f t="shared" si="53"/>
-        <v>771.85437319467201</v>
+        <v>720.74108025589419</v>
       </c>
       <c r="EA37" s="4">
         <f t="shared" si="53"/>
-        <v>764.13582946272527</v>
+        <v>713.53366945333528</v>
       </c>
       <c r="EB37" s="4">
         <f t="shared" si="53"/>
-        <v>756.49447116809802</v>
+        <v>706.39833275880187</v>
       </c>
       <c r="EC37" s="4">
         <f t="shared" si="53"/>
-        <v>748.92952645641708</v>
+        <v>699.33434943121381</v>
       </c>
       <c r="ED37" s="4">
         <f t="shared" si="53"/>
-        <v>741.44023119185294</v>
+        <v>692.34100593690164</v>
       </c>
       <c r="EE37" s="4">
         <f t="shared" si="53"/>
-        <v>734.02582887993447</v>
+        <v>685.41759587753256</v>
       </c>
       <c r="EF37" s="4">
         <f t="shared" si="53"/>
-        <v>726.68557059113516</v>
+        <v>678.56341991875718</v>
       </c>
       <c r="EG37" s="4">
         <f t="shared" si="53"/>
-        <v>719.41871488522384</v>
+        <v>671.77778571956958</v>
       </c>
       <c r="EH37" s="4">
         <f t="shared" si="53"/>
-        <v>712.22452773637156</v>
+        <v>665.06000786237382</v>
       </c>
       <c r="EI37" s="4">
         <f t="shared" si="53"/>
-        <v>705.10228245900782</v>
+        <v>658.40940778375011</v>
       </c>
       <c r="EJ37" s="4">
         <f t="shared" si="53"/>
-        <v>698.05125963441776</v>
+        <v>651.82531370591255</v>
       </c>
       <c r="EK37" s="4">
         <f t="shared" si="53"/>
-        <v>691.07074703807359</v>
+        <v>645.30706056885344</v>
       </c>
       <c r="EL37" s="4">
         <f t="shared" si="53"/>
-        <v>684.16003956769282</v>
+        <v>638.85398996316485</v>
       </c>
       <c r="EM37" s="4">
         <f t="shared" si="53"/>
-        <v>677.31843917201593</v>
+        <v>632.46545006353324</v>
       </c>
       <c r="EN37" s="4">
         <f t="shared" si="53"/>
-        <v>670.54525478029575</v>
+        <v>626.14079556289789</v>
       </c>
       <c r="EO37" s="4">
         <f t="shared" si="53"/>
-        <v>663.83980223249273</v>
+        <v>619.87938760726888</v>
       </c>
       <c r="EP37" s="4">
         <f t="shared" si="53"/>
-        <v>657.20140421016777</v>
+        <v>613.68059373119615</v>
       </c>
       <c r="EQ37" s="4">
         <f t="shared" si="53"/>
-        <v>650.62939016806604</v>
+        <v>607.54378779388423</v>
       </c>
       <c r="ER37" s="4">
         <f t="shared" si="53"/>
-        <v>644.12309626638535</v>
+        <v>601.4683499159454</v>
       </c>
       <c r="ES37" s="4">
         <f t="shared" si="53"/>
-        <v>637.68186530372145</v>
+        <v>595.45366641678595</v>
       </c>
       <c r="ET37" s="4">
         <f t="shared" si="53"/>
-        <v>631.30504665068418</v>
+        <v>589.49912975261805</v>
       </c>
       <c r="EU37" s="4">
         <f t="shared" si="53"/>
-        <v>624.99199618417731</v>
+        <v>583.60413845509186</v>
       </c>
       <c r="EV37" s="4">
         <f t="shared" si="53"/>
-        <v>618.74207622233553</v>
+        <v>577.76809707054099</v>
       </c>
     </row>
     <row r="38" spans="2:152" x14ac:dyDescent="0.3">
@@ -5532,43 +5696,43 @@
       </c>
       <c r="AF39" s="9">
         <f t="shared" si="58"/>
-        <v>29.431495156562267</v>
+        <v>29.129041192538295</v>
       </c>
       <c r="AG39" s="9">
         <f t="shared" si="58"/>
-        <v>33.255705182544972</v>
+        <v>32.656846333777466</v>
       </c>
       <c r="AH39" s="9">
         <f t="shared" si="58"/>
-        <v>35.495415773281159</v>
+        <v>34.605989401275821</v>
       </c>
       <c r="AI39" s="9">
         <f t="shared" si="58"/>
-        <v>36.904417142175447</v>
+        <v>35.730054939742381</v>
       </c>
       <c r="AJ39" s="9">
         <f t="shared" si="58"/>
-        <v>37.787242684327595</v>
+        <v>36.333376540163798</v>
       </c>
       <c r="AK39" s="9">
         <f t="shared" si="58"/>
-        <v>38.576884615156878</v>
+        <v>36.848752299436171</v>
       </c>
       <c r="AL39" s="9">
         <f t="shared" si="58"/>
-        <v>39.385250139732342</v>
+        <v>37.387900816042688</v>
       </c>
       <c r="AM39" s="9">
         <f t="shared" si="58"/>
-        <v>40.212833768292548</v>
+        <v>37.95113333709854</v>
       </c>
       <c r="AN39" s="9">
         <f t="shared" si="58"/>
-        <v>41.060144472452606</v>
+        <v>38.538780751107254</v>
       </c>
       <c r="AO39" s="9">
         <f t="shared" si="58"/>
-        <v>41.927706153710787</v>
+        <v>39.151193897887779</v>
       </c>
     </row>
     <row r="41" spans="2:152" x14ac:dyDescent="0.3">
@@ -6141,50 +6305,50 @@
       </c>
       <c r="AF47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AG47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AH47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AI47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AJ47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AK47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AL47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000138E-2</v>
       </c>
       <c r="AM47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AN47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-2.9999999999999916E-2</v>
       </c>
       <c r="AO47" s="10">
         <f t="shared" si="87"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-3.0000000000000027E-2</v>
       </c>
       <c r="AR47" s="1" t="s">
         <v>60</v>
       </c>
       <c r="AS47" s="3">
         <f>NPV(AS46,AE37:EV37)</f>
-        <v>22902.047088771727</v>
+        <v>21748.004637832266</v>
       </c>
     </row>
     <row r="48" spans="2:152" x14ac:dyDescent="0.3">
@@ -6402,50 +6566,50 @@
       </c>
       <c r="AF49" s="11">
         <f t="shared" si="91"/>
-        <v>0.18116672876586692</v>
+        <v>0.17462490116111473</v>
       </c>
       <c r="AG49" s="11">
         <f t="shared" si="91"/>
-        <v>8.8108732466602557E-2</v>
+        <v>8.3141530674251785E-2</v>
       </c>
       <c r="AH49" s="11">
         <f t="shared" si="91"/>
-        <v>5.0902185538335809E-2</v>
+        <v>4.648068647009107E-2</v>
       </c>
       <c r="AI49" s="11">
         <f t="shared" si="91"/>
-        <v>3.1530440447478547E-2</v>
+        <v>2.7357189799299686E-2</v>
       </c>
       <c r="AJ49" s="11">
         <f t="shared" si="91"/>
-        <v>2.2581759873649077E-2</v>
+        <v>1.8581417996818894E-2</v>
       </c>
       <c r="AK49" s="11">
         <f t="shared" si="91"/>
-        <v>2.0851852946606408E-2</v>
+        <v>1.7064738323157025E-2</v>
       </c>
       <c r="AL49" s="11">
         <f t="shared" si="91"/>
-        <v>2.0887948125385636E-2</v>
+        <v>1.7329688229966278E-2</v>
       </c>
       <c r="AM49" s="11">
         <f t="shared" si="91"/>
-        <v>2.0924220581955533E-2</v>
+        <v>1.7585038368641115E-2</v>
       </c>
       <c r="AN49" s="11">
         <f t="shared" si="91"/>
-        <v>2.096067476613217E-2</v>
+        <v>1.7831088060434652E-2</v>
       </c>
       <c r="AO49" s="11">
         <f t="shared" si="91"/>
-        <v>2.0997315214217105E-2</v>
+        <v>1.8068137651806593E-2</v>
       </c>
       <c r="AR49" s="1" t="s">
         <v>62</v>
       </c>
       <c r="AS49" s="3">
         <f>AS47+AS48</f>
-        <v>21349.047088771727</v>
+        <v>20195.004637832266</v>
       </c>
     </row>
     <row r="50" spans="2:45" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -6537,50 +6701,50 @@
       </c>
       <c r="AF50" s="10">
         <f t="shared" si="97"/>
-        <v>0.18116672876586692</v>
+        <v>0.17462490116111473</v>
       </c>
       <c r="AG50" s="10">
         <f t="shared" si="97"/>
-        <v>8.8108732466602557E-2</v>
+        <v>8.3141530674251785E-2</v>
       </c>
       <c r="AH50" s="10">
         <f t="shared" si="97"/>
-        <v>5.0902185538335809E-2</v>
+        <v>4.648068647009107E-2</v>
       </c>
       <c r="AI50" s="10">
         <f t="shared" si="97"/>
-        <v>3.1530440447478547E-2</v>
+        <v>2.7357189799299686E-2</v>
       </c>
       <c r="AJ50" s="10">
         <f t="shared" si="97"/>
-        <v>2.2581759873649077E-2</v>
+        <v>1.8581417996818894E-2</v>
       </c>
       <c r="AK50" s="10">
         <f t="shared" si="97"/>
-        <v>2.0851852946606408E-2</v>
+        <v>1.7064738323157025E-2</v>
       </c>
       <c r="AL50" s="10">
         <f t="shared" si="97"/>
-        <v>2.0887948125385636E-2</v>
+        <v>1.7329688229966278E-2</v>
       </c>
       <c r="AM50" s="10">
         <f t="shared" si="97"/>
-        <v>2.0924220581955533E-2</v>
+        <v>1.7585038368641115E-2</v>
       </c>
       <c r="AN50" s="10">
         <f t="shared" si="97"/>
-        <v>2.096067476613217E-2</v>
+        <v>1.7831088060434652E-2</v>
       </c>
       <c r="AO50" s="10">
         <f t="shared" si="97"/>
-        <v>2.0997315214217105E-2</v>
+        <v>1.8068137651806593E-2</v>
       </c>
       <c r="AR50" s="1" t="s">
         <v>63</v>
       </c>
       <c r="AS50" s="12">
         <f>AS49/AO38</f>
-        <v>474.10719717458863</v>
+        <v>448.47889491077649</v>
       </c>
     </row>
     <row r="51" spans="2:45" x14ac:dyDescent="0.3">
@@ -6691,7 +6855,7 @@
       </c>
       <c r="AG51" s="10">
         <f t="shared" si="101"/>
-        <v>0.26999999999999996</v>
+        <v>0.26999999999999991</v>
       </c>
       <c r="AH51" s="10">
         <f t="shared" si="101"/>
@@ -6699,7 +6863,7 @@
       </c>
       <c r="AI51" s="10">
         <f t="shared" si="101"/>
-        <v>0.26999999999999996</v>
+        <v>0.26999999999999991</v>
       </c>
       <c r="AJ51" s="10">
         <f t="shared" si="101"/>
@@ -6707,11 +6871,11 @@
       </c>
       <c r="AK51" s="10">
         <f t="shared" si="101"/>
-        <v>0.27</v>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AL51" s="10">
         <f t="shared" si="101"/>
-        <v>0.26999999999999991</v>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AM51" s="10">
         <f t="shared" si="101"/>
@@ -6719,11 +6883,11 @@
       </c>
       <c r="AN51" s="10">
         <f t="shared" si="101"/>
-        <v>0.26999999999999996</v>
+        <v>0.26999999999999991</v>
       </c>
       <c r="AO51" s="10">
         <f t="shared" si="101"/>
-        <v>0.26999999999999996</v>
+        <v>0.27</v>
       </c>
       <c r="AR51" s="1" t="s">
         <v>64</v>
@@ -6831,7 +6995,7 @@
       <c r="AE52" s="10"/>
       <c r="AF52" s="10">
         <f t="shared" ref="AF52:AO52" si="104">(AF18-AF20)/AF18</f>
-        <v>0.54999999999999993</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AG52" s="10">
         <f t="shared" si="104"/>
@@ -6839,23 +7003,23 @@
       </c>
       <c r="AH52" s="10">
         <f t="shared" si="104"/>
-        <v>0.54999999999999993</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AI52" s="10">
         <f t="shared" si="104"/>
-        <v>0.55000000000000004</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="AJ52" s="10">
         <f t="shared" si="104"/>
-        <v>0.55000000000000004</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="AK52" s="10">
         <f t="shared" si="104"/>
-        <v>0.55000000000000004</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="AL52" s="10">
         <f t="shared" si="104"/>
-        <v>0.54999999999999993</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AM52" s="10">
         <f t="shared" si="104"/>
@@ -6863,7 +7027,7 @@
       </c>
       <c r="AN52" s="10">
         <f t="shared" si="104"/>
-        <v>0.54999999999999993</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AO52" s="10">
         <f t="shared" si="104"/>
@@ -6874,7 +7038,7 @@
       </c>
       <c r="AS52" s="11">
         <f>AS50/AS51-1</f>
-        <v>-0.700027081825632</v>
+        <v>-0.71624239486822117</v>
       </c>
     </row>
     <row r="53" spans="2:45" x14ac:dyDescent="0.3">
@@ -6995,15 +7159,15 @@
       </c>
       <c r="AK53" s="10">
         <f t="shared" si="107"/>
-        <v>0.72</v>
+        <v>0.71999999999999986</v>
       </c>
       <c r="AL53" s="10">
         <f t="shared" si="107"/>
-        <v>0.72</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="AM53" s="10">
         <f t="shared" si="107"/>
-        <v>0.72</v>
+        <v>0.71999999999999986</v>
       </c>
       <c r="AN53" s="10">
         <f t="shared" si="107"/>
@@ -7011,7 +7175,7 @@
       </c>
       <c r="AO53" s="10">
         <f t="shared" si="107"/>
-        <v>0.72000000000000008</v>
+        <v>0.72</v>
       </c>
       <c r="AR53" s="1" t="s">
         <v>66</v>
@@ -7321,43 +7485,43 @@
       </c>
       <c r="AF56" s="10">
         <f t="shared" si="120"/>
-        <v>0.15527230383704985</v>
+        <v>0.15463335193925978</v>
       </c>
       <c r="AG56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16034477855995866</v>
+        <v>0.15922840590510653</v>
       </c>
       <c r="AH56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16252579389642688</v>
+        <v>0.16097291197738595</v>
       </c>
       <c r="AI56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16372713986211609</v>
+        <v>0.16175368519609865</v>
       </c>
       <c r="AJ56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16399545190984499</v>
+        <v>0.16160293016426877</v>
       </c>
       <c r="AK56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16408390772876102</v>
+        <v>0.16129009485203932</v>
       </c>
       <c r="AL56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16417603144885487</v>
+        <v>0.16100475044245965</v>
       </c>
       <c r="AM56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16427183159525899</v>
+        <v>0.16074607982943268</v>
       </c>
       <c r="AN56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16437131670371244</v>
+        <v>0.16051326896849322</v>
       </c>
       <c r="AO56" s="10">
         <f t="shared" si="120"/>
-        <v>0.16447449532263658</v>
+        <v>0.16030550950182892</v>
       </c>
     </row>
     <row r="57" spans="2:45" x14ac:dyDescent="0.3">
@@ -7635,7 +7799,7 @@
       </c>
       <c r="AM58" s="10">
         <f t="shared" si="129"/>
-        <v>0.1</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="AN58" s="10">
         <f t="shared" si="129"/>
@@ -7643,7 +7807,7 @@
       </c>
       <c r="AO58" s="10">
         <f t="shared" si="129"/>
-        <v>0.1</v>
+        <v>0.10000000000000002</v>
       </c>
     </row>
     <row r="59" spans="2:45" x14ac:dyDescent="0.3">
@@ -7750,43 +7914,43 @@
       </c>
       <c r="AF59" s="10">
         <f t="shared" ref="AF59:AO59" si="134">AF37/AF18</f>
-        <v>9.4584082458692917E-2</v>
+        <v>9.4133438187051555E-2</v>
       </c>
       <c r="AG59" s="10">
         <f t="shared" si="134"/>
-        <v>9.8219924412346046E-2</v>
+        <v>9.7433155100151131E-2</v>
       </c>
       <c r="AH59" s="10">
         <f t="shared" si="134"/>
-        <v>9.9757006074729621E-2</v>
+        <v>9.8662604636237217E-2</v>
       </c>
       <c r="AI59" s="10">
         <f t="shared" si="134"/>
-        <v>0.10054661193535375</v>
+        <v>9.9154750332889327E-2</v>
       </c>
       <c r="AJ59" s="10">
         <f t="shared" si="134"/>
-        <v>0.10067838756957373</v>
+        <v>9.8989664415670711E-2</v>
       </c>
       <c r="AK59" s="10">
         <f t="shared" si="134"/>
-        <v>0.10068284507169548</v>
+        <v>9.870934768941772E-2</v>
       </c>
       <c r="AL59" s="10">
         <f t="shared" si="134"/>
-        <v>0.10068942444503172</v>
+        <v>9.8447537653380116E-2</v>
       </c>
       <c r="AM59" s="10">
         <f t="shared" si="134"/>
-        <v>0.10069813372386889</v>
+        <v>9.8203691456595604E-2</v>
       </c>
       <c r="AN59" s="10">
         <f t="shared" si="134"/>
-        <v>0.1007089810537752</v>
+        <v>9.7977267353900263E-2</v>
       </c>
       <c r="AO59" s="10">
         <f t="shared" si="134"/>
-        <v>0.10072197469523517</v>
+        <v>9.7767726543030523E-2</v>
       </c>
     </row>
     <row r="61" spans="2:45" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -7886,43 +8050,43 @@
       </c>
       <c r="AF67" s="3">
         <f t="shared" si="137"/>
-        <v>1325.300226899999</v>
+        <v>1311.6807248999994</v>
       </c>
       <c r="AG67" s="3">
         <f t="shared" si="137"/>
-        <v>1497.50440437</v>
+        <v>1470.5377904099994</v>
       </c>
       <c r="AH67" s="3">
         <f t="shared" si="137"/>
-        <v>1598.3585722708506</v>
+        <v>1558.3077027394502</v>
       </c>
       <c r="AI67" s="3">
         <f t="shared" si="137"/>
-        <v>1661.8059039121604</v>
+        <v>1608.9243739365993</v>
       </c>
       <c r="AJ67" s="3">
         <f t="shared" si="137"/>
-        <v>1701.5595380752716</v>
+        <v>1636.0919456035758</v>
       </c>
       <c r="AK67" s="3">
         <f t="shared" si="137"/>
-        <v>1737.1171142205142</v>
+        <v>1659.2993160436108</v>
       </c>
       <c r="AL67" s="3">
         <f t="shared" si="137"/>
-        <v>1773.5178137921473</v>
+        <v>1683.5771737464024</v>
       </c>
       <c r="AM67" s="3">
         <f t="shared" si="137"/>
-        <v>1810.7839045862133</v>
+        <v>1708.9395341695474</v>
       </c>
       <c r="AN67" s="3">
         <f t="shared" si="137"/>
-        <v>1848.9383055945409</v>
+        <v>1735.4012972223597</v>
       </c>
       <c r="AO67" s="3">
         <f t="shared" si="137"/>
-        <v>1888.0046081015969</v>
+        <v>1762.9782612218867</v>
       </c>
     </row>
     <row r="68" spans="2:41" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -7983,43 +8147,43 @@
       </c>
       <c r="AF68" s="7">
         <f t="shared" ref="AF68:AO68" si="138">AF67*1.1</f>
-        <v>1457.8302495899991</v>
+        <v>1442.8487973899994</v>
       </c>
       <c r="AG68" s="7">
         <f t="shared" si="138"/>
-        <v>1647.2548448070002</v>
+        <v>1617.5915694509995</v>
       </c>
       <c r="AH68" s="7">
         <f t="shared" si="138"/>
-        <v>1758.1944294979357</v>
+        <v>1714.1384730133952</v>
       </c>
       <c r="AI68" s="7">
         <f t="shared" si="138"/>
-        <v>1827.9864943033765</v>
+        <v>1769.8168113302593</v>
       </c>
       <c r="AJ68" s="7">
         <f t="shared" si="138"/>
-        <v>1871.7154918827989</v>
+        <v>1799.7011401639336</v>
       </c>
       <c r="AK68" s="7">
         <f t="shared" si="138"/>
-        <v>1910.8288256425658</v>
+        <v>1825.229247647972</v>
       </c>
       <c r="AL68" s="7">
         <f t="shared" si="138"/>
-        <v>1950.8695951713621</v>
+        <v>1851.9348911210427</v>
       </c>
       <c r="AM68" s="7">
         <f t="shared" si="138"/>
-        <v>1991.8622950448348</v>
+        <v>1879.8334875865023</v>
       </c>
       <c r="AN68" s="7">
         <f t="shared" si="138"/>
-        <v>2033.8321361539952</v>
+        <v>1908.9414269445958</v>
       </c>
       <c r="AO68" s="7">
         <f t="shared" si="138"/>
-        <v>2076.8050689117567</v>
+        <v>1939.2760873440754</v>
       </c>
     </row>
     <row r="69" spans="2:41" x14ac:dyDescent="0.3">
@@ -9002,43 +9166,43 @@
       </c>
       <c r="AF80" s="7">
         <f t="shared" si="150"/>
-        <v>2019.440249589999</v>
+        <v>2004.4587973899993</v>
       </c>
       <c r="AG80" s="7">
         <f t="shared" si="150"/>
-        <v>2265.0258448069999</v>
+        <v>2235.3625694509992</v>
       </c>
       <c r="AH80" s="7">
         <f t="shared" si="150"/>
-        <v>2404.1314794979357</v>
+        <v>2360.075523013395</v>
       </c>
       <c r="AI80" s="7">
         <f t="shared" si="150"/>
-        <v>2496.1673263033763</v>
+        <v>2437.9976433302591</v>
       </c>
       <c r="AJ80" s="7">
         <f t="shared" si="150"/>
-        <v>2555.3298338427985</v>
+        <v>2483.3154821239332</v>
       </c>
       <c r="AK80" s="7">
         <f t="shared" si="150"/>
-        <v>2602.3176184417657</v>
+        <v>2516.7180404471719</v>
       </c>
       <c r="AL80" s="7">
         <f t="shared" si="150"/>
-        <v>2649.810544226546</v>
+        <v>2550.8758401762266</v>
       </c>
       <c r="AM80" s="7">
         <f t="shared" si="150"/>
-        <v>2697.7666815211223</v>
+        <v>2585.7378740627901</v>
       </c>
       <c r="AN80" s="7">
         <f t="shared" si="150"/>
-        <v>2746.1376906438086</v>
+        <v>2621.2469814344095</v>
       </c>
       <c r="AO80" s="7">
         <f t="shared" si="150"/>
-        <v>2794.8681228037663</v>
+        <v>2657.3391412360852</v>
       </c>
     </row>
     <row r="81" spans="2:139" x14ac:dyDescent="0.3">
@@ -9204,436 +9368,439 @@
       </c>
       <c r="AF82" s="7">
         <f t="shared" si="157"/>
-        <v>875.0002495899987</v>
+        <v>860.01879738999901</v>
       </c>
       <c r="AG82" s="7">
         <f t="shared" si="157"/>
-        <v>1097.6970448069997</v>
+        <v>1068.033769450999</v>
       </c>
       <c r="AH82" s="7">
         <f t="shared" si="157"/>
-        <v>1213.4561034979356</v>
+        <v>1169.4001470133949</v>
       </c>
       <c r="AI82" s="7">
         <f t="shared" si="157"/>
-        <v>1341.2122115833761</v>
+        <v>1283.0425286102588</v>
       </c>
       <c r="AJ82" s="7">
         <f t="shared" si="157"/>
-        <v>1435.0233725643984</v>
+        <v>1363.0090208455331</v>
       </c>
       <c r="AK82" s="7">
         <f t="shared" si="157"/>
-        <v>1515.6203510017176</v>
+        <v>1430.0207730071238</v>
       </c>
       <c r="AL82" s="7">
         <f t="shared" si="157"/>
-        <v>1595.7141948096994</v>
+        <v>1496.77949075938</v>
       </c>
       <c r="AM82" s="7">
         <f t="shared" si="157"/>
-        <v>1675.2932225867812</v>
+        <v>1563.2644151284489</v>
       </c>
       <c r="AN82" s="7">
         <f t="shared" si="157"/>
-        <v>1754.3384354774976</v>
+        <v>1629.4477262680984</v>
       </c>
       <c r="AO82" s="7">
         <f t="shared" si="157"/>
-        <v>1832.8228452924448</v>
+        <v>1695.2938637247637</v>
       </c>
       <c r="AP82" s="4">
         <f>AO82*(1+AS45)</f>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AQ82" s="4">
         <f t="shared" ref="AQ82:DB82" si="158">AP82*(1+AT45)</f>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AR82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AS82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AT82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AU82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AV82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AW82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AX82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AY82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="AZ82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BA82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BB82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BC82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BD82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BE82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BF82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BG82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BH82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BI82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BJ82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BK82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BL82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BM82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BN82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BO82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BP82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BQ82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BR82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BS82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BT82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BU82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BV82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BW82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BX82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BY82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="BZ82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CA82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CB82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CC82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CD82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CE82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CF82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CG82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CH82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CI82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CJ82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CK82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CL82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CM82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CN82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CO82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CP82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CQ82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CR82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CS82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CT82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CU82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CV82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CW82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CX82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CY82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="CZ82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DA82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DB82" s="4">
         <f t="shared" si="158"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DC82" s="4">
         <f t="shared" ref="DC82:EI82" si="159">DB82*(1+DF45)</f>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DD82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DE82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DF82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DG82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DH82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DI82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DJ82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DK82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DL82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DM82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DN82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DO82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DP82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DQ82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DR82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DS82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DT82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DU82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DV82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DW82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DX82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DY82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="DZ82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="EA82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="EB82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="EC82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="ED82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="EE82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="EF82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="EG82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="EH82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
+        <v>1678.3409250875161</v>
       </c>
       <c r="EI82" s="4">
         <f t="shared" si="159"/>
-        <v>1814.4946168395202</v>
-      </c>
+        <v>1678.3409250875161</v>
+      </c>
+    </row>
+    <row r="83" spans="2:139" x14ac:dyDescent="0.3">
+      <c r="U83" s="3"/>
     </row>
     <row r="84" spans="2:139" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
@@ -9657,7 +9824,7 @@
       </c>
       <c r="AS84" s="3">
         <f>NPV(AS46,AE82:EI82)</f>
-        <v>21807.524052147131</v>
+        <v>20423.641471330273</v>
       </c>
     </row>
     <row r="85" spans="2:139" x14ac:dyDescent="0.3">
@@ -9684,7 +9851,7 @@
       </c>
       <c r="AS88" s="3">
         <f>AS84+AS85</f>
-        <v>20254.524052147131</v>
+        <v>18870.641471330273</v>
       </c>
     </row>
     <row r="89" spans="2:139" x14ac:dyDescent="0.3">
@@ -9693,7 +9860,7 @@
       </c>
       <c r="AS89" s="16">
         <f>AS88/AO38</f>
-        <v>449.80066738057144</v>
+        <v>419.06820944548684</v>
       </c>
     </row>
     <row r="90" spans="2:139" x14ac:dyDescent="0.3">
@@ -9718,7 +9885,7 @@
       </c>
       <c r="AS91" s="11">
         <f>AS89/AS90-1</f>
-        <v>-0.71540609466588334</v>
+        <v>-0.73485086400159005</v>
       </c>
     </row>
     <row r="92" spans="2:139" x14ac:dyDescent="0.3">
@@ -9791,6 +9958,1445 @@
       <c r="B101" s="4" t="s">
         <v>106</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8064C1D-58F6-4C98-80B4-9DFE4531D286}">
+  <dimension ref="B2:T47"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="8.88671875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2">
+        <v>2022</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>2023</v>
+      </c>
+      <c r="R2" s="2">
+        <v>2024</v>
+      </c>
+      <c r="S2" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B4" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2935</v>
+      </c>
+      <c r="J5" s="3">
+        <f>R5-I5-H5-G5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>74</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>2434</v>
+      </c>
+      <c r="R5" s="3">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="3">
+        <v>-138</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-794</v>
+      </c>
+      <c r="I6" s="3">
+        <v>-271</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" ref="J6:J7" si="0">R6-I6-H6-G6</f>
+        <v>-490</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>-85</v>
+      </c>
+      <c r="M6" s="3">
+        <v>-650</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>-1408</v>
+      </c>
+      <c r="R6" s="3">
+        <v>-1693</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1067</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2979</v>
+      </c>
+      <c r="I7" s="3">
+        <v>996</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" si="0"/>
+        <v>2065</v>
+      </c>
+      <c r="K7" s="3">
+        <v>391</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1047</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1165</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3">
+        <v>1564</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>6118</v>
+      </c>
+      <c r="R7" s="3">
+        <v>7107</v>
+      </c>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="2:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="7">
+        <f>SUM(G5:G7)</f>
+        <v>929</v>
+      </c>
+      <c r="H8" s="7">
+        <f>SUM(H5:H7)</f>
+        <v>2185</v>
+      </c>
+      <c r="I8" s="7">
+        <f>SUM(I5:I7)</f>
+        <v>3660</v>
+      </c>
+      <c r="J8" s="7">
+        <f>SUM(J5:J7)</f>
+        <v>1575</v>
+      </c>
+      <c r="K8" s="7">
+        <f>SUM(K5:K7)</f>
+        <v>465</v>
+      </c>
+      <c r="L8" s="7">
+        <f>SUM(L5:L7)</f>
+        <v>962</v>
+      </c>
+      <c r="M8" s="7">
+        <f>SUM(M5:M7)</f>
+        <v>515</v>
+      </c>
+      <c r="P8" s="7">
+        <f>SUM(P5:P7)</f>
+        <v>1564</v>
+      </c>
+      <c r="Q8" s="7">
+        <f>SUM(Q5:Q7)</f>
+        <v>7144</v>
+      </c>
+      <c r="R8" s="7">
+        <f>SUM(R5:R7)</f>
+        <v>8349</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3297</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3266</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2365</v>
+      </c>
+      <c r="I9" s="3">
+        <v>5028</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5361</v>
+      </c>
+      <c r="K9" s="3">
+        <v>4539</v>
+      </c>
+      <c r="L9" s="3">
+        <v>4454</v>
+      </c>
+      <c r="M9" s="3">
+        <v>3877</v>
+      </c>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3">
+        <v>2304</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>3297</v>
+      </c>
+      <c r="R9" s="3">
+        <v>5361</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="3">
+        <v>13071</v>
+      </c>
+      <c r="G10" s="3">
+        <v>13600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>15783</v>
+      </c>
+      <c r="I10" s="3">
+        <v>15615</v>
+      </c>
+      <c r="J10" s="3">
+        <v>16838</v>
+      </c>
+      <c r="K10" s="3">
+        <v>16165</v>
+      </c>
+      <c r="L10" s="3">
+        <v>16003</v>
+      </c>
+      <c r="M10" s="3">
+        <v>15836</v>
+      </c>
+      <c r="P10" s="3">
+        <v>9650</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>13071</v>
+      </c>
+      <c r="R10" s="3">
+        <v>16838</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="7">
+        <f>SUM(F9:F10)</f>
+        <v>16368</v>
+      </c>
+      <c r="G11" s="7">
+        <f>SUM(G9:G10)</f>
+        <v>16866</v>
+      </c>
+      <c r="H11" s="7">
+        <f>SUM(H9:H10)</f>
+        <v>18148</v>
+      </c>
+      <c r="I11" s="7">
+        <f>SUM(I9:I10)</f>
+        <v>20643</v>
+      </c>
+      <c r="J11" s="7">
+        <f>SUM(J9:J10)</f>
+        <v>22199</v>
+      </c>
+      <c r="K11" s="7">
+        <f>SUM(K9:K10)</f>
+        <v>20704</v>
+      </c>
+      <c r="L11" s="7">
+        <f>SUM(L9:L10)</f>
+        <v>20457</v>
+      </c>
+      <c r="M11" s="7">
+        <f>SUM(M9:M10)</f>
+        <v>19713</v>
+      </c>
+      <c r="P11" s="7">
+        <f>SUM(P9:P10)</f>
+        <v>11954</v>
+      </c>
+      <c r="Q11" s="7">
+        <f>SUM(Q9:Q10)</f>
+        <v>16368</v>
+      </c>
+      <c r="R11" s="7">
+        <f>SUM(R9:R10)</f>
+        <v>22199</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="3">
+        <f>F10+G7</f>
+        <v>14138</v>
+      </c>
+      <c r="H12" s="3">
+        <f>G10+H7</f>
+        <v>16579</v>
+      </c>
+      <c r="I12" s="3">
+        <f>H10+I7</f>
+        <v>16779</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" ref="J12:L12" si="1">I10+J7</f>
+        <v>17680</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="1"/>
+        <v>17229</v>
+      </c>
+      <c r="L12" s="3">
+        <f>K10+L7</f>
+        <v>17212</v>
+      </c>
+      <c r="M12" s="3">
+        <f>L10+M7</f>
+        <v>17168</v>
+      </c>
+      <c r="Q12" s="3">
+        <f>P10+Q7</f>
+        <v>15768</v>
+      </c>
+      <c r="R12" s="3">
+        <f>Q10+R7</f>
+        <v>20178</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="3">
+        <f>G12-G10</f>
+        <v>538</v>
+      </c>
+      <c r="H13" s="3">
+        <f>H12-H10</f>
+        <v>796</v>
+      </c>
+      <c r="I13" s="3">
+        <f>I12-I10</f>
+        <v>1164</v>
+      </c>
+      <c r="J13" s="3">
+        <f t="shared" ref="J13:K13" si="2">J12-J10</f>
+        <v>842</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="2"/>
+        <v>1064</v>
+      </c>
+      <c r="L13" s="3">
+        <f>L12-L10</f>
+        <v>1209</v>
+      </c>
+      <c r="M13" s="3">
+        <f>M12-M10</f>
+        <v>1332</v>
+      </c>
+      <c r="Q13" s="3">
+        <f>Q12-Q10</f>
+        <v>2697</v>
+      </c>
+      <c r="R13" s="3">
+        <f>R12-R10</f>
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B14" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" ref="K14:L14" si="3">K13/G13-1</f>
+        <v>0.97769516728624528</v>
+      </c>
+      <c r="L14" s="10">
+        <f t="shared" si="3"/>
+        <v>0.51884422110552775</v>
+      </c>
+      <c r="M14" s="10">
+        <f>M13/I13-1</f>
+        <v>0.14432989690721643</v>
+      </c>
+      <c r="R14" s="10">
+        <f>R13/Q13-1</f>
+        <v>0.23841305153874681</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="21"/>
+      <c r="R15" s="10"/>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B16" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>7121</v>
+      </c>
+      <c r="I17" s="3">
+        <v>445</v>
+      </c>
+      <c r="J17" s="3">
+        <f>R17-I17-H17-G17</f>
+        <v>44</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>433</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P17" s="3">
+        <v>350</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>4927</v>
+      </c>
+      <c r="R17" s="3">
+        <v>7610</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-306</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1008</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-184</v>
+      </c>
+      <c r="J18" s="3">
+        <f t="shared" ref="J18:J19" si="4">R18-I18-H18-G18</f>
+        <v>-41</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-55</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-167</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-241</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-1396</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-1539</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1141</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1880</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1073</v>
+      </c>
+      <c r="J19" s="3">
+        <f t="shared" si="4"/>
+        <v>2143</v>
+      </c>
+      <c r="K19" s="3">
+        <v>881</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1059</v>
+      </c>
+      <c r="M19" s="3">
+        <v>1402</v>
+      </c>
+      <c r="P19" s="3">
+        <v>2909</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>4706</v>
+      </c>
+      <c r="R19" s="3">
+        <v>6237</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="7">
+        <f>SUM(G17:G19)</f>
+        <v>835</v>
+      </c>
+      <c r="H20" s="7">
+        <f>SUM(H17:H19)</f>
+        <v>7993</v>
+      </c>
+      <c r="I20" s="7">
+        <f>SUM(I17:I19)</f>
+        <v>1334</v>
+      </c>
+      <c r="J20" s="7">
+        <f>SUM(J17:J19)</f>
+        <v>2146</v>
+      </c>
+      <c r="K20" s="7">
+        <f>SUM(K17:K19)</f>
+        <v>826</v>
+      </c>
+      <c r="L20" s="7">
+        <f>SUM(L17:L19)</f>
+        <v>1325</v>
+      </c>
+      <c r="M20" s="7">
+        <f>SUM(M17:M19)</f>
+        <v>2661</v>
+      </c>
+      <c r="P20" s="7">
+        <f>SUM(P17:P19)</f>
+        <v>3259</v>
+      </c>
+      <c r="Q20" s="7">
+        <f>SUM(Q17:Q19)</f>
+        <v>8237</v>
+      </c>
+      <c r="R20" s="7">
+        <f>SUM(R17:R19)</f>
+        <v>12308</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="3">
+        <v>4460</v>
+      </c>
+      <c r="G21" s="3">
+        <v>4155</v>
+      </c>
+      <c r="H21" s="3">
+        <v>10268</v>
+      </c>
+      <c r="I21" s="3">
+        <v>10460</v>
+      </c>
+      <c r="J21" s="3">
+        <v>10529</v>
+      </c>
+      <c r="K21" s="3">
+        <v>10472</v>
+      </c>
+      <c r="L21" s="3">
+        <v>11136</v>
+      </c>
+      <c r="M21" s="3">
+        <v>11995</v>
+      </c>
+      <c r="P21" s="3">
+        <v>949</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>4460</v>
+      </c>
+      <c r="R21" s="3">
+        <v>10529</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="3">
+        <v>7121</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7452</v>
+      </c>
+      <c r="H22" s="3">
+        <v>8696</v>
+      </c>
+      <c r="I22" s="3">
+        <v>9052</v>
+      </c>
+      <c r="J22" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>10410</v>
+      </c>
+      <c r="L22" s="3">
+        <v>10457</v>
+      </c>
+      <c r="M22" s="3">
+        <v>11236</v>
+      </c>
+      <c r="P22" s="3">
+        <v>3934</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>7121</v>
+      </c>
+      <c r="R22" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="7">
+        <f>SUM(F21:F22)</f>
+        <v>11581</v>
+      </c>
+      <c r="G23" s="7">
+        <f>SUM(G21:G22)</f>
+        <v>11607</v>
+      </c>
+      <c r="H23" s="7">
+        <f>SUM(H21:H22)</f>
+        <v>18964</v>
+      </c>
+      <c r="I23" s="7">
+        <f>SUM(I21:I22)</f>
+        <v>19512</v>
+      </c>
+      <c r="J23" s="7">
+        <f>SUM(J21:J22)</f>
+        <v>20529</v>
+      </c>
+      <c r="K23" s="7">
+        <f>SUM(K21:K22)</f>
+        <v>20882</v>
+      </c>
+      <c r="L23" s="7">
+        <f>SUM(L21:L22)</f>
+        <v>21593</v>
+      </c>
+      <c r="M23" s="7">
+        <f>SUM(M21:M22)</f>
+        <v>23231</v>
+      </c>
+      <c r="P23" s="7">
+        <f>SUM(P21:P22)</f>
+        <v>4883</v>
+      </c>
+      <c r="Q23" s="7">
+        <f>SUM(Q21:Q22)</f>
+        <v>11581</v>
+      </c>
+      <c r="R23" s="7">
+        <f>SUM(R21:R22)</f>
+        <v>20529</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="3">
+        <f>F22+G19</f>
+        <v>8262</v>
+      </c>
+      <c r="H24" s="3">
+        <f>G22+H19</f>
+        <v>9332</v>
+      </c>
+      <c r="I24" s="3">
+        <f>H22+I19</f>
+        <v>9769</v>
+      </c>
+      <c r="J24" s="3">
+        <f t="shared" ref="J24:L24" si="5">I22+J19</f>
+        <v>11195</v>
+      </c>
+      <c r="K24" s="3">
+        <f t="shared" si="5"/>
+        <v>10881</v>
+      </c>
+      <c r="L24" s="3">
+        <f>K22+L19</f>
+        <v>11469</v>
+      </c>
+      <c r="M24" s="3">
+        <f>L22+M19</f>
+        <v>11859</v>
+      </c>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="3">
+        <f>G24-G22</f>
+        <v>810</v>
+      </c>
+      <c r="H25" s="3">
+        <f>H24-H22</f>
+        <v>636</v>
+      </c>
+      <c r="I25" s="3">
+        <f>I24-I22</f>
+        <v>717</v>
+      </c>
+      <c r="J25" s="3">
+        <f t="shared" ref="J25" si="6">J24-J22</f>
+        <v>1195</v>
+      </c>
+      <c r="K25" s="3">
+        <f t="shared" ref="K25" si="7">K24-K22</f>
+        <v>471</v>
+      </c>
+      <c r="L25" s="3">
+        <f>L24-L22</f>
+        <v>1012</v>
+      </c>
+      <c r="M25" s="3">
+        <f>M24-M22</f>
+        <v>623</v>
+      </c>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="K26" s="10">
+        <f t="shared" ref="K26" si="8">K25/G25-1</f>
+        <v>-0.41851851851851851</v>
+      </c>
+      <c r="L26" s="10">
+        <f t="shared" ref="L26" si="9">L25/H25-1</f>
+        <v>0.59119496855345921</v>
+      </c>
+      <c r="M26" s="10">
+        <f>M25/I25-1</f>
+        <v>-0.13110181311018132</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B27" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>357</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <f>R28-I28-H28-G28</f>
+        <v>617</v>
+      </c>
+      <c r="K28" s="3">
+        <v>9274</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-123</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <f t="shared" ref="J29:J30" si="10">R29-I29-H29-G29</f>
+        <v>-383</v>
+      </c>
+      <c r="K29" s="3">
+        <v>-1940</v>
+      </c>
+      <c r="L29" s="3">
+        <v>-3</v>
+      </c>
+      <c r="M29" s="3">
+        <v>-4</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>-506</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1812</v>
+      </c>
+      <c r="H30" s="3">
+        <v>974</v>
+      </c>
+      <c r="I30" s="3">
+        <v>482</v>
+      </c>
+      <c r="J30" s="3">
+        <f t="shared" si="10"/>
+        <v>1328</v>
+      </c>
+      <c r="K30" s="3">
+        <v>2357</v>
+      </c>
+      <c r="L30" s="3">
+        <v>297</v>
+      </c>
+      <c r="M30" s="3">
+        <v>299</v>
+      </c>
+      <c r="P30" s="3">
+        <v>1724</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>2183</v>
+      </c>
+      <c r="R30" s="3">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="7">
+        <f>SUM(G28:G30)</f>
+        <v>1812</v>
+      </c>
+      <c r="H31" s="7">
+        <f>SUM(H28:H30)</f>
+        <v>1208</v>
+      </c>
+      <c r="I31" s="7">
+        <f>SUM(I28:I30)</f>
+        <v>482</v>
+      </c>
+      <c r="J31" s="7">
+        <f>SUM(J28:J30)</f>
+        <v>1562</v>
+      </c>
+      <c r="K31" s="7">
+        <f>SUM(K28:K30)</f>
+        <v>9691</v>
+      </c>
+      <c r="L31" s="7">
+        <f>SUM(L28:L30)</f>
+        <v>294</v>
+      </c>
+      <c r="M31" s="7">
+        <f>SUM(M28:M30)</f>
+        <v>295</v>
+      </c>
+      <c r="P31" s="7">
+        <f>SUM(P28:P30)</f>
+        <v>1724</v>
+      </c>
+      <c r="Q31" s="7">
+        <f>SUM(Q28:Q30)</f>
+        <v>2183</v>
+      </c>
+      <c r="R31" s="7">
+        <f>SUM(R28:R30)</f>
+        <v>5064</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" s="3">
+        <v>174</v>
+      </c>
+      <c r="G32" s="3">
+        <v>174</v>
+      </c>
+      <c r="H32" s="3">
+        <v>408</v>
+      </c>
+      <c r="I32" s="3">
+        <v>408</v>
+      </c>
+      <c r="J32" s="3">
+        <v>643</v>
+      </c>
+      <c r="K32" s="3">
+        <v>7976</v>
+      </c>
+      <c r="L32" s="3">
+        <v>8117</v>
+      </c>
+      <c r="M32" s="3">
+        <v>8113</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3">
+        <v>174</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>174</v>
+      </c>
+      <c r="R32" s="3">
+        <v>643</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4113</v>
+      </c>
+      <c r="G33" s="3">
+        <v>5576</v>
+      </c>
+      <c r="H33" s="3">
+        <v>6201</v>
+      </c>
+      <c r="I33" s="3">
+        <v>6298</v>
+      </c>
+      <c r="J33" s="3">
+        <v>6875</v>
+      </c>
+      <c r="K33" s="3">
+        <v>9037</v>
+      </c>
+      <c r="L33" s="3">
+        <v>8814</v>
+      </c>
+      <c r="M33" s="3">
+        <v>8547</v>
+      </c>
+      <c r="P33" s="3">
+        <v>3364</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>4113</v>
+      </c>
+      <c r="R33" s="3">
+        <v>6875</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="7">
+        <f>SUM(F32:F33)</f>
+        <v>4287</v>
+      </c>
+      <c r="G34" s="7">
+        <f>SUM(G32:G33)</f>
+        <v>5750</v>
+      </c>
+      <c r="H34" s="7">
+        <f>SUM(H32:H33)</f>
+        <v>6609</v>
+      </c>
+      <c r="I34" s="7">
+        <f>SUM(I32:I33)</f>
+        <v>6706</v>
+      </c>
+      <c r="J34" s="7">
+        <f>SUM(J32:J33)</f>
+        <v>7518</v>
+      </c>
+      <c r="K34" s="7">
+        <f>SUM(K32:K33)</f>
+        <v>17013</v>
+      </c>
+      <c r="L34" s="7">
+        <f>SUM(L32:L33)</f>
+        <v>16931</v>
+      </c>
+      <c r="M34" s="7">
+        <f>SUM(M32:M33)</f>
+        <v>16660</v>
+      </c>
+      <c r="P34" s="7">
+        <f>SUM(P32:P33)</f>
+        <v>3538</v>
+      </c>
+      <c r="Q34" s="7">
+        <f>SUM(Q32:Q33)</f>
+        <v>4287</v>
+      </c>
+      <c r="R34" s="7">
+        <f>SUM(R32:R33)</f>
+        <v>7518</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" s="3">
+        <f>F33+G30</f>
+        <v>5925</v>
+      </c>
+      <c r="H35" s="3">
+        <f>G33+H30</f>
+        <v>6550</v>
+      </c>
+      <c r="I35" s="3">
+        <f>H33+I30</f>
+        <v>6683</v>
+      </c>
+      <c r="J35" s="3">
+        <f t="shared" ref="J35:L35" si="11">I33+J30</f>
+        <v>7626</v>
+      </c>
+      <c r="K35" s="3">
+        <f t="shared" si="11"/>
+        <v>9232</v>
+      </c>
+      <c r="L35" s="3">
+        <f>K33+L30</f>
+        <v>9334</v>
+      </c>
+      <c r="M35" s="3">
+        <f>L33+M30</f>
+        <v>9113</v>
+      </c>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+    </row>
+    <row r="36" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G36" s="3">
+        <f>G35-G33</f>
+        <v>349</v>
+      </c>
+      <c r="H36" s="3">
+        <f>H35-H33</f>
+        <v>349</v>
+      </c>
+      <c r="I36" s="3">
+        <f>I35-I33</f>
+        <v>385</v>
+      </c>
+      <c r="J36" s="3">
+        <f t="shared" ref="J36" si="12">J35-J33</f>
+        <v>751</v>
+      </c>
+      <c r="K36" s="3">
+        <f t="shared" ref="K36" si="13">K35-K33</f>
+        <v>195</v>
+      </c>
+      <c r="L36" s="3">
+        <f>L35-L33</f>
+        <v>520</v>
+      </c>
+      <c r="M36" s="3">
+        <f>M35-M33</f>
+        <v>566</v>
+      </c>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="K37" s="10">
+        <f t="shared" ref="K37" si="14">K36/G36-1</f>
+        <v>-0.44126074498567336</v>
+      </c>
+      <c r="L37" s="10">
+        <f t="shared" ref="L37" si="15">L36/H36-1</f>
+        <v>0.48997134670487097</v>
+      </c>
+      <c r="M37" s="10">
+        <f>M36/I36-1</f>
+        <v>0.47012987012987018</v>
+      </c>
+    </row>
+    <row r="38" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B38" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G39" s="3">
+        <v>620</v>
+      </c>
+      <c r="H39" s="3">
+        <v>737</v>
+      </c>
+      <c r="I39" s="3">
+        <v>763</v>
+      </c>
+      <c r="K39" s="3">
+        <v>325</v>
+      </c>
+      <c r="L39" s="3">
+        <v>664</v>
+      </c>
+      <c r="M39" s="3">
+        <v>555</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>3480</v>
+      </c>
+      <c r="R39" s="3">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="7">
+        <v>8381</v>
+      </c>
+      <c r="G40" s="7">
+        <v>8461</v>
+      </c>
+      <c r="H40" s="7">
+        <v>7938</v>
+      </c>
+      <c r="I40" s="7">
+        <v>8060</v>
+      </c>
+      <c r="J40" s="7">
+        <v>7712</v>
+      </c>
+      <c r="K40" s="7">
+        <v>6994</v>
+      </c>
+      <c r="L40" s="7">
+        <v>7192</v>
+      </c>
+      <c r="M40" s="7">
+        <v>7143</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>8381</v>
+      </c>
+      <c r="R40" s="7">
+        <v>7712</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H42" s="3">
+        <f>H9+H21+H32+H38</f>
+        <v>13041</v>
+      </c>
+      <c r="I42" s="3">
+        <f>I9+I21+I32+I38</f>
+        <v>15896</v>
+      </c>
+      <c r="L42" s="3">
+        <f>L9+L21+L32+L38</f>
+        <v>23707</v>
+      </c>
+      <c r="M42" s="3">
+        <f>M9+M21+M32+M38</f>
+        <v>23985</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="3">
+        <f>H10+H22+H33+H39</f>
+        <v>31417</v>
+      </c>
+      <c r="I43" s="3">
+        <f>I10+I22+I33+I39</f>
+        <v>31728</v>
+      </c>
+      <c r="L43" s="3">
+        <f>L10+L22+L33+L39</f>
+        <v>35938</v>
+      </c>
+      <c r="M43" s="3">
+        <f>M10+M22+M33+M39</f>
+        <v>36174</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="7">
+        <f>SUM(H42:H43)+H40</f>
+        <v>52396</v>
+      </c>
+      <c r="I44" s="7">
+        <f>SUM(I42:I43)+I40</f>
+        <v>55684</v>
+      </c>
+      <c r="L44" s="7">
+        <f>SUM(L42:L43)+L40</f>
+        <v>66837</v>
+      </c>
+      <c r="M44" s="7">
+        <f>SUM(M42:M43)+M40</f>
+        <v>67302</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H45" s="3">
+        <f>H46-H44</f>
+        <v>-3756</v>
+      </c>
+      <c r="I45" s="3">
+        <f>I46-I44</f>
+        <v>-3778</v>
+      </c>
+      <c r="L45" s="3">
+        <f>L46-L44</f>
+        <v>-3672</v>
+      </c>
+      <c r="M45" s="3">
+        <f>M46-M44</f>
+        <v>-3499</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H46" s="7">
+        <f>Model!P11</f>
+        <v>48640</v>
+      </c>
+      <c r="I46" s="7">
+        <f>Model!Q11</f>
+        <v>51906</v>
+      </c>
+      <c r="L46" s="7">
+        <f>Model!T11</f>
+        <v>63165</v>
+      </c>
+      <c r="M46" s="7">
+        <f>Model!U11</f>
+        <v>63803</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="M47" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
